--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,126 +486,152 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>行动ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>行动名称</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>行动描述</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>行动类型</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>消耗天数</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>随机权重</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>是否可重复</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>前置条件</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>载荷类型</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>载荷数值</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>载荷参数</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>关联配置ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>ActionType</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>act_cook</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>开火做菜</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>进行一场美食挑战，达标得奖励。</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" t="n">
-        <v>120</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>act_feast</t>
+          <t>act_cook</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>大宴宾客</t>
+          <t>开火做菜</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>更耗时的硬仗，目标更高、奖励更厚。</t>
+          <t>进行一场美食挑战，达标得奖励。</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -614,10 +640,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -627,7 +653,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -636,29 +662,29 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>act_market</t>
+          <t>act_feast</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>逛集市</t>
+          <t>大宴宾客</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>花点时间逛集市采购。</t>
+          <t>更耗时的硬仗，目标更高、奖励更厚。</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -668,30 +694,26 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>ev_market</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>act_tasting</t>
+          <t>act_market</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>办试菜会</t>
+          <t>逛集市</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>举办试菜会，给菜谱加菜。</t>
+          <t>花点时间逛集市采购。</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -703,7 +725,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -718,7 +740,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ev_tasting</t>
+          <t>ev_market</t>
         </is>
       </c>
     </row>
@@ -726,17 +748,17 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>act_rest</t>
+          <t>act_tasting</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>歇业一天</t>
+          <t>办试菜会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短暂休息，降低下一关要求分。</t>
+          <t>举办试菜会，给菜谱加菜。</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -748,7 +770,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -763,7 +785,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>ev_rest</t>
+          <t>ev_tasting</t>
         </is>
       </c>
     </row>
@@ -771,17 +793,17 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>act_recruit</t>
+          <t>act_rest</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>招募帮厨</t>
+          <t>歇业一天</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>招募帮厨，获得一件被动道具。</t>
+          <t>短暂休息，降低下一关要求分。</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -790,14 +812,14 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -808,7 +830,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>ev_recruit</t>
+          <t>ev_rest</t>
         </is>
       </c>
     </row>
@@ -816,17 +838,17 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>act_study</t>
+          <t>act_recruit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>钻研食谱</t>
+          <t>招募帮厨</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>钻研食谱，提升一道菜。</t>
+          <t>招募帮厨，获得一件被动道具。</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -838,11 +860,11 @@
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -853,7 +875,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>ev_upgrade</t>
+          <t>ev_recruit</t>
         </is>
       </c>
     </row>
@@ -861,26 +883,26 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>act_gamble</t>
+          <t>act_study</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>豪赌一桌</t>
+          <t>钻研食谱</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>高风险高回报，可能大赚也可能亏本。</t>
+          <t>钻研食谱，提升一道菜。</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -891,44 +913,44 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Gamble</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ev_upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>act_tip</t>
+          <t>act_gamble</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>收小费</t>
+          <t>豪赌一桌</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>客人很满意，留下一笔小费。</t>
+          <t>高风险高回报，可能大赚也可能亏本。</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Reward</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -938,11 +960,11 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>GainGold</t>
+          <t>Gamble</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
@@ -951,29 +973,29 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>act_shop</t>
+          <t>act_tip</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>逛逛商店</t>
+          <t>收小费</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>去食材店转转，买卖道具。</t>
+          <t>客人很满意，留下一笔小费。</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shop</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -981,12 +1003,57 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>GainGold</t>
+        </is>
+      </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>act_shop</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>逛逛商店</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>去食材店转转，买卖道具。</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>40</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="action" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="action_group" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="action_group_member" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="action_schedule_rule" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +485,31 @@
           <t>linkId</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>foodDifficulty</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>rewardKind</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>rewardPackageId</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>goldCurveId</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>hiddenScoreBonus</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -511,7 +539,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>消耗天数</t>
+          <t>默认消耗天数</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -547,6 +575,31 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>关联配置ID</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>美食难度(Normal/Hard/Boss)</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>美食奖励外观类型</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>美食奖励包ID</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>金币曲线ID</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>行动隐藏分加成</t>
         </is>
       </c>
     </row>
@@ -616,22 +669,46 @@
           <t>string</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>RewardKind</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>act_cook</t>
+          <t>act_food_gold</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>开火做菜</t>
+          <t>街边小吃</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>进行一场美食挑战，达标得奖励。</t>
+          <t>普通美食挑战，主要奖励金币。</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -640,7 +717,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>120</v>
@@ -650,410 +727,1946 @@
           <t>true</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>reward_food_gold</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>gold_normal</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
+          <t>act_food_fragment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>胃口扩张</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>普通美食挑战，主要奖励胃部碎片。</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>90</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>FragmentChoice</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>reward_food_fragment</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>gold_normal</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>act_food_passive</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>招牌菜试炼</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>普通美食挑战，主要奖励被动道具。</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>85</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>PassiveItemChoice</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>reward_food_passive</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>gold_normal</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>act_food_dish</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>新菜试做</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>普通美食挑战，主要奖励菜品。</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>100</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>DishChoice</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>reward_food_dish</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>gold_normal</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>act_food_hard_fragment</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>硬菜扩胃</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>更难美食挑战，主要奖励胃部碎片。</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>65</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>FragmentChoice</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>reward_food_hard_fragment</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>gold_hard</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>act_food_hard_passive</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>名厨考验</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>更难美食挑战，主要奖励被动道具。</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>60</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>PassiveItemChoice</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>reward_food_hard_passive</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>gold_hard</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>act_food_hard_dish</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>稀有菜谱</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>更难美食挑战，主要奖励菜品。</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>70</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>DishChoice</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>reward_food_hard_dish</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>gold_hard</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>act_cook</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>开火做菜</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>兼容旧配置：普通美食挑战，达标得奖励。</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>80</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>DishChoice</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>reward_food_dish</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>gold_normal</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
           <t>act_feast</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>大宴宾客</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>更耗时的硬仗，目标更高、奖励更厚。</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>兼容旧配置：更耗时的硬仗，目标更高、奖励更厚。</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>Food</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F12" t="n">
         <v>3</v>
       </c>
-      <c r="G5" t="n">
-        <v>70</v>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="G12" t="n">
+        <v>55</v>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
+      <c r="K12" t="n">
         <v>1.5</v>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>PassiveItemChoice</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>reward_food_hard_passive</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>gold_hard</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>act_market</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>逛集市</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>花点时间逛集市采购。</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
         <v>60</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>ev_market</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>act_tasting</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>办试菜会</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>举办试菜会，给菜谱加菜。</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>50</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>ev_tasting</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>act_rest</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>歇业一天</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>短暂休息，降低下一关要求分。</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>40</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>ev_rest</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>act_recruit</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>招募帮厨</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>招募帮厨，获得一件被动道具。</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>35</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>ev_recruit</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>act_study</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>钻研食谱</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>钻研食谱，提升一道菜。</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>ev_upgrade</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>act_gamble</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>豪赌一桌</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>高风险高回报，可能大赚也可能亏本。</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>30</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Gamble</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>50</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>act_tip</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>收小费</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>客人很满意，留下一笔小费。</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Reward</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>25</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>GainGold</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>25</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>act_shop</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>逛逛商店</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>去食材店转转，买卖道具。</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Shop</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>40</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ev_market</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>act_tasting</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>办试菜会</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>举办试菜会，给菜谱加菜。</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>50</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ev_tasting</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>DishChoice</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>act_rest</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>歇业一天</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>短暂休息，降低下一关要求分。</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>40</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ev_rest</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>act_recruit</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>招募帮厨</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>招募帮厨，获得一件被动道具。</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>35</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ev_recruit</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>PassiveItemChoice</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>act_study</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>钻研食谱</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>钻研食谱，提升一道菜。</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>30</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ev_upgrade</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>DishChoice</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>act_gamble</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>豪赌一桌</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>高风险高回报，可能大赚也可能亏本。</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>30</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Gamble</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>50</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>act_tip</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>收小费</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>客人很满意，留下一笔小费。</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>25</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>GainGold</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>25</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>act_shop</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>逛逛商店</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>去食材店转转，买卖道具。</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>40</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>weekFilter</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>preventRepeat</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>行动组ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>行动组名称</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>随机权重</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>周筛选：空/normal/boss/逗号周号</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>是否禁止相邻重复</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>grp_food_normal</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>普通美食组</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>grp_food_hard</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>普通更难美食组</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>65</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>grp_event_food</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>事件美食组</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>55</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>grp_reward</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>纯奖励组</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>35</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>grp_boss_food</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Boss美食组</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>groupId</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>actionId</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>costDaysMin</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>costDaysMax</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>成员ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>行动组ID</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>行动ID</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>最小耗时</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>最大耗时</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>组内展示权重</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>gm_normal_gold</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>grp_food_normal</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>act_food_gold</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>gm_normal_fragment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>grp_food_normal</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>act_food_fragment</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>gm_normal_passive</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>grp_food_normal</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>act_food_passive</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>gm_hard_gold</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>grp_food_hard</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>act_food_gold</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>gm_hard_fragment</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>grp_food_hard</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>act_food_hard_fragment</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>gm_hard_passive</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>grp_food_hard</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>act_food_hard_passive</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>gm_event_market</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>grp_event_food</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>act_market</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>gm_event_food</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>grp_event_food</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>act_food_passive</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>gm_reward_tip</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>grp_reward</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>act_tip</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>gm_boss_food</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>grp_boss_food</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>act_food_hard_passive</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>gm_boss_fragment</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>grp_boss_food</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>act_food_hard_fragment</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ruleType</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>groupId</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>startIndex</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>endIndex</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>windowSize</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>windowStart</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>windowEnd</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>minCount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>maxCount</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>weekFilter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>规则ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>优先级，越小越先放置</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>RangeCount/WindowCount</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>行动组ID</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>起始行动序号(1-based)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>结束行动序号(1-based)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>窗口大小</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>窗口内起点</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>窗口内终点</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>最少出现次数</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>最多出现次数</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>周筛选</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>rule_reward_early</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>RangeCount</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>grp_reward</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>rule_reward_late</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>RangeCount</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>grp_reward</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>rule_event_decade</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>WindowCount</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>grp_event_food</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>rule_boss_group</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RangeCount</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>grp_boss_food</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>11</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -8,9 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="action" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="action_group" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="action_group_member" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="action_schedule_rule" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -696,6 +693,7 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>act_food_gold</t>
@@ -727,9 +725,13 @@
           <t>true</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
         <v>1</v>
       </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -755,6 +757,7 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>act_food_fragment</t>
@@ -786,9 +789,13 @@
           <t>true</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
         <v>1</v>
       </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -814,6 +821,7 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>act_food_passive</t>
@@ -845,9 +853,13 @@
           <t>true</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
         <v>1</v>
       </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -873,6 +885,7 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>act_food_dish</t>
@@ -904,9 +917,13 @@
           <t>true</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
         <v>1</v>
       </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -932,6 +949,7 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>act_food_hard_fragment</t>
@@ -963,9 +981,13 @@
           <t>true</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
         <v>1.25</v>
       </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Hard</t>
@@ -991,6 +1013,7 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>act_food_hard_passive</t>
@@ -1022,9 +1045,13 @@
           <t>true</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
         <v>1.3</v>
       </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Hard</t>
@@ -1050,6 +1077,7 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>act_food_hard_dish</t>
@@ -1081,9 +1109,13 @@
           <t>true</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
         <v>1.25</v>
       </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Hard</t>
@@ -1109,6 +1141,7 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>act_cook</t>
@@ -1140,9 +1173,13 @@
           <t>true</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
         <v>1</v>
       </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -1168,6 +1205,7 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>act_feast</t>
@@ -1199,9 +1237,13 @@
           <t>true</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
         <v>1.5</v>
       </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Hard</t>
@@ -1227,6 +1269,7 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>act_market</t>
@@ -1258,9 +1301,12 @@
           <t>true</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
         <v>0</v>
       </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>ev_market</t>
@@ -1276,11 +1322,14 @@
           <t>Gold</t>
         </is>
       </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>act_tasting</t>
@@ -1312,9 +1361,12 @@
           <t>true</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
         <v>0</v>
       </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>ev_tasting</t>
@@ -1330,11 +1382,14 @@
           <t>DishChoice</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
           <t>act_rest</t>
@@ -1366,9 +1421,12 @@
           <t>true</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
         <v>0</v>
       </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>ev_rest</t>
@@ -1384,11 +1442,14 @@
           <t>Gold</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
           <t>act_recruit</t>
@@ -1420,9 +1481,12 @@
           <t>false</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
         <v>0</v>
       </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>ev_recruit</t>
@@ -1438,11 +1502,14 @@
           <t>PassiveItemChoice</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>act_study</t>
@@ -1474,9 +1541,12 @@
           <t>true</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
         <v>0</v>
       </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>ev_upgrade</t>
@@ -1492,11 +1562,14 @@
           <t>DishChoice</t>
         </is>
       </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
           <t>act_gamble</t>
@@ -1528,6 +1601,7 @@
           <t>true</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>Gamble</t>
@@ -1536,6 +1610,8 @@
       <c r="K18" t="n">
         <v>50</v>
       </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -1546,11 +1622,14 @@
           <t>Gold</t>
         </is>
       </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
           <t>act_tip</t>
@@ -1582,6 +1661,7 @@
           <t>true</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>GainGold</t>
@@ -1590,6 +1670,8 @@
       <c r="K19" t="n">
         <v>25</v>
       </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -1600,11 +1682,14 @@
           <t>Gold</t>
         </is>
       </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
           <t>act_shop</t>
@@ -1636,9 +1721,13 @@
           <t>true</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
         <v>0</v>
       </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -1649,1023 +1738,10 @@
           <t>Gold</t>
         </is>
       </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
         <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>weight</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>weekFilter</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>preventRepeat</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>##comment</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>行动组ID</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>行动组名称</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>随机权重</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>周筛选：空/normal/boss/逗号周号</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>是否禁止相邻重复</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>grp_food_normal</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>普通美食组</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>grp_food_hard</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>普通更难美食组</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>65</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>grp_event_food</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>事件美食组</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>55</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>grp_reward</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>纯奖励组</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>35</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>grp_boss_food</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Boss美食组</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>100</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>boss</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>groupId</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>actionId</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>costDaysMin</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>costDaysMax</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>weight</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>##comment</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>成员ID</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>行动组ID</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>行动ID</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>最小耗时</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>最大耗时</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>组内展示权重</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>gm_normal_gold</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>grp_food_normal</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>act_food_gold</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>gm_normal_fragment</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>grp_food_normal</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>act_food_fragment</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>gm_normal_passive</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>grp_food_normal</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>act_food_passive</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>gm_hard_gold</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>grp_food_hard</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>act_food_gold</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>gm_hard_fragment</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>grp_food_hard</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>act_food_hard_fragment</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>gm_hard_passive</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>grp_food_hard</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>act_food_hard_passive</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>gm_event_market</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>grp_event_food</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>act_market</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>gm_event_food</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>grp_event_food</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>act_food_passive</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>gm_reward_tip</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>grp_reward</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>act_tip</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>gm_boss_food</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>grp_boss_food</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>act_food_hard_passive</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>gm_boss_fragment</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>grp_boss_food</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>act_food_hard_fragment</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" t="n">
-        <v>90</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>ruleType</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>groupId</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>startIndex</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>endIndex</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>windowSize</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>windowStart</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>windowEnd</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>minCount</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>maxCount</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>weekFilter</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>##comment</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>规则ID</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>优先级，越小越先放置</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>RangeCount/WindowCount</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>行动组ID</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>起始行动序号(1-based)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>结束行动序号(1-based)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>窗口大小</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>窗口内起点</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>窗口内终点</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>最少出现次数</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>最多出现次数</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>周筛选</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>rule_reward_early</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>RangeCount</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>grp_reward</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>rule_reward_late</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>RangeCount</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>grp_reward</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G5" t="n">
-        <v>12</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>rule_event_decade</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>30</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>WindowCount</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>grp_event_food</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>10</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>8</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>rule_boss_group</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>RangeCount</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>grp_boss_food</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>11</v>
-      </c>
-      <c r="G7" t="n">
-        <v>12</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>boss</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="action" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="action_group" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="action_group_member" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="action_schedule_rule" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +891,17 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>act_food_dish</t>
+          <t>act_food_active</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>新菜试做</t>
+          <t>秘制小物</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>普通美食挑战，主要奖励菜品。</t>
+          <t>普通美食挑战，主要奖励主动道具。</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -907,10 +910,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -931,12 +934,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>DishChoice</t>
+          <t>ActiveItemGrant</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>reward_food_dish</t>
+          <t>reward_food_active</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -952,17 +955,17 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>act_food_hard_fragment</t>
+          <t>act_food_dish</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>硬菜扩胃</t>
+          <t>新菜试做</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>更难美食挑战，主要奖励胃部碎片。</t>
+          <t>普通美食挑战，主要奖励菜品。</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -971,10 +974,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -984,49 +987,49 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>FragmentChoice</t>
+          <t>DishChoice</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>reward_food_hard_fragment</t>
+          <t>reward_food_dish</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>gold_hard</t>
+          <t>gold_normal</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>act_food_hard_passive</t>
+          <t>act_food_hard_gold</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>名厨考验</t>
+          <t>重口硬菜</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>更难美食挑战，主要奖励被动道具。</t>
+          <t>更难美食挑战，主要奖励金币。</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1038,7 +1041,7 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1048,7 +1051,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -1059,12 +1062,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>PassiveItemChoice</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>reward_food_hard_passive</t>
+          <t>reward_food_hard_gold</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1073,24 +1076,24 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>act_food_hard_dish</t>
+          <t>act_food_hard_fragment</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>稀有菜谱</t>
+          <t>硬菜扩胃</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>更难美食挑战，主要奖励菜品。</t>
+          <t>更难美食挑战，主要奖励胃部碎片。</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1102,7 +1105,7 @@
         <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1123,12 +1126,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>DishChoice</t>
+          <t>FragmentChoice</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>reward_food_hard_dish</t>
+          <t>reward_food_hard_fragment</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1144,17 +1147,17 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>act_cook</t>
+          <t>act_food_hard_passive</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>开火做菜</t>
+          <t>名厨考验</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>兼容旧配置：普通美食挑战，达标得奖励。</t>
+          <t>更难美食挑战，主要奖励被动道具。</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1163,10 +1166,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1176,49 +1179,49 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>DishChoice</t>
+          <t>PassiveItemChoice</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>reward_food_dish</t>
+          <t>reward_food_hard_passive</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>gold_normal</t>
+          <t>gold_hard</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>act_feast</t>
+          <t>act_food_hard_active</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>大宴宾客</t>
+          <t>险中取巧</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>兼容旧配置：更耗时的硬仗，目标更高、奖励更厚。</t>
+          <t>更难美食挑战，主要奖励主动道具。</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1227,7 +1230,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -1240,7 +1243,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
@@ -1251,12 +1254,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>PassiveItemChoice</t>
+          <t>ActiveItemGrant</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>reward_food_hard_passive</t>
+          <t>reward_food_hard_active</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1265,36 +1268,36 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>act_market</t>
+          <t>act_food_hard_dish</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>逛集市</t>
+          <t>稀有菜谱</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>花点时间逛集市采购。</t>
+          <t>更难美食挑战，主要奖励菜品。</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1304,57 +1307,61 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>ev_market</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
+          <t>DishChoice</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>reward_food_hard_dish</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>gold_hard</t>
+        </is>
+      </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>act_tasting</t>
+          <t>act_cook</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>办试菜会</t>
+          <t>开火做菜</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>举办试菜会，给菜谱加菜。</t>
+          <t>兼容旧配置：普通美食挑战，达标得奖励。</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1364,14 +1371,10 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>ev_tasting</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -1382,8 +1385,16 @@
           <t>DishChoice</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>reward_food_dish</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>gold_normal</t>
+        </is>
+      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -1392,29 +1403,29 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>act_rest</t>
+          <t>act_feast</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>歇业一天</t>
+          <t>大宴宾客</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>短暂休息，降低下一关要求分。</t>
+          <t>兼容旧配置：更耗时的硬仗，目标更高、奖励更厚。</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1424,45 +1435,49 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>ev_rest</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+          <t>PassiveItemChoice</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>reward_food_hard_passive</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>gold_hard</t>
+        </is>
+      </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>act_recruit</t>
+          <t>act_market</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>招募帮厨</t>
+          <t>逛集市</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>招募帮厨，获得一件被动道具。</t>
+          <t>花点时间逛集市采购。</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1471,14 +1486,14 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1489,7 +1504,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>ev_recruit</t>
+          <t>ev_market</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1499,7 +1514,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>PassiveItemChoice</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1512,17 +1527,17 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>act_study</t>
+          <t>act_tasting</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>钻研食谱</t>
+          <t>办试菜会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>钻研食谱，提升一道菜。</t>
+          <t>举办试菜会，给菜谱加菜。</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1531,10 +1546,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1549,7 +1564,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>ev_upgrade</t>
+          <t>ev_tasting</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1572,29 +1587,29 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>act_gamble</t>
+          <t>act_rest</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>豪赌一桌</t>
+          <t>歇业一天</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>高风险高回报，可能大赚也可能亏本。</t>
+          <t>短暂休息，降低下一关要求分。</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1602,16 +1617,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Gamble</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ev_rest</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -1632,46 +1647,46 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>act_tip</t>
+          <t>act_recruit</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>收小费</t>
+          <t>招募帮厨</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>客人很满意，留下一笔小费。</t>
+          <t>招募帮厨，获得一件被动道具。</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Reward</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>GainGold</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>ev_recruit</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -1679,7 +1694,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>PassiveItemChoice</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -1692,29 +1707,29 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>act_shop</t>
+          <t>act_study</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>逛逛商店</t>
+          <t>钻研食谱</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>去食材店转转，买卖道具。</t>
+          <t>钻研食谱，提升一道菜。</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shop</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1727,7 +1742,11 @@
         <v>0</v>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>ev_upgrade</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -1735,7 +1754,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>DishChoice</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -1744,6 +1763,1292 @@
         <v>0</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>act_gamble</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>豪赌一桌</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>高风险高回报，可能大赚也可能亏本。</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>30</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Gamble</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>50</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>act_tip</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>收小费</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>客人很满意，留下一笔小费。</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>25</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>GainGold</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>25</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>act_shop</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>逛逛商店</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>去食材店转转，买卖道具。</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>40</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>groupType</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>weekFilter</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>preconditions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>行动组ID。</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>行动组显示名。</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>行动组描述。</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>行动组分类：food_normal/food_hard/event/reward 等。</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>周筛选：空=任意，normal=非Boss周，boss=Boss周，或逗号分隔周号。</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>普通空位填充时的行动组权重。</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>行动组前置条件。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>grp_food_normal</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>普通美食组</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>普通美食挑战，奖励外观混合金币、碎片、道具与菜品。</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>food_normal</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>grp_food_hard</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>困难美食组</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>更难美食挑战，目标更高、奖励更厚。</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>food_hard</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>55</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>grp_event_food</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>事件美食组</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>事件与美食穿插，调节局外节奏。</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>45</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>grp_reward</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>纯奖励组</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>直接奖励、商店或低风险收益。</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>reward</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>groupId</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>actionId</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>minCostDays</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>maxCostDays</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>行动组成员ID。</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>所属行动组ID。</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>行动ID。</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>组内随机权重。</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>本次行动最小耗时；&lt;=0 使用 action.costDays。</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>本次行动最大耗时；&lt;=0 使用 action.costDays。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>agm_normal_gold</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>grp_food_normal</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>act_food_gold</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>120</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>agm_normal_fragment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>grp_food_normal</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>act_food_fragment</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>90</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>agm_normal_passive</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>grp_food_normal</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>act_food_passive</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>85</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>agm_normal_active</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>grp_food_normal</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>act_food_active</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>75</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>agm_normal_dish</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>grp_food_normal</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>act_food_dish</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>agm_hard_gold</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>grp_food_hard</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>act_food_hard_gold</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>70</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>agm_hard_fragment</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>grp_food_hard</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>act_food_hard_fragment</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>65</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>agm_hard_passive</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>grp_food_hard</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>act_food_hard_passive</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>60</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>agm_hard_active</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>grp_food_hard</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>act_food_hard_active</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>55</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>agm_hard_dish</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>grp_food_hard</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>act_food_hard_dish</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>70</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>agm_event_market</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>grp_event_food</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>act_market</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>60</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>agm_event_tasting</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>grp_event_food</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>act_tasting</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>50</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>agm_event_rest</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>grp_event_food</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>act_rest</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>40</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>agm_event_recruit</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>grp_event_food</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>act_recruit</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>35</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>agm_event_study</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>grp_event_food</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>act_study</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>30</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>agm_reward_tip</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>grp_reward</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>act_tip</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>90</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>agm_reward_shop</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>grp_reward</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>act_shop</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>70</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>groupIds</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>minRunStep</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>maxRunStep</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>minCount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>maxCount</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>preconditions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>日程规则ID。</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>优先级，数值越大越先填充。</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>候选行动组ID，多个用 | 或逗号分隔。</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>整局行动序号窗口起点，1-based。</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>整局行动序号窗口终点，含。</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>该窗口内至少出现次数。</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>该窗口内最多出现次数。</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>同优先规则之间的权重。</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>规则前置条件。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>rule_reward_early</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>grp_reward</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>rule_reward_mid</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>95</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>grp_reward</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>rule_event_opening</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>80</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>grp_event_food</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>100</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -696,7 +696,6 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>act_food_gold</t>
@@ -728,13 +727,9 @@
           <t>true</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -760,7 +755,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>act_food_fragment</t>
@@ -792,13 +786,9 @@
           <t>true</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -824,7 +814,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>act_food_passive</t>
@@ -856,13 +845,9 @@
           <t>true</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -888,7 +873,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>act_food_active</t>
@@ -920,13 +904,9 @@
           <t>true</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -952,7 +932,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>act_food_dish</t>
@@ -984,13 +963,9 @@
           <t>true</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -1016,7 +991,6 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>act_food_hard_gold</t>
@@ -1048,13 +1022,9 @@
           <t>true</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
         <v>1.2</v>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Hard</t>
@@ -1080,7 +1050,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>act_food_hard_fragment</t>
@@ -1112,13 +1081,9 @@
           <t>true</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
         <v>1.25</v>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Hard</t>
@@ -1144,7 +1109,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>act_food_hard_passive</t>
@@ -1176,13 +1140,9 @@
           <t>true</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
         <v>1.3</v>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Hard</t>
@@ -1208,7 +1168,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>act_food_hard_active</t>
@@ -1240,13 +1199,9 @@
           <t>true</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
         <v>1.25</v>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Hard</t>
@@ -1272,7 +1227,6 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>act_food_hard_dish</t>
@@ -1304,13 +1258,9 @@
           <t>true</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
         <v>1.25</v>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Hard</t>
@@ -1336,7 +1286,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>act_cook</t>
@@ -1368,13 +1317,9 @@
           <t>true</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -1400,7 +1345,6 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
           <t>act_feast</t>
@@ -1432,13 +1376,9 @@
           <t>true</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
         <v>1.5</v>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Hard</t>
@@ -1464,7 +1404,6 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
           <t>act_market</t>
@@ -1496,12 +1435,9 @@
           <t>true</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>ev_market</t>
@@ -1517,14 +1453,11 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>act_tasting</t>
@@ -1556,12 +1489,9 @@
           <t>true</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>ev_tasting</t>
@@ -1577,14 +1507,11 @@
           <t>DishChoice</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
           <t>act_rest</t>
@@ -1616,12 +1543,9 @@
           <t>true</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>ev_rest</t>
@@ -1637,14 +1561,11 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
           <t>act_recruit</t>
@@ -1676,12 +1597,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>ev_recruit</t>
@@ -1697,14 +1615,11 @@
           <t>PassiveItemChoice</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
           <t>act_study</t>
@@ -1736,12 +1651,9 @@
           <t>true</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>ev_upgrade</t>
@@ -1757,14 +1669,11 @@
           <t>DishChoice</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
           <t>act_gamble</t>
@@ -1796,7 +1705,6 @@
           <t>true</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>Gamble</t>
@@ -1805,8 +1713,6 @@
       <c r="K21" t="n">
         <v>50</v>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -1817,14 +1723,11 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
           <t>act_tip</t>
@@ -1856,7 +1759,6 @@
           <t>true</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>GainGold</t>
@@ -1865,8 +1767,6 @@
       <c r="K22" t="n">
         <v>25</v>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -1877,14 +1777,11 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
           <t>act_shop</t>
@@ -1916,13 +1813,9 @@
           <t>true</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -1933,9 +1826,64 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>act_debug_shop_event</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>神秘商贩</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>测试用事件：触发后进入商店。</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>100</v>
+      </c>
+      <c r="H24" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>ev_debug_shop</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1950,7 +1898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2080,7 +2028,6 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>grp_food_normal</t>
@@ -2109,10 +2056,8 @@
       <c r="G4" t="n">
         <v>100</v>
       </c>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>grp_food_hard</t>
@@ -2133,14 +2078,11 @@
           <t>food_hard</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
         <v>55</v>
       </c>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>grp_event_food</t>
@@ -2169,10 +2111,8 @@
       <c r="G6" t="n">
         <v>45</v>
       </c>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>grp_reward</t>
@@ -2193,11 +2133,40 @@
           <t>reward</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>30</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>grp_debug_shop_event</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>测试商店事件组</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>测试用：首个行动固定为事件，并由事件进入商店。</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>debug_event</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2210,7 +2179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2325,7 +2294,6 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>agm_normal_gold</t>
@@ -2352,7 +2320,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>agm_normal_fragment</t>
@@ -2379,7 +2346,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>agm_normal_passive</t>
@@ -2406,7 +2372,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>agm_normal_active</t>
@@ -2433,7 +2398,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>agm_normal_dish</t>
@@ -2460,7 +2424,6 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>agm_hard_gold</t>
@@ -2487,7 +2450,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>agm_hard_fragment</t>
@@ -2514,7 +2476,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>agm_hard_passive</t>
@@ -2541,7 +2502,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>agm_hard_active</t>
@@ -2568,7 +2528,6 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>agm_hard_dish</t>
@@ -2595,7 +2554,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>agm_event_market</t>
@@ -2622,7 +2580,6 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
           <t>agm_event_tasting</t>
@@ -2649,7 +2606,6 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
           <t>agm_event_rest</t>
@@ -2676,7 +2632,6 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>agm_event_recruit</t>
@@ -2703,7 +2658,6 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
           <t>agm_event_study</t>
@@ -2730,7 +2684,6 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
           <t>agm_reward_tip</t>
@@ -2757,7 +2710,6 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
           <t>agm_reward_shop</t>
@@ -2780,6 +2732,32 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>agm_debug_shop_event</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>grp_debug_shop_event</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>act_debug_shop_event</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2794,7 +2772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2954,7 +2932,6 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>rule_reward_early</t>
@@ -2983,10 +2960,8 @@
       <c r="I4" t="n">
         <v>100</v>
       </c>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>rule_reward_mid</t>
@@ -3015,10 +2990,8 @@
       <c r="I5" t="n">
         <v>100</v>
       </c>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>rule_event_opening</t>
@@ -3047,7 +3020,37 @@
       <c r="I6" t="n">
         <v>100</v>
       </c>
-      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>rule_debug_first_shop_event</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>grp_debug_shop_event</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>100</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -4,17 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16760"/>
+    <workbookView windowHeight="16760" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="action" sheetId="1" r:id="rId1"/>
     <sheet name="large_group" sheetId="2" r:id="rId2"/>
-    <sheet name="large_member" sheetId="3" r:id="rId3"/>
-    <sheet name="medium_group" sheetId="4" r:id="rId4"/>
-    <sheet name="medium_member" sheetId="5" r:id="rId5"/>
-    <sheet name="small_group" sheetId="6" r:id="rId6"/>
-    <sheet name="small_member" sheetId="7" r:id="rId7"/>
-    <sheet name="action_schedule_rule" sheetId="8" r:id="rId8"/>
+    <sheet name="medium_group" sheetId="3" r:id="rId3"/>
+    <sheet name="small_group" sheetId="4" r:id="rId4"/>
+    <sheet name="action_schedule_rule" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="166">
   <si>
     <t>##var</t>
   </si>
@@ -291,304 +288,217 @@
     <t>act_interest8</t>
   </si>
   <si>
+    <t>ruleIds</t>
+  </si>
+  <si>
+    <t>fallbackWeights</t>
+  </si>
+  <si>
+    <t>*mediumGroupIds</t>
+  </si>
+  <si>
+    <t>大组ID</t>
+  </si>
+  <si>
+    <t>大组名</t>
+  </si>
+  <si>
+    <t>参与的日程规则ID(逗号分隔),空=仅保底</t>
+  </si>
+  <si>
+    <t>保底加权随机权重列表(按当前周-1取,越界取最后一个)</t>
+  </si>
+  <si>
+    <t>包含的中组ID列表→medium_group.id</t>
+  </si>
+  <si>
+    <t>list,float</t>
+  </si>
+  <si>
+    <t>list,string</t>
+  </si>
+  <si>
+    <t>lg_food_normal</t>
+  </si>
+  <si>
+    <t>普通美食大组</t>
+  </si>
+  <si>
+    <t>mg_food_normal</t>
+  </si>
+  <si>
+    <t>lg_food_hard</t>
+  </si>
+  <si>
+    <t>困难美食大组</t>
+  </si>
+  <si>
+    <t>mg_food_hard</t>
+  </si>
+  <si>
+    <t>lg_event</t>
+  </si>
+  <si>
+    <t>事件大组</t>
+  </si>
+  <si>
+    <t>rule_event_opening</t>
+  </si>
+  <si>
+    <t>mg_event</t>
+  </si>
+  <si>
+    <t>lg_reward</t>
+  </si>
+  <si>
+    <t>奖励大组</t>
+  </si>
+  <si>
+    <t>rule_reward_early,rule_reward_mid</t>
+  </si>
+  <si>
+    <t>mg_reward</t>
+  </si>
+  <si>
+    <t>lg_debug</t>
+  </si>
+  <si>
+    <t>调试大组</t>
+  </si>
+  <si>
+    <t>rule_debug_first</t>
+  </si>
+  <si>
+    <t>mg_debug</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>*smallGroupEntries</t>
+  </si>
+  <si>
+    <t>中组ID</t>
+  </si>
+  <si>
+    <t>中组名</t>
+  </si>
+  <si>
+    <t>被大组选中的权重</t>
+  </si>
+  <si>
+    <t>包含的小组及权重，格式 smallGroupId,weight</t>
+  </si>
+  <si>
+    <t>list,ActionSmallGroupEntry</t>
+  </si>
+  <si>
+    <t>普通美食中组</t>
+  </si>
+  <si>
+    <t>sg_food_a,100</t>
+  </si>
+  <si>
+    <t>sg_food_b,80</t>
+  </si>
+  <si>
+    <t>困难美食中组</t>
+  </si>
+  <si>
+    <t>sg_food_hard_a,100</t>
+  </si>
+  <si>
+    <t>sg_food_hard_b,80</t>
+  </si>
+  <si>
+    <t>事件中组</t>
+  </si>
+  <si>
+    <t>sg_event,100</t>
+  </si>
+  <si>
+    <t>奖励中组</t>
+  </si>
+  <si>
+    <t>sg_reward,100</t>
+  </si>
+  <si>
+    <t>调试中组</t>
+  </si>
+  <si>
+    <t>sg_debug,100</t>
+  </si>
+  <si>
+    <t>*actionIds</t>
+  </si>
+  <si>
+    <t>小组ID</t>
+  </si>
+  <si>
+    <t>小组名(调试用)</t>
+  </si>
+  <si>
+    <t>小组内固定行动ID列表→action.id</t>
+  </si>
+  <si>
+    <t>sg_food_a</t>
+  </si>
+  <si>
+    <t>美食A</t>
+  </si>
+  <si>
+    <t>sg_food_b</t>
+  </si>
+  <si>
+    <t>美食B</t>
+  </si>
+  <si>
+    <t>sg_food_hard_a</t>
+  </si>
+  <si>
+    <t>硬菜A</t>
+  </si>
+  <si>
+    <t>sg_food_hard_b</t>
+  </si>
+  <si>
+    <t>硬菜B</t>
+  </si>
+  <si>
+    <t>sg_event</t>
+  </si>
+  <si>
+    <t>事件</t>
+  </si>
+  <si>
+    <t>sg_reward</t>
+  </si>
+  <si>
+    <t>奖励</t>
+  </si>
+  <si>
+    <t>sg_debug</t>
+  </si>
+  <si>
+    <t>调试商店</t>
+  </si>
+  <si>
+    <t>priority</t>
+  </si>
+  <si>
+    <t>minRunStep</t>
+  </si>
+  <si>
+    <t>maxRunStep</t>
+  </si>
+  <si>
+    <t>minCount</t>
+  </si>
+  <si>
+    <t>maxCount</t>
+  </si>
+  <si>
     <t>preconditions</t>
-  </si>
-  <si>
-    <t>ruleIds</t>
-  </si>
-  <si>
-    <t>fallbackWeights</t>
-  </si>
-  <si>
-    <t>大组ID</t>
-  </si>
-  <si>
-    <t>大组名</t>
-  </si>
-  <si>
-    <t>大组前置条件</t>
-  </si>
-  <si>
-    <t>参与的日程规则ID(逗号分隔),空=仅保底</t>
-  </si>
-  <si>
-    <t>保底加权随机权重列表(按当前周-1取,越界取最后一个)</t>
-  </si>
-  <si>
-    <t>list,float</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>lg_food_normal</t>
-  </si>
-  <si>
-    <t>普通美食大组</t>
-  </si>
-  <si>
-    <t>lg_food_hard</t>
-  </si>
-  <si>
-    <t>困难美食大组</t>
-  </si>
-  <si>
-    <t>lg_event</t>
-  </si>
-  <si>
-    <t>事件大组</t>
-  </si>
-  <si>
-    <t>rule_event_opening</t>
-  </si>
-  <si>
-    <t>lg_reward</t>
-  </si>
-  <si>
-    <t>奖励大组</t>
-  </si>
-  <si>
-    <t>rule_reward_early,rule_reward_mid</t>
-  </si>
-  <si>
-    <t>lg_debug</t>
-  </si>
-  <si>
-    <t>调试大组</t>
-  </si>
-  <si>
-    <t>rule_debug_first</t>
-  </si>
-  <si>
-    <t>largeGroupId</t>
-  </si>
-  <si>
-    <t>mediumGroupId</t>
-  </si>
-  <si>
-    <t>成员ID</t>
-  </si>
-  <si>
-    <t>所属大组ID→large_group.id</t>
-  </si>
-  <si>
-    <t>中组ID→medium_group.id</t>
-  </si>
-  <si>
-    <t>lg_food_normal_0</t>
-  </si>
-  <si>
-    <t>mg_food_normal</t>
-  </si>
-  <si>
-    <t>lg_food_hard_0</t>
-  </si>
-  <si>
-    <t>mg_food_hard</t>
-  </si>
-  <si>
-    <t>lg_event_0</t>
-  </si>
-  <si>
-    <t>mg_event</t>
-  </si>
-  <si>
-    <t>lg_reward_0</t>
-  </si>
-  <si>
-    <t>mg_reward</t>
-  </si>
-  <si>
-    <t>lg_debug_0</t>
-  </si>
-  <si>
-    <t>mg_debug</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>中组ID</t>
-  </si>
-  <si>
-    <t>中组名</t>
-  </si>
-  <si>
-    <t>被大组选中的权重</t>
-  </si>
-  <si>
-    <t>普通美食中组</t>
-  </si>
-  <si>
-    <t>困难美食中组</t>
-  </si>
-  <si>
-    <t>事件中组</t>
-  </si>
-  <si>
-    <t>奖励中组</t>
-  </si>
-  <si>
-    <t>调试中组</t>
-  </si>
-  <si>
-    <t>smallGroupId</t>
-  </si>
-  <si>
-    <t>所属中组ID→medium_group.id</t>
-  </si>
-  <si>
-    <t>小组ID→small_group.id</t>
-  </si>
-  <si>
-    <t>中组内选该小组的权重</t>
-  </si>
-  <si>
-    <t>mg_food_normal_0</t>
-  </si>
-  <si>
-    <t>sg_food_a</t>
-  </si>
-  <si>
-    <t>mg_food_normal_1</t>
-  </si>
-  <si>
-    <t>sg_food_b</t>
-  </si>
-  <si>
-    <t>mg_food_hard_0</t>
-  </si>
-  <si>
-    <t>sg_food_hard_a</t>
-  </si>
-  <si>
-    <t>mg_food_hard_1</t>
-  </si>
-  <si>
-    <t>sg_food_hard_b</t>
-  </si>
-  <si>
-    <t>mg_event_0</t>
-  </si>
-  <si>
-    <t>sg_event</t>
-  </si>
-  <si>
-    <t>mg_reward_0</t>
-  </si>
-  <si>
-    <t>sg_reward</t>
-  </si>
-  <si>
-    <t>mg_debug_0</t>
-  </si>
-  <si>
-    <t>sg_debug</t>
-  </si>
-  <si>
-    <t>小组ID</t>
-  </si>
-  <si>
-    <t>小组名(调试用)</t>
-  </si>
-  <si>
-    <t>美食A</t>
-  </si>
-  <si>
-    <t>美食B</t>
-  </si>
-  <si>
-    <t>硬菜A</t>
-  </si>
-  <si>
-    <t>硬菜B</t>
-  </si>
-  <si>
-    <t>事件</t>
-  </si>
-  <si>
-    <t>奖励</t>
-  </si>
-  <si>
-    <t>调试商店</t>
-  </si>
-  <si>
-    <t>actionId</t>
-  </si>
-  <si>
-    <t>所属小组ID→small_group.id</t>
-  </si>
-  <si>
-    <t>行动ID→action.id</t>
-  </si>
-  <si>
-    <t>sg_food_a_0</t>
-  </si>
-  <si>
-    <t>sg_food_a_1</t>
-  </si>
-  <si>
-    <t>sg_food_a_2</t>
-  </si>
-  <si>
-    <t>sg_food_b_0</t>
-  </si>
-  <si>
-    <t>sg_food_b_1</t>
-  </si>
-  <si>
-    <t>sg_food_b_2</t>
-  </si>
-  <si>
-    <t>sg_food_hard_a_0</t>
-  </si>
-  <si>
-    <t>sg_food_hard_a_1</t>
-  </si>
-  <si>
-    <t>sg_food_hard_a_2</t>
-  </si>
-  <si>
-    <t>sg_food_hard_b_0</t>
-  </si>
-  <si>
-    <t>sg_food_hard_b_1</t>
-  </si>
-  <si>
-    <t>sg_food_hard_b_2</t>
-  </si>
-  <si>
-    <t>sg_event_0</t>
-  </si>
-  <si>
-    <t>sg_event_1</t>
-  </si>
-  <si>
-    <t>sg_event_2</t>
-  </si>
-  <si>
-    <t>sg_reward_0</t>
-  </si>
-  <si>
-    <t>sg_reward_1</t>
-  </si>
-  <si>
-    <t>sg_debug_0</t>
-  </si>
-  <si>
-    <t>priority</t>
-  </si>
-  <si>
-    <t>minRunStep</t>
-  </si>
-  <si>
-    <t>maxRunStep</t>
-  </si>
-  <si>
-    <t>minCount</t>
-  </si>
-  <si>
-    <t>maxCount</t>
   </si>
   <si>
     <t>规则ID(大组用 ruleIds 引用它)</t>
@@ -2057,10 +1967,8 @@
     <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
     <col min="2" max="2" width="16.4615384615385" customWidth="1"/>
     <col min="3" max="3" width="15.1538461538462" customWidth="1"/>
-    <col min="4" max="4" width="42.0769230769231" customWidth="1"/>
-    <col min="5" max="5" width="15.1538461538462" customWidth="1"/>
-    <col min="6" max="6" width="43.3076923076923" customWidth="1"/>
-    <col min="7" max="7" width="57.7692307692308" customWidth="1"/>
+    <col min="4" max="4" width="43.3076923076923" customWidth="1"/>
+    <col min="5" max="6" width="57.7692307692308" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2117,110 +2025,89 @@
         <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="F3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
         <v>94</v>
       </c>
+    </row>
+    <row r="4" spans="2:6">
       <c r="B4" t="s">
         <v>95</v>
       </c>
       <c r="C4" t="s">
         <v>96</v>
       </c>
-      <c r="D4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E4" t="s">
-        <v>94</v>
-      </c>
-      <c r="F4">
+      <c r="E4">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>94</v>
-      </c>
+      <c r="F4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6">
       <c r="B5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5" t="s">
-        <v>94</v>
-      </c>
-      <c r="F5">
+        <v>99</v>
+      </c>
+      <c r="E5">
         <v>55</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>94</v>
-      </c>
+      <c r="F5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6">
       <c r="B6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F6">
+        <v>103</v>
+      </c>
+      <c r="E6">
         <v>45</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
-        <v>94</v>
-      </c>
+      <c r="F6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6">
       <c r="B7" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
-      </c>
-      <c r="E7" t="s">
-        <v>104</v>
-      </c>
-      <c r="F7">
+        <v>107</v>
+      </c>
+      <c r="E7">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>94</v>
-      </c>
+      <c r="F7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6">
       <c r="B8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" t="s">
-        <v>107</v>
-      </c>
-      <c r="F8">
+        <v>111</v>
+      </c>
+      <c r="E8">
         <v>0</v>
+      </c>
+      <c r="F8" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -2232,16 +2119,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7" outlineLevelCol="3"/>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
-    <col min="2" max="2" width="18.7692307692308" customWidth="1"/>
-    <col min="3" max="3" width="29.8461538461538" customWidth="1"/>
-    <col min="4" max="4" width="28.1538461538462" customWidth="1"/>
+    <col min="2" max="2" width="17.6923076923077" customWidth="1"/>
+    <col min="3" max="3" width="15.1538461538462" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2249,27 +2137,33 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>108</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>113</v>
+      </c>
+      <c r="E1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>117</v>
+      </c>
+      <c r="E2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -2280,62 +2174,90 @@
         <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5">
       <c r="B4" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4">
-      <c r="B5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D5" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4">
+        <v>120</v>
+      </c>
+      <c r="D4">
+        <v>100</v>
+      </c>
+      <c r="E4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="5:5">
+      <c r="E5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
       <c r="B6" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4">
-      <c r="B7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4">
+        <v>123</v>
+      </c>
+      <c r="D6">
+        <v>55</v>
+      </c>
+      <c r="E6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="5:5">
+      <c r="E7" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
       <c r="B8" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
-      </c>
-      <c r="D8" t="s">
-        <v>122</v>
+        <v>126</v>
+      </c>
+      <c r="D8">
+        <v>45</v>
+      </c>
+      <c r="E8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5">
+      <c r="B9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D9">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
+      <c r="B10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C10" t="s">
+        <v>130</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -2347,13 +2269,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7" outlineLevelCol="3"/>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
-    <col min="2" max="2" width="17.6923076923077" customWidth="1"/>
-    <col min="3" max="3" width="15.1538461538462" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="2" max="3" width="16.5384615384615" customWidth="1"/>
+    <col min="4" max="4" width="36.3076923076923" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2367,7 +2287,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2375,13 +2295,13 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2395,62 +2315,139 @@
         <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="B4" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
-      </c>
-      <c r="D4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4">
-      <c r="B5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D5">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4">
-      <c r="B6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C6" t="s">
-        <v>129</v>
-      </c>
-      <c r="D6">
-        <v>45</v>
+        <v>137</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="4:4">
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="4:4">
+      <c r="D6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="B7" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="C7" t="s">
-        <v>130</v>
-      </c>
-      <c r="D7">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4">
-      <c r="B8" t="s">
-        <v>122</v>
-      </c>
-      <c r="C8" t="s">
-        <v>131</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
+        <v>139</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="4:4">
+      <c r="D8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="4:4">
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="B10" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="4:4">
+      <c r="D11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="4:4">
+      <c r="D12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4">
+      <c r="B13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C13" t="s">
+        <v>143</v>
+      </c>
+      <c r="D13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="4:4">
+      <c r="D14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="4:4">
+      <c r="D15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="B16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C16" t="s">
+        <v>145</v>
+      </c>
+      <c r="D16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4">
+      <c r="D17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="4:4">
+      <c r="D18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C19" t="s">
+        <v>147</v>
+      </c>
+      <c r="D19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="4:4">
+      <c r="D20" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="B21" t="s">
+        <v>148</v>
+      </c>
+      <c r="C21" t="s">
+        <v>149</v>
+      </c>
+      <c r="D21" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2460,520 +2457,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5">
-      <c r="B4" t="s">
-        <v>136</v>
-      </c>
-      <c r="C4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5">
-      <c r="B5" t="s">
-        <v>138</v>
-      </c>
-      <c r="C5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" t="s">
-        <v>139</v>
-      </c>
-      <c r="E5">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5">
-      <c r="B6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D6" t="s">
-        <v>141</v>
-      </c>
-      <c r="E6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5">
-      <c r="B7" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E7">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5">
-      <c r="B8" t="s">
-        <v>144</v>
-      </c>
-      <c r="C8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D8" t="s">
-        <v>145</v>
-      </c>
-      <c r="E8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5">
-      <c r="B9" t="s">
-        <v>146</v>
-      </c>
-      <c r="C9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D9" t="s">
-        <v>147</v>
-      </c>
-      <c r="E9">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5">
-      <c r="B10" t="s">
-        <v>148</v>
-      </c>
-      <c r="C10" t="s">
-        <v>122</v>
-      </c>
-      <c r="D10" t="s">
-        <v>149</v>
-      </c>
-      <c r="E10">
-        <v>100</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3">
-      <c r="B4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C4" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3">
-      <c r="B5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C5" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3">
-      <c r="B6" t="s">
-        <v>141</v>
-      </c>
-      <c r="C6" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3">
-      <c r="B7" t="s">
-        <v>143</v>
-      </c>
-      <c r="C7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3">
-      <c r="B8" t="s">
-        <v>145</v>
-      </c>
-      <c r="C8" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3">
-      <c r="B9" t="s">
-        <v>147</v>
-      </c>
-      <c r="C9" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3">
-      <c r="B10" t="s">
-        <v>149</v>
-      </c>
-      <c r="C10" t="s">
-        <v>158</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C2" t="s">
-        <v>160</v>
-      </c>
-      <c r="D2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4">
-      <c r="B4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C4" t="s">
-        <v>137</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4">
-      <c r="B5" t="s">
-        <v>163</v>
-      </c>
-      <c r="C5" t="s">
-        <v>137</v>
-      </c>
-      <c r="D5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4">
-      <c r="B6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4">
-      <c r="B7" t="s">
-        <v>165</v>
-      </c>
-      <c r="C7" t="s">
-        <v>139</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4">
-      <c r="B8" t="s">
-        <v>166</v>
-      </c>
-      <c r="C8" t="s">
-        <v>139</v>
-      </c>
-      <c r="D8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4">
-      <c r="B9" t="s">
-        <v>167</v>
-      </c>
-      <c r="C9" t="s">
-        <v>139</v>
-      </c>
-      <c r="D9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4">
-      <c r="B10" t="s">
-        <v>168</v>
-      </c>
-      <c r="C10" t="s">
-        <v>141</v>
-      </c>
-      <c r="D10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4">
-      <c r="B11" t="s">
-        <v>169</v>
-      </c>
-      <c r="C11" t="s">
-        <v>141</v>
-      </c>
-      <c r="D11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4">
-      <c r="B12" t="s">
-        <v>170</v>
-      </c>
-      <c r="C12" t="s">
-        <v>141</v>
-      </c>
-      <c r="D12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4">
-      <c r="B13" t="s">
-        <v>171</v>
-      </c>
-      <c r="C13" t="s">
-        <v>143</v>
-      </c>
-      <c r="D13" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4">
-      <c r="B14" t="s">
-        <v>172</v>
-      </c>
-      <c r="C14" t="s">
-        <v>143</v>
-      </c>
-      <c r="D14" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4">
-      <c r="B15" t="s">
-        <v>173</v>
-      </c>
-      <c r="C15" t="s">
-        <v>143</v>
-      </c>
-      <c r="D15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4">
-      <c r="B16" t="s">
-        <v>174</v>
-      </c>
-      <c r="C16" t="s">
-        <v>145</v>
-      </c>
-      <c r="D16" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4">
-      <c r="B17" t="s">
-        <v>175</v>
-      </c>
-      <c r="C17" t="s">
-        <v>145</v>
-      </c>
-      <c r="D17" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4">
-      <c r="B18" t="s">
-        <v>176</v>
-      </c>
-      <c r="C18" t="s">
-        <v>145</v>
-      </c>
-      <c r="D18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4">
-      <c r="B19" t="s">
-        <v>177</v>
-      </c>
-      <c r="C19" t="s">
-        <v>147</v>
-      </c>
-      <c r="D19" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4">
-      <c r="B20" t="s">
-        <v>178</v>
-      </c>
-      <c r="C20" t="s">
-        <v>147</v>
-      </c>
-      <c r="D20" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4">
-      <c r="B21" t="s">
-        <v>179</v>
-      </c>
-      <c r="C21" t="s">
-        <v>149</v>
-      </c>
-      <c r="D21" t="s">
-        <v>76</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H7"/>
@@ -2996,22 +2479,22 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D1" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="E1" t="s">
-        <v>182</v>
+        <v>152</v>
       </c>
       <c r="F1" t="s">
-        <v>183</v>
+        <v>153</v>
       </c>
       <c r="G1" t="s">
-        <v>184</v>
+        <v>154</v>
       </c>
       <c r="H1" t="s">
-        <v>85</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3019,25 +2502,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="C2" t="s">
-        <v>186</v>
+        <v>157</v>
       </c>
       <c r="D2" t="s">
-        <v>187</v>
+        <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="F2" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="G2" t="s">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="H2" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -3048,19 +2531,19 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
       <c r="D3" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
       <c r="E3" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
       <c r="F3" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
       <c r="G3" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
@@ -3068,7 +2551,7 @@
     </row>
     <row r="4" spans="2:7">
       <c r="B4" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -3088,7 +2571,7 @@
     </row>
     <row r="5" spans="2:7">
       <c r="B5" t="s">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="C5">
         <v>95</v>
@@ -3108,7 +2591,7 @@
     </row>
     <row r="6" spans="2:7">
       <c r="B6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C6">
         <v>80</v>
@@ -3128,7 +2611,7 @@
     </row>
     <row r="7" spans="2:7">
       <c r="B7" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C7">
         <v>1000</v>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16760" activeTab="2"/>
+    <workbookView windowHeight="16760"/>
   </bookViews>
   <sheets>
     <sheet name="action" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="166">
   <si>
     <t>##var</t>
   </si>
@@ -216,6 +216,66 @@
     <t>food_hard_dish</t>
   </si>
   <si>
+    <t>act_event</t>
+  </si>
+  <si>
+    <t>未知事件</t>
+  </si>
+  <si>
+    <t>一个待揭晓的事件。</t>
+  </si>
+  <si>
+    <t>Event</t>
+  </si>
+  <si>
+    <t>act_reward</t>
+  </si>
+  <si>
+    <t>额外收益</t>
+  </si>
+  <si>
+    <t>一份即时奖励。</t>
+  </si>
+  <si>
+    <t>Reward</t>
+  </si>
+  <si>
+    <t>act_negative</t>
+  </si>
+  <si>
+    <t>突发状况</t>
+  </si>
+  <si>
+    <t>一个有风险的抉择。</t>
+  </si>
+  <si>
+    <t>Negative</t>
+  </si>
+  <si>
+    <t>act_shop</t>
+  </si>
+  <si>
+    <t>逛逛商店</t>
+  </si>
+  <si>
+    <t>去食材店转转，买卖道具。</t>
+  </si>
+  <si>
+    <t>Shop</t>
+  </si>
+  <si>
+    <t>act_interest</t>
+  </si>
+  <si>
+    <t>收取利息</t>
+  </si>
+  <si>
+    <t>到点自动结算利息。</t>
+  </si>
+  <si>
+    <t>Interest</t>
+  </si>
+  <si>
     <t>act_boss</t>
   </si>
   <si>
@@ -225,67 +285,7 @@
     <t>带有特殊机制的盛宴挑战。</t>
   </si>
   <si>
-    <t>act_event</t>
-  </si>
-  <si>
-    <t>未知事件</t>
-  </si>
-  <si>
-    <t>一个待揭晓的事件。</t>
-  </si>
-  <si>
-    <t>Event</t>
-  </si>
-  <si>
-    <t>act_reward</t>
-  </si>
-  <si>
-    <t>额外收益</t>
-  </si>
-  <si>
-    <t>一份即时奖励。</t>
-  </si>
-  <si>
-    <t>Reward</t>
-  </si>
-  <si>
-    <t>act_negative</t>
-  </si>
-  <si>
-    <t>突发状况</t>
-  </si>
-  <si>
-    <t>一个有风险的抉择。</t>
-  </si>
-  <si>
-    <t>Negative</t>
-  </si>
-  <si>
-    <t>act_shop</t>
-  </si>
-  <si>
-    <t>逛逛商店</t>
-  </si>
-  <si>
-    <t>去食材店转转，买卖道具。</t>
-  </si>
-  <si>
-    <t>Shop</t>
-  </si>
-  <si>
-    <t>act_interest</t>
-  </si>
-  <si>
-    <t>收取利息</t>
-  </si>
-  <si>
-    <t>到点自动结算利息。</t>
-  </si>
-  <si>
-    <t>Interest</t>
-  </si>
-  <si>
-    <t>act_interest8</t>
+    <t>food_boss</t>
   </si>
   <si>
     <t>ruleIds</t>
@@ -1490,7 +1490,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
@@ -1823,27 +1823,28 @@
         <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="F14"/>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="2:8">
       <c r="B15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1854,16 +1855,16 @@
     </row>
     <row r="16" spans="2:8">
       <c r="B16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1874,81 +1875,64 @@
     </row>
     <row r="17" spans="2:8">
       <c r="B17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:8">
       <c r="B18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:8">
       <c r="B19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E19" t="s">
-        <v>83</v>
+        <v>23</v>
+      </c>
+      <c r="F19" t="s">
+        <v>84</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8">
-      <c r="B20" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E20" t="s">
-        <v>83</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
         <v>0</v>
       </c>
     </row>
@@ -2410,7 +2394,7 @@
         <v>145</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="4:4">
@@ -2431,12 +2415,12 @@
         <v>147</v>
       </c>
       <c r="D19" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="2:4">
@@ -2447,7 +2431,7 @@
         <v>149</v>
       </c>
       <c r="D21" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15200"/>
+    <workbookView windowHeight="15200" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="action" sheetId="1" r:id="rId1"/>
@@ -13,14 +13,14 @@
     <sheet name="action_schedule_rule" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">small_group!$B$1:$B$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">small_group!$B$1:$B$166</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="632">
   <si>
     <t>##var</t>
   </si>
@@ -277,18 +277,30 @@
     <t>普通美食大组</t>
   </si>
   <si>
+    <t>sg_normal_1,sg_normal_2,sg_normal_3,sg_normal_4,sg_normal_5,sg_normal_6,sg_normal_7,sg_normal_8,sg_normal_9,sg_normal_10,sg_normal_11,sg_normal_12,sg_normal_13,sg_normal_14,sg_normal_15,sg_normal_16,sg_normal_17,sg_normal_18,sg_normal_19,sg_normal_20</t>
+  </si>
+  <si>
     <t>lg_normalHard</t>
   </si>
   <si>
     <t>普通困难美食大组</t>
   </si>
   <si>
+    <t>sg_normalHard_1,sg_normalHard_2,sg_normalHard_3,sg_normalHard_4,sg_normalHard_5,sg_normalHard_6,sg_normalHard_7,sg_normalHard_8,sg_normalHard_9,sg_normalHard_10,sg_normalHard_11,sg_normalHard_12,sg_normalHard_13,sg_normalHard_14,sg_normalHard_15,sg_normalHard_16,sg_normalHard_17,sg_normalHard_18,sg_normalHard_19,sg_normalHard_20,sg_normalHard_21,sg_normalHard_22,sg_normalHard_23,sg_normalHard_24,sg_normalHard_25,sg_normalHard_26,sg_normalHard_27,sg_normalHard_28,sg_normalHard_29,sg_normalHard_30,sg_normalHard_31,sg_normalHard_32,sg_normalHard_33,sg_normalHard_34,sg_normalHard_35,sg_normalHard_36,sg_normalHard_37,sg_normalHard_38,sg_normalHard_39,sg_normalHard_40,sg_normalHard_41,sg_normalHard_42,sg_normalHard_43,sg_normalHard_44,sg_normalHard_45,sg_normalHard_46,sg_normalHard_47,sg_normalHard_48,sg_normalHard_49,sg_normalHard_50,sg_normalHard_51,sg_normalHard_52,sg_normalHard_53,sg_normalHard_54,sg_normalHard_55,sg_normalHard_56,sg_normalHard_57,sg_normalHard_58,sg_normalHard_59,sg_normalHard_60,sg_normalHard_61,sg_normalHard_62,sg_normalHard_63,sg_normalHard_64,sg_normalHard_65,sg_normalHard_66,sg_normalHard_67,sg_normalHard_68,sg_normalHard_69,sg_normalHard_70,sg_normalHard_71,sg_normalHard_72,sg_normalHard_73,sg_normalHard_74,sg_normalHard_75,sg_normalHard_76,sg_normalHard_77,sg_normalHard_78,sg_normalHard_79,sg_normalHard_80</t>
+  </si>
+  <si>
     <t>lg_hard</t>
   </si>
   <si>
     <t>困难美食大组</t>
   </si>
   <si>
+    <t>0,50,100,200</t>
+  </si>
+  <si>
+    <t>sg_hard_1,sg_hard_2,sg_hard_3,sg_hard_4,sg_hard_5,sg_hard_6,sg_hard_7,sg_hard_8,sg_hard_9,sg_hard_10,sg_hard_11,sg_hard_12,sg_hard_13,sg_hard_14,sg_hard_15,sg_hard_16,sg_hard_17,sg_hard_18,sg_hard_19,sg_hard_20</t>
+  </si>
+  <si>
     <t>lg_event</t>
   </si>
   <si>
@@ -298,6 +310,9 @@
     <t>rule_event_opening</t>
   </si>
   <si>
+    <t>sg_event_1</t>
+  </si>
+  <si>
     <t>lg_reward</t>
   </si>
   <si>
@@ -307,216 +322,240 @@
     <t>rule_reward_early,rule_reward_mid</t>
   </si>
   <si>
+    <t>50,50,50,50</t>
+  </si>
+  <si>
+    <t>sg_reward_1</t>
+  </si>
+  <si>
     <t>lg_normalEvent</t>
   </si>
   <si>
     <t>普通事件大组</t>
   </si>
   <si>
+    <t>sg_normalEvent_1,sg_normalEvent_2,sg_normalEvent_3,sg_normalEvent_4,sg_normalEvent_5,sg_normalEvent_6,sg_normalEvent_7,sg_normalEvent_8,sg_normalEvent_9,sg_normalEvent_10,sg_normalEvent_11,sg_normalEvent_12,sg_normalEvent_13,sg_normalEvent_14,sg_normalEvent_15</t>
+  </si>
+  <si>
     <t>lg_normalHardEvent</t>
   </si>
   <si>
+    <t>普通困难事件大组</t>
+  </si>
+  <si>
+    <t>sg_normalHardEvent_1,sg_normalHardEvent_2,sg_normalHardEvent_3,sg_normalHardEvent_4,sg_normalHardEvent_5,sg_normalHardEvent_6,sg_normalHardEvent_7,sg_normalHardEvent_8,sg_normalHardEvent_9,sg_normalHardEvent_10</t>
+  </si>
+  <si>
+    <t>lg_hardEvent</t>
+  </si>
+  <si>
+    <t>困难事件大组</t>
+  </si>
+  <si>
+    <t>0,50,100,100</t>
+  </si>
+  <si>
+    <t>sg_hardEvent_1,sg_hardEvent_2,sg_hardEvent_3,sg_hardEvent_4,sg_hardEvent_5,sg_hardEvent_6,sg_hardEvent_7,sg_hardEvent_8,sg_hardEvent_9,sg_hardEvent_10,sg_hardEvent_11,sg_hardEvent_12,sg_hardEvent_13,sg_hardEvent_14,sg_hardEvent_15</t>
+  </si>
+  <si>
+    <t>lg_debug</t>
+  </si>
+  <si>
+    <t>调试大组</t>
+  </si>
+  <si>
+    <t>rule_debug_first</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>mg_debug</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>actionIds</t>
+  </si>
+  <si>
+    <t>小组ID</t>
+  </si>
+  <si>
+    <t>小组名(调试用)</t>
+  </si>
+  <si>
+    <t>被大组选中的权重</t>
+  </si>
+  <si>
+    <t>小组内固定行动ID列表→action.id</t>
+  </si>
+  <si>
+    <t>sg_normal_1</t>
+  </si>
+  <si>
+    <t>普通1</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_fragment,act_food_passive</t>
+  </si>
+  <si>
+    <t>sg_normal_2</t>
+  </si>
+  <si>
+    <t>普通2</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_fragment,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalEvent_15</t>
+  </si>
+  <si>
+    <t>sg_normal_3</t>
+  </si>
+  <si>
+    <t>普通3</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_fragment,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHardEvent_1</t>
+  </si>
+  <si>
+    <t>sg_normal_4</t>
+  </si>
+  <si>
+    <t>普通4</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_hardEvent_1</t>
+  </si>
+  <si>
+    <t>sg_normal_5</t>
+  </si>
+  <si>
+    <t>普通5</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normal_6</t>
+  </si>
+  <si>
+    <t>普通6</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normal_7</t>
+  </si>
+  <si>
+    <t>普通7</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normal_8</t>
+  </si>
+  <si>
+    <t>普通8</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normal_9</t>
+  </si>
+  <si>
+    <t>普通9</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normal_10</t>
+  </si>
+  <si>
+    <t>普通10</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_food_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normal_11</t>
+  </si>
+  <si>
+    <t>普通11</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_fragment</t>
+  </si>
+  <si>
+    <t>sg_normal_12</t>
+  </si>
+  <si>
+    <t>普通12</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_passive</t>
+  </si>
+  <si>
+    <t>sg_normal_13</t>
+  </si>
+  <si>
+    <t>普通13</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normal_14</t>
+  </si>
+  <si>
+    <t>普通14</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normal_15</t>
+  </si>
+  <si>
+    <t>普通15</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_passive</t>
+  </si>
+  <si>
+    <t>sg_normal_16</t>
+  </si>
+  <si>
+    <t>普通16</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normal_17</t>
+  </si>
+  <si>
+    <t>普通17</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_dish</t>
+  </si>
+  <si>
     <t>普通困难混合大组</t>
   </si>
   <si>
-    <t>lg_hardEvent</t>
-  </si>
-  <si>
-    <t>困难事件大组</t>
-  </si>
-  <si>
-    <t>lg_debug</t>
-  </si>
-  <si>
-    <t>调试大组</t>
-  </si>
-  <si>
-    <t>rule_debug_first</t>
-  </si>
-  <si>
-    <t>mg_debug</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>actionIds</t>
-  </si>
-  <si>
-    <t>小组ID</t>
-  </si>
-  <si>
-    <t>小组名(调试用)</t>
-  </si>
-  <si>
-    <t>被大组选中的权重</t>
-  </si>
-  <si>
-    <t>小组内固定行动ID列表→action.id</t>
-  </si>
-  <si>
-    <t>sg_normal_1</t>
-  </si>
-  <si>
-    <t>普通1</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_fragment,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normal_2</t>
-  </si>
-  <si>
-    <t>普通2</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_fragment,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalEvent_15</t>
-  </si>
-  <si>
-    <t>sg_normal_3</t>
-  </si>
-  <si>
-    <t>普通3</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_fragment,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHardEvent_1</t>
-  </si>
-  <si>
-    <t>sg_normal_4</t>
-  </si>
-  <si>
-    <t>普通4</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_hardEvent_1</t>
-  </si>
-  <si>
-    <t>sg_normal_5</t>
-  </si>
-  <si>
-    <t>普通5</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normal_6</t>
-  </si>
-  <si>
-    <t>普通6</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normal_7</t>
-  </si>
-  <si>
-    <t>普通7</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normal_8</t>
-  </si>
-  <si>
-    <t>普通8</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normal_9</t>
-  </si>
-  <si>
-    <t>普通9</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normal_10</t>
-  </si>
-  <si>
-    <t>普通10</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_food_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normal_11</t>
-  </si>
-  <si>
-    <t>普通11</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_fragment</t>
-  </si>
-  <si>
-    <t>sg_normal_12</t>
-  </si>
-  <si>
-    <t>普通12</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normal_13</t>
-  </si>
-  <si>
-    <t>普通13</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normal_14</t>
-  </si>
-  <si>
-    <t>普通14</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normal_15</t>
-  </si>
-  <si>
-    <t>普通15</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normal_16</t>
-  </si>
-  <si>
-    <t>普通16</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normal_17</t>
-  </si>
-  <si>
-    <t>普通17</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_dish</t>
-  </si>
-  <si>
     <t>sg_normal_18</t>
   </si>
   <si>
@@ -1474,13 +1513,7 @@
     <t>act_food_hard_active,act_food_hard_dish</t>
   </si>
   <si>
-    <t>sg_event_1</t>
-  </si>
-  <si>
     <t>事件1</t>
-  </si>
-  <si>
-    <t>sg_reward_1</t>
   </si>
   <si>
     <t>奖励1</t>
@@ -2496,9 +2529,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3284,8 +3320,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
+  <dimension ref="A1:L12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
     <col min="2" max="2" width="21.8461538461538" style="1" customWidth="1"/>
@@ -3356,179 +3392,256 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="2:7">
+    <row r="4" spans="2:12">
       <c r="B4" s="1" t="s">
         <v>83</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,small_group!B4:B23)</f>
-        <v>sg_normal_1,sg_normal_2,sg_normal_3,sg_normal_4,sg_normal_5,sg_normal_6,sg_normal_7,sg_normal_8,sg_normal_9,sg_normal_10,sg_normal_11,sg_normal_12,sg_normal_13,sg_normal_14,sg_normal_15,sg_normal_16,sg_normal_17,sg_normal_18,sg_normal_19,sg_normal_20</v>
-      </c>
-      <c r="G4" s="1" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" spans="2:7">
+      <c r="E4" s="2">
+        <v>400300200150</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="I4" s="1">
+        <v>400</v>
+      </c>
+      <c r="J4" s="1">
+        <v>300</v>
+      </c>
+      <c r="K4" s="1">
+        <v>200</v>
+      </c>
+      <c r="L4" s="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12">
       <c r="B5" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,small_group!B24:B103)</f>
-        <v>sg_normalHard_1,sg_normalHard_2,sg_normalHard_3,sg_normalHard_4,sg_normalHard_5,sg_normalHard_6,sg_normalHard_7,sg_normalHard_8,sg_normalHard_9,sg_normalHard_10,sg_normalHard_11,sg_normalHard_12,sg_normalHard_13,sg_normalHard_14,sg_normalHard_15,sg_normalHard_16,sg_normalHard_17,sg_normalHard_18,sg_normalHard_19,sg_normalHard_20,sg_normalHard_21,sg_normalHard_22,sg_normalHard_23,sg_normalHard_24,sg_normalHard_25,sg_normalHard_26,sg_normalHard_27,sg_normalHard_28,sg_normalHard_29,sg_normalHard_30,sg_normalHard_31,sg_normalHard_32,sg_normalHard_33,sg_normalHard_34,sg_normalHard_35,sg_normalHard_36,sg_normalHard_37,sg_normalHard_38,sg_normalHard_39,sg_normalHard_40,sg_normalHard_41,sg_normalHard_42,sg_normalHard_43,sg_normalHard_44,sg_normalHard_45,sg_normalHard_46,sg_normalHard_47,sg_normalHard_48,sg_normalHard_49,sg_normalHard_50,sg_normalHard_51,sg_normalHard_52,sg_normalHard_53,sg_normalHard_54,sg_normalHard_55,sg_normalHard_56,sg_normalHard_57,sg_normalHard_58,sg_normalHard_59,sg_normalHard_60,sg_normalHard_61,sg_normalHard_62,sg_normalHard_63,sg_normalHard_64,sg_normalHard_65,sg_normalHard_66,sg_normalHard_67,sg_normalHard_68,sg_normalHard_69,sg_normalHard_70,sg_normalHard_71,sg_normalHard_72,sg_normalHard_73,sg_normalHard_74,sg_normalHard_75,sg_normalHard_76,sg_normalHard_77,sg_normalHard_78,sg_normalHard_79,sg_normalHard_80</v>
-      </c>
-      <c r="G5" s="1" t="str">
-        <f t="shared" ref="G5:G13" si="0">""</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" spans="2:7">
+        <v>87</v>
+      </c>
+      <c r="E5" s="2">
+        <v>200200250200</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="I5" s="1">
+        <v>200</v>
+      </c>
+      <c r="J5" s="1">
+        <v>200</v>
+      </c>
+      <c r="K5" s="1">
+        <v>250</v>
+      </c>
+      <c r="L5" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12">
       <c r="B6" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,small_group!B104:B123)</f>
-        <v>sg_hard_1,sg_hard_2,sg_hard_3,sg_hard_4,sg_hard_5,sg_hard_6,sg_hard_7,sg_hard_8,sg_hard_9,sg_hard_10,sg_hard_11,sg_hard_12,sg_hard_13,sg_hard_14,sg_hard_15,sg_hard_16,sg_hard_17,sg_hard_18,sg_hard_19,sg_hard_20</v>
-      </c>
-      <c r="G6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="7" spans="2:7">
+        <v>90</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>50</v>
+      </c>
+      <c r="K6" s="1">
+        <v>100</v>
+      </c>
+      <c r="L6" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12">
       <c r="B7" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E7" s="1">
-        <v>30</v>
-      </c>
-      <c r="F7" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,small_group!B124)</f>
-        <v>sg_event_1</v>
-      </c>
-      <c r="G7" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="2:7">
+        <v>95</v>
+      </c>
+      <c r="E7" s="2">
+        <v>100100100100</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="I7" s="1">
+        <v>100</v>
+      </c>
+      <c r="J7" s="1">
+        <v>100</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+      <c r="L7" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12">
       <c r="B8" s="1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" s="1">
-        <v>10</v>
-      </c>
-      <c r="F8" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,small_group!B125)</f>
-        <v>sg_reward_1</v>
-      </c>
-      <c r="G8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="2:7">
+        <v>99</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="I8" s="1">
+        <v>50</v>
+      </c>
+      <c r="J8" s="1">
+        <v>50</v>
+      </c>
+      <c r="K8" s="1">
+        <v>50</v>
+      </c>
+      <c r="L8" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12">
       <c r="B9" s="1" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,small_group!B126:B140)</f>
-        <v>sg_normalEvent_1,sg_normalEvent_2,sg_normalEvent_3,sg_normalEvent_4,sg_normalEvent_5,sg_normalEvent_6,sg_normalEvent_7,sg_normalEvent_8,sg_normalEvent_9,sg_normalEvent_10,sg_normalEvent_11,sg_normalEvent_12,sg_normalEvent_13,sg_normalEvent_14,sg_normalEvent_15</v>
-      </c>
-      <c r="G9" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="2:7">
+        <v>103</v>
+      </c>
+      <c r="E9" s="2">
+        <v>150150100100</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="I9" s="1">
+        <v>150</v>
+      </c>
+      <c r="J9" s="1">
+        <v>150</v>
+      </c>
+      <c r="K9" s="1">
+        <v>100</v>
+      </c>
+      <c r="L9" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12">
       <c r="B10" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,small_group!B141:B150)</f>
-        <v>sg_normalHardEvent_1,sg_normalHardEvent_2,sg_normalHardEvent_3,sg_normalHardEvent_4,sg_normalHardEvent_5,sg_normalHardEvent_6,sg_normalHardEvent_7,sg_normalHardEvent_8,sg_normalHardEvent_9,sg_normalHardEvent_10</v>
-      </c>
-      <c r="G10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="2:7">
+        <v>106</v>
+      </c>
+      <c r="E10" s="2">
+        <v>100100100100</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="I10" s="1">
+        <v>100</v>
+      </c>
+      <c r="J10" s="1">
+        <v>100</v>
+      </c>
+      <c r="K10" s="1">
+        <v>100</v>
+      </c>
+      <c r="L10" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12">
       <c r="B11" s="1" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F11" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,small_group!B151:B165)</f>
-        <v>sg_hardEvent_1,sg_hardEvent_2,sg_hardEvent_3,sg_hardEvent_4,sg_hardEvent_5,sg_hardEvent_6,sg_hardEvent_7,sg_hardEvent_8,sg_hardEvent_9,sg_hardEvent_10,sg_hardEvent_11,sg_hardEvent_12,sg_hardEvent_13,sg_hardEvent_14,sg_hardEvent_15</v>
-      </c>
-      <c r="G11" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="2:7">
+        <v>109</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>50</v>
+      </c>
+      <c r="K11" s="1">
+        <v>100</v>
+      </c>
+      <c r="L11" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12">
       <c r="B12" s="1" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E12" s="1"/>
+        <v>114</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="F12" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="7:7">
-      <c r="G13" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <v>116</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3570,10 +3683,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3581,16 +3694,16 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3612,177 +3725,166 @@
     </row>
     <row r="4" spans="2:5">
       <c r="B4" s="1" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D4" s="1">
         <v>100</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="2:18">
       <c r="B5" s="1" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D5" s="1">
         <v>100</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
+        <v>128</v>
+      </c>
       <c r="R5" s="1" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="2:18">
       <c r="B6" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="D6" s="1">
         <v>100</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
+        <v>132</v>
+      </c>
       <c r="R6" s="1" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="2:18">
       <c r="B7" s="1" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="D7" s="1">
         <v>100</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
+        <v>136</v>
+      </c>
       <c r="R7" s="1" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="B8" s="1" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="1" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="1" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="B11" s="1" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="D11" s="1">
         <v>100</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="B12" s="1" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="D12" s="1">
         <v>100</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="1" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="D13" s="1">
         <v>100</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="1" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="D14" s="1">
         <v>100</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
+        <v>158</v>
+      </c>
       <c r="L14" s="1" t="s">
         <v>83</v>
       </c>
@@ -3792,156 +3894,142 @@
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="D15" s="1">
         <v>100</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
+        <v>161</v>
+      </c>
       <c r="L15" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="1" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="D16" s="1">
         <v>100</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
+        <v>164</v>
+      </c>
       <c r="L16" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="2:13">
       <c r="B17" s="1" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="D17" s="1">
         <v>100</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
+        <v>167</v>
+      </c>
       <c r="L17" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="1" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="D18" s="1">
         <v>100</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
+        <v>170</v>
+      </c>
       <c r="L18" s="1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="1" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="D19" s="1">
         <v>100</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
+        <v>173</v>
+      </c>
       <c r="L19" s="1" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="1" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="D20" s="1">
         <v>100</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
+        <v>176</v>
+      </c>
       <c r="L20" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>98</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="2:20">
       <c r="B21" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="D21" s="1">
         <v>100</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
+        <v>180</v>
+      </c>
       <c r="L21" s="1" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>20</v>
@@ -3955,24 +4043,22 @@
     </row>
     <row r="22" spans="2:20">
       <c r="B22" s="1" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="D22" s="1">
         <v>100</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
+        <v>183</v>
+      </c>
       <c r="L22" s="1" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>20</v>
@@ -3986,19 +4072,17 @@
     </row>
     <row r="23" spans="2:20">
       <c r="B23" s="1" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="D23" s="1">
         <v>100</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
+        <v>186</v>
+      </c>
       <c r="R23" s="1" t="s">
         <v>20</v>
       </c>
@@ -4011,20 +4095,17 @@
     </row>
     <row r="24" spans="2:20">
       <c r="B24" s="1" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="D24" s="1">
         <v>100</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
+        <v>189</v>
+      </c>
       <c r="R24" s="1" t="s">
         <v>20</v>
       </c>
@@ -4037,20 +4118,17 @@
     </row>
     <row r="25" spans="2:20">
       <c r="B25" s="1" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="D25" s="1">
         <v>100</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
+        <v>192</v>
+      </c>
       <c r="R25" s="1" t="s">
         <v>20</v>
       </c>
@@ -4063,20 +4141,17 @@
     </row>
     <row r="26" spans="2:20">
       <c r="B26" s="1" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D26" s="1">
         <v>100</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
+        <v>195</v>
+      </c>
       <c r="R26" s="1" t="s">
         <v>20</v>
       </c>
@@ -4089,20 +4164,17 @@
     </row>
     <row r="27" spans="2:20">
       <c r="B27" s="1" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="D27" s="1">
         <v>100</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
+        <v>198</v>
+      </c>
       <c r="R27" s="1" t="s">
         <v>25</v>
       </c>
@@ -4115,20 +4187,17 @@
     </row>
     <row r="28" spans="2:20">
       <c r="B28" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="D28" s="1">
         <v>100</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
+        <v>201</v>
+      </c>
       <c r="R28" s="1" t="s">
         <v>25</v>
       </c>
@@ -4141,20 +4210,17 @@
     </row>
     <row r="29" spans="2:20">
       <c r="B29" s="1" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="D29" s="1">
         <v>100</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
+        <v>204</v>
+      </c>
       <c r="R29" s="1" t="s">
         <v>25</v>
       </c>
@@ -4167,20 +4233,17 @@
     </row>
     <row r="30" spans="2:20">
       <c r="B30" s="1" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="D30" s="1">
         <v>100</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
+        <v>207</v>
+      </c>
       <c r="R30" s="1" t="s">
         <v>28</v>
       </c>
@@ -4193,20 +4256,17 @@
     </row>
     <row r="31" spans="2:19">
       <c r="B31" s="1" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="D31" s="1">
         <v>100</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
+        <v>210</v>
+      </c>
       <c r="R31" s="1" t="s">
         <v>20</v>
       </c>
@@ -4216,20 +4276,17 @@
     </row>
     <row r="32" spans="2:19">
       <c r="B32" s="1" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="D32" s="1">
         <v>100</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
+        <v>213</v>
+      </c>
       <c r="R32" s="1" t="s">
         <v>20</v>
       </c>
@@ -4239,20 +4296,17 @@
     </row>
     <row r="33" spans="2:19">
       <c r="B33" s="1" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D33" s="1">
         <v>100</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
+        <v>216</v>
+      </c>
       <c r="R33" s="1" t="s">
         <v>20</v>
       </c>
@@ -4262,20 +4316,17 @@
     </row>
     <row r="34" spans="2:19">
       <c r="B34" s="1" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="D34" s="1">
         <v>100</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
+        <v>219</v>
+      </c>
       <c r="R34" s="1" t="s">
         <v>20</v>
       </c>
@@ -4285,20 +4336,17 @@
     </row>
     <row r="35" spans="2:19">
       <c r="B35" s="1" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="D35" s="1">
         <v>100</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
+        <v>222</v>
+      </c>
       <c r="R35" s="1" t="s">
         <v>25</v>
       </c>
@@ -4308,20 +4356,17 @@
     </row>
     <row r="36" spans="2:19">
       <c r="B36" s="1" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="D36" s="1">
         <v>100</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
+        <v>225</v>
+      </c>
       <c r="R36" s="1" t="s">
         <v>25</v>
       </c>
@@ -4331,20 +4376,17 @@
     </row>
     <row r="37" spans="2:19">
       <c r="B37" s="1" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="D37" s="1">
         <v>100</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
+        <v>228</v>
+      </c>
       <c r="L37" s="1" t="s">
         <v>20</v>
       </c>
@@ -4357,20 +4399,17 @@
     </row>
     <row r="38" spans="2:19">
       <c r="B38" s="1" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="D38" s="1">
         <v>100</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
+        <v>231</v>
+      </c>
       <c r="L38" s="1" t="s">
         <v>25</v>
       </c>
@@ -4383,20 +4422,17 @@
     </row>
     <row r="39" spans="2:19">
       <c r="B39" s="1" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="D39" s="1">
         <v>100</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
+        <v>234</v>
+      </c>
       <c r="L39" s="1" t="s">
         <v>28</v>
       </c>
@@ -4409,20 +4445,17 @@
     </row>
     <row r="40" spans="2:19">
       <c r="B40" s="1" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="D40" s="1">
         <v>100</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
+        <v>237</v>
+      </c>
       <c r="L40" s="1" t="s">
         <v>31</v>
       </c>
@@ -4435,591 +4468,564 @@
     </row>
     <row r="41" spans="2:12">
       <c r="B41" s="1" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="D41" s="1">
         <v>100</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
+        <v>240</v>
+      </c>
       <c r="L41" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="42" spans="2:5">
       <c r="B42" s="1" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="D42" s="1">
         <v>100</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
     </row>
     <row r="43" spans="2:12">
       <c r="B43" s="1" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="D43" s="1">
         <v>100</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
+        <v>246</v>
+      </c>
       <c r="L43" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="44" spans="2:12">
       <c r="B44" s="1" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="D44" s="1">
         <v>100</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
+        <v>249</v>
+      </c>
       <c r="L44" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="45" spans="2:12">
       <c r="B45" s="1" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="D45" s="1">
         <v>100</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
+        <v>252</v>
+      </c>
       <c r="L45" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="46" spans="2:12">
       <c r="B46" s="1" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="D46" s="1">
         <v>100</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
+        <v>255</v>
+      </c>
       <c r="L46" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="47" spans="2:12">
       <c r="B47" s="1" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="D47" s="1">
         <v>100</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
+        <v>258</v>
+      </c>
       <c r="L47" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="48" spans="2:12">
       <c r="B48" s="1" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="D48" s="1">
         <v>100</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
+        <v>261</v>
+      </c>
       <c r="L48" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="49" spans="2:12">
       <c r="B49" s="1" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="D49" s="1">
         <v>100</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
+        <v>264</v>
+      </c>
       <c r="L49" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="50" spans="2:5">
       <c r="B50" s="1" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="D50" s="1">
         <v>100</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
     </row>
     <row r="51" spans="2:5">
       <c r="B51" s="1" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="D51" s="1">
         <v>100</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
     </row>
     <row r="52" spans="2:5">
       <c r="B52" s="1" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="D52" s="1">
         <v>100</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
     </row>
     <row r="53" spans="2:5">
       <c r="B53" s="1" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="D53" s="1">
         <v>100</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
     </row>
     <row r="54" spans="2:5">
       <c r="B54" s="1" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="D54" s="1">
         <v>100</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="55" spans="2:5">
       <c r="B55" s="1" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="D55" s="1">
         <v>100</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
     </row>
     <row r="56" spans="2:5">
       <c r="B56" s="1" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="D56" s="1">
         <v>100</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
     </row>
     <row r="57" spans="2:5">
       <c r="B57" s="1" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="D57" s="1">
         <v>100</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
     </row>
     <row r="58" spans="2:5">
       <c r="B58" s="1" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="D58" s="1">
         <v>100</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="59" spans="2:5">
       <c r="B59" s="1" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="D59" s="1">
         <v>100</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
     </row>
     <row r="60" spans="2:5">
       <c r="B60" s="1" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="D60" s="1">
         <v>100</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
     </row>
     <row r="61" spans="2:5">
       <c r="B61" s="1" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="D61" s="1">
         <v>100</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
     </row>
     <row r="62" spans="2:5">
       <c r="B62" s="1" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="D62" s="1">
         <v>100</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
     </row>
     <row r="63" spans="2:5">
       <c r="B63" s="1" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="D63" s="1">
         <v>100</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
     </row>
     <row r="64" spans="2:5">
       <c r="B64" s="1" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="D64" s="1">
         <v>100</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
     </row>
     <row r="65" spans="2:5">
       <c r="B65" s="1" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D65" s="1">
         <v>100</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
     </row>
     <row r="66" spans="2:5">
       <c r="B66" s="1" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="D66" s="1">
         <v>100</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
     </row>
     <row r="67" spans="2:5">
       <c r="B67" s="1" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="D67" s="1">
         <v>100</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
     </row>
     <row r="68" spans="2:5">
       <c r="B68" s="1" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="D68" s="1">
         <v>100</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
     </row>
     <row r="69" spans="2:5">
       <c r="B69" s="1" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="D69" s="1">
         <v>100</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
     </row>
     <row r="70" spans="2:5">
       <c r="B70" s="1" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="D70" s="1">
         <v>100</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
     </row>
     <row r="71" spans="2:5">
       <c r="B71" s="1" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D71" s="1">
         <v>100</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
     </row>
     <row r="72" spans="2:5">
       <c r="B72" s="1" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="D72" s="1">
         <v>100</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
     </row>
     <row r="73" spans="2:5">
       <c r="B73" s="1" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="D73" s="1">
         <v>100</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="2:5">
       <c r="B74" s="1" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="D74" s="1">
         <v>100</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="2:5">
       <c r="B75" s="1" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="D75" s="1">
         <v>100</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76" spans="2:5">
       <c r="B76" s="1" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="D76" s="1">
         <v>100</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
     </row>
     <row r="77" spans="2:5">
       <c r="B77" s="1" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="D77" s="1">
         <v>100</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
     </row>
     <row r="78" spans="2:20">
       <c r="B78" s="1" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="D78" s="1">
         <v>100</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
+        <v>351</v>
+      </c>
       <c r="Q78" s="1" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="R78" s="1" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="S78" s="1">
         <v>80</v>
@@ -5030,65 +5036,56 @@
     </row>
     <row r="79" spans="2:20">
       <c r="B79" s="1" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="D79" s="1">
         <v>100</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="F79" s="1"/>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
+        <v>356</v>
+      </c>
       <c r="T79" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="80" spans="2:20">
       <c r="B80" s="1" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="D80" s="1">
         <v>100</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="F80" s="1"/>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
+        <v>359</v>
+      </c>
       <c r="T80" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="81" spans="2:20">
       <c r="B81" s="1" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="D81" s="1">
         <v>100</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
+        <v>362</v>
+      </c>
       <c r="Q81" s="1" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="R81" s="1" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="S81" s="1">
         <v>100</v>
@@ -5099,65 +5096,56 @@
     </row>
     <row r="82" spans="2:20">
       <c r="B82" s="1" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="D82" s="1">
         <v>100</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="1"/>
+        <v>367</v>
+      </c>
       <c r="T82" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="83" spans="2:20">
       <c r="B83" s="1" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="D83" s="1">
         <v>100</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="F83" s="1"/>
-      <c r="G83" s="1"/>
-      <c r="H83" s="1"/>
+        <v>370</v>
+      </c>
       <c r="T83" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="84" spans="2:20">
       <c r="B84" s="1" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="D84" s="1">
         <v>100</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="F84" s="1"/>
-      <c r="G84" s="1"/>
-      <c r="H84" s="1"/>
+        <v>373</v>
+      </c>
       <c r="Q84" s="1" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="R84" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="S84" s="1">
         <v>80</v>
@@ -5168,62 +5156,53 @@
     </row>
     <row r="85" spans="2:20">
       <c r="B85" s="1" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="D85" s="1">
         <v>100</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="F85" s="1"/>
-      <c r="G85" s="1"/>
-      <c r="H85" s="1"/>
+        <v>378</v>
+      </c>
       <c r="T85" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="86" spans="2:20">
       <c r="B86" s="1" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="D86" s="1">
         <v>100</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="F86" s="1"/>
-      <c r="G86" s="1"/>
-      <c r="H86" s="1"/>
+        <v>381</v>
+      </c>
       <c r="T86" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="87" spans="2:20">
       <c r="B87" s="1" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="D87" s="1">
         <v>100</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="F87" s="1"/>
-      <c r="G87" s="1"/>
-      <c r="H87" s="1"/>
+        <v>384</v>
+      </c>
       <c r="Q87" s="1" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="R87" s="1" t="s">
         <v>54</v>
@@ -5237,62 +5216,53 @@
     </row>
     <row r="88" spans="2:20">
       <c r="B88" s="1" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="D88" s="1">
         <v>100</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="F88" s="1"/>
-      <c r="G88" s="1"/>
-      <c r="H88" s="1"/>
+        <v>388</v>
+      </c>
       <c r="T88" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="89" spans="2:20">
       <c r="B89" s="1" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="D89" s="1">
         <v>100</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="F89" s="1"/>
-      <c r="G89" s="1"/>
-      <c r="H89" s="1"/>
+        <v>391</v>
+      </c>
       <c r="T89" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="90" spans="2:20">
       <c r="B90" s="1" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="D90" s="1">
         <v>100</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="F90" s="1"/>
-      <c r="G90" s="1"/>
-      <c r="H90" s="1"/>
+        <v>394</v>
+      </c>
       <c r="Q90" s="1" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="R90" s="1" t="s">
         <v>58</v>
@@ -5306,45 +5276,39 @@
     </row>
     <row r="91" spans="2:20">
       <c r="B91" s="1" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="D91" s="1">
         <v>100</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="F91" s="1"/>
-      <c r="G91" s="1"/>
-      <c r="H91" s="1"/>
+        <v>398</v>
+      </c>
       <c r="T91" s="1" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="92" spans="2:20">
       <c r="B92" s="1" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="D92" s="1">
         <v>100</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="F92" s="1"/>
-      <c r="G92" s="1"/>
-      <c r="H92" s="1"/>
+        <v>401</v>
+      </c>
       <c r="Q92" s="1" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="R92" s="1" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="S92" s="1">
         <v>100</v>
@@ -5355,444 +5319,444 @@
     </row>
     <row r="93" spans="2:5">
       <c r="B93" s="1" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="D93" s="1">
         <v>100</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
     </row>
     <row r="94" spans="2:5">
       <c r="B94" s="1" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="D94" s="1">
         <v>100</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
     </row>
     <row r="95" spans="2:5">
       <c r="B95" s="1" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="D95" s="1">
         <v>100</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
     </row>
     <row r="96" spans="2:5">
       <c r="B96" s="1" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="D96" s="1">
         <v>100</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
     </row>
     <row r="97" spans="2:5">
       <c r="B97" s="1" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="D97" s="1">
         <v>100</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
     </row>
     <row r="98" spans="2:5">
       <c r="B98" s="1" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="D98" s="1">
         <v>100</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
     </row>
     <row r="99" spans="2:5">
       <c r="B99" s="1" t="s">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="D99" s="1">
         <v>100</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
     </row>
     <row r="100" spans="2:5">
       <c r="B100" s="1" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="D100" s="1">
         <v>100</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>414</v>
+        <v>427</v>
       </c>
     </row>
     <row r="101" spans="2:5">
       <c r="B101" s="1" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="D101" s="1">
         <v>100</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
     </row>
     <row r="102" spans="2:5">
       <c r="B102" s="1" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="D102" s="1">
         <v>100</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
     </row>
     <row r="103" spans="2:5">
       <c r="B103" s="1" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="D103" s="1">
         <v>100</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
     </row>
     <row r="104" spans="2:5">
       <c r="B104" s="1" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="D104" s="1">
         <v>100</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
     </row>
     <row r="105" spans="2:5">
       <c r="B105" s="1" t="s">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="D105" s="1">
         <v>100</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>429</v>
+        <v>442</v>
       </c>
     </row>
     <row r="106" spans="2:5">
       <c r="B106" s="1" t="s">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="D106" s="1">
         <v>100</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>432</v>
+        <v>445</v>
       </c>
     </row>
     <row r="107" spans="2:5">
       <c r="B107" s="1" t="s">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="D107" s="1">
         <v>100</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>435</v>
+        <v>448</v>
       </c>
     </row>
     <row r="108" spans="2:5">
       <c r="B108" s="1" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="D108" s="1">
         <v>100</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>438</v>
+        <v>451</v>
       </c>
     </row>
     <row r="109" spans="2:5">
       <c r="B109" s="1" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="D109" s="1">
         <v>100</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
     </row>
     <row r="110" spans="2:5">
       <c r="B110" s="1" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="D110" s="1">
         <v>100</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
     </row>
     <row r="111" spans="2:5">
       <c r="B111" s="1" t="s">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="D111" s="1">
         <v>100</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
     </row>
     <row r="112" spans="2:5">
       <c r="B112" s="1" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="D112" s="1">
         <v>100</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
     </row>
     <row r="113" spans="2:5">
       <c r="B113" s="1" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="D113" s="1">
         <v>100</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>453</v>
+        <v>466</v>
       </c>
     </row>
     <row r="114" spans="2:5">
       <c r="B114" s="1" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="D114" s="1">
         <v>100</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>456</v>
+        <v>469</v>
       </c>
     </row>
     <row r="115" spans="2:5">
       <c r="B115" s="1" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="D115" s="1">
         <v>100</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
     </row>
     <row r="116" spans="2:5">
       <c r="B116" s="1" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="D116" s="1">
         <v>100</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>462</v>
+        <v>475</v>
       </c>
     </row>
     <row r="117" spans="2:5">
       <c r="B117" s="1" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="D117" s="1">
         <v>100</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
     </row>
     <row r="118" spans="2:5">
       <c r="B118" s="1" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="D118" s="1">
         <v>100</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>468</v>
+        <v>481</v>
       </c>
     </row>
     <row r="119" spans="2:5">
       <c r="B119" s="1" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="D119" s="1">
         <v>100</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
     </row>
     <row r="120" spans="2:5">
       <c r="B120" s="1" t="s">
-        <v>472</v>
+        <v>485</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="D120" s="1">
         <v>100</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
     </row>
     <row r="121" spans="2:5">
       <c r="B121" s="1" t="s">
-        <v>475</v>
+        <v>488</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="D121" s="1">
         <v>100</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>477</v>
+        <v>490</v>
       </c>
     </row>
     <row r="122" spans="2:5">
       <c r="B122" s="1" t="s">
-        <v>478</v>
+        <v>491</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>479</v>
+        <v>492</v>
       </c>
       <c r="D122" s="1">
         <v>100</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>480</v>
+        <v>493</v>
       </c>
     </row>
     <row r="123" spans="2:5">
       <c r="B123" s="1" t="s">
-        <v>481</v>
+        <v>494</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>482</v>
+        <v>495</v>
       </c>
       <c r="D123" s="1">
         <v>100</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>483</v>
+        <v>496</v>
       </c>
     </row>
     <row r="124" spans="2:5">
       <c r="B124" s="1" t="s">
-        <v>484</v>
+        <v>96</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="D124" s="1">
         <v>100</v>
@@ -5803,10 +5767,10 @@
     </row>
     <row r="125" spans="2:5">
       <c r="B125" s="1" t="s">
-        <v>486</v>
+        <v>101</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="D125" s="1">
         <v>100</v>
@@ -5817,570 +5781,570 @@
     </row>
     <row r="126" spans="2:5">
       <c r="B126" s="1" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="D126" s="1">
         <v>100</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
     </row>
     <row r="127" spans="2:5">
       <c r="B127" s="1" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="D127" s="1">
         <v>100</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
     </row>
     <row r="128" spans="2:5">
       <c r="B128" s="1" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="D128" s="1">
         <v>100</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
     </row>
     <row r="129" spans="2:5">
       <c r="B129" s="1" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="D129" s="1">
         <v>100</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
     </row>
     <row r="130" spans="2:5">
       <c r="B130" s="1" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="D130" s="1">
         <v>100</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
     </row>
     <row r="131" spans="2:5">
       <c r="B131" s="1" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="D131" s="1">
         <v>100</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
     </row>
     <row r="132" spans="2:5">
       <c r="B132" s="1" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="D132" s="1">
         <v>100</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
     </row>
     <row r="133" spans="2:5">
       <c r="B133" s="1" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="D133" s="1">
         <v>100</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
     </row>
     <row r="134" spans="2:5">
       <c r="B134" s="1" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="D134" s="1">
         <v>100</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>514</v>
+        <v>525</v>
       </c>
     </row>
     <row r="135" spans="2:5">
       <c r="B135" s="1" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="D135" s="1">
         <v>100</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
     </row>
     <row r="136" spans="2:5">
       <c r="B136" s="1" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="D136" s="1">
         <v>100</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
     </row>
     <row r="137" spans="2:5">
       <c r="B137" s="1" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="D137" s="1">
         <v>100</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
     </row>
     <row r="138" spans="2:5">
       <c r="B138" s="1" t="s">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="D138" s="1">
         <v>100</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
     </row>
     <row r="139" spans="2:5">
       <c r="B139" s="1" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="D139" s="1">
         <v>100</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
     </row>
     <row r="140" spans="2:5">
       <c r="B140" s="1" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="D140" s="1">
         <v>100</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
     </row>
     <row r="141" spans="2:5">
       <c r="B141" s="1" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="D141" s="1">
         <v>100</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>533</v>
+        <v>544</v>
       </c>
     </row>
     <row r="142" spans="2:5">
       <c r="B142" s="1" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="D142" s="1">
         <v>100</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>536</v>
+        <v>547</v>
       </c>
     </row>
     <row r="143" spans="2:5">
       <c r="B143" s="1" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="D143" s="1">
         <v>100</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
     </row>
     <row r="144" spans="2:5">
       <c r="B144" s="1" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="D144" s="1">
         <v>100</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
     </row>
     <row r="145" spans="2:5">
       <c r="B145" s="1" t="s">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="D145" s="1">
         <v>100</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>545</v>
+        <v>556</v>
       </c>
     </row>
     <row r="146" spans="2:5">
       <c r="B146" s="1" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="D146" s="1">
         <v>100</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>548</v>
+        <v>559</v>
       </c>
     </row>
     <row r="147" spans="2:5">
       <c r="B147" s="1" t="s">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="D147" s="1">
         <v>100</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>551</v>
+        <v>562</v>
       </c>
     </row>
     <row r="148" spans="2:5">
       <c r="B148" s="1" t="s">
-        <v>552</v>
+        <v>563</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="D148" s="1">
         <v>100</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>554</v>
+        <v>565</v>
       </c>
     </row>
     <row r="149" spans="2:5">
       <c r="B149" s="1" t="s">
-        <v>555</v>
+        <v>566</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="D149" s="1">
         <v>100</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
     </row>
     <row r="150" spans="2:5">
       <c r="B150" s="1" t="s">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>559</v>
+        <v>570</v>
       </c>
       <c r="D150" s="1">
         <v>100</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>560</v>
+        <v>571</v>
       </c>
     </row>
     <row r="151" spans="2:5">
       <c r="B151" s="1" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="D151" s="1">
         <v>100</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>562</v>
+        <v>573</v>
       </c>
     </row>
     <row r="152" spans="2:5">
       <c r="B152" s="1" t="s">
-        <v>563</v>
+        <v>574</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="D152" s="1">
         <v>100</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>565</v>
+        <v>576</v>
       </c>
     </row>
     <row r="153" spans="2:5">
       <c r="B153" s="1" t="s">
-        <v>566</v>
+        <v>577</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>567</v>
+        <v>578</v>
       </c>
       <c r="D153" s="1">
         <v>100</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>568</v>
+        <v>579</v>
       </c>
     </row>
     <row r="154" spans="2:5">
       <c r="B154" s="1" t="s">
-        <v>569</v>
+        <v>580</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>570</v>
+        <v>581</v>
       </c>
       <c r="D154" s="1">
         <v>100</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>571</v>
+        <v>582</v>
       </c>
     </row>
     <row r="155" spans="2:5">
       <c r="B155" s="1" t="s">
-        <v>572</v>
+        <v>583</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>573</v>
+        <v>584</v>
       </c>
       <c r="D155" s="1">
         <v>100</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
     </row>
     <row r="156" spans="2:5">
       <c r="B156" s="1" t="s">
-        <v>575</v>
+        <v>586</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>576</v>
+        <v>587</v>
       </c>
       <c r="D156" s="1">
         <v>100</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>577</v>
+        <v>588</v>
       </c>
     </row>
     <row r="157" spans="2:5">
       <c r="B157" s="1" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="D157" s="1">
         <v>100</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>580</v>
+        <v>591</v>
       </c>
     </row>
     <row r="158" spans="2:5">
       <c r="B158" s="1" t="s">
-        <v>581</v>
+        <v>592</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>582</v>
+        <v>593</v>
       </c>
       <c r="D158" s="1">
         <v>100</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
     </row>
     <row r="159" spans="2:5">
       <c r="B159" s="1" t="s">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>585</v>
+        <v>596</v>
       </c>
       <c r="D159" s="1">
         <v>100</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
     </row>
     <row r="160" spans="2:5">
       <c r="B160" s="1" t="s">
-        <v>587</v>
+        <v>598</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>588</v>
+        <v>599</v>
       </c>
       <c r="D160" s="1">
         <v>100</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>589</v>
+        <v>600</v>
       </c>
     </row>
     <row r="161" spans="2:5">
       <c r="B161" s="1" t="s">
-        <v>590</v>
+        <v>601</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>591</v>
+        <v>602</v>
       </c>
       <c r="D161" s="1">
         <v>100</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>592</v>
+        <v>603</v>
       </c>
     </row>
     <row r="162" spans="2:5">
       <c r="B162" s="1" t="s">
-        <v>593</v>
+        <v>604</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>594</v>
+        <v>605</v>
       </c>
       <c r="D162" s="1">
         <v>100</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>595</v>
+        <v>606</v>
       </c>
     </row>
     <row r="163" spans="2:5">
       <c r="B163" s="1" t="s">
-        <v>596</v>
+        <v>607</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>597</v>
+        <v>608</v>
       </c>
       <c r="D163" s="1">
         <v>100</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>598</v>
+        <v>609</v>
       </c>
     </row>
     <row r="164" spans="2:5">
       <c r="B164" s="1" t="s">
-        <v>599</v>
+        <v>610</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>600</v>
+        <v>611</v>
       </c>
       <c r="D164" s="1">
         <v>100</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>601</v>
+        <v>612</v>
       </c>
     </row>
     <row r="165" spans="2:5">
       <c r="B165" s="1" t="s">
-        <v>602</v>
+        <v>613</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>603</v>
+        <v>614</v>
       </c>
       <c r="D165" s="1">
         <v>100</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>604</v>
+        <v>615</v>
       </c>
     </row>
     <row r="166" spans="2:5">
       <c r="B166" s="1" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="D166" s="1">
         <v>100</v>
@@ -6390,7 +6354,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:B83">
+  <autoFilter ref="B1:B166">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6421,22 +6385,22 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>605</v>
+        <v>616</v>
       </c>
       <c r="D1" t="s">
-        <v>606</v>
+        <v>617</v>
       </c>
       <c r="E1" t="s">
-        <v>607</v>
+        <v>618</v>
       </c>
       <c r="F1" t="s">
-        <v>608</v>
+        <v>619</v>
       </c>
       <c r="G1" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="H1" t="s">
-        <v>610</v>
+        <v>621</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6444,25 +6408,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>611</v>
+        <v>622</v>
       </c>
       <c r="C2" t="s">
-        <v>612</v>
+        <v>623</v>
       </c>
       <c r="D2" t="s">
-        <v>613</v>
+        <v>624</v>
       </c>
       <c r="E2" t="s">
-        <v>614</v>
+        <v>625</v>
       </c>
       <c r="F2" t="s">
-        <v>615</v>
+        <v>626</v>
       </c>
       <c r="G2" t="s">
-        <v>616</v>
+        <v>627</v>
       </c>
       <c r="H2" t="s">
-        <v>617</v>
+        <v>628</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6473,19 +6437,19 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>618</v>
+        <v>629</v>
       </c>
       <c r="D3" t="s">
-        <v>618</v>
+        <v>629</v>
       </c>
       <c r="E3" t="s">
-        <v>618</v>
+        <v>629</v>
       </c>
       <c r="F3" t="s">
-        <v>618</v>
+        <v>629</v>
       </c>
       <c r="G3" t="s">
-        <v>618</v>
+        <v>629</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
@@ -6493,7 +6457,7 @@
     </row>
     <row r="4" spans="2:7">
       <c r="B4" t="s">
-        <v>619</v>
+        <v>630</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -6513,7 +6477,7 @@
     </row>
     <row r="5" spans="2:7">
       <c r="B5" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="C5">
         <v>95</v>
@@ -6533,7 +6497,7 @@
     </row>
     <row r="6" spans="2:7">
       <c r="B6" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C6">
         <v>80</v>
@@ -6553,7 +6517,7 @@
     </row>
     <row r="7" spans="2:7">
       <c r="B7" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="C7">
         <v>1000</v>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="622">
   <si>
     <t>##var</t>
   </si>
@@ -277,30 +277,18 @@
     <t>普通美食大组</t>
   </si>
   <si>
-    <t>sg_normal_1,sg_normal_2,sg_normal_3,sg_normal_4,sg_normal_5,sg_normal_6,sg_normal_7,sg_normal_8,sg_normal_9,sg_normal_10,sg_normal_11,sg_normal_12,sg_normal_13,sg_normal_14,sg_normal_15,sg_normal_16,sg_normal_17,sg_normal_18,sg_normal_19,sg_normal_20</t>
-  </si>
-  <si>
     <t>lg_normalHard</t>
   </si>
   <si>
     <t>普通困难美食大组</t>
   </si>
   <si>
-    <t>sg_normalHard_1,sg_normalHard_2,sg_normalHard_3,sg_normalHard_4,sg_normalHard_5,sg_normalHard_6,sg_normalHard_7,sg_normalHard_8,sg_normalHard_9,sg_normalHard_10,sg_normalHard_11,sg_normalHard_12,sg_normalHard_13,sg_normalHard_14,sg_normalHard_15,sg_normalHard_16,sg_normalHard_17,sg_normalHard_18,sg_normalHard_19,sg_normalHard_20,sg_normalHard_21,sg_normalHard_22,sg_normalHard_23,sg_normalHard_24,sg_normalHard_25,sg_normalHard_26,sg_normalHard_27,sg_normalHard_28,sg_normalHard_29,sg_normalHard_30,sg_normalHard_31,sg_normalHard_32,sg_normalHard_33,sg_normalHard_34,sg_normalHard_35,sg_normalHard_36,sg_normalHard_37,sg_normalHard_38,sg_normalHard_39,sg_normalHard_40,sg_normalHard_41,sg_normalHard_42,sg_normalHard_43,sg_normalHard_44,sg_normalHard_45,sg_normalHard_46,sg_normalHard_47,sg_normalHard_48,sg_normalHard_49,sg_normalHard_50,sg_normalHard_51,sg_normalHard_52,sg_normalHard_53,sg_normalHard_54,sg_normalHard_55,sg_normalHard_56,sg_normalHard_57,sg_normalHard_58,sg_normalHard_59,sg_normalHard_60,sg_normalHard_61,sg_normalHard_62,sg_normalHard_63,sg_normalHard_64,sg_normalHard_65,sg_normalHard_66,sg_normalHard_67,sg_normalHard_68,sg_normalHard_69,sg_normalHard_70,sg_normalHard_71,sg_normalHard_72,sg_normalHard_73,sg_normalHard_74,sg_normalHard_75,sg_normalHard_76,sg_normalHard_77,sg_normalHard_78,sg_normalHard_79,sg_normalHard_80</t>
-  </si>
-  <si>
     <t>lg_hard</t>
   </si>
   <si>
     <t>困难美食大组</t>
   </si>
   <si>
-    <t>0,50,100,200</t>
-  </si>
-  <si>
-    <t>sg_hard_1,sg_hard_2,sg_hard_3,sg_hard_4,sg_hard_5,sg_hard_6,sg_hard_7,sg_hard_8,sg_hard_9,sg_hard_10,sg_hard_11,sg_hard_12,sg_hard_13,sg_hard_14,sg_hard_15,sg_hard_16,sg_hard_17,sg_hard_18,sg_hard_19,sg_hard_20</t>
-  </si>
-  <si>
     <t>lg_event</t>
   </si>
   <si>
@@ -322,9 +310,6 @@
     <t>rule_reward_early,rule_reward_mid</t>
   </si>
   <si>
-    <t>50,50,50,50</t>
-  </si>
-  <si>
     <t>sg_reward_1</t>
   </si>
   <si>
@@ -334,30 +319,18 @@
     <t>普通事件大组</t>
   </si>
   <si>
-    <t>sg_normalEvent_1,sg_normalEvent_2,sg_normalEvent_3,sg_normalEvent_4,sg_normalEvent_5,sg_normalEvent_6,sg_normalEvent_7,sg_normalEvent_8,sg_normalEvent_9,sg_normalEvent_10,sg_normalEvent_11,sg_normalEvent_12,sg_normalEvent_13,sg_normalEvent_14,sg_normalEvent_15</t>
-  </si>
-  <si>
     <t>lg_normalHardEvent</t>
   </si>
   <si>
     <t>普通困难事件大组</t>
   </si>
   <si>
-    <t>sg_normalHardEvent_1,sg_normalHardEvent_2,sg_normalHardEvent_3,sg_normalHardEvent_4,sg_normalHardEvent_5,sg_normalHardEvent_6,sg_normalHardEvent_7,sg_normalHardEvent_8,sg_normalHardEvent_9,sg_normalHardEvent_10</t>
-  </si>
-  <si>
     <t>lg_hardEvent</t>
   </si>
   <si>
     <t>困难事件大组</t>
   </si>
   <si>
-    <t>0,50,100,100</t>
-  </si>
-  <si>
-    <t>sg_hardEvent_1,sg_hardEvent_2,sg_hardEvent_3,sg_hardEvent_4,sg_hardEvent_5,sg_hardEvent_6,sg_hardEvent_7,sg_hardEvent_8,sg_hardEvent_9,sg_hardEvent_10,sg_hardEvent_11,sg_hardEvent_12,sg_hardEvent_13,sg_hardEvent_14,sg_hardEvent_15</t>
-  </si>
-  <si>
     <t>lg_debug</t>
   </si>
   <si>
@@ -367,9 +340,6 @@
     <t>rule_debug_first</t>
   </si>
   <si>
-    <t>0,0,0,0</t>
-  </si>
-  <si>
     <t>mg_debug</t>
   </si>
   <si>
@@ -397,7 +367,7 @@
     <t>普通1</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_fragment,act_food_passive</t>
+    <t>act_food_gold|act_food_fragment|act_food_passive</t>
   </si>
   <si>
     <t>sg_normal_2</t>
@@ -406,7 +376,7 @@
     <t>普通2</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_fragment,act_food_active</t>
+    <t>act_food_gold|act_food_fragment|act_food_active</t>
   </si>
   <si>
     <t>sg_normalEvent_15</t>
@@ -418,7 +388,7 @@
     <t>普通3</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_fragment,act_food_dish</t>
+    <t>act_food_gold|act_food_fragment|act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHardEvent_1</t>
@@ -430,7 +400,7 @@
     <t>普通4</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_passive,act_food_active</t>
+    <t>act_food_gold|act_food_passive|act_food_active</t>
   </si>
   <si>
     <t>sg_hardEvent_1</t>
@@ -442,7 +412,7 @@
     <t>普通5</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_passive,act_food_dish</t>
+    <t>act_food_gold|act_food_passive|act_food_dish</t>
   </si>
   <si>
     <t>sg_normal_6</t>
@@ -451,7 +421,7 @@
     <t>普通6</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_active,act_food_dish</t>
+    <t>act_food_gold|act_food_active|act_food_dish</t>
   </si>
   <si>
     <t>sg_normal_7</t>
@@ -460,7 +430,7 @@
     <t>普通7</t>
   </si>
   <si>
-    <t>act_food_fragment,act_food_passive,act_food_active</t>
+    <t>act_food_fragment|act_food_passive|act_food_active</t>
   </si>
   <si>
     <t>sg_normal_8</t>
@@ -469,7 +439,7 @@
     <t>普通8</t>
   </si>
   <si>
-    <t>act_food_fragment,act_food_passive,act_food_dish</t>
+    <t>act_food_fragment|act_food_passive|act_food_dish</t>
   </si>
   <si>
     <t>sg_normal_9</t>
@@ -478,7 +448,7 @@
     <t>普通9</t>
   </si>
   <si>
-    <t>act_food_fragment,act_food_active,act_food_dish</t>
+    <t>act_food_fragment|act_food_active|act_food_dish</t>
   </si>
   <si>
     <t>sg_normal_10</t>
@@ -487,7 +457,7 @@
     <t>普通10</t>
   </si>
   <si>
-    <t>act_food_passive,act_food_active,act_food_dish</t>
+    <t>act_food_passive|act_food_active|act_food_dish</t>
   </si>
   <si>
     <t>sg_normal_11</t>
@@ -496,7 +466,7 @@
     <t>普通11</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_fragment</t>
+    <t>act_food_gold|act_food_fragment</t>
   </si>
   <si>
     <t>sg_normal_12</t>
@@ -505,7 +475,7 @@
     <t>普通12</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_passive</t>
+    <t>act_food_gold|act_food_passive</t>
   </si>
   <si>
     <t>sg_normal_13</t>
@@ -514,7 +484,7 @@
     <t>普通13</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_active</t>
+    <t>act_food_gold|act_food_active</t>
   </si>
   <si>
     <t>sg_normal_14</t>
@@ -523,7 +493,7 @@
     <t>普通14</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_dish</t>
+    <t>act_food_gold|act_food_dish</t>
   </si>
   <si>
     <t>sg_normal_15</t>
@@ -532,7 +502,7 @@
     <t>普通15</t>
   </si>
   <si>
-    <t>act_food_fragment,act_food_passive</t>
+    <t>act_food_fragment|act_food_passive</t>
   </si>
   <si>
     <t>sg_normal_16</t>
@@ -541,7 +511,7 @@
     <t>普通16</t>
   </si>
   <si>
-    <t>act_food_fragment,act_food_active</t>
+    <t>act_food_fragment|act_food_active</t>
   </si>
   <si>
     <t>sg_normal_17</t>
@@ -550,7 +520,7 @@
     <t>普通17</t>
   </si>
   <si>
-    <t>act_food_fragment,act_food_dish</t>
+    <t>act_food_fragment|act_food_dish</t>
   </si>
   <si>
     <t>普通困难混合大组</t>
@@ -562,7 +532,7 @@
     <t>普通18</t>
   </si>
   <si>
-    <t>act_food_passive,act_food_active</t>
+    <t>act_food_passive|act_food_active</t>
   </si>
   <si>
     <t>sg_normal_19</t>
@@ -571,7 +541,7 @@
     <t>普通19</t>
   </si>
   <si>
-    <t>act_food_passive,act_food_dish</t>
+    <t>act_food_passive|act_food_dish</t>
   </si>
   <si>
     <t>sg_normal_20</t>
@@ -580,7 +550,7 @@
     <t>普通20</t>
   </si>
   <si>
-    <t>act_food_active,act_food_dish</t>
+    <t>act_food_active|act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_1</t>
@@ -589,7 +559,7 @@
     <t>普通困难1</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_fragment,act_food_passive</t>
+    <t>act_food_hard_gold|act_food_fragment|act_food_passive</t>
   </si>
   <si>
     <t>sg_normalHard_2</t>
@@ -598,7 +568,7 @@
     <t>普通困难2</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_fragment,act_food_active</t>
+    <t>act_food_hard_gold|act_food_fragment|act_food_active</t>
   </si>
   <si>
     <t>sg_normalHard_3</t>
@@ -607,7 +577,7 @@
     <t>普通困难3</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_fragment,act_food_dish</t>
+    <t>act_food_hard_gold|act_food_fragment|act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_4</t>
@@ -616,7 +586,7 @@
     <t>普通困难4</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_passive,act_food_active</t>
+    <t>act_food_hard_gold|act_food_passive|act_food_active</t>
   </si>
   <si>
     <t>sg_normalHard_5</t>
@@ -625,7 +595,7 @@
     <t>普通困难5</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_passive,act_food_dish</t>
+    <t>act_food_hard_gold|act_food_passive|act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_6</t>
@@ -634,7 +604,7 @@
     <t>普通困难6</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_active,act_food_dish</t>
+    <t>act_food_hard_gold|act_food_active|act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_7</t>
@@ -643,7 +613,7 @@
     <t>普通困难7</t>
   </si>
   <si>
-    <t>act_food_hard_fragment,act_food_passive,act_food_active</t>
+    <t>act_food_hard_fragment|act_food_passive|act_food_active</t>
   </si>
   <si>
     <t>sg_normalHard_8</t>
@@ -652,7 +622,7 @@
     <t>普通困难8</t>
   </si>
   <si>
-    <t>act_food_hard_fragment,act_food_passive,act_food_dish</t>
+    <t>act_food_hard_fragment|act_food_passive|act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_9</t>
@@ -661,7 +631,7 @@
     <t>普通困难9</t>
   </si>
   <si>
-    <t>act_food_hard_fragment,act_food_active,act_food_dish</t>
+    <t>act_food_hard_fragment|act_food_active|act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_10</t>
@@ -670,7 +640,7 @@
     <t>普通困难10</t>
   </si>
   <si>
-    <t>act_food_hard_passive,act_food_active,act_food_dish</t>
+    <t>act_food_hard_passive|act_food_active|act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_11</t>
@@ -679,7 +649,7 @@
     <t>普通困难11</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_fragment</t>
+    <t>act_food_hard_gold|act_food_fragment</t>
   </si>
   <si>
     <t>sg_normalHard_12</t>
@@ -688,7 +658,7 @@
     <t>普通困难12</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_passive</t>
+    <t>act_food_hard_gold|act_food_passive</t>
   </si>
   <si>
     <t>sg_normalHard_13</t>
@@ -697,7 +667,7 @@
     <t>普通困难13</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_active</t>
+    <t>act_food_hard_gold|act_food_active</t>
   </si>
   <si>
     <t>sg_normalHard_14</t>
@@ -706,7 +676,7 @@
     <t>普通困难14</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_dish</t>
+    <t>act_food_hard_gold|act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_15</t>
@@ -715,7 +685,7 @@
     <t>普通困难15</t>
   </si>
   <si>
-    <t>act_food_hard_fragment,act_food_passive</t>
+    <t>act_food_hard_fragment|act_food_passive</t>
   </si>
   <si>
     <t>sg_normalHard_16</t>
@@ -724,7 +694,7 @@
     <t>普通困难16</t>
   </si>
   <si>
-    <t>act_food_hard_fragment,act_food_active</t>
+    <t>act_food_hard_fragment|act_food_active</t>
   </si>
   <si>
     <t>sg_normalHard_17</t>
@@ -733,7 +703,7 @@
     <t>普通困难17</t>
   </si>
   <si>
-    <t>act_food_hard_fragment,act_food_dish</t>
+    <t>act_food_hard_fragment|act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_18</t>
@@ -742,7 +712,7 @@
     <t>普通困难18</t>
   </si>
   <si>
-    <t>act_food_hard_passive,act_food_active</t>
+    <t>act_food_hard_passive|act_food_active</t>
   </si>
   <si>
     <t>sg_normalHard_19</t>
@@ -751,7 +721,7 @@
     <t>普通困难19</t>
   </si>
   <si>
-    <t>act_food_hard_passive,act_food_dish</t>
+    <t>act_food_hard_passive|act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_20</t>
@@ -760,7 +730,7 @@
     <t>普通困难20</t>
   </si>
   <si>
-    <t>act_food_hard_active,act_food_dish</t>
+    <t>act_food_hard_active|act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_21</t>
@@ -769,7 +739,7 @@
     <t>普通困难21</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_hard_fragment,act_food_passive</t>
+    <t>act_food_gold|act_food_hard_fragment|act_food_passive</t>
   </si>
   <si>
     <t>sg_normalHard_22</t>
@@ -778,7 +748,7 @@
     <t>普通困难22</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_hard_fragment,act_food_active</t>
+    <t>act_food_gold|act_food_hard_fragment|act_food_active</t>
   </si>
   <si>
     <t>sg_normalHard_23</t>
@@ -787,7 +757,7 @@
     <t>普通困难23</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_hard_fragment,act_food_dish</t>
+    <t>act_food_gold|act_food_hard_fragment|act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_24</t>
@@ -796,7 +766,7 @@
     <t>普通困难24</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_hard_passive,act_food_active</t>
+    <t>act_food_gold|act_food_hard_passive|act_food_active</t>
   </si>
   <si>
     <t>sg_normalHard_25</t>
@@ -805,7 +775,7 @@
     <t>普通困难25</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_hard_passive,act_food_dish</t>
+    <t>act_food_gold|act_food_hard_passive|act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_26</t>
@@ -814,7 +784,7 @@
     <t>普通困难26</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_hard_active,act_food_dish</t>
+    <t>act_food_gold|act_food_hard_active|act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_27</t>
@@ -823,7 +793,7 @@
     <t>普通困难27</t>
   </si>
   <si>
-    <t>act_food_fragment,act_food_hard_passive,act_food_active</t>
+    <t>act_food_fragment|act_food_hard_passive|act_food_active</t>
   </si>
   <si>
     <t>sg_normalHard_28</t>
@@ -832,7 +802,7 @@
     <t>普通困难28</t>
   </si>
   <si>
-    <t>act_food_fragment,act_food_hard_passive,act_food_dish</t>
+    <t>act_food_fragment|act_food_hard_passive|act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_29</t>
@@ -841,7 +811,7 @@
     <t>普通困难29</t>
   </si>
   <si>
-    <t>act_food_fragment,act_food_hard_active,act_food_dish</t>
+    <t>act_food_fragment|act_food_hard_active|act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_30</t>
@@ -850,7 +820,7 @@
     <t>普通困难30</t>
   </si>
   <si>
-    <t>act_food_passive,act_food_hard_active,act_food_dish</t>
+    <t>act_food_passive|act_food_hard_active|act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_31</t>
@@ -859,7 +829,7 @@
     <t>普通困难31</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_hard_fragment</t>
+    <t>act_food_gold|act_food_hard_fragment</t>
   </si>
   <si>
     <t>sg_normalHard_32</t>
@@ -868,7 +838,7 @@
     <t>普通困难32</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_hard_passive</t>
+    <t>act_food_gold|act_food_hard_passive</t>
   </si>
   <si>
     <t>sg_normalHard_33</t>
@@ -877,7 +847,7 @@
     <t>普通困难33</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_hard_active</t>
+    <t>act_food_gold|act_food_hard_active</t>
   </si>
   <si>
     <t>sg_normalHard_34</t>
@@ -886,7 +856,7 @@
     <t>普通困难34</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_hard_dish</t>
+    <t>act_food_gold|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_35</t>
@@ -895,7 +865,7 @@
     <t>普通困难35</t>
   </si>
   <si>
-    <t>act_food_fragment,act_food_hard_passive</t>
+    <t>act_food_fragment|act_food_hard_passive</t>
   </si>
   <si>
     <t>sg_normalHard_36</t>
@@ -904,7 +874,7 @@
     <t>普通困难36</t>
   </si>
   <si>
-    <t>act_food_fragment,act_food_hard_active</t>
+    <t>act_food_fragment|act_food_hard_active</t>
   </si>
   <si>
     <t>sg_normalHard_37</t>
@@ -913,7 +883,7 @@
     <t>普通困难37</t>
   </si>
   <si>
-    <t>act_food_fragment,act_food_hard_dish</t>
+    <t>act_food_fragment|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_38</t>
@@ -922,7 +892,7 @@
     <t>普通困难38</t>
   </si>
   <si>
-    <t>act_food_passive,act_food_hard_active</t>
+    <t>act_food_passive|act_food_hard_active</t>
   </si>
   <si>
     <t>sg_normalHard_39</t>
@@ -931,7 +901,7 @@
     <t>普通困难39</t>
   </si>
   <si>
-    <t>act_food_passive,act_food_hard_dish</t>
+    <t>act_food_passive|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_40</t>
@@ -940,7 +910,7 @@
     <t>普通困难40</t>
   </si>
   <si>
-    <t>act_food_active,act_food_hard_dish</t>
+    <t>act_food_active|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_41</t>
@@ -949,7 +919,7 @@
     <t>普通困难41</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_fragment,act_food_hard_passive</t>
+    <t>act_food_gold|act_food_fragment|act_food_hard_passive</t>
   </si>
   <si>
     <t>sg_normalHard_42</t>
@@ -958,7 +928,7 @@
     <t>普通困难42</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_fragment,act_food_hard_active</t>
+    <t>act_food_gold|act_food_fragment|act_food_hard_active</t>
   </si>
   <si>
     <t>sg_normalHard_43</t>
@@ -967,7 +937,7 @@
     <t>普通困难43</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_fragment,act_food_hard_dish</t>
+    <t>act_food_gold|act_food_fragment|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_44</t>
@@ -976,7 +946,7 @@
     <t>普通困难44</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_passive,act_food_hard_active</t>
+    <t>act_food_gold|act_food_passive|act_food_hard_active</t>
   </si>
   <si>
     <t>sg_normalHard_45</t>
@@ -985,7 +955,7 @@
     <t>普通困难45</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_passive,act_food_hard_dish</t>
+    <t>act_food_gold|act_food_passive|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_46</t>
@@ -994,7 +964,7 @@
     <t>普通困难46</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_active,act_food_hard_dish</t>
+    <t>act_food_gold|act_food_active|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_47</t>
@@ -1003,7 +973,7 @@
     <t>普通困难47</t>
   </si>
   <si>
-    <t>act_food_fragment,act_food_passive,act_food_hard_active</t>
+    <t>act_food_fragment|act_food_passive|act_food_hard_active</t>
   </si>
   <si>
     <t>sg_normalHard_48</t>
@@ -1012,7 +982,7 @@
     <t>普通困难48</t>
   </si>
   <si>
-    <t>act_food_fragment,act_food_passive,act_food_hard_dish</t>
+    <t>act_food_fragment|act_food_passive|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_49</t>
@@ -1021,7 +991,7 @@
     <t>普通困难49</t>
   </si>
   <si>
-    <t>act_food_fragment,act_food_active,act_food_hard_dish</t>
+    <t>act_food_fragment|act_food_active|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_50</t>
@@ -1030,7 +1000,7 @@
     <t>普通困难50</t>
   </si>
   <si>
-    <t>act_food_passive,act_food_active,act_food_hard_dish</t>
+    <t>act_food_passive|act_food_active|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_51</t>
@@ -1039,7 +1009,7 @@
     <t>普通困难51</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_hard_fragment,act_food_passive</t>
+    <t>act_food_hard_gold|act_food_hard_fragment|act_food_passive</t>
   </si>
   <si>
     <t>sg_normalHard_52</t>
@@ -1048,7 +1018,7 @@
     <t>普通困难52</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_hard_fragment,act_food_active</t>
+    <t>act_food_hard_gold|act_food_hard_fragment|act_food_active</t>
   </si>
   <si>
     <t>sg_normalHard_53</t>
@@ -1057,7 +1027,7 @@
     <t>普通困难53</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_hard_fragment,act_food_dish</t>
+    <t>act_food_hard_gold|act_food_hard_fragment|act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_54</t>
@@ -1066,7 +1036,7 @@
     <t>普通困难54</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_hard_passive,act_food_active</t>
+    <t>act_food_hard_gold|act_food_hard_passive|act_food_active</t>
   </si>
   <si>
     <t>sg_normalHard_55</t>
@@ -1075,7 +1045,7 @@
     <t>普通困难55</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_hard_passive,act_food_dish</t>
+    <t>act_food_hard_gold|act_food_hard_passive|act_food_dish</t>
   </si>
   <si>
     <t>sg_food_b</t>
@@ -1090,7 +1060,7 @@
     <t>普通困难56</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_hard_active,act_food_dish</t>
+    <t>act_food_hard_gold|act_food_hard_active|act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_57</t>
@@ -1099,7 +1069,7 @@
     <t>普通困难57</t>
   </si>
   <si>
-    <t>act_food_hard_fragment,act_food_hard_passive,act_food_active</t>
+    <t>act_food_hard_fragment|act_food_hard_passive|act_food_active</t>
   </si>
   <si>
     <t>sg_normalHard_58</t>
@@ -1108,7 +1078,7 @@
     <t>普通困难58</t>
   </si>
   <si>
-    <t>act_food_hard_fragment,act_food_hard_passive,act_food_dish</t>
+    <t>act_food_hard_fragment|act_food_hard_passive|act_food_dish</t>
   </si>
   <si>
     <t>sg_food_hard_a</t>
@@ -1123,7 +1093,7 @@
     <t>普通困难59</t>
   </si>
   <si>
-    <t>act_food_hard_fragment,act_food_hard_active,act_food_dish</t>
+    <t>act_food_hard_fragment|act_food_hard_active|act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_60</t>
@@ -1132,7 +1102,7 @@
     <t>普通困难60</t>
   </si>
   <si>
-    <t>act_food_hard_passive,act_food_hard_active,act_food_dish</t>
+    <t>act_food_hard_passive|act_food_hard_active|act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_61</t>
@@ -1141,7 +1111,7 @@
     <t>普通困难61</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_hard_fragment,act_food_hard_passive</t>
+    <t>act_food_gold|act_food_hard_fragment|act_food_hard_passive</t>
   </si>
   <si>
     <t>sg_food_hard_b</t>
@@ -1156,7 +1126,7 @@
     <t>普通困难62</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_hard_fragment,act_food_hard_active</t>
+    <t>act_food_gold|act_food_hard_fragment|act_food_hard_active</t>
   </si>
   <si>
     <t>sg_normalHard_63</t>
@@ -1165,7 +1135,7 @@
     <t>普通困难63</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_hard_fragment,act_food_hard_dish</t>
+    <t>act_food_gold|act_food_hard_fragment|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_64</t>
@@ -1174,7 +1144,7 @@
     <t>普通困难64</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_hard_passive,act_food_hard_active</t>
+    <t>act_food_gold|act_food_hard_passive|act_food_hard_active</t>
   </si>
   <si>
     <t>sg_event</t>
@@ -1186,7 +1156,7 @@
     <t>普通困难65</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_hard_passive,act_food_hard_dish</t>
+    <t>act_food_gold|act_food_hard_passive|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_66</t>
@@ -1195,7 +1165,7 @@
     <t>普通困难66</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_hard_active,act_food_hard_dish</t>
+    <t>act_food_gold|act_food_hard_active|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_67</t>
@@ -1204,7 +1174,7 @@
     <t>普通困难67</t>
   </si>
   <si>
-    <t>act_food_fragment,act_food_hard_passive,act_food_hard_active</t>
+    <t>act_food_fragment|act_food_hard_passive|act_food_hard_active</t>
   </si>
   <si>
     <t>sg_reward</t>
@@ -1216,7 +1186,7 @@
     <t>普通困难68</t>
   </si>
   <si>
-    <t>act_food_fragment,act_food_hard_passive,act_food_hard_dish</t>
+    <t>act_food_fragment|act_food_hard_passive|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_69</t>
@@ -1225,7 +1195,7 @@
     <t>普通困难69</t>
   </si>
   <si>
-    <t>act_food_fragment,act_food_hard_active,act_food_hard_dish</t>
+    <t>act_food_fragment|act_food_hard_active|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_debug</t>
@@ -1240,7 +1210,7 @@
     <t>普通困难70</t>
   </si>
   <si>
-    <t>act_food_passive,act_food_hard_active,act_food_hard_dish</t>
+    <t>act_food_passive|act_food_hard_active|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_71</t>
@@ -1249,7 +1219,7 @@
     <t>普通困难71</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_fragment,act_food_hard_passive</t>
+    <t>act_food_hard_gold|act_food_fragment|act_food_hard_passive</t>
   </si>
   <si>
     <t>sg_normalHard_72</t>
@@ -1258,7 +1228,7 @@
     <t>普通困难72</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_fragment,act_food_hard_active</t>
+    <t>act_food_hard_gold|act_food_fragment|act_food_hard_active</t>
   </si>
   <si>
     <t>sg_normalHard_73</t>
@@ -1267,7 +1237,7 @@
     <t>普通困难73</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_fragment,act_food_hard_dish</t>
+    <t>act_food_hard_gold|act_food_fragment|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_74</t>
@@ -1276,7 +1246,7 @@
     <t>普通困难74</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_passive,act_food_hard_active</t>
+    <t>act_food_hard_gold|act_food_passive|act_food_hard_active</t>
   </si>
   <si>
     <t>sg_normalHard_75</t>
@@ -1285,7 +1255,7 @@
     <t>普通困难75</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_passive,act_food_hard_dish</t>
+    <t>act_food_hard_gold|act_food_passive|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_76</t>
@@ -1294,7 +1264,7 @@
     <t>普通困难76</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_active,act_food_hard_dish</t>
+    <t>act_food_hard_gold|act_food_active|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_77</t>
@@ -1303,7 +1273,7 @@
     <t>普通困难77</t>
   </si>
   <si>
-    <t>act_food_hard_fragment,act_food_passive,act_food_hard_active</t>
+    <t>act_food_hard_fragment|act_food_passive|act_food_hard_active</t>
   </si>
   <si>
     <t>sg_normalHard_78</t>
@@ -1312,7 +1282,7 @@
     <t>普通困难78</t>
   </si>
   <si>
-    <t>act_food_hard_fragment,act_food_passive,act_food_hard_dish</t>
+    <t>act_food_hard_fragment|act_food_passive|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_79</t>
@@ -1321,7 +1291,7 @@
     <t>普通困难79</t>
   </si>
   <si>
-    <t>act_food_hard_fragment,act_food_active,act_food_hard_dish</t>
+    <t>act_food_hard_fragment|act_food_active|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_80</t>
@@ -1330,7 +1300,7 @@
     <t>普通困难80</t>
   </si>
   <si>
-    <t>act_food_hard_passive,act_food_active,act_food_hard_dish</t>
+    <t>act_food_hard_passive|act_food_active|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_hard_1</t>
@@ -1339,7 +1309,7 @@
     <t>困难1</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_hard_fragment,act_food_hard_passive</t>
+    <t>act_food_hard_gold|act_food_hard_fragment|act_food_hard_passive</t>
   </si>
   <si>
     <t>sg_hard_2</t>
@@ -1348,7 +1318,7 @@
     <t>困难2</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_hard_fragment,act_food_hard_active</t>
+    <t>act_food_hard_gold|act_food_hard_fragment|act_food_hard_active</t>
   </si>
   <si>
     <t>sg_hard_3</t>
@@ -1357,7 +1327,7 @@
     <t>困难3</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_hard_fragment,act_food_hard_dish</t>
+    <t>act_food_hard_gold|act_food_hard_fragment|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_hard_4</t>
@@ -1366,7 +1336,7 @@
     <t>困难4</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_hard_passive,act_food_hard_active</t>
+    <t>act_food_hard_gold|act_food_hard_passive|act_food_hard_active</t>
   </si>
   <si>
     <t>sg_hard_5</t>
@@ -1375,7 +1345,7 @@
     <t>困难5</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_hard_passive,act_food_hard_dish</t>
+    <t>act_food_hard_gold|act_food_hard_passive|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_hard_6</t>
@@ -1384,7 +1354,7 @@
     <t>困难6</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_hard_active,act_food_hard_dish</t>
+    <t>act_food_hard_gold|act_food_hard_active|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_hard_7</t>
@@ -1393,7 +1363,7 @@
     <t>困难7</t>
   </si>
   <si>
-    <t>act_food_hard_fragment,act_food_hard_passive,act_food_hard_active</t>
+    <t>act_food_hard_fragment|act_food_hard_passive|act_food_hard_active</t>
   </si>
   <si>
     <t>sg_hard_8</t>
@@ -1402,7 +1372,7 @@
     <t>困难8</t>
   </si>
   <si>
-    <t>act_food_hard_fragment,act_food_hard_passive,act_food_hard_dish</t>
+    <t>act_food_hard_fragment|act_food_hard_passive|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_hard_9</t>
@@ -1411,7 +1381,7 @@
     <t>困难9</t>
   </si>
   <si>
-    <t>act_food_hard_fragment,act_food_hard_active,act_food_hard_dish</t>
+    <t>act_food_hard_fragment|act_food_hard_active|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_hard_10</t>
@@ -1420,7 +1390,7 @@
     <t>困难10</t>
   </si>
   <si>
-    <t>act_food_hard_passive,act_food_hard_active,act_food_hard_dish</t>
+    <t>act_food_hard_passive|act_food_hard_active|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_hard_11</t>
@@ -1429,7 +1399,7 @@
     <t>困难11</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_hard_fragment</t>
+    <t>act_food_hard_gold|act_food_hard_fragment</t>
   </si>
   <si>
     <t>sg_hard_12</t>
@@ -1438,7 +1408,7 @@
     <t>困难12</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_hard_passive</t>
+    <t>act_food_hard_gold|act_food_hard_passive</t>
   </si>
   <si>
     <t>sg_hard_13</t>
@@ -1447,7 +1417,7 @@
     <t>困难13</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_hard_active</t>
+    <t>act_food_hard_gold|act_food_hard_active</t>
   </si>
   <si>
     <t>sg_hard_14</t>
@@ -1456,7 +1426,7 @@
     <t>困难14</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_hard_dish</t>
+    <t>act_food_hard_gold|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_hard_15</t>
@@ -1465,7 +1435,7 @@
     <t>困难15</t>
   </si>
   <si>
-    <t>act_food_hard_fragment,act_food_hard_passive</t>
+    <t>act_food_hard_fragment|act_food_hard_passive</t>
   </si>
   <si>
     <t>sg_hard_16</t>
@@ -1474,7 +1444,7 @@
     <t>困难16</t>
   </si>
   <si>
-    <t>act_food_hard_fragment,act_food_hard_active</t>
+    <t>act_food_hard_fragment|act_food_hard_active</t>
   </si>
   <si>
     <t>sg_hard_17</t>
@@ -1483,7 +1453,7 @@
     <t>困难17</t>
   </si>
   <si>
-    <t>act_food_hard_fragment,act_food_hard_dish</t>
+    <t>act_food_hard_fragment|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_hard_18</t>
@@ -1492,7 +1462,7 @@
     <t>困难18</t>
   </si>
   <si>
-    <t>act_food_hard_passive,act_food_hard_active</t>
+    <t>act_food_hard_passive|act_food_hard_active</t>
   </si>
   <si>
     <t>sg_hard_19</t>
@@ -1501,7 +1471,7 @@
     <t>困难19</t>
   </si>
   <si>
-    <t>act_food_hard_passive,act_food_hard_dish</t>
+    <t>act_food_hard_passive|act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_hard_20</t>
@@ -1510,7 +1480,7 @@
     <t>困难20</t>
   </si>
   <si>
-    <t>act_food_hard_active,act_food_hard_dish</t>
+    <t>act_food_hard_active|act_food_hard_dish</t>
   </si>
   <si>
     <t>事件1</t>
@@ -1525,7 +1495,7 @@
     <t>普通事件1</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_fragment,act_event</t>
+    <t>act_food_gold|act_food_fragment|act_event</t>
   </si>
   <si>
     <t>sg_normalEvent_2</t>
@@ -1534,7 +1504,7 @@
     <t>普通事件2</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_passive,act_event</t>
+    <t>act_food_gold|act_food_passive|act_event</t>
   </si>
   <si>
     <t>sg_normalEvent_3</t>
@@ -1543,7 +1513,7 @@
     <t>普通事件3</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_active,act_event</t>
+    <t>act_food_gold|act_food_active|act_event</t>
   </si>
   <si>
     <t>sg_normalEvent_4</t>
@@ -1552,7 +1522,7 @@
     <t>普通事件4</t>
   </si>
   <si>
-    <t>act_food_gold,act_food_dish,act_event</t>
+    <t>act_food_gold|act_food_dish|act_event</t>
   </si>
   <si>
     <t>sg_normalEvent_5</t>
@@ -1561,7 +1531,7 @@
     <t>普通事件5</t>
   </si>
   <si>
-    <t>act_food_fragment,act_food_passive,act_event</t>
+    <t>act_food_fragment|act_food_passive|act_event</t>
   </si>
   <si>
     <t>sg_normalEvent_6</t>
@@ -1570,7 +1540,7 @@
     <t>普通事件6</t>
   </si>
   <si>
-    <t>act_food_fragment,act_food_active,act_event</t>
+    <t>act_food_fragment|act_food_active|act_event</t>
   </si>
   <si>
     <t>sg_normalEvent_7</t>
@@ -1579,7 +1549,7 @@
     <t>普通事件7</t>
   </si>
   <si>
-    <t>act_food_fragment,act_food_dish,act_event</t>
+    <t>act_food_fragment|act_food_dish|act_event</t>
   </si>
   <si>
     <t>sg_normalEvent_8</t>
@@ -1588,7 +1558,7 @@
     <t>普通事件8</t>
   </si>
   <si>
-    <t>act_food_passive,act_food_active,act_event</t>
+    <t>act_food_passive|act_food_active|act_event</t>
   </si>
   <si>
     <t>sg_normalEvent_9</t>
@@ -1597,7 +1567,7 @@
     <t>普通事件9</t>
   </si>
   <si>
-    <t>act_food_passive,act_food_dish,act_event</t>
+    <t>act_food_passive|act_food_dish|act_event</t>
   </si>
   <si>
     <t>sg_normalEvent_10</t>
@@ -1606,7 +1576,7 @@
     <t>普通事件10</t>
   </si>
   <si>
-    <t>act_food_active,act_food_dish,act_event</t>
+    <t>act_food_active|act_food_dish|act_event</t>
   </si>
   <si>
     <t>sg_normalEvent_11</t>
@@ -1615,7 +1585,7 @@
     <t>普通事件11</t>
   </si>
   <si>
-    <t>act_food_gold,act_event</t>
+    <t>act_food_gold|act_event</t>
   </si>
   <si>
     <t>sg_normalEvent_12</t>
@@ -1624,7 +1594,7 @@
     <t>普通事件12</t>
   </si>
   <si>
-    <t>act_food_fragment,act_event</t>
+    <t>act_food_fragment|act_event</t>
   </si>
   <si>
     <t>sg_normalEvent_13</t>
@@ -1633,7 +1603,7 @@
     <t>普通事件13</t>
   </si>
   <si>
-    <t>act_food_passive,act_event</t>
+    <t>act_food_passive|act_event</t>
   </si>
   <si>
     <t>sg_normalEvent_14</t>
@@ -1642,19 +1612,19 @@
     <t>普通事件14</t>
   </si>
   <si>
-    <t>act_food_active,act_event</t>
+    <t>act_food_active|act_event</t>
   </si>
   <si>
     <t>普通事件15</t>
   </si>
   <si>
-    <t>act_food_dish,act_event</t>
+    <t>act_food_dish|act_event</t>
   </si>
   <si>
     <t>普通困难事件1</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_fragment,act_event</t>
+    <t>act_food_hard_gold|act_food_fragment|act_event</t>
   </si>
   <si>
     <t>sg_normalHardEvent_2</t>
@@ -1663,7 +1633,7 @@
     <t>普通困难事件2</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_passive,act_event</t>
+    <t>act_food_hard_gold|act_food_passive|act_event</t>
   </si>
   <si>
     <t>sg_normalHardEvent_3</t>
@@ -1672,7 +1642,7 @@
     <t>普通困难事件3</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_active,act_event</t>
+    <t>act_food_hard_gold|act_food_active|act_event</t>
   </si>
   <si>
     <t>sg_normalHardEvent_4</t>
@@ -1681,7 +1651,7 @@
     <t>普通困难事件4</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_dish,act_event</t>
+    <t>act_food_hard_gold|act_food_dish|act_event</t>
   </si>
   <si>
     <t>sg_normalHardEvent_5</t>
@@ -1690,7 +1660,7 @@
     <t>普通困难事件5</t>
   </si>
   <si>
-    <t>act_food_hard_fragment,act_food_passive,act_event</t>
+    <t>act_food_hard_fragment|act_food_passive|act_event</t>
   </si>
   <si>
     <t>sg_normalHardEvent_6</t>
@@ -1699,7 +1669,7 @@
     <t>普通困难事件6</t>
   </si>
   <si>
-    <t>act_food_hard_fragment,act_food_active,act_event</t>
+    <t>act_food_hard_fragment|act_food_active|act_event</t>
   </si>
   <si>
     <t>sg_normalHardEvent_7</t>
@@ -1708,7 +1678,7 @@
     <t>普通困难事件7</t>
   </si>
   <si>
-    <t>act_food_hard_fragment,act_food_dish,act_event</t>
+    <t>act_food_hard_fragment|act_food_dish|act_event</t>
   </si>
   <si>
     <t>sg_normalHardEvent_8</t>
@@ -1717,7 +1687,7 @@
     <t>普通困难事件8</t>
   </si>
   <si>
-    <t>act_food_hard_passive,act_food_active,act_event</t>
+    <t>act_food_hard_passive|act_food_active|act_event</t>
   </si>
   <si>
     <t>sg_normalHardEvent_9</t>
@@ -1726,7 +1696,7 @@
     <t>普通困难事件9</t>
   </si>
   <si>
-    <t>act_food_hard_passive,act_food_dish,act_event</t>
+    <t>act_food_hard_passive|act_food_dish|act_event</t>
   </si>
   <si>
     <t>sg_normalHardEvent_10</t>
@@ -1735,13 +1705,13 @@
     <t>普通困难事件10</t>
   </si>
   <si>
-    <t>act_food_hard_active,act_food_dish,act_event</t>
+    <t>act_food_hard_active|act_food_dish|act_event</t>
   </si>
   <si>
     <t>困难事件1</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_hard_fragment,act_event</t>
+    <t>act_food_hard_gold|act_food_hard_fragment|act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_2</t>
@@ -1750,7 +1720,7 @@
     <t>困难事件2</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_hard_passive,act_event</t>
+    <t>act_food_hard_gold|act_food_hard_passive|act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_3</t>
@@ -1759,7 +1729,7 @@
     <t>困难事件3</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_hard_active,act_event</t>
+    <t>act_food_hard_gold|act_food_hard_active|act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_4</t>
@@ -1768,7 +1738,7 @@
     <t>困难事件4</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_food_hard_dish,act_event</t>
+    <t>act_food_hard_gold|act_food_hard_dish|act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_5</t>
@@ -1777,7 +1747,7 @@
     <t>困难事件5</t>
   </si>
   <si>
-    <t>act_food_hard_fragment,act_food_hard_passive,act_event</t>
+    <t>act_food_hard_fragment|act_food_hard_passive|act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_6</t>
@@ -1786,7 +1756,7 @@
     <t>困难事件6</t>
   </si>
   <si>
-    <t>act_food_hard_fragment,act_food_hard_active,act_event</t>
+    <t>act_food_hard_fragment|act_food_hard_active|act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_7</t>
@@ -1795,7 +1765,7 @@
     <t>困难事件7</t>
   </si>
   <si>
-    <t>act_food_hard_fragment,act_food_hard_dish,act_event</t>
+    <t>act_food_hard_fragment|act_food_hard_dish|act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_8</t>
@@ -1804,7 +1774,7 @@
     <t>困难事件8</t>
   </si>
   <si>
-    <t>act_food_hard_passive,act_food_hard_active,act_event</t>
+    <t>act_food_hard_passive|act_food_hard_active|act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_9</t>
@@ -1813,7 +1783,7 @@
     <t>困难事件9</t>
   </si>
   <si>
-    <t>act_food_hard_passive,act_food_hard_dish,act_event</t>
+    <t>act_food_hard_passive|act_food_hard_dish|act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_10</t>
@@ -1822,7 +1792,7 @@
     <t>困难事件10</t>
   </si>
   <si>
-    <t>act_food_hard_active,act_food_hard_dish,act_event</t>
+    <t>act_food_hard_active|act_food_hard_dish|act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_11</t>
@@ -1831,7 +1801,7 @@
     <t>困难事件11</t>
   </si>
   <si>
-    <t>act_food_hard_gold,act_event</t>
+    <t>act_food_hard_gold|act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_12</t>
@@ -1840,7 +1810,7 @@
     <t>困难事件12</t>
   </si>
   <si>
-    <t>act_food_hard_fragment,act_event</t>
+    <t>act_food_hard_fragment|act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_13</t>
@@ -1849,7 +1819,7 @@
     <t>困难事件13</t>
   </si>
   <si>
-    <t>act_food_hard_passive,act_event</t>
+    <t>act_food_hard_passive|act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_14</t>
@@ -1858,7 +1828,7 @@
     <t>困难事件14</t>
   </si>
   <si>
-    <t>act_food_hard_active,act_event</t>
+    <t>act_food_hard_active|act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_15</t>
@@ -1867,7 +1837,7 @@
     <t>困难事件15</t>
   </si>
   <si>
-    <t>act_food_hard_dish,act_event</t>
+    <t>act_food_hard_dish|act_event</t>
   </si>
   <si>
     <t>priority</t>
@@ -3399,13 +3369,18 @@
       <c r="C4" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="2">
-        <v>400300200150</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G4" s="1"/>
+      <c r="E4" s="2" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,I4:L4)</f>
+        <v>400,300,200,150</v>
+      </c>
+      <c r="F4" s="3" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,small_group!B4:B23)</f>
+        <v>sg_normal_1|sg_normal_2|sg_normal_3|sg_normal_4|sg_normal_5|sg_normal_6|sg_normal_7|sg_normal_8|sg_normal_9|sg_normal_10|sg_normal_11|sg_normal_12|sg_normal_13|sg_normal_14|sg_normal_15|sg_normal_16|sg_normal_17|sg_normal_18|sg_normal_19|sg_normal_20</v>
+      </c>
+      <c r="G4" s="1" t="str">
+        <f>""</f>
+        <v/>
+      </c>
       <c r="I4" s="1">
         <v>400</v>
       </c>
@@ -3421,18 +3396,23 @@
     </row>
     <row r="5" spans="2:12">
       <c r="B5" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" s="2">
-        <v>200200250200</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G5" s="1"/>
+      <c r="E5" s="2" t="str">
+        <f t="shared" ref="E5:E12" si="0">_xlfn.TEXTJOIN(",",TRUE,I5:L5)</f>
+        <v>200,200,250,200</v>
+      </c>
+      <c r="F5" s="3" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,small_group!B24:B103)</f>
+        <v>sg_normalHard_1|sg_normalHard_2|sg_normalHard_3|sg_normalHard_4|sg_normalHard_5|sg_normalHard_6|sg_normalHard_7|sg_normalHard_8|sg_normalHard_9|sg_normalHard_10|sg_normalHard_11|sg_normalHard_12|sg_normalHard_13|sg_normalHard_14|sg_normalHard_15|sg_normalHard_16|sg_normalHard_17|sg_normalHard_18|sg_normalHard_19|sg_normalHard_20|sg_normalHard_21|sg_normalHard_22|sg_normalHard_23|sg_normalHard_24|sg_normalHard_25|sg_normalHard_26|sg_normalHard_27|sg_normalHard_28|sg_normalHard_29|sg_normalHard_30|sg_normalHard_31|sg_normalHard_32|sg_normalHard_33|sg_normalHard_34|sg_normalHard_35|sg_normalHard_36|sg_normalHard_37|sg_normalHard_38|sg_normalHard_39|sg_normalHard_40|sg_normalHard_41|sg_normalHard_42|sg_normalHard_43|sg_normalHard_44|sg_normalHard_45|sg_normalHard_46|sg_normalHard_47|sg_normalHard_48|sg_normalHard_49|sg_normalHard_50|sg_normalHard_51|sg_normalHard_52|sg_normalHard_53|sg_normalHard_54|sg_normalHard_55|sg_normalHard_56|sg_normalHard_57|sg_normalHard_58|sg_normalHard_59|sg_normalHard_60|sg_normalHard_61|sg_normalHard_62|sg_normalHard_63|sg_normalHard_64|sg_normalHard_65|sg_normalHard_66|sg_normalHard_67|sg_normalHard_68|sg_normalHard_69|sg_normalHard_70|sg_normalHard_71|sg_normalHard_72|sg_normalHard_73|sg_normalHard_74|sg_normalHard_75|sg_normalHard_76|sg_normalHard_77|sg_normalHard_78|sg_normalHard_79|sg_normalHard_80</v>
+      </c>
+      <c r="G5" s="1" t="str">
+        <f t="shared" ref="G5:G12" si="1">""</f>
+        <v/>
+      </c>
       <c r="I5" s="1">
         <v>200</v>
       </c>
@@ -3448,18 +3428,23 @@
     </row>
     <row r="6" spans="2:12">
       <c r="B6" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G6" s="1"/>
+        <v>88</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>0,50,100,200</v>
+      </c>
+      <c r="F6" s="3" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,small_group!B104:B123)</f>
+        <v>sg_hard_1|sg_hard_2|sg_hard_3|sg_hard_4|sg_hard_5|sg_hard_6|sg_hard_7|sg_hard_8|sg_hard_9|sg_hard_10|sg_hard_11|sg_hard_12|sg_hard_13|sg_hard_14|sg_hard_15|sg_hard_16|sg_hard_17|sg_hard_18|sg_hard_19|sg_hard_20</v>
+      </c>
+      <c r="G6" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="I6" s="1">
         <v>0</v>
       </c>
@@ -3475,21 +3460,25 @@
     </row>
     <row r="7" spans="2:12">
       <c r="B7" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E7" s="2">
-        <v>100100100100</v>
+        <v>91</v>
+      </c>
+      <c r="E7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>100,100,100,100</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="G7" s="1"/>
+        <v>92</v>
+      </c>
+      <c r="G7" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="I7" s="1">
         <v>100</v>
       </c>
@@ -3505,21 +3494,25 @@
     </row>
     <row r="8" spans="2:12">
       <c r="B8" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
+      </c>
+      <c r="E8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>50,50,50,50</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="G8" s="1"/>
+        <v>96</v>
+      </c>
+      <c r="G8" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="I8" s="1">
         <v>50</v>
       </c>
@@ -3535,18 +3528,23 @@
     </row>
     <row r="9" spans="2:12">
       <c r="B9" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" s="2">
-        <v>150150100100</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="G9" s="1"/>
+        <v>98</v>
+      </c>
+      <c r="E9" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>150,150,100,100</v>
+      </c>
+      <c r="F9" s="3" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,small_group!B126:B140)</f>
+        <v>sg_normalEvent_1|sg_normalEvent_2|sg_normalEvent_3|sg_normalEvent_4|sg_normalEvent_5|sg_normalEvent_6|sg_normalEvent_7|sg_normalEvent_8|sg_normalEvent_9|sg_normalEvent_10|sg_normalEvent_11|sg_normalEvent_12|sg_normalEvent_13|sg_normalEvent_14|sg_normalEvent_15</v>
+      </c>
+      <c r="G9" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="I9" s="1">
         <v>150</v>
       </c>
@@ -3562,18 +3560,23 @@
     </row>
     <row r="10" spans="2:12">
       <c r="B10" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E10" s="2">
-        <v>100100100100</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G10" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="E10" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>100,100,100,100</v>
+      </c>
+      <c r="F10" s="3" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,small_group!B141:B150)</f>
+        <v>sg_normalHardEvent_1|sg_normalHardEvent_2|sg_normalHardEvent_3|sg_normalHardEvent_4|sg_normalHardEvent_5|sg_normalHardEvent_6|sg_normalHardEvent_7|sg_normalHardEvent_8|sg_normalHardEvent_9|sg_normalHardEvent_10</v>
+      </c>
+      <c r="G10" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="I10" s="1">
         <v>100</v>
       </c>
@@ -3589,18 +3592,23 @@
     </row>
     <row r="11" spans="2:12">
       <c r="B11" s="1" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G11" s="1"/>
+        <v>102</v>
+      </c>
+      <c r="E11" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>0,50,100,100</v>
+      </c>
+      <c r="F11" s="3" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,small_group!B151:B165)</f>
+        <v>sg_hardEvent_1|sg_hardEvent_2|sg_hardEvent_3|sg_hardEvent_4|sg_hardEvent_5|sg_hardEvent_6|sg_hardEvent_7|sg_hardEvent_8|sg_hardEvent_9|sg_hardEvent_10|sg_hardEvent_11|sg_hardEvent_12|sg_hardEvent_13|sg_hardEvent_14|sg_hardEvent_15</v>
+      </c>
+      <c r="G11" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="I11" s="1">
         <v>0</v>
       </c>
@@ -3616,21 +3624,25 @@
     </row>
     <row r="12" spans="2:12">
       <c r="B12" s="1" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>115</v>
+        <v>105</v>
+      </c>
+      <c r="E12" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>0,0,0,0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G12" s="1"/>
+        <v>106</v>
+      </c>
+      <c r="G12" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="I12" s="1">
         <v>0</v>
       </c>
@@ -3683,10 +3695,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3694,16 +3706,16 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3725,165 +3737,165 @@
     </row>
     <row r="4" spans="2:5">
       <c r="B4" s="1" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D4" s="1">
         <v>100</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="2:18">
       <c r="B5" s="1" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D5" s="1">
         <v>100</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="2:18">
       <c r="B6" s="1" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D6" s="1">
         <v>100</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="2:18">
       <c r="B7" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D7" s="1">
         <v>100</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="B8" s="1" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="B11" s="1" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="D11" s="1">
         <v>100</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="B12" s="1" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="D12" s="1">
         <v>100</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="1" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D13" s="1">
         <v>100</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="1" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="D14" s="1">
         <v>100</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>83</v>
@@ -3894,142 +3906,142 @@
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="1" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="D15" s="1">
         <v>100</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="L15" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="M15" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="1" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="D16" s="1">
         <v>100</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="2:13">
       <c r="B17" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="D17" s="1">
         <v>100</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="D18" s="1">
         <v>100</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="1" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="D19" s="1">
         <v>100</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="1" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D20" s="1">
         <v>100</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="2:20">
       <c r="B21" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D21" s="1">
         <v>100</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>20</v>
@@ -4043,22 +4055,22 @@
     </row>
     <row r="22" spans="2:20">
       <c r="B22" s="1" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D22" s="1">
         <v>100</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>20</v>
@@ -4072,16 +4084,16 @@
     </row>
     <row r="23" spans="2:20">
       <c r="B23" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="D23" s="1">
         <v>100</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="R23" s="1" t="s">
         <v>20</v>
@@ -4095,16 +4107,16 @@
     </row>
     <row r="24" spans="2:20">
       <c r="B24" s="1" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="D24" s="1">
         <v>100</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="R24" s="1" t="s">
         <v>20</v>
@@ -4118,16 +4130,16 @@
     </row>
     <row r="25" spans="2:20">
       <c r="B25" s="1" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D25" s="1">
         <v>100</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>20</v>
@@ -4141,16 +4153,16 @@
     </row>
     <row r="26" spans="2:20">
       <c r="B26" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="D26" s="1">
         <v>100</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>20</v>
@@ -4164,16 +4176,16 @@
     </row>
     <row r="27" spans="2:20">
       <c r="B27" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D27" s="1">
         <v>100</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="R27" s="1" t="s">
         <v>25</v>
@@ -4187,16 +4199,16 @@
     </row>
     <row r="28" spans="2:20">
       <c r="B28" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="D28" s="1">
         <v>100</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="R28" s="1" t="s">
         <v>25</v>
@@ -4210,16 +4222,16 @@
     </row>
     <row r="29" spans="2:20">
       <c r="B29" s="1" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="D29" s="1">
         <v>100</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="R29" s="1" t="s">
         <v>25</v>
@@ -4233,16 +4245,16 @@
     </row>
     <row r="30" spans="2:20">
       <c r="B30" s="1" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="D30" s="1">
         <v>100</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="R30" s="1" t="s">
         <v>28</v>
@@ -4256,16 +4268,16 @@
     </row>
     <row r="31" spans="2:19">
       <c r="B31" s="1" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="D31" s="1">
         <v>100</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="R31" s="1" t="s">
         <v>20</v>
@@ -4276,16 +4288,16 @@
     </row>
     <row r="32" spans="2:19">
       <c r="B32" s="1" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="D32" s="1">
         <v>100</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>20</v>
@@ -4296,16 +4308,16 @@
     </row>
     <row r="33" spans="2:19">
       <c r="B33" s="1" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="D33" s="1">
         <v>100</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="R33" s="1" t="s">
         <v>20</v>
@@ -4316,16 +4328,16 @@
     </row>
     <row r="34" spans="2:19">
       <c r="B34" s="1" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="D34" s="1">
         <v>100</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="R34" s="1" t="s">
         <v>20</v>
@@ -4336,16 +4348,16 @@
     </row>
     <row r="35" spans="2:19">
       <c r="B35" s="1" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="D35" s="1">
         <v>100</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>25</v>
@@ -4356,16 +4368,16 @@
     </row>
     <row r="36" spans="2:19">
       <c r="B36" s="1" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="D36" s="1">
         <v>100</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="R36" s="1" t="s">
         <v>25</v>
@@ -4376,16 +4388,16 @@
     </row>
     <row r="37" spans="2:19">
       <c r="B37" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="D37" s="1">
         <v>100</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>20</v>
@@ -4399,16 +4411,16 @@
     </row>
     <row r="38" spans="2:19">
       <c r="B38" s="1" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="D38" s="1">
         <v>100</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>25</v>
@@ -4422,16 +4434,16 @@
     </row>
     <row r="39" spans="2:19">
       <c r="B39" s="1" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="D39" s="1">
         <v>100</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>28</v>
@@ -4445,16 +4457,16 @@
     </row>
     <row r="40" spans="2:19">
       <c r="B40" s="1" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="D40" s="1">
         <v>100</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>31</v>
@@ -4468,16 +4480,16 @@
     </row>
     <row r="41" spans="2:12">
       <c r="B41" s="1" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="D41" s="1">
         <v>100</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="L41" s="1" t="s">
         <v>34</v>
@@ -4485,30 +4497,30 @@
     </row>
     <row r="42" spans="2:5">
       <c r="B42" s="1" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="D42" s="1">
         <v>100</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
     </row>
     <row r="43" spans="2:12">
       <c r="B43" s="1" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="D43" s="1">
         <v>100</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="L43" s="1" t="s">
         <v>37</v>
@@ -4516,16 +4528,16 @@
     </row>
     <row r="44" spans="2:12">
       <c r="B44" s="1" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="D44" s="1">
         <v>100</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="L44" s="1" t="s">
         <v>41</v>
@@ -4533,16 +4545,16 @@
     </row>
     <row r="45" spans="2:12">
       <c r="B45" s="1" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="D45" s="1">
         <v>100</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>44</v>
@@ -4550,16 +4562,16 @@
     </row>
     <row r="46" spans="2:12">
       <c r="B46" s="1" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D46" s="1">
         <v>100</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>47</v>
@@ -4567,16 +4579,16 @@
     </row>
     <row r="47" spans="2:12">
       <c r="B47" s="1" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="D47" s="1">
         <v>100</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="L47" s="1" t="s">
         <v>50</v>
@@ -4584,16 +4596,16 @@
     </row>
     <row r="48" spans="2:12">
       <c r="B48" s="1" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="D48" s="1">
         <v>100</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>53</v>
@@ -4601,16 +4613,16 @@
     </row>
     <row r="49" spans="2:12">
       <c r="B49" s="1" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="D49" s="1">
         <v>100</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="L49" s="1" t="s">
         <v>57</v>
@@ -4618,414 +4630,414 @@
     </row>
     <row r="50" spans="2:5">
       <c r="B50" s="1" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="D50" s="1">
         <v>100</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
     </row>
     <row r="51" spans="2:5">
       <c r="B51" s="1" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="D51" s="1">
         <v>100</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
     </row>
     <row r="52" spans="2:5">
       <c r="B52" s="1" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D52" s="1">
         <v>100</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
     </row>
     <row r="53" spans="2:5">
       <c r="B53" s="1" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="D53" s="1">
         <v>100</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
     </row>
     <row r="54" spans="2:5">
       <c r="B54" s="1" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="D54" s="1">
         <v>100</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
     </row>
     <row r="55" spans="2:5">
       <c r="B55" s="1" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="D55" s="1">
         <v>100</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
     </row>
     <row r="56" spans="2:5">
       <c r="B56" s="1" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="D56" s="1">
         <v>100</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
     </row>
     <row r="57" spans="2:5">
       <c r="B57" s="1" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="D57" s="1">
         <v>100</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
     </row>
     <row r="58" spans="2:5">
       <c r="B58" s="1" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="D58" s="1">
         <v>100</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
     </row>
     <row r="59" spans="2:5">
       <c r="B59" s="1" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="D59" s="1">
         <v>100</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
     </row>
     <row r="60" spans="2:5">
       <c r="B60" s="1" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="D60" s="1">
         <v>100</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
     </row>
     <row r="61" spans="2:5">
       <c r="B61" s="1" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D61" s="1">
         <v>100</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
     </row>
     <row r="62" spans="2:5">
       <c r="B62" s="1" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="D62" s="1">
         <v>100</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
     </row>
     <row r="63" spans="2:5">
       <c r="B63" s="1" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="D63" s="1">
         <v>100</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
     </row>
     <row r="64" spans="2:5">
       <c r="B64" s="1" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="D64" s="1">
         <v>100</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
     </row>
     <row r="65" spans="2:5">
       <c r="B65" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="D65" s="1">
         <v>100</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
     </row>
     <row r="66" spans="2:5">
       <c r="B66" s="1" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="D66" s="1">
         <v>100</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
     </row>
     <row r="67" spans="2:5">
       <c r="B67" s="1" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D67" s="1">
         <v>100</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
     </row>
     <row r="68" spans="2:5">
       <c r="B68" s="1" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="D68" s="1">
         <v>100</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
     </row>
     <row r="69" spans="2:5">
       <c r="B69" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="D69" s="1">
         <v>100</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
     </row>
     <row r="70" spans="2:5">
       <c r="B70" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="D70" s="1">
         <v>100</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
     </row>
     <row r="71" spans="2:5">
       <c r="B71" s="1" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="D71" s="1">
         <v>100</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
     </row>
     <row r="72" spans="2:5">
       <c r="B72" s="1" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="D72" s="1">
         <v>100</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
     </row>
     <row r="73" spans="2:5">
       <c r="B73" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="D73" s="1">
         <v>100</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
     </row>
     <row r="74" spans="2:5">
       <c r="B74" s="1" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="D74" s="1">
         <v>100</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
     </row>
     <row r="75" spans="2:5">
       <c r="B75" s="1" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="D75" s="1">
         <v>100</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
     </row>
     <row r="76" spans="2:5">
       <c r="B76" s="1" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="D76" s="1">
         <v>100</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77" spans="2:5">
       <c r="B77" s="1" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="D77" s="1">
         <v>100</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="2:20">
       <c r="B78" s="1" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D78" s="1">
         <v>100</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="R78" s="1" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="S78" s="1">
         <v>80</v>
@@ -5036,16 +5048,16 @@
     </row>
     <row r="79" spans="2:20">
       <c r="B79" s="1" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="D79" s="1">
         <v>100</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="T79" s="1" t="s">
         <v>31</v>
@@ -5053,16 +5065,16 @@
     </row>
     <row r="80" spans="2:20">
       <c r="B80" s="1" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="D80" s="1">
         <v>100</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="T80" s="1" t="s">
         <v>34</v>
@@ -5070,22 +5082,22 @@
     </row>
     <row r="81" spans="2:20">
       <c r="B81" s="1" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="D81" s="1">
         <v>100</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="Q81" s="1" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="R81" s="1" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="S81" s="1">
         <v>100</v>
@@ -5096,16 +5108,16 @@
     </row>
     <row r="82" spans="2:20">
       <c r="B82" s="1" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="D82" s="1">
         <v>100</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="T82" s="1" t="s">
         <v>50</v>
@@ -5113,16 +5125,16 @@
     </row>
     <row r="83" spans="2:20">
       <c r="B83" s="1" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D83" s="1">
         <v>100</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="T83" s="1" t="s">
         <v>44</v>
@@ -5130,22 +5142,22 @@
     </row>
     <row r="84" spans="2:20">
       <c r="B84" s="1" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="D84" s="1">
         <v>100</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="Q84" s="1" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="R84" s="1" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="S84" s="1">
         <v>80</v>
@@ -5156,16 +5168,16 @@
     </row>
     <row r="85" spans="2:20">
       <c r="B85" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="D85" s="1">
         <v>100</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="T85" s="1" t="s">
         <v>47</v>
@@ -5173,16 +5185,16 @@
     </row>
     <row r="86" spans="2:20">
       <c r="B86" s="1" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="D86" s="1">
         <v>100</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="T86" s="1" t="s">
         <v>50</v>
@@ -5190,19 +5202,19 @@
     </row>
     <row r="87" spans="2:20">
       <c r="B87" s="1" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="D87" s="1">
         <v>100</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="Q87" s="1" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="R87" s="1" t="s">
         <v>54</v>
@@ -5216,16 +5228,16 @@
     </row>
     <row r="88" spans="2:20">
       <c r="B88" s="1" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="D88" s="1">
         <v>100</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="T88" s="1" t="s">
         <v>20</v>
@@ -5233,16 +5245,16 @@
     </row>
     <row r="89" spans="2:20">
       <c r="B89" s="1" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="D89" s="1">
         <v>100</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="T89" s="1" t="s">
         <v>34</v>
@@ -5250,19 +5262,19 @@
     </row>
     <row r="90" spans="2:20">
       <c r="B90" s="1" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="D90" s="1">
         <v>100</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="Q90" s="1" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="R90" s="1" t="s">
         <v>58</v>
@@ -5276,16 +5288,16 @@
     </row>
     <row r="91" spans="2:20">
       <c r="B91" s="1" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="D91" s="1">
         <v>100</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="T91" s="1" t="s">
         <v>61</v>
@@ -5293,22 +5305,22 @@
     </row>
     <row r="92" spans="2:20">
       <c r="B92" s="1" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="D92" s="1">
         <v>100</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="Q92" s="1" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="R92" s="1" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="S92" s="1">
         <v>100</v>
@@ -5319,444 +5331,444 @@
     </row>
     <row r="93" spans="2:5">
       <c r="B93" s="1" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="D93" s="1">
         <v>100</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
     </row>
     <row r="94" spans="2:5">
       <c r="B94" s="1" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="D94" s="1">
         <v>100</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
     </row>
     <row r="95" spans="2:5">
       <c r="B95" s="1" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="D95" s="1">
         <v>100</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
     </row>
     <row r="96" spans="2:5">
       <c r="B96" s="1" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="D96" s="1">
         <v>100</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
     </row>
     <row r="97" spans="2:5">
       <c r="B97" s="1" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="D97" s="1">
         <v>100</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
     </row>
     <row r="98" spans="2:5">
       <c r="B98" s="1" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="D98" s="1">
         <v>100</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
     </row>
     <row r="99" spans="2:5">
       <c r="B99" s="1" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="D99" s="1">
         <v>100</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
     </row>
     <row r="100" spans="2:5">
       <c r="B100" s="1" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="D100" s="1">
         <v>100</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
     </row>
     <row r="101" spans="2:5">
       <c r="B101" s="1" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="D101" s="1">
         <v>100</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
     </row>
     <row r="102" spans="2:5">
       <c r="B102" s="1" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="D102" s="1">
         <v>100</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
     </row>
     <row r="103" spans="2:5">
       <c r="B103" s="1" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="D103" s="1">
         <v>100</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
     </row>
     <row r="104" spans="2:5">
       <c r="B104" s="1" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="D104" s="1">
         <v>100</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
     </row>
     <row r="105" spans="2:5">
       <c r="B105" s="1" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="D105" s="1">
         <v>100</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
     </row>
     <row r="106" spans="2:5">
       <c r="B106" s="1" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="D106" s="1">
         <v>100</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
     </row>
     <row r="107" spans="2:5">
       <c r="B107" s="1" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="D107" s="1">
         <v>100</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
     </row>
     <row r="108" spans="2:5">
       <c r="B108" s="1" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="D108" s="1">
         <v>100</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
     </row>
     <row r="109" spans="2:5">
       <c r="B109" s="1" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="D109" s="1">
         <v>100</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
     </row>
     <row r="110" spans="2:5">
       <c r="B110" s="1" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="D110" s="1">
         <v>100</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="111" spans="2:5">
       <c r="B111" s="1" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="D111" s="1">
         <v>100</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
     </row>
     <row r="112" spans="2:5">
       <c r="B112" s="1" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="D112" s="1">
         <v>100</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
     </row>
     <row r="113" spans="2:5">
       <c r="B113" s="1" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="D113" s="1">
         <v>100</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
     </row>
     <row r="114" spans="2:5">
       <c r="B114" s="1" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="D114" s="1">
         <v>100</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
     </row>
     <row r="115" spans="2:5">
       <c r="B115" s="1" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="D115" s="1">
         <v>100</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
     </row>
     <row r="116" spans="2:5">
       <c r="B116" s="1" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="D116" s="1">
         <v>100</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
     </row>
     <row r="117" spans="2:5">
       <c r="B117" s="1" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="D117" s="1">
         <v>100</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
     </row>
     <row r="118" spans="2:5">
       <c r="B118" s="1" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="D118" s="1">
         <v>100</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
     </row>
     <row r="119" spans="2:5">
       <c r="B119" s="1" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="D119" s="1">
         <v>100</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
     </row>
     <row r="120" spans="2:5">
       <c r="B120" s="1" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="D120" s="1">
         <v>100</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
     </row>
     <row r="121" spans="2:5">
       <c r="B121" s="1" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="D121" s="1">
         <v>100</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
     </row>
     <row r="122" spans="2:5">
       <c r="B122" s="1" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="D122" s="1">
         <v>100</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
     </row>
     <row r="123" spans="2:5">
       <c r="B123" s="1" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="D123" s="1">
         <v>100</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
     </row>
     <row r="124" spans="2:5">
       <c r="B124" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="D124" s="1">
         <v>100</v>
@@ -5767,10 +5779,10 @@
     </row>
     <row r="125" spans="2:5">
       <c r="B125" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="D125" s="1">
         <v>100</v>
@@ -5781,570 +5793,570 @@
     </row>
     <row r="126" spans="2:5">
       <c r="B126" s="1" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="D126" s="1">
         <v>100</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
     </row>
     <row r="127" spans="2:5">
       <c r="B127" s="1" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="D127" s="1">
         <v>100</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
     </row>
     <row r="128" spans="2:5">
       <c r="B128" s="1" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="D128" s="1">
         <v>100</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
     </row>
     <row r="129" spans="2:5">
       <c r="B129" s="1" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="D129" s="1">
         <v>100</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
     </row>
     <row r="130" spans="2:5">
       <c r="B130" s="1" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="D130" s="1">
         <v>100</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
     </row>
     <row r="131" spans="2:5">
       <c r="B131" s="1" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="D131" s="1">
         <v>100</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
     </row>
     <row r="132" spans="2:5">
       <c r="B132" s="1" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="D132" s="1">
         <v>100</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
     </row>
     <row r="133" spans="2:5">
       <c r="B133" s="1" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="D133" s="1">
         <v>100</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
     </row>
     <row r="134" spans="2:5">
       <c r="B134" s="1" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="D134" s="1">
         <v>100</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
     </row>
     <row r="135" spans="2:5">
       <c r="B135" s="1" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="D135" s="1">
         <v>100</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
     </row>
     <row r="136" spans="2:5">
       <c r="B136" s="1" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="D136" s="1">
         <v>100</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
     </row>
     <row r="137" spans="2:5">
       <c r="B137" s="1" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="D137" s="1">
         <v>100</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
     </row>
     <row r="138" spans="2:5">
       <c r="B138" s="1" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="D138" s="1">
         <v>100</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
     </row>
     <row r="139" spans="2:5">
       <c r="B139" s="1" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="D139" s="1">
         <v>100</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
     </row>
     <row r="140" spans="2:5">
       <c r="B140" s="1" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="D140" s="1">
         <v>100</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
     </row>
     <row r="141" spans="2:5">
       <c r="B141" s="1" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="D141" s="1">
         <v>100</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
     </row>
     <row r="142" spans="2:5">
       <c r="B142" s="1" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="D142" s="1">
         <v>100</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
     </row>
     <row r="143" spans="2:5">
       <c r="B143" s="1" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="D143" s="1">
         <v>100</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
     </row>
     <row r="144" spans="2:5">
       <c r="B144" s="1" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="D144" s="1">
         <v>100</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
     </row>
     <row r="145" spans="2:5">
       <c r="B145" s="1" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="D145" s="1">
         <v>100</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
     </row>
     <row r="146" spans="2:5">
       <c r="B146" s="1" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="D146" s="1">
         <v>100</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
     </row>
     <row r="147" spans="2:5">
       <c r="B147" s="1" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="D147" s="1">
         <v>100</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
     </row>
     <row r="148" spans="2:5">
       <c r="B148" s="1" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="D148" s="1">
         <v>100</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
     </row>
     <row r="149" spans="2:5">
       <c r="B149" s="1" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="D149" s="1">
         <v>100</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
     </row>
     <row r="150" spans="2:5">
       <c r="B150" s="1" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="D150" s="1">
         <v>100</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
     </row>
     <row r="151" spans="2:5">
       <c r="B151" s="1" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="D151" s="1">
         <v>100</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
     </row>
     <row r="152" spans="2:5">
       <c r="B152" s="1" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="D152" s="1">
         <v>100</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
     </row>
     <row r="153" spans="2:5">
       <c r="B153" s="1" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="D153" s="1">
         <v>100</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
     </row>
     <row r="154" spans="2:5">
       <c r="B154" s="1" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="D154" s="1">
         <v>100</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
     </row>
     <row r="155" spans="2:5">
       <c r="B155" s="1" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="D155" s="1">
         <v>100</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
     </row>
     <row r="156" spans="2:5">
       <c r="B156" s="1" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="D156" s="1">
         <v>100</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
     </row>
     <row r="157" spans="2:5">
       <c r="B157" s="1" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="D157" s="1">
         <v>100</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
     </row>
     <row r="158" spans="2:5">
       <c r="B158" s="1" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="D158" s="1">
         <v>100</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
     </row>
     <row r="159" spans="2:5">
       <c r="B159" s="1" t="s">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="D159" s="1">
         <v>100</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>597</v>
+        <v>587</v>
       </c>
     </row>
     <row r="160" spans="2:5">
       <c r="B160" s="1" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="D160" s="1">
         <v>100</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
     </row>
     <row r="161" spans="2:5">
       <c r="B161" s="1" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="D161" s="1">
         <v>100</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
     </row>
     <row r="162" spans="2:5">
       <c r="B162" s="1" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="D162" s="1">
         <v>100</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
     </row>
     <row r="163" spans="2:5">
       <c r="B163" s="1" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="D163" s="1">
         <v>100</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
     </row>
     <row r="164" spans="2:5">
       <c r="B164" s="1" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="D164" s="1">
         <v>100</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
     </row>
     <row r="165" spans="2:5">
       <c r="B165" s="1" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="D165" s="1">
         <v>100</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
     </row>
     <row r="166" spans="2:5">
       <c r="B166" s="1" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="D166" s="1">
         <v>100</v>
@@ -6385,22 +6397,22 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="D1" t="s">
-        <v>617</v>
+        <v>607</v>
       </c>
       <c r="E1" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="F1" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="G1" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="H1" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6408,25 +6420,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="C2" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="D2" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="E2" t="s">
-        <v>625</v>
+        <v>615</v>
       </c>
       <c r="F2" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="G2" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="H2" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6437,19 +6449,19 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="D3" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="E3" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="F3" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="G3" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
@@ -6457,7 +6469,7 @@
     </row>
     <row r="4" spans="2:7">
       <c r="B4" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -6477,7 +6489,7 @@
     </row>
     <row r="5" spans="2:7">
       <c r="B5" t="s">
-        <v>631</v>
+        <v>621</v>
       </c>
       <c r="C5">
         <v>95</v>
@@ -6497,7 +6509,7 @@
     </row>
     <row r="6" spans="2:7">
       <c r="B6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C6">
         <v>80</v>
@@ -6517,7 +6529,7 @@
     </row>
     <row r="7" spans="2:7">
       <c r="B7" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C7">
         <v>1000</v>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15200" activeTab="1"/>
+    <workbookView windowHeight="16760" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="action" sheetId="1" r:id="rId1"/>
@@ -15,12 +15,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">small_group!$B$1:$B$166</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="626">
   <si>
     <t>##var</t>
   </si>
@@ -265,10 +278,10 @@
     <t>包含的小组ID列表→small_group.id</t>
   </si>
   <si>
-    <t>list,float</t>
-  </si>
-  <si>
-    <t>list,string</t>
+    <t>(list#sep=,),float</t>
+  </si>
+  <si>
+    <t>(list#sep=,),string</t>
   </si>
   <si>
     <t>lg_normal</t>
@@ -340,7 +353,7 @@
     <t>rule_debug_first</t>
   </si>
   <si>
-    <t>mg_debug</t>
+    <t>sg_debug</t>
   </si>
   <si>
     <t>weight</t>
@@ -367,7 +380,7 @@
     <t>普通1</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_fragment|act_food_passive</t>
+    <t>act_food_gold,act_food_fragment,act_food_passive</t>
   </si>
   <si>
     <t>sg_normal_2</t>
@@ -376,7 +389,7 @@
     <t>普通2</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_fragment|act_food_active</t>
+    <t>act_food_gold,act_food_fragment,act_food_active</t>
   </si>
   <si>
     <t>sg_normalEvent_15</t>
@@ -388,7 +401,7 @@
     <t>普通3</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_fragment|act_food_dish</t>
+    <t>act_food_gold,act_food_fragment,act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHardEvent_1</t>
@@ -400,7 +413,7 @@
     <t>普通4</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_passive|act_food_active</t>
+    <t>act_food_gold,act_food_passive,act_food_active</t>
   </si>
   <si>
     <t>sg_hardEvent_1</t>
@@ -412,7 +425,7 @@
     <t>普通5</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_passive|act_food_dish</t>
+    <t>act_food_gold,act_food_passive,act_food_dish</t>
   </si>
   <si>
     <t>sg_normal_6</t>
@@ -421,7 +434,7 @@
     <t>普通6</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_active|act_food_dish</t>
+    <t>act_food_gold,act_food_active,act_food_dish</t>
   </si>
   <si>
     <t>sg_normal_7</t>
@@ -430,7 +443,7 @@
     <t>普通7</t>
   </si>
   <si>
-    <t>act_food_fragment|act_food_passive|act_food_active</t>
+    <t>act_food_fragment,act_food_passive,act_food_active</t>
   </si>
   <si>
     <t>sg_normal_8</t>
@@ -439,7 +452,7 @@
     <t>普通8</t>
   </si>
   <si>
-    <t>act_food_fragment|act_food_passive|act_food_dish</t>
+    <t>act_food_fragment,act_food_passive,act_food_dish</t>
   </si>
   <si>
     <t>sg_normal_9</t>
@@ -448,7 +461,7 @@
     <t>普通9</t>
   </si>
   <si>
-    <t>act_food_fragment|act_food_active|act_food_dish</t>
+    <t>act_food_fragment,act_food_active,act_food_dish</t>
   </si>
   <si>
     <t>sg_normal_10</t>
@@ -457,7 +470,7 @@
     <t>普通10</t>
   </si>
   <si>
-    <t>act_food_passive|act_food_active|act_food_dish</t>
+    <t>act_food_passive,act_food_active,act_food_dish</t>
   </si>
   <si>
     <t>sg_normal_11</t>
@@ -466,7 +479,7 @@
     <t>普通11</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_fragment</t>
+    <t>act_food_gold,act_food_fragment</t>
   </si>
   <si>
     <t>sg_normal_12</t>
@@ -475,7 +488,7 @@
     <t>普通12</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_passive</t>
+    <t>act_food_gold,act_food_passive</t>
   </si>
   <si>
     <t>sg_normal_13</t>
@@ -484,7 +497,7 @@
     <t>普通13</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_active</t>
+    <t>act_food_gold,act_food_active</t>
   </si>
   <si>
     <t>sg_normal_14</t>
@@ -493,7 +506,7 @@
     <t>普通14</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_dish</t>
+    <t>act_food_gold,act_food_dish</t>
   </si>
   <si>
     <t>sg_normal_15</t>
@@ -502,7 +515,7 @@
     <t>普通15</t>
   </si>
   <si>
-    <t>act_food_fragment|act_food_passive</t>
+    <t>act_food_fragment,act_food_passive</t>
   </si>
   <si>
     <t>sg_normal_16</t>
@@ -511,7 +524,7 @@
     <t>普通16</t>
   </si>
   <si>
-    <t>act_food_fragment|act_food_active</t>
+    <t>act_food_fragment,act_food_active</t>
   </si>
   <si>
     <t>sg_normal_17</t>
@@ -520,7 +533,7 @@
     <t>普通17</t>
   </si>
   <si>
-    <t>act_food_fragment|act_food_dish</t>
+    <t>act_food_fragment,act_food_dish</t>
   </si>
   <si>
     <t>普通困难混合大组</t>
@@ -532,7 +545,7 @@
     <t>普通18</t>
   </si>
   <si>
-    <t>act_food_passive|act_food_active</t>
+    <t>act_food_passive,act_food_active</t>
   </si>
   <si>
     <t>sg_normal_19</t>
@@ -541,7 +554,7 @@
     <t>普通19</t>
   </si>
   <si>
-    <t>act_food_passive|act_food_dish</t>
+    <t>act_food_passive,act_food_dish</t>
   </si>
   <si>
     <t>sg_normal_20</t>
@@ -550,7 +563,7 @@
     <t>普通20</t>
   </si>
   <si>
-    <t>act_food_active|act_food_dish</t>
+    <t>act_food_active,act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_1</t>
@@ -559,7 +572,7 @@
     <t>普通困难1</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_fragment|act_food_passive</t>
+    <t>act_food_hard_gold,act_food_fragment,act_food_passive</t>
   </si>
   <si>
     <t>sg_normalHard_2</t>
@@ -568,7 +581,7 @@
     <t>普通困难2</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_fragment|act_food_active</t>
+    <t>act_food_hard_gold,act_food_fragment,act_food_active</t>
   </si>
   <si>
     <t>sg_normalHard_3</t>
@@ -577,7 +590,7 @@
     <t>普通困难3</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_fragment|act_food_dish</t>
+    <t>act_food_hard_gold,act_food_fragment,act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_4</t>
@@ -586,7 +599,7 @@
     <t>普通困难4</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_passive|act_food_active</t>
+    <t>act_food_hard_gold,act_food_passive,act_food_active</t>
   </si>
   <si>
     <t>sg_normalHard_5</t>
@@ -595,7 +608,7 @@
     <t>普通困难5</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_passive|act_food_dish</t>
+    <t>act_food_hard_gold,act_food_passive,act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_6</t>
@@ -604,7 +617,7 @@
     <t>普通困难6</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_active|act_food_dish</t>
+    <t>act_food_hard_gold,act_food_active,act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_7</t>
@@ -613,7 +626,7 @@
     <t>普通困难7</t>
   </si>
   <si>
-    <t>act_food_hard_fragment|act_food_passive|act_food_active</t>
+    <t>act_food_hard_fragment,act_food_passive,act_food_active</t>
   </si>
   <si>
     <t>sg_normalHard_8</t>
@@ -622,7 +635,7 @@
     <t>普通困难8</t>
   </si>
   <si>
-    <t>act_food_hard_fragment|act_food_passive|act_food_dish</t>
+    <t>act_food_hard_fragment,act_food_passive,act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_9</t>
@@ -631,7 +644,7 @@
     <t>普通困难9</t>
   </si>
   <si>
-    <t>act_food_hard_fragment|act_food_active|act_food_dish</t>
+    <t>act_food_hard_fragment,act_food_active,act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_10</t>
@@ -640,7 +653,7 @@
     <t>普通困难10</t>
   </si>
   <si>
-    <t>act_food_hard_passive|act_food_active|act_food_dish</t>
+    <t>act_food_hard_passive,act_food_active,act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_11</t>
@@ -649,7 +662,7 @@
     <t>普通困难11</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_fragment</t>
+    <t>act_food_hard_gold,act_food_fragment</t>
   </si>
   <si>
     <t>sg_normalHard_12</t>
@@ -658,7 +671,7 @@
     <t>普通困难12</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_passive</t>
+    <t>act_food_hard_gold,act_food_passive</t>
   </si>
   <si>
     <t>sg_normalHard_13</t>
@@ -667,7 +680,7 @@
     <t>普通困难13</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_active</t>
+    <t>act_food_hard_gold,act_food_active</t>
   </si>
   <si>
     <t>sg_normalHard_14</t>
@@ -676,7 +689,7 @@
     <t>普通困难14</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_dish</t>
+    <t>act_food_hard_gold,act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_15</t>
@@ -685,7 +698,7 @@
     <t>普通困难15</t>
   </si>
   <si>
-    <t>act_food_hard_fragment|act_food_passive</t>
+    <t>act_food_hard_fragment,act_food_passive</t>
   </si>
   <si>
     <t>sg_normalHard_16</t>
@@ -694,7 +707,7 @@
     <t>普通困难16</t>
   </si>
   <si>
-    <t>act_food_hard_fragment|act_food_active</t>
+    <t>act_food_hard_fragment,act_food_active</t>
   </si>
   <si>
     <t>sg_normalHard_17</t>
@@ -703,7 +716,7 @@
     <t>普通困难17</t>
   </si>
   <si>
-    <t>act_food_hard_fragment|act_food_dish</t>
+    <t>act_food_hard_fragment,act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_18</t>
@@ -712,7 +725,7 @@
     <t>普通困难18</t>
   </si>
   <si>
-    <t>act_food_hard_passive|act_food_active</t>
+    <t>act_food_hard_passive,act_food_active</t>
   </si>
   <si>
     <t>sg_normalHard_19</t>
@@ -721,7 +734,7 @@
     <t>普通困难19</t>
   </si>
   <si>
-    <t>act_food_hard_passive|act_food_dish</t>
+    <t>act_food_hard_passive,act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_20</t>
@@ -730,7 +743,7 @@
     <t>普通困难20</t>
   </si>
   <si>
-    <t>act_food_hard_active|act_food_dish</t>
+    <t>act_food_hard_active,act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_21</t>
@@ -739,7 +752,7 @@
     <t>普通困难21</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_hard_fragment|act_food_passive</t>
+    <t>act_food_gold,act_food_hard_fragment,act_food_passive</t>
   </si>
   <si>
     <t>sg_normalHard_22</t>
@@ -748,7 +761,7 @@
     <t>普通困难22</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_hard_fragment|act_food_active</t>
+    <t>act_food_gold,act_food_hard_fragment,act_food_active</t>
   </si>
   <si>
     <t>sg_normalHard_23</t>
@@ -757,7 +770,7 @@
     <t>普通困难23</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_hard_fragment|act_food_dish</t>
+    <t>act_food_gold,act_food_hard_fragment,act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_24</t>
@@ -766,7 +779,7 @@
     <t>普通困难24</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_hard_passive|act_food_active</t>
+    <t>act_food_gold,act_food_hard_passive,act_food_active</t>
   </si>
   <si>
     <t>sg_normalHard_25</t>
@@ -775,7 +788,7 @@
     <t>普通困难25</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_hard_passive|act_food_dish</t>
+    <t>act_food_gold,act_food_hard_passive,act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_26</t>
@@ -784,7 +797,7 @@
     <t>普通困难26</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_hard_active|act_food_dish</t>
+    <t>act_food_gold,act_food_hard_active,act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_27</t>
@@ -793,7 +806,7 @@
     <t>普通困难27</t>
   </si>
   <si>
-    <t>act_food_fragment|act_food_hard_passive|act_food_active</t>
+    <t>act_food_fragment,act_food_hard_passive,act_food_active</t>
   </si>
   <si>
     <t>sg_normalHard_28</t>
@@ -802,7 +815,7 @@
     <t>普通困难28</t>
   </si>
   <si>
-    <t>act_food_fragment|act_food_hard_passive|act_food_dish</t>
+    <t>act_food_fragment,act_food_hard_passive,act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_29</t>
@@ -811,7 +824,7 @@
     <t>普通困难29</t>
   </si>
   <si>
-    <t>act_food_fragment|act_food_hard_active|act_food_dish</t>
+    <t>act_food_fragment,act_food_hard_active,act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_30</t>
@@ -820,7 +833,7 @@
     <t>普通困难30</t>
   </si>
   <si>
-    <t>act_food_passive|act_food_hard_active|act_food_dish</t>
+    <t>act_food_passive,act_food_hard_active,act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_31</t>
@@ -829,7 +842,7 @@
     <t>普通困难31</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_hard_fragment</t>
+    <t>act_food_gold,act_food_hard_fragment</t>
   </si>
   <si>
     <t>sg_normalHard_32</t>
@@ -838,7 +851,7 @@
     <t>普通困难32</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_hard_passive</t>
+    <t>act_food_gold,act_food_hard_passive</t>
   </si>
   <si>
     <t>sg_normalHard_33</t>
@@ -847,7 +860,7 @@
     <t>普通困难33</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_hard_active</t>
+    <t>act_food_gold,act_food_hard_active</t>
   </si>
   <si>
     <t>sg_normalHard_34</t>
@@ -856,7 +869,7 @@
     <t>普通困难34</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_hard_dish</t>
+    <t>act_food_gold,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_35</t>
@@ -865,7 +878,7 @@
     <t>普通困难35</t>
   </si>
   <si>
-    <t>act_food_fragment|act_food_hard_passive</t>
+    <t>act_food_fragment,act_food_hard_passive</t>
   </si>
   <si>
     <t>sg_normalHard_36</t>
@@ -874,7 +887,7 @@
     <t>普通困难36</t>
   </si>
   <si>
-    <t>act_food_fragment|act_food_hard_active</t>
+    <t>act_food_fragment,act_food_hard_active</t>
   </si>
   <si>
     <t>sg_normalHard_37</t>
@@ -883,7 +896,7 @@
     <t>普通困难37</t>
   </si>
   <si>
-    <t>act_food_fragment|act_food_hard_dish</t>
+    <t>act_food_fragment,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_38</t>
@@ -892,7 +905,7 @@
     <t>普通困难38</t>
   </si>
   <si>
-    <t>act_food_passive|act_food_hard_active</t>
+    <t>act_food_passive,act_food_hard_active</t>
   </si>
   <si>
     <t>sg_normalHard_39</t>
@@ -901,7 +914,7 @@
     <t>普通困难39</t>
   </si>
   <si>
-    <t>act_food_passive|act_food_hard_dish</t>
+    <t>act_food_passive,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_40</t>
@@ -910,7 +923,7 @@
     <t>普通困难40</t>
   </si>
   <si>
-    <t>act_food_active|act_food_hard_dish</t>
+    <t>act_food_active,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_41</t>
@@ -919,7 +932,7 @@
     <t>普通困难41</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_fragment|act_food_hard_passive</t>
+    <t>act_food_gold,act_food_fragment,act_food_hard_passive</t>
   </si>
   <si>
     <t>sg_normalHard_42</t>
@@ -928,7 +941,7 @@
     <t>普通困难42</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_fragment|act_food_hard_active</t>
+    <t>act_food_gold,act_food_fragment,act_food_hard_active</t>
   </si>
   <si>
     <t>sg_normalHard_43</t>
@@ -937,7 +950,7 @@
     <t>普通困难43</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_fragment|act_food_hard_dish</t>
+    <t>act_food_gold,act_food_fragment,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_44</t>
@@ -946,7 +959,7 @@
     <t>普通困难44</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_passive|act_food_hard_active</t>
+    <t>act_food_gold,act_food_passive,act_food_hard_active</t>
   </si>
   <si>
     <t>sg_normalHard_45</t>
@@ -955,7 +968,7 @@
     <t>普通困难45</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_passive|act_food_hard_dish</t>
+    <t>act_food_gold,act_food_passive,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_46</t>
@@ -964,7 +977,7 @@
     <t>普通困难46</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_active|act_food_hard_dish</t>
+    <t>act_food_gold,act_food_active,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_47</t>
@@ -973,7 +986,7 @@
     <t>普通困难47</t>
   </si>
   <si>
-    <t>act_food_fragment|act_food_passive|act_food_hard_active</t>
+    <t>act_food_fragment,act_food_passive,act_food_hard_active</t>
   </si>
   <si>
     <t>sg_normalHard_48</t>
@@ -982,7 +995,7 @@
     <t>普通困难48</t>
   </si>
   <si>
-    <t>act_food_fragment|act_food_passive|act_food_hard_dish</t>
+    <t>act_food_fragment,act_food_passive,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_49</t>
@@ -991,7 +1004,7 @@
     <t>普通困难49</t>
   </si>
   <si>
-    <t>act_food_fragment|act_food_active|act_food_hard_dish</t>
+    <t>act_food_fragment,act_food_active,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_50</t>
@@ -1000,7 +1013,7 @@
     <t>普通困难50</t>
   </si>
   <si>
-    <t>act_food_passive|act_food_active|act_food_hard_dish</t>
+    <t>act_food_passive,act_food_active,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_51</t>
@@ -1009,7 +1022,7 @@
     <t>普通困难51</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_hard_fragment|act_food_passive</t>
+    <t>act_food_hard_gold,act_food_hard_fragment,act_food_passive</t>
   </si>
   <si>
     <t>sg_normalHard_52</t>
@@ -1018,7 +1031,7 @@
     <t>普通困难52</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_hard_fragment|act_food_active</t>
+    <t>act_food_hard_gold,act_food_hard_fragment,act_food_active</t>
   </si>
   <si>
     <t>sg_normalHard_53</t>
@@ -1027,7 +1040,7 @@
     <t>普通困难53</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_hard_fragment|act_food_dish</t>
+    <t>act_food_hard_gold,act_food_hard_fragment,act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_54</t>
@@ -1036,7 +1049,7 @@
     <t>普通困难54</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_hard_passive|act_food_active</t>
+    <t>act_food_hard_gold,act_food_hard_passive,act_food_active</t>
   </si>
   <si>
     <t>sg_normalHard_55</t>
@@ -1045,7 +1058,7 @@
     <t>普通困难55</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_hard_passive|act_food_dish</t>
+    <t>act_food_hard_gold,act_food_hard_passive,act_food_dish</t>
   </si>
   <si>
     <t>sg_food_b</t>
@@ -1060,7 +1073,7 @@
     <t>普通困难56</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_hard_active|act_food_dish</t>
+    <t>act_food_hard_gold,act_food_hard_active,act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_57</t>
@@ -1069,7 +1082,7 @@
     <t>普通困难57</t>
   </si>
   <si>
-    <t>act_food_hard_fragment|act_food_hard_passive|act_food_active</t>
+    <t>act_food_hard_fragment,act_food_hard_passive,act_food_active</t>
   </si>
   <si>
     <t>sg_normalHard_58</t>
@@ -1078,7 +1091,7 @@
     <t>普通困难58</t>
   </si>
   <si>
-    <t>act_food_hard_fragment|act_food_hard_passive|act_food_dish</t>
+    <t>act_food_hard_fragment,act_food_hard_passive,act_food_dish</t>
   </si>
   <si>
     <t>sg_food_hard_a</t>
@@ -1093,7 +1106,7 @@
     <t>普通困难59</t>
   </si>
   <si>
-    <t>act_food_hard_fragment|act_food_hard_active|act_food_dish</t>
+    <t>act_food_hard_fragment,act_food_hard_active,act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_60</t>
@@ -1102,7 +1115,7 @@
     <t>普通困难60</t>
   </si>
   <si>
-    <t>act_food_hard_passive|act_food_hard_active|act_food_dish</t>
+    <t>act_food_hard_passive,act_food_hard_active,act_food_dish</t>
   </si>
   <si>
     <t>sg_normalHard_61</t>
@@ -1111,7 +1124,7 @@
     <t>普通困难61</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_hard_fragment|act_food_hard_passive</t>
+    <t>act_food_gold,act_food_hard_fragment,act_food_hard_passive</t>
   </si>
   <si>
     <t>sg_food_hard_b</t>
@@ -1126,7 +1139,7 @@
     <t>普通困难62</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_hard_fragment|act_food_hard_active</t>
+    <t>act_food_gold,act_food_hard_fragment,act_food_hard_active</t>
   </si>
   <si>
     <t>sg_normalHard_63</t>
@@ -1135,7 +1148,7 @@
     <t>普通困难63</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_hard_fragment|act_food_hard_dish</t>
+    <t>act_food_gold,act_food_hard_fragment,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_64</t>
@@ -1144,7 +1157,7 @@
     <t>普通困难64</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_hard_passive|act_food_hard_active</t>
+    <t>act_food_gold,act_food_hard_passive,act_food_hard_active</t>
   </si>
   <si>
     <t>sg_event</t>
@@ -1156,7 +1169,7 @@
     <t>普通困难65</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_hard_passive|act_food_hard_dish</t>
+    <t>act_food_gold,act_food_hard_passive,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_66</t>
@@ -1165,7 +1178,7 @@
     <t>普通困难66</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_hard_active|act_food_hard_dish</t>
+    <t>act_food_gold,act_food_hard_active,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_67</t>
@@ -1174,7 +1187,7 @@
     <t>普通困难67</t>
   </si>
   <si>
-    <t>act_food_fragment|act_food_hard_passive|act_food_hard_active</t>
+    <t>act_food_fragment,act_food_hard_passive,act_food_hard_active</t>
   </si>
   <si>
     <t>sg_reward</t>
@@ -1186,7 +1199,7 @@
     <t>普通困难68</t>
   </si>
   <si>
-    <t>act_food_fragment|act_food_hard_passive|act_food_hard_dish</t>
+    <t>act_food_fragment,act_food_hard_passive,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_69</t>
@@ -1195,10 +1208,7 @@
     <t>普通困难69</t>
   </si>
   <si>
-    <t>act_food_fragment|act_food_hard_active|act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_debug</t>
+    <t>act_food_fragment,act_food_hard_active,act_food_hard_dish</t>
   </si>
   <si>
     <t>调试商店</t>
@@ -1210,7 +1220,7 @@
     <t>普通困难70</t>
   </si>
   <si>
-    <t>act_food_passive|act_food_hard_active|act_food_hard_dish</t>
+    <t>act_food_passive,act_food_hard_active,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_71</t>
@@ -1219,7 +1229,7 @@
     <t>普通困难71</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_fragment|act_food_hard_passive</t>
+    <t>act_food_hard_gold,act_food_fragment,act_food_hard_passive</t>
   </si>
   <si>
     <t>sg_normalHard_72</t>
@@ -1228,7 +1238,7 @@
     <t>普通困难72</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_fragment|act_food_hard_active</t>
+    <t>act_food_hard_gold,act_food_fragment,act_food_hard_active</t>
   </si>
   <si>
     <t>sg_normalHard_73</t>
@@ -1237,7 +1247,7 @@
     <t>普通困难73</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_fragment|act_food_hard_dish</t>
+    <t>act_food_hard_gold,act_food_fragment,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_74</t>
@@ -1246,7 +1256,7 @@
     <t>普通困难74</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_passive|act_food_hard_active</t>
+    <t>act_food_hard_gold,act_food_passive,act_food_hard_active</t>
   </si>
   <si>
     <t>sg_normalHard_75</t>
@@ -1255,7 +1265,7 @@
     <t>普通困难75</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_passive|act_food_hard_dish</t>
+    <t>act_food_hard_gold,act_food_passive,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_76</t>
@@ -1264,7 +1274,7 @@
     <t>普通困难76</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_active|act_food_hard_dish</t>
+    <t>act_food_hard_gold,act_food_active,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_77</t>
@@ -1273,7 +1283,7 @@
     <t>普通困难77</t>
   </si>
   <si>
-    <t>act_food_hard_fragment|act_food_passive|act_food_hard_active</t>
+    <t>act_food_hard_fragment,act_food_passive,act_food_hard_active</t>
   </si>
   <si>
     <t>sg_normalHard_78</t>
@@ -1282,7 +1292,7 @@
     <t>普通困难78</t>
   </si>
   <si>
-    <t>act_food_hard_fragment|act_food_passive|act_food_hard_dish</t>
+    <t>act_food_hard_fragment,act_food_passive,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_79</t>
@@ -1291,7 +1301,7 @@
     <t>普通困难79</t>
   </si>
   <si>
-    <t>act_food_hard_fragment|act_food_active|act_food_hard_dish</t>
+    <t>act_food_hard_fragment,act_food_active,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_normalHard_80</t>
@@ -1300,7 +1310,7 @@
     <t>普通困难80</t>
   </si>
   <si>
-    <t>act_food_hard_passive|act_food_active|act_food_hard_dish</t>
+    <t>act_food_hard_passive,act_food_active,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_hard_1</t>
@@ -1309,7 +1319,7 @@
     <t>困难1</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_hard_fragment|act_food_hard_passive</t>
+    <t>act_food_hard_gold,act_food_hard_fragment,act_food_hard_passive</t>
   </si>
   <si>
     <t>sg_hard_2</t>
@@ -1318,7 +1328,7 @@
     <t>困难2</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_hard_fragment|act_food_hard_active</t>
+    <t>act_food_hard_gold,act_food_hard_fragment,act_food_hard_active</t>
   </si>
   <si>
     <t>sg_hard_3</t>
@@ -1327,7 +1337,7 @@
     <t>困难3</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_hard_fragment|act_food_hard_dish</t>
+    <t>act_food_hard_gold,act_food_hard_fragment,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_hard_4</t>
@@ -1336,7 +1346,7 @@
     <t>困难4</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_hard_passive|act_food_hard_active</t>
+    <t>act_food_hard_gold,act_food_hard_passive,act_food_hard_active</t>
   </si>
   <si>
     <t>sg_hard_5</t>
@@ -1345,7 +1355,7 @@
     <t>困难5</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_hard_passive|act_food_hard_dish</t>
+    <t>act_food_hard_gold,act_food_hard_passive,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_hard_6</t>
@@ -1354,7 +1364,7 @@
     <t>困难6</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_hard_active|act_food_hard_dish</t>
+    <t>act_food_hard_gold,act_food_hard_active,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_hard_7</t>
@@ -1363,7 +1373,7 @@
     <t>困难7</t>
   </si>
   <si>
-    <t>act_food_hard_fragment|act_food_hard_passive|act_food_hard_active</t>
+    <t>act_food_hard_fragment,act_food_hard_passive,act_food_hard_active</t>
   </si>
   <si>
     <t>sg_hard_8</t>
@@ -1372,7 +1382,7 @@
     <t>困难8</t>
   </si>
   <si>
-    <t>act_food_hard_fragment|act_food_hard_passive|act_food_hard_dish</t>
+    <t>act_food_hard_fragment,act_food_hard_passive,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_hard_9</t>
@@ -1381,7 +1391,7 @@
     <t>困难9</t>
   </si>
   <si>
-    <t>act_food_hard_fragment|act_food_hard_active|act_food_hard_dish</t>
+    <t>act_food_hard_fragment,act_food_hard_active,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_hard_10</t>
@@ -1390,7 +1400,7 @@
     <t>困难10</t>
   </si>
   <si>
-    <t>act_food_hard_passive|act_food_hard_active|act_food_hard_dish</t>
+    <t>act_food_hard_passive,act_food_hard_active,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_hard_11</t>
@@ -1399,7 +1409,7 @@
     <t>困难11</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_hard_fragment</t>
+    <t>act_food_hard_gold,act_food_hard_fragment</t>
   </si>
   <si>
     <t>sg_hard_12</t>
@@ -1408,7 +1418,7 @@
     <t>困难12</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_hard_passive</t>
+    <t>act_food_hard_gold,act_food_hard_passive</t>
   </si>
   <si>
     <t>sg_hard_13</t>
@@ -1417,7 +1427,7 @@
     <t>困难13</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_hard_active</t>
+    <t>act_food_hard_gold,act_food_hard_active</t>
   </si>
   <si>
     <t>sg_hard_14</t>
@@ -1426,7 +1436,7 @@
     <t>困难14</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_hard_dish</t>
+    <t>act_food_hard_gold,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_hard_15</t>
@@ -1435,7 +1445,7 @@
     <t>困难15</t>
   </si>
   <si>
-    <t>act_food_hard_fragment|act_food_hard_passive</t>
+    <t>act_food_hard_fragment,act_food_hard_passive</t>
   </si>
   <si>
     <t>sg_hard_16</t>
@@ -1444,7 +1454,7 @@
     <t>困难16</t>
   </si>
   <si>
-    <t>act_food_hard_fragment|act_food_hard_active</t>
+    <t>act_food_hard_fragment,act_food_hard_active</t>
   </si>
   <si>
     <t>sg_hard_17</t>
@@ -1453,7 +1463,7 @@
     <t>困难17</t>
   </si>
   <si>
-    <t>act_food_hard_fragment|act_food_hard_dish</t>
+    <t>act_food_hard_fragment,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_hard_18</t>
@@ -1462,7 +1472,7 @@
     <t>困难18</t>
   </si>
   <si>
-    <t>act_food_hard_passive|act_food_hard_active</t>
+    <t>act_food_hard_passive,act_food_hard_active</t>
   </si>
   <si>
     <t>sg_hard_19</t>
@@ -1471,7 +1481,7 @@
     <t>困难19</t>
   </si>
   <si>
-    <t>act_food_hard_passive|act_food_hard_dish</t>
+    <t>act_food_hard_passive,act_food_hard_dish</t>
   </si>
   <si>
     <t>sg_hard_20</t>
@@ -1480,7 +1490,7 @@
     <t>困难20</t>
   </si>
   <si>
-    <t>act_food_hard_active|act_food_hard_dish</t>
+    <t>act_food_hard_active,act_food_hard_dish</t>
   </si>
   <si>
     <t>事件1</t>
@@ -1495,7 +1505,7 @@
     <t>普通事件1</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_fragment|act_event</t>
+    <t>act_food_gold,act_food_fragment,act_event</t>
   </si>
   <si>
     <t>sg_normalEvent_2</t>
@@ -1504,7 +1514,7 @@
     <t>普通事件2</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_passive|act_event</t>
+    <t>act_food_gold,act_food_passive,act_event</t>
   </si>
   <si>
     <t>sg_normalEvent_3</t>
@@ -1513,7 +1523,7 @@
     <t>普通事件3</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_active|act_event</t>
+    <t>act_food_gold,act_food_active,act_event</t>
   </si>
   <si>
     <t>sg_normalEvent_4</t>
@@ -1522,7 +1532,7 @@
     <t>普通事件4</t>
   </si>
   <si>
-    <t>act_food_gold|act_food_dish|act_event</t>
+    <t>act_food_gold,act_food_dish,act_event</t>
   </si>
   <si>
     <t>sg_normalEvent_5</t>
@@ -1531,7 +1541,7 @@
     <t>普通事件5</t>
   </si>
   <si>
-    <t>act_food_fragment|act_food_passive|act_event</t>
+    <t>act_food_fragment,act_food_passive,act_event</t>
   </si>
   <si>
     <t>sg_normalEvent_6</t>
@@ -1540,7 +1550,7 @@
     <t>普通事件6</t>
   </si>
   <si>
-    <t>act_food_fragment|act_food_active|act_event</t>
+    <t>act_food_fragment,act_food_active,act_event</t>
   </si>
   <si>
     <t>sg_normalEvent_7</t>
@@ -1549,7 +1559,7 @@
     <t>普通事件7</t>
   </si>
   <si>
-    <t>act_food_fragment|act_food_dish|act_event</t>
+    <t>act_food_fragment,act_food_dish,act_event</t>
   </si>
   <si>
     <t>sg_normalEvent_8</t>
@@ -1558,7 +1568,7 @@
     <t>普通事件8</t>
   </si>
   <si>
-    <t>act_food_passive|act_food_active|act_event</t>
+    <t>act_food_passive,act_food_active,act_event</t>
   </si>
   <si>
     <t>sg_normalEvent_9</t>
@@ -1567,7 +1577,7 @@
     <t>普通事件9</t>
   </si>
   <si>
-    <t>act_food_passive|act_food_dish|act_event</t>
+    <t>act_food_passive,act_food_dish,act_event</t>
   </si>
   <si>
     <t>sg_normalEvent_10</t>
@@ -1576,7 +1586,7 @@
     <t>普通事件10</t>
   </si>
   <si>
-    <t>act_food_active|act_food_dish|act_event</t>
+    <t>act_food_active,act_food_dish,act_event</t>
   </si>
   <si>
     <t>sg_normalEvent_11</t>
@@ -1585,7 +1595,7 @@
     <t>普通事件11</t>
   </si>
   <si>
-    <t>act_food_gold|act_event</t>
+    <t>act_food_gold,act_event</t>
   </si>
   <si>
     <t>sg_normalEvent_12</t>
@@ -1594,7 +1604,7 @@
     <t>普通事件12</t>
   </si>
   <si>
-    <t>act_food_fragment|act_event</t>
+    <t>act_food_fragment,act_event</t>
   </si>
   <si>
     <t>sg_normalEvent_13</t>
@@ -1603,7 +1613,7 @@
     <t>普通事件13</t>
   </si>
   <si>
-    <t>act_food_passive|act_event</t>
+    <t>act_food_passive,act_event</t>
   </si>
   <si>
     <t>sg_normalEvent_14</t>
@@ -1612,19 +1622,19 @@
     <t>普通事件14</t>
   </si>
   <si>
-    <t>act_food_active|act_event</t>
+    <t>act_food_active,act_event</t>
   </si>
   <si>
     <t>普通事件15</t>
   </si>
   <si>
-    <t>act_food_dish|act_event</t>
+    <t>act_food_dish,act_event</t>
   </si>
   <si>
     <t>普通困难事件1</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_fragment|act_event</t>
+    <t>act_food_hard_gold,act_food_fragment,act_event</t>
   </si>
   <si>
     <t>sg_normalHardEvent_2</t>
@@ -1633,7 +1643,7 @@
     <t>普通困难事件2</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_passive|act_event</t>
+    <t>act_food_hard_gold,act_food_passive,act_event</t>
   </si>
   <si>
     <t>sg_normalHardEvent_3</t>
@@ -1642,7 +1652,7 @@
     <t>普通困难事件3</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_active|act_event</t>
+    <t>act_food_hard_gold,act_food_active,act_event</t>
   </si>
   <si>
     <t>sg_normalHardEvent_4</t>
@@ -1651,7 +1661,7 @@
     <t>普通困难事件4</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_dish|act_event</t>
+    <t>act_food_hard_gold,act_food_dish,act_event</t>
   </si>
   <si>
     <t>sg_normalHardEvent_5</t>
@@ -1660,7 +1670,7 @@
     <t>普通困难事件5</t>
   </si>
   <si>
-    <t>act_food_hard_fragment|act_food_passive|act_event</t>
+    <t>act_food_hard_fragment,act_food_passive,act_event</t>
   </si>
   <si>
     <t>sg_normalHardEvent_6</t>
@@ -1669,7 +1679,7 @@
     <t>普通困难事件6</t>
   </si>
   <si>
-    <t>act_food_hard_fragment|act_food_active|act_event</t>
+    <t>act_food_hard_fragment,act_food_active,act_event</t>
   </si>
   <si>
     <t>sg_normalHardEvent_7</t>
@@ -1678,7 +1688,7 @@
     <t>普通困难事件7</t>
   </si>
   <si>
-    <t>act_food_hard_fragment|act_food_dish|act_event</t>
+    <t>act_food_hard_fragment,act_food_dish,act_event</t>
   </si>
   <si>
     <t>sg_normalHardEvent_8</t>
@@ -1687,7 +1697,7 @@
     <t>普通困难事件8</t>
   </si>
   <si>
-    <t>act_food_hard_passive|act_food_active|act_event</t>
+    <t>act_food_hard_passive,act_food_active,act_event</t>
   </si>
   <si>
     <t>sg_normalHardEvent_9</t>
@@ -1696,7 +1706,7 @@
     <t>普通困难事件9</t>
   </si>
   <si>
-    <t>act_food_hard_passive|act_food_dish|act_event</t>
+    <t>act_food_hard_passive,act_food_dish,act_event</t>
   </si>
   <si>
     <t>sg_normalHardEvent_10</t>
@@ -1705,13 +1715,13 @@
     <t>普通困难事件10</t>
   </si>
   <si>
-    <t>act_food_hard_active|act_food_dish|act_event</t>
+    <t>act_food_hard_active,act_food_dish,act_event</t>
   </si>
   <si>
     <t>困难事件1</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_hard_fragment|act_event</t>
+    <t>act_food_hard_gold,act_food_hard_fragment,act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_2</t>
@@ -1720,7 +1730,7 @@
     <t>困难事件2</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_hard_passive|act_event</t>
+    <t>act_food_hard_gold,act_food_hard_passive,act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_3</t>
@@ -1729,7 +1739,7 @@
     <t>困难事件3</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_hard_active|act_event</t>
+    <t>act_food_hard_gold,act_food_hard_active,act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_4</t>
@@ -1738,7 +1748,7 @@
     <t>困难事件4</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_food_hard_dish|act_event</t>
+    <t>act_food_hard_gold,act_food_hard_dish,act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_5</t>
@@ -1747,7 +1757,7 @@
     <t>困难事件5</t>
   </si>
   <si>
-    <t>act_food_hard_fragment|act_food_hard_passive|act_event</t>
+    <t>act_food_hard_fragment,act_food_hard_passive,act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_6</t>
@@ -1756,7 +1766,7 @@
     <t>困难事件6</t>
   </si>
   <si>
-    <t>act_food_hard_fragment|act_food_hard_active|act_event</t>
+    <t>act_food_hard_fragment,act_food_hard_active,act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_7</t>
@@ -1765,7 +1775,7 @@
     <t>困难事件7</t>
   </si>
   <si>
-    <t>act_food_hard_fragment|act_food_hard_dish|act_event</t>
+    <t>act_food_hard_fragment,act_food_hard_dish,act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_8</t>
@@ -1774,7 +1784,7 @@
     <t>困难事件8</t>
   </si>
   <si>
-    <t>act_food_hard_passive|act_food_hard_active|act_event</t>
+    <t>act_food_hard_passive,act_food_hard_active,act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_9</t>
@@ -1783,7 +1793,7 @@
     <t>困难事件9</t>
   </si>
   <si>
-    <t>act_food_hard_passive|act_food_hard_dish|act_event</t>
+    <t>act_food_hard_passive,act_food_hard_dish,act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_10</t>
@@ -1792,7 +1802,7 @@
     <t>困难事件10</t>
   </si>
   <si>
-    <t>act_food_hard_active|act_food_hard_dish|act_event</t>
+    <t>act_food_hard_active,act_food_hard_dish,act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_11</t>
@@ -1801,7 +1811,7 @@
     <t>困难事件11</t>
   </si>
   <si>
-    <t>act_food_hard_gold|act_event</t>
+    <t>act_food_hard_gold,act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_12</t>
@@ -1810,7 +1820,7 @@
     <t>困难事件12</t>
   </si>
   <si>
-    <t>act_food_hard_fragment|act_event</t>
+    <t>act_food_hard_fragment,act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_13</t>
@@ -1819,7 +1829,7 @@
     <t>困难事件13</t>
   </si>
   <si>
-    <t>act_food_hard_passive|act_event</t>
+    <t>act_food_hard_passive,act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_14</t>
@@ -1828,7 +1838,7 @@
     <t>困难事件14</t>
   </si>
   <si>
-    <t>act_food_hard_active|act_event</t>
+    <t>act_food_hard_active,act_event</t>
   </si>
   <si>
     <t>sg_hardEvent_15</t>
@@ -1837,7 +1847,7 @@
     <t>困难事件15</t>
   </si>
   <si>
-    <t>act_food_hard_dish|act_event</t>
+    <t>act_food_hard_dish,act_event</t>
   </si>
   <si>
     <t>priority</t>
@@ -1858,6 +1868,9 @@
     <t>preconditions</t>
   </si>
   <si>
+    <t>activeWeeks</t>
+  </si>
+  <si>
     <t>规则ID(大组用 ruleIds 引用它)</t>
   </si>
   <si>
@@ -1879,10 +1892,22 @@
     <t>规则前置条件</t>
   </si>
   <si>
+    <t>生效周列表；空=全部周</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
+    <t>(list#sep=,),int</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>rule_reward_early</t>
+  </si>
+  <si>
+    <t>1,2,3,4,5,6,7,8</t>
   </si>
   <si>
     <t>rule_reward_mid</t>
@@ -1891,7 +1916,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -2499,10 +2524,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3342,7 +3370,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" ht="17" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -3355,7 +3383,7 @@
       <c r="D3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>81</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -3369,13 +3397,13 @@
       <c r="C4" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="2" t="str">
+      <c r="E4" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,I4:L4)</f>
         <v>400,300,200,150</v>
       </c>
-      <c r="F4" s="3" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,small_group!B4:B23)</f>
-        <v>sg_normal_1|sg_normal_2|sg_normal_3|sg_normal_4|sg_normal_5|sg_normal_6|sg_normal_7|sg_normal_8|sg_normal_9|sg_normal_10|sg_normal_11|sg_normal_12|sg_normal_13|sg_normal_14|sg_normal_15|sg_normal_16|sg_normal_17|sg_normal_18|sg_normal_19|sg_normal_20</v>
+      <c r="F4" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,small_group!B4:B23)</f>
+        <v>sg_normal_1,sg_normal_2,sg_normal_3,sg_normal_4,sg_normal_5,sg_normal_6,sg_normal_7,sg_normal_8,sg_normal_9,sg_normal_10,sg_normal_11,sg_normal_12,sg_normal_13,sg_normal_14,sg_normal_15,sg_normal_16,sg_normal_17,sg_normal_18,sg_normal_19,sg_normal_20</v>
       </c>
       <c r="G4" s="1" t="str">
         <f>""</f>
@@ -3401,13 +3429,13 @@
       <c r="C5" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="2" t="str">
+      <c r="E5" s="3" t="str">
         <f t="shared" ref="E5:E12" si="0">_xlfn.TEXTJOIN(",",TRUE,I5:L5)</f>
         <v>200,200,250,200</v>
       </c>
-      <c r="F5" s="3" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,small_group!B24:B103)</f>
-        <v>sg_normalHard_1|sg_normalHard_2|sg_normalHard_3|sg_normalHard_4|sg_normalHard_5|sg_normalHard_6|sg_normalHard_7|sg_normalHard_8|sg_normalHard_9|sg_normalHard_10|sg_normalHard_11|sg_normalHard_12|sg_normalHard_13|sg_normalHard_14|sg_normalHard_15|sg_normalHard_16|sg_normalHard_17|sg_normalHard_18|sg_normalHard_19|sg_normalHard_20|sg_normalHard_21|sg_normalHard_22|sg_normalHard_23|sg_normalHard_24|sg_normalHard_25|sg_normalHard_26|sg_normalHard_27|sg_normalHard_28|sg_normalHard_29|sg_normalHard_30|sg_normalHard_31|sg_normalHard_32|sg_normalHard_33|sg_normalHard_34|sg_normalHard_35|sg_normalHard_36|sg_normalHard_37|sg_normalHard_38|sg_normalHard_39|sg_normalHard_40|sg_normalHard_41|sg_normalHard_42|sg_normalHard_43|sg_normalHard_44|sg_normalHard_45|sg_normalHard_46|sg_normalHard_47|sg_normalHard_48|sg_normalHard_49|sg_normalHard_50|sg_normalHard_51|sg_normalHard_52|sg_normalHard_53|sg_normalHard_54|sg_normalHard_55|sg_normalHard_56|sg_normalHard_57|sg_normalHard_58|sg_normalHard_59|sg_normalHard_60|sg_normalHard_61|sg_normalHard_62|sg_normalHard_63|sg_normalHard_64|sg_normalHard_65|sg_normalHard_66|sg_normalHard_67|sg_normalHard_68|sg_normalHard_69|sg_normalHard_70|sg_normalHard_71|sg_normalHard_72|sg_normalHard_73|sg_normalHard_74|sg_normalHard_75|sg_normalHard_76|sg_normalHard_77|sg_normalHard_78|sg_normalHard_79|sg_normalHard_80</v>
+      <c r="F5" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,small_group!B24:B103)</f>
+        <v>sg_normalHard_1,sg_normalHard_2,sg_normalHard_3,sg_normalHard_4,sg_normalHard_5,sg_normalHard_6,sg_normalHard_7,sg_normalHard_8,sg_normalHard_9,sg_normalHard_10,sg_normalHard_11,sg_normalHard_12,sg_normalHard_13,sg_normalHard_14,sg_normalHard_15,sg_normalHard_16,sg_normalHard_17,sg_normalHard_18,sg_normalHard_19,sg_normalHard_20,sg_normalHard_21,sg_normalHard_22,sg_normalHard_23,sg_normalHard_24,sg_normalHard_25,sg_normalHard_26,sg_normalHard_27,sg_normalHard_28,sg_normalHard_29,sg_normalHard_30,sg_normalHard_31,sg_normalHard_32,sg_normalHard_33,sg_normalHard_34,sg_normalHard_35,sg_normalHard_36,sg_normalHard_37,sg_normalHard_38,sg_normalHard_39,sg_normalHard_40,sg_normalHard_41,sg_normalHard_42,sg_normalHard_43,sg_normalHard_44,sg_normalHard_45,sg_normalHard_46,sg_normalHard_47,sg_normalHard_48,sg_normalHard_49,sg_normalHard_50,sg_normalHard_51,sg_normalHard_52,sg_normalHard_53,sg_normalHard_54,sg_normalHard_55,sg_normalHard_56,sg_normalHard_57,sg_normalHard_58,sg_normalHard_59,sg_normalHard_60,sg_normalHard_61,sg_normalHard_62,sg_normalHard_63,sg_normalHard_64,sg_normalHard_65,sg_normalHard_66,sg_normalHard_67,sg_normalHard_68,sg_normalHard_69,sg_normalHard_70,sg_normalHard_71,sg_normalHard_72,sg_normalHard_73,sg_normalHard_74,sg_normalHard_75,sg_normalHard_76,sg_normalHard_77,sg_normalHard_78,sg_normalHard_79,sg_normalHard_80</v>
       </c>
       <c r="G5" s="1" t="str">
         <f t="shared" ref="G5:G12" si="1">""</f>
@@ -3433,13 +3461,13 @@
       <c r="C6" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E6" s="2" t="str">
+      <c r="E6" s="3" t="str">
         <f t="shared" si="0"/>
         <v>0,50,100,200</v>
       </c>
-      <c r="F6" s="3" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,small_group!B104:B123)</f>
-        <v>sg_hard_1|sg_hard_2|sg_hard_3|sg_hard_4|sg_hard_5|sg_hard_6|sg_hard_7|sg_hard_8|sg_hard_9|sg_hard_10|sg_hard_11|sg_hard_12|sg_hard_13|sg_hard_14|sg_hard_15|sg_hard_16|sg_hard_17|sg_hard_18|sg_hard_19|sg_hard_20</v>
+      <c r="F6" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,small_group!B104:B123)</f>
+        <v>sg_hard_1,sg_hard_2,sg_hard_3,sg_hard_4,sg_hard_5,sg_hard_6,sg_hard_7,sg_hard_8,sg_hard_9,sg_hard_10,sg_hard_11,sg_hard_12,sg_hard_13,sg_hard_14,sg_hard_15,sg_hard_16,sg_hard_17,sg_hard_18,sg_hard_19,sg_hard_20</v>
       </c>
       <c r="G6" s="1" t="str">
         <f t="shared" si="1"/>
@@ -3468,11 +3496,11 @@
       <c r="D7" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E7" s="2" t="str">
+      <c r="E7" s="3" t="str">
         <f t="shared" si="0"/>
         <v>100,100,100,100</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>92</v>
       </c>
       <c r="G7" s="1" t="str">
@@ -3502,11 +3530,11 @@
       <c r="D8" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E8" s="2" t="str">
+      <c r="E8" s="3" t="str">
         <f t="shared" si="0"/>
         <v>50,50,50,50</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="4" t="s">
         <v>96</v>
       </c>
       <c r="G8" s="1" t="str">
@@ -3533,13 +3561,13 @@
       <c r="C9" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E9" s="2" t="str">
+      <c r="E9" s="3" t="str">
         <f t="shared" si="0"/>
         <v>150,150,100,100</v>
       </c>
-      <c r="F9" s="3" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,small_group!B126:B140)</f>
-        <v>sg_normalEvent_1|sg_normalEvent_2|sg_normalEvent_3|sg_normalEvent_4|sg_normalEvent_5|sg_normalEvent_6|sg_normalEvent_7|sg_normalEvent_8|sg_normalEvent_9|sg_normalEvent_10|sg_normalEvent_11|sg_normalEvent_12|sg_normalEvent_13|sg_normalEvent_14|sg_normalEvent_15</v>
+      <c r="F9" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,small_group!B126:B140)</f>
+        <v>sg_normalEvent_1,sg_normalEvent_2,sg_normalEvent_3,sg_normalEvent_4,sg_normalEvent_5,sg_normalEvent_6,sg_normalEvent_7,sg_normalEvent_8,sg_normalEvent_9,sg_normalEvent_10,sg_normalEvent_11,sg_normalEvent_12,sg_normalEvent_13,sg_normalEvent_14,sg_normalEvent_15</v>
       </c>
       <c r="G9" s="1" t="str">
         <f t="shared" si="1"/>
@@ -3565,13 +3593,13 @@
       <c r="C10" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E10" s="2" t="str">
+      <c r="E10" s="3" t="str">
         <f t="shared" si="0"/>
         <v>100,100,100,100</v>
       </c>
-      <c r="F10" s="3" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,small_group!B141:B150)</f>
-        <v>sg_normalHardEvent_1|sg_normalHardEvent_2|sg_normalHardEvent_3|sg_normalHardEvent_4|sg_normalHardEvent_5|sg_normalHardEvent_6|sg_normalHardEvent_7|sg_normalHardEvent_8|sg_normalHardEvent_9|sg_normalHardEvent_10</v>
+      <c r="F10" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,small_group!B141:B150)</f>
+        <v>sg_normalHardEvent_1,sg_normalHardEvent_2,sg_normalHardEvent_3,sg_normalHardEvent_4,sg_normalHardEvent_5,sg_normalHardEvent_6,sg_normalHardEvent_7,sg_normalHardEvent_8,sg_normalHardEvent_9,sg_normalHardEvent_10</v>
       </c>
       <c r="G10" s="1" t="str">
         <f t="shared" si="1"/>
@@ -3597,13 +3625,13 @@
       <c r="C11" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E11" s="2" t="str">
+      <c r="E11" s="3" t="str">
         <f t="shared" si="0"/>
         <v>0,50,100,100</v>
       </c>
-      <c r="F11" s="3" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,small_group!B151:B165)</f>
-        <v>sg_hardEvent_1|sg_hardEvent_2|sg_hardEvent_3|sg_hardEvent_4|sg_hardEvent_5|sg_hardEvent_6|sg_hardEvent_7|sg_hardEvent_8|sg_hardEvent_9|sg_hardEvent_10|sg_hardEvent_11|sg_hardEvent_12|sg_hardEvent_13|sg_hardEvent_14|sg_hardEvent_15</v>
+      <c r="F11" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,small_group!B151:B165)</f>
+        <v>sg_hardEvent_1,sg_hardEvent_2,sg_hardEvent_3,sg_hardEvent_4,sg_hardEvent_5,sg_hardEvent_6,sg_hardEvent_7,sg_hardEvent_8,sg_hardEvent_9,sg_hardEvent_10,sg_hardEvent_11,sg_hardEvent_12,sg_hardEvent_13,sg_hardEvent_14,sg_hardEvent_15</v>
       </c>
       <c r="G11" s="1" t="str">
         <f t="shared" si="1"/>
@@ -3632,7 +3660,7 @@
       <c r="D12" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E12" s="2" t="str">
+      <c r="E12" s="3" t="str">
         <f t="shared" si="0"/>
         <v>0,0,0,0</v>
       </c>
@@ -5317,10 +5345,10 @@
         <v>391</v>
       </c>
       <c r="Q92" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="R92" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="R92" s="1" t="s">
-        <v>393</v>
       </c>
       <c r="S92" s="1">
         <v>100</v>
@@ -5331,436 +5359,436 @@
     </row>
     <row r="93" spans="2:5">
       <c r="B93" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="D93" s="1">
+        <v>100</v>
+      </c>
+      <c r="E93" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="D93" s="1">
-        <v>100</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="94" spans="2:5">
       <c r="B94" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C94" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="D94" s="1">
+        <v>100</v>
+      </c>
+      <c r="E94" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="D94" s="1">
-        <v>100</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="95" spans="2:5">
       <c r="B95" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="D95" s="1">
+        <v>100</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>401</v>
-      </c>
-      <c r="D95" s="1">
-        <v>100</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="96" spans="2:5">
       <c r="B96" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="D96" s="1">
+        <v>100</v>
+      </c>
+      <c r="E96" s="1" t="s">
         <v>404</v>
-      </c>
-      <c r="D96" s="1">
-        <v>100</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="97" spans="2:5">
       <c r="B97" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C97" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="D97" s="1">
+        <v>100</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="D97" s="1">
-        <v>100</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="98" spans="2:5">
       <c r="B98" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C98" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="D98" s="1">
+        <v>100</v>
+      </c>
+      <c r="E98" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="D98" s="1">
-        <v>100</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="99" spans="2:5">
       <c r="B99" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C99" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="D99" s="1">
+        <v>100</v>
+      </c>
+      <c r="E99" s="1" t="s">
         <v>413</v>
-      </c>
-      <c r="D99" s="1">
-        <v>100</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="100" spans="2:5">
       <c r="B100" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C100" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="D100" s="1">
+        <v>100</v>
+      </c>
+      <c r="E100" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="D100" s="1">
-        <v>100</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="101" spans="2:5">
       <c r="B101" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C101" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="D101" s="1">
+        <v>100</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="D101" s="1">
-        <v>100</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="102" spans="2:5">
       <c r="B102" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C102" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="D102" s="1">
+        <v>100</v>
+      </c>
+      <c r="E102" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="D102" s="1">
-        <v>100</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="103" spans="2:5">
       <c r="B103" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="D103" s="1">
+        <v>100</v>
+      </c>
+      <c r="E103" s="1" t="s">
         <v>425</v>
-      </c>
-      <c r="D103" s="1">
-        <v>100</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="104" spans="2:5">
       <c r="B104" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="D104" s="1">
+        <v>100</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>428</v>
-      </c>
-      <c r="D104" s="1">
-        <v>100</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="105" spans="2:5">
       <c r="B105" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="D105" s="1">
+        <v>100</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="D105" s="1">
-        <v>100</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="106" spans="2:5">
       <c r="B106" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C106" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="D106" s="1">
+        <v>100</v>
+      </c>
+      <c r="E106" s="1" t="s">
         <v>434</v>
-      </c>
-      <c r="D106" s="1">
-        <v>100</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="107" spans="2:5">
       <c r="B107" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C107" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="D107" s="1">
+        <v>100</v>
+      </c>
+      <c r="E107" s="1" t="s">
         <v>437</v>
-      </c>
-      <c r="D107" s="1">
-        <v>100</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="108" spans="2:5">
       <c r="B108" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C108" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="D108" s="1">
+        <v>100</v>
+      </c>
+      <c r="E108" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="D108" s="1">
-        <v>100</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="109" spans="2:5">
       <c r="B109" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C109" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="D109" s="1">
+        <v>100</v>
+      </c>
+      <c r="E109" s="1" t="s">
         <v>443</v>
-      </c>
-      <c r="D109" s="1">
-        <v>100</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="110" spans="2:5">
       <c r="B110" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C110" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="D110" s="1">
+        <v>100</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="D110" s="1">
-        <v>100</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="111" spans="2:5">
       <c r="B111" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C111" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="D111" s="1">
+        <v>100</v>
+      </c>
+      <c r="E111" s="1" t="s">
         <v>449</v>
-      </c>
-      <c r="D111" s="1">
-        <v>100</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="112" spans="2:5">
       <c r="B112" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="D112" s="1">
+        <v>100</v>
+      </c>
+      <c r="E112" s="1" t="s">
         <v>452</v>
-      </c>
-      <c r="D112" s="1">
-        <v>100</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="113" spans="2:5">
       <c r="B113" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C113" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="D113" s="1">
+        <v>100</v>
+      </c>
+      <c r="E113" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="D113" s="1">
-        <v>100</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="114" spans="2:5">
       <c r="B114" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C114" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="D114" s="1">
+        <v>100</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="D114" s="1">
-        <v>100</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="115" spans="2:5">
       <c r="B115" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C115" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="D115" s="1">
+        <v>100</v>
+      </c>
+      <c r="E115" s="1" t="s">
         <v>461</v>
-      </c>
-      <c r="D115" s="1">
-        <v>100</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="116" spans="2:5">
       <c r="B116" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C116" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="D116" s="1">
+        <v>100</v>
+      </c>
+      <c r="E116" s="1" t="s">
         <v>464</v>
-      </c>
-      <c r="D116" s="1">
-        <v>100</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="117" spans="2:5">
       <c r="B117" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C117" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="D117" s="1">
+        <v>100</v>
+      </c>
+      <c r="E117" s="1" t="s">
         <v>467</v>
-      </c>
-      <c r="D117" s="1">
-        <v>100</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="118" spans="2:5">
       <c r="B118" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C118" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="D118" s="1">
+        <v>100</v>
+      </c>
+      <c r="E118" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="D118" s="1">
-        <v>100</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="119" spans="2:5">
       <c r="B119" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C119" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="D119" s="1">
+        <v>100</v>
+      </c>
+      <c r="E119" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="D119" s="1">
-        <v>100</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="120" spans="2:5">
       <c r="B120" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C120" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="D120" s="1">
+        <v>100</v>
+      </c>
+      <c r="E120" s="1" t="s">
         <v>476</v>
-      </c>
-      <c r="D120" s="1">
-        <v>100</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="121" spans="2:5">
       <c r="B121" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C121" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="D121" s="1">
+        <v>100</v>
+      </c>
+      <c r="E121" s="1" t="s">
         <v>479</v>
-      </c>
-      <c r="D121" s="1">
-        <v>100</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="122" spans="2:5">
       <c r="B122" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C122" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="D122" s="1">
+        <v>100</v>
+      </c>
+      <c r="E122" s="1" t="s">
         <v>482</v>
-      </c>
-      <c r="D122" s="1">
-        <v>100</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="123" spans="2:5">
       <c r="B123" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C123" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="C123" s="1" t="s">
+      <c r="D123" s="1">
+        <v>100</v>
+      </c>
+      <c r="E123" s="1" t="s">
         <v>485</v>
-      </c>
-      <c r="D123" s="1">
-        <v>100</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="124" spans="2:5">
@@ -5768,7 +5796,7 @@
         <v>92</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D124" s="1">
         <v>100</v>
@@ -5782,7 +5810,7 @@
         <v>96</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D125" s="1">
         <v>100</v>
@@ -5793,198 +5821,198 @@
     </row>
     <row r="126" spans="2:5">
       <c r="B126" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="C126" s="1" t="s">
+      <c r="D126" s="1">
+        <v>100</v>
+      </c>
+      <c r="E126" s="1" t="s">
         <v>490</v>
-      </c>
-      <c r="D126" s="1">
-        <v>100</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="127" spans="2:5">
       <c r="B127" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C127" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="D127" s="1">
+        <v>100</v>
+      </c>
+      <c r="E127" s="1" t="s">
         <v>493</v>
-      </c>
-      <c r="D127" s="1">
-        <v>100</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="128" spans="2:5">
       <c r="B128" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C128" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="C128" s="1" t="s">
+      <c r="D128" s="1">
+        <v>100</v>
+      </c>
+      <c r="E128" s="1" t="s">
         <v>496</v>
-      </c>
-      <c r="D128" s="1">
-        <v>100</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="129" spans="2:5">
       <c r="B129" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C129" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="C129" s="1" t="s">
+      <c r="D129" s="1">
+        <v>100</v>
+      </c>
+      <c r="E129" s="1" t="s">
         <v>499</v>
-      </c>
-      <c r="D129" s="1">
-        <v>100</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="130" spans="2:5">
       <c r="B130" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C130" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="C130" s="1" t="s">
+      <c r="D130" s="1">
+        <v>100</v>
+      </c>
+      <c r="E130" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="D130" s="1">
-        <v>100</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="131" spans="2:5">
       <c r="B131" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C131" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="C131" s="1" t="s">
+      <c r="D131" s="1">
+        <v>100</v>
+      </c>
+      <c r="E131" s="1" t="s">
         <v>505</v>
-      </c>
-      <c r="D131" s="1">
-        <v>100</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="132" spans="2:5">
       <c r="B132" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C132" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="C132" s="1" t="s">
+      <c r="D132" s="1">
+        <v>100</v>
+      </c>
+      <c r="E132" s="1" t="s">
         <v>508</v>
-      </c>
-      <c r="D132" s="1">
-        <v>100</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="133" spans="2:5">
       <c r="B133" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="C133" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="C133" s="1" t="s">
+      <c r="D133" s="1">
+        <v>100</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>511</v>
-      </c>
-      <c r="D133" s="1">
-        <v>100</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="134" spans="2:5">
       <c r="B134" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C134" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="C134" s="1" t="s">
+      <c r="D134" s="1">
+        <v>100</v>
+      </c>
+      <c r="E134" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="D134" s="1">
-        <v>100</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="135" spans="2:5">
       <c r="B135" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="C135" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="C135" s="1" t="s">
+      <c r="D135" s="1">
+        <v>100</v>
+      </c>
+      <c r="E135" s="1" t="s">
         <v>517</v>
-      </c>
-      <c r="D135" s="1">
-        <v>100</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="136" spans="2:5">
       <c r="B136" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="C136" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="C136" s="1" t="s">
+      <c r="D136" s="1">
+        <v>100</v>
+      </c>
+      <c r="E136" s="1" t="s">
         <v>520</v>
-      </c>
-      <c r="D136" s="1">
-        <v>100</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="137" spans="2:5">
       <c r="B137" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="C137" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="C137" s="1" t="s">
+      <c r="D137" s="1">
+        <v>100</v>
+      </c>
+      <c r="E137" s="1" t="s">
         <v>523</v>
-      </c>
-      <c r="D137" s="1">
-        <v>100</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="138" spans="2:5">
       <c r="B138" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C138" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="C138" s="1" t="s">
+      <c r="D138" s="1">
+        <v>100</v>
+      </c>
+      <c r="E138" s="1" t="s">
         <v>526</v>
-      </c>
-      <c r="D138" s="1">
-        <v>100</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="139" spans="2:5">
       <c r="B139" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="C139" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="C139" s="1" t="s">
+      <c r="D139" s="1">
+        <v>100</v>
+      </c>
+      <c r="E139" s="1" t="s">
         <v>529</v>
-      </c>
-      <c r="D139" s="1">
-        <v>100</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="140" spans="2:5">
@@ -5992,13 +6020,13 @@
         <v>119</v>
       </c>
       <c r="C140" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="D140" s="1">
+        <v>100</v>
+      </c>
+      <c r="E140" s="1" t="s">
         <v>531</v>
-      </c>
-      <c r="D140" s="1">
-        <v>100</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="141" spans="2:5">
@@ -6006,139 +6034,139 @@
         <v>123</v>
       </c>
       <c r="C141" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="D141" s="1">
+        <v>100</v>
+      </c>
+      <c r="E141" s="1" t="s">
         <v>533</v>
-      </c>
-      <c r="D141" s="1">
-        <v>100</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="142" spans="2:5">
       <c r="B142" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C142" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="C142" s="1" t="s">
+      <c r="D142" s="1">
+        <v>100</v>
+      </c>
+      <c r="E142" s="1" t="s">
         <v>536</v>
-      </c>
-      <c r="D142" s="1">
-        <v>100</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="143" spans="2:5">
       <c r="B143" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C143" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="C143" s="1" t="s">
+      <c r="D143" s="1">
+        <v>100</v>
+      </c>
+      <c r="E143" s="1" t="s">
         <v>539</v>
-      </c>
-      <c r="D143" s="1">
-        <v>100</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="144" spans="2:5">
       <c r="B144" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="C144" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C144" s="1" t="s">
+      <c r="D144" s="1">
+        <v>100</v>
+      </c>
+      <c r="E144" s="1" t="s">
         <v>542</v>
-      </c>
-      <c r="D144" s="1">
-        <v>100</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="145" spans="2:5">
       <c r="B145" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C145" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="C145" s="1" t="s">
+      <c r="D145" s="1">
+        <v>100</v>
+      </c>
+      <c r="E145" s="1" t="s">
         <v>545</v>
-      </c>
-      <c r="D145" s="1">
-        <v>100</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="146" spans="2:5">
       <c r="B146" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="C146" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="C146" s="1" t="s">
+      <c r="D146" s="1">
+        <v>100</v>
+      </c>
+      <c r="E146" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="D146" s="1">
-        <v>100</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="147" spans="2:5">
       <c r="B147" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="C147" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="C147" s="1" t="s">
+      <c r="D147" s="1">
+        <v>100</v>
+      </c>
+      <c r="E147" s="1" t="s">
         <v>551</v>
-      </c>
-      <c r="D147" s="1">
-        <v>100</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="148" spans="2:5">
       <c r="B148" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="C148" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C148" s="1" t="s">
+      <c r="D148" s="1">
+        <v>100</v>
+      </c>
+      <c r="E148" s="1" t="s">
         <v>554</v>
-      </c>
-      <c r="D148" s="1">
-        <v>100</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="149" spans="2:5">
       <c r="B149" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="C149" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="C149" s="1" t="s">
+      <c r="D149" s="1">
+        <v>100</v>
+      </c>
+      <c r="E149" s="1" t="s">
         <v>557</v>
-      </c>
-      <c r="D149" s="1">
-        <v>100</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="150" spans="2:5">
       <c r="B150" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C150" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="C150" s="1" t="s">
+      <c r="D150" s="1">
+        <v>100</v>
+      </c>
+      <c r="E150" s="1" t="s">
         <v>560</v>
-      </c>
-      <c r="D150" s="1">
-        <v>100</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="151" spans="2:5">
@@ -6146,217 +6174,217 @@
         <v>127</v>
       </c>
       <c r="C151" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="D151" s="1">
+        <v>100</v>
+      </c>
+      <c r="E151" s="1" t="s">
         <v>562</v>
-      </c>
-      <c r="D151" s="1">
-        <v>100</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="152" spans="2:5">
       <c r="B152" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="C152" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="C152" s="1" t="s">
+      <c r="D152" s="1">
+        <v>100</v>
+      </c>
+      <c r="E152" s="1" t="s">
         <v>565</v>
-      </c>
-      <c r="D152" s="1">
-        <v>100</v>
-      </c>
-      <c r="E152" s="1" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="153" spans="2:5">
       <c r="B153" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="C153" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="C153" s="1" t="s">
+      <c r="D153" s="1">
+        <v>100</v>
+      </c>
+      <c r="E153" s="1" t="s">
         <v>568</v>
-      </c>
-      <c r="D153" s="1">
-        <v>100</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="154" spans="2:5">
       <c r="B154" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="C154" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="C154" s="1" t="s">
+      <c r="D154" s="1">
+        <v>100</v>
+      </c>
+      <c r="E154" s="1" t="s">
         <v>571</v>
-      </c>
-      <c r="D154" s="1">
-        <v>100</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="155" spans="2:5">
       <c r="B155" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="C155" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="C155" s="1" t="s">
+      <c r="D155" s="1">
+        <v>100</v>
+      </c>
+      <c r="E155" s="1" t="s">
         <v>574</v>
-      </c>
-      <c r="D155" s="1">
-        <v>100</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="156" spans="2:5">
       <c r="B156" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="C156" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="C156" s="1" t="s">
+      <c r="D156" s="1">
+        <v>100</v>
+      </c>
+      <c r="E156" s="1" t="s">
         <v>577</v>
-      </c>
-      <c r="D156" s="1">
-        <v>100</v>
-      </c>
-      <c r="E156" s="1" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="157" spans="2:5">
       <c r="B157" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="C157" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="C157" s="1" t="s">
+      <c r="D157" s="1">
+        <v>100</v>
+      </c>
+      <c r="E157" s="1" t="s">
         <v>580</v>
-      </c>
-      <c r="D157" s="1">
-        <v>100</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="158" spans="2:5">
       <c r="B158" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="C158" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="C158" s="1" t="s">
+      <c r="D158" s="1">
+        <v>100</v>
+      </c>
+      <c r="E158" s="1" t="s">
         <v>583</v>
-      </c>
-      <c r="D158" s="1">
-        <v>100</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="159" spans="2:5">
       <c r="B159" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="C159" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="C159" s="1" t="s">
+      <c r="D159" s="1">
+        <v>100</v>
+      </c>
+      <c r="E159" s="1" t="s">
         <v>586</v>
-      </c>
-      <c r="D159" s="1">
-        <v>100</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="160" spans="2:5">
       <c r="B160" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="C160" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="C160" s="1" t="s">
+      <c r="D160" s="1">
+        <v>100</v>
+      </c>
+      <c r="E160" s="1" t="s">
         <v>589</v>
-      </c>
-      <c r="D160" s="1">
-        <v>100</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="161" spans="2:5">
       <c r="B161" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="C161" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="C161" s="1" t="s">
+      <c r="D161" s="1">
+        <v>100</v>
+      </c>
+      <c r="E161" s="1" t="s">
         <v>592</v>
-      </c>
-      <c r="D161" s="1">
-        <v>100</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="162" spans="2:5">
       <c r="B162" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="C162" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="C162" s="1" t="s">
+      <c r="D162" s="1">
+        <v>100</v>
+      </c>
+      <c r="E162" s="1" t="s">
         <v>595</v>
-      </c>
-      <c r="D162" s="1">
-        <v>100</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="163" spans="2:5">
       <c r="B163" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="C163" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="C163" s="1" t="s">
+      <c r="D163" s="1">
+        <v>100</v>
+      </c>
+      <c r="E163" s="1" t="s">
         <v>598</v>
-      </c>
-      <c r="D163" s="1">
-        <v>100</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="164" spans="2:5">
       <c r="B164" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="C164" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="C164" s="1" t="s">
+      <c r="D164" s="1">
+        <v>100</v>
+      </c>
+      <c r="E164" s="1" t="s">
         <v>601</v>
-      </c>
-      <c r="D164" s="1">
-        <v>100</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="165" spans="2:5">
       <c r="B165" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C165" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="C165" s="1" t="s">
+      <c r="D165" s="1">
+        <v>100</v>
+      </c>
+      <c r="E165" s="1" t="s">
         <v>604</v>
-      </c>
-      <c r="D165" s="1">
-        <v>100</v>
-      </c>
-      <c r="E165" s="1" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="166" spans="2:5">
       <c r="B166" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C166" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>393</v>
       </c>
       <c r="D166" s="1">
         <v>100</v>
@@ -6366,7 +6394,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:B166">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:B166" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6377,8 +6405,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="7"/>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
     <col min="2" max="2" width="32.2307692307692" customWidth="1"/>
@@ -6389,7 +6417,7 @@
     <col min="8" max="8" width="15.1538461538462" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6397,25 +6425,28 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>605</v>
+      </c>
+      <c r="D1" t="s">
         <v>606</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>607</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>608</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>609</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>610</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -6440,8 +6471,11 @@
       <c r="H2" t="s">
         <v>618</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -6449,27 +6483,33 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D3" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E3" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F3" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="G3" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="2:7">
+      <c r="I3" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>622</v>
+      </c>
       <c r="B4" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -6486,10 +6526,19 @@
       <c r="G4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="2:7">
+      <c r="H4" t="s">
+        <v>622</v>
+      </c>
+      <c r="I4" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>622</v>
+      </c>
       <c r="B5" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="C5">
         <v>95</v>
@@ -6506,8 +6555,17 @@
       <c r="G5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="2:7">
+      <c r="H5" t="s">
+        <v>622</v>
+      </c>
+      <c r="I5" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>622</v>
+      </c>
       <c r="B6" t="s">
         <v>91</v>
       </c>
@@ -6526,8 +6584,17 @@
       <c r="G6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="2:7">
+      <c r="H6" t="s">
+        <v>622</v>
+      </c>
+      <c r="I6" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>622</v>
+      </c>
       <c r="B7" t="s">
         <v>105</v>
       </c>
@@ -6545,6 +6612,194 @@
       </c>
       <c r="G7">
         <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>622</v>
+      </c>
+      <c r="I7" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B8" t="s">
+        <v>622</v>
+      </c>
+      <c r="C8" t="s">
+        <v>622</v>
+      </c>
+      <c r="D8" t="s">
+        <v>622</v>
+      </c>
+      <c r="E8" t="s">
+        <v>622</v>
+      </c>
+      <c r="F8" t="s">
+        <v>622</v>
+      </c>
+      <c r="G8" t="s">
+        <v>622</v>
+      </c>
+      <c r="H8" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>622</v>
+      </c>
+      <c r="B9" t="s">
+        <v>622</v>
+      </c>
+      <c r="C9" t="s">
+        <v>622</v>
+      </c>
+      <c r="D9" t="s">
+        <v>622</v>
+      </c>
+      <c r="E9" t="s">
+        <v>622</v>
+      </c>
+      <c r="F9" t="s">
+        <v>622</v>
+      </c>
+      <c r="G9" t="s">
+        <v>622</v>
+      </c>
+      <c r="H9" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>622</v>
+      </c>
+      <c r="B10" t="s">
+        <v>622</v>
+      </c>
+      <c r="C10" t="s">
+        <v>622</v>
+      </c>
+      <c r="D10" t="s">
+        <v>622</v>
+      </c>
+      <c r="E10" t="s">
+        <v>622</v>
+      </c>
+      <c r="F10" t="s">
+        <v>622</v>
+      </c>
+      <c r="G10" t="s">
+        <v>622</v>
+      </c>
+      <c r="H10" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>622</v>
+      </c>
+      <c r="B11" t="s">
+        <v>622</v>
+      </c>
+      <c r="C11" t="s">
+        <v>622</v>
+      </c>
+      <c r="D11" t="s">
+        <v>622</v>
+      </c>
+      <c r="E11" t="s">
+        <v>622</v>
+      </c>
+      <c r="F11" t="s">
+        <v>622</v>
+      </c>
+      <c r="G11" t="s">
+        <v>622</v>
+      </c>
+      <c r="H11" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>622</v>
+      </c>
+      <c r="B12" t="s">
+        <v>622</v>
+      </c>
+      <c r="C12" t="s">
+        <v>622</v>
+      </c>
+      <c r="D12" t="s">
+        <v>622</v>
+      </c>
+      <c r="E12" t="s">
+        <v>622</v>
+      </c>
+      <c r="F12" t="s">
+        <v>622</v>
+      </c>
+      <c r="G12" t="s">
+        <v>622</v>
+      </c>
+      <c r="H12" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>622</v>
+      </c>
+      <c r="B13" t="s">
+        <v>622</v>
+      </c>
+      <c r="C13" t="s">
+        <v>622</v>
+      </c>
+      <c r="D13" t="s">
+        <v>622</v>
+      </c>
+      <c r="E13" t="s">
+        <v>622</v>
+      </c>
+      <c r="F13" t="s">
+        <v>622</v>
+      </c>
+      <c r="G13" t="s">
+        <v>622</v>
+      </c>
+      <c r="H13" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>622</v>
+      </c>
+      <c r="B14" t="s">
+        <v>622</v>
+      </c>
+      <c r="C14" t="s">
+        <v>622</v>
+      </c>
+      <c r="D14" t="s">
+        <v>622</v>
+      </c>
+      <c r="E14" t="s">
+        <v>622</v>
+      </c>
+      <c r="F14" t="s">
+        <v>622</v>
+      </c>
+      <c r="G14" t="s">
+        <v>622</v>
+      </c>
+      <c r="H14" t="s">
+        <v>622</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16760" activeTab="1"/>
+    <workbookView windowHeight="15240"/>
   </bookViews>
   <sheets>
     <sheet name="action" sheetId="1" r:id="rId1"/>
@@ -15,25 +15,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">small_group!$B$1:$B$166</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="613">
   <si>
     <t>##var</t>
   </si>
@@ -98,10 +85,7 @@
     <t>act_food_gold</t>
   </si>
   <si>
-    <t>美食</t>
-  </si>
-  <si>
-    <t>普通美食：主要奖励金币。</t>
+    <t>日常营业</t>
   </si>
   <si>
     <t>Food</t>
@@ -113,46 +97,31 @@
     <t>act_food_fragment</t>
   </si>
   <si>
-    <t>普通美食：主要奖励胃部碎片。</t>
-  </si>
-  <si>
     <t>food_fragment</t>
   </si>
   <si>
     <t>act_food_passive</t>
   </si>
   <si>
-    <t>普通美食：主要奖励被动道具。</t>
-  </si>
-  <si>
     <t>food_passive</t>
   </si>
   <si>
     <t>act_food_active</t>
   </si>
   <si>
-    <t>普通美食：主要奖励主动道具。</t>
-  </si>
-  <si>
     <t>food_active</t>
   </si>
   <si>
     <t>act_food_dish</t>
   </si>
   <si>
-    <t>普通美食：主要奖励菜品。</t>
-  </si>
-  <si>
     <t>food_dish</t>
   </si>
   <si>
     <t>act_food_hard_gold</t>
   </si>
   <si>
-    <t>超级美食</t>
-  </si>
-  <si>
-    <t>困难美食：主要奖励金币。</t>
+    <t>火热营业</t>
   </si>
   <si>
     <t>food_hard_gold</t>
@@ -161,1036 +130,1015 @@
     <t>act_food_hard_fragment</t>
   </si>
   <si>
-    <t>困难美食：主要奖励胃部碎片。</t>
-  </si>
-  <si>
     <t>food_hard_fragment</t>
   </si>
   <si>
     <t>act_food_hard_passive</t>
   </si>
   <si>
-    <t>困难美食：主要奖励被动道具。</t>
-  </si>
-  <si>
     <t>food_hard_passive</t>
   </si>
   <si>
     <t>act_food_hard_active</t>
   </si>
   <si>
-    <t>困难美食：主要奖励主动道具。</t>
-  </si>
-  <si>
     <t>food_hard_active</t>
   </si>
   <si>
     <t>act_food_hard_dish</t>
   </si>
   <si>
-    <t>困难美食：主要奖励菜品。</t>
-  </si>
-  <si>
     <t>food_hard_dish</t>
   </si>
   <si>
     <t>act_event</t>
   </si>
   <si>
+    <t>突发事件</t>
+  </si>
+  <si>
+    <t>Event</t>
+  </si>
+  <si>
+    <t>act_reward</t>
+  </si>
+  <si>
+    <t>幸运事件</t>
+  </si>
+  <si>
+    <t>Reward</t>
+  </si>
+  <si>
+    <t>act_shop</t>
+  </si>
+  <si>
+    <t>商店进货</t>
+  </si>
+  <si>
+    <t>Shop</t>
+  </si>
+  <si>
+    <t>act_interest</t>
+  </si>
+  <si>
+    <t>收取利息</t>
+  </si>
+  <si>
+    <t>Interest</t>
+  </si>
+  <si>
+    <t>act_boss</t>
+  </si>
+  <si>
+    <t>美食家评鉴</t>
+  </si>
+  <si>
+    <t>food_boss</t>
+  </si>
+  <si>
+    <t>ruleIds</t>
+  </si>
+  <si>
+    <t>fallbackWeights</t>
+  </si>
+  <si>
+    <t>smallGroupIds</t>
+  </si>
+  <si>
+    <t>大组ID</t>
+  </si>
+  <si>
+    <t>大组名</t>
+  </si>
+  <si>
+    <t>参与的日程规则ID(逗号分隔),空=仅保底</t>
+  </si>
+  <si>
+    <t>随机权重列表(按周配)</t>
+  </si>
+  <si>
+    <t>包含的小组ID列表→small_group.id</t>
+  </si>
+  <si>
+    <t>(list#sep=,),float</t>
+  </si>
+  <si>
+    <t>(list#sep=,),string</t>
+  </si>
+  <si>
+    <t>lg_normal</t>
+  </si>
+  <si>
+    <t>普通美食大组</t>
+  </si>
+  <si>
+    <t>lg_normalHard</t>
+  </si>
+  <si>
+    <t>普通困难美食大组</t>
+  </si>
+  <si>
+    <t>lg_hard</t>
+  </si>
+  <si>
+    <t>困难美食大组</t>
+  </si>
+  <si>
+    <t>lg_event</t>
+  </si>
+  <si>
+    <t>事件大组</t>
+  </si>
+  <si>
+    <t>rule_event_opening</t>
+  </si>
+  <si>
+    <t>sg_event_1</t>
+  </si>
+  <si>
+    <t>lg_reward</t>
+  </si>
+  <si>
+    <t>奖励大组</t>
+  </si>
+  <si>
+    <t>rule_reward_early,rule_reward_mid</t>
+  </si>
+  <si>
+    <t>sg_reward_1</t>
+  </si>
+  <si>
+    <t>lg_normalEvent</t>
+  </si>
+  <si>
+    <t>普通事件大组</t>
+  </si>
+  <si>
+    <t>lg_normalHardEvent</t>
+  </si>
+  <si>
+    <t>普通困难事件大组</t>
+  </si>
+  <si>
+    <t>lg_hardEvent</t>
+  </si>
+  <si>
+    <t>困难事件大组</t>
+  </si>
+  <si>
+    <t>lg_debug</t>
+  </si>
+  <si>
+    <t>调试大组</t>
+  </si>
+  <si>
+    <t>rule_debug_first</t>
+  </si>
+  <si>
+    <t>sg_debug</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>actionIds</t>
+  </si>
+  <si>
+    <t>小组ID</t>
+  </si>
+  <si>
+    <t>小组名(调试用)</t>
+  </si>
+  <si>
+    <t>被大组选中的权重</t>
+  </si>
+  <si>
+    <t>小组内固定行动ID列表→action.id</t>
+  </si>
+  <si>
+    <t>sg_normal_1</t>
+  </si>
+  <si>
+    <t>普通1</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_fragment,act_food_passive</t>
+  </si>
+  <si>
+    <t>sg_normal_2</t>
+  </si>
+  <si>
+    <t>普通2</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_fragment,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalEvent_15</t>
+  </si>
+  <si>
+    <t>sg_normal_3</t>
+  </si>
+  <si>
+    <t>普通3</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_fragment,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHardEvent_1</t>
+  </si>
+  <si>
+    <t>sg_normal_4</t>
+  </si>
+  <si>
+    <t>普通4</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_hardEvent_1</t>
+  </si>
+  <si>
+    <t>sg_normal_5</t>
+  </si>
+  <si>
+    <t>普通5</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normal_6</t>
+  </si>
+  <si>
+    <t>普通6</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normal_7</t>
+  </si>
+  <si>
+    <t>普通7</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normal_8</t>
+  </si>
+  <si>
+    <t>普通8</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normal_9</t>
+  </si>
+  <si>
+    <t>普通9</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normal_10</t>
+  </si>
+  <si>
+    <t>普通10</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_food_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normal_11</t>
+  </si>
+  <si>
+    <t>普通11</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_fragment</t>
+  </si>
+  <si>
+    <t>sg_normal_12</t>
+  </si>
+  <si>
+    <t>普通12</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_passive</t>
+  </si>
+  <si>
+    <t>sg_normal_13</t>
+  </si>
+  <si>
+    <t>普通13</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normal_14</t>
+  </si>
+  <si>
+    <t>普通14</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normal_15</t>
+  </si>
+  <si>
+    <t>普通15</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_passive</t>
+  </si>
+  <si>
+    <t>sg_normal_16</t>
+  </si>
+  <si>
+    <t>普通16</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normal_17</t>
+  </si>
+  <si>
+    <t>普通17</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_dish</t>
+  </si>
+  <si>
+    <t>普通困难混合大组</t>
+  </si>
+  <si>
+    <t>sg_normal_18</t>
+  </si>
+  <si>
+    <t>普通18</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normal_19</t>
+  </si>
+  <si>
+    <t>普通19</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normal_20</t>
+  </si>
+  <si>
+    <t>普通20</t>
+  </si>
+  <si>
+    <t>act_food_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_1</t>
+  </si>
+  <si>
+    <t>普通困难1</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_fragment,act_food_passive</t>
+  </si>
+  <si>
+    <t>sg_normalHard_2</t>
+  </si>
+  <si>
+    <t>普通困难2</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_fragment,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_3</t>
+  </si>
+  <si>
+    <t>普通困难3</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_fragment,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_4</t>
+  </si>
+  <si>
+    <t>普通困难4</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_5</t>
+  </si>
+  <si>
+    <t>普通困难5</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_6</t>
+  </si>
+  <si>
+    <t>普通困难6</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_7</t>
+  </si>
+  <si>
+    <t>普通困难7</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_8</t>
+  </si>
+  <si>
+    <t>普通困难8</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_9</t>
+  </si>
+  <si>
+    <t>普通困难9</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_10</t>
+  </si>
+  <si>
+    <t>普通困难10</t>
+  </si>
+  <si>
+    <t>act_food_hard_passive,act_food_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_11</t>
+  </si>
+  <si>
+    <t>普通困难11</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_fragment</t>
+  </si>
+  <si>
+    <t>sg_normalHard_12</t>
+  </si>
+  <si>
+    <t>普通困难12</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_passive</t>
+  </si>
+  <si>
+    <t>sg_normalHard_13</t>
+  </si>
+  <si>
+    <t>普通困难13</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_14</t>
+  </si>
+  <si>
+    <t>普通困难14</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_15</t>
+  </si>
+  <si>
+    <t>普通困难15</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_passive</t>
+  </si>
+  <si>
+    <t>sg_normalHard_16</t>
+  </si>
+  <si>
+    <t>普通困难16</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_17</t>
+  </si>
+  <si>
+    <t>普通困难17</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_18</t>
+  </si>
+  <si>
+    <t>普通困难18</t>
+  </si>
+  <si>
+    <t>act_food_hard_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_19</t>
+  </si>
+  <si>
+    <t>普通困难19</t>
+  </si>
+  <si>
+    <t>act_food_hard_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_20</t>
+  </si>
+  <si>
+    <t>普通困难20</t>
+  </si>
+  <si>
+    <t>act_food_hard_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_21</t>
+  </si>
+  <si>
+    <t>普通困难21</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_fragment,act_food_passive</t>
+  </si>
+  <si>
+    <t>sg_normalHard_22</t>
+  </si>
+  <si>
+    <t>普通困难22</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_fragment,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_23</t>
+  </si>
+  <si>
+    <t>普通困难23</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_fragment,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_24</t>
+  </si>
+  <si>
+    <t>普通困难24</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_25</t>
+  </si>
+  <si>
+    <t>普通困难25</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_26</t>
+  </si>
+  <si>
+    <t>普通困难26</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_27</t>
+  </si>
+  <si>
+    <t>普通困难27</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_hard_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_28</t>
+  </si>
+  <si>
+    <t>普通困难28</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_hard_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_29</t>
+  </si>
+  <si>
+    <t>普通困难29</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_hard_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_30</t>
+  </si>
+  <si>
+    <t>普通困难30</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_food_hard_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_31</t>
+  </si>
+  <si>
+    <t>普通困难31</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_fragment</t>
+  </si>
+  <si>
+    <t>sg_normalHard_32</t>
+  </si>
+  <si>
+    <t>普通困难32</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_passive</t>
+  </si>
+  <si>
+    <t>sg_normalHard_33</t>
+  </si>
+  <si>
+    <t>普通困难33</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_34</t>
+  </si>
+  <si>
+    <t>普通困难34</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_35</t>
+  </si>
+  <si>
+    <t>普通困难35</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_hard_passive</t>
+  </si>
+  <si>
+    <t>sg_normalHard_36</t>
+  </si>
+  <si>
+    <t>普通困难36</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_37</t>
+  </si>
+  <si>
+    <t>普通困难37</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_38</t>
+  </si>
+  <si>
+    <t>普通困难38</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_39</t>
+  </si>
+  <si>
+    <t>普通困难39</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_40</t>
+  </si>
+  <si>
+    <t>普通困难40</t>
+  </si>
+  <si>
+    <t>act_food_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_41</t>
+  </si>
+  <si>
+    <t>普通困难41</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_fragment,act_food_hard_passive</t>
+  </si>
+  <si>
+    <t>sg_normalHard_42</t>
+  </si>
+  <si>
+    <t>普通困难42</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_fragment,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_43</t>
+  </si>
+  <si>
+    <t>普通困难43</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_fragment,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_44</t>
+  </si>
+  <si>
+    <t>普通困难44</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_passive,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_45</t>
+  </si>
+  <si>
+    <t>普通困难45</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_passive,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_46</t>
+  </si>
+  <si>
+    <t>普通困难46</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_47</t>
+  </si>
+  <si>
+    <t>普通困难47</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_passive,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_48</t>
+  </si>
+  <si>
+    <t>普通困难48</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_passive,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_49</t>
+  </si>
+  <si>
+    <t>普通困难49</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_50</t>
+  </si>
+  <si>
+    <t>普通困难50</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_food_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_51</t>
+  </si>
+  <si>
+    <t>普通困难51</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_fragment,act_food_passive</t>
+  </si>
+  <si>
+    <t>sg_normalHard_52</t>
+  </si>
+  <si>
+    <t>普通困难52</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_fragment,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_53</t>
+  </si>
+  <si>
+    <t>普通困难53</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_fragment,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_54</t>
+  </si>
+  <si>
+    <t>普通困难54</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_55</t>
+  </si>
+  <si>
+    <t>普通困难55</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_food_b</t>
+  </si>
+  <si>
+    <t>美食B</t>
+  </si>
+  <si>
+    <t>sg_normalHard_56</t>
+  </si>
+  <si>
+    <t>普通困难56</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_57</t>
+  </si>
+  <si>
+    <t>普通困难57</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_hard_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_58</t>
+  </si>
+  <si>
+    <t>普通困难58</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_hard_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_food_hard_a</t>
+  </si>
+  <si>
+    <t>硬菜A</t>
+  </si>
+  <si>
+    <t>sg_normalHard_59</t>
+  </si>
+  <si>
+    <t>普通困难59</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_hard_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_60</t>
+  </si>
+  <si>
+    <t>普通困难60</t>
+  </si>
+  <si>
+    <t>act_food_hard_passive,act_food_hard_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_61</t>
+  </si>
+  <si>
+    <t>普通困难61</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_fragment,act_food_hard_passive</t>
+  </si>
+  <si>
+    <t>sg_food_hard_b</t>
+  </si>
+  <si>
+    <t>硬菜B</t>
+  </si>
+  <si>
+    <t>sg_normalHard_62</t>
+  </si>
+  <si>
+    <t>普通困难62</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_fragment,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_63</t>
+  </si>
+  <si>
+    <t>普通困难63</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_fragment,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_64</t>
+  </si>
+  <si>
+    <t>普通困难64</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_passive,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_event</t>
+  </si>
+  <si>
     <t>事件</t>
   </si>
   <si>
-    <t>一个待揭晓的事件。</t>
-  </si>
-  <si>
-    <t>Event</t>
-  </si>
-  <si>
-    <t>act_reward</t>
+    <t>sg_normalHard_65</t>
+  </si>
+  <si>
+    <t>普通困难65</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_passive,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_66</t>
+  </si>
+  <si>
+    <t>普通困难66</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_67</t>
+  </si>
+  <si>
+    <t>普通困难67</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_hard_passive,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_reward</t>
   </si>
   <si>
     <t>奖励</t>
-  </si>
-  <si>
-    <t>一份即时奖励。</t>
-  </si>
-  <si>
-    <t>Reward</t>
-  </si>
-  <si>
-    <t>act_shop</t>
-  </si>
-  <si>
-    <t>商店</t>
-  </si>
-  <si>
-    <t>去食材店转转，买卖道具。</t>
-  </si>
-  <si>
-    <t>Shop</t>
-  </si>
-  <si>
-    <t>act_interest</t>
-  </si>
-  <si>
-    <t>利息</t>
-  </si>
-  <si>
-    <t>到点自动结算利息。</t>
-  </si>
-  <si>
-    <t>Interest</t>
-  </si>
-  <si>
-    <t>act_boss</t>
-  </si>
-  <si>
-    <t>盛宴</t>
-  </si>
-  <si>
-    <t>带有特殊机制的盛宴挑战。</t>
-  </si>
-  <si>
-    <t>food_boss</t>
-  </si>
-  <si>
-    <t>ruleIds</t>
-  </si>
-  <si>
-    <t>fallbackWeights</t>
-  </si>
-  <si>
-    <t>smallGroupIds</t>
-  </si>
-  <si>
-    <t>大组ID</t>
-  </si>
-  <si>
-    <t>大组名</t>
-  </si>
-  <si>
-    <t>参与的日程规则ID(逗号分隔),空=仅保底</t>
-  </si>
-  <si>
-    <t>随机权重列表(按周配)</t>
-  </si>
-  <si>
-    <t>包含的小组ID列表→small_group.id</t>
-  </si>
-  <si>
-    <t>(list#sep=,),float</t>
-  </si>
-  <si>
-    <t>(list#sep=,),string</t>
-  </si>
-  <si>
-    <t>lg_normal</t>
-  </si>
-  <si>
-    <t>普通美食大组</t>
-  </si>
-  <si>
-    <t>lg_normalHard</t>
-  </si>
-  <si>
-    <t>普通困难美食大组</t>
-  </si>
-  <si>
-    <t>lg_hard</t>
-  </si>
-  <si>
-    <t>困难美食大组</t>
-  </si>
-  <si>
-    <t>lg_event</t>
-  </si>
-  <si>
-    <t>事件大组</t>
-  </si>
-  <si>
-    <t>rule_event_opening</t>
-  </si>
-  <si>
-    <t>sg_event_1</t>
-  </si>
-  <si>
-    <t>lg_reward</t>
-  </si>
-  <si>
-    <t>奖励大组</t>
-  </si>
-  <si>
-    <t>rule_reward_early,rule_reward_mid</t>
-  </si>
-  <si>
-    <t>sg_reward_1</t>
-  </si>
-  <si>
-    <t>lg_normalEvent</t>
-  </si>
-  <si>
-    <t>普通事件大组</t>
-  </si>
-  <si>
-    <t>lg_normalHardEvent</t>
-  </si>
-  <si>
-    <t>普通困难事件大组</t>
-  </si>
-  <si>
-    <t>lg_hardEvent</t>
-  </si>
-  <si>
-    <t>困难事件大组</t>
-  </si>
-  <si>
-    <t>lg_debug</t>
-  </si>
-  <si>
-    <t>调试大组</t>
-  </si>
-  <si>
-    <t>rule_debug_first</t>
-  </si>
-  <si>
-    <t>sg_debug</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>actionIds</t>
-  </si>
-  <si>
-    <t>小组ID</t>
-  </si>
-  <si>
-    <t>小组名(调试用)</t>
-  </si>
-  <si>
-    <t>被大组选中的权重</t>
-  </si>
-  <si>
-    <t>小组内固定行动ID列表→action.id</t>
-  </si>
-  <si>
-    <t>sg_normal_1</t>
-  </si>
-  <si>
-    <t>普通1</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_fragment,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normal_2</t>
-  </si>
-  <si>
-    <t>普通2</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_fragment,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalEvent_15</t>
-  </si>
-  <si>
-    <t>sg_normal_3</t>
-  </si>
-  <si>
-    <t>普通3</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_fragment,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHardEvent_1</t>
-  </si>
-  <si>
-    <t>sg_normal_4</t>
-  </si>
-  <si>
-    <t>普通4</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_hardEvent_1</t>
-  </si>
-  <si>
-    <t>sg_normal_5</t>
-  </si>
-  <si>
-    <t>普通5</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normal_6</t>
-  </si>
-  <si>
-    <t>普通6</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normal_7</t>
-  </si>
-  <si>
-    <t>普通7</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normal_8</t>
-  </si>
-  <si>
-    <t>普通8</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normal_9</t>
-  </si>
-  <si>
-    <t>普通9</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normal_10</t>
-  </si>
-  <si>
-    <t>普通10</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_food_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normal_11</t>
-  </si>
-  <si>
-    <t>普通11</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_fragment</t>
-  </si>
-  <si>
-    <t>sg_normal_12</t>
-  </si>
-  <si>
-    <t>普通12</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normal_13</t>
-  </si>
-  <si>
-    <t>普通13</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normal_14</t>
-  </si>
-  <si>
-    <t>普通14</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normal_15</t>
-  </si>
-  <si>
-    <t>普通15</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normal_16</t>
-  </si>
-  <si>
-    <t>普通16</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normal_17</t>
-  </si>
-  <si>
-    <t>普通17</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_dish</t>
-  </si>
-  <si>
-    <t>普通困难混合大组</t>
-  </si>
-  <si>
-    <t>sg_normal_18</t>
-  </si>
-  <si>
-    <t>普通18</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normal_19</t>
-  </si>
-  <si>
-    <t>普通19</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normal_20</t>
-  </si>
-  <si>
-    <t>普通20</t>
-  </si>
-  <si>
-    <t>act_food_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_1</t>
-  </si>
-  <si>
-    <t>普通困难1</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_fragment,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normalHard_2</t>
-  </si>
-  <si>
-    <t>普通困难2</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_fragment,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_3</t>
-  </si>
-  <si>
-    <t>普通困难3</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_fragment,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_4</t>
-  </si>
-  <si>
-    <t>普通困难4</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_5</t>
-  </si>
-  <si>
-    <t>普通困难5</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_6</t>
-  </si>
-  <si>
-    <t>普通困难6</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_7</t>
-  </si>
-  <si>
-    <t>普通困难7</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_8</t>
-  </si>
-  <si>
-    <t>普通困难8</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_9</t>
-  </si>
-  <si>
-    <t>普通困难9</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_10</t>
-  </si>
-  <si>
-    <t>普通困难10</t>
-  </si>
-  <si>
-    <t>act_food_hard_passive,act_food_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_11</t>
-  </si>
-  <si>
-    <t>普通困难11</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_fragment</t>
-  </si>
-  <si>
-    <t>sg_normalHard_12</t>
-  </si>
-  <si>
-    <t>普通困难12</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normalHard_13</t>
-  </si>
-  <si>
-    <t>普通困难13</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_14</t>
-  </si>
-  <si>
-    <t>普通困难14</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_15</t>
-  </si>
-  <si>
-    <t>普通困难15</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normalHard_16</t>
-  </si>
-  <si>
-    <t>普通困难16</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_17</t>
-  </si>
-  <si>
-    <t>普通困难17</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_18</t>
-  </si>
-  <si>
-    <t>普通困难18</t>
-  </si>
-  <si>
-    <t>act_food_hard_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_19</t>
-  </si>
-  <si>
-    <t>普通困难19</t>
-  </si>
-  <si>
-    <t>act_food_hard_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_20</t>
-  </si>
-  <si>
-    <t>普通困难20</t>
-  </si>
-  <si>
-    <t>act_food_hard_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_21</t>
-  </si>
-  <si>
-    <t>普通困难21</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_fragment,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normalHard_22</t>
-  </si>
-  <si>
-    <t>普通困难22</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_fragment,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_23</t>
-  </si>
-  <si>
-    <t>普通困难23</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_fragment,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_24</t>
-  </si>
-  <si>
-    <t>普通困难24</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_25</t>
-  </si>
-  <si>
-    <t>普通困难25</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_26</t>
-  </si>
-  <si>
-    <t>普通困难26</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_27</t>
-  </si>
-  <si>
-    <t>普通困难27</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_hard_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_28</t>
-  </si>
-  <si>
-    <t>普通困难28</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_hard_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_29</t>
-  </si>
-  <si>
-    <t>普通困难29</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_hard_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_30</t>
-  </si>
-  <si>
-    <t>普通困难30</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_food_hard_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_31</t>
-  </si>
-  <si>
-    <t>普通困难31</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_fragment</t>
-  </si>
-  <si>
-    <t>sg_normalHard_32</t>
-  </si>
-  <si>
-    <t>普通困难32</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_passive</t>
-  </si>
-  <si>
-    <t>sg_normalHard_33</t>
-  </si>
-  <si>
-    <t>普通困难33</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_34</t>
-  </si>
-  <si>
-    <t>普通困难34</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_35</t>
-  </si>
-  <si>
-    <t>普通困难35</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_hard_passive</t>
-  </si>
-  <si>
-    <t>sg_normalHard_36</t>
-  </si>
-  <si>
-    <t>普通困难36</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_37</t>
-  </si>
-  <si>
-    <t>普通困难37</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_38</t>
-  </si>
-  <si>
-    <t>普通困难38</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_39</t>
-  </si>
-  <si>
-    <t>普通困难39</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_40</t>
-  </si>
-  <si>
-    <t>普通困难40</t>
-  </si>
-  <si>
-    <t>act_food_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_41</t>
-  </si>
-  <si>
-    <t>普通困难41</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_fragment,act_food_hard_passive</t>
-  </si>
-  <si>
-    <t>sg_normalHard_42</t>
-  </si>
-  <si>
-    <t>普通困难42</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_fragment,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_43</t>
-  </si>
-  <si>
-    <t>普通困难43</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_fragment,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_44</t>
-  </si>
-  <si>
-    <t>普通困难44</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_passive,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_45</t>
-  </si>
-  <si>
-    <t>普通困难45</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_passive,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_46</t>
-  </si>
-  <si>
-    <t>普通困难46</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_47</t>
-  </si>
-  <si>
-    <t>普通困难47</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_passive,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_48</t>
-  </si>
-  <si>
-    <t>普通困难48</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_passive,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_49</t>
-  </si>
-  <si>
-    <t>普通困难49</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_50</t>
-  </si>
-  <si>
-    <t>普通困难50</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_food_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_51</t>
-  </si>
-  <si>
-    <t>普通困难51</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_fragment,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normalHard_52</t>
-  </si>
-  <si>
-    <t>普通困难52</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_fragment,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_53</t>
-  </si>
-  <si>
-    <t>普通困难53</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_fragment,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_54</t>
-  </si>
-  <si>
-    <t>普通困难54</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_55</t>
-  </si>
-  <si>
-    <t>普通困难55</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_food_b</t>
-  </si>
-  <si>
-    <t>美食B</t>
-  </si>
-  <si>
-    <t>sg_normalHard_56</t>
-  </si>
-  <si>
-    <t>普通困难56</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_57</t>
-  </si>
-  <si>
-    <t>普通困难57</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_hard_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_58</t>
-  </si>
-  <si>
-    <t>普通困难58</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_hard_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_food_hard_a</t>
-  </si>
-  <si>
-    <t>硬菜A</t>
-  </si>
-  <si>
-    <t>sg_normalHard_59</t>
-  </si>
-  <si>
-    <t>普通困难59</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_hard_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_60</t>
-  </si>
-  <si>
-    <t>普通困难60</t>
-  </si>
-  <si>
-    <t>act_food_hard_passive,act_food_hard_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_61</t>
-  </si>
-  <si>
-    <t>普通困难61</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_fragment,act_food_hard_passive</t>
-  </si>
-  <si>
-    <t>sg_food_hard_b</t>
-  </si>
-  <si>
-    <t>硬菜B</t>
-  </si>
-  <si>
-    <t>sg_normalHard_62</t>
-  </si>
-  <si>
-    <t>普通困难62</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_fragment,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_63</t>
-  </si>
-  <si>
-    <t>普通困难63</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_fragment,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_64</t>
-  </si>
-  <si>
-    <t>普通困难64</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_passive,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_event</t>
-  </si>
-  <si>
-    <t>sg_normalHard_65</t>
-  </si>
-  <si>
-    <t>普通困难65</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_passive,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_66</t>
-  </si>
-  <si>
-    <t>普通困难66</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_67</t>
-  </si>
-  <si>
-    <t>普通困难67</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_hard_passive,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_reward</t>
   </si>
   <si>
     <t>sg_normalHard_68</t>
@@ -1916,7 +1864,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -2983,14 +2931,12 @@
       <c r="C4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4"/>
+      <c r="E4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>23</v>
-      </c>
-      <c r="F4" t="s">
-        <v>24</v>
       </c>
       <c r="G4">
         <v>0.5</v>
@@ -3001,19 +2947,17 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
       </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
+      <c r="D5"/>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G5">
         <v>0.5</v>
@@ -3024,19 +2968,17 @@
     </row>
     <row r="6" spans="2:8">
       <c r="B6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
       </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
+      <c r="D6"/>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G6">
         <v>0.5</v>
@@ -3047,19 +2989,17 @@
     </row>
     <row r="7" spans="2:8">
       <c r="B7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
         <v>21</v>
       </c>
-      <c r="D7" t="s">
-        <v>32</v>
-      </c>
+      <c r="D7"/>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G7">
         <v>0.5</v>
@@ -3070,19 +3010,17 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
         <v>21</v>
       </c>
-      <c r="D8" t="s">
-        <v>35</v>
-      </c>
+      <c r="D8"/>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G8">
         <v>0.5</v>
@@ -3093,19 +3031,17 @@
     </row>
     <row r="9" spans="2:8">
       <c r="B9" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>39</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D9"/>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G9">
         <v>0.7</v>
@@ -3116,19 +3052,17 @@
     </row>
     <row r="10" spans="2:8">
       <c r="B10" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" t="s">
-        <v>42</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D10"/>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F10" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G10">
         <v>0.7</v>
@@ -3139,19 +3073,17 @@
     </row>
     <row r="11" spans="2:8">
       <c r="B11" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11"/>
+      <c r="E11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" t="s">
         <v>38</v>
-      </c>
-      <c r="D11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" t="s">
-        <v>46</v>
       </c>
       <c r="G11">
         <v>0.7</v>
@@ -3162,19 +3094,17 @@
     </row>
     <row r="12" spans="2:8">
       <c r="B12" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" t="s">
-        <v>48</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D12"/>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F12" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G12">
         <v>0.7</v>
@@ -3185,19 +3115,17 @@
     </row>
     <row r="13" spans="2:8">
       <c r="B13" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" t="s">
-        <v>51</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D13"/>
       <c r="E13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F13" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="G13">
         <v>0.7</v>
@@ -3208,16 +3136,14 @@
     </row>
     <row r="14" spans="2:8">
       <c r="B14" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" t="s">
-        <v>55</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="D14"/>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G14">
         <v>0.5</v>
@@ -3228,16 +3154,14 @@
     </row>
     <row r="15" spans="2:8">
       <c r="B15" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" t="s">
-        <v>59</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="D15"/>
       <c r="E15" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -3248,16 +3172,14 @@
     </row>
     <row r="16" spans="2:8">
       <c r="B16" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" t="s">
-        <v>63</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D16"/>
       <c r="E16" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3268,16 +3190,14 @@
     </row>
     <row r="17" spans="2:8">
       <c r="B17" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" t="s">
-        <v>67</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="D17"/>
       <c r="E17" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3288,19 +3208,17 @@
     </row>
     <row r="18" spans="2:8">
       <c r="B18" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" t="s">
-        <v>71</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="D18"/>
       <c r="E18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F18" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -3341,13 +3259,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3355,19 +3273,19 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:6">
@@ -3384,18 +3302,18 @@
         <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="2:12">
       <c r="B4" s="1" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="E4" s="3" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,I4:L4)</f>
@@ -3424,10 +3342,10 @@
     </row>
     <row r="5" spans="2:12">
       <c r="B5" s="1" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="E5" s="3" t="str">
         <f t="shared" ref="E5:E12" si="0">_xlfn.TEXTJOIN(",",TRUE,I5:L5)</f>
@@ -3456,10 +3374,10 @@
     </row>
     <row r="6" spans="2:12">
       <c r="B6" s="1" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="E6" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3488,20 +3406,20 @@
     </row>
     <row r="7" spans="2:12">
       <c r="B7" s="1" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="E7" s="3" t="str">
         <f t="shared" si="0"/>
         <v>100,100,100,100</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="G7" s="1" t="str">
         <f t="shared" si="1"/>
@@ -3522,20 +3440,20 @@
     </row>
     <row r="8" spans="2:12">
       <c r="B8" s="1" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E8" s="3" t="str">
         <f t="shared" si="0"/>
         <v>50,50,50,50</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="G8" s="1" t="str">
         <f t="shared" si="1"/>
@@ -3556,10 +3474,10 @@
     </row>
     <row r="9" spans="2:12">
       <c r="B9" s="1" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E9" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3588,10 +3506,10 @@
     </row>
     <row r="10" spans="2:12">
       <c r="B10" s="1" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E10" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3620,10 +3538,10 @@
     </row>
     <row r="11" spans="2:12">
       <c r="B11" s="1" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="E11" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3652,20 +3570,20 @@
     </row>
     <row r="12" spans="2:12">
       <c r="B12" s="1" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="E12" s="3" t="str">
         <f t="shared" si="0"/>
         <v>0,0,0,0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="G12" s="1" t="str">
         <f t="shared" si="1"/>
@@ -3723,10 +3641,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3734,16 +3652,16 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3760,1512 +3678,1512 @@
         <v>19</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="B4" s="1" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="D4" s="1">
         <v>100</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:18">
       <c r="B5" s="1" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="D5" s="1">
         <v>100</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="2:18">
       <c r="B6" s="1" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="D6" s="1">
         <v>100</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="2:18">
       <c r="B7" s="1" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="D7" s="1">
         <v>100</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="B8" s="1" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="1" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="1" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="B11" s="1" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D11" s="1">
         <v>100</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="B12" s="1" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="D12" s="1">
         <v>100</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="1" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="D13" s="1">
         <v>100</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="1" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="D14" s="1">
         <v>100</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="1" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D15" s="1">
         <v>100</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="1" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="D16" s="1">
         <v>100</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="2:13">
       <c r="B17" s="1" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="D17" s="1">
         <v>100</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="1" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="D18" s="1">
         <v>100</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="D19" s="1">
         <v>100</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="1" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="D20" s="1">
         <v>100</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="2:20">
       <c r="B21" s="1" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D21" s="1">
         <v>100</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>20</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="2:20">
       <c r="B22" s="1" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="D22" s="1">
         <v>100</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>20</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="2:20">
       <c r="B23" s="1" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="D23" s="1">
         <v>100</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="R23" s="1" t="s">
         <v>20</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="2:20">
       <c r="B24" s="1" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="D24" s="1">
         <v>100</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="R24" s="1" t="s">
         <v>20</v>
       </c>
       <c r="S24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T24" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="25" spans="2:20">
       <c r="B25" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="D25" s="1">
         <v>100</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>20</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="2:20">
       <c r="B26" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="D26" s="1">
         <v>100</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="2:20">
       <c r="B27" s="1" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="D27" s="1">
         <v>100</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T27" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="T27" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="28" spans="2:20">
       <c r="B28" s="1" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="D28" s="1">
         <v>100</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="2:20">
       <c r="B29" s="1" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="D29" s="1">
         <v>100</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="2:20">
       <c r="B30" s="1" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="D30" s="1">
         <v>100</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="R30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="S30" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="T30" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="2:19">
       <c r="B31" s="1" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="D31" s="1">
         <v>100</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="R31" s="1" t="s">
         <v>20</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="2:19">
       <c r="B32" s="1" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="D32" s="1">
         <v>100</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>20</v>
       </c>
       <c r="S32" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="2:19">
       <c r="B33" s="1" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="D33" s="1">
         <v>100</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="R33" s="1" t="s">
         <v>20</v>
       </c>
       <c r="S33" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="2:19">
       <c r="B34" s="1" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="D34" s="1">
         <v>100</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="R34" s="1" t="s">
         <v>20</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="2:19">
       <c r="B35" s="1" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="D35" s="1">
         <v>100</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="2:19">
       <c r="B36" s="1" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D36" s="1">
         <v>100</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S36" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="2:19">
       <c r="B37" s="1" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="D37" s="1">
         <v>100</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>20</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="2:19">
       <c r="B38" s="1" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="D38" s="1">
         <v>100</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S38" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="S38" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="39" spans="2:19">
       <c r="B39" s="1" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="D39" s="1">
         <v>100</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="S39" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="2:19">
       <c r="B40" s="1" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="D40" s="1">
         <v>100</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="S40" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="2:12">
       <c r="B41" s="1" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="D41" s="1">
         <v>100</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="2:5">
       <c r="B42" s="1" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="D42" s="1">
         <v>100</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
     </row>
     <row r="43" spans="2:12">
       <c r="B43" s="1" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="D43" s="1">
         <v>100</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="2:12">
       <c r="B44" s="1" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="D44" s="1">
         <v>100</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="2:12">
       <c r="B45" s="1" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="D45" s="1">
         <v>100</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="2:12">
       <c r="B46" s="1" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="D46" s="1">
         <v>100</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" spans="2:12">
       <c r="B47" s="1" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="D47" s="1">
         <v>100</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="2:12">
       <c r="B48" s="1" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="D48" s="1">
         <v>100</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" spans="2:12">
       <c r="B49" s="1" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="D49" s="1">
         <v>100</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50" spans="2:5">
       <c r="B50" s="1" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="D50" s="1">
         <v>100</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
     </row>
     <row r="51" spans="2:5">
       <c r="B51" s="1" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="D51" s="1">
         <v>100</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
     </row>
     <row r="52" spans="2:5">
       <c r="B52" s="1" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="D52" s="1">
         <v>100</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
     </row>
     <row r="53" spans="2:5">
       <c r="B53" s="1" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="D53" s="1">
         <v>100</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="54" spans="2:5">
       <c r="B54" s="1" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="D54" s="1">
         <v>100</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
     </row>
     <row r="55" spans="2:5">
       <c r="B55" s="1" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="D55" s="1">
         <v>100</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
     </row>
     <row r="56" spans="2:5">
       <c r="B56" s="1" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="D56" s="1">
         <v>100</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
     </row>
     <row r="57" spans="2:5">
       <c r="B57" s="1" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="D57" s="1">
         <v>100</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
     </row>
     <row r="58" spans="2:5">
       <c r="B58" s="1" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="D58" s="1">
         <v>100</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
     </row>
     <row r="59" spans="2:5">
       <c r="B59" s="1" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="D59" s="1">
         <v>100</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
     </row>
     <row r="60" spans="2:5">
       <c r="B60" s="1" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="D60" s="1">
         <v>100</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
     </row>
     <row r="61" spans="2:5">
       <c r="B61" s="1" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="D61" s="1">
         <v>100</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
     </row>
     <row r="62" spans="2:5">
       <c r="B62" s="1" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="D62" s="1">
         <v>100</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
     </row>
     <row r="63" spans="2:5">
       <c r="B63" s="1" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="D63" s="1">
         <v>100</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
     </row>
     <row r="64" spans="2:5">
       <c r="B64" s="1" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="D64" s="1">
         <v>100</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
     </row>
     <row r="65" spans="2:5">
       <c r="B65" s="1" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="D65" s="1">
         <v>100</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
     </row>
     <row r="66" spans="2:5">
       <c r="B66" s="1" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="D66" s="1">
         <v>100</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
     </row>
     <row r="67" spans="2:5">
       <c r="B67" s="1" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="D67" s="1">
         <v>100</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
     </row>
     <row r="68" spans="2:5">
       <c r="B68" s="1" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="D68" s="1">
         <v>100</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
     </row>
     <row r="69" spans="2:5">
       <c r="B69" s="1" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="D69" s="1">
         <v>100</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
     </row>
     <row r="70" spans="2:5">
       <c r="B70" s="1" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="D70" s="1">
         <v>100</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
     </row>
     <row r="71" spans="2:5">
       <c r="B71" s="1" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="D71" s="1">
         <v>100</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
     </row>
     <row r="72" spans="2:5">
       <c r="B72" s="1" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="D72" s="1">
         <v>100</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
     </row>
     <row r="73" spans="2:5">
       <c r="B73" s="1" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="D73" s="1">
         <v>100</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
     </row>
     <row r="74" spans="2:5">
       <c r="B74" s="1" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="D74" s="1">
         <v>100</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
     </row>
     <row r="75" spans="2:5">
       <c r="B75" s="1" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="D75" s="1">
         <v>100</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
     </row>
     <row r="76" spans="2:5">
       <c r="B76" s="1" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="D76" s="1">
         <v>100</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
     </row>
     <row r="77" spans="2:5">
       <c r="B77" s="1" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="D77" s="1">
         <v>100</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
     </row>
     <row r="78" spans="2:20">
       <c r="B78" s="1" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="D78" s="1">
         <v>100</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="R78" s="1" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="S78" s="1">
         <v>80</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79" spans="2:20">
       <c r="B79" s="1" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="D79" s="1">
         <v>100</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="T79" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="80" spans="2:20">
       <c r="B80" s="1" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="D80" s="1">
         <v>100</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="T80" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="81" spans="2:20">
       <c r="B81" s="1" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="D81" s="1">
         <v>100</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="Q81" s="1" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="R81" s="1" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="S81" s="1">
         <v>100</v>
       </c>
       <c r="T81" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="82" spans="2:20">
       <c r="B82" s="1" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="D82" s="1">
         <v>100</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="T82" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="83" spans="2:20">
       <c r="B83" s="1" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="D83" s="1">
         <v>100</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="T83" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="84" spans="2:20">
       <c r="B84" s="1" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="D84" s="1">
         <v>100</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="Q84" s="1" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="R84" s="1" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="S84" s="1">
         <v>80</v>
       </c>
       <c r="T84" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="85" spans="2:20">
       <c r="B85" s="1" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="D85" s="1">
         <v>100</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="T85" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="86" spans="2:20">
       <c r="B86" s="1" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="D86" s="1">
         <v>100</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="87" spans="2:20">
       <c r="B87" s="1" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="D87" s="1">
         <v>100</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="Q87" s="1" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="R87" s="1" t="s">
-        <v>54</v>
+        <v>361</v>
       </c>
       <c r="S87" s="1">
         <v>100</v>
       </c>
       <c r="T87" s="1" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="88" spans="2:20">
       <c r="B88" s="1" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="D88" s="1">
         <v>100</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="T88" s="1" t="s">
         <v>20</v>
@@ -5273,1128 +5191,1128 @@
     </row>
     <row r="89" spans="2:20">
       <c r="B89" s="1" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="D89" s="1">
         <v>100</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="T89" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="90" spans="2:20">
       <c r="B90" s="1" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="D90" s="1">
         <v>100</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="Q90" s="1" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>58</v>
+        <v>372</v>
       </c>
       <c r="S90" s="1">
         <v>100</v>
       </c>
       <c r="T90" s="1" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="91" spans="2:20">
       <c r="B91" s="1" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="D91" s="1">
         <v>100</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="T91" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="92" spans="2:20">
       <c r="B92" s="1" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="D92" s="1">
         <v>100</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="Q92" s="1" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="R92" s="1" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="S92" s="1">
         <v>100</v>
       </c>
       <c r="T92" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="93" spans="2:5">
       <c r="B93" s="1" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="D93" s="1">
         <v>100</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
     </row>
     <row r="94" spans="2:5">
       <c r="B94" s="1" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="D94" s="1">
         <v>100</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
     </row>
     <row r="95" spans="2:5">
       <c r="B95" s="1" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="D95" s="1">
         <v>100</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
     </row>
     <row r="96" spans="2:5">
       <c r="B96" s="1" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="D96" s="1">
         <v>100</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
     </row>
     <row r="97" spans="2:5">
       <c r="B97" s="1" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
       <c r="D97" s="1">
         <v>100</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
     </row>
     <row r="98" spans="2:5">
       <c r="B98" s="1" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="D98" s="1">
         <v>100</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
     </row>
     <row r="99" spans="2:5">
       <c r="B99" s="1" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="D99" s="1">
         <v>100</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
     </row>
     <row r="100" spans="2:5">
       <c r="B100" s="1" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="D100" s="1">
         <v>100</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
     </row>
     <row r="101" spans="2:5">
       <c r="B101" s="1" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>418</v>
+        <v>405</v>
       </c>
       <c r="D101" s="1">
         <v>100</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>419</v>
+        <v>406</v>
       </c>
     </row>
     <row r="102" spans="2:5">
       <c r="B102" s="1" t="s">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="D102" s="1">
         <v>100</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
     </row>
     <row r="103" spans="2:5">
       <c r="B103" s="1" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="D103" s="1">
         <v>100</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
     </row>
     <row r="104" spans="2:5">
       <c r="B104" s="1" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="D104" s="1">
         <v>100</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
     </row>
     <row r="105" spans="2:5">
       <c r="B105" s="1" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="D105" s="1">
         <v>100</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
     </row>
     <row r="106" spans="2:5">
       <c r="B106" s="1" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="D106" s="1">
         <v>100</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
     </row>
     <row r="107" spans="2:5">
       <c r="B107" s="1" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="D107" s="1">
         <v>100</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
     </row>
     <row r="108" spans="2:5">
       <c r="B108" s="1" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="D108" s="1">
         <v>100</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
     </row>
     <row r="109" spans="2:5">
       <c r="B109" s="1" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="D109" s="1">
         <v>100</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
     </row>
     <row r="110" spans="2:5">
       <c r="B110" s="1" t="s">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="D110" s="1">
         <v>100</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
     </row>
     <row r="111" spans="2:5">
       <c r="B111" s="1" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="D111" s="1">
         <v>100</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
     </row>
     <row r="112" spans="2:5">
       <c r="B112" s="1" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="D112" s="1">
         <v>100</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
     </row>
     <row r="113" spans="2:5">
       <c r="B113" s="1" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="D113" s="1">
         <v>100</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
     </row>
     <row r="114" spans="2:5">
       <c r="B114" s="1" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="D114" s="1">
         <v>100</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
     </row>
     <row r="115" spans="2:5">
       <c r="B115" s="1" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="D115" s="1">
         <v>100</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
     </row>
     <row r="116" spans="2:5">
       <c r="B116" s="1" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="D116" s="1">
         <v>100</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
     </row>
     <row r="117" spans="2:5">
       <c r="B117" s="1" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="D117" s="1">
         <v>100</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
     </row>
     <row r="118" spans="2:5">
       <c r="B118" s="1" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="D118" s="1">
         <v>100</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
     </row>
     <row r="119" spans="2:5">
       <c r="B119" s="1" t="s">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="D119" s="1">
         <v>100</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
     </row>
     <row r="120" spans="2:5">
       <c r="B120" s="1" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="D120" s="1">
         <v>100</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
     </row>
     <row r="121" spans="2:5">
       <c r="B121" s="1" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="D121" s="1">
         <v>100</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
     </row>
     <row r="122" spans="2:5">
       <c r="B122" s="1" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="D122" s="1">
         <v>100</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>482</v>
+        <v>469</v>
       </c>
     </row>
     <row r="123" spans="2:5">
       <c r="B123" s="1" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="D123" s="1">
         <v>100</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>485</v>
+        <v>472</v>
       </c>
     </row>
     <row r="124" spans="2:5">
       <c r="B124" s="1" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="D124" s="1">
         <v>100</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="125" spans="2:5">
       <c r="B125" s="1" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="D125" s="1">
         <v>100</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="126" spans="2:5">
       <c r="B126" s="1" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="D126" s="1">
         <v>100</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
     </row>
     <row r="127" spans="2:5">
       <c r="B127" s="1" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="D127" s="1">
         <v>100</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
     </row>
     <row r="128" spans="2:5">
       <c r="B128" s="1" t="s">
-        <v>494</v>
+        <v>481</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
       <c r="D128" s="1">
         <v>100</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
     </row>
     <row r="129" spans="2:5">
       <c r="B129" s="1" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="D129" s="1">
         <v>100</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
     </row>
     <row r="130" spans="2:5">
       <c r="B130" s="1" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="D130" s="1">
         <v>100</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
     </row>
     <row r="131" spans="2:5">
       <c r="B131" s="1" t="s">
-        <v>503</v>
+        <v>490</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
       <c r="D131" s="1">
         <v>100</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
     </row>
     <row r="132" spans="2:5">
       <c r="B132" s="1" t="s">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="D132" s="1">
         <v>100</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>508</v>
+        <v>495</v>
       </c>
     </row>
     <row r="133" spans="2:5">
       <c r="B133" s="1" t="s">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>510</v>
+        <v>497</v>
       </c>
       <c r="D133" s="1">
         <v>100</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>511</v>
+        <v>498</v>
       </c>
     </row>
     <row r="134" spans="2:5">
       <c r="B134" s="1" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="D134" s="1">
         <v>100</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
     </row>
     <row r="135" spans="2:5">
       <c r="B135" s="1" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="D135" s="1">
         <v>100</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
     </row>
     <row r="136" spans="2:5">
       <c r="B136" s="1" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
       <c r="D136" s="1">
         <v>100</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
     </row>
     <row r="137" spans="2:5">
       <c r="B137" s="1" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="D137" s="1">
         <v>100</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
     </row>
     <row r="138" spans="2:5">
       <c r="B138" s="1" t="s">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="D138" s="1">
         <v>100</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
     </row>
     <row r="139" spans="2:5">
       <c r="B139" s="1" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>528</v>
+        <v>515</v>
       </c>
       <c r="D139" s="1">
         <v>100</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
     </row>
     <row r="140" spans="2:5">
       <c r="B140" s="1" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>530</v>
+        <v>517</v>
       </c>
       <c r="D140" s="1">
         <v>100</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>531</v>
+        <v>518</v>
       </c>
     </row>
     <row r="141" spans="2:5">
       <c r="B141" s="1" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="D141" s="1">
         <v>100</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>533</v>
+        <v>520</v>
       </c>
     </row>
     <row r="142" spans="2:5">
       <c r="B142" s="1" t="s">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="D142" s="1">
         <v>100</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
     </row>
     <row r="143" spans="2:5">
       <c r="B143" s="1" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
       <c r="D143" s="1">
         <v>100</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
     </row>
     <row r="144" spans="2:5">
       <c r="B144" s="1" t="s">
-        <v>540</v>
+        <v>527</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>541</v>
+        <v>528</v>
       </c>
       <c r="D144" s="1">
         <v>100</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
     </row>
     <row r="145" spans="2:5">
       <c r="B145" s="1" t="s">
-        <v>543</v>
+        <v>530</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="D145" s="1">
         <v>100</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
     </row>
     <row r="146" spans="2:5">
       <c r="B146" s="1" t="s">
-        <v>546</v>
+        <v>533</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>547</v>
+        <v>534</v>
       </c>
       <c r="D146" s="1">
         <v>100</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>548</v>
+        <v>535</v>
       </c>
     </row>
     <row r="147" spans="2:5">
       <c r="B147" s="1" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="D147" s="1">
         <v>100</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>551</v>
+        <v>538</v>
       </c>
     </row>
     <row r="148" spans="2:5">
       <c r="B148" s="1" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>553</v>
+        <v>540</v>
       </c>
       <c r="D148" s="1">
         <v>100</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>554</v>
+        <v>541</v>
       </c>
     </row>
     <row r="149" spans="2:5">
       <c r="B149" s="1" t="s">
-        <v>555</v>
+        <v>542</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>556</v>
+        <v>543</v>
       </c>
       <c r="D149" s="1">
         <v>100</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>557</v>
+        <v>544</v>
       </c>
     </row>
     <row r="150" spans="2:5">
       <c r="B150" s="1" t="s">
-        <v>558</v>
+        <v>545</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>559</v>
+        <v>546</v>
       </c>
       <c r="D150" s="1">
         <v>100</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>560</v>
+        <v>547</v>
       </c>
     </row>
     <row r="151" spans="2:5">
       <c r="B151" s="1" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>561</v>
+        <v>548</v>
       </c>
       <c r="D151" s="1">
         <v>100</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>562</v>
+        <v>549</v>
       </c>
     </row>
     <row r="152" spans="2:5">
       <c r="B152" s="1" t="s">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="D152" s="1">
         <v>100</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
     </row>
     <row r="153" spans="2:5">
       <c r="B153" s="1" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>567</v>
+        <v>554</v>
       </c>
       <c r="D153" s="1">
         <v>100</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>568</v>
+        <v>555</v>
       </c>
     </row>
     <row r="154" spans="2:5">
       <c r="B154" s="1" t="s">
-        <v>569</v>
+        <v>556</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>570</v>
+        <v>557</v>
       </c>
       <c r="D154" s="1">
         <v>100</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
     </row>
     <row r="155" spans="2:5">
       <c r="B155" s="1" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="D155" s="1">
         <v>100</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>574</v>
+        <v>561</v>
       </c>
     </row>
     <row r="156" spans="2:5">
       <c r="B156" s="1" t="s">
-        <v>575</v>
+        <v>562</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="D156" s="1">
         <v>100</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
     </row>
     <row r="157" spans="2:5">
       <c r="B157" s="1" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>579</v>
+        <v>566</v>
       </c>
       <c r="D157" s="1">
         <v>100</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>580</v>
+        <v>567</v>
       </c>
     </row>
     <row r="158" spans="2:5">
       <c r="B158" s="1" t="s">
-        <v>581</v>
+        <v>568</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>582</v>
+        <v>569</v>
       </c>
       <c r="D158" s="1">
         <v>100</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>583</v>
+        <v>570</v>
       </c>
     </row>
     <row r="159" spans="2:5">
       <c r="B159" s="1" t="s">
-        <v>584</v>
+        <v>571</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>585</v>
+        <v>572</v>
       </c>
       <c r="D159" s="1">
         <v>100</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
     </row>
     <row r="160" spans="2:5">
       <c r="B160" s="1" t="s">
-        <v>587</v>
+        <v>574</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>588</v>
+        <v>575</v>
       </c>
       <c r="D160" s="1">
         <v>100</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>589</v>
+        <v>576</v>
       </c>
     </row>
     <row r="161" spans="2:5">
       <c r="B161" s="1" t="s">
-        <v>590</v>
+        <v>577</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>591</v>
+        <v>578</v>
       </c>
       <c r="D161" s="1">
         <v>100</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>592</v>
+        <v>579</v>
       </c>
     </row>
     <row r="162" spans="2:5">
       <c r="B162" s="1" t="s">
-        <v>593</v>
+        <v>580</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>594</v>
+        <v>581</v>
       </c>
       <c r="D162" s="1">
         <v>100</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>595</v>
+        <v>582</v>
       </c>
     </row>
     <row r="163" spans="2:5">
       <c r="B163" s="1" t="s">
-        <v>596</v>
+        <v>583</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>597</v>
+        <v>584</v>
       </c>
       <c r="D163" s="1">
         <v>100</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
     </row>
     <row r="164" spans="2:5">
       <c r="B164" s="1" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>600</v>
+        <v>587</v>
       </c>
       <c r="D164" s="1">
         <v>100</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
     </row>
     <row r="165" spans="2:5">
       <c r="B165" s="1" t="s">
-        <v>602</v>
+        <v>589</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>603</v>
+        <v>590</v>
       </c>
       <c r="D165" s="1">
         <v>100</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>604</v>
+        <v>591</v>
       </c>
     </row>
     <row r="166" spans="2:5">
       <c r="B166" s="1" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="D166" s="1">
         <v>100</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:B166" etc:filterBottomFollowUsedRange="0">
+  <autoFilter ref="B1:B166">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6425,25 +6343,25 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>605</v>
+        <v>592</v>
       </c>
       <c r="D1" t="s">
-        <v>606</v>
+        <v>593</v>
       </c>
       <c r="E1" t="s">
-        <v>607</v>
+        <v>594</v>
       </c>
       <c r="F1" t="s">
-        <v>608</v>
+        <v>595</v>
       </c>
       <c r="G1" t="s">
-        <v>609</v>
+        <v>596</v>
       </c>
       <c r="H1" t="s">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="I1" t="s">
-        <v>611</v>
+        <v>598</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6451,28 +6369,28 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>612</v>
+        <v>599</v>
       </c>
       <c r="C2" t="s">
-        <v>613</v>
+        <v>600</v>
       </c>
       <c r="D2" t="s">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="E2" t="s">
-        <v>615</v>
+        <v>602</v>
       </c>
       <c r="F2" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="G2" t="s">
-        <v>617</v>
+        <v>604</v>
       </c>
       <c r="H2" t="s">
-        <v>618</v>
+        <v>605</v>
       </c>
       <c r="I2" t="s">
-        <v>619</v>
+        <v>606</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -6483,33 +6401,33 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>620</v>
+        <v>607</v>
       </c>
       <c r="D3" t="s">
-        <v>620</v>
+        <v>607</v>
       </c>
       <c r="E3" t="s">
-        <v>620</v>
+        <v>607</v>
       </c>
       <c r="F3" t="s">
-        <v>620</v>
+        <v>607</v>
       </c>
       <c r="G3" t="s">
-        <v>620</v>
+        <v>607</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>621</v>
+        <v>608</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="B4" t="s">
-        <v>623</v>
+        <v>610</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -6527,18 +6445,18 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="I4" t="s">
-        <v>624</v>
+        <v>611</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="B5" t="s">
-        <v>625</v>
+        <v>612</v>
       </c>
       <c r="C5">
         <v>95</v>
@@ -6556,18 +6474,18 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="I5" t="s">
-        <v>624</v>
+        <v>611</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C6">
         <v>80</v>
@@ -6585,18 +6503,18 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="I6" t="s">
-        <v>624</v>
+        <v>611</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="C7">
         <v>1000</v>
@@ -6614,192 +6532,192 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="I7" t="s">
-        <v>624</v>
+        <v>611</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="B8" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="C8" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="D8" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="E8" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="F8" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="G8" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="H8" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="B9" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="C9" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="D9" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="E9" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="F9" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="G9" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="H9" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="B10" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="C10" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="D10" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="E10" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="F10" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="G10" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="H10" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="B11" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="C11" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="D11" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="E11" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="F11" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="G11" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="H11" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="B12" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="C12" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="D12" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="E12" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="F12" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="G12" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="H12" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="B13" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="C13" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="D13" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="E13" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="F13" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="G13" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="H13" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="B14" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="C14" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="D14" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="E14" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="F14" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="G14" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="H14" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -190,7 +190,7 @@
     <t>act_boss</t>
   </si>
   <si>
-    <t>美食家评鉴</t>
+    <t>星级评鉴</t>
   </si>
   <si>
     <t>food_boss</t>
@@ -2931,7 +2931,6 @@
       <c r="C4" t="s">
         <v>21</v>
       </c>
-      <c r="D4"/>
       <c r="E4" t="s">
         <v>22</v>
       </c>
@@ -2952,7 +2951,6 @@
       <c r="C5" t="s">
         <v>21</v>
       </c>
-      <c r="D5"/>
       <c r="E5" t="s">
         <v>22</v>
       </c>
@@ -2973,7 +2971,6 @@
       <c r="C6" t="s">
         <v>21</v>
       </c>
-      <c r="D6"/>
       <c r="E6" t="s">
         <v>22</v>
       </c>
@@ -2994,7 +2991,6 @@
       <c r="C7" t="s">
         <v>21</v>
       </c>
-      <c r="D7"/>
       <c r="E7" t="s">
         <v>22</v>
       </c>
@@ -3015,7 +3011,6 @@
       <c r="C8" t="s">
         <v>21</v>
       </c>
-      <c r="D8"/>
       <c r="E8" t="s">
         <v>22</v>
       </c>
@@ -3036,7 +3031,6 @@
       <c r="C9" t="s">
         <v>33</v>
       </c>
-      <c r="D9"/>
       <c r="E9" t="s">
         <v>22</v>
       </c>
@@ -3057,7 +3051,6 @@
       <c r="C10" t="s">
         <v>33</v>
       </c>
-      <c r="D10"/>
       <c r="E10" t="s">
         <v>22</v>
       </c>
@@ -3078,7 +3071,6 @@
       <c r="C11" t="s">
         <v>33</v>
       </c>
-      <c r="D11"/>
       <c r="E11" t="s">
         <v>22</v>
       </c>
@@ -3099,7 +3091,6 @@
       <c r="C12" t="s">
         <v>33</v>
       </c>
-      <c r="D12"/>
       <c r="E12" t="s">
         <v>22</v>
       </c>
@@ -3120,7 +3111,6 @@
       <c r="C13" t="s">
         <v>33</v>
       </c>
-      <c r="D13"/>
       <c r="E13" t="s">
         <v>22</v>
       </c>
@@ -3141,7 +3131,6 @@
       <c r="C14" t="s">
         <v>44</v>
       </c>
-      <c r="D14"/>
       <c r="E14" t="s">
         <v>45</v>
       </c>
@@ -3159,7 +3148,6 @@
       <c r="C15" t="s">
         <v>47</v>
       </c>
-      <c r="D15"/>
       <c r="E15" t="s">
         <v>48</v>
       </c>
@@ -3177,7 +3165,6 @@
       <c r="C16" t="s">
         <v>50</v>
       </c>
-      <c r="D16"/>
       <c r="E16" t="s">
         <v>51</v>
       </c>
@@ -3195,7 +3182,6 @@
       <c r="C17" t="s">
         <v>53</v>
       </c>
-      <c r="D17"/>
       <c r="E17" t="s">
         <v>54</v>
       </c>
@@ -3213,7 +3199,6 @@
       <c r="C18" t="s">
         <v>56</v>
       </c>
-      <c r="D18"/>
       <c r="E18" t="s">
         <v>22</v>
       </c>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15240"/>
+    <workbookView windowHeight="15280" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="action" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="613">
   <si>
     <t>##var</t>
   </si>
@@ -286,1579 +286,1579 @@
     <t>困难事件大组</t>
   </si>
   <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>actionIds</t>
+  </si>
+  <si>
+    <t>小组ID</t>
+  </si>
+  <si>
+    <t>小组名(调试用)</t>
+  </si>
+  <si>
+    <t>被大组选中的权重</t>
+  </si>
+  <si>
+    <t>小组内固定行动ID列表→action.id</t>
+  </si>
+  <si>
+    <t>sg_normal_1</t>
+  </si>
+  <si>
+    <t>普通1</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_fragment,act_food_passive</t>
+  </si>
+  <si>
+    <t>sg_normal_2</t>
+  </si>
+  <si>
+    <t>普通2</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_fragment,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalEvent_15</t>
+  </si>
+  <si>
+    <t>sg_normal_3</t>
+  </si>
+  <si>
+    <t>普通3</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_fragment,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHardEvent_1</t>
+  </si>
+  <si>
+    <t>sg_normal_4</t>
+  </si>
+  <si>
+    <t>普通4</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_hardEvent_1</t>
+  </si>
+  <si>
+    <t>sg_normal_5</t>
+  </si>
+  <si>
+    <t>普通5</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normal_6</t>
+  </si>
+  <si>
+    <t>普通6</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normal_7</t>
+  </si>
+  <si>
+    <t>普通7</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normal_8</t>
+  </si>
+  <si>
+    <t>普通8</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normal_9</t>
+  </si>
+  <si>
+    <t>普通9</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normal_10</t>
+  </si>
+  <si>
+    <t>普通10</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_food_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normal_11</t>
+  </si>
+  <si>
+    <t>普通11</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_fragment</t>
+  </si>
+  <si>
+    <t>sg_normal_12</t>
+  </si>
+  <si>
+    <t>普通12</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_passive</t>
+  </si>
+  <si>
+    <t>sg_normal_13</t>
+  </si>
+  <si>
+    <t>普通13</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normal_14</t>
+  </si>
+  <si>
+    <t>普通14</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normal_15</t>
+  </si>
+  <si>
+    <t>普通15</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_passive</t>
+  </si>
+  <si>
+    <t>sg_normal_16</t>
+  </si>
+  <si>
+    <t>普通16</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normal_17</t>
+  </si>
+  <si>
+    <t>普通17</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_dish</t>
+  </si>
+  <si>
+    <t>普通困难混合大组</t>
+  </si>
+  <si>
+    <t>sg_normal_18</t>
+  </si>
+  <si>
+    <t>普通18</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normal_19</t>
+  </si>
+  <si>
+    <t>普通19</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_food_dish</t>
+  </si>
+  <si>
     <t>lg_debug</t>
   </si>
   <si>
     <t>调试大组</t>
   </si>
   <si>
+    <t>sg_normal_20</t>
+  </si>
+  <si>
+    <t>普通20</t>
+  </si>
+  <si>
+    <t>act_food_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_1</t>
+  </si>
+  <si>
+    <t>普通困难1</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_fragment,act_food_passive</t>
+  </si>
+  <si>
+    <t>sg_normalHard_2</t>
+  </si>
+  <si>
+    <t>普通困难2</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_fragment,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_3</t>
+  </si>
+  <si>
+    <t>普通困难3</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_fragment,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_4</t>
+  </si>
+  <si>
+    <t>普通困难4</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_5</t>
+  </si>
+  <si>
+    <t>普通困难5</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_6</t>
+  </si>
+  <si>
+    <t>普通困难6</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_7</t>
+  </si>
+  <si>
+    <t>普通困难7</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_8</t>
+  </si>
+  <si>
+    <t>普通困难8</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_9</t>
+  </si>
+  <si>
+    <t>普通困难9</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_10</t>
+  </si>
+  <si>
+    <t>普通困难10</t>
+  </si>
+  <si>
+    <t>act_food_hard_passive,act_food_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_11</t>
+  </si>
+  <si>
+    <t>普通困难11</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_fragment</t>
+  </si>
+  <si>
+    <t>sg_normalHard_12</t>
+  </si>
+  <si>
+    <t>普通困难12</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_passive</t>
+  </si>
+  <si>
+    <t>sg_normalHard_13</t>
+  </si>
+  <si>
+    <t>普通困难13</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_14</t>
+  </si>
+  <si>
+    <t>普通困难14</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_15</t>
+  </si>
+  <si>
+    <t>普通困难15</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_passive</t>
+  </si>
+  <si>
+    <t>sg_normalHard_16</t>
+  </si>
+  <si>
+    <t>普通困难16</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_17</t>
+  </si>
+  <si>
+    <t>普通困难17</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_18</t>
+  </si>
+  <si>
+    <t>普通困难18</t>
+  </si>
+  <si>
+    <t>act_food_hard_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_19</t>
+  </si>
+  <si>
+    <t>普通困难19</t>
+  </si>
+  <si>
+    <t>act_food_hard_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_20</t>
+  </si>
+  <si>
+    <t>普通困难20</t>
+  </si>
+  <si>
+    <t>act_food_hard_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_21</t>
+  </si>
+  <si>
+    <t>普通困难21</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_fragment,act_food_passive</t>
+  </si>
+  <si>
+    <t>sg_normalHard_22</t>
+  </si>
+  <si>
+    <t>普通困难22</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_fragment,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_23</t>
+  </si>
+  <si>
+    <t>普通困难23</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_fragment,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_24</t>
+  </si>
+  <si>
+    <t>普通困难24</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_25</t>
+  </si>
+  <si>
+    <t>普通困难25</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_26</t>
+  </si>
+  <si>
+    <t>普通困难26</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_27</t>
+  </si>
+  <si>
+    <t>普通困难27</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_hard_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_28</t>
+  </si>
+  <si>
+    <t>普通困难28</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_hard_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_29</t>
+  </si>
+  <si>
+    <t>普通困难29</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_hard_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_30</t>
+  </si>
+  <si>
+    <t>普通困难30</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_food_hard_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_31</t>
+  </si>
+  <si>
+    <t>普通困难31</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_fragment</t>
+  </si>
+  <si>
+    <t>sg_normalHard_32</t>
+  </si>
+  <si>
+    <t>普通困难32</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_passive</t>
+  </si>
+  <si>
+    <t>sg_normalHard_33</t>
+  </si>
+  <si>
+    <t>普通困难33</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_34</t>
+  </si>
+  <si>
+    <t>普通困难34</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_35</t>
+  </si>
+  <si>
+    <t>普通困难35</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_hard_passive</t>
+  </si>
+  <si>
+    <t>sg_normalHard_36</t>
+  </si>
+  <si>
+    <t>普通困难36</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_37</t>
+  </si>
+  <si>
+    <t>普通困难37</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_38</t>
+  </si>
+  <si>
+    <t>普通困难38</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_39</t>
+  </si>
+  <si>
+    <t>普通困难39</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_40</t>
+  </si>
+  <si>
+    <t>普通困难40</t>
+  </si>
+  <si>
+    <t>act_food_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_41</t>
+  </si>
+  <si>
+    <t>普通困难41</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_fragment,act_food_hard_passive</t>
+  </si>
+  <si>
+    <t>sg_normalHard_42</t>
+  </si>
+  <si>
+    <t>普通困难42</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_fragment,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_43</t>
+  </si>
+  <si>
+    <t>普通困难43</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_fragment,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_44</t>
+  </si>
+  <si>
+    <t>普通困难44</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_passive,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_45</t>
+  </si>
+  <si>
+    <t>普通困难45</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_passive,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_46</t>
+  </si>
+  <si>
+    <t>普通困难46</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_47</t>
+  </si>
+  <si>
+    <t>普通困难47</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_passive,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_48</t>
+  </si>
+  <si>
+    <t>普通困难48</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_passive,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_49</t>
+  </si>
+  <si>
+    <t>普通困难49</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_50</t>
+  </si>
+  <si>
+    <t>普通困难50</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_food_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_51</t>
+  </si>
+  <si>
+    <t>普通困难51</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_fragment,act_food_passive</t>
+  </si>
+  <si>
+    <t>sg_normalHard_52</t>
+  </si>
+  <si>
+    <t>普通困难52</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_fragment,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_53</t>
+  </si>
+  <si>
+    <t>普通困难53</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_fragment,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_54</t>
+  </si>
+  <si>
+    <t>普通困难54</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_55</t>
+  </si>
+  <si>
+    <t>普通困难55</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_food_b</t>
+  </si>
+  <si>
+    <t>美食B</t>
+  </si>
+  <si>
+    <t>sg_normalHard_56</t>
+  </si>
+  <si>
+    <t>普通困难56</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_57</t>
+  </si>
+  <si>
+    <t>普通困难57</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_hard_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_58</t>
+  </si>
+  <si>
+    <t>普通困难58</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_hard_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_food_hard_a</t>
+  </si>
+  <si>
+    <t>硬菜A</t>
+  </si>
+  <si>
+    <t>sg_normalHard_59</t>
+  </si>
+  <si>
+    <t>普通困难59</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_hard_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_60</t>
+  </si>
+  <si>
+    <t>普通困难60</t>
+  </si>
+  <si>
+    <t>act_food_hard_passive,act_food_hard_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_61</t>
+  </si>
+  <si>
+    <t>普通困难61</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_fragment,act_food_hard_passive</t>
+  </si>
+  <si>
+    <t>sg_food_hard_b</t>
+  </si>
+  <si>
+    <t>硬菜B</t>
+  </si>
+  <si>
+    <t>sg_normalHard_62</t>
+  </si>
+  <si>
+    <t>普通困难62</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_fragment,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_63</t>
+  </si>
+  <si>
+    <t>普通困难63</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_fragment,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_64</t>
+  </si>
+  <si>
+    <t>普通困难64</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_passive,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_event</t>
+  </si>
+  <si>
+    <t>事件</t>
+  </si>
+  <si>
+    <t>sg_normalHard_65</t>
+  </si>
+  <si>
+    <t>普通困难65</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_passive,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_66</t>
+  </si>
+  <si>
+    <t>普通困难66</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_67</t>
+  </si>
+  <si>
+    <t>普通困难67</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_hard_passive,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_reward</t>
+  </si>
+  <si>
+    <t>奖励</t>
+  </si>
+  <si>
+    <t>sg_normalHard_68</t>
+  </si>
+  <si>
+    <t>普通困难68</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_hard_passive,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_69</t>
+  </si>
+  <si>
+    <t>普通困难69</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_hard_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_debug</t>
+  </si>
+  <si>
+    <t>调试商店</t>
+  </si>
+  <si>
+    <t>sg_normalHard_70</t>
+  </si>
+  <si>
+    <t>普通困难70</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_food_hard_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_71</t>
+  </si>
+  <si>
+    <t>普通困难71</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_fragment,act_food_hard_passive</t>
+  </si>
+  <si>
+    <t>sg_normalHard_72</t>
+  </si>
+  <si>
+    <t>普通困难72</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_fragment,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_73</t>
+  </si>
+  <si>
+    <t>普通困难73</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_fragment,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_74</t>
+  </si>
+  <si>
+    <t>普通困难74</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_passive,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_75</t>
+  </si>
+  <si>
+    <t>普通困难75</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_passive,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_76</t>
+  </si>
+  <si>
+    <t>普通困难76</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_77</t>
+  </si>
+  <si>
+    <t>普通困难77</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_passive,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_78</t>
+  </si>
+  <si>
+    <t>普通困难78</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_passive,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_79</t>
+  </si>
+  <si>
+    <t>普通困难79</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_80</t>
+  </si>
+  <si>
+    <t>普通困难80</t>
+  </si>
+  <si>
+    <t>act_food_hard_passive,act_food_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_hard_1</t>
+  </si>
+  <si>
+    <t>困难1</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_fragment,act_food_hard_passive</t>
+  </si>
+  <si>
+    <t>sg_hard_2</t>
+  </si>
+  <si>
+    <t>困难2</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_fragment,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_hard_3</t>
+  </si>
+  <si>
+    <t>困难3</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_fragment,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_hard_4</t>
+  </si>
+  <si>
+    <t>困难4</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_passive,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_hard_5</t>
+  </si>
+  <si>
+    <t>困难5</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_passive,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_hard_6</t>
+  </si>
+  <si>
+    <t>困难6</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_hard_7</t>
+  </si>
+  <si>
+    <t>困难7</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_hard_passive,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_hard_8</t>
+  </si>
+  <si>
+    <t>困难8</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_hard_passive,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_hard_9</t>
+  </si>
+  <si>
+    <t>困难9</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_hard_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_hard_10</t>
+  </si>
+  <si>
+    <t>困难10</t>
+  </si>
+  <si>
+    <t>act_food_hard_passive,act_food_hard_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_hard_11</t>
+  </si>
+  <si>
+    <t>困难11</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_fragment</t>
+  </si>
+  <si>
+    <t>sg_hard_12</t>
+  </si>
+  <si>
+    <t>困难12</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_passive</t>
+  </si>
+  <si>
+    <t>sg_hard_13</t>
+  </si>
+  <si>
+    <t>困难13</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_hard_14</t>
+  </si>
+  <si>
+    <t>困难14</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_hard_15</t>
+  </si>
+  <si>
+    <t>困难15</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_hard_passive</t>
+  </si>
+  <si>
+    <t>sg_hard_16</t>
+  </si>
+  <si>
+    <t>困难16</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_hard_17</t>
+  </si>
+  <si>
+    <t>困难17</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_hard_18</t>
+  </si>
+  <si>
+    <t>困难18</t>
+  </si>
+  <si>
+    <t>act_food_hard_passive,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_hard_19</t>
+  </si>
+  <si>
+    <t>困难19</t>
+  </si>
+  <si>
+    <t>act_food_hard_passive,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_hard_20</t>
+  </si>
+  <si>
+    <t>困难20</t>
+  </si>
+  <si>
+    <t>act_food_hard_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>事件1</t>
+  </si>
+  <si>
+    <t>奖励1</t>
+  </si>
+  <si>
+    <t>sg_normalEvent_1</t>
+  </si>
+  <si>
+    <t>普通事件1</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_fragment,act_event</t>
+  </si>
+  <si>
+    <t>sg_normalEvent_2</t>
+  </si>
+  <si>
+    <t>普通事件2</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_passive,act_event</t>
+  </si>
+  <si>
+    <t>sg_normalEvent_3</t>
+  </si>
+  <si>
+    <t>普通事件3</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_active,act_event</t>
+  </si>
+  <si>
+    <t>sg_normalEvent_4</t>
+  </si>
+  <si>
+    <t>普通事件4</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_dish,act_event</t>
+  </si>
+  <si>
+    <t>sg_normalEvent_5</t>
+  </si>
+  <si>
+    <t>普通事件5</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_passive,act_event</t>
+  </si>
+  <si>
+    <t>sg_normalEvent_6</t>
+  </si>
+  <si>
+    <t>普通事件6</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_active,act_event</t>
+  </si>
+  <si>
+    <t>sg_normalEvent_7</t>
+  </si>
+  <si>
+    <t>普通事件7</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_dish,act_event</t>
+  </si>
+  <si>
+    <t>sg_normalEvent_8</t>
+  </si>
+  <si>
+    <t>普通事件8</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_food_active,act_event</t>
+  </si>
+  <si>
+    <t>sg_normalEvent_9</t>
+  </si>
+  <si>
+    <t>普通事件9</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_food_dish,act_event</t>
+  </si>
+  <si>
+    <t>sg_normalEvent_10</t>
+  </si>
+  <si>
+    <t>普通事件10</t>
+  </si>
+  <si>
+    <t>act_food_active,act_food_dish,act_event</t>
+  </si>
+  <si>
+    <t>sg_normalEvent_11</t>
+  </si>
+  <si>
+    <t>普通事件11</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_event</t>
+  </si>
+  <si>
+    <t>sg_normalEvent_12</t>
+  </si>
+  <si>
+    <t>普通事件12</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_event</t>
+  </si>
+  <si>
+    <t>sg_normalEvent_13</t>
+  </si>
+  <si>
+    <t>普通事件13</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_event</t>
+  </si>
+  <si>
+    <t>sg_normalEvent_14</t>
+  </si>
+  <si>
+    <t>普通事件14</t>
+  </si>
+  <si>
+    <t>act_food_active,act_event</t>
+  </si>
+  <si>
+    <t>普通事件15</t>
+  </si>
+  <si>
+    <t>act_food_dish,act_event</t>
+  </si>
+  <si>
+    <t>普通困难事件1</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_fragment,act_event</t>
+  </si>
+  <si>
+    <t>sg_normalHardEvent_2</t>
+  </si>
+  <si>
+    <t>普通困难事件2</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_passive,act_event</t>
+  </si>
+  <si>
+    <t>sg_normalHardEvent_3</t>
+  </si>
+  <si>
+    <t>普通困难事件3</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_active,act_event</t>
+  </si>
+  <si>
+    <t>sg_normalHardEvent_4</t>
+  </si>
+  <si>
+    <t>普通困难事件4</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_dish,act_event</t>
+  </si>
+  <si>
+    <t>sg_normalHardEvent_5</t>
+  </si>
+  <si>
+    <t>普通困难事件5</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_passive,act_event</t>
+  </si>
+  <si>
+    <t>sg_normalHardEvent_6</t>
+  </si>
+  <si>
+    <t>普通困难事件6</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_active,act_event</t>
+  </si>
+  <si>
+    <t>sg_normalHardEvent_7</t>
+  </si>
+  <si>
+    <t>普通困难事件7</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_dish,act_event</t>
+  </si>
+  <si>
+    <t>sg_normalHardEvent_8</t>
+  </si>
+  <si>
+    <t>普通困难事件8</t>
+  </si>
+  <si>
+    <t>act_food_hard_passive,act_food_active,act_event</t>
+  </si>
+  <si>
+    <t>sg_normalHardEvent_9</t>
+  </si>
+  <si>
+    <t>普通困难事件9</t>
+  </si>
+  <si>
+    <t>act_food_hard_passive,act_food_dish,act_event</t>
+  </si>
+  <si>
+    <t>sg_normalHardEvent_10</t>
+  </si>
+  <si>
+    <t>普通困难事件10</t>
+  </si>
+  <si>
+    <t>act_food_hard_active,act_food_dish,act_event</t>
+  </si>
+  <si>
+    <t>困难事件1</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_fragment,act_event</t>
+  </si>
+  <si>
+    <t>sg_hardEvent_2</t>
+  </si>
+  <si>
+    <t>困难事件2</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_passive,act_event</t>
+  </si>
+  <si>
+    <t>sg_hardEvent_3</t>
+  </si>
+  <si>
+    <t>困难事件3</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_active,act_event</t>
+  </si>
+  <si>
+    <t>sg_hardEvent_4</t>
+  </si>
+  <si>
+    <t>困难事件4</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_dish,act_event</t>
+  </si>
+  <si>
+    <t>sg_hardEvent_5</t>
+  </si>
+  <si>
+    <t>困难事件5</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_hard_passive,act_event</t>
+  </si>
+  <si>
+    <t>sg_hardEvent_6</t>
+  </si>
+  <si>
+    <t>困难事件6</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_hard_active,act_event</t>
+  </si>
+  <si>
+    <t>sg_hardEvent_7</t>
+  </si>
+  <si>
+    <t>困难事件7</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_hard_dish,act_event</t>
+  </si>
+  <si>
+    <t>sg_hardEvent_8</t>
+  </si>
+  <si>
+    <t>困难事件8</t>
+  </si>
+  <si>
+    <t>act_food_hard_passive,act_food_hard_active,act_event</t>
+  </si>
+  <si>
+    <t>sg_hardEvent_9</t>
+  </si>
+  <si>
+    <t>困难事件9</t>
+  </si>
+  <si>
+    <t>act_food_hard_passive,act_food_hard_dish,act_event</t>
+  </si>
+  <si>
+    <t>sg_hardEvent_10</t>
+  </si>
+  <si>
+    <t>困难事件10</t>
+  </si>
+  <si>
+    <t>act_food_hard_active,act_food_hard_dish,act_event</t>
+  </si>
+  <si>
+    <t>sg_hardEvent_11</t>
+  </si>
+  <si>
+    <t>困难事件11</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_event</t>
+  </si>
+  <si>
+    <t>sg_hardEvent_12</t>
+  </si>
+  <si>
+    <t>困难事件12</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_event</t>
+  </si>
+  <si>
+    <t>sg_hardEvent_13</t>
+  </si>
+  <si>
+    <t>困难事件13</t>
+  </si>
+  <si>
+    <t>act_food_hard_passive,act_event</t>
+  </si>
+  <si>
+    <t>sg_hardEvent_14</t>
+  </si>
+  <si>
+    <t>困难事件14</t>
+  </si>
+  <si>
+    <t>act_food_hard_active,act_event</t>
+  </si>
+  <si>
+    <t>sg_hardEvent_15</t>
+  </si>
+  <si>
+    <t>困难事件15</t>
+  </si>
+  <si>
+    <t>act_food_hard_dish,act_event</t>
+  </si>
+  <si>
+    <t>priority</t>
+  </si>
+  <si>
+    <t>minRunStep</t>
+  </si>
+  <si>
+    <t>maxRunStep</t>
+  </si>
+  <si>
+    <t>minCount</t>
+  </si>
+  <si>
+    <t>maxCount</t>
+  </si>
+  <si>
+    <t>preconditions</t>
+  </si>
+  <si>
+    <t>activeWeeks</t>
+  </si>
+  <si>
+    <t>规则ID(大组用 ruleIds 引用它)</t>
+  </si>
+  <si>
+    <t>优先级,越大越先填充</t>
+  </si>
+  <si>
+    <t>整局行动序号窗口起点,1-based</t>
+  </si>
+  <si>
+    <t>窗口终点,含</t>
+  </si>
+  <si>
+    <t>窗口内至少出现次数</t>
+  </si>
+  <si>
+    <t>窗口内最多出现次数</t>
+  </si>
+  <si>
+    <t>规则前置条件</t>
+  </si>
+  <si>
+    <t>生效周列表；空=全部周</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>(list#sep=,),int</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>rule_reward_early</t>
+  </si>
+  <si>
+    <t>1,2,3,4,5,6,7,8</t>
+  </si>
+  <si>
+    <t>rule_reward_mid</t>
+  </si>
+  <si>
     <t>rule_debug_first</t>
-  </si>
-  <si>
-    <t>sg_debug</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>actionIds</t>
-  </si>
-  <si>
-    <t>小组ID</t>
-  </si>
-  <si>
-    <t>小组名(调试用)</t>
-  </si>
-  <si>
-    <t>被大组选中的权重</t>
-  </si>
-  <si>
-    <t>小组内固定行动ID列表→action.id</t>
-  </si>
-  <si>
-    <t>sg_normal_1</t>
-  </si>
-  <si>
-    <t>普通1</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_fragment,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normal_2</t>
-  </si>
-  <si>
-    <t>普通2</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_fragment,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalEvent_15</t>
-  </si>
-  <si>
-    <t>sg_normal_3</t>
-  </si>
-  <si>
-    <t>普通3</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_fragment,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHardEvent_1</t>
-  </si>
-  <si>
-    <t>sg_normal_4</t>
-  </si>
-  <si>
-    <t>普通4</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_hardEvent_1</t>
-  </si>
-  <si>
-    <t>sg_normal_5</t>
-  </si>
-  <si>
-    <t>普通5</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normal_6</t>
-  </si>
-  <si>
-    <t>普通6</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normal_7</t>
-  </si>
-  <si>
-    <t>普通7</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normal_8</t>
-  </si>
-  <si>
-    <t>普通8</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normal_9</t>
-  </si>
-  <si>
-    <t>普通9</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normal_10</t>
-  </si>
-  <si>
-    <t>普通10</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_food_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normal_11</t>
-  </si>
-  <si>
-    <t>普通11</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_fragment</t>
-  </si>
-  <si>
-    <t>sg_normal_12</t>
-  </si>
-  <si>
-    <t>普通12</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normal_13</t>
-  </si>
-  <si>
-    <t>普通13</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normal_14</t>
-  </si>
-  <si>
-    <t>普通14</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normal_15</t>
-  </si>
-  <si>
-    <t>普通15</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normal_16</t>
-  </si>
-  <si>
-    <t>普通16</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normal_17</t>
-  </si>
-  <si>
-    <t>普通17</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_dish</t>
-  </si>
-  <si>
-    <t>普通困难混合大组</t>
-  </si>
-  <si>
-    <t>sg_normal_18</t>
-  </si>
-  <si>
-    <t>普通18</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normal_19</t>
-  </si>
-  <si>
-    <t>普通19</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normal_20</t>
-  </si>
-  <si>
-    <t>普通20</t>
-  </si>
-  <si>
-    <t>act_food_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_1</t>
-  </si>
-  <si>
-    <t>普通困难1</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_fragment,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normalHard_2</t>
-  </si>
-  <si>
-    <t>普通困难2</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_fragment,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_3</t>
-  </si>
-  <si>
-    <t>普通困难3</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_fragment,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_4</t>
-  </si>
-  <si>
-    <t>普通困难4</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_5</t>
-  </si>
-  <si>
-    <t>普通困难5</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_6</t>
-  </si>
-  <si>
-    <t>普通困难6</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_7</t>
-  </si>
-  <si>
-    <t>普通困难7</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_8</t>
-  </si>
-  <si>
-    <t>普通困难8</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_9</t>
-  </si>
-  <si>
-    <t>普通困难9</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_10</t>
-  </si>
-  <si>
-    <t>普通困难10</t>
-  </si>
-  <si>
-    <t>act_food_hard_passive,act_food_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_11</t>
-  </si>
-  <si>
-    <t>普通困难11</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_fragment</t>
-  </si>
-  <si>
-    <t>sg_normalHard_12</t>
-  </si>
-  <si>
-    <t>普通困难12</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normalHard_13</t>
-  </si>
-  <si>
-    <t>普通困难13</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_14</t>
-  </si>
-  <si>
-    <t>普通困难14</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_15</t>
-  </si>
-  <si>
-    <t>普通困难15</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normalHard_16</t>
-  </si>
-  <si>
-    <t>普通困难16</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_17</t>
-  </si>
-  <si>
-    <t>普通困难17</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_18</t>
-  </si>
-  <si>
-    <t>普通困难18</t>
-  </si>
-  <si>
-    <t>act_food_hard_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_19</t>
-  </si>
-  <si>
-    <t>普通困难19</t>
-  </si>
-  <si>
-    <t>act_food_hard_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_20</t>
-  </si>
-  <si>
-    <t>普通困难20</t>
-  </si>
-  <si>
-    <t>act_food_hard_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_21</t>
-  </si>
-  <si>
-    <t>普通困难21</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_fragment,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normalHard_22</t>
-  </si>
-  <si>
-    <t>普通困难22</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_fragment,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_23</t>
-  </si>
-  <si>
-    <t>普通困难23</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_fragment,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_24</t>
-  </si>
-  <si>
-    <t>普通困难24</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_25</t>
-  </si>
-  <si>
-    <t>普通困难25</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_26</t>
-  </si>
-  <si>
-    <t>普通困难26</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_27</t>
-  </si>
-  <si>
-    <t>普通困难27</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_hard_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_28</t>
-  </si>
-  <si>
-    <t>普通困难28</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_hard_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_29</t>
-  </si>
-  <si>
-    <t>普通困难29</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_hard_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_30</t>
-  </si>
-  <si>
-    <t>普通困难30</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_food_hard_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_31</t>
-  </si>
-  <si>
-    <t>普通困难31</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_fragment</t>
-  </si>
-  <si>
-    <t>sg_normalHard_32</t>
-  </si>
-  <si>
-    <t>普通困难32</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_passive</t>
-  </si>
-  <si>
-    <t>sg_normalHard_33</t>
-  </si>
-  <si>
-    <t>普通困难33</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_34</t>
-  </si>
-  <si>
-    <t>普通困难34</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_35</t>
-  </si>
-  <si>
-    <t>普通困难35</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_hard_passive</t>
-  </si>
-  <si>
-    <t>sg_normalHard_36</t>
-  </si>
-  <si>
-    <t>普通困难36</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_37</t>
-  </si>
-  <si>
-    <t>普通困难37</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_38</t>
-  </si>
-  <si>
-    <t>普通困难38</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_39</t>
-  </si>
-  <si>
-    <t>普通困难39</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_40</t>
-  </si>
-  <si>
-    <t>普通困难40</t>
-  </si>
-  <si>
-    <t>act_food_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_41</t>
-  </si>
-  <si>
-    <t>普通困难41</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_fragment,act_food_hard_passive</t>
-  </si>
-  <si>
-    <t>sg_normalHard_42</t>
-  </si>
-  <si>
-    <t>普通困难42</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_fragment,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_43</t>
-  </si>
-  <si>
-    <t>普通困难43</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_fragment,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_44</t>
-  </si>
-  <si>
-    <t>普通困难44</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_passive,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_45</t>
-  </si>
-  <si>
-    <t>普通困难45</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_passive,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_46</t>
-  </si>
-  <si>
-    <t>普通困难46</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_47</t>
-  </si>
-  <si>
-    <t>普通困难47</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_passive,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_48</t>
-  </si>
-  <si>
-    <t>普通困难48</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_passive,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_49</t>
-  </si>
-  <si>
-    <t>普通困难49</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_50</t>
-  </si>
-  <si>
-    <t>普通困难50</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_food_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_51</t>
-  </si>
-  <si>
-    <t>普通困难51</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_fragment,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normalHard_52</t>
-  </si>
-  <si>
-    <t>普通困难52</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_fragment,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_53</t>
-  </si>
-  <si>
-    <t>普通困难53</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_fragment,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_54</t>
-  </si>
-  <si>
-    <t>普通困难54</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_55</t>
-  </si>
-  <si>
-    <t>普通困难55</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_food_b</t>
-  </si>
-  <si>
-    <t>美食B</t>
-  </si>
-  <si>
-    <t>sg_normalHard_56</t>
-  </si>
-  <si>
-    <t>普通困难56</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_57</t>
-  </si>
-  <si>
-    <t>普通困难57</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_hard_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_58</t>
-  </si>
-  <si>
-    <t>普通困难58</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_hard_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_food_hard_a</t>
-  </si>
-  <si>
-    <t>硬菜A</t>
-  </si>
-  <si>
-    <t>sg_normalHard_59</t>
-  </si>
-  <si>
-    <t>普通困难59</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_hard_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_60</t>
-  </si>
-  <si>
-    <t>普通困难60</t>
-  </si>
-  <si>
-    <t>act_food_hard_passive,act_food_hard_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_61</t>
-  </si>
-  <si>
-    <t>普通困难61</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_fragment,act_food_hard_passive</t>
-  </si>
-  <si>
-    <t>sg_food_hard_b</t>
-  </si>
-  <si>
-    <t>硬菜B</t>
-  </si>
-  <si>
-    <t>sg_normalHard_62</t>
-  </si>
-  <si>
-    <t>普通困难62</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_fragment,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_63</t>
-  </si>
-  <si>
-    <t>普通困难63</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_fragment,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_64</t>
-  </si>
-  <si>
-    <t>普通困难64</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_passive,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_event</t>
-  </si>
-  <si>
-    <t>事件</t>
-  </si>
-  <si>
-    <t>sg_normalHard_65</t>
-  </si>
-  <si>
-    <t>普通困难65</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_passive,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_66</t>
-  </si>
-  <si>
-    <t>普通困难66</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_67</t>
-  </si>
-  <si>
-    <t>普通困难67</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_hard_passive,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_reward</t>
-  </si>
-  <si>
-    <t>奖励</t>
-  </si>
-  <si>
-    <t>sg_normalHard_68</t>
-  </si>
-  <si>
-    <t>普通困难68</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_hard_passive,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_69</t>
-  </si>
-  <si>
-    <t>普通困难69</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_hard_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>调试商店</t>
-  </si>
-  <si>
-    <t>sg_normalHard_70</t>
-  </si>
-  <si>
-    <t>普通困难70</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_food_hard_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_71</t>
-  </si>
-  <si>
-    <t>普通困难71</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_fragment,act_food_hard_passive</t>
-  </si>
-  <si>
-    <t>sg_normalHard_72</t>
-  </si>
-  <si>
-    <t>普通困难72</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_fragment,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_73</t>
-  </si>
-  <si>
-    <t>普通困难73</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_fragment,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_74</t>
-  </si>
-  <si>
-    <t>普通困难74</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_passive,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_75</t>
-  </si>
-  <si>
-    <t>普通困难75</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_passive,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_76</t>
-  </si>
-  <si>
-    <t>普通困难76</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_77</t>
-  </si>
-  <si>
-    <t>普通困难77</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_passive,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_78</t>
-  </si>
-  <si>
-    <t>普通困难78</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_passive,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_79</t>
-  </si>
-  <si>
-    <t>普通困难79</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_80</t>
-  </si>
-  <si>
-    <t>普通困难80</t>
-  </si>
-  <si>
-    <t>act_food_hard_passive,act_food_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_hard_1</t>
-  </si>
-  <si>
-    <t>困难1</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_fragment,act_food_hard_passive</t>
-  </si>
-  <si>
-    <t>sg_hard_2</t>
-  </si>
-  <si>
-    <t>困难2</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_fragment,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_hard_3</t>
-  </si>
-  <si>
-    <t>困难3</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_fragment,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_hard_4</t>
-  </si>
-  <si>
-    <t>困难4</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_passive,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_hard_5</t>
-  </si>
-  <si>
-    <t>困难5</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_passive,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_hard_6</t>
-  </si>
-  <si>
-    <t>困难6</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_hard_7</t>
-  </si>
-  <si>
-    <t>困难7</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_hard_passive,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_hard_8</t>
-  </si>
-  <si>
-    <t>困难8</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_hard_passive,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_hard_9</t>
-  </si>
-  <si>
-    <t>困难9</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_hard_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_hard_10</t>
-  </si>
-  <si>
-    <t>困难10</t>
-  </si>
-  <si>
-    <t>act_food_hard_passive,act_food_hard_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_hard_11</t>
-  </si>
-  <si>
-    <t>困难11</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_fragment</t>
-  </si>
-  <si>
-    <t>sg_hard_12</t>
-  </si>
-  <si>
-    <t>困难12</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_passive</t>
-  </si>
-  <si>
-    <t>sg_hard_13</t>
-  </si>
-  <si>
-    <t>困难13</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_hard_14</t>
-  </si>
-  <si>
-    <t>困难14</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_hard_15</t>
-  </si>
-  <si>
-    <t>困难15</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_hard_passive</t>
-  </si>
-  <si>
-    <t>sg_hard_16</t>
-  </si>
-  <si>
-    <t>困难16</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_hard_17</t>
-  </si>
-  <si>
-    <t>困难17</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_hard_18</t>
-  </si>
-  <si>
-    <t>困难18</t>
-  </si>
-  <si>
-    <t>act_food_hard_passive,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_hard_19</t>
-  </si>
-  <si>
-    <t>困难19</t>
-  </si>
-  <si>
-    <t>act_food_hard_passive,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_hard_20</t>
-  </si>
-  <si>
-    <t>困难20</t>
-  </si>
-  <si>
-    <t>act_food_hard_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>事件1</t>
-  </si>
-  <si>
-    <t>奖励1</t>
-  </si>
-  <si>
-    <t>sg_normalEvent_1</t>
-  </si>
-  <si>
-    <t>普通事件1</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_fragment,act_event</t>
-  </si>
-  <si>
-    <t>sg_normalEvent_2</t>
-  </si>
-  <si>
-    <t>普通事件2</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_passive,act_event</t>
-  </si>
-  <si>
-    <t>sg_normalEvent_3</t>
-  </si>
-  <si>
-    <t>普通事件3</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_active,act_event</t>
-  </si>
-  <si>
-    <t>sg_normalEvent_4</t>
-  </si>
-  <si>
-    <t>普通事件4</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_dish,act_event</t>
-  </si>
-  <si>
-    <t>sg_normalEvent_5</t>
-  </si>
-  <si>
-    <t>普通事件5</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_passive,act_event</t>
-  </si>
-  <si>
-    <t>sg_normalEvent_6</t>
-  </si>
-  <si>
-    <t>普通事件6</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_active,act_event</t>
-  </si>
-  <si>
-    <t>sg_normalEvent_7</t>
-  </si>
-  <si>
-    <t>普通事件7</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_dish,act_event</t>
-  </si>
-  <si>
-    <t>sg_normalEvent_8</t>
-  </si>
-  <si>
-    <t>普通事件8</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_food_active,act_event</t>
-  </si>
-  <si>
-    <t>sg_normalEvent_9</t>
-  </si>
-  <si>
-    <t>普通事件9</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_food_dish,act_event</t>
-  </si>
-  <si>
-    <t>sg_normalEvent_10</t>
-  </si>
-  <si>
-    <t>普通事件10</t>
-  </si>
-  <si>
-    <t>act_food_active,act_food_dish,act_event</t>
-  </si>
-  <si>
-    <t>sg_normalEvent_11</t>
-  </si>
-  <si>
-    <t>普通事件11</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_event</t>
-  </si>
-  <si>
-    <t>sg_normalEvent_12</t>
-  </si>
-  <si>
-    <t>普通事件12</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_event</t>
-  </si>
-  <si>
-    <t>sg_normalEvent_13</t>
-  </si>
-  <si>
-    <t>普通事件13</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_event</t>
-  </si>
-  <si>
-    <t>sg_normalEvent_14</t>
-  </si>
-  <si>
-    <t>普通事件14</t>
-  </si>
-  <si>
-    <t>act_food_active,act_event</t>
-  </si>
-  <si>
-    <t>普通事件15</t>
-  </si>
-  <si>
-    <t>act_food_dish,act_event</t>
-  </si>
-  <si>
-    <t>普通困难事件1</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_fragment,act_event</t>
-  </si>
-  <si>
-    <t>sg_normalHardEvent_2</t>
-  </si>
-  <si>
-    <t>普通困难事件2</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_passive,act_event</t>
-  </si>
-  <si>
-    <t>sg_normalHardEvent_3</t>
-  </si>
-  <si>
-    <t>普通困难事件3</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_active,act_event</t>
-  </si>
-  <si>
-    <t>sg_normalHardEvent_4</t>
-  </si>
-  <si>
-    <t>普通困难事件4</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_dish,act_event</t>
-  </si>
-  <si>
-    <t>sg_normalHardEvent_5</t>
-  </si>
-  <si>
-    <t>普通困难事件5</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_passive,act_event</t>
-  </si>
-  <si>
-    <t>sg_normalHardEvent_6</t>
-  </si>
-  <si>
-    <t>普通困难事件6</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_active,act_event</t>
-  </si>
-  <si>
-    <t>sg_normalHardEvent_7</t>
-  </si>
-  <si>
-    <t>普通困难事件7</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_dish,act_event</t>
-  </si>
-  <si>
-    <t>sg_normalHardEvent_8</t>
-  </si>
-  <si>
-    <t>普通困难事件8</t>
-  </si>
-  <si>
-    <t>act_food_hard_passive,act_food_active,act_event</t>
-  </si>
-  <si>
-    <t>sg_normalHardEvent_9</t>
-  </si>
-  <si>
-    <t>普通困难事件9</t>
-  </si>
-  <si>
-    <t>act_food_hard_passive,act_food_dish,act_event</t>
-  </si>
-  <si>
-    <t>sg_normalHardEvent_10</t>
-  </si>
-  <si>
-    <t>普通困难事件10</t>
-  </si>
-  <si>
-    <t>act_food_hard_active,act_food_dish,act_event</t>
-  </si>
-  <si>
-    <t>困难事件1</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_fragment,act_event</t>
-  </si>
-  <si>
-    <t>sg_hardEvent_2</t>
-  </si>
-  <si>
-    <t>困难事件2</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_passive,act_event</t>
-  </si>
-  <si>
-    <t>sg_hardEvent_3</t>
-  </si>
-  <si>
-    <t>困难事件3</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_active,act_event</t>
-  </si>
-  <si>
-    <t>sg_hardEvent_4</t>
-  </si>
-  <si>
-    <t>困难事件4</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_dish,act_event</t>
-  </si>
-  <si>
-    <t>sg_hardEvent_5</t>
-  </si>
-  <si>
-    <t>困难事件5</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_hard_passive,act_event</t>
-  </si>
-  <si>
-    <t>sg_hardEvent_6</t>
-  </si>
-  <si>
-    <t>困难事件6</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_hard_active,act_event</t>
-  </si>
-  <si>
-    <t>sg_hardEvent_7</t>
-  </si>
-  <si>
-    <t>困难事件7</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_hard_dish,act_event</t>
-  </si>
-  <si>
-    <t>sg_hardEvent_8</t>
-  </si>
-  <si>
-    <t>困难事件8</t>
-  </si>
-  <si>
-    <t>act_food_hard_passive,act_food_hard_active,act_event</t>
-  </si>
-  <si>
-    <t>sg_hardEvent_9</t>
-  </si>
-  <si>
-    <t>困难事件9</t>
-  </si>
-  <si>
-    <t>act_food_hard_passive,act_food_hard_dish,act_event</t>
-  </si>
-  <si>
-    <t>sg_hardEvent_10</t>
-  </si>
-  <si>
-    <t>困难事件10</t>
-  </si>
-  <si>
-    <t>act_food_hard_active,act_food_hard_dish,act_event</t>
-  </si>
-  <si>
-    <t>sg_hardEvent_11</t>
-  </si>
-  <si>
-    <t>困难事件11</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_event</t>
-  </si>
-  <si>
-    <t>sg_hardEvent_12</t>
-  </si>
-  <si>
-    <t>困难事件12</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_event</t>
-  </si>
-  <si>
-    <t>sg_hardEvent_13</t>
-  </si>
-  <si>
-    <t>困难事件13</t>
-  </si>
-  <si>
-    <t>act_food_hard_passive,act_event</t>
-  </si>
-  <si>
-    <t>sg_hardEvent_14</t>
-  </si>
-  <si>
-    <t>困难事件14</t>
-  </si>
-  <si>
-    <t>act_food_hard_active,act_event</t>
-  </si>
-  <si>
-    <t>sg_hardEvent_15</t>
-  </si>
-  <si>
-    <t>困难事件15</t>
-  </si>
-  <si>
-    <t>act_food_hard_dish,act_event</t>
-  </si>
-  <si>
-    <t>priority</t>
-  </si>
-  <si>
-    <t>minRunStep</t>
-  </si>
-  <si>
-    <t>maxRunStep</t>
-  </si>
-  <si>
-    <t>minCount</t>
-  </si>
-  <si>
-    <t>maxCount</t>
-  </si>
-  <si>
-    <t>preconditions</t>
-  </si>
-  <si>
-    <t>activeWeeks</t>
-  </si>
-  <si>
-    <t>规则ID(大组用 ruleIds 引用它)</t>
-  </si>
-  <si>
-    <t>优先级,越大越先填充</t>
-  </si>
-  <si>
-    <t>整局行动序号窗口起点,1-based</t>
-  </si>
-  <si>
-    <t>窗口终点,含</t>
-  </si>
-  <si>
-    <t>窗口内至少出现次数</t>
-  </si>
-  <si>
-    <t>窗口内最多出现次数</t>
-  </si>
-  <si>
-    <t>规则前置条件</t>
-  </si>
-  <si>
-    <t>生效周列表；空=全部周</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>(list#sep=,),int</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>rule_reward_early</t>
-  </si>
-  <si>
-    <t>1,2,3,4,5,6,7,8</t>
-  </si>
-  <si>
-    <t>rule_reward_mid</t>
   </si>
 </sst>
 </file>
@@ -3553,39 +3553,8 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="2:12">
-      <c r="B12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>0,0,0,0</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G12" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I12" s="1">
-        <v>0</v>
-      </c>
-      <c r="J12" s="1">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1">
-        <v>0</v>
-      </c>
-      <c r="L12" s="1">
-        <v>0</v>
-      </c>
+    <row r="12" spans="5:5">
+      <c r="E12" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3626,10 +3595,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3637,16 +3606,16 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3668,165 +3637,165 @@
     </row>
     <row r="4" spans="2:5">
       <c r="B4" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D4" s="1">
         <v>100</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="2:18">
       <c r="B5" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D5" s="1">
         <v>100</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="2:18">
       <c r="B6" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D6" s="1">
         <v>100</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="2:18">
       <c r="B7" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D7" s="1">
         <v>100</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="B8" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="B11" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D11" s="1">
         <v>100</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="B12" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D12" s="1">
         <v>100</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D13" s="1">
         <v>100</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D14" s="1">
         <v>100</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>68</v>
@@ -3837,16 +3806,16 @@
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D15" s="1">
         <v>100</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>70</v>
@@ -3857,16 +3826,16 @@
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D16" s="1">
         <v>100</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="L16" s="1" t="s">
         <v>72</v>
@@ -3877,16 +3846,16 @@
     </row>
     <row r="17" spans="2:13">
       <c r="B17" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D17" s="1">
         <v>100</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="L17" s="1" t="s">
         <v>74</v>
@@ -3897,16 +3866,16 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D18" s="1">
         <v>100</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>78</v>
@@ -3917,16 +3886,16 @@
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D19" s="1">
         <v>100</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="L19" s="1" t="s">
         <v>82</v>
@@ -3937,36 +3906,36 @@
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D20" s="1">
         <v>100</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="L20" s="1" t="s">
         <v>84</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="2:20">
       <c r="B21" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D21" s="1">
         <v>100</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L21" s="1" t="s">
         <v>86</v>
@@ -3986,22 +3955,22 @@
     </row>
     <row r="22" spans="2:20">
       <c r="B22" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D22" s="1">
+        <v>100</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="M22" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D22" s="1">
-        <v>100</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>20</v>
@@ -4015,16 +3984,16 @@
     </row>
     <row r="23" spans="2:20">
       <c r="B23" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D23" s="1">
+        <v>100</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="D23" s="1">
-        <v>100</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>161</v>
       </c>
       <c r="R23" s="1" t="s">
         <v>20</v>
@@ -4038,16 +4007,16 @@
     </row>
     <row r="24" spans="2:20">
       <c r="B24" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D24" s="1">
+        <v>100</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D24" s="1">
-        <v>100</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="R24" s="1" t="s">
         <v>20</v>
@@ -4061,16 +4030,16 @@
     </row>
     <row r="25" spans="2:20">
       <c r="B25" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D25" s="1">
+        <v>100</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D25" s="1">
-        <v>100</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>167</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>20</v>
@@ -4084,16 +4053,16 @@
     </row>
     <row r="26" spans="2:20">
       <c r="B26" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D26" s="1">
+        <v>100</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D26" s="1">
-        <v>100</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>170</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>20</v>
@@ -4107,16 +4076,16 @@
     </row>
     <row r="27" spans="2:20">
       <c r="B27" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D27" s="1">
+        <v>100</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D27" s="1">
-        <v>100</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>173</v>
       </c>
       <c r="R27" s="1" t="s">
         <v>24</v>
@@ -4130,16 +4099,16 @@
     </row>
     <row r="28" spans="2:20">
       <c r="B28" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D28" s="1">
+        <v>100</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="D28" s="1">
-        <v>100</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="R28" s="1" t="s">
         <v>24</v>
@@ -4153,16 +4122,16 @@
     </row>
     <row r="29" spans="2:20">
       <c r="B29" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D29" s="1">
+        <v>100</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D29" s="1">
-        <v>100</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="R29" s="1" t="s">
         <v>24</v>
@@ -4176,16 +4145,16 @@
     </row>
     <row r="30" spans="2:20">
       <c r="B30" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D30" s="1">
+        <v>100</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D30" s="1">
-        <v>100</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>182</v>
       </c>
       <c r="R30" s="1" t="s">
         <v>26</v>
@@ -4199,16 +4168,16 @@
     </row>
     <row r="31" spans="2:19">
       <c r="B31" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D31" s="1">
+        <v>100</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="D31" s="1">
-        <v>100</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>185</v>
       </c>
       <c r="R31" s="1" t="s">
         <v>20</v>
@@ -4219,16 +4188,16 @@
     </row>
     <row r="32" spans="2:19">
       <c r="B32" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D32" s="1">
+        <v>100</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D32" s="1">
-        <v>100</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>20</v>
@@ -4239,16 +4208,16 @@
     </row>
     <row r="33" spans="2:19">
       <c r="B33" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D33" s="1">
+        <v>100</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D33" s="1">
-        <v>100</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="R33" s="1" t="s">
         <v>20</v>
@@ -4259,16 +4228,16 @@
     </row>
     <row r="34" spans="2:19">
       <c r="B34" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D34" s="1">
+        <v>100</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="D34" s="1">
-        <v>100</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>194</v>
       </c>
       <c r="R34" s="1" t="s">
         <v>20</v>
@@ -4279,16 +4248,16 @@
     </row>
     <row r="35" spans="2:19">
       <c r="B35" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D35" s="1">
+        <v>100</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D35" s="1">
-        <v>100</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>197</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>24</v>
@@ -4299,16 +4268,16 @@
     </row>
     <row r="36" spans="2:19">
       <c r="B36" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D36" s="1">
+        <v>100</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D36" s="1">
-        <v>100</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="R36" s="1" t="s">
         <v>24</v>
@@ -4319,16 +4288,16 @@
     </row>
     <row r="37" spans="2:19">
       <c r="B37" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D37" s="1">
+        <v>100</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="D37" s="1">
-        <v>100</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>203</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>20</v>
@@ -4342,16 +4311,16 @@
     </row>
     <row r="38" spans="2:19">
       <c r="B38" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D38" s="1">
+        <v>100</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D38" s="1">
-        <v>100</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>24</v>
@@ -4365,16 +4334,16 @@
     </row>
     <row r="39" spans="2:19">
       <c r="B39" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D39" s="1">
+        <v>100</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="D39" s="1">
-        <v>100</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>209</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>26</v>
@@ -4388,16 +4357,16 @@
     </row>
     <row r="40" spans="2:19">
       <c r="B40" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D40" s="1">
+        <v>100</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="D40" s="1">
-        <v>100</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>212</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>28</v>
@@ -4411,16 +4380,16 @@
     </row>
     <row r="41" spans="2:12">
       <c r="B41" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D41" s="1">
+        <v>100</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="D41" s="1">
-        <v>100</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>215</v>
       </c>
       <c r="L41" s="1" t="s">
         <v>30</v>
@@ -4428,30 +4397,30 @@
     </row>
     <row r="42" spans="2:5">
       <c r="B42" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D42" s="1">
+        <v>100</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="D42" s="1">
-        <v>100</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="43" spans="2:12">
       <c r="B43" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D43" s="1">
+        <v>100</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="D43" s="1">
-        <v>100</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>221</v>
       </c>
       <c r="L43" s="1" t="s">
         <v>32</v>
@@ -4459,16 +4428,16 @@
     </row>
     <row r="44" spans="2:12">
       <c r="B44" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D44" s="1">
+        <v>100</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="D44" s="1">
-        <v>100</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>224</v>
       </c>
       <c r="L44" s="1" t="s">
         <v>35</v>
@@ -4476,16 +4445,16 @@
     </row>
     <row r="45" spans="2:12">
       <c r="B45" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D45" s="1">
+        <v>100</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>225</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D45" s="1">
-        <v>100</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>227</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>37</v>
@@ -4493,16 +4462,16 @@
     </row>
     <row r="46" spans="2:12">
       <c r="B46" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D46" s="1">
+        <v>100</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>228</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="D46" s="1">
-        <v>100</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>230</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>39</v>
@@ -4510,16 +4479,16 @@
     </row>
     <row r="47" spans="2:12">
       <c r="B47" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D47" s="1">
+        <v>100</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="D47" s="1">
-        <v>100</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>233</v>
       </c>
       <c r="L47" s="1" t="s">
         <v>41</v>
@@ -4527,16 +4496,16 @@
     </row>
     <row r="48" spans="2:12">
       <c r="B48" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D48" s="1">
+        <v>100</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="D48" s="1">
-        <v>100</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>236</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>43</v>
@@ -4544,16 +4513,16 @@
     </row>
     <row r="49" spans="2:12">
       <c r="B49" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D49" s="1">
+        <v>100</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="D49" s="1">
-        <v>100</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>239</v>
       </c>
       <c r="L49" s="1" t="s">
         <v>46</v>
@@ -4561,414 +4530,414 @@
     </row>
     <row r="50" spans="2:5">
       <c r="B50" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D50" s="1">
+        <v>100</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="D50" s="1">
-        <v>100</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="51" spans="2:5">
       <c r="B51" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D51" s="1">
+        <v>100</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="D51" s="1">
-        <v>100</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="52" spans="2:5">
       <c r="B52" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D52" s="1">
+        <v>100</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="D52" s="1">
-        <v>100</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="53" spans="2:5">
       <c r="B53" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D53" s="1">
+        <v>100</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="D53" s="1">
-        <v>100</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="54" spans="2:5">
       <c r="B54" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D54" s="1">
+        <v>100</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="D54" s="1">
-        <v>100</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="55" spans="2:5">
       <c r="B55" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D55" s="1">
+        <v>100</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="D55" s="1">
-        <v>100</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="56" spans="2:5">
       <c r="B56" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D56" s="1">
+        <v>100</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>258</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="D56" s="1">
-        <v>100</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="57" spans="2:5">
       <c r="B57" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D57" s="1">
+        <v>100</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="D57" s="1">
-        <v>100</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="58" spans="2:5">
       <c r="B58" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D58" s="1">
+        <v>100</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>264</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="D58" s="1">
-        <v>100</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="59" spans="2:5">
       <c r="B59" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D59" s="1">
+        <v>100</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>267</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="D59" s="1">
-        <v>100</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="60" spans="2:5">
       <c r="B60" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D60" s="1">
+        <v>100</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="D60" s="1">
-        <v>100</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="61" spans="2:5">
       <c r="B61" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D61" s="1">
+        <v>100</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="D61" s="1">
-        <v>100</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="62" spans="2:5">
       <c r="B62" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D62" s="1">
+        <v>100</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="D62" s="1">
-        <v>100</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="63" spans="2:5">
       <c r="B63" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D63" s="1">
+        <v>100</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="D63" s="1">
-        <v>100</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="64" spans="2:5">
       <c r="B64" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D64" s="1">
+        <v>100</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="D64" s="1">
-        <v>100</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="65" spans="2:5">
       <c r="B65" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D65" s="1">
+        <v>100</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="D65" s="1">
-        <v>100</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="66" spans="2:5">
       <c r="B66" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D66" s="1">
+        <v>100</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D66" s="1">
-        <v>100</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="67" spans="2:5">
       <c r="B67" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D67" s="1">
+        <v>100</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="D67" s="1">
-        <v>100</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="68" spans="2:5">
       <c r="B68" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D68" s="1">
+        <v>100</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="D68" s="1">
-        <v>100</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="69" spans="2:5">
       <c r="B69" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D69" s="1">
+        <v>100</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>297</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="D69" s="1">
-        <v>100</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="70" spans="2:5">
       <c r="B70" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D70" s="1">
+        <v>100</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="D70" s="1">
-        <v>100</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="71" spans="2:5">
       <c r="B71" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D71" s="1">
+        <v>100</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>303</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="D71" s="1">
-        <v>100</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="72" spans="2:5">
       <c r="B72" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D72" s="1">
+        <v>100</v>
+      </c>
+      <c r="E72" s="1" t="s">
         <v>306</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="D72" s="1">
-        <v>100</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="73" spans="2:5">
       <c r="B73" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D73" s="1">
+        <v>100</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D73" s="1">
-        <v>100</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="74" spans="2:5">
       <c r="B74" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D74" s="1">
+        <v>100</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="D74" s="1">
-        <v>100</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="75" spans="2:5">
       <c r="B75" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D75" s="1">
+        <v>100</v>
+      </c>
+      <c r="E75" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="D75" s="1">
-        <v>100</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="76" spans="2:5">
       <c r="B76" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D76" s="1">
+        <v>100</v>
+      </c>
+      <c r="E76" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="D76" s="1">
-        <v>100</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="77" spans="2:5">
       <c r="B77" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D77" s="1">
+        <v>100</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="D77" s="1">
-        <v>100</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="78" spans="2:20">
       <c r="B78" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D78" s="1">
+        <v>100</v>
+      </c>
+      <c r="E78" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="Q78" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="D78" s="1">
-        <v>100</v>
-      </c>
-      <c r="E78" s="1" t="s">
+      <c r="R78" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="Q78" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="R78" s="1" t="s">
-        <v>328</v>
       </c>
       <c r="S78" s="1">
         <v>80</v>
@@ -4979,16 +4948,16 @@
     </row>
     <row r="79" spans="2:20">
       <c r="B79" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="D79" s="1">
+        <v>100</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="D79" s="1">
-        <v>100</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>331</v>
       </c>
       <c r="T79" s="1" t="s">
         <v>28</v>
@@ -4996,16 +4965,16 @@
     </row>
     <row r="80" spans="2:20">
       <c r="B80" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D80" s="1">
+        <v>100</v>
+      </c>
+      <c r="E80" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="D80" s="1">
-        <v>100</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>334</v>
       </c>
       <c r="T80" s="1" t="s">
         <v>30</v>
@@ -5013,22 +4982,22 @@
     </row>
     <row r="81" spans="2:20">
       <c r="B81" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="D81" s="1">
+        <v>100</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="Q81" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="D81" s="1">
-        <v>100</v>
-      </c>
-      <c r="E81" s="1" t="s">
+      <c r="R81" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="Q81" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="R81" s="1" t="s">
-        <v>339</v>
       </c>
       <c r="S81" s="1">
         <v>100</v>
@@ -5039,16 +5008,16 @@
     </row>
     <row r="82" spans="2:20">
       <c r="B82" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D82" s="1">
+        <v>100</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="D82" s="1">
-        <v>100</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>342</v>
       </c>
       <c r="T82" s="1" t="s">
         <v>41</v>
@@ -5056,16 +5025,16 @@
     </row>
     <row r="83" spans="2:20">
       <c r="B83" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D83" s="1">
+        <v>100</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="D83" s="1">
-        <v>100</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>345</v>
       </c>
       <c r="T83" s="1" t="s">
         <v>37</v>
@@ -5073,22 +5042,22 @@
     </row>
     <row r="84" spans="2:20">
       <c r="B84" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D84" s="1">
+        <v>100</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="Q84" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="D84" s="1">
-        <v>100</v>
-      </c>
-      <c r="E84" s="1" t="s">
+      <c r="R84" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="Q84" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="R84" s="1" t="s">
-        <v>350</v>
       </c>
       <c r="S84" s="1">
         <v>80</v>
@@ -5099,16 +5068,16 @@
     </row>
     <row r="85" spans="2:20">
       <c r="B85" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D85" s="1">
+        <v>100</v>
+      </c>
+      <c r="E85" s="1" t="s">
         <v>351</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="D85" s="1">
-        <v>100</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>353</v>
       </c>
       <c r="T85" s="1" t="s">
         <v>39</v>
@@ -5116,16 +5085,16 @@
     </row>
     <row r="86" spans="2:20">
       <c r="B86" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D86" s="1">
+        <v>100</v>
+      </c>
+      <c r="E86" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="D86" s="1">
-        <v>100</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>356</v>
       </c>
       <c r="T86" s="1" t="s">
         <v>41</v>
@@ -5133,22 +5102,22 @@
     </row>
     <row r="87" spans="2:20">
       <c r="B87" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="D87" s="1">
+        <v>100</v>
+      </c>
+      <c r="E87" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="Q87" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="D87" s="1">
-        <v>100</v>
-      </c>
-      <c r="E87" s="1" t="s">
+      <c r="R87" s="1" t="s">
         <v>359</v>
-      </c>
-      <c r="Q87" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="R87" s="1" t="s">
-        <v>361</v>
       </c>
       <c r="S87" s="1">
         <v>100</v>
@@ -5159,16 +5128,16 @@
     </row>
     <row r="88" spans="2:20">
       <c r="B88" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="D88" s="1">
+        <v>100</v>
+      </c>
+      <c r="E88" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="D88" s="1">
-        <v>100</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>364</v>
       </c>
       <c r="T88" s="1" t="s">
         <v>20</v>
@@ -5176,16 +5145,16 @@
     </row>
     <row r="89" spans="2:20">
       <c r="B89" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D89" s="1">
+        <v>100</v>
+      </c>
+      <c r="E89" s="1" t="s">
         <v>365</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="D89" s="1">
-        <v>100</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>367</v>
       </c>
       <c r="T89" s="1" t="s">
         <v>30</v>
@@ -5193,22 +5162,22 @@
     </row>
     <row r="90" spans="2:20">
       <c r="B90" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D90" s="1">
+        <v>100</v>
+      </c>
+      <c r="E90" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="Q90" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="D90" s="1">
-        <v>100</v>
-      </c>
-      <c r="E90" s="1" t="s">
+      <c r="R90" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="Q90" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="R90" s="1" t="s">
-        <v>372</v>
       </c>
       <c r="S90" s="1">
         <v>100</v>
@@ -5219,16 +5188,16 @@
     </row>
     <row r="91" spans="2:20">
       <c r="B91" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D91" s="1">
+        <v>100</v>
+      </c>
+      <c r="E91" s="1" t="s">
         <v>373</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="D91" s="1">
-        <v>100</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>375</v>
       </c>
       <c r="T91" s="1" t="s">
         <v>49</v>
@@ -5236,22 +5205,22 @@
     </row>
     <row r="92" spans="2:20">
       <c r="B92" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="D92" s="1">
+        <v>100</v>
+      </c>
+      <c r="E92" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="Q92" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="D92" s="1">
-        <v>100</v>
-      </c>
-      <c r="E92" s="1" t="s">
+      <c r="R92" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="Q92" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="R92" s="1" t="s">
-        <v>379</v>
       </c>
       <c r="S92" s="1">
         <v>100</v>
@@ -5262,436 +5231,436 @@
     </row>
     <row r="93" spans="2:5">
       <c r="B93" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="D93" s="1">
+        <v>100</v>
+      </c>
+      <c r="E93" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="D93" s="1">
-        <v>100</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="94" spans="2:5">
       <c r="B94" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C94" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="D94" s="1">
+        <v>100</v>
+      </c>
+      <c r="E94" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="D94" s="1">
-        <v>100</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="95" spans="2:5">
       <c r="B95" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="D95" s="1">
+        <v>100</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>387</v>
-      </c>
-      <c r="D95" s="1">
-        <v>100</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="96" spans="2:5">
       <c r="B96" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="D96" s="1">
+        <v>100</v>
+      </c>
+      <c r="E96" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="D96" s="1">
-        <v>100</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="97" spans="2:5">
       <c r="B97" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C97" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="D97" s="1">
+        <v>100</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>393</v>
-      </c>
-      <c r="D97" s="1">
-        <v>100</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="98" spans="2:5">
       <c r="B98" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C98" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="D98" s="1">
+        <v>100</v>
+      </c>
+      <c r="E98" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="D98" s="1">
-        <v>100</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="99" spans="2:5">
       <c r="B99" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C99" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="D99" s="1">
+        <v>100</v>
+      </c>
+      <c r="E99" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="D99" s="1">
-        <v>100</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="100" spans="2:5">
       <c r="B100" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C100" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="D100" s="1">
+        <v>100</v>
+      </c>
+      <c r="E100" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="D100" s="1">
-        <v>100</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="101" spans="2:5">
       <c r="B101" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C101" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="D101" s="1">
+        <v>100</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="D101" s="1">
-        <v>100</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="102" spans="2:5">
       <c r="B102" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C102" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="D102" s="1">
+        <v>100</v>
+      </c>
+      <c r="E102" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="D102" s="1">
-        <v>100</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="103" spans="2:5">
       <c r="B103" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="D103" s="1">
+        <v>100</v>
+      </c>
+      <c r="E103" s="1" t="s">
         <v>411</v>
-      </c>
-      <c r="D103" s="1">
-        <v>100</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="104" spans="2:5">
       <c r="B104" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="D104" s="1">
+        <v>100</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="D104" s="1">
-        <v>100</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="105" spans="2:5">
       <c r="B105" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="D105" s="1">
+        <v>100</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="D105" s="1">
-        <v>100</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="106" spans="2:5">
       <c r="B106" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C106" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="D106" s="1">
+        <v>100</v>
+      </c>
+      <c r="E106" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="D106" s="1">
-        <v>100</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="107" spans="2:5">
       <c r="B107" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C107" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="D107" s="1">
+        <v>100</v>
+      </c>
+      <c r="E107" s="1" t="s">
         <v>423</v>
-      </c>
-      <c r="D107" s="1">
-        <v>100</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="108" spans="2:5">
       <c r="B108" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C108" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="D108" s="1">
+        <v>100</v>
+      </c>
+      <c r="E108" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="D108" s="1">
-        <v>100</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="109" spans="2:5">
       <c r="B109" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C109" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="D109" s="1">
+        <v>100</v>
+      </c>
+      <c r="E109" s="1" t="s">
         <v>429</v>
-      </c>
-      <c r="D109" s="1">
-        <v>100</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="110" spans="2:5">
       <c r="B110" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C110" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="D110" s="1">
+        <v>100</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="D110" s="1">
-        <v>100</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="111" spans="2:5">
       <c r="B111" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C111" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="D111" s="1">
+        <v>100</v>
+      </c>
+      <c r="E111" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="D111" s="1">
-        <v>100</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="112" spans="2:5">
       <c r="B112" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="D112" s="1">
+        <v>100</v>
+      </c>
+      <c r="E112" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="D112" s="1">
-        <v>100</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="113" spans="2:5">
       <c r="B113" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C113" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="D113" s="1">
+        <v>100</v>
+      </c>
+      <c r="E113" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="D113" s="1">
-        <v>100</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="114" spans="2:5">
       <c r="B114" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="C114" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="D114" s="1">
+        <v>100</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>444</v>
-      </c>
-      <c r="D114" s="1">
-        <v>100</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="115" spans="2:5">
       <c r="B115" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C115" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="D115" s="1">
+        <v>100</v>
+      </c>
+      <c r="E115" s="1" t="s">
         <v>447</v>
-      </c>
-      <c r="D115" s="1">
-        <v>100</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="116" spans="2:5">
       <c r="B116" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C116" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="D116" s="1">
+        <v>100</v>
+      </c>
+      <c r="E116" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="D116" s="1">
-        <v>100</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="117" spans="2:5">
       <c r="B117" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C117" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="D117" s="1">
+        <v>100</v>
+      </c>
+      <c r="E117" s="1" t="s">
         <v>453</v>
-      </c>
-      <c r="D117" s="1">
-        <v>100</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="118" spans="2:5">
       <c r="B118" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="C118" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="D118" s="1">
+        <v>100</v>
+      </c>
+      <c r="E118" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="D118" s="1">
-        <v>100</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="119" spans="2:5">
       <c r="B119" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C119" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="D119" s="1">
+        <v>100</v>
+      </c>
+      <c r="E119" s="1" t="s">
         <v>459</v>
-      </c>
-      <c r="D119" s="1">
-        <v>100</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="120" spans="2:5">
       <c r="B120" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C120" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="D120" s="1">
+        <v>100</v>
+      </c>
+      <c r="E120" s="1" t="s">
         <v>462</v>
-      </c>
-      <c r="D120" s="1">
-        <v>100</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="121" spans="2:5">
       <c r="B121" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C121" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="D121" s="1">
+        <v>100</v>
+      </c>
+      <c r="E121" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="D121" s="1">
-        <v>100</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="122" spans="2:5">
       <c r="B122" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C122" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="D122" s="1">
+        <v>100</v>
+      </c>
+      <c r="E122" s="1" t="s">
         <v>468</v>
-      </c>
-      <c r="D122" s="1">
-        <v>100</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="123" spans="2:5">
       <c r="B123" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C123" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="C123" s="1" t="s">
+      <c r="D123" s="1">
+        <v>100</v>
+      </c>
+      <c r="E123" s="1" t="s">
         <v>471</v>
-      </c>
-      <c r="D123" s="1">
-        <v>100</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="124" spans="2:5">
@@ -5699,7 +5668,7 @@
         <v>77</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D124" s="1">
         <v>100</v>
@@ -5713,7 +5682,7 @@
         <v>81</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D125" s="1">
         <v>100</v>
@@ -5724,570 +5693,570 @@
     </row>
     <row r="126" spans="2:5">
       <c r="B126" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="C126" s="1" t="s">
+      <c r="D126" s="1">
+        <v>100</v>
+      </c>
+      <c r="E126" s="1" t="s">
         <v>476</v>
-      </c>
-      <c r="D126" s="1">
-        <v>100</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="127" spans="2:5">
       <c r="B127" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C127" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="D127" s="1">
+        <v>100</v>
+      </c>
+      <c r="E127" s="1" t="s">
         <v>479</v>
-      </c>
-      <c r="D127" s="1">
-        <v>100</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="128" spans="2:5">
       <c r="B128" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C128" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="C128" s="1" t="s">
+      <c r="D128" s="1">
+        <v>100</v>
+      </c>
+      <c r="E128" s="1" t="s">
         <v>482</v>
-      </c>
-      <c r="D128" s="1">
-        <v>100</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="129" spans="2:5">
       <c r="B129" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C129" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="C129" s="1" t="s">
+      <c r="D129" s="1">
+        <v>100</v>
+      </c>
+      <c r="E129" s="1" t="s">
         <v>485</v>
-      </c>
-      <c r="D129" s="1">
-        <v>100</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="130" spans="2:5">
       <c r="B130" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C130" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="C130" s="1" t="s">
+      <c r="D130" s="1">
+        <v>100</v>
+      </c>
+      <c r="E130" s="1" t="s">
         <v>488</v>
-      </c>
-      <c r="D130" s="1">
-        <v>100</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="131" spans="2:5">
       <c r="B131" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C131" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="C131" s="1" t="s">
+      <c r="D131" s="1">
+        <v>100</v>
+      </c>
+      <c r="E131" s="1" t="s">
         <v>491</v>
-      </c>
-      <c r="D131" s="1">
-        <v>100</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="132" spans="2:5">
       <c r="B132" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C132" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="C132" s="1" t="s">
+      <c r="D132" s="1">
+        <v>100</v>
+      </c>
+      <c r="E132" s="1" t="s">
         <v>494</v>
-      </c>
-      <c r="D132" s="1">
-        <v>100</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="133" spans="2:5">
       <c r="B133" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C133" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="C133" s="1" t="s">
+      <c r="D133" s="1">
+        <v>100</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>497</v>
-      </c>
-      <c r="D133" s="1">
-        <v>100</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="134" spans="2:5">
       <c r="B134" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C134" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="C134" s="1" t="s">
+      <c r="D134" s="1">
+        <v>100</v>
+      </c>
+      <c r="E134" s="1" t="s">
         <v>500</v>
-      </c>
-      <c r="D134" s="1">
-        <v>100</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="135" spans="2:5">
       <c r="B135" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C135" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="C135" s="1" t="s">
+      <c r="D135" s="1">
+        <v>100</v>
+      </c>
+      <c r="E135" s="1" t="s">
         <v>503</v>
-      </c>
-      <c r="D135" s="1">
-        <v>100</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="136" spans="2:5">
       <c r="B136" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C136" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="C136" s="1" t="s">
+      <c r="D136" s="1">
+        <v>100</v>
+      </c>
+      <c r="E136" s="1" t="s">
         <v>506</v>
-      </c>
-      <c r="D136" s="1">
-        <v>100</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="137" spans="2:5">
       <c r="B137" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C137" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="C137" s="1" t="s">
+      <c r="D137" s="1">
+        <v>100</v>
+      </c>
+      <c r="E137" s="1" t="s">
         <v>509</v>
-      </c>
-      <c r="D137" s="1">
-        <v>100</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="138" spans="2:5">
       <c r="B138" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C138" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="C138" s="1" t="s">
+      <c r="D138" s="1">
+        <v>100</v>
+      </c>
+      <c r="E138" s="1" t="s">
         <v>512</v>
-      </c>
-      <c r="D138" s="1">
-        <v>100</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="139" spans="2:5">
       <c r="B139" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C139" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="C139" s="1" t="s">
+      <c r="D139" s="1">
+        <v>100</v>
+      </c>
+      <c r="E139" s="1" t="s">
         <v>515</v>
-      </c>
-      <c r="D139" s="1">
-        <v>100</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="140" spans="2:5">
       <c r="B140" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C140" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="D140" s="1">
+        <v>100</v>
+      </c>
+      <c r="E140" s="1" t="s">
         <v>517</v>
-      </c>
-      <c r="D140" s="1">
-        <v>100</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="141" spans="2:5">
       <c r="B141" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C141" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="D141" s="1">
+        <v>100</v>
+      </c>
+      <c r="E141" s="1" t="s">
         <v>519</v>
-      </c>
-      <c r="D141" s="1">
-        <v>100</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="142" spans="2:5">
       <c r="B142" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="C142" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="C142" s="1" t="s">
+      <c r="D142" s="1">
+        <v>100</v>
+      </c>
+      <c r="E142" s="1" t="s">
         <v>522</v>
-      </c>
-      <c r="D142" s="1">
-        <v>100</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="143" spans="2:5">
       <c r="B143" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="C143" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="C143" s="1" t="s">
+      <c r="D143" s="1">
+        <v>100</v>
+      </c>
+      <c r="E143" s="1" t="s">
         <v>525</v>
-      </c>
-      <c r="D143" s="1">
-        <v>100</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="144" spans="2:5">
       <c r="B144" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="C144" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="C144" s="1" t="s">
+      <c r="D144" s="1">
+        <v>100</v>
+      </c>
+      <c r="E144" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="D144" s="1">
-        <v>100</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="145" spans="2:5">
       <c r="B145" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C145" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="C145" s="1" t="s">
+      <c r="D145" s="1">
+        <v>100</v>
+      </c>
+      <c r="E145" s="1" t="s">
         <v>531</v>
-      </c>
-      <c r="D145" s="1">
-        <v>100</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="146" spans="2:5">
       <c r="B146" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="C146" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="C146" s="1" t="s">
+      <c r="D146" s="1">
+        <v>100</v>
+      </c>
+      <c r="E146" s="1" t="s">
         <v>534</v>
-      </c>
-      <c r="D146" s="1">
-        <v>100</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="147" spans="2:5">
       <c r="B147" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C147" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C147" s="1" t="s">
+      <c r="D147" s="1">
+        <v>100</v>
+      </c>
+      <c r="E147" s="1" t="s">
         <v>537</v>
-      </c>
-      <c r="D147" s="1">
-        <v>100</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="148" spans="2:5">
       <c r="B148" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="C148" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="C148" s="1" t="s">
+      <c r="D148" s="1">
+        <v>100</v>
+      </c>
+      <c r="E148" s="1" t="s">
         <v>540</v>
-      </c>
-      <c r="D148" s="1">
-        <v>100</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="149" spans="2:5">
       <c r="B149" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="C149" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="C149" s="1" t="s">
+      <c r="D149" s="1">
+        <v>100</v>
+      </c>
+      <c r="E149" s="1" t="s">
         <v>543</v>
-      </c>
-      <c r="D149" s="1">
-        <v>100</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="150" spans="2:5">
       <c r="B150" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C150" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="C150" s="1" t="s">
+      <c r="D150" s="1">
+        <v>100</v>
+      </c>
+      <c r="E150" s="1" t="s">
         <v>546</v>
-      </c>
-      <c r="D150" s="1">
-        <v>100</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="151" spans="2:5">
       <c r="B151" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C151" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D151" s="1">
+        <v>100</v>
+      </c>
+      <c r="E151" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="D151" s="1">
-        <v>100</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="152" spans="2:5">
       <c r="B152" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="C152" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="C152" s="1" t="s">
+      <c r="D152" s="1">
+        <v>100</v>
+      </c>
+      <c r="E152" s="1" t="s">
         <v>551</v>
-      </c>
-      <c r="D152" s="1">
-        <v>100</v>
-      </c>
-      <c r="E152" s="1" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="153" spans="2:5">
       <c r="B153" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="C153" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C153" s="1" t="s">
+      <c r="D153" s="1">
+        <v>100</v>
+      </c>
+      <c r="E153" s="1" t="s">
         <v>554</v>
-      </c>
-      <c r="D153" s="1">
-        <v>100</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="154" spans="2:5">
       <c r="B154" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="C154" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="C154" s="1" t="s">
+      <c r="D154" s="1">
+        <v>100</v>
+      </c>
+      <c r="E154" s="1" t="s">
         <v>557</v>
-      </c>
-      <c r="D154" s="1">
-        <v>100</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="155" spans="2:5">
       <c r="B155" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C155" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="C155" s="1" t="s">
+      <c r="D155" s="1">
+        <v>100</v>
+      </c>
+      <c r="E155" s="1" t="s">
         <v>560</v>
-      </c>
-      <c r="D155" s="1">
-        <v>100</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="156" spans="2:5">
       <c r="B156" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="C156" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="C156" s="1" t="s">
+      <c r="D156" s="1">
+        <v>100</v>
+      </c>
+      <c r="E156" s="1" t="s">
         <v>563</v>
-      </c>
-      <c r="D156" s="1">
-        <v>100</v>
-      </c>
-      <c r="E156" s="1" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="157" spans="2:5">
       <c r="B157" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="C157" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="C157" s="1" t="s">
+      <c r="D157" s="1">
+        <v>100</v>
+      </c>
+      <c r="E157" s="1" t="s">
         <v>566</v>
-      </c>
-      <c r="D157" s="1">
-        <v>100</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="158" spans="2:5">
       <c r="B158" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="C158" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="C158" s="1" t="s">
+      <c r="D158" s="1">
+        <v>100</v>
+      </c>
+      <c r="E158" s="1" t="s">
         <v>569</v>
-      </c>
-      <c r="D158" s="1">
-        <v>100</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="159" spans="2:5">
       <c r="B159" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="C159" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="C159" s="1" t="s">
+      <c r="D159" s="1">
+        <v>100</v>
+      </c>
+      <c r="E159" s="1" t="s">
         <v>572</v>
-      </c>
-      <c r="D159" s="1">
-        <v>100</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="160" spans="2:5">
       <c r="B160" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C160" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="C160" s="1" t="s">
+      <c r="D160" s="1">
+        <v>100</v>
+      </c>
+      <c r="E160" s="1" t="s">
         <v>575</v>
-      </c>
-      <c r="D160" s="1">
-        <v>100</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="161" spans="2:5">
       <c r="B161" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="C161" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="C161" s="1" t="s">
+      <c r="D161" s="1">
+        <v>100</v>
+      </c>
+      <c r="E161" s="1" t="s">
         <v>578</v>
-      </c>
-      <c r="D161" s="1">
-        <v>100</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="162" spans="2:5">
       <c r="B162" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="C162" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="C162" s="1" t="s">
+      <c r="D162" s="1">
+        <v>100</v>
+      </c>
+      <c r="E162" s="1" t="s">
         <v>581</v>
-      </c>
-      <c r="D162" s="1">
-        <v>100</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="163" spans="2:5">
       <c r="B163" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="C163" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="C163" s="1" t="s">
+      <c r="D163" s="1">
+        <v>100</v>
+      </c>
+      <c r="E163" s="1" t="s">
         <v>584</v>
-      </c>
-      <c r="D163" s="1">
-        <v>100</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="164" spans="2:5">
       <c r="B164" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="C164" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="C164" s="1" t="s">
+      <c r="D164" s="1">
+        <v>100</v>
+      </c>
+      <c r="E164" s="1" t="s">
         <v>587</v>
-      </c>
-      <c r="D164" s="1">
-        <v>100</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="165" spans="2:5">
       <c r="B165" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="C165" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="C165" s="1" t="s">
+      <c r="D165" s="1">
+        <v>100</v>
+      </c>
+      <c r="E165" s="1" t="s">
         <v>590</v>
-      </c>
-      <c r="D165" s="1">
-        <v>100</v>
-      </c>
-      <c r="E165" s="1" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="166" spans="2:5">
       <c r="B166" s="1" t="s">
-        <v>91</v>
+        <v>377</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D166" s="1">
         <v>100</v>
@@ -6328,25 +6297,25 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>591</v>
+      </c>
+      <c r="D1" t="s">
         <v>592</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>593</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>594</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>595</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>596</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>597</v>
-      </c>
-      <c r="I1" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6354,28 +6323,28 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>598</v>
+      </c>
+      <c r="C2" t="s">
         <v>599</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>600</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>601</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>602</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>603</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>604</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>605</v>
-      </c>
-      <c r="I2" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -6386,33 +6355,33 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="G3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
+        <v>608</v>
+      </c>
+      <c r="B4" t="s">
         <v>609</v>
-      </c>
-      <c r="B4" t="s">
-        <v>610</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -6430,18 +6399,18 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="I4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B5" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C5">
         <v>95</v>
@@ -6459,15 +6428,15 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="I5" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B6" t="s">
         <v>76</v>
@@ -6488,18 +6457,18 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="I6" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>612</v>
       </c>
       <c r="C7">
         <v>1000</v>
@@ -6517,192 +6486,192 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="I7" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B8" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C8" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D8" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E8" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F8" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G8" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H8" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B9" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C9" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D9" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E9" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F9" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G9" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H9" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B10" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C10" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D10" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E10" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F10" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G10" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H10" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B11" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C11" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D11" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E11" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F11" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G11" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H11" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B12" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C12" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D12" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E12" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F12" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G12" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H12" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15280" activeTab="1"/>
+    <workbookView windowHeight="15300" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="action" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="612">
   <si>
     <t>##var</t>
   </si>
@@ -256,1189 +256,1186 @@
     <t>sg_event_1</t>
   </si>
   <si>
+    <t>lg_normalEvent</t>
+  </si>
+  <si>
+    <t>普通事件大组</t>
+  </si>
+  <si>
+    <t>lg_normalHardEvent</t>
+  </si>
+  <si>
+    <t>普通困难事件大组</t>
+  </si>
+  <si>
+    <t>lg_hardEvent</t>
+  </si>
+  <si>
+    <t>困难事件大组</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>actionIds</t>
+  </si>
+  <si>
+    <t>小组ID</t>
+  </si>
+  <si>
+    <t>小组名(调试用)</t>
+  </si>
+  <si>
+    <t>被大组选中的权重</t>
+  </si>
+  <si>
+    <t>小组内固定行动ID列表→action.id</t>
+  </si>
+  <si>
+    <t>sg_normal_1</t>
+  </si>
+  <si>
+    <t>普通1</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_fragment,act_food_passive</t>
+  </si>
+  <si>
+    <t>sg_normal_2</t>
+  </si>
+  <si>
+    <t>普通2</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_fragment,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalEvent_15</t>
+  </si>
+  <si>
+    <t>sg_normal_3</t>
+  </si>
+  <si>
+    <t>普通3</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_fragment,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHardEvent_1</t>
+  </si>
+  <si>
+    <t>sg_normal_4</t>
+  </si>
+  <si>
+    <t>普通4</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_hardEvent_1</t>
+  </si>
+  <si>
+    <t>sg_normal_5</t>
+  </si>
+  <si>
+    <t>普通5</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normal_6</t>
+  </si>
+  <si>
+    <t>普通6</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normal_7</t>
+  </si>
+  <si>
+    <t>普通7</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normal_8</t>
+  </si>
+  <si>
+    <t>普通8</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normal_9</t>
+  </si>
+  <si>
+    <t>普通9</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normal_10</t>
+  </si>
+  <si>
+    <t>普通10</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_food_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normal_11</t>
+  </si>
+  <si>
+    <t>普通11</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_fragment</t>
+  </si>
+  <si>
+    <t>sg_normal_12</t>
+  </si>
+  <si>
+    <t>普通12</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_passive</t>
+  </si>
+  <si>
+    <t>sg_normal_13</t>
+  </si>
+  <si>
+    <t>普通13</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normal_14</t>
+  </si>
+  <si>
+    <t>普通14</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normal_15</t>
+  </si>
+  <si>
+    <t>普通15</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_passive</t>
+  </si>
+  <si>
     <t>lg_reward</t>
   </si>
   <si>
     <t>奖励大组</t>
   </si>
   <si>
-    <t>rule_reward_early,rule_reward_mid</t>
+    <t>sg_normal_16</t>
+  </si>
+  <si>
+    <t>普通16</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normal_17</t>
+  </si>
+  <si>
+    <t>普通17</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_dish</t>
+  </si>
+  <si>
+    <t>普通困难混合大组</t>
+  </si>
+  <si>
+    <t>sg_normal_18</t>
+  </si>
+  <si>
+    <t>普通18</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normal_19</t>
+  </si>
+  <si>
+    <t>普通19</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>lg_debug</t>
+  </si>
+  <si>
+    <t>调试大组</t>
+  </si>
+  <si>
+    <t>sg_normal_20</t>
+  </si>
+  <si>
+    <t>普通20</t>
+  </si>
+  <si>
+    <t>act_food_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_1</t>
+  </si>
+  <si>
+    <t>普通困难1</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_fragment,act_food_passive</t>
+  </si>
+  <si>
+    <t>sg_normalHard_2</t>
+  </si>
+  <si>
+    <t>普通困难2</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_fragment,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_3</t>
+  </si>
+  <si>
+    <t>普通困难3</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_fragment,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_4</t>
+  </si>
+  <si>
+    <t>普通困难4</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_5</t>
+  </si>
+  <si>
+    <t>普通困难5</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_6</t>
+  </si>
+  <si>
+    <t>普通困难6</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_7</t>
+  </si>
+  <si>
+    <t>普通困难7</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_8</t>
+  </si>
+  <si>
+    <t>普通困难8</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_9</t>
+  </si>
+  <si>
+    <t>普通困难9</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_10</t>
+  </si>
+  <si>
+    <t>普通困难10</t>
+  </si>
+  <si>
+    <t>act_food_hard_passive,act_food_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_11</t>
+  </si>
+  <si>
+    <t>普通困难11</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_fragment</t>
+  </si>
+  <si>
+    <t>sg_normalHard_12</t>
+  </si>
+  <si>
+    <t>普通困难12</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_passive</t>
+  </si>
+  <si>
+    <t>sg_normalHard_13</t>
+  </si>
+  <si>
+    <t>普通困难13</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_14</t>
+  </si>
+  <si>
+    <t>普通困难14</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_15</t>
+  </si>
+  <si>
+    <t>普通困难15</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_passive</t>
+  </si>
+  <si>
+    <t>sg_normalHard_16</t>
+  </si>
+  <si>
+    <t>普通困难16</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_17</t>
+  </si>
+  <si>
+    <t>普通困难17</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_18</t>
+  </si>
+  <si>
+    <t>普通困难18</t>
+  </si>
+  <si>
+    <t>act_food_hard_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_19</t>
+  </si>
+  <si>
+    <t>普通困难19</t>
+  </si>
+  <si>
+    <t>act_food_hard_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_20</t>
+  </si>
+  <si>
+    <t>普通困难20</t>
+  </si>
+  <si>
+    <t>act_food_hard_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_21</t>
+  </si>
+  <si>
+    <t>普通困难21</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_fragment,act_food_passive</t>
+  </si>
+  <si>
+    <t>sg_normalHard_22</t>
+  </si>
+  <si>
+    <t>普通困难22</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_fragment,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_23</t>
+  </si>
+  <si>
+    <t>普通困难23</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_fragment,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_24</t>
+  </si>
+  <si>
+    <t>普通困难24</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_25</t>
+  </si>
+  <si>
+    <t>普通困难25</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_26</t>
+  </si>
+  <si>
+    <t>普通困难26</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_27</t>
+  </si>
+  <si>
+    <t>普通困难27</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_hard_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_28</t>
+  </si>
+  <si>
+    <t>普通困难28</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_hard_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_29</t>
+  </si>
+  <si>
+    <t>普通困难29</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_hard_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_30</t>
+  </si>
+  <si>
+    <t>普通困难30</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_food_hard_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_31</t>
+  </si>
+  <si>
+    <t>普通困难31</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_fragment</t>
+  </si>
+  <si>
+    <t>sg_normalHard_32</t>
+  </si>
+  <si>
+    <t>普通困难32</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_passive</t>
+  </si>
+  <si>
+    <t>sg_normalHard_33</t>
+  </si>
+  <si>
+    <t>普通困难33</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_34</t>
+  </si>
+  <si>
+    <t>普通困难34</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_35</t>
+  </si>
+  <si>
+    <t>普通困难35</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_hard_passive</t>
+  </si>
+  <si>
+    <t>sg_normalHard_36</t>
+  </si>
+  <si>
+    <t>普通困难36</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_37</t>
+  </si>
+  <si>
+    <t>普通困难37</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_38</t>
+  </si>
+  <si>
+    <t>普通困难38</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_39</t>
+  </si>
+  <si>
+    <t>普通困难39</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_40</t>
+  </si>
+  <si>
+    <t>普通困难40</t>
+  </si>
+  <si>
+    <t>act_food_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_41</t>
+  </si>
+  <si>
+    <t>普通困难41</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_fragment,act_food_hard_passive</t>
+  </si>
+  <si>
+    <t>sg_normalHard_42</t>
+  </si>
+  <si>
+    <t>普通困难42</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_fragment,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_43</t>
+  </si>
+  <si>
+    <t>普通困难43</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_fragment,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_44</t>
+  </si>
+  <si>
+    <t>普通困难44</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_passive,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_45</t>
+  </si>
+  <si>
+    <t>普通困难45</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_passive,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_46</t>
+  </si>
+  <si>
+    <t>普通困难46</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_47</t>
+  </si>
+  <si>
+    <t>普通困难47</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_passive,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_48</t>
+  </si>
+  <si>
+    <t>普通困难48</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_passive,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_49</t>
+  </si>
+  <si>
+    <t>普通困难49</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_50</t>
+  </si>
+  <si>
+    <t>普通困难50</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_food_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_51</t>
+  </si>
+  <si>
+    <t>普通困难51</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_fragment,act_food_passive</t>
+  </si>
+  <si>
+    <t>sg_normalHard_52</t>
+  </si>
+  <si>
+    <t>普通困难52</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_fragment,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_53</t>
+  </si>
+  <si>
+    <t>普通困难53</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_fragment,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_54</t>
+  </si>
+  <si>
+    <t>普通困难54</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_55</t>
+  </si>
+  <si>
+    <t>普通困难55</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_food_b</t>
+  </si>
+  <si>
+    <t>美食B</t>
+  </si>
+  <si>
+    <t>sg_normalHard_56</t>
+  </si>
+  <si>
+    <t>普通困难56</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_57</t>
+  </si>
+  <si>
+    <t>普通困难57</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_hard_passive,act_food_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_58</t>
+  </si>
+  <si>
+    <t>普通困难58</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_hard_passive,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_food_hard_a</t>
+  </si>
+  <si>
+    <t>硬菜A</t>
+  </si>
+  <si>
+    <t>sg_normalHard_59</t>
+  </si>
+  <si>
+    <t>普通困难59</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_hard_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_60</t>
+  </si>
+  <si>
+    <t>普通困难60</t>
+  </si>
+  <si>
+    <t>act_food_hard_passive,act_food_hard_active,act_food_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_61</t>
+  </si>
+  <si>
+    <t>普通困难61</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_fragment,act_food_hard_passive</t>
+  </si>
+  <si>
+    <t>sg_food_hard_b</t>
+  </si>
+  <si>
+    <t>硬菜B</t>
+  </si>
+  <si>
+    <t>sg_normalHard_62</t>
+  </si>
+  <si>
+    <t>普通困难62</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_fragment,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_63</t>
+  </si>
+  <si>
+    <t>普通困难63</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_fragment,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_64</t>
+  </si>
+  <si>
+    <t>普通困难64</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_passive,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_event</t>
+  </si>
+  <si>
+    <t>事件</t>
+  </si>
+  <si>
+    <t>sg_normalHard_65</t>
+  </si>
+  <si>
+    <t>普通困难65</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_passive,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_66</t>
+  </si>
+  <si>
+    <t>普通困难66</t>
+  </si>
+  <si>
+    <t>act_food_gold,act_food_hard_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_67</t>
+  </si>
+  <si>
+    <t>普通困难67</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_hard_passive,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_reward</t>
+  </si>
+  <si>
+    <t>奖励</t>
+  </si>
+  <si>
+    <t>sg_normalHard_68</t>
+  </si>
+  <si>
+    <t>普通困难68</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_hard_passive,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_69</t>
+  </si>
+  <si>
+    <t>普通困难69</t>
+  </si>
+  <si>
+    <t>act_food_fragment,act_food_hard_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_debug</t>
+  </si>
+  <si>
+    <t>调试商店</t>
+  </si>
+  <si>
+    <t>sg_normalHard_70</t>
+  </si>
+  <si>
+    <t>普通困难70</t>
+  </si>
+  <si>
+    <t>act_food_passive,act_food_hard_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_71</t>
+  </si>
+  <si>
+    <t>普通困难71</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_fragment,act_food_hard_passive</t>
+  </si>
+  <si>
+    <t>sg_normalHard_72</t>
+  </si>
+  <si>
+    <t>普通困难72</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_fragment,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_73</t>
+  </si>
+  <si>
+    <t>普通困难73</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_fragment,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_74</t>
+  </si>
+  <si>
+    <t>普通困难74</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_passive,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_75</t>
+  </si>
+  <si>
+    <t>普通困难75</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_passive,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_76</t>
+  </si>
+  <si>
+    <t>普通困难76</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_77</t>
+  </si>
+  <si>
+    <t>普通困难77</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_passive,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_normalHard_78</t>
+  </si>
+  <si>
+    <t>普通困难78</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_passive,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_79</t>
+  </si>
+  <si>
+    <t>普通困难79</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_normalHard_80</t>
+  </si>
+  <si>
+    <t>普通困难80</t>
+  </si>
+  <si>
+    <t>act_food_hard_passive,act_food_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_hard_1</t>
+  </si>
+  <si>
+    <t>困难1</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_fragment,act_food_hard_passive</t>
+  </si>
+  <si>
+    <t>sg_hard_2</t>
+  </si>
+  <si>
+    <t>困难2</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_fragment,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_hard_3</t>
+  </si>
+  <si>
+    <t>困难3</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_fragment,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_hard_4</t>
+  </si>
+  <si>
+    <t>困难4</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_passive,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_hard_5</t>
+  </si>
+  <si>
+    <t>困难5</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_passive,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_hard_6</t>
+  </si>
+  <si>
+    <t>困难6</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_hard_7</t>
+  </si>
+  <si>
+    <t>困难7</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_hard_passive,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_hard_8</t>
+  </si>
+  <si>
+    <t>困难8</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_hard_passive,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_hard_9</t>
+  </si>
+  <si>
+    <t>困难9</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_hard_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_hard_10</t>
+  </si>
+  <si>
+    <t>困难10</t>
+  </si>
+  <si>
+    <t>act_food_hard_passive,act_food_hard_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_hard_11</t>
+  </si>
+  <si>
+    <t>困难11</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_fragment</t>
+  </si>
+  <si>
+    <t>sg_hard_12</t>
+  </si>
+  <si>
+    <t>困难12</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_passive</t>
+  </si>
+  <si>
+    <t>sg_hard_13</t>
+  </si>
+  <si>
+    <t>困难13</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_hard_14</t>
+  </si>
+  <si>
+    <t>困难14</t>
+  </si>
+  <si>
+    <t>act_food_hard_gold,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_hard_15</t>
+  </si>
+  <si>
+    <t>困难15</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_hard_passive</t>
+  </si>
+  <si>
+    <t>sg_hard_16</t>
+  </si>
+  <si>
+    <t>困难16</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_hard_17</t>
+  </si>
+  <si>
+    <t>困难17</t>
+  </si>
+  <si>
+    <t>act_food_hard_fragment,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_hard_18</t>
+  </si>
+  <si>
+    <t>困难18</t>
+  </si>
+  <si>
+    <t>act_food_hard_passive,act_food_hard_active</t>
+  </si>
+  <si>
+    <t>sg_hard_19</t>
+  </si>
+  <si>
+    <t>困难19</t>
+  </si>
+  <si>
+    <t>act_food_hard_passive,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>sg_hard_20</t>
+  </si>
+  <si>
+    <t>困难20</t>
+  </si>
+  <si>
+    <t>act_food_hard_active,act_food_hard_dish</t>
+  </si>
+  <si>
+    <t>事件1</t>
   </si>
   <si>
     <t>sg_reward_1</t>
-  </si>
-  <si>
-    <t>lg_normalEvent</t>
-  </si>
-  <si>
-    <t>普通事件大组</t>
-  </si>
-  <si>
-    <t>lg_normalHardEvent</t>
-  </si>
-  <si>
-    <t>普通困难事件大组</t>
-  </si>
-  <si>
-    <t>lg_hardEvent</t>
-  </si>
-  <si>
-    <t>困难事件大组</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>actionIds</t>
-  </si>
-  <si>
-    <t>小组ID</t>
-  </si>
-  <si>
-    <t>小组名(调试用)</t>
-  </si>
-  <si>
-    <t>被大组选中的权重</t>
-  </si>
-  <si>
-    <t>小组内固定行动ID列表→action.id</t>
-  </si>
-  <si>
-    <t>sg_normal_1</t>
-  </si>
-  <si>
-    <t>普通1</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_fragment,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normal_2</t>
-  </si>
-  <si>
-    <t>普通2</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_fragment,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalEvent_15</t>
-  </si>
-  <si>
-    <t>sg_normal_3</t>
-  </si>
-  <si>
-    <t>普通3</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_fragment,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHardEvent_1</t>
-  </si>
-  <si>
-    <t>sg_normal_4</t>
-  </si>
-  <si>
-    <t>普通4</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_hardEvent_1</t>
-  </si>
-  <si>
-    <t>sg_normal_5</t>
-  </si>
-  <si>
-    <t>普通5</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normal_6</t>
-  </si>
-  <si>
-    <t>普通6</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normal_7</t>
-  </si>
-  <si>
-    <t>普通7</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normal_8</t>
-  </si>
-  <si>
-    <t>普通8</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normal_9</t>
-  </si>
-  <si>
-    <t>普通9</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normal_10</t>
-  </si>
-  <si>
-    <t>普通10</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_food_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normal_11</t>
-  </si>
-  <si>
-    <t>普通11</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_fragment</t>
-  </si>
-  <si>
-    <t>sg_normal_12</t>
-  </si>
-  <si>
-    <t>普通12</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normal_13</t>
-  </si>
-  <si>
-    <t>普通13</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normal_14</t>
-  </si>
-  <si>
-    <t>普通14</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normal_15</t>
-  </si>
-  <si>
-    <t>普通15</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normal_16</t>
-  </si>
-  <si>
-    <t>普通16</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normal_17</t>
-  </si>
-  <si>
-    <t>普通17</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_dish</t>
-  </si>
-  <si>
-    <t>普通困难混合大组</t>
-  </si>
-  <si>
-    <t>sg_normal_18</t>
-  </si>
-  <si>
-    <t>普通18</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normal_19</t>
-  </si>
-  <si>
-    <t>普通19</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>lg_debug</t>
-  </si>
-  <si>
-    <t>调试大组</t>
-  </si>
-  <si>
-    <t>sg_normal_20</t>
-  </si>
-  <si>
-    <t>普通20</t>
-  </si>
-  <si>
-    <t>act_food_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_1</t>
-  </si>
-  <si>
-    <t>普通困难1</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_fragment,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normalHard_2</t>
-  </si>
-  <si>
-    <t>普通困难2</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_fragment,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_3</t>
-  </si>
-  <si>
-    <t>普通困难3</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_fragment,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_4</t>
-  </si>
-  <si>
-    <t>普通困难4</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_5</t>
-  </si>
-  <si>
-    <t>普通困难5</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_6</t>
-  </si>
-  <si>
-    <t>普通困难6</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_7</t>
-  </si>
-  <si>
-    <t>普通困难7</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_8</t>
-  </si>
-  <si>
-    <t>普通困难8</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_9</t>
-  </si>
-  <si>
-    <t>普通困难9</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_10</t>
-  </si>
-  <si>
-    <t>普通困难10</t>
-  </si>
-  <si>
-    <t>act_food_hard_passive,act_food_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_11</t>
-  </si>
-  <si>
-    <t>普通困难11</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_fragment</t>
-  </si>
-  <si>
-    <t>sg_normalHard_12</t>
-  </si>
-  <si>
-    <t>普通困难12</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normalHard_13</t>
-  </si>
-  <si>
-    <t>普通困难13</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_14</t>
-  </si>
-  <si>
-    <t>普通困难14</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_15</t>
-  </si>
-  <si>
-    <t>普通困难15</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normalHard_16</t>
-  </si>
-  <si>
-    <t>普通困难16</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_17</t>
-  </si>
-  <si>
-    <t>普通困难17</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_18</t>
-  </si>
-  <si>
-    <t>普通困难18</t>
-  </si>
-  <si>
-    <t>act_food_hard_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_19</t>
-  </si>
-  <si>
-    <t>普通困难19</t>
-  </si>
-  <si>
-    <t>act_food_hard_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_20</t>
-  </si>
-  <si>
-    <t>普通困难20</t>
-  </si>
-  <si>
-    <t>act_food_hard_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_21</t>
-  </si>
-  <si>
-    <t>普通困难21</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_fragment,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normalHard_22</t>
-  </si>
-  <si>
-    <t>普通困难22</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_fragment,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_23</t>
-  </si>
-  <si>
-    <t>普通困难23</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_fragment,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_24</t>
-  </si>
-  <si>
-    <t>普通困难24</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_25</t>
-  </si>
-  <si>
-    <t>普通困难25</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_26</t>
-  </si>
-  <si>
-    <t>普通困难26</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_27</t>
-  </si>
-  <si>
-    <t>普通困难27</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_hard_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_28</t>
-  </si>
-  <si>
-    <t>普通困难28</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_hard_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_29</t>
-  </si>
-  <si>
-    <t>普通困难29</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_hard_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_30</t>
-  </si>
-  <si>
-    <t>普通困难30</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_food_hard_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_31</t>
-  </si>
-  <si>
-    <t>普通困难31</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_fragment</t>
-  </si>
-  <si>
-    <t>sg_normalHard_32</t>
-  </si>
-  <si>
-    <t>普通困难32</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_passive</t>
-  </si>
-  <si>
-    <t>sg_normalHard_33</t>
-  </si>
-  <si>
-    <t>普通困难33</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_34</t>
-  </si>
-  <si>
-    <t>普通困难34</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_35</t>
-  </si>
-  <si>
-    <t>普通困难35</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_hard_passive</t>
-  </si>
-  <si>
-    <t>sg_normalHard_36</t>
-  </si>
-  <si>
-    <t>普通困难36</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_37</t>
-  </si>
-  <si>
-    <t>普通困难37</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_38</t>
-  </si>
-  <si>
-    <t>普通困难38</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_39</t>
-  </si>
-  <si>
-    <t>普通困难39</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_40</t>
-  </si>
-  <si>
-    <t>普通困难40</t>
-  </si>
-  <si>
-    <t>act_food_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_41</t>
-  </si>
-  <si>
-    <t>普通困难41</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_fragment,act_food_hard_passive</t>
-  </si>
-  <si>
-    <t>sg_normalHard_42</t>
-  </si>
-  <si>
-    <t>普通困难42</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_fragment,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_43</t>
-  </si>
-  <si>
-    <t>普通困难43</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_fragment,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_44</t>
-  </si>
-  <si>
-    <t>普通困难44</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_passive,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_45</t>
-  </si>
-  <si>
-    <t>普通困难45</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_passive,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_46</t>
-  </si>
-  <si>
-    <t>普通困难46</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_47</t>
-  </si>
-  <si>
-    <t>普通困难47</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_passive,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_48</t>
-  </si>
-  <si>
-    <t>普通困难48</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_passive,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_49</t>
-  </si>
-  <si>
-    <t>普通困难49</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_50</t>
-  </si>
-  <si>
-    <t>普通困难50</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_food_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_51</t>
-  </si>
-  <si>
-    <t>普通困难51</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_fragment,act_food_passive</t>
-  </si>
-  <si>
-    <t>sg_normalHard_52</t>
-  </si>
-  <si>
-    <t>普通困难52</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_fragment,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_53</t>
-  </si>
-  <si>
-    <t>普通困难53</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_fragment,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_54</t>
-  </si>
-  <si>
-    <t>普通困难54</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_55</t>
-  </si>
-  <si>
-    <t>普通困难55</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_food_b</t>
-  </si>
-  <si>
-    <t>美食B</t>
-  </si>
-  <si>
-    <t>sg_normalHard_56</t>
-  </si>
-  <si>
-    <t>普通困难56</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_57</t>
-  </si>
-  <si>
-    <t>普通困难57</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_hard_passive,act_food_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_58</t>
-  </si>
-  <si>
-    <t>普通困难58</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_hard_passive,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_food_hard_a</t>
-  </si>
-  <si>
-    <t>硬菜A</t>
-  </si>
-  <si>
-    <t>sg_normalHard_59</t>
-  </si>
-  <si>
-    <t>普通困难59</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_hard_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_60</t>
-  </si>
-  <si>
-    <t>普通困难60</t>
-  </si>
-  <si>
-    <t>act_food_hard_passive,act_food_hard_active,act_food_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_61</t>
-  </si>
-  <si>
-    <t>普通困难61</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_fragment,act_food_hard_passive</t>
-  </si>
-  <si>
-    <t>sg_food_hard_b</t>
-  </si>
-  <si>
-    <t>硬菜B</t>
-  </si>
-  <si>
-    <t>sg_normalHard_62</t>
-  </si>
-  <si>
-    <t>普通困难62</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_fragment,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_63</t>
-  </si>
-  <si>
-    <t>普通困难63</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_fragment,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_64</t>
-  </si>
-  <si>
-    <t>普通困难64</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_passive,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_event</t>
-  </si>
-  <si>
-    <t>事件</t>
-  </si>
-  <si>
-    <t>sg_normalHard_65</t>
-  </si>
-  <si>
-    <t>普通困难65</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_passive,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_66</t>
-  </si>
-  <si>
-    <t>普通困难66</t>
-  </si>
-  <si>
-    <t>act_food_gold,act_food_hard_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_67</t>
-  </si>
-  <si>
-    <t>普通困难67</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_hard_passive,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_reward</t>
-  </si>
-  <si>
-    <t>奖励</t>
-  </si>
-  <si>
-    <t>sg_normalHard_68</t>
-  </si>
-  <si>
-    <t>普通困难68</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_hard_passive,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_69</t>
-  </si>
-  <si>
-    <t>普通困难69</t>
-  </si>
-  <si>
-    <t>act_food_fragment,act_food_hard_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_debug</t>
-  </si>
-  <si>
-    <t>调试商店</t>
-  </si>
-  <si>
-    <t>sg_normalHard_70</t>
-  </si>
-  <si>
-    <t>普通困难70</t>
-  </si>
-  <si>
-    <t>act_food_passive,act_food_hard_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_71</t>
-  </si>
-  <si>
-    <t>普通困难71</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_fragment,act_food_hard_passive</t>
-  </si>
-  <si>
-    <t>sg_normalHard_72</t>
-  </si>
-  <si>
-    <t>普通困难72</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_fragment,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_73</t>
-  </si>
-  <si>
-    <t>普通困难73</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_fragment,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_74</t>
-  </si>
-  <si>
-    <t>普通困难74</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_passive,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_75</t>
-  </si>
-  <si>
-    <t>普通困难75</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_passive,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_76</t>
-  </si>
-  <si>
-    <t>普通困难76</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_77</t>
-  </si>
-  <si>
-    <t>普通困难77</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_passive,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_normalHard_78</t>
-  </si>
-  <si>
-    <t>普通困难78</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_passive,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_79</t>
-  </si>
-  <si>
-    <t>普通困难79</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_normalHard_80</t>
-  </si>
-  <si>
-    <t>普通困难80</t>
-  </si>
-  <si>
-    <t>act_food_hard_passive,act_food_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_hard_1</t>
-  </si>
-  <si>
-    <t>困难1</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_fragment,act_food_hard_passive</t>
-  </si>
-  <si>
-    <t>sg_hard_2</t>
-  </si>
-  <si>
-    <t>困难2</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_fragment,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_hard_3</t>
-  </si>
-  <si>
-    <t>困难3</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_fragment,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_hard_4</t>
-  </si>
-  <si>
-    <t>困难4</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_passive,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_hard_5</t>
-  </si>
-  <si>
-    <t>困难5</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_passive,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_hard_6</t>
-  </si>
-  <si>
-    <t>困难6</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_hard_7</t>
-  </si>
-  <si>
-    <t>困难7</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_hard_passive,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_hard_8</t>
-  </si>
-  <si>
-    <t>困难8</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_hard_passive,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_hard_9</t>
-  </si>
-  <si>
-    <t>困难9</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_hard_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_hard_10</t>
-  </si>
-  <si>
-    <t>困难10</t>
-  </si>
-  <si>
-    <t>act_food_hard_passive,act_food_hard_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_hard_11</t>
-  </si>
-  <si>
-    <t>困难11</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_fragment</t>
-  </si>
-  <si>
-    <t>sg_hard_12</t>
-  </si>
-  <si>
-    <t>困难12</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_passive</t>
-  </si>
-  <si>
-    <t>sg_hard_13</t>
-  </si>
-  <si>
-    <t>困难13</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_hard_14</t>
-  </si>
-  <si>
-    <t>困难14</t>
-  </si>
-  <si>
-    <t>act_food_hard_gold,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_hard_15</t>
-  </si>
-  <si>
-    <t>困难15</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_hard_passive</t>
-  </si>
-  <si>
-    <t>sg_hard_16</t>
-  </si>
-  <si>
-    <t>困难16</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_hard_17</t>
-  </si>
-  <si>
-    <t>困难17</t>
-  </si>
-  <si>
-    <t>act_food_hard_fragment,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_hard_18</t>
-  </si>
-  <si>
-    <t>困难18</t>
-  </si>
-  <si>
-    <t>act_food_hard_passive,act_food_hard_active</t>
-  </si>
-  <si>
-    <t>sg_hard_19</t>
-  </si>
-  <si>
-    <t>困难19</t>
-  </si>
-  <si>
-    <t>act_food_hard_passive,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>sg_hard_20</t>
-  </si>
-  <si>
-    <t>困难20</t>
-  </si>
-  <si>
-    <t>act_food_hard_active,act_food_hard_dish</t>
-  </si>
-  <si>
-    <t>事件1</t>
   </si>
   <si>
     <t>奖励1</t>
@@ -3221,7 +3218,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
@@ -3333,7 +3330,7 @@
         <v>71</v>
       </c>
       <c r="E5" s="3" t="str">
-        <f t="shared" ref="E5:E12" si="0">_xlfn.TEXTJOIN(",",TRUE,I5:L5)</f>
+        <f>_xlfn.TEXTJOIN(",",TRUE,I5:L5)</f>
         <v>200,200,250,200</v>
       </c>
       <c r="F5" s="4" t="str">
@@ -3341,7 +3338,7 @@
         <v>sg_normalHard_1,sg_normalHard_2,sg_normalHard_3,sg_normalHard_4,sg_normalHard_5,sg_normalHard_6,sg_normalHard_7,sg_normalHard_8,sg_normalHard_9,sg_normalHard_10,sg_normalHard_11,sg_normalHard_12,sg_normalHard_13,sg_normalHard_14,sg_normalHard_15,sg_normalHard_16,sg_normalHard_17,sg_normalHard_18,sg_normalHard_19,sg_normalHard_20,sg_normalHard_21,sg_normalHard_22,sg_normalHard_23,sg_normalHard_24,sg_normalHard_25,sg_normalHard_26,sg_normalHard_27,sg_normalHard_28,sg_normalHard_29,sg_normalHard_30,sg_normalHard_31,sg_normalHard_32,sg_normalHard_33,sg_normalHard_34,sg_normalHard_35,sg_normalHard_36,sg_normalHard_37,sg_normalHard_38,sg_normalHard_39,sg_normalHard_40,sg_normalHard_41,sg_normalHard_42,sg_normalHard_43,sg_normalHard_44,sg_normalHard_45,sg_normalHard_46,sg_normalHard_47,sg_normalHard_48,sg_normalHard_49,sg_normalHard_50,sg_normalHard_51,sg_normalHard_52,sg_normalHard_53,sg_normalHard_54,sg_normalHard_55,sg_normalHard_56,sg_normalHard_57,sg_normalHard_58,sg_normalHard_59,sg_normalHard_60,sg_normalHard_61,sg_normalHard_62,sg_normalHard_63,sg_normalHard_64,sg_normalHard_65,sg_normalHard_66,sg_normalHard_67,sg_normalHard_68,sg_normalHard_69,sg_normalHard_70,sg_normalHard_71,sg_normalHard_72,sg_normalHard_73,sg_normalHard_74,sg_normalHard_75,sg_normalHard_76,sg_normalHard_77,sg_normalHard_78,sg_normalHard_79,sg_normalHard_80</v>
       </c>
       <c r="G5" s="1" t="str">
-        <f t="shared" ref="G5:G12" si="1">""</f>
+        <f>""</f>
         <v/>
       </c>
       <c r="I5" s="1">
@@ -3365,7 +3362,7 @@
         <v>73</v>
       </c>
       <c r="E6" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(",",TRUE,I6:L6)</f>
         <v>0,50,100,200</v>
       </c>
       <c r="F6" s="4" t="str">
@@ -3373,7 +3370,7 @@
         <v>sg_hard_1,sg_hard_2,sg_hard_3,sg_hard_4,sg_hard_5,sg_hard_6,sg_hard_7,sg_hard_8,sg_hard_9,sg_hard_10,sg_hard_11,sg_hard_12,sg_hard_13,sg_hard_14,sg_hard_15,sg_hard_16,sg_hard_17,sg_hard_18,sg_hard_19,sg_hard_20</v>
       </c>
       <c r="G6" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>""</f>
         <v/>
       </c>
       <c r="I6" s="1">
@@ -3400,14 +3397,14 @@
         <v>76</v>
       </c>
       <c r="E7" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(",",TRUE,I7:L7)</f>
         <v>100,100,100,100</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>77</v>
       </c>
       <c r="G7" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>""</f>
         <v/>
       </c>
       <c r="I7" s="1">
@@ -3430,57 +3427,55 @@
       <c r="C8" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="E8" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>50,50,50,50</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>81</v>
+        <f>_xlfn.TEXTJOIN(",",TRUE,I8:L8)</f>
+        <v>150,150,100,100</v>
+      </c>
+      <c r="F8" s="4" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,small_group!B126:B140)</f>
+        <v>sg_normalEvent_1,sg_normalEvent_2,sg_normalEvent_3,sg_normalEvent_4,sg_normalEvent_5,sg_normalEvent_6,sg_normalEvent_7,sg_normalEvent_8,sg_normalEvent_9,sg_normalEvent_10,sg_normalEvent_11,sg_normalEvent_12,sg_normalEvent_13,sg_normalEvent_14,sg_normalEvent_15</v>
       </c>
       <c r="G8" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>""</f>
         <v/>
       </c>
       <c r="I8" s="1">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="J8" s="1">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="K8" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L8" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="2:12">
       <c r="B9" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E9" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>150,150,100,100</v>
+        <f>_xlfn.TEXTJOIN(",",TRUE,I9:L9)</f>
+        <v>100,100,100,100</v>
       </c>
       <c r="F9" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,small_group!B126:B140)</f>
-        <v>sg_normalEvent_1,sg_normalEvent_2,sg_normalEvent_3,sg_normalEvent_4,sg_normalEvent_5,sg_normalEvent_6,sg_normalEvent_7,sg_normalEvent_8,sg_normalEvent_9,sg_normalEvent_10,sg_normalEvent_11,sg_normalEvent_12,sg_normalEvent_13,sg_normalEvent_14,sg_normalEvent_15</v>
+        <f>_xlfn.TEXTJOIN(",",TRUE,small_group!B141:B150)</f>
+        <v>sg_normalHardEvent_1,sg_normalHardEvent_2,sg_normalHardEvent_3,sg_normalHardEvent_4,sg_normalHardEvent_5,sg_normalHardEvent_6,sg_normalHardEvent_7,sg_normalHardEvent_8,sg_normalHardEvent_9,sg_normalHardEvent_10</v>
       </c>
       <c r="G9" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>""</f>
         <v/>
       </c>
       <c r="I9" s="1">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J9" s="1">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -3491,70 +3486,38 @@
     </row>
     <row r="10" spans="2:12">
       <c r="B10" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E10" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>100,100,100,100</v>
+        <f>_xlfn.TEXTJOIN(",",TRUE,I10:L10)</f>
+        <v>0,50,100,100</v>
       </c>
       <c r="F10" s="4" t="str">
-        <f>_xlfn.TEXTJOIN(",",TRUE,small_group!B141:B150)</f>
-        <v>sg_normalHardEvent_1,sg_normalHardEvent_2,sg_normalHardEvent_3,sg_normalHardEvent_4,sg_normalHardEvent_5,sg_normalHardEvent_6,sg_normalHardEvent_7,sg_normalHardEvent_8,sg_normalHardEvent_9,sg_normalHardEvent_10</v>
-      </c>
-      <c r="G10" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I10" s="1">
-        <v>100</v>
-      </c>
-      <c r="J10" s="1">
-        <v>100</v>
-      </c>
-      <c r="K10" s="1">
-        <v>100</v>
-      </c>
-      <c r="L10" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12">
-      <c r="B11" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E11" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>0,50,100,100</v>
-      </c>
-      <c r="F11" s="4" t="str">
         <f>_xlfn.TEXTJOIN(",",TRUE,small_group!B151:B165)</f>
         <v>sg_hardEvent_1,sg_hardEvent_2,sg_hardEvent_3,sg_hardEvent_4,sg_hardEvent_5,sg_hardEvent_6,sg_hardEvent_7,sg_hardEvent_8,sg_hardEvent_9,sg_hardEvent_10,sg_hardEvent_11,sg_hardEvent_12,sg_hardEvent_13,sg_hardEvent_14,sg_hardEvent_15</v>
       </c>
-      <c r="G11" s="1" t="str">
-        <f t="shared" si="1"/>
+      <c r="G10" s="1" t="str">
+        <f>""</f>
         <v/>
       </c>
-      <c r="I11" s="1">
+      <c r="I10" s="1">
         <v>0</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J10" s="1">
         <v>50</v>
       </c>
-      <c r="K11" s="1">
-        <v>100</v>
-      </c>
-      <c r="L11" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="5:5">
-      <c r="E12" s="3"/>
+      <c r="K10" s="1">
+        <v>100</v>
+      </c>
+      <c r="L10" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="5:5">
+      <c r="E11" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3595,10 +3558,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3606,16 +3569,16 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3637,165 +3600,165 @@
     </row>
     <row r="4" spans="2:5">
       <c r="B4" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D4" s="1">
         <v>100</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="2:18">
       <c r="B5" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D5" s="1">
         <v>100</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="2:18">
       <c r="B6" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D6" s="1">
         <v>100</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="2:18">
       <c r="B7" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D7" s="1">
         <v>100</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="B8" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="B11" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D11" s="1">
         <v>100</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="B12" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D12" s="1">
         <v>100</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D13" s="1">
         <v>100</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D14" s="1">
         <v>100</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>68</v>
@@ -3806,16 +3769,16 @@
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D15" s="1">
         <v>100</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>70</v>
@@ -3826,16 +3789,16 @@
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D16" s="1">
         <v>100</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L16" s="1" t="s">
         <v>72</v>
@@ -3846,16 +3809,16 @@
     </row>
     <row r="17" spans="2:13">
       <c r="B17" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D17" s="1">
         <v>100</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="L17" s="1" t="s">
         <v>74</v>
@@ -3866,82 +3829,82 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D18" s="1">
+        <v>100</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M18" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D18" s="1">
-        <v>100</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D19" s="1">
+        <v>100</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D19" s="1">
-        <v>100</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="L19" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D20" s="1">
+        <v>100</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="L20" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="M20" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="D20" s="1">
-        <v>100</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="21" spans="2:20">
       <c r="B21" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D21" s="1">
+        <v>100</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D21" s="1">
-        <v>100</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="L21" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>20</v>
@@ -3955,22 +3918,22 @@
     </row>
     <row r="22" spans="2:20">
       <c r="B22" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D22" s="1">
+        <v>100</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="L22" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D22" s="1">
-        <v>100</v>
-      </c>
-      <c r="E22" s="1" t="s">
+      <c r="M22" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>20</v>
@@ -3984,16 +3947,16 @@
     </row>
     <row r="23" spans="2:20">
       <c r="B23" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D23" s="1">
+        <v>100</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="D23" s="1">
-        <v>100</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="R23" s="1" t="s">
         <v>20</v>
@@ -4007,16 +3970,16 @@
     </row>
     <row r="24" spans="2:20">
       <c r="B24" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D24" s="1">
+        <v>100</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="D24" s="1">
-        <v>100</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="R24" s="1" t="s">
         <v>20</v>
@@ -4030,16 +3993,16 @@
     </row>
     <row r="25" spans="2:20">
       <c r="B25" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D25" s="1">
+        <v>100</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D25" s="1">
-        <v>100</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>165</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>20</v>
@@ -4053,16 +4016,16 @@
     </row>
     <row r="26" spans="2:20">
       <c r="B26" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D26" s="1">
+        <v>100</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D26" s="1">
-        <v>100</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>20</v>
@@ -4076,16 +4039,16 @@
     </row>
     <row r="27" spans="2:20">
       <c r="B27" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D27" s="1">
+        <v>100</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D27" s="1">
-        <v>100</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>171</v>
       </c>
       <c r="R27" s="1" t="s">
         <v>24</v>
@@ -4099,16 +4062,16 @@
     </row>
     <row r="28" spans="2:20">
       <c r="B28" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D28" s="1">
+        <v>100</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D28" s="1">
-        <v>100</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="R28" s="1" t="s">
         <v>24</v>
@@ -4122,16 +4085,16 @@
     </row>
     <row r="29" spans="2:20">
       <c r="B29" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D29" s="1">
+        <v>100</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="D29" s="1">
-        <v>100</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>177</v>
       </c>
       <c r="R29" s="1" t="s">
         <v>24</v>
@@ -4145,16 +4108,16 @@
     </row>
     <row r="30" spans="2:20">
       <c r="B30" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D30" s="1">
+        <v>100</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D30" s="1">
-        <v>100</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="R30" s="1" t="s">
         <v>26</v>
@@ -4168,16 +4131,16 @@
     </row>
     <row r="31" spans="2:19">
       <c r="B31" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D31" s="1">
+        <v>100</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D31" s="1">
-        <v>100</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>183</v>
       </c>
       <c r="R31" s="1" t="s">
         <v>20</v>
@@ -4188,16 +4151,16 @@
     </row>
     <row r="32" spans="2:19">
       <c r="B32" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D32" s="1">
+        <v>100</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="D32" s="1">
-        <v>100</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>186</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>20</v>
@@ -4208,16 +4171,16 @@
     </row>
     <row r="33" spans="2:19">
       <c r="B33" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D33" s="1">
+        <v>100</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D33" s="1">
-        <v>100</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="R33" s="1" t="s">
         <v>20</v>
@@ -4228,16 +4191,16 @@
     </row>
     <row r="34" spans="2:19">
       <c r="B34" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D34" s="1">
+        <v>100</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D34" s="1">
-        <v>100</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>192</v>
       </c>
       <c r="R34" s="1" t="s">
         <v>20</v>
@@ -4248,16 +4211,16 @@
     </row>
     <row r="35" spans="2:19">
       <c r="B35" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D35" s="1">
+        <v>100</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="D35" s="1">
-        <v>100</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>195</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>24</v>
@@ -4268,16 +4231,16 @@
     </row>
     <row r="36" spans="2:19">
       <c r="B36" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D36" s="1">
+        <v>100</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="D36" s="1">
-        <v>100</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="R36" s="1" t="s">
         <v>24</v>
@@ -4288,16 +4251,16 @@
     </row>
     <row r="37" spans="2:19">
       <c r="B37" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D37" s="1">
+        <v>100</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="D37" s="1">
-        <v>100</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>201</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>20</v>
@@ -4311,16 +4274,16 @@
     </row>
     <row r="38" spans="2:19">
       <c r="B38" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D38" s="1">
+        <v>100</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D38" s="1">
-        <v>100</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>24</v>
@@ -4334,16 +4297,16 @@
     </row>
     <row r="39" spans="2:19">
       <c r="B39" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D39" s="1">
+        <v>100</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="D39" s="1">
-        <v>100</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>207</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>26</v>
@@ -4357,16 +4320,16 @@
     </row>
     <row r="40" spans="2:19">
       <c r="B40" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D40" s="1">
+        <v>100</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="D40" s="1">
-        <v>100</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>28</v>
@@ -4380,16 +4343,16 @@
     </row>
     <row r="41" spans="2:12">
       <c r="B41" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D41" s="1">
+        <v>100</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D41" s="1">
-        <v>100</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="L41" s="1" t="s">
         <v>30</v>
@@ -4397,30 +4360,30 @@
     </row>
     <row r="42" spans="2:5">
       <c r="B42" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D42" s="1">
+        <v>100</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="D42" s="1">
-        <v>100</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="43" spans="2:12">
       <c r="B43" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D43" s="1">
+        <v>100</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="D43" s="1">
-        <v>100</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>219</v>
       </c>
       <c r="L43" s="1" t="s">
         <v>32</v>
@@ -4428,16 +4391,16 @@
     </row>
     <row r="44" spans="2:12">
       <c r="B44" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D44" s="1">
+        <v>100</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D44" s="1">
-        <v>100</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>222</v>
       </c>
       <c r="L44" s="1" t="s">
         <v>35</v>
@@ -4445,16 +4408,16 @@
     </row>
     <row r="45" spans="2:12">
       <c r="B45" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D45" s="1">
+        <v>100</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="D45" s="1">
-        <v>100</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>225</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>37</v>
@@ -4462,16 +4425,16 @@
     </row>
     <row r="46" spans="2:12">
       <c r="B46" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D46" s="1">
+        <v>100</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D46" s="1">
-        <v>100</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>228</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>39</v>
@@ -4479,16 +4442,16 @@
     </row>
     <row r="47" spans="2:12">
       <c r="B47" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D47" s="1">
+        <v>100</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="D47" s="1">
-        <v>100</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>231</v>
       </c>
       <c r="L47" s="1" t="s">
         <v>41</v>
@@ -4496,16 +4459,16 @@
     </row>
     <row r="48" spans="2:12">
       <c r="B48" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D48" s="1">
+        <v>100</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="D48" s="1">
-        <v>100</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>234</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>43</v>
@@ -4513,16 +4476,16 @@
     </row>
     <row r="49" spans="2:12">
       <c r="B49" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D49" s="1">
+        <v>100</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="D49" s="1">
-        <v>100</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>237</v>
       </c>
       <c r="L49" s="1" t="s">
         <v>46</v>
@@ -4530,414 +4493,414 @@
     </row>
     <row r="50" spans="2:5">
       <c r="B50" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D50" s="1">
+        <v>100</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="D50" s="1">
-        <v>100</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="51" spans="2:5">
       <c r="B51" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D51" s="1">
+        <v>100</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="D51" s="1">
-        <v>100</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="52" spans="2:5">
       <c r="B52" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D52" s="1">
+        <v>100</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="D52" s="1">
-        <v>100</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="53" spans="2:5">
       <c r="B53" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D53" s="1">
+        <v>100</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="D53" s="1">
-        <v>100</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="54" spans="2:5">
       <c r="B54" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D54" s="1">
+        <v>100</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="D54" s="1">
-        <v>100</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="55" spans="2:5">
       <c r="B55" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D55" s="1">
+        <v>100</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D55" s="1">
-        <v>100</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="56" spans="2:5">
       <c r="B56" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D56" s="1">
+        <v>100</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="D56" s="1">
-        <v>100</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="57" spans="2:5">
       <c r="B57" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D57" s="1">
+        <v>100</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="D57" s="1">
-        <v>100</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="58" spans="2:5">
       <c r="B58" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D58" s="1">
+        <v>100</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="D58" s="1">
-        <v>100</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="59" spans="2:5">
       <c r="B59" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D59" s="1">
+        <v>100</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="D59" s="1">
-        <v>100</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="60" spans="2:5">
       <c r="B60" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D60" s="1">
+        <v>100</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="D60" s="1">
-        <v>100</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="61" spans="2:5">
       <c r="B61" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D61" s="1">
+        <v>100</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="D61" s="1">
-        <v>100</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="62" spans="2:5">
       <c r="B62" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D62" s="1">
+        <v>100</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="D62" s="1">
-        <v>100</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="63" spans="2:5">
       <c r="B63" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="D63" s="1">
+        <v>100</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="D63" s="1">
-        <v>100</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="64" spans="2:5">
       <c r="B64" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D64" s="1">
+        <v>100</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="D64" s="1">
-        <v>100</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="65" spans="2:5">
       <c r="B65" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D65" s="1">
+        <v>100</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D65" s="1">
-        <v>100</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="66" spans="2:5">
       <c r="B66" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D66" s="1">
+        <v>100</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="D66" s="1">
-        <v>100</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="67" spans="2:5">
       <c r="B67" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D67" s="1">
+        <v>100</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="D67" s="1">
-        <v>100</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="68" spans="2:5">
       <c r="B68" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="D68" s="1">
+        <v>100</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>292</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="D68" s="1">
-        <v>100</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="69" spans="2:5">
       <c r="B69" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D69" s="1">
+        <v>100</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="D69" s="1">
-        <v>100</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="70" spans="2:5">
       <c r="B70" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D70" s="1">
+        <v>100</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="D70" s="1">
-        <v>100</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="71" spans="2:5">
       <c r="B71" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D71" s="1">
+        <v>100</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>301</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="D71" s="1">
-        <v>100</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="72" spans="2:5">
       <c r="B72" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D72" s="1">
+        <v>100</v>
+      </c>
+      <c r="E72" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="D72" s="1">
-        <v>100</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="73" spans="2:5">
       <c r="B73" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D73" s="1">
+        <v>100</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="D73" s="1">
-        <v>100</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="74" spans="2:5">
       <c r="B74" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D74" s="1">
+        <v>100</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="D74" s="1">
-        <v>100</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="75" spans="2:5">
       <c r="B75" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D75" s="1">
+        <v>100</v>
+      </c>
+      <c r="E75" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="D75" s="1">
-        <v>100</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="76" spans="2:5">
       <c r="B76" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D76" s="1">
+        <v>100</v>
+      </c>
+      <c r="E76" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="D76" s="1">
-        <v>100</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="77" spans="2:5">
       <c r="B77" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D77" s="1">
+        <v>100</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="D77" s="1">
-        <v>100</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="78" spans="2:20">
       <c r="B78" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D78" s="1">
+        <v>100</v>
+      </c>
+      <c r="E78" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="Q78" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="D78" s="1">
-        <v>100</v>
-      </c>
-      <c r="E78" s="1" t="s">
+      <c r="R78" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="Q78" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="R78" s="1" t="s">
-        <v>326</v>
       </c>
       <c r="S78" s="1">
         <v>80</v>
@@ -4948,16 +4911,16 @@
     </row>
     <row r="79" spans="2:20">
       <c r="B79" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="D79" s="1">
+        <v>100</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="D79" s="1">
-        <v>100</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>329</v>
       </c>
       <c r="T79" s="1" t="s">
         <v>28</v>
@@ -4965,16 +4928,16 @@
     </row>
     <row r="80" spans="2:20">
       <c r="B80" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D80" s="1">
+        <v>100</v>
+      </c>
+      <c r="E80" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="D80" s="1">
-        <v>100</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>332</v>
       </c>
       <c r="T80" s="1" t="s">
         <v>30</v>
@@ -4982,22 +4945,22 @@
     </row>
     <row r="81" spans="2:20">
       <c r="B81" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D81" s="1">
+        <v>100</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="Q81" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="D81" s="1">
-        <v>100</v>
-      </c>
-      <c r="E81" s="1" t="s">
+      <c r="R81" s="1" t="s">
         <v>335</v>
-      </c>
-      <c r="Q81" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="R81" s="1" t="s">
-        <v>337</v>
       </c>
       <c r="S81" s="1">
         <v>100</v>
@@ -5008,16 +4971,16 @@
     </row>
     <row r="82" spans="2:20">
       <c r="B82" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D82" s="1">
+        <v>100</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="D82" s="1">
-        <v>100</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>340</v>
       </c>
       <c r="T82" s="1" t="s">
         <v>41</v>
@@ -5025,16 +4988,16 @@
     </row>
     <row r="83" spans="2:20">
       <c r="B83" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D83" s="1">
+        <v>100</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="D83" s="1">
-        <v>100</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>343</v>
       </c>
       <c r="T83" s="1" t="s">
         <v>37</v>
@@ -5042,22 +5005,22 @@
     </row>
     <row r="84" spans="2:20">
       <c r="B84" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D84" s="1">
+        <v>100</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="Q84" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="D84" s="1">
-        <v>100</v>
-      </c>
-      <c r="E84" s="1" t="s">
+      <c r="R84" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="Q84" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="R84" s="1" t="s">
-        <v>348</v>
       </c>
       <c r="S84" s="1">
         <v>80</v>
@@ -5068,16 +5031,16 @@
     </row>
     <row r="85" spans="2:20">
       <c r="B85" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D85" s="1">
+        <v>100</v>
+      </c>
+      <c r="E85" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="D85" s="1">
-        <v>100</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>351</v>
       </c>
       <c r="T85" s="1" t="s">
         <v>39</v>
@@ -5085,16 +5048,16 @@
     </row>
     <row r="86" spans="2:20">
       <c r="B86" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D86" s="1">
+        <v>100</v>
+      </c>
+      <c r="E86" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="D86" s="1">
-        <v>100</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>354</v>
       </c>
       <c r="T86" s="1" t="s">
         <v>41</v>
@@ -5102,22 +5065,22 @@
     </row>
     <row r="87" spans="2:20">
       <c r="B87" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="D87" s="1">
+        <v>100</v>
+      </c>
+      <c r="E87" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="Q87" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="D87" s="1">
-        <v>100</v>
-      </c>
-      <c r="E87" s="1" t="s">
+      <c r="R87" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="Q87" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="R87" s="1" t="s">
-        <v>359</v>
       </c>
       <c r="S87" s="1">
         <v>100</v>
@@ -5128,16 +5091,16 @@
     </row>
     <row r="88" spans="2:20">
       <c r="B88" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D88" s="1">
+        <v>100</v>
+      </c>
+      <c r="E88" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="D88" s="1">
-        <v>100</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>362</v>
       </c>
       <c r="T88" s="1" t="s">
         <v>20</v>
@@ -5145,16 +5108,16 @@
     </row>
     <row r="89" spans="2:20">
       <c r="B89" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D89" s="1">
+        <v>100</v>
+      </c>
+      <c r="E89" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="D89" s="1">
-        <v>100</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>365</v>
       </c>
       <c r="T89" s="1" t="s">
         <v>30</v>
@@ -5162,22 +5125,22 @@
     </row>
     <row r="90" spans="2:20">
       <c r="B90" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="D90" s="1">
+        <v>100</v>
+      </c>
+      <c r="E90" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="Q90" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="D90" s="1">
-        <v>100</v>
-      </c>
-      <c r="E90" s="1" t="s">
+      <c r="R90" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="Q90" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="R90" s="1" t="s">
-        <v>370</v>
       </c>
       <c r="S90" s="1">
         <v>100</v>
@@ -5188,16 +5151,16 @@
     </row>
     <row r="91" spans="2:20">
       <c r="B91" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D91" s="1">
+        <v>100</v>
+      </c>
+      <c r="E91" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="D91" s="1">
-        <v>100</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="T91" s="1" t="s">
         <v>49</v>
@@ -5205,22 +5168,22 @@
     </row>
     <row r="92" spans="2:20">
       <c r="B92" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D92" s="1">
+        <v>100</v>
+      </c>
+      <c r="E92" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="Q92" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="D92" s="1">
-        <v>100</v>
-      </c>
-      <c r="E92" s="1" t="s">
+      <c r="R92" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="Q92" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="R92" s="1" t="s">
-        <v>378</v>
       </c>
       <c r="S92" s="1">
         <v>100</v>
@@ -5231,436 +5194,436 @@
     </row>
     <row r="93" spans="2:5">
       <c r="B93" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D93" s="1">
+        <v>100</v>
+      </c>
+      <c r="E93" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D93" s="1">
-        <v>100</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="94" spans="2:5">
       <c r="B94" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D94" s="1">
+        <v>100</v>
+      </c>
+      <c r="E94" s="1" t="s">
         <v>382</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D94" s="1">
-        <v>100</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="95" spans="2:5">
       <c r="B95" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D95" s="1">
+        <v>100</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="D95" s="1">
-        <v>100</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="96" spans="2:5">
       <c r="B96" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D96" s="1">
+        <v>100</v>
+      </c>
+      <c r="E96" s="1" t="s">
         <v>388</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="D96" s="1">
-        <v>100</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="97" spans="2:5">
       <c r="B97" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D97" s="1">
+        <v>100</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="D97" s="1">
-        <v>100</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="98" spans="2:5">
       <c r="B98" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="D98" s="1">
+        <v>100</v>
+      </c>
+      <c r="E98" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="D98" s="1">
-        <v>100</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="99" spans="2:5">
       <c r="B99" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="D99" s="1">
+        <v>100</v>
+      </c>
+      <c r="E99" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="D99" s="1">
-        <v>100</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="100" spans="2:5">
       <c r="B100" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="D100" s="1">
+        <v>100</v>
+      </c>
+      <c r="E100" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="D100" s="1">
-        <v>100</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="101" spans="2:5">
       <c r="B101" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="D101" s="1">
+        <v>100</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="D101" s="1">
-        <v>100</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="102" spans="2:5">
       <c r="B102" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="D102" s="1">
+        <v>100</v>
+      </c>
+      <c r="E102" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="D102" s="1">
-        <v>100</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="103" spans="2:5">
       <c r="B103" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D103" s="1">
+        <v>100</v>
+      </c>
+      <c r="E103" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D103" s="1">
-        <v>100</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="104" spans="2:5">
       <c r="B104" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="D104" s="1">
+        <v>100</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>412</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="D104" s="1">
-        <v>100</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="105" spans="2:5">
       <c r="B105" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="D105" s="1">
+        <v>100</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="D105" s="1">
-        <v>100</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="106" spans="2:5">
       <c r="B106" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D106" s="1">
+        <v>100</v>
+      </c>
+      <c r="E106" s="1" t="s">
         <v>418</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="D106" s="1">
-        <v>100</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="107" spans="2:5">
       <c r="B107" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D107" s="1">
+        <v>100</v>
+      </c>
+      <c r="E107" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="D107" s="1">
-        <v>100</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="108" spans="2:5">
       <c r="B108" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="D108" s="1">
+        <v>100</v>
+      </c>
+      <c r="E108" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="D108" s="1">
-        <v>100</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="109" spans="2:5">
       <c r="B109" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="D109" s="1">
+        <v>100</v>
+      </c>
+      <c r="E109" s="1" t="s">
         <v>427</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="D109" s="1">
-        <v>100</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="110" spans="2:5">
       <c r="B110" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="D110" s="1">
+        <v>100</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="D110" s="1">
-        <v>100</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="111" spans="2:5">
       <c r="B111" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="D111" s="1">
+        <v>100</v>
+      </c>
+      <c r="E111" s="1" t="s">
         <v>433</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="D111" s="1">
-        <v>100</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="112" spans="2:5">
       <c r="B112" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D112" s="1">
+        <v>100</v>
+      </c>
+      <c r="E112" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="D112" s="1">
-        <v>100</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="113" spans="2:5">
       <c r="B113" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="D113" s="1">
+        <v>100</v>
+      </c>
+      <c r="E113" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="D113" s="1">
-        <v>100</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="114" spans="2:5">
       <c r="B114" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D114" s="1">
+        <v>100</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D114" s="1">
-        <v>100</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="115" spans="2:5">
       <c r="B115" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="D115" s="1">
+        <v>100</v>
+      </c>
+      <c r="E115" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="D115" s="1">
-        <v>100</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="116" spans="2:5">
       <c r="B116" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="D116" s="1">
+        <v>100</v>
+      </c>
+      <c r="E116" s="1" t="s">
         <v>448</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="D116" s="1">
-        <v>100</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="117" spans="2:5">
       <c r="B117" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="D117" s="1">
+        <v>100</v>
+      </c>
+      <c r="E117" s="1" t="s">
         <v>451</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="D117" s="1">
-        <v>100</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="118" spans="2:5">
       <c r="B118" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="D118" s="1">
+        <v>100</v>
+      </c>
+      <c r="E118" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="D118" s="1">
-        <v>100</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="119" spans="2:5">
       <c r="B119" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="D119" s="1">
+        <v>100</v>
+      </c>
+      <c r="E119" s="1" t="s">
         <v>457</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="D119" s="1">
-        <v>100</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="120" spans="2:5">
       <c r="B120" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="D120" s="1">
+        <v>100</v>
+      </c>
+      <c r="E120" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="D120" s="1">
-        <v>100</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="121" spans="2:5">
       <c r="B121" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="D121" s="1">
+        <v>100</v>
+      </c>
+      <c r="E121" s="1" t="s">
         <v>463</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="D121" s="1">
-        <v>100</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="122" spans="2:5">
       <c r="B122" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="D122" s="1">
+        <v>100</v>
+      </c>
+      <c r="E122" s="1" t="s">
         <v>466</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="D122" s="1">
-        <v>100</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="123" spans="2:5">
       <c r="B123" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="D123" s="1">
+        <v>100</v>
+      </c>
+      <c r="E123" s="1" t="s">
         <v>469</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="D123" s="1">
-        <v>100</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="124" spans="2:5">
@@ -5668,7 +5631,7 @@
         <v>77</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D124" s="1">
         <v>100</v>
@@ -5679,10 +5642,10 @@
     </row>
     <row r="125" spans="2:5">
       <c r="B125" s="1" t="s">
-        <v>81</v>
+        <v>471</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D125" s="1">
         <v>100</v>
@@ -5693,570 +5656,570 @@
     </row>
     <row r="126" spans="2:5">
       <c r="B126" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="C126" s="1" t="s">
+      <c r="D126" s="1">
+        <v>100</v>
+      </c>
+      <c r="E126" s="1" t="s">
         <v>475</v>
-      </c>
-      <c r="D126" s="1">
-        <v>100</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="127" spans="2:5">
       <c r="B127" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C127" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="D127" s="1">
+        <v>100</v>
+      </c>
+      <c r="E127" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="D127" s="1">
-        <v>100</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="128" spans="2:5">
       <c r="B128" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C128" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="C128" s="1" t="s">
+      <c r="D128" s="1">
+        <v>100</v>
+      </c>
+      <c r="E128" s="1" t="s">
         <v>481</v>
-      </c>
-      <c r="D128" s="1">
-        <v>100</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="129" spans="2:5">
       <c r="B129" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C129" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="C129" s="1" t="s">
+      <c r="D129" s="1">
+        <v>100</v>
+      </c>
+      <c r="E129" s="1" t="s">
         <v>484</v>
-      </c>
-      <c r="D129" s="1">
-        <v>100</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="130" spans="2:5">
       <c r="B130" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C130" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="C130" s="1" t="s">
+      <c r="D130" s="1">
+        <v>100</v>
+      </c>
+      <c r="E130" s="1" t="s">
         <v>487</v>
-      </c>
-      <c r="D130" s="1">
-        <v>100</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="131" spans="2:5">
       <c r="B131" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C131" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="C131" s="1" t="s">
+      <c r="D131" s="1">
+        <v>100</v>
+      </c>
+      <c r="E131" s="1" t="s">
         <v>490</v>
-      </c>
-      <c r="D131" s="1">
-        <v>100</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="132" spans="2:5">
       <c r="B132" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C132" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="C132" s="1" t="s">
+      <c r="D132" s="1">
+        <v>100</v>
+      </c>
+      <c r="E132" s="1" t="s">
         <v>493</v>
-      </c>
-      <c r="D132" s="1">
-        <v>100</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="133" spans="2:5">
       <c r="B133" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C133" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="C133" s="1" t="s">
+      <c r="D133" s="1">
+        <v>100</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>496</v>
-      </c>
-      <c r="D133" s="1">
-        <v>100</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="134" spans="2:5">
       <c r="B134" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C134" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="C134" s="1" t="s">
+      <c r="D134" s="1">
+        <v>100</v>
+      </c>
+      <c r="E134" s="1" t="s">
         <v>499</v>
-      </c>
-      <c r="D134" s="1">
-        <v>100</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="135" spans="2:5">
       <c r="B135" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C135" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="C135" s="1" t="s">
+      <c r="D135" s="1">
+        <v>100</v>
+      </c>
+      <c r="E135" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="D135" s="1">
-        <v>100</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="136" spans="2:5">
       <c r="B136" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C136" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="C136" s="1" t="s">
+      <c r="D136" s="1">
+        <v>100</v>
+      </c>
+      <c r="E136" s="1" t="s">
         <v>505</v>
-      </c>
-      <c r="D136" s="1">
-        <v>100</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="137" spans="2:5">
       <c r="B137" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C137" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="C137" s="1" t="s">
+      <c r="D137" s="1">
+        <v>100</v>
+      </c>
+      <c r="E137" s="1" t="s">
         <v>508</v>
-      </c>
-      <c r="D137" s="1">
-        <v>100</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="138" spans="2:5">
       <c r="B138" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="C138" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="C138" s="1" t="s">
+      <c r="D138" s="1">
+        <v>100</v>
+      </c>
+      <c r="E138" s="1" t="s">
         <v>511</v>
-      </c>
-      <c r="D138" s="1">
-        <v>100</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="139" spans="2:5">
       <c r="B139" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C139" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="C139" s="1" t="s">
+      <c r="D139" s="1">
+        <v>100</v>
+      </c>
+      <c r="E139" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="D139" s="1">
-        <v>100</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="140" spans="2:5">
       <c r="B140" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C140" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="D140" s="1">
+        <v>100</v>
+      </c>
+      <c r="E140" s="1" t="s">
         <v>516</v>
-      </c>
-      <c r="D140" s="1">
-        <v>100</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="141" spans="2:5">
       <c r="B141" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C141" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D141" s="1">
+        <v>100</v>
+      </c>
+      <c r="E141" s="1" t="s">
         <v>518</v>
-      </c>
-      <c r="D141" s="1">
-        <v>100</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="142" spans="2:5">
       <c r="B142" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C142" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="C142" s="1" t="s">
+      <c r="D142" s="1">
+        <v>100</v>
+      </c>
+      <c r="E142" s="1" t="s">
         <v>521</v>
-      </c>
-      <c r="D142" s="1">
-        <v>100</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="143" spans="2:5">
       <c r="B143" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="C143" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="C143" s="1" t="s">
+      <c r="D143" s="1">
+        <v>100</v>
+      </c>
+      <c r="E143" s="1" t="s">
         <v>524</v>
-      </c>
-      <c r="D143" s="1">
-        <v>100</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="144" spans="2:5">
       <c r="B144" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="C144" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="C144" s="1" t="s">
+      <c r="D144" s="1">
+        <v>100</v>
+      </c>
+      <c r="E144" s="1" t="s">
         <v>527</v>
-      </c>
-      <c r="D144" s="1">
-        <v>100</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="145" spans="2:5">
       <c r="B145" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C145" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="C145" s="1" t="s">
+      <c r="D145" s="1">
+        <v>100</v>
+      </c>
+      <c r="E145" s="1" t="s">
         <v>530</v>
-      </c>
-      <c r="D145" s="1">
-        <v>100</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="146" spans="2:5">
       <c r="B146" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C146" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="C146" s="1" t="s">
+      <c r="D146" s="1">
+        <v>100</v>
+      </c>
+      <c r="E146" s="1" t="s">
         <v>533</v>
-      </c>
-      <c r="D146" s="1">
-        <v>100</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="147" spans="2:5">
       <c r="B147" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C147" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="C147" s="1" t="s">
+      <c r="D147" s="1">
+        <v>100</v>
+      </c>
+      <c r="E147" s="1" t="s">
         <v>536</v>
-      </c>
-      <c r="D147" s="1">
-        <v>100</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="148" spans="2:5">
       <c r="B148" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C148" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="C148" s="1" t="s">
+      <c r="D148" s="1">
+        <v>100</v>
+      </c>
+      <c r="E148" s="1" t="s">
         <v>539</v>
-      </c>
-      <c r="D148" s="1">
-        <v>100</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="149" spans="2:5">
       <c r="B149" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="C149" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C149" s="1" t="s">
+      <c r="D149" s="1">
+        <v>100</v>
+      </c>
+      <c r="E149" s="1" t="s">
         <v>542</v>
-      </c>
-      <c r="D149" s="1">
-        <v>100</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="150" spans="2:5">
       <c r="B150" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C150" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="C150" s="1" t="s">
+      <c r="D150" s="1">
+        <v>100</v>
+      </c>
+      <c r="E150" s="1" t="s">
         <v>545</v>
-      </c>
-      <c r="D150" s="1">
-        <v>100</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="151" spans="2:5">
       <c r="B151" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C151" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="D151" s="1">
+        <v>100</v>
+      </c>
+      <c r="E151" s="1" t="s">
         <v>547</v>
-      </c>
-      <c r="D151" s="1">
-        <v>100</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="152" spans="2:5">
       <c r="B152" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="C152" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="C152" s="1" t="s">
+      <c r="D152" s="1">
+        <v>100</v>
+      </c>
+      <c r="E152" s="1" t="s">
         <v>550</v>
-      </c>
-      <c r="D152" s="1">
-        <v>100</v>
-      </c>
-      <c r="E152" s="1" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="153" spans="2:5">
       <c r="B153" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C153" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="C153" s="1" t="s">
+      <c r="D153" s="1">
+        <v>100</v>
+      </c>
+      <c r="E153" s="1" t="s">
         <v>553</v>
-      </c>
-      <c r="D153" s="1">
-        <v>100</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="154" spans="2:5">
       <c r="B154" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="C154" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="C154" s="1" t="s">
+      <c r="D154" s="1">
+        <v>100</v>
+      </c>
+      <c r="E154" s="1" t="s">
         <v>556</v>
-      </c>
-      <c r="D154" s="1">
-        <v>100</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="155" spans="2:5">
       <c r="B155" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="C155" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="C155" s="1" t="s">
+      <c r="D155" s="1">
+        <v>100</v>
+      </c>
+      <c r="E155" s="1" t="s">
         <v>559</v>
-      </c>
-      <c r="D155" s="1">
-        <v>100</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="156" spans="2:5">
       <c r="B156" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="C156" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="C156" s="1" t="s">
+      <c r="D156" s="1">
+        <v>100</v>
+      </c>
+      <c r="E156" s="1" t="s">
         <v>562</v>
-      </c>
-      <c r="D156" s="1">
-        <v>100</v>
-      </c>
-      <c r="E156" s="1" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="157" spans="2:5">
       <c r="B157" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="C157" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="C157" s="1" t="s">
+      <c r="D157" s="1">
+        <v>100</v>
+      </c>
+      <c r="E157" s="1" t="s">
         <v>565</v>
-      </c>
-      <c r="D157" s="1">
-        <v>100</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="158" spans="2:5">
       <c r="B158" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="C158" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="C158" s="1" t="s">
+      <c r="D158" s="1">
+        <v>100</v>
+      </c>
+      <c r="E158" s="1" t="s">
         <v>568</v>
-      </c>
-      <c r="D158" s="1">
-        <v>100</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="159" spans="2:5">
       <c r="B159" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="C159" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="C159" s="1" t="s">
+      <c r="D159" s="1">
+        <v>100</v>
+      </c>
+      <c r="E159" s="1" t="s">
         <v>571</v>
-      </c>
-      <c r="D159" s="1">
-        <v>100</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="160" spans="2:5">
       <c r="B160" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="C160" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="C160" s="1" t="s">
+      <c r="D160" s="1">
+        <v>100</v>
+      </c>
+      <c r="E160" s="1" t="s">
         <v>574</v>
-      </c>
-      <c r="D160" s="1">
-        <v>100</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="161" spans="2:5">
       <c r="B161" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="C161" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="C161" s="1" t="s">
+      <c r="D161" s="1">
+        <v>100</v>
+      </c>
+      <c r="E161" s="1" t="s">
         <v>577</v>
-      </c>
-      <c r="D161" s="1">
-        <v>100</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="162" spans="2:5">
       <c r="B162" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="C162" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="C162" s="1" t="s">
+      <c r="D162" s="1">
+        <v>100</v>
+      </c>
+      <c r="E162" s="1" t="s">
         <v>580</v>
-      </c>
-      <c r="D162" s="1">
-        <v>100</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="163" spans="2:5">
       <c r="B163" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="C163" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="C163" s="1" t="s">
+      <c r="D163" s="1">
+        <v>100</v>
+      </c>
+      <c r="E163" s="1" t="s">
         <v>583</v>
-      </c>
-      <c r="D163" s="1">
-        <v>100</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="164" spans="2:5">
       <c r="B164" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="C164" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="C164" s="1" t="s">
+      <c r="D164" s="1">
+        <v>100</v>
+      </c>
+      <c r="E164" s="1" t="s">
         <v>586</v>
-      </c>
-      <c r="D164" s="1">
-        <v>100</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="165" spans="2:5">
       <c r="B165" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="C165" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="C165" s="1" t="s">
+      <c r="D165" s="1">
+        <v>100</v>
+      </c>
+      <c r="E165" s="1" t="s">
         <v>589</v>
-      </c>
-      <c r="D165" s="1">
-        <v>100</v>
-      </c>
-      <c r="E165" s="1" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="166" spans="2:5">
       <c r="B166" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D166" s="1">
         <v>100</v>
@@ -6297,25 +6260,25 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>590</v>
+      </c>
+      <c r="D1" t="s">
         <v>591</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>592</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>593</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>594</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>595</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>596</v>
-      </c>
-      <c r="I1" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6323,28 +6286,28 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>597</v>
+      </c>
+      <c r="C2" t="s">
         <v>598</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>599</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>600</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>601</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>602</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>603</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>604</v>
-      </c>
-      <c r="I2" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -6355,33 +6318,33 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D3" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E3" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F3" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="G3" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H3" t="s">
         <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
+        <v>607</v>
+      </c>
+      <c r="B4" t="s">
         <v>608</v>
-      </c>
-      <c r="B4" t="s">
-        <v>609</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -6399,18 +6362,18 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="I4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B5" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C5">
         <v>95</v>
@@ -6428,15 +6391,15 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="I5" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B6" t="s">
         <v>76</v>
@@ -6457,18 +6420,18 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="I6" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B7" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C7">
         <v>1000</v>
@@ -6486,192 +6449,192 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="I7" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B8" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C8" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D8" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E8" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F8" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G8" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H8" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B9" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C9" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D9" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E9" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F9" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G9" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H9" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B11" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C11" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D11" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E11" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F11" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G11" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H11" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B12" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C12" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D12" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E12" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F12" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G12" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H12" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -2832,7 +2832,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
@@ -2846,7 +2846,7 @@
     <col min="9" max="10" width="21.7692307692308" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2865,14 +2865,29 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>effectType</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>effectValue</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>effectParam</t>
+        </is>
+      </c>
+      <c r="J1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2891,14 +2906,29 @@
       <c r="F2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>即时效果类型</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>即时效果数值</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>即时效果参数</t>
+        </is>
+      </c>
+      <c r="J2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
+      <c r="K2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -2917,14 +2947,29 @@
       <c r="F3" t="s">
         <v>17</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>EffectType</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J3" t="s">
         <v>19</v>
       </c>
-      <c r="H3" t="s">
+      <c r="K3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:11">
       <c r="B4" t="s">
         <v>20</v>
       </c>
@@ -2937,14 +2982,22 @@
       <c r="F4" t="s">
         <v>23</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="J4">
         <v>0.5</v>
       </c>
-      <c r="H4">
+      <c r="K4">
         <v>1.2</v>
       </c>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:11">
       <c r="B5" t="s">
         <v>24</v>
       </c>
@@ -2957,14 +3010,22 @@
       <c r="F5" t="s">
         <v>25</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="J5">
         <v>0.5</v>
       </c>
-      <c r="H5">
+      <c r="K5">
         <v>1.2</v>
       </c>
     </row>
-    <row r="6" spans="2:8">
+    <row r="6" spans="2:11">
       <c r="B6" t="s">
         <v>26</v>
       </c>
@@ -2977,14 +3038,22 @@
       <c r="F6" t="s">
         <v>27</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="J6">
         <v>0.5</v>
       </c>
-      <c r="H6">
+      <c r="K6">
         <v>1.2</v>
       </c>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7" spans="2:11">
       <c r="B7" t="s">
         <v>28</v>
       </c>
@@ -2997,14 +3066,22 @@
       <c r="F7" t="s">
         <v>29</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="J7">
         <v>0.5</v>
       </c>
-      <c r="H7">
+      <c r="K7">
         <v>1.2</v>
       </c>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:11">
       <c r="B8" t="s">
         <v>30</v>
       </c>
@@ -3017,14 +3094,22 @@
       <c r="F8" t="s">
         <v>31</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="J8">
         <v>0.5</v>
       </c>
-      <c r="H8">
+      <c r="K8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="9" spans="2:8">
+    <row r="9" spans="2:11">
       <c r="B9" t="s">
         <v>32</v>
       </c>
@@ -3037,14 +3122,22 @@
       <c r="F9" t="s">
         <v>34</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="J9">
         <v>0.7</v>
       </c>
-      <c r="H9">
+      <c r="K9">
         <v>1.5</v>
       </c>
     </row>
-    <row r="10" spans="2:8">
+    <row r="10" spans="2:11">
       <c r="B10" t="s">
         <v>35</v>
       </c>
@@ -3057,14 +3150,22 @@
       <c r="F10" t="s">
         <v>36</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="J10">
         <v>0.7</v>
       </c>
-      <c r="H10">
+      <c r="K10">
         <v>1.5</v>
       </c>
     </row>
-    <row r="11" spans="2:8">
+    <row r="11" spans="2:11">
       <c r="B11" t="s">
         <v>37</v>
       </c>
@@ -3077,14 +3178,22 @@
       <c r="F11" t="s">
         <v>38</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="J11">
         <v>0.7</v>
       </c>
-      <c r="H11">
+      <c r="K11">
         <v>1.5</v>
       </c>
     </row>
-    <row r="12" spans="2:8">
+    <row r="12" spans="2:11">
       <c r="B12" t="s">
         <v>39</v>
       </c>
@@ -3097,14 +3206,22 @@
       <c r="F12" t="s">
         <v>40</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="J12">
         <v>0.7</v>
       </c>
-      <c r="H12">
+      <c r="K12">
         <v>1.5</v>
       </c>
     </row>
-    <row r="13" spans="2:8">
+    <row r="13" spans="2:11">
       <c r="B13" t="s">
         <v>41</v>
       </c>
@@ -3117,14 +3234,22 @@
       <c r="F13" t="s">
         <v>42</v>
       </c>
-      <c r="G13">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="J13">
         <v>0.7</v>
       </c>
-      <c r="H13">
+      <c r="K13">
         <v>1.5</v>
       </c>
     </row>
-    <row r="14" spans="2:8">
+    <row r="14" spans="2:11">
       <c r="B14" t="s">
         <v>43</v>
       </c>
@@ -3134,14 +3259,22 @@
       <c r="E14" t="s">
         <v>45</v>
       </c>
-      <c r="G14">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="J14">
         <v>0.5</v>
       </c>
-      <c r="H14">
+      <c r="K14">
         <v>1.5</v>
       </c>
     </row>
-    <row r="15" spans="2:8">
+    <row r="15" spans="2:11">
       <c r="B15" t="s">
         <v>46</v>
       </c>
@@ -3151,14 +3284,22 @@
       <c r="E15" t="s">
         <v>48</v>
       </c>
-      <c r="G15">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="J15">
         <v>1</v>
       </c>
-      <c r="H15">
+      <c r="K15">
         <v>1.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8">
+    <row r="16" spans="2:11">
       <c r="B16" t="s">
         <v>49</v>
       </c>
@@ -3168,14 +3309,22 @@
       <c r="E16" t="s">
         <v>51</v>
       </c>
-      <c r="G16">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="2:8">
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11">
       <c r="B17" t="s">
         <v>52</v>
       </c>
@@ -3185,14 +3334,22 @@
       <c r="E17" t="s">
         <v>54</v>
       </c>
-      <c r="G17">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="2:8">
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11">
       <c r="B18" t="s">
         <v>55</v>
       </c>
@@ -3205,10 +3362,80 @@
       <c r="F18" t="s">
         <v>57</v>
       </c>
-      <c r="G18">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H18">
         <v>0</v>
       </c>
-      <c r="H18">
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>act_loan_repay</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>偿还高利贷</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Effect</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>GainGold</t>
+        </is>
+      </c>
+      <c r="H19">
+        <v>-400</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>act_gold_clear</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>月末清算</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Effect</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LoseAllGold</t>
+        </is>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
         <v>0</v>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="action" sheetId="1" r:id="R3351c4b8e13a4531"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="large_group" sheetId="2" r:id="Ra71137e0b86346f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="small_group" sheetId="3" r:id="Rdfd835ba0bff4b86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="action_schedule_rule" sheetId="4" r:id="Rfc6906cc2c384c00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="action" sheetId="1" r:id="R6576080d418f47ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="large_group" sheetId="2" r:id="Ra3439c55a0eb4465"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="small_group" sheetId="3" r:id="R9c6255f543794d35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="action_schedule_rule" sheetId="4" r:id="R503f61ff0cc34f9d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -118,15 +118,9 @@
     <x:t xml:space="preserve">food_passive</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">act_food_active_strengthen_strengthen</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">food_active_strengthen</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">act_food_active_ajust</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">food_active_ajust</x:t>
   </x:si>
   <x:si>
@@ -157,9 +151,6 @@
     <x:t xml:space="preserve">food_hard_active_strengthen</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">act_food_hard_active_ajust</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">food_hard_active_ajust</x:t>
   </x:si>
   <x:si>
@@ -265,12 +256,6 @@
     <x:t xml:space="preserve">包含的小组ID列表→small_group.id</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">list,float</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">list,string</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">lg_normal</x:t>
   </x:si>
   <x:si>
@@ -298,1195 +283,1195 @@
     <x:t xml:space="preserve">事件大组</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">rule_reward_early,rule_reward_mid</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">lg_normalEvent</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通事件大组</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">lg_normalHardEvent</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难事件大组</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">lg_hardEvent</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">困难事件大组</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">weight</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">actionIds</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">小组ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">小组名(调试用)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">被大组选中的权重</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">小组内固定行动ID列表→action.id</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normal_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_fragment|act_food_passive</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normal_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_fragment|act_food_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalEvent_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normal_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_fragment|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHardEvent_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normal_4</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通4</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_passive|act_food_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_hardEvent_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normal_5</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通5</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_passive|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normal_6</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通6</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_active_strengthen|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normal_7</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通7</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_fragment|act_food_passive|act_food_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normal_8</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通8</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_fragment|act_food_passive|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normal_9</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通9</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_fragment|act_food_active_strengthen|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normal_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通10</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_passive|act_food_active_strengthen|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normal_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通11</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_fragment</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normal_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通12</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_passive</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normal_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通13</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normal_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通14</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normal_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通15</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_fragment|act_food_passive</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">lg_reward</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">奖励大组</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normal_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通16</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_fragment|act_food_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normal_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通17</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_fragment|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难混合大组</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normal_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通18</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_passive|act_food_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normal_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通19</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_passive|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">lg_debug</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">调试大组</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normal_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通20</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_active_strengthen|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_fragment|act_food_passive</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_fragment|act_food_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_fragment|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_4</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难4</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_passive|act_food_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_5</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难5</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_passive|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_6</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难6</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_active_strengthen|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_7</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难7</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_fragment|act_food_passive|act_food_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_8</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难8</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_fragment|act_food_passive|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_9</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难9</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_fragment|act_food_active_strengthen|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难10</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_passive|act_food_active_strengthen|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难11</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_fragment</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难12</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_passive</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难13</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难14</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难15</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_fragment|act_food_passive</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难16</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_fragment|act_food_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难17</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_fragment|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难18</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_passive|act_food_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难19</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_passive|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难20</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_active_strengthen|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_21</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难21</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_hard_fragment|act_food_passive</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_22</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难22</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_hard_fragment|act_food_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_23</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难23</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_hard_fragment|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_24</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难24</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_hard_passive|act_food_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_25</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难25</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_hard_passive|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_26</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难26</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_hard_active_strengthen|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_27</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难27</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_fragment|act_food_hard_passive|act_food_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_28</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难28</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_fragment|act_food_hard_passive|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_29</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难29</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_fragment|act_food_hard_active_strengthen|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_30</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难30</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_passive|act_food_hard_active_strengthen|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_31</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难31</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_hard_fragment</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_32</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难32</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_hard_passive</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_33</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难33</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_hard_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_34</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难34</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_35</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难35</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_fragment|act_food_hard_passive</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_36</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难36</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_fragment|act_food_hard_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_37</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难37</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_fragment|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_38</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难38</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_passive|act_food_hard_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_39</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难39</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_passive|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_40</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难40</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_active_strengthen|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_41</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难41</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_fragment|act_food_hard_passive</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_42</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难42</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_fragment|act_food_hard_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_43</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难43</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_fragment|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_44</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难44</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_passive|act_food_hard_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_45</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难45</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_passive|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_46</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难46</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_active_strengthen|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_47</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难47</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_fragment|act_food_passive|act_food_hard_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_48</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难48</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_fragment|act_food_passive|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_49</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难49</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_fragment|act_food_active_strengthen|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_50</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难50</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_passive|act_food_active_strengthen|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_51</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难51</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_fragment|act_food_passive</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_52</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难52</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_fragment|act_food_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_53</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难53</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_fragment|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_54</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难54</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_passive|act_food_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_55</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难55</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_passive|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_food_b</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">美食B</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_56</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难56</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_active_strengthen|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_57</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难57</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_fragment|act_food_hard_passive|act_food_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_58</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难58</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_fragment|act_food_hard_passive|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_food_hard_a</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">硬菜A</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_59</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难59</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_fragment|act_food_hard_active_strengthen|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_60</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难60</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_passive|act_food_hard_active_strengthen|act_food_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_61</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难61</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_hard_fragment|act_food_hard_passive</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_food_hard_b</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">硬菜B</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_62</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难62</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_hard_fragment|act_food_hard_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_63</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难63</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_hard_fragment|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_64</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难64</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_hard_passive|act_food_hard_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_event</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">事件</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_65</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难65</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_hard_passive|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_66</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难66</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_gold|act_food_hard_active_strengthen|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_67</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难67</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_fragment|act_food_hard_passive|act_food_hard_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_reward</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">奖励</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_68</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难68</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_fragment|act_food_hard_passive|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_69</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难69</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_fragment|act_food_hard_active_strengthen|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_debug</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">调试商店</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_70</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难70</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_passive|act_food_hard_active_strengthen|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_71</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难71</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_fragment|act_food_hard_passive</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_72</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难72</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_fragment|act_food_hard_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_73</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难73</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_fragment|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_74</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难74</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_passive|act_food_hard_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_75</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难75</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_passive|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_76</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难76</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_active_strengthen|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_77</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难77</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_fragment|act_food_passive|act_food_hard_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_78</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难78</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_fragment|act_food_passive|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_79</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难79</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_fragment|act_food_active_strengthen|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_normalHard_80</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">普通困难80</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_passive|act_food_active_strengthen|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_hard_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">困难1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_fragment|act_food_hard_passive</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_hard_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">困难2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_fragment|act_food_hard_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_hard_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">困难3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_fragment|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_hard_4</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">困难4</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_passive|act_food_hard_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_hard_5</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">困难5</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_passive|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_hard_6</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">困难6</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_active_strengthen|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_hard_7</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">困难7</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_fragment|act_food_hard_passive|act_food_hard_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_hard_8</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">困难8</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_fragment|act_food_hard_passive|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_hard_9</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">困难9</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_fragment|act_food_hard_active_strengthen|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_hard_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">困难10</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_passive|act_food_hard_active_strengthen|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_hard_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">困难11</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_fragment</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_hard_12</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">困难12</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_passive</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_hard_13</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">困难13</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_hard_14</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">困难14</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_hard_15</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">困难15</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_fragment|act_food_hard_passive</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_hard_16</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">困难16</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_fragment|act_food_hard_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_hard_17</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">困难17</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_fragment|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_hard_18</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">困难18</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_passive|act_food_hard_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_hard_19</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">困难19</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_passive|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">sg_hard_20</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">困难20</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">act_food_hard_active_strengthen|act_food_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">sg_event_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">rule_reward_early,rule_reward_mid</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">lg_normalEvent</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通事件大组</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">lg_normalHardEvent</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难事件大组</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">lg_hardEvent</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">困难事件大组</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">weight</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">actionIds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">小组ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">小组名(调试用)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">被大组选中的权重</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">小组内固定行动ID列表→action.id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normal_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_fragment|act_food_passive</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normal_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_fragment|act_food_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalEvent_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normal_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_fragment|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHardEvent_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normal_4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_passive|act_food_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_hardEvent_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normal_5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_passive|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normal_6</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通6</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_active_strengthen|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normal_7</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通7</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_fragment|act_food_passive|act_food_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normal_8</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通8</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_fragment|act_food_passive|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normal_9</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通9</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_fragment|act_food_active_strengthen|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normal_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通10</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_passive|act_food_active_strengthen|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normal_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通11</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_fragment</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normal_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通12</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_passive</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normal_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通13</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normal_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通14</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normal_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通15</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_fragment|act_food_passive</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">lg_reward</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">奖励大组</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normal_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通16</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_fragment|act_food_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normal_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通17</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_fragment|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难混合大组</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normal_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通18</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_passive|act_food_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normal_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通19</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_passive|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">lg_debug</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">调试大组</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normal_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通20</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_active_strengthen|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_fragment|act_food_passive</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_fragment|act_food_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_fragment|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_passive|act_food_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_passive|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_6</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难6</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_active_strengthen|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_7</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难7</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_fragment|act_food_passive|act_food_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_8</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难8</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_fragment|act_food_passive|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_9</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难9</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_fragment|act_food_active_strengthen|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难10</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_passive|act_food_active_strengthen|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难11</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_fragment</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难12</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_passive</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难13</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难14</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难15</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_fragment|act_food_passive</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难16</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_fragment|act_food_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难17</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_fragment|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难18</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_passive|act_food_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难19</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_passive|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难20</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_active_strengthen|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_21</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难21</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_hard_fragment|act_food_passive</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_22</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难22</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_hard_fragment|act_food_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_23</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难23</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_hard_fragment|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_24</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难24</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_hard_passive|act_food_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_25</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难25</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_hard_passive|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_26</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难26</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_hard_active_strengthen|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_27</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难27</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_fragment|act_food_hard_passive|act_food_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_28</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难28</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_fragment|act_food_hard_passive|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_29</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难29</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_fragment|act_food_hard_active_strengthen|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_30</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难30</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_passive|act_food_hard_active_strengthen|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_31</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难31</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_hard_fragment</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_32</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难32</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_hard_passive</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_33</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难33</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_hard_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_34</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难34</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_35</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难35</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_fragment|act_food_hard_passive</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_36</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难36</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_fragment|act_food_hard_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_37</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难37</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_fragment|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_38</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难38</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_passive|act_food_hard_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_39</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难39</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_passive|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_40</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难40</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_active_strengthen|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_41</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难41</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_fragment|act_food_hard_passive</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_42</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难42</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_fragment|act_food_hard_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_43</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难43</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_fragment|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_44</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难44</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_passive|act_food_hard_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_45</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难45</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_passive|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_46</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难46</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_active_strengthen|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_47</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难47</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_fragment|act_food_passive|act_food_hard_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_48</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难48</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_fragment|act_food_passive|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_49</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难49</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_fragment|act_food_active_strengthen|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_50</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难50</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_passive|act_food_active_strengthen|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_51</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难51</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_fragment|act_food_passive</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_52</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难52</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_fragment|act_food_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_53</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难53</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_fragment|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_54</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难54</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_passive|act_food_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_55</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难55</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_passive|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_food_b</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">美食B</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_56</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难56</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_active_strengthen|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_57</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难57</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_fragment|act_food_hard_passive|act_food_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_58</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难58</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_fragment|act_food_hard_passive|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_food_hard_a</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">硬菜A</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_59</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难59</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_fragment|act_food_hard_active_strengthen|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_60</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难60</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_passive|act_food_hard_active_strengthen|act_food_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_61</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难61</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_hard_fragment|act_food_hard_passive</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_food_hard_b</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">硬菜B</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_62</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难62</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_hard_fragment|act_food_hard_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_63</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难63</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_hard_fragment|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_64</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难64</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_hard_passive|act_food_hard_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_event</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">事件</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_65</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难65</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_hard_passive|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_66</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难66</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_gold|act_food_hard_active_strengthen|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_67</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难67</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_fragment|act_food_hard_passive|act_food_hard_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_reward</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">奖励</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_68</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难68</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_fragment|act_food_hard_passive|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_69</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难69</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_fragment|act_food_hard_active_strengthen|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_debug</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">调试商店</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_70</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难70</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_passive|act_food_hard_active_strengthen|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_71</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难71</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_fragment|act_food_hard_passive</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_72</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难72</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_fragment|act_food_hard_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_73</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难73</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_fragment|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_74</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难74</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_passive|act_food_hard_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_75</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难75</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_passive|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_76</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难76</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_active_strengthen|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_77</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难77</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_fragment|act_food_passive|act_food_hard_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_78</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难78</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_fragment|act_food_passive|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_79</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难79</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_fragment|act_food_active_strengthen|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_normalHard_80</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通困难80</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_passive|act_food_active_strengthen|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_hard_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">困难1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_fragment|act_food_hard_passive</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_hard_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">困难2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_fragment|act_food_hard_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_hard_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">困难3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_fragment|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_hard_4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">困难4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_passive|act_food_hard_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_hard_5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">困难5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_passive|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_hard_6</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">困难6</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_active_strengthen|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_hard_7</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">困难7</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_fragment|act_food_hard_passive|act_food_hard_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_hard_8</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">困难8</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_fragment|act_food_hard_passive|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_hard_9</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">困难9</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_fragment|act_food_hard_active_strengthen|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_hard_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">困难10</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_passive|act_food_hard_active_strengthen|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_hard_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">困难11</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_fragment</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_hard_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">困难12</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_passive</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_hard_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">困难13</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_hard_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">困难14</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_gold|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_hard_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">困难15</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_fragment|act_food_hard_passive</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_hard_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">困难16</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_fragment|act_food_hard_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_hard_17</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">困难17</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_fragment|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_hard_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">困难18</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_passive|act_food_hard_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_hard_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">困难19</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_passive|act_food_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sg_hard_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">困难20</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">act_food_hard_active_strengthen|act_food_hard_active_adjust</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">事件1</x:t>
@@ -2899,8 +2884,8 @@
       </x:c>
     </x:row>
     <x:row r="7" s="4" customFormat="1">
-      <x:c r="B7" s="4" t="s">
-        <x:v>35</x:v>
+      <x:c r="B7" s="4" t="str">
+        <x:v>act_food_active_strengthen</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
         <x:v>28</x:v>
@@ -2909,7 +2894,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="F7" s="4" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G7" s="4" t="str">
         <x:v>None</x:v>
@@ -2926,8 +2911,8 @@
       </x:c>
     </x:row>
     <x:row r="8" s="4" customFormat="1">
-      <x:c r="B8" s="4" t="s">
-        <x:v>37</x:v>
+      <x:c r="B8" s="4" t="str">
+        <x:v>act_food_active_adjust</x:v>
       </x:c>
       <x:c r="C8" s="4" t="s">
         <x:v>28</x:v>
@@ -2936,7 +2921,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="F8" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G8" s="4" t="str">
         <x:v>None</x:v>
@@ -2954,16 +2939,16 @@
     </x:row>
     <x:row r="9">
       <x:c r="B9" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E9" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="F9" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G9" t="str">
         <x:v>None</x:v>
@@ -2981,16 +2966,16 @@
     </x:row>
     <x:row r="10">
       <x:c r="B10" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E10" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="F10" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G10" t="str">
         <x:v>None</x:v>
@@ -3008,16 +2993,16 @@
     </x:row>
     <x:row r="11">
       <x:c r="B11" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E11" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="F11" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G11" t="str">
         <x:v>None</x:v>
@@ -3035,16 +3020,16 @@
     </x:row>
     <x:row r="12" s="4" customFormat="1">
       <x:c r="B12" s="4" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E12" s="4" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="F12" s="4" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G12" s="4" t="str">
         <x:v>None</x:v>
@@ -3061,17 +3046,17 @@
       </x:c>
     </x:row>
     <x:row r="13" s="4" customFormat="1">
-      <x:c r="B13" s="4" t="s">
-        <x:v>48</x:v>
+      <x:c r="B13" s="4" t="str">
+        <x:v>act_food_hard_active_adjust</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E13" s="4" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="F13" s="4" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G13" s="4" t="str">
         <x:v>None</x:v>
@@ -3089,13 +3074,13 @@
     </x:row>
     <x:row r="14">
       <x:c r="B14" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E14" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G14" t="str">
         <x:v>None</x:v>
@@ -3113,13 +3098,13 @@
     </x:row>
     <x:row r="15">
       <x:c r="B15" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E15" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G15" t="str">
         <x:v>None</x:v>
@@ -3137,13 +3122,13 @@
     </x:row>
     <x:row r="16">
       <x:c r="B16" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E16" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G16" t="str">
         <x:v>None</x:v>
@@ -3161,13 +3146,13 @@
     </x:row>
     <x:row r="17">
       <x:c r="B17" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C17" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E17" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G17" t="str">
         <x:v>None</x:v>
@@ -3185,16 +3170,16 @@
     </x:row>
     <x:row r="18">
       <x:c r="B18" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E18" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="F18" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G18" t="str">
         <x:v>None</x:v>
@@ -3212,16 +3197,16 @@
     </x:row>
     <x:row r="19" s="4" customFormat="1">
       <x:c r="A19" s="4" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B19" s="4" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C19" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E19" s="4" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="B19" s="4" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C19" s="4" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E19" s="4" t="s">
-        <x:v>68</x:v>
       </x:c>
       <x:c r="G19" s="4" t="str">
         <x:v>None</x:v>
@@ -3239,16 +3224,16 @@
     </x:row>
     <x:row r="20">
       <x:c r="B20" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C20" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E20" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G20" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="C20" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="E20" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G20" t="s">
-        <x:v>72</x:v>
       </x:c>
       <x:c r="H20">
         <x:v>-400</x:v>
@@ -3262,16 +3247,16 @@
     </x:row>
     <x:row r="21">
       <x:c r="B21" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E21" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G21" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H21">
         <x:v>0</x:v>
@@ -3312,13 +3297,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="2" s="1" customFormat="1">
@@ -3326,19 +3311,19 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s">
+      <x:c r="F2" s="1" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1">
@@ -3354,27 +3339,26 @@
       <x:c r="D3" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F3" s="1" t="s">
-        <x:v>85</x:v>
+      <x:c r="E3" s="1" t="str">
+        <x:v>(list#sep=,),float</x:v>
+      </x:c>
+      <x:c r="F3" s="1" t="str">
+        <x:v>(list#sep=|),string</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="1" customFormat="1">
       <x:c r="B4" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E4" s="2" t="str">
         <x:f t="shared" ref="E4:E10" si="0">_xlfn.TEXTJOIN(",",TRUE,I4:L4)</x:f>
         <x:v>400,300,200,150</x:v>
       </x:c>
-      <x:c r="F4" s="3" t="e">
-        <x:f>_xlfn.TEXTJOIN("|",TRUE,[1]small_group!B4:B23)</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="F4" s="3" t="str">
+        <x:v>sg_normal_1|sg_normal_2|sg_normal_3|sg_normal_4|sg_normal_5|sg_normal_6|sg_normal_7|sg_normal_8|sg_normal_9|sg_normal_10|sg_normal_11|sg_normal_12|sg_normal_13|sg_normal_14|sg_normal_15|sg_normal_16|sg_normal_17|sg_normal_18|sg_normal_19|sg_normal_20</x:v>
       </x:c>
       <x:c r="G4" s="1" t="str">
         <x:f t="shared" ref="G4:G10" si="1">""</x:f>
@@ -3394,18 +3378,17 @@
     </x:row>
     <x:row r="5" s="1" customFormat="1">
       <x:c r="B5" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E5" s="2" t="str">
         <x:f t="shared" si="0"/>
         <x:v>200,200,250,200</x:v>
       </x:c>
-      <x:c r="F5" s="3" t="e">
-        <x:f>_xlfn.TEXTJOIN("|",TRUE,[1]small_group!B24:B103)</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="F5" s="3" t="str">
+        <x:v>sg_normalHard_1|sg_normalHard_2|sg_normalHard_3|sg_normalHard_4|sg_normalHard_5|sg_normalHard_6|sg_normalHard_7|sg_normalHard_8|sg_normalHard_9|sg_normalHard_10|sg_normalHard_11|sg_normalHard_12|sg_normalHard_13|sg_normalHard_14|sg_normalHard_15|sg_normalHard_16|sg_normalHard_17|sg_normalHard_18|sg_normalHard_19|sg_normalHard_20|sg_normalHard_21|sg_normalHard_22|sg_normalHard_23|sg_normalHard_24|sg_normalHard_25|sg_normalHard_26|sg_normalHard_27|sg_normalHard_28|sg_normalHard_29|sg_normalHard_30|sg_normalHard_31|sg_normalHard_32|sg_normalHard_33|sg_normalHard_34|sg_normalHard_35|sg_normalHard_36|sg_normalHard_37|sg_normalHard_38|sg_normalHard_39|sg_normalHard_40|sg_normalHard_41|sg_normalHard_42|sg_normalHard_43|sg_normalHard_44|sg_normalHard_45|sg_normalHard_46|sg_normalHard_47|sg_normalHard_48|sg_normalHard_49|sg_normalHard_50|sg_normalHard_51|sg_normalHard_52|sg_normalHard_53|sg_normalHard_54|sg_normalHard_55|sg_normalHard_56|sg_normalHard_57|sg_normalHard_58|sg_normalHard_59|sg_normalHard_60|sg_normalHard_61|sg_normalHard_62|sg_normalHard_63|sg_normalHard_64|sg_normalHard_65|sg_normalHard_66|sg_normalHard_67|sg_normalHard_68|sg_normalHard_69|sg_normalHard_70|sg_normalHard_71|sg_normalHard_72|sg_normalHard_73|sg_normalHard_74|sg_normalHard_75|sg_normalHard_76|sg_normalHard_77|sg_normalHard_78|sg_normalHard_79|sg_normalHard_80</x:v>
       </x:c>
       <x:c r="G5" s="1" t="str">
         <x:f t="shared" si="1"/>
@@ -3425,18 +3408,17 @@
     </x:row>
     <x:row r="6" s="1" customFormat="1">
       <x:c r="B6" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E6" s="2" t="str">
         <x:f t="shared" si="0"/>
         <x:v>0,50,100,200</x:v>
       </x:c>
-      <x:c r="F6" s="3" t="e">
-        <x:f>_xlfn.TEXTJOIN("|",TRUE,[1]small_group!B104:B123)</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="F6" s="3" t="str">
+        <x:v>sg_hard_1|sg_hard_2|sg_hard_3|sg_hard_4|sg_hard_5|sg_hard_6|sg_hard_7|sg_hard_8|sg_hard_9|sg_hard_10|sg_hard_11|sg_hard_12|sg_hard_13|sg_hard_14|sg_hard_15|sg_hard_16|sg_hard_17|sg_hard_18|sg_hard_19|sg_hard_20</x:v>
       </x:c>
       <x:c r="G6" s="1" t="str">
         <x:f t="shared" si="1"/>
@@ -3454,22 +3436,22 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="O6" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1">
       <x:c r="B7" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E7" s="2" t="str">
         <x:f t="shared" si="0"/>
         <x:v>100,100,100,100</x:v>
       </x:c>
-      <x:c r="F7" s="3" t="s">
-        <x:v>95</x:v>
+      <x:c r="F7" s="3" t="str">
+        <x:v>sg_event_1</x:v>
       </x:c>
       <x:c r="G7" s="1" t="str">
         <x:f t="shared" si="1"/>
@@ -3487,23 +3469,22 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="O7" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="1" customFormat="1">
       <x:c r="B8" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E8" s="2" t="str">
         <x:f t="shared" si="0"/>
         <x:v>150,150,100,100</x:v>
       </x:c>
-      <x:c r="F8" s="3" t="e">
-        <x:f>_xlfn.TEXTJOIN("|",TRUE,[1]small_group!B126:B140)</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="F8" s="3" t="str">
+        <x:v>sg_normalEvent_1|sg_normalEvent_2|sg_normalEvent_3|sg_normalEvent_4|sg_normalEvent_5|sg_normalEvent_6|sg_normalEvent_7|sg_normalEvent_8|sg_normalEvent_9|sg_normalEvent_10|sg_normalEvent_11|sg_normalEvent_12|sg_normalEvent_13|sg_normalEvent_14|sg_normalEvent_15</x:v>
       </x:c>
       <x:c r="G8" s="1" t="str">
         <x:f t="shared" si="1"/>
@@ -3523,18 +3504,17 @@
     </x:row>
     <x:row r="9" s="1" customFormat="1">
       <x:c r="B9" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E9" s="2" t="str">
         <x:f t="shared" si="0"/>
         <x:v>100,100,100,100</x:v>
       </x:c>
-      <x:c r="F9" s="3" t="e">
-        <x:f>_xlfn.TEXTJOIN("|",TRUE,[1]small_group!B141:B150)</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="F9" s="3" t="str">
+        <x:v>sg_normalHardEvent_1|sg_normalHardEvent_2|sg_normalHardEvent_3|sg_normalHardEvent_4|sg_normalHardEvent_5|sg_normalHardEvent_6|sg_normalHardEvent_7|sg_normalHardEvent_8|sg_normalHardEvent_9|sg_normalHardEvent_10</x:v>
       </x:c>
       <x:c r="G9" s="1" t="str">
         <x:f t="shared" si="1"/>
@@ -3554,18 +3534,17 @@
     </x:row>
     <x:row r="10" s="1" customFormat="1">
       <x:c r="B10" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E10" s="2" t="str">
         <x:f t="shared" si="0"/>
         <x:v>0,50,100,100</x:v>
       </x:c>
-      <x:c r="F10" s="3" t="e">
-        <x:f>_xlfn.TEXTJOIN("|",TRUE,[1]small_group!B151:B165)</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="F10" s="3" t="str">
+        <x:v>sg_hardEvent_1|sg_hardEvent_2|sg_hardEvent_3|sg_hardEvent_4|sg_hardEvent_5|sg_hardEvent_6|sg_hardEvent_7|sg_hardEvent_8|sg_hardEvent_9|sg_hardEvent_10|sg_hardEvent_11|sg_hardEvent_12|sg_hardEvent_13|sg_hardEvent_14|sg_hardEvent_15</x:v>
       </x:c>
       <x:c r="G10" s="1" t="str">
         <x:f t="shared" si="1"/>
@@ -3622,10 +3601,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="2" s="1" customFormat="1">
@@ -3633,16 +3612,16 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1">
@@ -3658,317 +3637,317 @@
       <x:c r="D3" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>85</x:v>
+      <x:c r="E3" s="1" t="str">
+        <x:v>(list#sep=|),string</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="1" customFormat="1">
       <x:c r="B4" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1">
       <x:c r="B5" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="R5" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1">
       <x:c r="B6" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="R6" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1">
       <x:c r="B7" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="R7" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="1" customFormat="1">
       <x:c r="B8" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="1" customFormat="1">
       <x:c r="B9" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="1" customFormat="1">
       <x:c r="B10" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="1" customFormat="1">
       <x:c r="B11" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="1" customFormat="1">
       <x:c r="B12" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="1" customFormat="1">
       <x:c r="B13" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="14" s="1" customFormat="1">
       <x:c r="B14" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="L14" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="M14" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="15" s="1" customFormat="1">
       <x:c r="B15" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="L15" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="M15" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="16" s="1" customFormat="1">
       <x:c r="B16" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="L16" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="M16" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="17" s="1" customFormat="1">
       <x:c r="B17" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="L17" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="M17" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="18" s="1" customFormat="1">
       <x:c r="B18" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="L18" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="M18" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="19" s="1" customFormat="1">
       <x:c r="B19" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="L19" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="M19" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="20" s="1" customFormat="1">
       <x:c r="B20" s="1" t="s">
-        <x:v>162</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="L20" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M20" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="21" s="1" customFormat="1">
       <x:c r="B21" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="L21" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="M21" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="R21" s="1" t="s">
         <x:v>27</x:v>
@@ -3982,22 +3961,22 @@
     </x:row>
     <x:row r="22" s="1" customFormat="1">
       <x:c r="B22" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>170</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="L22" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="M22" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="R22" s="1" t="s">
         <x:v>27</x:v>
@@ -4006,21 +3985,21 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="T22" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="23" s="1" customFormat="1">
       <x:c r="B23" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="R23" s="1" t="s">
         <x:v>27</x:v>
@@ -4029,21 +4008,21 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="T23" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="24" s="1" customFormat="1">
       <x:c r="B24" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>181</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="R24" s="1" t="s">
         <x:v>27</x:v>
@@ -4052,21 +4031,21 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="T24" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="25" s="1" customFormat="1">
       <x:c r="B25" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>183</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="R25" s="1" t="s">
         <x:v>27</x:v>
@@ -4075,44 +4054,44 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="T25" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="26" s="1" customFormat="1">
       <x:c r="B26" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>187</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="R26" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="S26" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="T26" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="27" s="1" customFormat="1">
       <x:c r="B27" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>189</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="R27" s="1" t="s">
         <x:v>31</x:v>
@@ -4121,21 +4100,21 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="T27" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="28" s="1" customFormat="1">
       <x:c r="B28" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="R28" s="1" t="s">
         <x:v>31</x:v>
@@ -4144,67 +4123,67 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="T28" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="29" s="1" customFormat="1">
       <x:c r="B29" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>196</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="R29" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="S29" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="T29" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="30" s="1" customFormat="1">
       <x:c r="B30" s="1" t="s">
-        <x:v>197</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>198</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="R30" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="S30" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="T30" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="31" s="1" customFormat="1">
       <x:c r="B31" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="R31" s="1" t="s">
         <x:v>27</x:v>
@@ -4215,16 +4194,16 @@
     </x:row>
     <x:row r="32" s="1" customFormat="1">
       <x:c r="B32" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>204</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="R32" s="1" t="s">
         <x:v>27</x:v>
@@ -4235,56 +4214,56 @@
     </x:row>
     <x:row r="33" s="1" customFormat="1">
       <x:c r="B33" s="1" t="s">
-        <x:v>206</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>207</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>208</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="R33" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="S33" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="34" s="1" customFormat="1">
       <x:c r="B34" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>210</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>211</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="R34" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="S34" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="35" s="1" customFormat="1">
       <x:c r="B35" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>213</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>214</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="R35" s="1" t="s">
         <x:v>31</x:v>
@@ -4295,36 +4274,36 @@
     </x:row>
     <x:row r="36" s="1" customFormat="1">
       <x:c r="B36" s="1" t="s">
-        <x:v>215</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>216</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>217</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="R36" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="S36" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="37" s="1" customFormat="1">
       <x:c r="B37" s="1" t="s">
-        <x:v>218</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>219</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>220</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="L37" s="1" t="s">
         <x:v>27</x:v>
@@ -4333,21 +4312,21 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="S37" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="38" s="1" customFormat="1">
       <x:c r="B38" s="1" t="s">
-        <x:v>221</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>222</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>223</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="L38" s="1" t="s">
         <x:v>31</x:v>
@@ -4356,21 +4335,21 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="S38" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="39" s="1" customFormat="1">
       <x:c r="B39" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>225</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>226</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="L39" s="1" t="s">
         <x:v>33</x:v>
@@ -4379,592 +4358,592 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="S39" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="40" s="1" customFormat="1">
       <x:c r="B40" s="1" t="s">
-        <x:v>227</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>229</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="L40" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="R40" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="S40" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="41" s="1" customFormat="1">
       <x:c r="B41" s="1" t="s">
-        <x:v>230</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>231</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>232</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="L41" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="42" s="1" customFormat="1">
       <x:c r="B42" s="1" t="s">
-        <x:v>233</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>234</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>235</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="43" s="1" customFormat="1">
       <x:c r="B43" s="1" t="s">
-        <x:v>236</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>237</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>238</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="L43" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="44" s="1" customFormat="1">
       <x:c r="B44" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>240</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>241</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="L44" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="45" s="1" customFormat="1">
       <x:c r="B45" s="1" t="s">
-        <x:v>242</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>244</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="L45" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="46" s="1" customFormat="1">
       <x:c r="B46" s="1" t="s">
-        <x:v>245</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="L46" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="47" s="1" customFormat="1">
       <x:c r="B47" s="1" t="s">
-        <x:v>248</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>249</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>250</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="L47" s="1" t="s">
-        <x:v>251</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="48" s="1" customFormat="1">
       <x:c r="B48" s="1" t="s">
-        <x:v>252</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>253</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>254</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="L48" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="49" s="1" customFormat="1">
       <x:c r="B49" s="1" t="s">
-        <x:v>255</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>257</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="L49" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="50" s="1" customFormat="1">
       <x:c r="B50" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>259</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="51" s="1" customFormat="1">
       <x:c r="B51" s="1" t="s">
-        <x:v>261</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="52" s="1" customFormat="1">
       <x:c r="B52" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>265</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="53" s="1" customFormat="1">
       <x:c r="B53" s="1" t="s">
-        <x:v>267</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>268</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>269</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="54" s="1" customFormat="1">
       <x:c r="B54" s="1" t="s">
-        <x:v>270</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>271</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>272</x:v>
+        <x:v>266</x:v>
       </x:c>
     </x:row>
     <x:row r="55" s="1" customFormat="1">
       <x:c r="B55" s="1" t="s">
-        <x:v>273</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>275</x:v>
+        <x:v>269</x:v>
       </x:c>
     </x:row>
     <x:row r="56" s="1" customFormat="1">
       <x:c r="B56" s="1" t="s">
-        <x:v>276</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>277</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>278</x:v>
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="57" s="1" customFormat="1">
       <x:c r="B57" s="1" t="s">
-        <x:v>279</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>280</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D57" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>281</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="58" s="1" customFormat="1">
       <x:c r="B58" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="59" s="1" customFormat="1">
       <x:c r="B59" s="1" t="s">
-        <x:v>285</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>286</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>287</x:v>
+        <x:v>281</x:v>
       </x:c>
     </x:row>
     <x:row r="60" s="1" customFormat="1">
       <x:c r="B60" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>289</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="D60" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>290</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="61" s="1" customFormat="1">
       <x:c r="B61" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D61" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>287</x:v>
       </x:c>
     </x:row>
     <x:row r="62" s="1" customFormat="1">
       <x:c r="B62" s="1" t="s">
-        <x:v>294</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>295</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D62" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>296</x:v>
+        <x:v>290</x:v>
       </x:c>
     </x:row>
     <x:row r="63" s="1" customFormat="1">
       <x:c r="B63" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>298</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D63" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>299</x:v>
+        <x:v>293</x:v>
       </x:c>
     </x:row>
     <x:row r="64" s="1" customFormat="1">
       <x:c r="B64" s="1" t="s">
-        <x:v>300</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>301</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="D64" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>302</x:v>
+        <x:v>296</x:v>
       </x:c>
     </x:row>
     <x:row r="65" s="1" customFormat="1">
       <x:c r="B65" s="1" t="s">
-        <x:v>303</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>304</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="D65" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>305</x:v>
+        <x:v>299</x:v>
       </x:c>
     </x:row>
     <x:row r="66" s="1" customFormat="1">
       <x:c r="B66" s="1" t="s">
-        <x:v>306</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>307</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="D66" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>308</x:v>
+        <x:v>302</x:v>
       </x:c>
     </x:row>
     <x:row r="67" s="1" customFormat="1">
       <x:c r="B67" s="1" t="s">
-        <x:v>309</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>310</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="D67" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>311</x:v>
+        <x:v>305</x:v>
       </x:c>
     </x:row>
     <x:row r="68" s="1" customFormat="1">
       <x:c r="B68" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>313</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="D68" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>314</x:v>
+        <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="69" s="1" customFormat="1">
       <x:c r="B69" s="1" t="s">
-        <x:v>315</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>316</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="D69" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>317</x:v>
+        <x:v>311</x:v>
       </x:c>
     </x:row>
     <x:row r="70" s="1" customFormat="1">
       <x:c r="B70" s="1" t="s">
-        <x:v>318</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="D70" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>314</x:v>
       </x:c>
     </x:row>
     <x:row r="71" s="1" customFormat="1">
       <x:c r="B71" s="1" t="s">
-        <x:v>321</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="D71" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>317</x:v>
       </x:c>
     </x:row>
     <x:row r="72" s="1" customFormat="1">
       <x:c r="B72" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="D72" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>326</x:v>
+        <x:v>320</x:v>
       </x:c>
     </x:row>
     <x:row r="73" s="1" customFormat="1">
       <x:c r="B73" s="1" t="s">
-        <x:v>327</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="D73" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>323</x:v>
       </x:c>
     </x:row>
     <x:row r="74" s="1" customFormat="1">
       <x:c r="B74" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="D74" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>326</x:v>
       </x:c>
     </x:row>
     <x:row r="75" s="1" customFormat="1">
       <x:c r="B75" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="D75" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>329</x:v>
       </x:c>
     </x:row>
     <x:row r="76" s="1" customFormat="1">
       <x:c r="B76" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>337</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="D76" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>332</x:v>
       </x:c>
     </x:row>
     <x:row r="77" s="1" customFormat="1">
       <x:c r="B77" s="1" t="s">
-        <x:v>339</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>340</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="D77" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>341</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="78" s="1" customFormat="1">
       <x:c r="B78" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>343</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="D78" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="Q78" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="R78" s="1" t="s">
-        <x:v>346</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="S78" s="1">
         <x:v>80</x:v>
@@ -4975,196 +4954,196 @@
     </x:row>
     <x:row r="79" s="1" customFormat="1">
       <x:c r="B79" s="1" t="s">
-        <x:v>347</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>348</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="D79" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="T79" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="80" s="1" customFormat="1">
       <x:c r="B80" s="1" t="s">
-        <x:v>350</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="D80" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="T80" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="81" s="1" customFormat="1">
       <x:c r="B81" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="D81" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="Q81" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="R81" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="S81" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="T81" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="82" s="1" customFormat="1">
       <x:c r="B82" s="1" t="s">
-        <x:v>358</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>359</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="D82" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>360</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="T82" s="1" t="s">
-        <x:v>251</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="83" s="1" customFormat="1">
       <x:c r="B83" s="1" t="s">
-        <x:v>361</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>362</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="D83" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>363</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="T83" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="84" s="1" customFormat="1">
       <x:c r="B84" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>365</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="D84" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>366</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="Q84" s="1" t="s">
-        <x:v>367</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="R84" s="1" t="s">
-        <x:v>368</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="S84" s="1">
         <x:v>80</x:v>
       </x:c>
       <x:c r="T84" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="85" s="1" customFormat="1">
       <x:c r="B85" s="1" t="s">
-        <x:v>369</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>370</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D85" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>371</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="T85" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="86" s="1" customFormat="1">
       <x:c r="B86" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>373</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="D86" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>374</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="T86" s="1" t="s">
-        <x:v>251</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="87" s="1" customFormat="1">
       <x:c r="B87" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>376</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="D87" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="Q87" s="1" t="s">
-        <x:v>378</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="R87" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="S87" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="T87" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="88" s="1" customFormat="1">
       <x:c r="B88" s="1" t="s">
-        <x:v>380</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>381</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="D88" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="T88" s="1" t="s">
         <x:v>27</x:v>
@@ -5172,1124 +5151,1124 @@
     </x:row>
     <x:row r="89" s="1" customFormat="1">
       <x:c r="B89" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>384</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="D89" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="T89" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="90" s="1" customFormat="1">
       <x:c r="B90" s="1" t="s">
-        <x:v>386</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>387</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="D90" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>388</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="Q90" s="1" t="s">
-        <x:v>389</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="R90" s="1" t="s">
-        <x:v>390</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="S90" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="T90" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="91" s="1" customFormat="1">
       <x:c r="B91" s="1" t="s">
-        <x:v>391</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>392</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="D91" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="T91" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="92" s="1" customFormat="1">
       <x:c r="B92" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="D92" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="Q92" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="R92" s="1" t="s">
-        <x:v>398</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="S92" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="T92" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="93" s="1" customFormat="1">
       <x:c r="B93" s="1" t="s">
-        <x:v>399</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>400</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="D93" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>395</x:v>
       </x:c>
     </x:row>
     <x:row r="94" s="1" customFormat="1">
       <x:c r="B94" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>403</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="D94" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>398</x:v>
       </x:c>
     </x:row>
     <x:row r="95" s="1" customFormat="1">
       <x:c r="B95" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="D95" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
-        <x:v>407</x:v>
+        <x:v>401</x:v>
       </x:c>
     </x:row>
     <x:row r="96" s="1" customFormat="1">
       <x:c r="B96" s="1" t="s">
-        <x:v>408</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>409</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="D96" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>404</x:v>
       </x:c>
     </x:row>
     <x:row r="97" s="1" customFormat="1">
       <x:c r="B97" s="1" t="s">
-        <x:v>411</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>412</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="D97" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>413</x:v>
+        <x:v>407</x:v>
       </x:c>
     </x:row>
     <x:row r="98" s="1" customFormat="1">
       <x:c r="B98" s="1" t="s">
-        <x:v>414</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>415</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="D98" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>410</x:v>
       </x:c>
     </x:row>
     <x:row r="99" s="1" customFormat="1">
       <x:c r="B99" s="1" t="s">
-        <x:v>417</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="D99" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>413</x:v>
       </x:c>
     </x:row>
     <x:row r="100" s="1" customFormat="1">
       <x:c r="B100" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="D100" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>416</x:v>
       </x:c>
     </x:row>
     <x:row r="101" s="1" customFormat="1">
       <x:c r="B101" s="1" t="s">
-        <x:v>423</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="D101" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>419</x:v>
       </x:c>
     </x:row>
     <x:row r="102" s="1" customFormat="1">
       <x:c r="B102" s="1" t="s">
-        <x:v>426</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="D102" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>422</x:v>
       </x:c>
     </x:row>
     <x:row r="103" s="1" customFormat="1">
       <x:c r="B103" s="1" t="s">
-        <x:v>429</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>430</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="D103" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
-        <x:v>431</x:v>
+        <x:v>425</x:v>
       </x:c>
     </x:row>
     <x:row r="104" s="1" customFormat="1">
       <x:c r="B104" s="1" t="s">
-        <x:v>432</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>433</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="D104" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>434</x:v>
+        <x:v>428</x:v>
       </x:c>
     </x:row>
     <x:row r="105" s="1" customFormat="1">
       <x:c r="B105" s="1" t="s">
-        <x:v>435</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>436</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>437</x:v>
+        <x:v>431</x:v>
       </x:c>
     </x:row>
     <x:row r="106" s="1" customFormat="1">
       <x:c r="B106" s="1" t="s">
-        <x:v>438</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>439</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>440</x:v>
+        <x:v>434</x:v>
       </x:c>
     </x:row>
     <x:row r="107" s="1" customFormat="1">
       <x:c r="B107" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>442</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="D107" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>437</x:v>
       </x:c>
     </x:row>
     <x:row r="108" s="1" customFormat="1">
       <x:c r="B108" s="1" t="s">
-        <x:v>444</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>445</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="D108" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>446</x:v>
+        <x:v>440</x:v>
       </x:c>
     </x:row>
     <x:row r="109" s="1" customFormat="1">
       <x:c r="B109" s="1" t="s">
-        <x:v>447</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>448</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="D109" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>449</x:v>
+        <x:v>443</x:v>
       </x:c>
     </x:row>
     <x:row r="110" s="1" customFormat="1">
       <x:c r="B110" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>451</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="D110" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E110" s="1" t="s">
-        <x:v>452</x:v>
+        <x:v>446</x:v>
       </x:c>
     </x:row>
     <x:row r="111" s="1" customFormat="1">
       <x:c r="B111" s="1" t="s">
-        <x:v>453</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>454</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="D111" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
-        <x:v>455</x:v>
+        <x:v>449</x:v>
       </x:c>
     </x:row>
     <x:row r="112" s="1" customFormat="1">
       <x:c r="B112" s="1" t="s">
-        <x:v>456</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
-        <x:v>457</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="D112" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>452</x:v>
       </x:c>
     </x:row>
     <x:row r="113" s="1" customFormat="1">
       <x:c r="B113" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="D113" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E113" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>455</x:v>
       </x:c>
     </x:row>
     <x:row r="114" s="1" customFormat="1">
       <x:c r="B114" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="C114" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="D114" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E114" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>458</x:v>
       </x:c>
     </x:row>
     <x:row r="115" s="1" customFormat="1">
       <x:c r="B115" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="C115" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D115" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E115" s="1" t="s">
-        <x:v>467</x:v>
+        <x:v>461</x:v>
       </x:c>
     </x:row>
     <x:row r="116" s="1" customFormat="1">
       <x:c r="B116" s="1" t="s">
-        <x:v>468</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="C116" s="1" t="s">
-        <x:v>469</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="D116" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E116" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>464</x:v>
       </x:c>
     </x:row>
     <x:row r="117" s="1" customFormat="1">
       <x:c r="B117" s="1" t="s">
-        <x:v>471</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="C117" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="D117" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E117" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>467</x:v>
       </x:c>
     </x:row>
     <x:row r="118" s="1" customFormat="1">
       <x:c r="B118" s="1" t="s">
-        <x:v>474</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="C118" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="D118" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E118" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="119" s="1" customFormat="1">
       <x:c r="B119" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="C119" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="D119" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E119" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>473</x:v>
       </x:c>
     </x:row>
     <x:row r="120" s="1" customFormat="1">
       <x:c r="B120" s="1" t="s">
-        <x:v>480</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="C120" s="1" t="s">
-        <x:v>481</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="D120" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E120" s="1" t="s">
-        <x:v>482</x:v>
+        <x:v>476</x:v>
       </x:c>
     </x:row>
     <x:row r="121" s="1" customFormat="1">
       <x:c r="B121" s="1" t="s">
-        <x:v>483</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C121" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="D121" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E121" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>479</x:v>
       </x:c>
     </x:row>
     <x:row r="122" s="1" customFormat="1">
       <x:c r="B122" s="1" t="s">
-        <x:v>486</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="C122" s="1" t="s">
-        <x:v>487</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="D122" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E122" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>482</x:v>
       </x:c>
     </x:row>
     <x:row r="123" s="1" customFormat="1">
       <x:c r="B123" s="1" t="s">
-        <x:v>489</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="C123" s="1" t="s">
-        <x:v>490</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="D123" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E123" s="1" t="s">
-        <x:v>491</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="124" s="1" customFormat="1">
       <x:c r="B124" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="C124" s="1" t="s">
-        <x:v>492</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="D124" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E124" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="125" s="1" customFormat="1">
       <x:c r="B125" s="1" t="s">
-        <x:v>493</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="C125" s="1" t="s">
-        <x:v>494</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="D125" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E125" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="126" s="1" customFormat="1">
       <x:c r="B126" s="1" t="s">
-        <x:v>495</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="C126" s="1" t="s">
-        <x:v>496</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="D126" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E126" s="1" t="s">
-        <x:v>497</x:v>
+        <x:v>492</x:v>
       </x:c>
     </x:row>
     <x:row r="127" s="1" customFormat="1">
       <x:c r="B127" s="1" t="s">
-        <x:v>498</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="C127" s="1" t="s">
-        <x:v>499</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="D127" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E127" s="1" t="s">
-        <x:v>500</x:v>
+        <x:v>495</x:v>
       </x:c>
     </x:row>
     <x:row r="128" s="1" customFormat="1">
       <x:c r="B128" s="1" t="s">
-        <x:v>501</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="C128" s="1" t="s">
-        <x:v>502</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="D128" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E128" s="1" t="s">
-        <x:v>503</x:v>
+        <x:v>498</x:v>
       </x:c>
     </x:row>
     <x:row r="129" s="1" customFormat="1">
       <x:c r="B129" s="1" t="s">
-        <x:v>504</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="C129" s="1" t="s">
-        <x:v>505</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="D129" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E129" s="1" t="s">
-        <x:v>506</x:v>
+        <x:v>501</x:v>
       </x:c>
     </x:row>
     <x:row r="130" s="1" customFormat="1">
       <x:c r="B130" s="1" t="s">
-        <x:v>507</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="C130" s="1" t="s">
-        <x:v>508</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="D130" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E130" s="1" t="s">
-        <x:v>509</x:v>
+        <x:v>504</x:v>
       </x:c>
     </x:row>
     <x:row r="131" s="1" customFormat="1">
       <x:c r="B131" s="1" t="s">
-        <x:v>510</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="C131" s="1" t="s">
-        <x:v>511</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="D131" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E131" s="1" t="s">
-        <x:v>512</x:v>
+        <x:v>507</x:v>
       </x:c>
     </x:row>
     <x:row r="132" s="1" customFormat="1">
       <x:c r="B132" s="1" t="s">
-        <x:v>513</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="C132" s="1" t="s">
-        <x:v>514</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="D132" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E132" s="1" t="s">
-        <x:v>515</x:v>
+        <x:v>510</x:v>
       </x:c>
     </x:row>
     <x:row r="133" s="1" customFormat="1">
       <x:c r="B133" s="1" t="s">
-        <x:v>516</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="C133" s="1" t="s">
-        <x:v>517</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="D133" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E133" s="1" t="s">
-        <x:v>518</x:v>
+        <x:v>513</x:v>
       </x:c>
     </x:row>
     <x:row r="134" s="1" customFormat="1">
       <x:c r="B134" s="1" t="s">
-        <x:v>519</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="C134" s="1" t="s">
-        <x:v>520</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="D134" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E134" s="1" t="s">
-        <x:v>521</x:v>
+        <x:v>516</x:v>
       </x:c>
     </x:row>
     <x:row r="135" s="1" customFormat="1">
       <x:c r="B135" s="1" t="s">
-        <x:v>522</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="C135" s="1" t="s">
-        <x:v>523</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="D135" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E135" s="1" t="s">
-        <x:v>524</x:v>
+        <x:v>519</x:v>
       </x:c>
     </x:row>
     <x:row r="136" s="1" customFormat="1">
       <x:c r="B136" s="1" t="s">
-        <x:v>525</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C136" s="1" t="s">
-        <x:v>526</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="D136" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E136" s="1" t="s">
-        <x:v>527</x:v>
+        <x:v>522</x:v>
       </x:c>
     </x:row>
     <x:row r="137" s="1" customFormat="1">
       <x:c r="B137" s="1" t="s">
-        <x:v>528</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="C137" s="1" t="s">
-        <x:v>529</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="D137" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E137" s="1" t="s">
-        <x:v>530</x:v>
+        <x:v>525</x:v>
       </x:c>
     </x:row>
     <x:row r="138" s="1" customFormat="1">
       <x:c r="B138" s="1" t="s">
-        <x:v>531</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="C138" s="1" t="s">
-        <x:v>532</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="D138" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E138" s="1" t="s">
-        <x:v>533</x:v>
+        <x:v>528</x:v>
       </x:c>
     </x:row>
     <x:row r="139" s="1" customFormat="1">
       <x:c r="B139" s="1" t="s">
-        <x:v>534</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="C139" s="1" t="s">
-        <x:v>535</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="D139" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E139" s="1" t="s">
-        <x:v>536</x:v>
+        <x:v>531</x:v>
       </x:c>
     </x:row>
     <x:row r="140" s="1" customFormat="1">
       <x:c r="B140" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C140" s="1" t="s">
-        <x:v>537</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="D140" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E140" s="1" t="s">
-        <x:v>538</x:v>
+        <x:v>533</x:v>
       </x:c>
     </x:row>
     <x:row r="141" s="1" customFormat="1">
       <x:c r="B141" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C141" s="1" t="s">
-        <x:v>539</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="D141" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E141" s="1" t="s">
-        <x:v>540</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="142" s="1" customFormat="1">
       <x:c r="B142" s="1" t="s">
-        <x:v>541</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="C142" s="1" t="s">
-        <x:v>542</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="D142" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E142" s="1" t="s">
-        <x:v>543</x:v>
+        <x:v>538</x:v>
       </x:c>
     </x:row>
     <x:row r="143" s="1" customFormat="1">
       <x:c r="B143" s="1" t="s">
-        <x:v>544</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="C143" s="1" t="s">
-        <x:v>545</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="D143" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E143" s="1" t="s">
-        <x:v>546</x:v>
+        <x:v>541</x:v>
       </x:c>
     </x:row>
     <x:row r="144" s="1" customFormat="1">
       <x:c r="B144" s="1" t="s">
-        <x:v>547</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="C144" s="1" t="s">
-        <x:v>548</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="D144" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E144" s="1" t="s">
-        <x:v>549</x:v>
+        <x:v>544</x:v>
       </x:c>
     </x:row>
     <x:row r="145" s="1" customFormat="1">
       <x:c r="B145" s="1" t="s">
-        <x:v>550</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="C145" s="1" t="s">
-        <x:v>551</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="D145" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E145" s="1" t="s">
-        <x:v>552</x:v>
+        <x:v>547</x:v>
       </x:c>
     </x:row>
     <x:row r="146" s="1" customFormat="1">
       <x:c r="B146" s="1" t="s">
-        <x:v>553</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="C146" s="1" t="s">
-        <x:v>554</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="D146" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E146" s="1" t="s">
-        <x:v>555</x:v>
+        <x:v>550</x:v>
       </x:c>
     </x:row>
     <x:row r="147" s="1" customFormat="1">
       <x:c r="B147" s="1" t="s">
-        <x:v>556</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="C147" s="1" t="s">
-        <x:v>557</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="D147" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E147" s="1" t="s">
-        <x:v>558</x:v>
+        <x:v>553</x:v>
       </x:c>
     </x:row>
     <x:row r="148" s="1" customFormat="1">
       <x:c r="B148" s="1" t="s">
-        <x:v>559</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="C148" s="1" t="s">
-        <x:v>560</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="D148" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E148" s="1" t="s">
-        <x:v>561</x:v>
+        <x:v>556</x:v>
       </x:c>
     </x:row>
     <x:row r="149" s="1" customFormat="1">
       <x:c r="B149" s="1" t="s">
-        <x:v>562</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="C149" s="1" t="s">
-        <x:v>563</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="D149" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E149" s="1" t="s">
-        <x:v>564</x:v>
+        <x:v>559</x:v>
       </x:c>
     </x:row>
     <x:row r="150" s="1" customFormat="1">
       <x:c r="B150" s="1" t="s">
-        <x:v>565</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="C150" s="1" t="s">
-        <x:v>566</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="D150" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E150" s="1" t="s">
-        <x:v>567</x:v>
+        <x:v>562</x:v>
       </x:c>
     </x:row>
     <x:row r="151" s="1" customFormat="1">
       <x:c r="B151" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C151" s="1" t="s">
-        <x:v>568</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="D151" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E151" s="1" t="s">
-        <x:v>569</x:v>
+        <x:v>564</x:v>
       </x:c>
     </x:row>
     <x:row r="152" s="1" customFormat="1">
       <x:c r="B152" s="1" t="s">
-        <x:v>570</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="C152" s="1" t="s">
-        <x:v>571</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="D152" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E152" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>567</x:v>
       </x:c>
     </x:row>
     <x:row r="153" s="1" customFormat="1">
       <x:c r="B153" s="1" t="s">
-        <x:v>573</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="C153" s="1" t="s">
-        <x:v>574</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="D153" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E153" s="1" t="s">
-        <x:v>575</x:v>
+        <x:v>570</x:v>
       </x:c>
     </x:row>
     <x:row r="154" s="1" customFormat="1">
       <x:c r="B154" s="1" t="s">
-        <x:v>576</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="C154" s="1" t="s">
-        <x:v>577</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="D154" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E154" s="1" t="s">
-        <x:v>578</x:v>
+        <x:v>573</x:v>
       </x:c>
     </x:row>
     <x:row r="155" s="1" customFormat="1">
       <x:c r="B155" s="1" t="s">
-        <x:v>579</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="C155" s="1" t="s">
-        <x:v>580</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="D155" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E155" s="1" t="s">
-        <x:v>581</x:v>
+        <x:v>576</x:v>
       </x:c>
     </x:row>
     <x:row r="156" s="1" customFormat="1">
       <x:c r="B156" s="1" t="s">
-        <x:v>582</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="C156" s="1" t="s">
-        <x:v>583</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="D156" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E156" s="1" t="s">
-        <x:v>584</x:v>
+        <x:v>579</x:v>
       </x:c>
     </x:row>
     <x:row r="157" s="1" customFormat="1">
       <x:c r="B157" s="1" t="s">
-        <x:v>585</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="C157" s="1" t="s">
-        <x:v>586</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="D157" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E157" s="1" t="s">
-        <x:v>587</x:v>
+        <x:v>582</x:v>
       </x:c>
     </x:row>
     <x:row r="158" s="1" customFormat="1">
       <x:c r="B158" s="1" t="s">
-        <x:v>588</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="C158" s="1" t="s">
-        <x:v>589</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="D158" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E158" s="1" t="s">
-        <x:v>590</x:v>
+        <x:v>585</x:v>
       </x:c>
     </x:row>
     <x:row r="159" s="1" customFormat="1">
       <x:c r="B159" s="1" t="s">
-        <x:v>591</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="C159" s="1" t="s">
-        <x:v>592</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="D159" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E159" s="1" t="s">
-        <x:v>593</x:v>
+        <x:v>588</x:v>
       </x:c>
     </x:row>
     <x:row r="160" s="1" customFormat="1">
       <x:c r="B160" s="1" t="s">
-        <x:v>594</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="C160" s="1" t="s">
-        <x:v>595</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="D160" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E160" s="1" t="s">
-        <x:v>596</x:v>
+        <x:v>591</x:v>
       </x:c>
     </x:row>
     <x:row r="161" s="1" customFormat="1">
       <x:c r="B161" s="1" t="s">
-        <x:v>597</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="C161" s="1" t="s">
-        <x:v>598</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="D161" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E161" s="1" t="s">
-        <x:v>599</x:v>
+        <x:v>594</x:v>
       </x:c>
     </x:row>
     <x:row r="162" s="1" customFormat="1">
       <x:c r="B162" s="1" t="s">
-        <x:v>600</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="C162" s="1" t="s">
-        <x:v>601</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="D162" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E162" s="1" t="s">
-        <x:v>602</x:v>
+        <x:v>597</x:v>
       </x:c>
     </x:row>
     <x:row r="163" s="1" customFormat="1">
       <x:c r="B163" s="1" t="s">
-        <x:v>603</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="C163" s="1" t="s">
-        <x:v>604</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="D163" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E163" s="1" t="s">
-        <x:v>605</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="164" s="1" customFormat="1">
       <x:c r="B164" s="1" t="s">
-        <x:v>606</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="C164" s="1" t="s">
-        <x:v>607</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="D164" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E164" s="1" t="s">
-        <x:v>608</x:v>
+        <x:v>603</x:v>
       </x:c>
     </x:row>
     <x:row r="165" s="1" customFormat="1">
       <x:c r="B165" s="1" t="s">
-        <x:v>609</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="C165" s="1" t="s">
-        <x:v>610</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="D165" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E165" s="1" t="s">
-        <x:v>611</x:v>
+        <x:v>606</x:v>
       </x:c>
     </x:row>
     <x:row r="166" s="1" customFormat="1">
       <x:c r="B166" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="C166" s="1" t="s">
-        <x:v>398</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="D166" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E166" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6318,22 +6297,22 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C1" t="s">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="D1" t="s">
+        <x:v>608</x:v>
+      </x:c>
+      <x:c r="E1" t="s">
+        <x:v>609</x:v>
+      </x:c>
+      <x:c r="F1" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="G1" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="H1" t="s">
         <x:v>612</x:v>
-      </x:c>
-      <x:c r="D1" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="E1" t="s">
-        <x:v>614</x:v>
-      </x:c>
-      <x:c r="F1" t="s">
-        <x:v>615</x:v>
-      </x:c>
-      <x:c r="G1" t="s">
-        <x:v>616</x:v>
-      </x:c>
-      <x:c r="H1" t="s">
-        <x:v>617</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -6341,25 +6320,25 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B2" t="s">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="C2" t="s">
+        <x:v>614</x:v>
+      </x:c>
+      <x:c r="D2" t="s">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="E2" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="F2" t="s">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="G2" t="s">
         <x:v>618</x:v>
       </x:c>
-      <x:c r="C2" t="s">
+      <x:c r="H2" t="s">
         <x:v>619</x:v>
-      </x:c>
-      <x:c r="D2" t="s">
-        <x:v>620</x:v>
-      </x:c>
-      <x:c r="E2" t="s">
-        <x:v>621</x:v>
-      </x:c>
-      <x:c r="F2" t="s">
-        <x:v>622</x:v>
-      </x:c>
-      <x:c r="G2" t="s">
-        <x:v>623</x:v>
-      </x:c>
-      <x:c r="H2" t="s">
-        <x:v>624</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -6370,19 +6349,19 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C3" t="s">
-        <x:v>625</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="D3" t="s">
-        <x:v>625</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="E3" t="s">
-        <x:v>625</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="F3" t="s">
-        <x:v>625</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="G3" t="s">
-        <x:v>625</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="H3" t="s">
         <x:v>23</x:v>
@@ -6390,10 +6369,10 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B4" t="s">
-        <x:v>626</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="C4">
         <x:v>100</x:v>
@@ -6413,10 +6392,10 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>627</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="C5">
         <x:v>95</x:v>
@@ -6436,10 +6415,10 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>92</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C6">
         <x:v>80</x:v>
@@ -6459,10 +6438,10 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>628</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="C7">
         <x:v>1000</x:v>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -3516,8 +3516,10 @@
       <c r="H17">
         <v>0</v>
       </c>
-      <c r="I17" t="s">
-        <v>32</v>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ev_interest</t>
+        </is>
       </c>
       <c r="J17">
         <v>0</v>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15280"/>
+    <workbookView windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="action" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="641">
   <si>
     <t>##var</t>
   </si>
@@ -190,6 +190,9 @@
     <t>幸运事件</t>
   </si>
   <si>
+    <t>幸运的未知事件</t>
+  </si>
+  <si>
     <t>Reward</t>
   </si>
   <si>
@@ -199,6 +202,10 @@
     <t>商店采购</t>
   </si>
   <si>
+    <t>摆满了
+琳琅满目的食物与道具</t>
+  </si>
+  <si>
     <t>Shop</t>
   </si>
   <si>
@@ -208,9 +215,16 @@
     <t>收取利息</t>
   </si>
   <si>
+    <t>满5金币收获1金币
+最多收获30金币</t>
+  </si>
+  <si>
     <t>Interest</t>
   </si>
   <si>
+    <t>ev_interest</t>
+  </si>
+  <si>
     <t>act_boss</t>
   </si>
   <si>
@@ -229,6 +243,9 @@
     <t>抽奖机</t>
   </si>
   <si>
+    <t>一定能中大奖</t>
+  </si>
+  <si>
     <t>Slot</t>
   </si>
   <si>
@@ -238,6 +255,9 @@
     <t>偿还高利贷</t>
   </si>
   <si>
+    <t>扣除400金币</t>
+  </si>
+  <si>
     <t>Effect</t>
   </si>
   <si>
@@ -248,6 +268,9 @@
   </si>
   <si>
     <t>月末清算</t>
+  </si>
+  <si>
+    <t>扣除所有金币</t>
   </si>
   <si>
     <t>LoseAllGold</t>
@@ -2510,7 +2533,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2521,7 +2544,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3016,206 +3047,207 @@
   <dimension ref="A1:K21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
-    <col min="2" max="2" width="25.3076923076923" customWidth="1"/>
-    <col min="3" max="3" width="37.1538461538462" customWidth="1"/>
-    <col min="4" max="4" width="34.5384615384615" customWidth="1"/>
-    <col min="5" max="5" width="24.7692307692308" customWidth="1"/>
-    <col min="6" max="6" width="35.6923076923077" customWidth="1"/>
-    <col min="7" max="7" width="25.6153846153846" customWidth="1"/>
-    <col min="8" max="8" width="23.2307692307692" customWidth="1"/>
-    <col min="9" max="10" width="21.7692307692308" customWidth="1"/>
+    <col min="1" max="1" width="13.0769230769231" style="5" customWidth="1"/>
+    <col min="2" max="2" width="25.3076923076923" style="5" customWidth="1"/>
+    <col min="3" max="3" width="37.1538461538462" style="5" customWidth="1"/>
+    <col min="4" max="4" width="34.5384615384615" style="5" customWidth="1"/>
+    <col min="5" max="5" width="24.7692307692308" style="5" customWidth="1"/>
+    <col min="6" max="6" width="35.6923076923077" style="5" customWidth="1"/>
+    <col min="7" max="7" width="25.6153846153846" style="5" customWidth="1"/>
+    <col min="8" max="8" width="23.2307692307692" style="5" customWidth="1"/>
+    <col min="9" max="10" width="21.7692307692308" style="5" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" t="s">
+      <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="5" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" t="s">
+      <c r="A3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="2:11">
-      <c r="B4" t="s">
+      <c r="B4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="5">
         <v>0</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="5">
         <v>0.7</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="5">
         <v>1.2</v>
       </c>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" t="s">
+      <c r="B5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="5">
         <v>0</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="5">
         <v>0.7</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="5">
         <v>1.2</v>
       </c>
     </row>
     <row r="6" spans="2:11">
-      <c r="B6" t="s">
+      <c r="B6" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="5">
         <v>0</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="5">
         <v>0.7</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="5">
         <v>1.2</v>
       </c>
     </row>
@@ -3238,13 +3270,13 @@
       <c r="H7" s="4">
         <v>0</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="5">
         <v>0.7</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="5">
         <v>1.2</v>
       </c>
     </row>
@@ -3267,100 +3299,100 @@
       <c r="H8" s="4">
         <v>0</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="5">
         <v>0.7</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="5">
         <v>1.2</v>
       </c>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" t="s">
+      <c r="B9" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="5">
         <v>0</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="5">
         <v>0.8</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="5">
         <v>1.3</v>
       </c>
     </row>
     <row r="10" spans="2:11">
-      <c r="B10" t="s">
+      <c r="B10" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="5">
         <v>0</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="5">
         <v>0.8</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="5">
         <v>1.3</v>
       </c>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" t="s">
+      <c r="B11" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="5">
         <v>0</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="5">
         <v>0.8</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="5">
         <v>1.3</v>
       </c>
     </row>
@@ -3383,13 +3415,13 @@
       <c r="H12" s="4">
         <v>0</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="5">
         <v>0.8</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="5">
         <v>1.3</v>
       </c>
     </row>
@@ -3412,163 +3444,173 @@
       <c r="H13" s="4">
         <v>0</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="5">
         <v>0.8</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="5">
         <v>1.3</v>
       </c>
     </row>
     <row r="14" spans="2:11">
-      <c r="B14" t="s">
+      <c r="B14" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="5">
         <v>0</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="5">
         <v>0.8</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="5">
         <v>1.3</v>
       </c>
     </row>
     <row r="15" spans="2:11">
-      <c r="B15" t="s">
+      <c r="B15" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E15" t="s">
+      <c r="D15" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G15" t="s">
+      <c r="E15" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="5">
         <v>0</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="5">
         <v>0</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:11">
-      <c r="B16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" t="s">
+    <row r="16" ht="34" spans="2:11">
+      <c r="B16" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E16" t="s">
+      <c r="C16" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="G16" t="s">
+      <c r="D16" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="5">
         <v>0</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="5">
         <v>0</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:11">
-      <c r="B17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" t="s">
+    <row r="17" ht="34" spans="2:11">
+      <c r="B17" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G17" t="s">
+      <c r="C17" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="5">
         <v>0</v>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>ev_interest</t>
-        </is>
-      </c>
-      <c r="J17">
+      <c r="I17" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J17" s="5">
         <v>0</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:11">
-      <c r="B18" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" t="s">
-        <v>65</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="B18" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F18" t="s">
-        <v>66</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="F18" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="5">
         <v>0</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="5">
         <v>0</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="19" s="4" customFormat="1" spans="1:11">
       <c r="A19" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>31</v>
@@ -3576,59 +3618,65 @@
       <c r="H19" s="4">
         <v>0</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="5">
         <v>0</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:11">
-      <c r="B20" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" t="s">
-        <v>72</v>
-      </c>
-      <c r="E20" t="s">
-        <v>73</v>
-      </c>
-      <c r="G20" t="s">
-        <v>74</v>
-      </c>
-      <c r="H20">
+      <c r="B20" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H20" s="5">
         <v>-400</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="5">
         <v>0</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="2:11">
-      <c r="B21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" t="s">
-        <v>73</v>
-      </c>
-      <c r="G21" t="s">
-        <v>77</v>
-      </c>
-      <c r="H21">
+      <c r="B21" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H21" s="5">
         <v>0</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="5">
         <v>0</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="5">
         <v>0</v>
       </c>
     </row>
@@ -3664,13 +3712,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:6">
@@ -3678,19 +3726,19 @@
         <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:6">
@@ -3707,25 +3755,25 @@
         <v>23</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="2:12">
       <c r="B4" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E4" s="2" t="str">
         <f t="shared" ref="E4:E10" si="0">_xlfn.TEXTJOIN(",",TRUE,I4:L4)</f>
         <v>400,300,200,150</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G4" s="1" t="str">
         <f t="shared" ref="G4:G10" si="1">""</f>
@@ -3746,17 +3794,17 @@
     </row>
     <row r="5" s="1" customFormat="1" spans="2:12">
       <c r="B5" s="1" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E5" s="2" t="str">
         <f t="shared" si="0"/>
         <v>200,200,250,200</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G5" s="1" t="str">
         <f t="shared" si="1"/>
@@ -3777,17 +3825,17 @@
     </row>
     <row r="6" s="1" customFormat="1" spans="2:15">
       <c r="B6" s="1" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E6" s="2" t="str">
         <f t="shared" si="0"/>
         <v>0,50,100,200</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="G6" s="1" t="str">
         <f t="shared" si="1"/>
@@ -3806,22 +3854,22 @@
         <v>200</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="2:15">
       <c r="B7" s="1" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E7" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100,100,100,100</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="G7" s="1" t="str">
         <f t="shared" si="1"/>
@@ -3840,22 +3888,22 @@
         <v>100</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="2:12">
       <c r="B8" s="1" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="E8" s="2" t="str">
         <f t="shared" si="0"/>
         <v>150,150,100,100</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G8" s="1" t="str">
         <f t="shared" si="1"/>
@@ -3876,17 +3924,17 @@
     </row>
     <row r="9" s="1" customFormat="1" spans="2:12">
       <c r="B9" s="1" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E9" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100,100,100,100</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="G9" s="1" t="str">
         <f t="shared" si="1"/>
@@ -3907,17 +3955,17 @@
     </row>
     <row r="10" s="1" customFormat="1" spans="2:12">
       <c r="B10" s="1" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="E10" s="2" t="str">
         <f t="shared" si="0"/>
         <v>0,50,100,100</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G10" s="1" t="str">
         <f t="shared" si="1"/>
@@ -3978,10 +4026,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:5">
@@ -3989,16 +4037,16 @@
         <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:5">
@@ -4015,316 +4063,316 @@
         <v>26</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="2:5">
       <c r="B4" s="1" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D4" s="1">
         <v>100</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="2:18">
       <c r="B5" s="1" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D5" s="1">
         <v>100</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="2:18">
       <c r="B6" s="1" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D6" s="1">
         <v>100</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="2:18">
       <c r="B7" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D7" s="1">
         <v>100</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="2:5">
       <c r="B8" s="1" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="2:5">
       <c r="B9" s="1" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="2:5">
       <c r="B10" s="1" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="2:5">
       <c r="B11" s="1" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D11" s="1">
         <v>100</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="2:5">
       <c r="B12" s="1" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="D12" s="1">
         <v>100</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="2:5">
       <c r="B13" s="1" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="D13" s="1">
         <v>100</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="2:13">
       <c r="B14" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="D14" s="1">
         <v>100</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="2:13">
       <c r="B15" s="1" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D15" s="1">
         <v>100</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="2:13">
       <c r="B16" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="D16" s="1">
         <v>100</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="2:13">
       <c r="B17" s="1" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D17" s="1">
         <v>100</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="2:13">
       <c r="B18" s="1" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D18" s="1">
         <v>100</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="2:13">
       <c r="B19" s="1" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D19" s="1">
         <v>100</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="2:13">
       <c r="B20" s="1" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="D20" s="1">
         <v>100</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="2:20">
       <c r="B21" s="1" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="D21" s="1">
         <v>100</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>27</v>
@@ -4338,22 +4386,22 @@
     </row>
     <row r="22" s="1" customFormat="1" spans="2:20">
       <c r="B22" s="1" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="D22" s="1">
         <v>100</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>27</v>
@@ -4367,16 +4415,16 @@
     </row>
     <row r="23" s="1" customFormat="1" spans="2:20">
       <c r="B23" s="1" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="D23" s="1">
         <v>100</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="R23" s="1" t="s">
         <v>27</v>
@@ -4390,16 +4438,16 @@
     </row>
     <row r="24" s="1" customFormat="1" spans="2:20">
       <c r="B24" s="1" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D24" s="1">
         <v>100</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="R24" s="1" t="s">
         <v>27</v>
@@ -4413,16 +4461,16 @@
     </row>
     <row r="25" s="1" customFormat="1" spans="2:20">
       <c r="B25" s="1" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="D25" s="1">
         <v>100</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>27</v>
@@ -4436,16 +4484,16 @@
     </row>
     <row r="26" s="1" customFormat="1" spans="2:20">
       <c r="B26" s="1" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D26" s="1">
         <v>100</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>27</v>
@@ -4459,16 +4507,16 @@
     </row>
     <row r="27" s="1" customFormat="1" spans="2:20">
       <c r="B27" s="1" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="D27" s="1">
         <v>100</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="R27" s="1" t="s">
         <v>33</v>
@@ -4482,16 +4530,16 @@
     </row>
     <row r="28" s="1" customFormat="1" spans="2:20">
       <c r="B28" s="1" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D28" s="1">
         <v>100</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="R28" s="1" t="s">
         <v>33</v>
@@ -4505,16 +4553,16 @@
     </row>
     <row r="29" s="1" customFormat="1" spans="2:20">
       <c r="B29" s="1" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="D29" s="1">
         <v>100</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="R29" s="1" t="s">
         <v>33</v>
@@ -4528,16 +4576,16 @@
     </row>
     <row r="30" s="1" customFormat="1" spans="2:20">
       <c r="B30" s="1" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="D30" s="1">
         <v>100</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="R30" s="1" t="s">
         <v>35</v>
@@ -4551,16 +4599,16 @@
     </row>
     <row r="31" s="1" customFormat="1" spans="2:19">
       <c r="B31" s="1" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="D31" s="1">
         <v>100</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="R31" s="1" t="s">
         <v>27</v>
@@ -4571,16 +4619,16 @@
     </row>
     <row r="32" s="1" customFormat="1" spans="2:19">
       <c r="B32" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D32" s="1">
         <v>100</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>27</v>
@@ -4591,16 +4639,16 @@
     </row>
     <row r="33" s="1" customFormat="1" spans="2:19">
       <c r="B33" s="1" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="D33" s="1">
         <v>100</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="R33" s="1" t="s">
         <v>27</v>
@@ -4611,16 +4659,16 @@
     </row>
     <row r="34" s="1" customFormat="1" spans="2:19">
       <c r="B34" s="1" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="D34" s="1">
         <v>100</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="R34" s="1" t="s">
         <v>27</v>
@@ -4631,16 +4679,16 @@
     </row>
     <row r="35" s="1" customFormat="1" spans="2:19">
       <c r="B35" s="1" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="D35" s="1">
         <v>100</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>33</v>
@@ -4651,16 +4699,16 @@
     </row>
     <row r="36" s="1" customFormat="1" spans="2:19">
       <c r="B36" s="1" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="D36" s="1">
         <v>100</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="R36" s="1" t="s">
         <v>33</v>
@@ -4671,16 +4719,16 @@
     </row>
     <row r="37" s="1" customFormat="1" spans="2:19">
       <c r="B37" s="1" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="D37" s="1">
         <v>100</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>27</v>
@@ -4694,16 +4742,16 @@
     </row>
     <row r="38" s="1" customFormat="1" spans="2:19">
       <c r="B38" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="D38" s="1">
         <v>100</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>33</v>
@@ -4717,16 +4765,16 @@
     </row>
     <row r="39" s="1" customFormat="1" spans="2:19">
       <c r="B39" s="1" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="D39" s="1">
         <v>100</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>35</v>
@@ -4740,16 +4788,16 @@
     </row>
     <row r="40" s="1" customFormat="1" spans="2:19">
       <c r="B40" s="1" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D40" s="1">
         <v>100</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>37</v>
@@ -4763,16 +4811,16 @@
     </row>
     <row r="41" s="1" customFormat="1" spans="2:12">
       <c r="B41" s="1" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="D41" s="1">
         <v>100</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="L41" s="1" t="s">
         <v>39</v>
@@ -4780,30 +4828,30 @@
     </row>
     <row r="42" s="1" customFormat="1" spans="2:5">
       <c r="B42" s="1" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="D42" s="1">
         <v>100</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" spans="2:12">
       <c r="B43" s="1" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="D43" s="1">
         <v>100</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="L43" s="1" t="s">
         <v>41</v>
@@ -4811,16 +4859,16 @@
     </row>
     <row r="44" s="1" customFormat="1" spans="2:12">
       <c r="B44" s="1" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="D44" s="1">
         <v>100</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="L44" s="1" t="s">
         <v>44</v>
@@ -4828,16 +4876,16 @@
     </row>
     <row r="45" s="1" customFormat="1" spans="2:12">
       <c r="B45" s="1" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="D45" s="1">
         <v>100</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>46</v>
@@ -4845,16 +4893,16 @@
     </row>
     <row r="46" s="1" customFormat="1" spans="2:12">
       <c r="B46" s="1" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="D46" s="1">
         <v>100</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>48</v>
@@ -4862,16 +4910,16 @@
     </row>
     <row r="47" s="1" customFormat="1" spans="2:12">
       <c r="B47" s="1" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="D47" s="1">
         <v>100</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L47" s="1" t="s">
         <v>50</v>
@@ -4879,16 +4927,16 @@
     </row>
     <row r="48" s="1" customFormat="1" spans="2:12">
       <c r="B48" s="1" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="D48" s="1">
         <v>100</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>52</v>
@@ -4896,16 +4944,16 @@
     </row>
     <row r="49" s="1" customFormat="1" spans="2:12">
       <c r="B49" s="1" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="D49" s="1">
         <v>100</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="L49" s="1" t="s">
         <v>55</v>
@@ -4913,414 +4961,414 @@
     </row>
     <row r="50" s="1" customFormat="1" spans="2:5">
       <c r="B50" s="1" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="D50" s="1">
         <v>100</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" spans="2:5">
       <c r="B51" s="1" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="D51" s="1">
         <v>100</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" spans="2:5">
       <c r="B52" s="1" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="D52" s="1">
         <v>100</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" spans="2:5">
       <c r="B53" s="1" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="D53" s="1">
         <v>100</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" spans="2:5">
       <c r="B54" s="1" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="D54" s="1">
         <v>100</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" spans="2:5">
       <c r="B55" s="1" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="D55" s="1">
         <v>100</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" spans="2:5">
       <c r="B56" s="1" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="D56" s="1">
         <v>100</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" spans="2:5">
       <c r="B57" s="1" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="D57" s="1">
         <v>100</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" spans="2:5">
       <c r="B58" s="1" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="D58" s="1">
         <v>100</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" spans="2:5">
       <c r="B59" s="1" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="D59" s="1">
         <v>100</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" spans="2:5">
       <c r="B60" s="1" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="D60" s="1">
         <v>100</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" spans="2:5">
       <c r="B61" s="1" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="D61" s="1">
         <v>100</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" spans="2:5">
       <c r="B62" s="1" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="D62" s="1">
         <v>100</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" spans="2:5">
       <c r="B63" s="1" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="D63" s="1">
         <v>100</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
     </row>
     <row r="64" s="1" customFormat="1" spans="2:5">
       <c r="B64" s="1" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="D64" s="1">
         <v>100</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
     </row>
     <row r="65" s="1" customFormat="1" spans="2:5">
       <c r="B65" s="1" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="D65" s="1">
         <v>100</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
     </row>
     <row r="66" s="1" customFormat="1" spans="2:5">
       <c r="B66" s="1" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="D66" s="1">
         <v>100</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
     </row>
     <row r="67" s="1" customFormat="1" spans="2:5">
       <c r="B67" s="1" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="D67" s="1">
         <v>100</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
     </row>
     <row r="68" s="1" customFormat="1" spans="2:5">
       <c r="B68" s="1" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="D68" s="1">
         <v>100</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
     </row>
     <row r="69" s="1" customFormat="1" spans="2:5">
       <c r="B69" s="1" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="D69" s="1">
         <v>100</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="70" s="1" customFormat="1" spans="2:5">
       <c r="B70" s="1" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="D70" s="1">
         <v>100</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
     </row>
     <row r="71" s="1" customFormat="1" spans="2:5">
       <c r="B71" s="1" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="D71" s="1">
         <v>100</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" s="1" customFormat="1" spans="2:5">
       <c r="B72" s="1" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="D72" s="1">
         <v>100</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" spans="2:5">
       <c r="B73" s="1" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="D73" s="1">
         <v>100</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="1" spans="2:5">
       <c r="B74" s="1" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="D74" s="1">
         <v>100</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="1" spans="2:5">
       <c r="B75" s="1" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="D75" s="1">
         <v>100</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
     </row>
     <row r="76" s="1" customFormat="1" spans="2:5">
       <c r="B76" s="1" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="D76" s="1">
         <v>100</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" spans="2:5">
       <c r="B77" s="1" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="D77" s="1">
         <v>100</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
     </row>
     <row r="78" s="1" customFormat="1" spans="2:20">
       <c r="B78" s="1" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="D78" s="1">
         <v>100</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="R78" s="1" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="S78" s="1">
         <v>80</v>
@@ -5331,16 +5379,16 @@
     </row>
     <row r="79" s="1" customFormat="1" spans="2:20">
       <c r="B79" s="1" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="D79" s="1">
         <v>100</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="T79" s="1" t="s">
         <v>37</v>
@@ -5348,16 +5396,16 @@
     </row>
     <row r="80" s="1" customFormat="1" spans="2:20">
       <c r="B80" s="1" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="D80" s="1">
         <v>100</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="T80" s="1" t="s">
         <v>39</v>
@@ -5365,22 +5413,22 @@
     </row>
     <row r="81" s="1" customFormat="1" spans="2:20">
       <c r="B81" s="1" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="D81" s="1">
         <v>100</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="Q81" s="1" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="R81" s="1" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="S81" s="1">
         <v>100</v>
@@ -5391,16 +5439,16 @@
     </row>
     <row r="82" s="1" customFormat="1" spans="2:20">
       <c r="B82" s="1" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="D82" s="1">
         <v>100</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="T82" s="1" t="s">
         <v>50</v>
@@ -5408,16 +5456,16 @@
     </row>
     <row r="83" s="1" customFormat="1" spans="2:20">
       <c r="B83" s="1" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="D83" s="1">
         <v>100</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="T83" s="1" t="s">
         <v>46</v>
@@ -5425,22 +5473,22 @@
     </row>
     <row r="84" s="1" customFormat="1" spans="2:20">
       <c r="B84" s="1" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="D84" s="1">
         <v>100</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="Q84" s="1" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="R84" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="S84" s="1">
         <v>80</v>
@@ -5451,16 +5499,16 @@
     </row>
     <row r="85" s="1" customFormat="1" spans="2:20">
       <c r="B85" s="1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="D85" s="1">
         <v>100</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="T85" s="1" t="s">
         <v>48</v>
@@ -5468,16 +5516,16 @@
     </row>
     <row r="86" s="1" customFormat="1" spans="2:20">
       <c r="B86" s="1" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="D86" s="1">
         <v>100</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="T86" s="1" t="s">
         <v>50</v>
@@ -5485,22 +5533,22 @@
     </row>
     <row r="87" s="1" customFormat="1" spans="2:20">
       <c r="B87" s="1" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="D87" s="1">
         <v>100</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="Q87" s="1" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="R87" s="1" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="S87" s="1">
         <v>100</v>
@@ -5511,16 +5559,16 @@
     </row>
     <row r="88" s="1" customFormat="1" spans="2:20">
       <c r="B88" s="1" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="D88" s="1">
         <v>100</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="T88" s="1" t="s">
         <v>27</v>
@@ -5528,16 +5576,16 @@
     </row>
     <row r="89" s="1" customFormat="1" spans="2:20">
       <c r="B89" s="1" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="D89" s="1">
         <v>100</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="T89" s="1" t="s">
         <v>39</v>
@@ -5545,22 +5593,22 @@
     </row>
     <row r="90" s="1" customFormat="1" spans="2:20">
       <c r="B90" s="1" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="D90" s="1">
         <v>100</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="Q90" s="1" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="S90" s="1">
         <v>100</v>
@@ -5571,487 +5619,487 @@
     </row>
     <row r="91" s="1" customFormat="1" spans="2:20">
       <c r="B91" s="1" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="D91" s="1">
         <v>100</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="T91" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="92" s="1" customFormat="1" spans="2:20">
       <c r="B92" s="1" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="D92" s="1">
         <v>100</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="Q92" s="1" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="R92" s="1" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="S92" s="1">
         <v>100</v>
       </c>
       <c r="T92" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="93" s="1" customFormat="1" spans="2:5">
       <c r="B93" s="1" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="D93" s="1">
         <v>100</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
     </row>
     <row r="94" s="1" customFormat="1" spans="2:5">
       <c r="B94" s="1" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="D94" s="1">
         <v>100</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" spans="2:5">
       <c r="B95" s="1" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="D95" s="1">
         <v>100</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
     </row>
     <row r="96" s="1" customFormat="1" spans="2:5">
       <c r="B96" s="1" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="D96" s="1">
         <v>100</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
     </row>
     <row r="97" s="1" customFormat="1" spans="2:5">
       <c r="B97" s="1" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="D97" s="1">
         <v>100</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
     </row>
     <row r="98" s="1" customFormat="1" spans="2:5">
       <c r="B98" s="1" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="D98" s="1">
         <v>100</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
     </row>
     <row r="99" s="1" customFormat="1" spans="2:5">
       <c r="B99" s="1" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="D99" s="1">
         <v>100</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
     </row>
     <row r="100" s="1" customFormat="1" spans="2:5">
       <c r="B100" s="1" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="D100" s="1">
         <v>100</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
     </row>
     <row r="101" s="1" customFormat="1" spans="2:5">
       <c r="B101" s="1" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="D101" s="1">
         <v>100</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
     </row>
     <row r="102" s="1" customFormat="1" spans="2:5">
       <c r="B102" s="1" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="D102" s="1">
         <v>100</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
     </row>
     <row r="103" s="1" customFormat="1" spans="2:5">
       <c r="B103" s="1" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="D103" s="1">
         <v>100</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
     </row>
     <row r="104" s="1" customFormat="1" spans="2:5">
       <c r="B104" s="1" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="D104" s="1">
         <v>100</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" spans="2:5">
       <c r="B105" s="1" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="D105" s="1">
         <v>100</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
     </row>
     <row r="106" s="1" customFormat="1" spans="2:5">
       <c r="B106" s="1" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="D106" s="1">
         <v>100</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
     </row>
     <row r="107" s="1" customFormat="1" spans="2:5">
       <c r="B107" s="1" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="D107" s="1">
         <v>100</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
     </row>
     <row r="108" s="1" customFormat="1" spans="2:5">
       <c r="B108" s="1" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="D108" s="1">
         <v>100</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
     </row>
     <row r="109" s="1" customFormat="1" spans="2:5">
       <c r="B109" s="1" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="D109" s="1">
         <v>100</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
     </row>
     <row r="110" s="1" customFormat="1" spans="2:5">
       <c r="B110" s="1" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="D110" s="1">
         <v>100</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
     </row>
     <row r="111" s="1" customFormat="1" spans="2:5">
       <c r="B111" s="1" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="D111" s="1">
         <v>100</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
     </row>
     <row r="112" s="1" customFormat="1" spans="2:5">
       <c r="B112" s="1" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="D112" s="1">
         <v>100</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
     </row>
     <row r="113" s="1" customFormat="1" spans="2:5">
       <c r="B113" s="1" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="D113" s="1">
         <v>100</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
     </row>
     <row r="114" s="1" customFormat="1" spans="2:5">
       <c r="B114" s="1" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="D114" s="1">
         <v>100</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
     </row>
     <row r="115" s="1" customFormat="1" spans="2:5">
       <c r="B115" s="1" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="D115" s="1">
         <v>100</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
     </row>
     <row r="116" s="1" customFormat="1" spans="2:5">
       <c r="B116" s="1" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="D116" s="1">
         <v>100</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
     </row>
     <row r="117" s="1" customFormat="1" spans="2:5">
       <c r="B117" s="1" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="D117" s="1">
         <v>100</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
     </row>
     <row r="118" s="1" customFormat="1" spans="2:5">
       <c r="B118" s="1" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="D118" s="1">
         <v>100</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
     </row>
     <row r="119" s="1" customFormat="1" spans="2:5">
       <c r="B119" s="1" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="D119" s="1">
         <v>100</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
     </row>
     <row r="120" s="1" customFormat="1" spans="2:5">
       <c r="B120" s="1" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="D120" s="1">
         <v>100</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
     </row>
     <row r="121" s="1" customFormat="1" spans="2:5">
       <c r="B121" s="1" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="D121" s="1">
         <v>100</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
     </row>
     <row r="122" s="1" customFormat="1" spans="2:5">
       <c r="B122" s="1" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="D122" s="1">
         <v>100</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
     </row>
     <row r="123" s="1" customFormat="1" spans="2:5">
       <c r="B123" s="1" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="D123" s="1">
         <v>100</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
     </row>
     <row r="124" s="1" customFormat="1" spans="2:5">
       <c r="B124" s="1" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="D124" s="1">
         <v>100</v>
@@ -6062,10 +6110,10 @@
     </row>
     <row r="125" s="1" customFormat="1" spans="2:5">
       <c r="B125" s="1" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="D125" s="1">
         <v>100</v>
@@ -6076,576 +6124,576 @@
     </row>
     <row r="126" s="1" customFormat="1" spans="2:5">
       <c r="B126" s="1" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="D126" s="1">
         <v>100</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
     </row>
     <row r="127" s="1" customFormat="1" spans="2:5">
       <c r="B127" s="1" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="D127" s="1">
         <v>100</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
     </row>
     <row r="128" s="1" customFormat="1" spans="2:5">
       <c r="B128" s="1" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="D128" s="1">
         <v>100</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
     </row>
     <row r="129" s="1" customFormat="1" spans="2:5">
       <c r="B129" s="1" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="D129" s="1">
         <v>100</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
     </row>
     <row r="130" s="1" customFormat="1" spans="2:5">
       <c r="B130" s="1" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="D130" s="1">
         <v>100</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
     </row>
     <row r="131" s="1" customFormat="1" spans="2:5">
       <c r="B131" s="1" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="D131" s="1">
         <v>100</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
     </row>
     <row r="132" s="1" customFormat="1" spans="2:5">
       <c r="B132" s="1" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="D132" s="1">
         <v>100</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
     </row>
     <row r="133" s="1" customFormat="1" spans="2:5">
       <c r="B133" s="1" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="D133" s="1">
         <v>100</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
     </row>
     <row r="134" s="1" customFormat="1" spans="2:5">
       <c r="B134" s="1" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="D134" s="1">
         <v>100</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
     </row>
     <row r="135" s="1" customFormat="1" spans="2:5">
       <c r="B135" s="1" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="D135" s="1">
         <v>100</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
     </row>
     <row r="136" s="1" customFormat="1" spans="2:5">
       <c r="B136" s="1" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="D136" s="1">
         <v>100</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
     </row>
     <row r="137" s="1" customFormat="1" spans="2:5">
       <c r="B137" s="1" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="D137" s="1">
         <v>100</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
     </row>
     <row r="138" s="1" customFormat="1" spans="2:5">
       <c r="B138" s="1" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="D138" s="1">
         <v>100</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
     </row>
     <row r="139" s="1" customFormat="1" spans="2:5">
       <c r="B139" s="1" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="D139" s="1">
         <v>100</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
     </row>
     <row r="140" s="1" customFormat="1" spans="2:5">
       <c r="B140" s="1" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="D140" s="1">
         <v>100</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
     </row>
     <row r="141" s="1" customFormat="1" spans="2:5">
       <c r="B141" s="1" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="D141" s="1">
         <v>100</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
     </row>
     <row r="142" s="1" customFormat="1" spans="2:5">
       <c r="B142" s="1" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="D142" s="1">
         <v>100</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
     </row>
     <row r="143" s="1" customFormat="1" spans="2:5">
       <c r="B143" s="1" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="D143" s="1">
         <v>100</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
     </row>
     <row r="144" s="1" customFormat="1" spans="2:5">
       <c r="B144" s="1" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="D144" s="1">
         <v>100</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
     </row>
     <row r="145" s="1" customFormat="1" spans="2:5">
       <c r="B145" s="1" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="D145" s="1">
         <v>100</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
     </row>
     <row r="146" s="1" customFormat="1" spans="2:5">
       <c r="B146" s="1" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="D146" s="1">
         <v>100</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
     </row>
     <row r="147" s="1" customFormat="1" spans="2:5">
       <c r="B147" s="1" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="D147" s="1">
         <v>100</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
     </row>
     <row r="148" s="1" customFormat="1" spans="2:5">
       <c r="B148" s="1" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D148" s="1">
         <v>100</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
     </row>
     <row r="149" s="1" customFormat="1" spans="2:5">
       <c r="B149" s="1" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="D149" s="1">
         <v>100</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
     </row>
     <row r="150" s="1" customFormat="1" spans="2:5">
       <c r="B150" s="1" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="D150" s="1">
         <v>100</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
     </row>
     <row r="151" s="1" customFormat="1" spans="2:5">
       <c r="B151" s="1" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="D151" s="1">
         <v>100</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
     </row>
     <row r="152" s="1" customFormat="1" spans="2:5">
       <c r="B152" s="1" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="D152" s="1">
         <v>100</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
     </row>
     <row r="153" s="1" customFormat="1" spans="2:5">
       <c r="B153" s="1" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="D153" s="1">
         <v>100</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
     </row>
     <row r="154" s="1" customFormat="1" spans="2:5">
       <c r="B154" s="1" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="D154" s="1">
         <v>100</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
     </row>
     <row r="155" s="1" customFormat="1" spans="2:5">
       <c r="B155" s="1" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="D155" s="1">
         <v>100</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
     </row>
     <row r="156" s="1" customFormat="1" spans="2:5">
       <c r="B156" s="1" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="D156" s="1">
         <v>100</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
     </row>
     <row r="157" s="1" customFormat="1" spans="2:5">
       <c r="B157" s="1" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="D157" s="1">
         <v>100</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
     </row>
     <row r="158" s="1" customFormat="1" spans="2:5">
       <c r="B158" s="1" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="D158" s="1">
         <v>100</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
     </row>
     <row r="159" s="1" customFormat="1" spans="2:5">
       <c r="B159" s="1" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="D159" s="1">
         <v>100</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
     </row>
     <row r="160" s="1" customFormat="1" spans="2:5">
       <c r="B160" s="1" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="D160" s="1">
         <v>100</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
     </row>
     <row r="161" s="1" customFormat="1" spans="2:5">
       <c r="B161" s="1" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="D161" s="1">
         <v>100</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
     </row>
     <row r="162" s="1" customFormat="1" spans="2:5">
       <c r="B162" s="1" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="D162" s="1">
         <v>100</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
     </row>
     <row r="163" s="1" customFormat="1" spans="2:5">
       <c r="B163" s="1" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="D163" s="1">
         <v>100</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
     </row>
     <row r="164" s="1" customFormat="1" spans="2:5">
       <c r="B164" s="1" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="D164" s="1">
         <v>100</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
     </row>
     <row r="165" s="1" customFormat="1" spans="2:5">
       <c r="B165" s="1" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="D165" s="1">
         <v>100</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
     </row>
     <row r="166" s="1" customFormat="1" spans="2:5">
       <c r="B166" s="1" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="D166" s="1">
         <v>100</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -6677,22 +6725,22 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="D1" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="E1" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="F1" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="G1" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="H1" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6700,25 +6748,25 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="C2" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="D2" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="E2" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="F2" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="G2" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="H2" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6729,19 +6777,19 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="D3" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="E3" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="F3" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="G3" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="H3" t="s">
         <v>23</v>
@@ -6749,10 +6797,10 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -6772,10 +6820,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="C5">
         <v>95</v>
@@ -6795,10 +6843,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C6">
         <v>80</v>
@@ -6818,10 +6866,10 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B7" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="C7">
         <v>1000</v>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -190,7 +190,7 @@
     <t>幸运事件</t>
   </si>
   <si>
-    <t>幸运的未知事件</t>
+    <t>这是好事啊</t>
   </si>
   <si>
     <t>Reward</t>
@@ -202,8 +202,7 @@
     <t>商店采购</t>
   </si>
   <si>
-    <t>摆满了
-琳琅满目的食物与道具</t>
+    <t>琳琅满目的食物与道具</t>
   </si>
   <si>
     <t>Shop</t>
@@ -2533,7 +2532,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2545,9 +2544,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3047,207 +3043,207 @@
   <dimension ref="A1:K21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="13.0769230769231" style="5" customWidth="1"/>
-    <col min="2" max="2" width="25.3076923076923" style="5" customWidth="1"/>
-    <col min="3" max="3" width="37.1538461538462" style="5" customWidth="1"/>
-    <col min="4" max="4" width="34.5384615384615" style="5" customWidth="1"/>
-    <col min="5" max="5" width="24.7692307692308" style="5" customWidth="1"/>
-    <col min="6" max="6" width="35.6923076923077" style="5" customWidth="1"/>
-    <col min="7" max="7" width="25.6153846153846" style="5" customWidth="1"/>
-    <col min="8" max="8" width="23.2307692307692" style="5" customWidth="1"/>
-    <col min="9" max="10" width="21.7692307692308" style="5" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.3076923076923" style="1" customWidth="1"/>
+    <col min="3" max="3" width="37.1538461538462" style="1" customWidth="1"/>
+    <col min="4" max="4" width="34.5384615384615" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24.7692307692308" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.6923076923077" style="1" customWidth="1"/>
+    <col min="7" max="7" width="25.6153846153846" style="1" customWidth="1"/>
+    <col min="8" max="8" width="23.2307692307692" style="1" customWidth="1"/>
+    <col min="9" max="10" width="21.7692307692308" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="2:11">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="1">
         <v>0</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="1">
         <v>0.7</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="1">
         <v>1.2</v>
       </c>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="1">
         <v>0</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="1">
         <v>0.7</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="1">
         <v>1.2</v>
       </c>
     </row>
     <row r="6" spans="2:11">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="1">
         <v>0</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="1">
         <v>0.7</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="1">
         <v>1.2</v>
       </c>
     </row>
@@ -3270,13 +3266,13 @@
       <c r="H7" s="4">
         <v>0</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="1">
         <v>0.7</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="1">
         <v>1.2</v>
       </c>
     </row>
@@ -3299,100 +3295,100 @@
       <c r="H8" s="4">
         <v>0</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="1">
         <v>0.7</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K8" s="1">
         <v>1.2</v>
       </c>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="1">
         <v>0</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="1">
         <v>0.8</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9" s="1">
         <v>1.3</v>
       </c>
     </row>
     <row r="10" spans="2:11">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="1">
         <v>0</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="1">
         <v>0.8</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K10" s="1">
         <v>1.3</v>
       </c>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="1">
         <v>0</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="1">
         <v>0.8</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K11" s="1">
         <v>1.3</v>
       </c>
     </row>
@@ -3415,13 +3411,13 @@
       <c r="H12" s="4">
         <v>0</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="1">
         <v>0.8</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K12" s="1">
         <v>1.3</v>
       </c>
     </row>
@@ -3444,155 +3440,155 @@
       <c r="H13" s="4">
         <v>0</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J13" s="1">
         <v>0.8</v>
       </c>
-      <c r="K13" s="5">
+      <c r="K13" s="1">
         <v>1.3</v>
       </c>
     </row>
     <row r="14" spans="2:11">
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="1">
         <v>0</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J14" s="5">
+      <c r="J14" s="1">
         <v>0.8</v>
       </c>
-      <c r="K14" s="5">
+      <c r="K14" s="1">
         <v>1.3</v>
       </c>
     </row>
     <row r="15" spans="2:11">
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="1">
         <v>0</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J15" s="5">
+      <c r="J15" s="1">
         <v>0</v>
       </c>
-      <c r="K15" s="5">
+      <c r="K15" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="34" spans="2:11">
-      <c r="B16" s="5" t="s">
+    <row r="16" ht="17" spans="2:11">
+      <c r="B16" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="1">
         <v>0</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J16" s="5">
+      <c r="J16" s="1">
         <v>0</v>
       </c>
-      <c r="K16" s="5">
+      <c r="K16" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="17" ht="34" spans="2:11">
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="1">
         <v>0</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="I17" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J17" s="5">
+      <c r="J17" s="1">
         <v>0</v>
       </c>
-      <c r="K17" s="5">
+      <c r="K17" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:11">
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="1">
         <v>0</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="I18" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J18" s="5">
+      <c r="J18" s="1">
         <v>0</v>
       </c>
-      <c r="K18" s="5">
+      <c r="K18" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3618,65 +3614,65 @@
       <c r="H19" s="4">
         <v>0</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="I19" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="5">
+      <c r="J19" s="1">
         <v>0</v>
       </c>
-      <c r="K19" s="5">
+      <c r="K19" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:11">
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="1">
         <v>-400</v>
       </c>
-      <c r="J20" s="5">
+      <c r="J20" s="1">
         <v>0</v>
       </c>
-      <c r="K20" s="5">
+      <c r="K20" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="2:11">
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="1">
         <v>0</v>
       </c>
-      <c r="J21" s="5">
+      <c r="J21" s="1">
         <v>0</v>
       </c>
-      <c r="K21" s="5">
+      <c r="K21" s="1">
         <v>0</v>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15300"/>
+    <workbookView windowHeight="15340"/>
   </bookViews>
   <sheets>
     <sheet name="action" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="659">
   <si>
     <t>##var</t>
   </si>
@@ -52,6 +52,12 @@
     <t>maxCostDays</t>
   </si>
   <si>
+    <t>rewardTitle</t>
+  </si>
+  <si>
+    <t>rewardDesc</t>
+  </si>
+  <si>
     <t>##comment</t>
   </si>
   <si>
@@ -85,6 +91,12 @@
     <t>本次最大耗时(0.1天)</t>
   </si>
   <si>
+    <t>奖励 Tip 标题</t>
+  </si>
+  <si>
+    <t>奖励 Tip 描述</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -115,7 +127,11 @@
     <t>None</t>
   </si>
   <si>
-    <t/>
+    <t>金币奖励</t>
+  </si>
+  <si>
+    <t>完成营业额外得
+一些金币</t>
   </si>
   <si>
     <t>act_food_fragment</t>
@@ -124,24 +140,52 @@
     <t>food_fragment</t>
   </si>
   <si>
+    <t>餐桌碎片包</t>
+  </si>
+  <si>
+    <t>完成营业额外得
+餐桌格子3选1</t>
+  </si>
+  <si>
     <t>act_food_passive</t>
   </si>
   <si>
     <t>food_passive</t>
   </si>
   <si>
+    <t>被动道具</t>
+  </si>
+  <si>
+    <t>完成营业额外得
+道具2选1</t>
+  </si>
+  <si>
     <t>act_food_active_strengthen</t>
   </si>
   <si>
     <t>food_active_strengthen</t>
   </si>
   <si>
+    <t>强化主动道具</t>
+  </si>
+  <si>
+    <t>完成营业额外得
+强化箱2选1</t>
+  </si>
+  <si>
     <t>act_food_active_adjust</t>
   </si>
   <si>
     <t>food_active_ajust</t>
   </si>
   <si>
+    <t>调整主动道具</t>
+  </si>
+  <si>
+    <t>完成营业额外得
+调整单2选1</t>
+  </si>
+  <si>
     <t>act_food_hard_gold</t>
   </si>
   <si>
@@ -151,28 +195,48 @@
     <t>food_hard_gold</t>
   </si>
   <si>
+    <t>完成营业额外得
+大量金币</t>
+  </si>
+  <si>
     <t>act_food_hard_fragment</t>
   </si>
   <si>
     <t>food_hard_fragment</t>
   </si>
   <si>
+    <t>完成营业额外得
+更大的餐桌格子3选1</t>
+  </si>
+  <si>
     <t>act_food_hard_passive</t>
   </si>
   <si>
     <t>food_hard_passive</t>
   </si>
   <si>
+    <t>完成营业额外得
+道具4选1</t>
+  </si>
+  <si>
     <t>act_food_hard_active_strengthen</t>
   </si>
   <si>
     <t>food_hard_active_strengthen</t>
   </si>
   <si>
+    <t>完成营业额外得
+强化箱4选1</t>
+  </si>
+  <si>
     <t>act_food_hard_active_adjust</t>
   </si>
   <si>
     <t>food_hard_active_ajust</t>
+  </si>
+  <si>
+    <t>完成营业额外得
+调整单4选1</t>
   </si>
   <si>
     <t>act_event</t>
@@ -2532,7 +2596,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2548,6 +2612,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3040,7 +3107,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
@@ -3051,11 +3118,13 @@
     <col min="6" max="6" width="35.6923076923077" style="1" customWidth="1"/>
     <col min="7" max="7" width="25.6153846153846" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.2307692307692" style="1" customWidth="1"/>
-    <col min="9" max="10" width="21.7692307692308" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1"/>
+    <col min="9" max="11" width="21.7692307692308" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15.1538461538462" style="1" customWidth="1"/>
+    <col min="13" max="13" width="54" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" ht="17" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3089,472 +3158,521 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" ht="17" spans="1:13">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" ht="17" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11">
+        <v>30</v>
+      </c>
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" ht="34" spans="2:13">
       <c r="B4" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H4" s="1">
         <v>0</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="J4" s="1">
         <v>0.7</v>
       </c>
       <c r="K4" s="1">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="5" spans="2:11">
+      <c r="L4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" ht="34" spans="2:13">
       <c r="B5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="J5" s="1">
         <v>0.7</v>
       </c>
       <c r="K5" s="1">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="6" spans="2:11">
+      <c r="L5" t="s">
+        <v>40</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" ht="34" spans="2:13">
       <c r="B6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="J6" s="1">
         <v>0.7</v>
       </c>
       <c r="K6" s="1">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="7" s="4" customFormat="1" spans="2:11">
+      <c r="L6" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" s="4" customFormat="1" ht="34" spans="2:13">
       <c r="B7" s="4" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H7" s="4">
         <v>0</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="I7" s="1"/>
       <c r="J7" s="1">
         <v>0.7</v>
       </c>
       <c r="K7" s="1">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="8" s="4" customFormat="1" spans="2:11">
+      <c r="L7" t="s">
+        <v>48</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" s="4" customFormat="1" ht="34" spans="2:13">
       <c r="B8" s="4" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H8" s="4">
         <v>0</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="I8" s="1"/>
       <c r="J8" s="1">
         <v>0.7</v>
       </c>
       <c r="K8" s="1">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="9" spans="2:11">
+      <c r="L8" t="s">
+        <v>52</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" ht="34" spans="2:13">
       <c r="B9" s="1" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="J9" s="1">
         <v>0.8</v>
       </c>
       <c r="K9" s="1">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="10" spans="2:11">
+      <c r="L9" t="s">
+        <v>36</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" ht="34" spans="2:13">
       <c r="B10" s="1" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="J10" s="1">
         <v>0.8</v>
       </c>
       <c r="K10" s="1">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="11" spans="2:11">
+      <c r="L10" t="s">
+        <v>40</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" ht="34" spans="2:13">
       <c r="B11" s="1" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="J11" s="1">
         <v>0.8</v>
       </c>
       <c r="K11" s="1">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="12" s="4" customFormat="1" spans="2:11">
+      <c r="L11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" s="4" customFormat="1" ht="34" spans="2:13">
       <c r="B12" s="4" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H12" s="4">
         <v>0</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="I12" s="1"/>
       <c r="J12" s="1">
         <v>0.8</v>
       </c>
       <c r="K12" s="1">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="13" s="4" customFormat="1" spans="2:11">
+      <c r="L12" t="s">
+        <v>48</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" s="4" customFormat="1" ht="34" spans="2:13">
       <c r="B13" s="4" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H13" s="4">
         <v>0</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="I13" s="1"/>
       <c r="J13" s="1">
         <v>0.8</v>
       </c>
       <c r="K13" s="1">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="14" spans="2:11">
+      <c r="L13" t="s">
+        <v>52</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13">
       <c r="B14" s="1" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H14" s="1">
         <v>0</v>
       </c>
-      <c r="I14" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="J14" s="1">
         <v>0.8</v>
       </c>
       <c r="K14" s="1">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="15" spans="2:11">
+      <c r="L14"/>
+      <c r="M14" s="6"/>
+    </row>
+    <row r="15" spans="2:13">
       <c r="B15" s="1" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H15" s="1">
         <v>0</v>
       </c>
-      <c r="I15" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="J15" s="1">
         <v>0</v>
       </c>
       <c r="K15" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" ht="17" spans="2:11">
+      <c r="L15"/>
+      <c r="M15" s="6"/>
+    </row>
+    <row r="16" ht="17" spans="2:13">
       <c r="B16" s="1" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H16" s="1">
         <v>0</v>
       </c>
-      <c r="I16" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="J16" s="1">
         <v>0</v>
       </c>
       <c r="K16" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" ht="34" spans="2:11">
+      <c r="L16"/>
+      <c r="M16" s="6"/>
+    </row>
+    <row r="17" ht="34" spans="2:13">
       <c r="B17" s="1" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="J17" s="1">
         <v>0</v>
@@ -3562,119 +3680,126 @@
       <c r="K17" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="2:11">
+      <c r="L17"/>
+      <c r="M17" s="6"/>
+    </row>
+    <row r="18" spans="2:13">
       <c r="B18" s="1" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
       </c>
-      <c r="I18" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="J18" s="1">
         <v>0</v>
       </c>
       <c r="K18" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" s="4" customFormat="1" spans="1:11">
+      <c r="L18"/>
+      <c r="M18" s="6"/>
+    </row>
+    <row r="19" s="4" customFormat="1" spans="1:13">
       <c r="A19" s="4" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H19" s="4">
         <v>0</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="I19" s="1"/>
       <c r="J19" s="1">
         <v>0</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="2:11">
+      <c r="L19"/>
+      <c r="M19" s="6"/>
+    </row>
+    <row r="20" spans="2:13">
       <c r="B20" s="1" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="H20" s="1">
         <v>-400</v>
       </c>
+      <c r="I20"/>
       <c r="J20" s="1">
         <v>0</v>
       </c>
       <c r="K20" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="2:11">
+      <c r="L20"/>
+      <c r="M20" s="6"/>
+    </row>
+    <row r="21" spans="2:13">
       <c r="B21" s="1" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="H21" s="1">
         <v>0</v>
       </c>
+      <c r="I21"/>
       <c r="J21" s="1">
         <v>0</v>
       </c>
       <c r="K21" s="1">
         <v>0</v>
       </c>
+      <c r="L21"/>
+      <c r="M21" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3708,68 +3833,68 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="2:12">
       <c r="B4" s="1" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="E4" s="2" t="str">
         <f t="shared" ref="E4:E10" si="0">_xlfn.TEXTJOIN(",",TRUE,I4:L4)</f>
         <v>400,300,200,150</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="G4" s="1" t="str">
         <f t="shared" ref="G4:G10" si="1">""</f>
@@ -3790,17 +3915,17 @@
     </row>
     <row r="5" s="1" customFormat="1" spans="2:12">
       <c r="B5" s="1" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="E5" s="2" t="str">
         <f t="shared" si="0"/>
         <v>200,200,250,200</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="G5" s="1" t="str">
         <f t="shared" si="1"/>
@@ -3821,17 +3946,17 @@
     </row>
     <row r="6" s="1" customFormat="1" spans="2:15">
       <c r="B6" s="1" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="E6" s="2" t="str">
         <f t="shared" si="0"/>
         <v>0,50,100,200</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="G6" s="1" t="str">
         <f t="shared" si="1"/>
@@ -3850,22 +3975,22 @@
         <v>200</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="2:15">
       <c r="B7" s="1" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="E7" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100,100,100,100</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="G7" s="1" t="str">
         <f t="shared" si="1"/>
@@ -3884,22 +4009,22 @@
         <v>100</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="2:12">
       <c r="B8" s="1" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2" t="str">
         <f t="shared" si="0"/>
         <v>150,150,100,100</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="G8" s="1" t="str">
         <f t="shared" si="1"/>
@@ -3920,17 +4045,17 @@
     </row>
     <row r="9" s="1" customFormat="1" spans="2:12">
       <c r="B9" s="1" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="E9" s="2" t="str">
         <f t="shared" si="0"/>
         <v>100,100,100,100</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="G9" s="1" t="str">
         <f t="shared" si="1"/>
@@ -3951,17 +4076,17 @@
     </row>
     <row r="10" s="1" customFormat="1" spans="2:12">
       <c r="B10" s="1" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="E10" s="2" t="str">
         <f t="shared" si="0"/>
         <v>0,50,100,100</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="G10" s="1" t="str">
         <f t="shared" si="1"/>
@@ -4022,2674 +4147,2674 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="2:5">
       <c r="B4" s="1" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="D4" s="1">
         <v>100</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="2:18">
       <c r="B5" s="1" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="D5" s="1">
         <v>100</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="2:18">
       <c r="B6" s="1" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="D6" s="1">
         <v>100</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="2:18">
       <c r="B7" s="1" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="D7" s="1">
         <v>100</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="2:5">
       <c r="B8" s="1" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="2:5">
       <c r="B9" s="1" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="2:5">
       <c r="B10" s="1" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="2:5">
       <c r="B11" s="1" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="D11" s="1">
         <v>100</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="2:5">
       <c r="B12" s="1" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D12" s="1">
         <v>100</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="2:5">
       <c r="B13" s="1" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="D13" s="1">
         <v>100</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="2:13">
       <c r="B14" s="1" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="D14" s="1">
         <v>100</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="2:13">
       <c r="B15" s="1" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="D15" s="1">
         <v>100</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="2:13">
       <c r="B16" s="1" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="D16" s="1">
         <v>100</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="2:13">
       <c r="B17" s="1" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="D17" s="1">
         <v>100</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="2:13">
       <c r="B18" s="1" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="D18" s="1">
         <v>100</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="2:13">
       <c r="B19" s="1" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="D19" s="1">
         <v>100</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="2:13">
       <c r="B20" s="1" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="D20" s="1">
         <v>100</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="2:20">
       <c r="B21" s="1" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="D21" s="1">
         <v>100</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="2:20">
       <c r="B22" s="1" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="D22" s="1">
         <v>100</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="2:20">
       <c r="B23" s="1" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="D23" s="1">
         <v>100</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="2:20">
       <c r="B24" s="1" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="D24" s="1">
         <v>100</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="2:20">
       <c r="B25" s="1" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="D25" s="1">
         <v>100</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" spans="2:20">
       <c r="B26" s="1" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="D26" s="1">
         <v>100</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="2:20">
       <c r="B27" s="1" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="D27" s="1">
         <v>100</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="2:20">
       <c r="B28" s="1" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="D28" s="1">
         <v>100</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="2:20">
       <c r="B29" s="1" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="D29" s="1">
         <v>100</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="2:20">
       <c r="B30" s="1" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="D30" s="1">
         <v>100</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="2:19">
       <c r="B31" s="1" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="D31" s="1">
         <v>100</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="2:19">
       <c r="B32" s="1" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="D32" s="1">
         <v>100</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S32" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" spans="2:19">
       <c r="B33" s="1" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="D33" s="1">
         <v>100</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S33" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" spans="2:19">
       <c r="B34" s="1" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="D34" s="1">
         <v>100</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="2:19">
       <c r="B35" s="1" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="D35" s="1">
         <v>100</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="2:19">
       <c r="B36" s="1" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D36" s="1">
         <v>100</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="S36" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="2:19">
       <c r="B37" s="1" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="D37" s="1">
         <v>100</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" spans="2:19">
       <c r="B38" s="1" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="D38" s="1">
         <v>100</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="S38" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="2:19">
       <c r="B39" s="1" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="D39" s="1">
         <v>100</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="S39" s="1" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" spans="2:19">
       <c r="B40" s="1" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="D40" s="1">
         <v>100</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="S40" s="1" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="2:12">
       <c r="B41" s="1" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="D41" s="1">
         <v>100</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="2:5">
       <c r="B42" s="1" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="D42" s="1">
         <v>100</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" spans="2:12">
       <c r="B43" s="1" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="D43" s="1">
         <v>100</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="2:12">
       <c r="B44" s="1" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="D44" s="1">
         <v>100</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" spans="2:12">
       <c r="B45" s="1" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="D45" s="1">
         <v>100</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="2:12">
       <c r="B46" s="1" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="D46" s="1">
         <v>100</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" spans="2:12">
       <c r="B47" s="1" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="D47" s="1">
         <v>100</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="2:12">
       <c r="B48" s="1" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="D48" s="1">
         <v>100</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" spans="2:12">
       <c r="B49" s="1" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="D49" s="1">
         <v>100</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" spans="2:5">
       <c r="B50" s="1" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="D50" s="1">
         <v>100</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" spans="2:5">
       <c r="B51" s="1" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="D51" s="1">
         <v>100</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" spans="2:5">
       <c r="B52" s="1" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="D52" s="1">
         <v>100</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" spans="2:5">
       <c r="B53" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="D53" s="1">
         <v>100</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" spans="2:5">
       <c r="B54" s="1" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="D54" s="1">
         <v>100</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" spans="2:5">
       <c r="B55" s="1" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="D55" s="1">
         <v>100</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" spans="2:5">
       <c r="B56" s="1" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="D56" s="1">
         <v>100</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" spans="2:5">
       <c r="B57" s="1" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="D57" s="1">
         <v>100</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" spans="2:5">
       <c r="B58" s="1" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="D58" s="1">
         <v>100</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" spans="2:5">
       <c r="B59" s="1" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="D59" s="1">
         <v>100</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" spans="2:5">
       <c r="B60" s="1" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="D60" s="1">
         <v>100</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" spans="2:5">
       <c r="B61" s="1" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="D61" s="1">
         <v>100</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" spans="2:5">
       <c r="B62" s="1" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="D62" s="1">
         <v>100</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" spans="2:5">
       <c r="B63" s="1" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="D63" s="1">
         <v>100</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" s="1" customFormat="1" spans="2:5">
       <c r="B64" s="1" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="D64" s="1">
         <v>100</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
     </row>
     <row r="65" s="1" customFormat="1" spans="2:5">
       <c r="B65" s="1" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="D65" s="1">
         <v>100</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
     </row>
     <row r="66" s="1" customFormat="1" spans="2:5">
       <c r="B66" s="1" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="D66" s="1">
         <v>100</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
     </row>
     <row r="67" s="1" customFormat="1" spans="2:5">
       <c r="B67" s="1" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="D67" s="1">
         <v>100</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
     </row>
     <row r="68" s="1" customFormat="1" spans="2:5">
       <c r="B68" s="1" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="D68" s="1">
         <v>100</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
     </row>
     <row r="69" s="1" customFormat="1" spans="2:5">
       <c r="B69" s="1" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="D69" s="1">
         <v>100</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
     </row>
     <row r="70" s="1" customFormat="1" spans="2:5">
       <c r="B70" s="1" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="D70" s="1">
         <v>100</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
     </row>
     <row r="71" s="1" customFormat="1" spans="2:5">
       <c r="B71" s="1" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="D71" s="1">
         <v>100</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
     </row>
     <row r="72" s="1" customFormat="1" spans="2:5">
       <c r="B72" s="1" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="D72" s="1">
         <v>100</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" spans="2:5">
       <c r="B73" s="1" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="D73" s="1">
         <v>100</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="1" spans="2:5">
       <c r="B74" s="1" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="D74" s="1">
         <v>100</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="1" spans="2:5">
       <c r="B75" s="1" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="D75" s="1">
         <v>100</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
     </row>
     <row r="76" s="1" customFormat="1" spans="2:5">
       <c r="B76" s="1" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="D76" s="1">
         <v>100</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" spans="2:5">
       <c r="B77" s="1" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="D77" s="1">
         <v>100</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
     </row>
     <row r="78" s="1" customFormat="1" spans="2:20">
       <c r="B78" s="1" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="D78" s="1">
         <v>100</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="R78" s="1" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="S78" s="1">
         <v>80</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="79" s="1" customFormat="1" spans="2:20">
       <c r="B79" s="1" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="D79" s="1">
         <v>100</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="T79" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="80" s="1" customFormat="1" spans="2:20">
       <c r="B80" s="1" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="D80" s="1">
         <v>100</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="T80" s="1" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="81" s="1" customFormat="1" spans="2:20">
       <c r="B81" s="1" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="D81" s="1">
         <v>100</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="Q81" s="1" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="R81" s="1" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="S81" s="1">
         <v>100</v>
       </c>
       <c r="T81" s="1" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="82" s="1" customFormat="1" spans="2:20">
       <c r="B82" s="1" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="D82" s="1">
         <v>100</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="T82" s="1" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="83" s="1" customFormat="1" spans="2:20">
       <c r="B83" s="1" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="D83" s="1">
         <v>100</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="T83" s="1" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
     </row>
     <row r="84" s="1" customFormat="1" spans="2:20">
       <c r="B84" s="1" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="D84" s="1">
         <v>100</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="Q84" s="1" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="R84" s="1" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="S84" s="1">
         <v>80</v>
       </c>
       <c r="T84" s="1" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="85" s="1" customFormat="1" spans="2:20">
       <c r="B85" s="1" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="D85" s="1">
         <v>100</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="T85" s="1" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
     </row>
     <row r="86" s="1" customFormat="1" spans="2:20">
       <c r="B86" s="1" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="D86" s="1">
         <v>100</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="87" s="1" customFormat="1" spans="2:20">
       <c r="B87" s="1" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="D87" s="1">
         <v>100</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="Q87" s="1" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="R87" s="1" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="S87" s="1">
         <v>100</v>
       </c>
       <c r="T87" s="1" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
     </row>
     <row r="88" s="1" customFormat="1" spans="2:20">
       <c r="B88" s="1" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="D88" s="1">
         <v>100</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="T88" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="89" s="1" customFormat="1" spans="2:20">
       <c r="B89" s="1" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="D89" s="1">
         <v>100</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="T89" s="1" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="90" s="1" customFormat="1" spans="2:20">
       <c r="B90" s="1" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="D90" s="1">
         <v>100</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="Q90" s="1" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="S90" s="1">
         <v>100</v>
       </c>
       <c r="T90" s="1" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
     </row>
     <row r="91" s="1" customFormat="1" spans="2:20">
       <c r="B91" s="1" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="D91" s="1">
         <v>100</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="T91" s="1" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="92" s="1" customFormat="1" spans="2:20">
       <c r="B92" s="1" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="D92" s="1">
         <v>100</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="Q92" s="1" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="R92" s="1" t="s">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="S92" s="1">
         <v>100</v>
       </c>
       <c r="T92" s="1" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="93" s="1" customFormat="1" spans="2:5">
       <c r="B93" s="1" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="D93" s="1">
         <v>100</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
     </row>
     <row r="94" s="1" customFormat="1" spans="2:5">
       <c r="B94" s="1" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="D94" s="1">
         <v>100</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" spans="2:5">
       <c r="B95" s="1" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="D95" s="1">
         <v>100</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>419</v>
+        <v>437</v>
       </c>
     </row>
     <row r="96" s="1" customFormat="1" spans="2:5">
       <c r="B96" s="1" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="D96" s="1">
         <v>100</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>422</v>
+        <v>440</v>
       </c>
     </row>
     <row r="97" s="1" customFormat="1" spans="2:5">
       <c r="B97" s="1" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="D97" s="1">
         <v>100</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
     </row>
     <row r="98" s="1" customFormat="1" spans="2:5">
       <c r="B98" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="D98" s="1">
         <v>100</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
     </row>
     <row r="99" s="1" customFormat="1" spans="2:5">
       <c r="B99" s="1" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="D99" s="1">
         <v>100</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
     </row>
     <row r="100" s="1" customFormat="1" spans="2:5">
       <c r="B100" s="1" t="s">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
       <c r="D100" s="1">
         <v>100</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>434</v>
+        <v>452</v>
       </c>
     </row>
     <row r="101" s="1" customFormat="1" spans="2:5">
       <c r="B101" s="1" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>436</v>
+        <v>454</v>
       </c>
       <c r="D101" s="1">
         <v>100</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
     </row>
     <row r="102" s="1" customFormat="1" spans="2:5">
       <c r="B102" s="1" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="D102" s="1">
         <v>100</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
     </row>
     <row r="103" s="1" customFormat="1" spans="2:5">
       <c r="B103" s="1" t="s">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="D103" s="1">
         <v>100</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
     </row>
     <row r="104" s="1" customFormat="1" spans="2:5">
       <c r="B104" s="1" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="D104" s="1">
         <v>100</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" spans="2:5">
       <c r="B105" s="1" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="D105" s="1">
         <v>100</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
     </row>
     <row r="106" s="1" customFormat="1" spans="2:5">
       <c r="B106" s="1" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="D106" s="1">
         <v>100</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>452</v>
+        <v>470</v>
       </c>
     </row>
     <row r="107" s="1" customFormat="1" spans="2:5">
       <c r="B107" s="1" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>454</v>
+        <v>472</v>
       </c>
       <c r="D107" s="1">
         <v>100</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>455</v>
+        <v>473</v>
       </c>
     </row>
     <row r="108" s="1" customFormat="1" spans="2:5">
       <c r="B108" s="1" t="s">
-        <v>456</v>
+        <v>474</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="D108" s="1">
         <v>100</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
     </row>
     <row r="109" s="1" customFormat="1" spans="2:5">
       <c r="B109" s="1" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>460</v>
+        <v>478</v>
       </c>
       <c r="D109" s="1">
         <v>100</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
     </row>
     <row r="110" s="1" customFormat="1" spans="2:5">
       <c r="B110" s="1" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="D110" s="1">
         <v>100</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
     </row>
     <row r="111" s="1" customFormat="1" spans="2:5">
       <c r="B111" s="1" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="D111" s="1">
         <v>100</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>467</v>
+        <v>485</v>
       </c>
     </row>
     <row r="112" s="1" customFormat="1" spans="2:5">
       <c r="B112" s="1" t="s">
-        <v>468</v>
+        <v>486</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="D112" s="1">
         <v>100</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>470</v>
+        <v>488</v>
       </c>
     </row>
     <row r="113" s="1" customFormat="1" spans="2:5">
       <c r="B113" s="1" t="s">
-        <v>471</v>
+        <v>489</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>472</v>
+        <v>490</v>
       </c>
       <c r="D113" s="1">
         <v>100</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
     </row>
     <row r="114" s="1" customFormat="1" spans="2:5">
       <c r="B114" s="1" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="D114" s="1">
         <v>100</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>476</v>
+        <v>494</v>
       </c>
     </row>
     <row r="115" s="1" customFormat="1" spans="2:5">
       <c r="B115" s="1" t="s">
-        <v>477</v>
+        <v>495</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="D115" s="1">
         <v>100</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
     </row>
     <row r="116" s="1" customFormat="1" spans="2:5">
       <c r="B116" s="1" t="s">
-        <v>480</v>
+        <v>498</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>481</v>
+        <v>499</v>
       </c>
       <c r="D116" s="1">
         <v>100</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
     </row>
     <row r="117" s="1" customFormat="1" spans="2:5">
       <c r="B117" s="1" t="s">
-        <v>483</v>
+        <v>501</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>484</v>
+        <v>502</v>
       </c>
       <c r="D117" s="1">
         <v>100</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>485</v>
+        <v>503</v>
       </c>
     </row>
     <row r="118" s="1" customFormat="1" spans="2:5">
       <c r="B118" s="1" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>487</v>
+        <v>505</v>
       </c>
       <c r="D118" s="1">
         <v>100</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>488</v>
+        <v>506</v>
       </c>
     </row>
     <row r="119" s="1" customFormat="1" spans="2:5">
       <c r="B119" s="1" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="D119" s="1">
         <v>100</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>491</v>
+        <v>509</v>
       </c>
     </row>
     <row r="120" s="1" customFormat="1" spans="2:5">
       <c r="B120" s="1" t="s">
-        <v>492</v>
+        <v>510</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="D120" s="1">
         <v>100</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
     </row>
     <row r="121" s="1" customFormat="1" spans="2:5">
       <c r="B121" s="1" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="D121" s="1">
         <v>100</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
     </row>
     <row r="122" s="1" customFormat="1" spans="2:5">
       <c r="B122" s="1" t="s">
-        <v>498</v>
+        <v>516</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="D122" s="1">
         <v>100</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>500</v>
+        <v>518</v>
       </c>
     </row>
     <row r="123" s="1" customFormat="1" spans="2:5">
       <c r="B123" s="1" t="s">
-        <v>501</v>
+        <v>519</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>502</v>
+        <v>520</v>
       </c>
       <c r="D123" s="1">
         <v>100</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>503</v>
+        <v>521</v>
       </c>
     </row>
     <row r="124" s="1" customFormat="1" spans="2:5">
       <c r="B124" s="1" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>504</v>
+        <v>522</v>
       </c>
       <c r="D124" s="1">
         <v>100</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
     </row>
     <row r="125" s="1" customFormat="1" spans="2:5">
       <c r="B125" s="1" t="s">
-        <v>505</v>
+        <v>523</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>506</v>
+        <v>524</v>
       </c>
       <c r="D125" s="1">
         <v>100</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
     </row>
     <row r="126" s="1" customFormat="1" spans="2:5">
       <c r="B126" s="1" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>508</v>
+        <v>526</v>
       </c>
       <c r="D126" s="1">
         <v>100</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>509</v>
+        <v>527</v>
       </c>
     </row>
     <row r="127" s="1" customFormat="1" spans="2:5">
       <c r="B127" s="1" t="s">
-        <v>510</v>
+        <v>528</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>511</v>
+        <v>529</v>
       </c>
       <c r="D127" s="1">
         <v>100</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>512</v>
+        <v>530</v>
       </c>
     </row>
     <row r="128" s="1" customFormat="1" spans="2:5">
       <c r="B128" s="1" t="s">
-        <v>513</v>
+        <v>531</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="D128" s="1">
         <v>100</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>515</v>
+        <v>533</v>
       </c>
     </row>
     <row r="129" s="1" customFormat="1" spans="2:5">
       <c r="B129" s="1" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>517</v>
+        <v>535</v>
       </c>
       <c r="D129" s="1">
         <v>100</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>518</v>
+        <v>536</v>
       </c>
     </row>
     <row r="130" s="1" customFormat="1" spans="2:5">
       <c r="B130" s="1" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>520</v>
+        <v>538</v>
       </c>
       <c r="D130" s="1">
         <v>100</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
     </row>
     <row r="131" s="1" customFormat="1" spans="2:5">
       <c r="B131" s="1" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>523</v>
+        <v>541</v>
       </c>
       <c r="D131" s="1">
         <v>100</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>524</v>
+        <v>542</v>
       </c>
     </row>
     <row r="132" s="1" customFormat="1" spans="2:5">
       <c r="B132" s="1" t="s">
-        <v>525</v>
+        <v>543</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>526</v>
+        <v>544</v>
       </c>
       <c r="D132" s="1">
         <v>100</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>527</v>
+        <v>545</v>
       </c>
     </row>
     <row r="133" s="1" customFormat="1" spans="2:5">
       <c r="B133" s="1" t="s">
-        <v>528</v>
+        <v>546</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
       <c r="D133" s="1">
         <v>100</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>530</v>
+        <v>548</v>
       </c>
     </row>
     <row r="134" s="1" customFormat="1" spans="2:5">
       <c r="B134" s="1" t="s">
-        <v>531</v>
+        <v>549</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>532</v>
+        <v>550</v>
       </c>
       <c r="D134" s="1">
         <v>100</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>533</v>
+        <v>551</v>
       </c>
     </row>
     <row r="135" s="1" customFormat="1" spans="2:5">
       <c r="B135" s="1" t="s">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>535</v>
+        <v>553</v>
       </c>
       <c r="D135" s="1">
         <v>100</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>536</v>
+        <v>554</v>
       </c>
     </row>
     <row r="136" s="1" customFormat="1" spans="2:5">
       <c r="B136" s="1" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="D136" s="1">
         <v>100</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>539</v>
+        <v>557</v>
       </c>
     </row>
     <row r="137" s="1" customFormat="1" spans="2:5">
       <c r="B137" s="1" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="D137" s="1">
         <v>100</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>542</v>
+        <v>560</v>
       </c>
     </row>
     <row r="138" s="1" customFormat="1" spans="2:5">
       <c r="B138" s="1" t="s">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>544</v>
+        <v>562</v>
       </c>
       <c r="D138" s="1">
         <v>100</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>545</v>
+        <v>563</v>
       </c>
     </row>
     <row r="139" s="1" customFormat="1" spans="2:5">
       <c r="B139" s="1" t="s">
-        <v>546</v>
+        <v>564</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>547</v>
+        <v>565</v>
       </c>
       <c r="D139" s="1">
         <v>100</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>548</v>
+        <v>566</v>
       </c>
     </row>
     <row r="140" s="1" customFormat="1" spans="2:5">
       <c r="B140" s="1" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>549</v>
+        <v>567</v>
       </c>
       <c r="D140" s="1">
         <v>100</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>550</v>
+        <v>568</v>
       </c>
     </row>
     <row r="141" s="1" customFormat="1" spans="2:5">
       <c r="B141" s="1" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>551</v>
+        <v>569</v>
       </c>
       <c r="D141" s="1">
         <v>100</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>552</v>
+        <v>570</v>
       </c>
     </row>
     <row r="142" s="1" customFormat="1" spans="2:5">
       <c r="B142" s="1" t="s">
-        <v>553</v>
+        <v>571</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>554</v>
+        <v>572</v>
       </c>
       <c r="D142" s="1">
         <v>100</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>555</v>
+        <v>573</v>
       </c>
     </row>
     <row r="143" s="1" customFormat="1" spans="2:5">
       <c r="B143" s="1" t="s">
-        <v>556</v>
+        <v>574</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>557</v>
+        <v>575</v>
       </c>
       <c r="D143" s="1">
         <v>100</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>558</v>
+        <v>576</v>
       </c>
     </row>
     <row r="144" s="1" customFormat="1" spans="2:5">
       <c r="B144" s="1" t="s">
-        <v>559</v>
+        <v>577</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>560</v>
+        <v>578</v>
       </c>
       <c r="D144" s="1">
         <v>100</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>561</v>
+        <v>579</v>
       </c>
     </row>
     <row r="145" s="1" customFormat="1" spans="2:5">
       <c r="B145" s="1" t="s">
-        <v>562</v>
+        <v>580</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>563</v>
+        <v>581</v>
       </c>
       <c r="D145" s="1">
         <v>100</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>564</v>
+        <v>582</v>
       </c>
     </row>
     <row r="146" s="1" customFormat="1" spans="2:5">
       <c r="B146" s="1" t="s">
-        <v>565</v>
+        <v>583</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>566</v>
+        <v>584</v>
       </c>
       <c r="D146" s="1">
         <v>100</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>567</v>
+        <v>585</v>
       </c>
     </row>
     <row r="147" s="1" customFormat="1" spans="2:5">
       <c r="B147" s="1" t="s">
-        <v>568</v>
+        <v>586</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>569</v>
+        <v>587</v>
       </c>
       <c r="D147" s="1">
         <v>100</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>570</v>
+        <v>588</v>
       </c>
     </row>
     <row r="148" s="1" customFormat="1" spans="2:5">
       <c r="B148" s="1" t="s">
-        <v>571</v>
+        <v>589</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>572</v>
+        <v>590</v>
       </c>
       <c r="D148" s="1">
         <v>100</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>573</v>
+        <v>591</v>
       </c>
     </row>
     <row r="149" s="1" customFormat="1" spans="2:5">
       <c r="B149" s="1" t="s">
-        <v>574</v>
+        <v>592</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>575</v>
+        <v>593</v>
       </c>
       <c r="D149" s="1">
         <v>100</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>576</v>
+        <v>594</v>
       </c>
     </row>
     <row r="150" s="1" customFormat="1" spans="2:5">
       <c r="B150" s="1" t="s">
-        <v>577</v>
+        <v>595</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>578</v>
+        <v>596</v>
       </c>
       <c r="D150" s="1">
         <v>100</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>579</v>
+        <v>597</v>
       </c>
     </row>
     <row r="151" s="1" customFormat="1" spans="2:5">
       <c r="B151" s="1" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>580</v>
+        <v>598</v>
       </c>
       <c r="D151" s="1">
         <v>100</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>581</v>
+        <v>599</v>
       </c>
     </row>
     <row r="152" s="1" customFormat="1" spans="2:5">
       <c r="B152" s="1" t="s">
-        <v>582</v>
+        <v>600</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>583</v>
+        <v>601</v>
       </c>
       <c r="D152" s="1">
         <v>100</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>584</v>
+        <v>602</v>
       </c>
     </row>
     <row r="153" s="1" customFormat="1" spans="2:5">
       <c r="B153" s="1" t="s">
-        <v>585</v>
+        <v>603</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="D153" s="1">
         <v>100</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>587</v>
+        <v>605</v>
       </c>
     </row>
     <row r="154" s="1" customFormat="1" spans="2:5">
       <c r="B154" s="1" t="s">
-        <v>588</v>
+        <v>606</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>589</v>
+        <v>607</v>
       </c>
       <c r="D154" s="1">
         <v>100</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>590</v>
+        <v>608</v>
       </c>
     </row>
     <row r="155" s="1" customFormat="1" spans="2:5">
       <c r="B155" s="1" t="s">
-        <v>591</v>
+        <v>609</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>592</v>
+        <v>610</v>
       </c>
       <c r="D155" s="1">
         <v>100</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>593</v>
+        <v>611</v>
       </c>
     </row>
     <row r="156" s="1" customFormat="1" spans="2:5">
       <c r="B156" s="1" t="s">
-        <v>594</v>
+        <v>612</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>595</v>
+        <v>613</v>
       </c>
       <c r="D156" s="1">
         <v>100</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>596</v>
+        <v>614</v>
       </c>
     </row>
     <row r="157" s="1" customFormat="1" spans="2:5">
       <c r="B157" s="1" t="s">
-        <v>597</v>
+        <v>615</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>598</v>
+        <v>616</v>
       </c>
       <c r="D157" s="1">
         <v>100</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>599</v>
+        <v>617</v>
       </c>
     </row>
     <row r="158" s="1" customFormat="1" spans="2:5">
       <c r="B158" s="1" t="s">
-        <v>600</v>
+        <v>618</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>601</v>
+        <v>619</v>
       </c>
       <c r="D158" s="1">
         <v>100</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>602</v>
+        <v>620</v>
       </c>
     </row>
     <row r="159" s="1" customFormat="1" spans="2:5">
       <c r="B159" s="1" t="s">
-        <v>603</v>
+        <v>621</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>604</v>
+        <v>622</v>
       </c>
       <c r="D159" s="1">
         <v>100</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>605</v>
+        <v>623</v>
       </c>
     </row>
     <row r="160" s="1" customFormat="1" spans="2:5">
       <c r="B160" s="1" t="s">
-        <v>606</v>
+        <v>624</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>607</v>
+        <v>625</v>
       </c>
       <c r="D160" s="1">
         <v>100</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
     </row>
     <row r="161" s="1" customFormat="1" spans="2:5">
       <c r="B161" s="1" t="s">
-        <v>609</v>
+        <v>627</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>610</v>
+        <v>628</v>
       </c>
       <c r="D161" s="1">
         <v>100</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>611</v>
+        <v>629</v>
       </c>
     </row>
     <row r="162" s="1" customFormat="1" spans="2:5">
       <c r="B162" s="1" t="s">
-        <v>612</v>
+        <v>630</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>613</v>
+        <v>631</v>
       </c>
       <c r="D162" s="1">
         <v>100</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>614</v>
+        <v>632</v>
       </c>
     </row>
     <row r="163" s="1" customFormat="1" spans="2:5">
       <c r="B163" s="1" t="s">
-        <v>615</v>
+        <v>633</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>616</v>
+        <v>634</v>
       </c>
       <c r="D163" s="1">
         <v>100</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>617</v>
+        <v>635</v>
       </c>
     </row>
     <row r="164" s="1" customFormat="1" spans="2:5">
       <c r="B164" s="1" t="s">
-        <v>618</v>
+        <v>636</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>619</v>
+        <v>637</v>
       </c>
       <c r="D164" s="1">
         <v>100</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>620</v>
+        <v>638</v>
       </c>
     </row>
     <row r="165" s="1" customFormat="1" spans="2:5">
       <c r="B165" s="1" t="s">
-        <v>621</v>
+        <v>639</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>622</v>
+        <v>640</v>
       </c>
       <c r="D165" s="1">
         <v>100</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>623</v>
+        <v>641</v>
       </c>
     </row>
     <row r="166" s="1" customFormat="1" spans="2:5">
       <c r="B166" s="1" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="D166" s="1">
         <v>100</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -6721,82 +6846,82 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>624</v>
+        <v>642</v>
       </c>
       <c r="D1" t="s">
-        <v>625</v>
+        <v>643</v>
       </c>
       <c r="E1" t="s">
-        <v>626</v>
+        <v>644</v>
       </c>
       <c r="F1" t="s">
-        <v>627</v>
+        <v>645</v>
       </c>
       <c r="G1" t="s">
-        <v>628</v>
+        <v>646</v>
       </c>
       <c r="H1" t="s">
-        <v>629</v>
+        <v>647</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>630</v>
+        <v>648</v>
       </c>
       <c r="C2" t="s">
-        <v>631</v>
+        <v>649</v>
       </c>
       <c r="D2" t="s">
-        <v>632</v>
+        <v>650</v>
       </c>
       <c r="E2" t="s">
-        <v>633</v>
+        <v>651</v>
       </c>
       <c r="F2" t="s">
-        <v>634</v>
+        <v>652</v>
       </c>
       <c r="G2" t="s">
-        <v>635</v>
+        <v>653</v>
       </c>
       <c r="H2" t="s">
-        <v>636</v>
+        <v>654</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>637</v>
+        <v>655</v>
       </c>
       <c r="D3" t="s">
-        <v>637</v>
+        <v>655</v>
       </c>
       <c r="E3" t="s">
-        <v>637</v>
+        <v>655</v>
       </c>
       <c r="F3" t="s">
-        <v>637</v>
+        <v>655</v>
       </c>
       <c r="G3" t="s">
-        <v>637</v>
+        <v>655</v>
       </c>
       <c r="H3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s">
-        <v>638</v>
+        <v>656</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -6816,10 +6941,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="B5" t="s">
-        <v>639</v>
+        <v>657</v>
       </c>
       <c r="C5">
         <v>95</v>
@@ -6839,10 +6964,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="C6">
         <v>80</v>
@@ -6862,10 +6987,10 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="B7" t="s">
-        <v>640</v>
+        <v>658</v>
       </c>
       <c r="C7">
         <v>1000</v>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15340"/>
+    <workbookView windowHeight="15280"/>
   </bookViews>
   <sheets>
     <sheet name="action" sheetId="1" r:id="rId1"/>
@@ -127,7 +127,7 @@
     <t>None</t>
   </si>
   <si>
-    <t>金币奖励</t>
+    <t>金币</t>
   </si>
   <si>
     <t>完成营业额外得
@@ -140,11 +140,11 @@
     <t>food_fragment</t>
   </si>
   <si>
-    <t>餐桌碎片包</t>
+    <t>餐桌格</t>
   </si>
   <si>
     <t>完成营业额外得
-餐桌格子3选1</t>
+餐桌格3选1</t>
   </si>
   <si>
     <t>act_food_passive</t>
@@ -153,7 +153,7 @@
     <t>food_passive</t>
   </si>
   <si>
-    <t>被动道具</t>
+    <t>道具</t>
   </si>
   <si>
     <t>完成营业额外得
@@ -166,7 +166,7 @@
     <t>food_active_strengthen</t>
   </si>
   <si>
-    <t>强化主动道具</t>
+    <t>强化箱</t>
   </si>
   <si>
     <t>完成营业额外得
@@ -179,7 +179,7 @@
     <t>food_active_ajust</t>
   </si>
   <si>
-    <t>调整主动道具</t>
+    <t>调整单</t>
   </si>
   <si>
     <t>完成营业额外得
@@ -206,7 +206,7 @@
   </si>
   <si>
     <t>完成营业额外得
-更大的餐桌格子3选1</t>
+更大的餐桌格3选1</t>
   </si>
   <si>
     <t>act_food_hard_passive</t>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15280"/>
+    <workbookView windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="action" sheetId="1" r:id="rId1"/>
@@ -127,11 +127,10 @@
     <t>None</t>
   </si>
   <si>
-    <t>金币</t>
-  </si>
-  <si>
-    <t>完成营业额外得
-一些金币</t>
+    <t>一些金币</t>
+  </si>
+  <si>
+    <t>用于商店采购</t>
   </si>
   <si>
     <t>act_food_fragment</t>
@@ -143,8 +142,7 @@
     <t>餐桌格</t>
   </si>
   <si>
-    <t>完成营业额外得
-餐桌格3选1</t>
+    <t>扩大餐桌大小</t>
   </si>
   <si>
     <t>act_food_passive</t>
@@ -153,11 +151,10 @@
     <t>food_passive</t>
   </si>
   <si>
-    <t>道具</t>
-  </si>
-  <si>
-    <t>完成营业额外得
-道具2选1</t>
+    <t>道具2选1</t>
+  </si>
+  <si>
+    <t>带来持续性的增益</t>
   </si>
   <si>
     <t>act_food_active_strengthen</t>
@@ -166,11 +163,10 @@
     <t>food_active_strengthen</t>
   </si>
   <si>
-    <t>强化箱</t>
-  </si>
-  <si>
-    <t>完成营业额外得
-强化箱2选1</t>
+    <t>强化箱2选1</t>
+  </si>
+  <si>
+    <t>强化食物与餐桌格</t>
   </si>
   <si>
     <t>act_food_active_adjust</t>
@@ -179,11 +175,10 @@
     <t>food_active_ajust</t>
   </si>
   <si>
-    <t>调整单</t>
-  </si>
-  <si>
-    <t>完成营业额外得
-调整单2选1</t>
+    <t>调整单2选1</t>
+  </si>
+  <si>
+    <t>调整行动与时间轴</t>
   </si>
   <si>
     <t>act_food_hard_gold</t>
@@ -195,8 +190,7 @@
     <t>food_hard_gold</t>
   </si>
   <si>
-    <t>完成营业额外得
-大量金币</t>
+    <t>大量金币</t>
   </si>
   <si>
     <t>act_food_hard_fragment</t>
@@ -205,8 +199,7 @@
     <t>food_hard_fragment</t>
   </si>
   <si>
-    <t>完成营业额外得
-更大的餐桌格3选1</t>
+    <t>大餐桌格</t>
   </si>
   <si>
     <t>act_food_hard_passive</t>
@@ -215,8 +208,7 @@
     <t>food_hard_passive</t>
   </si>
   <si>
-    <t>完成营业额外得
-道具4选1</t>
+    <t>道具4选1</t>
   </si>
   <si>
     <t>act_food_hard_active_strengthen</t>
@@ -225,8 +217,7 @@
     <t>food_hard_active_strengthen</t>
   </si>
   <si>
-    <t>完成营业额外得
-强化箱4选1</t>
+    <t>强化箱4选1</t>
   </si>
   <si>
     <t>act_food_hard_active_adjust</t>
@@ -235,8 +226,7 @@
     <t>food_hard_active_ajust</t>
   </si>
   <si>
-    <t>完成营业额外得
-调整单4选1</t>
+    <t>调整单4选1</t>
   </si>
   <si>
     <t>act_event</t>
@@ -3247,7 +3237,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" ht="34" spans="2:13">
+    <row r="4" ht="17" spans="2:13">
       <c r="B4" s="1" t="s">
         <v>31</v>
       </c>
@@ -3279,7 +3269,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" ht="34" spans="2:13">
+    <row r="5" ht="17" spans="2:13">
       <c r="B5" s="1" t="s">
         <v>38</v>
       </c>
@@ -3311,7 +3301,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" ht="34" spans="2:13">
+    <row r="6" ht="17" spans="2:13">
       <c r="B6" s="1" t="s">
         <v>42</v>
       </c>
@@ -3343,7 +3333,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" s="4" customFormat="1" ht="34" spans="2:13">
+    <row r="7" s="4" customFormat="1" ht="17" spans="2:13">
       <c r="B7" s="4" t="s">
         <v>46</v>
       </c>
@@ -3376,7 +3366,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" s="4" customFormat="1" ht="34" spans="2:13">
+    <row r="8" s="4" customFormat="1" ht="17" spans="2:13">
       <c r="B8" s="4" t="s">
         <v>50</v>
       </c>
@@ -3409,7 +3399,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" ht="34" spans="2:13">
+    <row r="9" ht="17" spans="2:13">
       <c r="B9" s="1" t="s">
         <v>54</v>
       </c>
@@ -3435,13 +3425,13 @@
         <v>1.3</v>
       </c>
       <c r="L9" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" ht="34" spans="2:13">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" ht="17" spans="2:13">
       <c r="B10" s="1" t="s">
         <v>58</v>
       </c>
@@ -3467,13 +3457,13 @@
         <v>1.3</v>
       </c>
       <c r="L10" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" ht="34" spans="2:13">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" ht="17" spans="2:13">
       <c r="B11" s="1" t="s">
         <v>61</v>
       </c>
@@ -3499,13 +3489,13 @@
         <v>1.3</v>
       </c>
       <c r="L11" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" s="4" customFormat="1" ht="34" spans="2:13">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" s="4" customFormat="1" ht="17" spans="2:13">
       <c r="B12" s="4" t="s">
         <v>64</v>
       </c>
@@ -3532,13 +3522,13 @@
         <v>1.3</v>
       </c>
       <c r="L12" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" s="4" customFormat="1" ht="34" spans="2:13">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" s="4" customFormat="1" ht="17" spans="2:13">
       <c r="B13" s="4" t="s">
         <v>67</v>
       </c>
@@ -3565,10 +3555,10 @@
         <v>1.3</v>
       </c>
       <c r="L13" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="2:13">

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15300"/>
+    <workbookView windowHeight="15360" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="action" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="670">
   <si>
     <t>##var</t>
   </si>
@@ -332,7 +332,13 @@
     <t>ruleIds</t>
   </si>
   <si>
-    <t>fallbackWeights</t>
+    <t>*fallbackWeights</t>
+  </si>
+  <si>
+    <t>*minGuaranteeCounts</t>
+  </si>
+  <si>
+    <t>*maxGuaranteeCounts</t>
   </si>
   <si>
     <t>smallGroupIds</t>
@@ -344,16 +350,25 @@
     <t>大组名</t>
   </si>
   <si>
-    <t>参与的日程规则ID(逗号分隔),空=仅保底</t>
-  </si>
-  <si>
-    <t>随机权重列表(按周配)</t>
+    <t>兼容旧日程规则ID（当前大组随机逻辑不再使用）</t>
+  </si>
+  <si>
+    <t>随机权重（按周逐行配置）</t>
+  </si>
+  <si>
+    <t>最小保底累计次数（按周逐行；每格按行动用|分隔；-1=不限）</t>
+  </si>
+  <si>
+    <t>最大保底累计次数（按周逐行；每格按行动用|分隔；-1=不限）</t>
   </si>
   <si>
     <t>包含的小组ID列表→small_group.id</t>
   </si>
   <si>
-    <t>(list#sep=,),float</t>
+    <t>list,float</t>
+  </si>
+  <si>
+    <t>list,(list#sep=|),int</t>
   </si>
   <si>
     <t>(list#sep=|),string</t>
@@ -365,6 +380,12 @@
     <t>普通美食大组</t>
   </si>
   <si>
+    <t>1|1|1|1|2|2|2|2</t>
+  </si>
+  <si>
+    <t>1|2|2|2|2|3|3|3</t>
+  </si>
+  <si>
     <t>sg_normal_1|sg_normal_2|sg_normal_3|sg_normal_4|sg_normal_5|sg_normal_6|sg_normal_7|sg_normal_8|sg_normal_9|sg_normal_10|sg_normal_11|sg_normal_12|sg_normal_13|sg_normal_14|sg_normal_15|sg_normal_16|sg_normal_17|sg_normal_18|sg_normal_19|sg_normal_20</t>
   </si>
   <si>
@@ -374,6 +395,12 @@
     <t>普通困难美食大组</t>
   </si>
   <si>
+    <t>0|0|0|0|1|1|1|1</t>
+  </si>
+  <si>
+    <t>0|0|1|1|1|1|2|2</t>
+  </si>
+  <si>
     <t>sg_normalHard_1|sg_normalHard_2|sg_normalHard_3|sg_normalHard_4|sg_normalHard_5|sg_normalHard_6|sg_normalHard_7|sg_normalHard_8|sg_normalHard_9|sg_normalHard_10|sg_normalHard_11|sg_normalHard_12|sg_normalHard_13|sg_normalHard_14|sg_normalHard_15|sg_normalHard_16|sg_normalHard_17|sg_normalHard_18|sg_normalHard_19|sg_normalHard_20|sg_normalHard_21|sg_normalHard_22|sg_normalHard_23|sg_normalHard_24|sg_normalHard_25|sg_normalHard_26|sg_normalHard_27|sg_normalHard_28|sg_normalHard_29|sg_normalHard_30|sg_normalHard_31|sg_normalHard_32|sg_normalHard_33|sg_normalHard_34|sg_normalHard_35|sg_normalHard_36|sg_normalHard_37|sg_normalHard_38|sg_normalHard_39|sg_normalHard_40|sg_normalHard_41|sg_normalHard_42|sg_normalHard_43|sg_normalHard_44|sg_normalHard_45|sg_normalHard_46|sg_normalHard_47|sg_normalHard_48|sg_normalHard_49|sg_normalHard_50|sg_normalHard_51|sg_normalHard_52|sg_normalHard_53|sg_normalHard_54|sg_normalHard_55|sg_normalHard_56|sg_normalHard_57|sg_normalHard_58|sg_normalHard_59|sg_normalHard_60|sg_normalHard_61|sg_normalHard_62|sg_normalHard_63|sg_normalHard_64|sg_normalHard_65|sg_normalHard_66|sg_normalHard_67|sg_normalHard_68|sg_normalHard_69|sg_normalHard_70|sg_normalHard_71|sg_normalHard_72|sg_normalHard_73|sg_normalHard_74|sg_normalHard_75|sg_normalHard_76|sg_normalHard_77|sg_normalHard_78|sg_normalHard_79|sg_normalHard_80</t>
   </si>
   <si>
@@ -381,6 +408,12 @@
   </si>
   <si>
     <t>困难美食大组</t>
+  </si>
+  <si>
+    <t>0|0|0|0|0|0|0|0</t>
+  </si>
+  <si>
+    <t>0|0|0|0|0|1|1|1</t>
   </si>
   <si>
     <t>sg_hard_1|sg_hard_2|sg_hard_3|sg_hard_4|sg_hard_5|sg_hard_6|sg_hard_7|sg_hard_8|sg_hard_9|sg_hard_10|sg_hard_11|sg_hard_12|sg_hard_13|sg_hard_14|sg_hard_15|sg_hard_16|sg_hard_17|sg_hard_18|sg_hard_19|sg_hard_20</t>
@@ -3800,19 +3833,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:Q42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
     <col min="2" max="2" width="21.8461538461538" style="1" customWidth="1"/>
     <col min="3" max="3" width="24.8461538461538" style="1" customWidth="1"/>
     <col min="4" max="4" width="43.3076923076923" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.8461538461538" style="1" customWidth="1"/>
-    <col min="6" max="6" width="37.5384615384615" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="24" style="1" customWidth="1"/>
+    <col min="6" max="7" width="44" style="1" customWidth="1"/>
+    <col min="8" max="8" width="37.5384615384615" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3828,31 +3862,43 @@
       <c r="E1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:6">
+      <c r="G1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:6">
+        <v>112</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -3866,237 +3912,579 @@
         <v>27</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="2:12">
+        <v>115</v>
+      </c>
+      <c r="F3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="2:14">
       <c r="B4" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E4" s="2" t="str">
-        <f t="shared" ref="E4:E10" si="0">_xlfn.TEXTJOIN(",",TRUE,I4:L4)</f>
-        <v>400,300,200,150</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G4" s="1" t="str">
-        <f t="shared" ref="G4:G10" si="1">""</f>
+        <v>119</v>
+      </c>
+      <c r="E4" s="2">
+        <v>400</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I4" s="1" t="str">
+        <f>""</f>
         <v/>
       </c>
-      <c r="I4" s="1">
+      <c r="K4" s="1">
         <v>400</v>
       </c>
-      <c r="J4" s="1">
+      <c r="L4" s="1">
         <v>300</v>
       </c>
-      <c r="K4" s="1">
+      <c r="M4" s="1">
         <v>200</v>
       </c>
-      <c r="L4" s="1">
+      <c r="N4" s="1">
         <v>150</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="2:12">
-      <c r="B5" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E5" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>200,200,250,200</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="G5" s="1" t="str">
-        <f t="shared" si="1"/>
+    <row r="5" s="1" customFormat="1" spans="5:8">
+      <c r="E5" s="2">
+        <v>300</v>
+      </c>
+      <c r="F5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="5:8">
+      <c r="E6" s="2">
+        <v>200</v>
+      </c>
+      <c r="F6" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="5:8">
+      <c r="E7" s="2">
+        <v>150</v>
+      </c>
+      <c r="F7" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="2:14">
+      <c r="B8" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E8" s="2">
+        <v>200</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I8" s="1" t="str">
+        <f>""</f>
         <v/>
       </c>
-      <c r="I5" s="1">
+      <c r="K8" s="1">
         <v>200</v>
       </c>
-      <c r="J5" s="1">
+      <c r="L8" s="1">
         <v>200</v>
       </c>
-      <c r="K5" s="1">
+      <c r="M8" s="1">
         <v>250</v>
       </c>
-      <c r="L5" s="1">
+      <c r="N8" s="1">
         <v>200</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="2:15">
-      <c r="B6" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C6" s="1" t="s">
+    <row r="9" s="1" customFormat="1" spans="5:8">
+      <c r="E9" s="2">
+        <v>200</v>
+      </c>
+      <c r="F9" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G9" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="5:8">
+      <c r="E10" s="2">
+        <v>250</v>
+      </c>
+      <c r="F10" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G10" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="5:8">
+      <c r="E11" s="2">
+        <v>300</v>
+      </c>
+      <c r="F11" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G11" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="2:17">
+      <c r="B12" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="I12" s="1" t="str">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>50</v>
+      </c>
+      <c r="M12" s="1">
+        <v>100</v>
+      </c>
+      <c r="N12" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="5:8">
+      <c r="E13" s="2">
+        <v>50</v>
+      </c>
+      <c r="F13" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G13" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="5:8">
+      <c r="E14" s="2">
+        <v>100</v>
+      </c>
+      <c r="F14" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G14" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="5:8">
+      <c r="E15" s="2">
+        <v>200</v>
+      </c>
+      <c r="F15" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G15" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="2:17">
+      <c r="B16" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E16" s="2">
+        <v>100</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E6" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>0,50,100,200</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G6" s="1" t="str">
-        <f t="shared" si="1"/>
+      <c r="H16" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="I16" s="1" t="str">
+        <f>""</f>
         <v/>
       </c>
-      <c r="I6" s="1">
+      <c r="K16" s="1">
+        <v>100</v>
+      </c>
+      <c r="L16" s="1">
+        <v>100</v>
+      </c>
+      <c r="M16" s="1">
+        <v>100</v>
+      </c>
+      <c r="N16" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="5:8">
+      <c r="E17" s="2">
+        <v>100</v>
+      </c>
+      <c r="F17" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G17" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="5:8">
+      <c r="E18" s="2">
+        <v>100</v>
+      </c>
+      <c r="F18" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G18" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H18" s="3"/>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="5:8">
+      <c r="E19" s="2">
+        <v>100</v>
+      </c>
+      <c r="F19" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G19" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="2:14">
+      <c r="B20" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E20" s="2">
+        <v>150</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I20" s="1" t="str">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="K20" s="1">
+        <v>150</v>
+      </c>
+      <c r="L20" s="1">
+        <v>150</v>
+      </c>
+      <c r="M20" s="1">
+        <v>100</v>
+      </c>
+      <c r="N20" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="5:8">
+      <c r="E21" s="2">
+        <v>150</v>
+      </c>
+      <c r="F21" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G21" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="5:8">
+      <c r="E22" s="2">
+        <v>100</v>
+      </c>
+      <c r="F22" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G22" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="5:8">
+      <c r="E23" s="2">
+        <v>100</v>
+      </c>
+      <c r="F23" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G23" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H23" s="3"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="2:14">
+      <c r="B24" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E24" s="2">
+        <v>100</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="I24" s="1" t="str">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="K24" s="1">
+        <v>100</v>
+      </c>
+      <c r="L24" s="1">
+        <v>100</v>
+      </c>
+      <c r="M24" s="1">
+        <v>100</v>
+      </c>
+      <c r="N24" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="5:8">
+      <c r="E25" s="2">
+        <v>100</v>
+      </c>
+      <c r="F25" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G25" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H25" s="3"/>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="5:8">
+      <c r="E26" s="2">
+        <v>100</v>
+      </c>
+      <c r="F26" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G26" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H26" s="3"/>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="5:8">
+      <c r="E27" s="2">
+        <v>100</v>
+      </c>
+      <c r="F27" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G27" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H27" s="3"/>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="2:14">
+      <c r="B28" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E28" s="2">
         <v>0</v>
       </c>
-      <c r="J6" s="1">
+      <c r="F28" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="I28" s="1" t="str">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1">
         <v>50</v>
       </c>
-      <c r="K6" s="1">
-        <v>100</v>
-      </c>
-      <c r="L6" s="1">
-        <v>200</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="2:15">
-      <c r="B7" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E7" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>100,100,100,100</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="G7" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I7" s="1">
-        <v>100</v>
-      </c>
-      <c r="J7" s="1">
-        <v>100</v>
-      </c>
-      <c r="K7" s="1">
-        <v>100</v>
-      </c>
-      <c r="L7" s="1">
-        <v>100</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="2:12">
-      <c r="B8" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E8" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>150,150,100,100</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="G8" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I8" s="1">
-        <v>150</v>
-      </c>
-      <c r="J8" s="1">
-        <v>150</v>
-      </c>
-      <c r="K8" s="1">
-        <v>100</v>
-      </c>
-      <c r="L8" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="2:12">
-      <c r="B9" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E9" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>100,100,100,100</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="G9" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I9" s="1">
-        <v>100</v>
-      </c>
-      <c r="J9" s="1">
-        <v>100</v>
-      </c>
-      <c r="K9" s="1">
-        <v>100</v>
-      </c>
-      <c r="L9" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="2:12">
-      <c r="B10" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E10" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>0,50,100,100</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="G10" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I10" s="1">
-        <v>0</v>
-      </c>
-      <c r="J10" s="1">
+      <c r="M28" s="1">
+        <v>100</v>
+      </c>
+      <c r="N28" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="5:7">
+      <c r="E29" s="2">
         <v>50</v>
       </c>
-      <c r="K10" s="1">
-        <v>100</v>
-      </c>
-      <c r="L10" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="5:5">
-      <c r="E11" s="2"/>
+      <c r="F29" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G29" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="5:7">
+      <c r="E30" s="2">
+        <v>100</v>
+      </c>
+      <c r="F30" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G30" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="5:7">
+      <c r="E31" s="2">
+        <v>100</v>
+      </c>
+      <c r="F31" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G31" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="5:7">
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+    </row>
+    <row r="33" s="1" customFormat="1" spans="5:7">
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+    </row>
+    <row r="34" s="1" customFormat="1" spans="5:7">
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+    </row>
+    <row r="35" s="1" customFormat="1" spans="5:7">
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+    </row>
+    <row r="36" s="1" customFormat="1" spans="5:7">
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="5:7">
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+    </row>
+    <row r="38" s="1" customFormat="1" spans="5:7">
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="5:7">
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+    </row>
+    <row r="40" s="1" customFormat="1" spans="5:7">
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+    </row>
+    <row r="41" s="1" customFormat="1" spans="5:7">
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+    </row>
+    <row r="42" s="1" customFormat="1" spans="5:7">
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4137,10 +4525,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:5">
@@ -4148,16 +4536,16 @@
         <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:5">
@@ -4174,316 +4562,316 @@
         <v>30</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="2:5">
       <c r="B4" s="1" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="D4" s="1">
         <v>100</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="2:18">
       <c r="B5" s="1" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D5" s="1">
         <v>100</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="2:18">
       <c r="B6" s="1" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="D6" s="1">
         <v>100</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="2:18">
       <c r="B7" s="1" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="D7" s="1">
         <v>100</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="2:5">
       <c r="B8" s="1" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="2:5">
       <c r="B9" s="1" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="2:5">
       <c r="B10" s="1" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="2:5">
       <c r="B11" s="1" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="D11" s="1">
         <v>100</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="2:5">
       <c r="B12" s="1" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="D12" s="1">
         <v>100</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="2:5">
       <c r="B13" s="1" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D13" s="1">
         <v>100</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="2:13">
       <c r="B14" s="1" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D14" s="1">
         <v>100</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="2:13">
       <c r="B15" s="1" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="D15" s="1">
         <v>100</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="2:13">
       <c r="B16" s="1" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="D16" s="1">
         <v>100</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="2:13">
       <c r="B17" s="1" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="D17" s="1">
         <v>100</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="2:13">
       <c r="B18" s="1" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="D18" s="1">
         <v>100</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="2:13">
       <c r="B19" s="1" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="D19" s="1">
         <v>100</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="2:13">
       <c r="B20" s="1" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="D20" s="1">
         <v>100</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="2:20">
       <c r="B21" s="1" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="D21" s="1">
         <v>100</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>31</v>
@@ -4497,22 +4885,22 @@
     </row>
     <row r="22" s="1" customFormat="1" spans="2:20">
       <c r="B22" s="1" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="D22" s="1">
         <v>100</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>31</v>
@@ -4526,16 +4914,16 @@
     </row>
     <row r="23" s="1" customFormat="1" spans="2:20">
       <c r="B23" s="1" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="D23" s="1">
         <v>100</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="R23" s="1" t="s">
         <v>31</v>
@@ -4549,16 +4937,16 @@
     </row>
     <row r="24" s="1" customFormat="1" spans="2:20">
       <c r="B24" s="1" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="D24" s="1">
         <v>100</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="R24" s="1" t="s">
         <v>31</v>
@@ -4572,16 +4960,16 @@
     </row>
     <row r="25" s="1" customFormat="1" spans="2:20">
       <c r="B25" s="1" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="D25" s="1">
         <v>100</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>31</v>
@@ -4595,16 +4983,16 @@
     </row>
     <row r="26" s="1" customFormat="1" spans="2:20">
       <c r="B26" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D26" s="1">
         <v>100</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>31</v>
@@ -4618,16 +5006,16 @@
     </row>
     <row r="27" s="1" customFormat="1" spans="2:20">
       <c r="B27" s="1" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="D27" s="1">
         <v>100</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="R27" s="1" t="s">
         <v>38</v>
@@ -4641,16 +5029,16 @@
     </row>
     <row r="28" s="1" customFormat="1" spans="2:20">
       <c r="B28" s="1" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="D28" s="1">
         <v>100</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="R28" s="1" t="s">
         <v>38</v>
@@ -4664,16 +5052,16 @@
     </row>
     <row r="29" s="1" customFormat="1" spans="2:20">
       <c r="B29" s="1" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="D29" s="1">
         <v>100</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="R29" s="1" t="s">
         <v>38</v>
@@ -4687,16 +5075,16 @@
     </row>
     <row r="30" s="1" customFormat="1" spans="2:20">
       <c r="B30" s="1" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="D30" s="1">
         <v>100</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="R30" s="1" t="s">
         <v>42</v>
@@ -4710,16 +5098,16 @@
     </row>
     <row r="31" s="1" customFormat="1" spans="2:19">
       <c r="B31" s="1" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D31" s="1">
         <v>100</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="R31" s="1" t="s">
         <v>31</v>
@@ -4730,16 +5118,16 @@
     </row>
     <row r="32" s="1" customFormat="1" spans="2:19">
       <c r="B32" s="1" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D32" s="1">
         <v>100</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>31</v>
@@ -4750,16 +5138,16 @@
     </row>
     <row r="33" s="1" customFormat="1" spans="2:19">
       <c r="B33" s="1" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D33" s="1">
         <v>100</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="R33" s="1" t="s">
         <v>31</v>
@@ -4770,16 +5158,16 @@
     </row>
     <row r="34" s="1" customFormat="1" spans="2:19">
       <c r="B34" s="1" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="D34" s="1">
         <v>100</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="R34" s="1" t="s">
         <v>31</v>
@@ -4790,16 +5178,16 @@
     </row>
     <row r="35" s="1" customFormat="1" spans="2:19">
       <c r="B35" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D35" s="1">
         <v>100</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>38</v>
@@ -4810,16 +5198,16 @@
     </row>
     <row r="36" s="1" customFormat="1" spans="2:19">
       <c r="B36" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="D36" s="1">
         <v>100</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="R36" s="1" t="s">
         <v>38</v>
@@ -4830,16 +5218,16 @@
     </row>
     <row r="37" s="1" customFormat="1" spans="2:19">
       <c r="B37" s="1" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="D37" s="1">
         <v>100</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>31</v>
@@ -4853,16 +5241,16 @@
     </row>
     <row r="38" s="1" customFormat="1" spans="2:19">
       <c r="B38" s="1" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="D38" s="1">
         <v>100</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>38</v>
@@ -4876,16 +5264,16 @@
     </row>
     <row r="39" s="1" customFormat="1" spans="2:19">
       <c r="B39" s="1" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="D39" s="1">
         <v>100</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>42</v>
@@ -4899,16 +5287,16 @@
     </row>
     <row r="40" s="1" customFormat="1" spans="2:19">
       <c r="B40" s="1" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="D40" s="1">
         <v>100</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>46</v>
@@ -4922,16 +5310,16 @@
     </row>
     <row r="41" s="1" customFormat="1" spans="2:12">
       <c r="B41" s="1" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="D41" s="1">
         <v>100</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="L41" s="1" t="s">
         <v>50</v>
@@ -4939,30 +5327,30 @@
     </row>
     <row r="42" s="1" customFormat="1" spans="2:5">
       <c r="B42" s="1" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="D42" s="1">
         <v>100</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" spans="2:12">
       <c r="B43" s="1" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="D43" s="1">
         <v>100</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="L43" s="1" t="s">
         <v>54</v>
@@ -4970,16 +5358,16 @@
     </row>
     <row r="44" s="1" customFormat="1" spans="2:12">
       <c r="B44" s="1" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="D44" s="1">
         <v>100</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="L44" s="1" t="s">
         <v>58</v>
@@ -4987,16 +5375,16 @@
     </row>
     <row r="45" s="1" customFormat="1" spans="2:12">
       <c r="B45" s="1" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="D45" s="1">
         <v>100</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>61</v>
@@ -5004,16 +5392,16 @@
     </row>
     <row r="46" s="1" customFormat="1" spans="2:12">
       <c r="B46" s="1" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="D46" s="1">
         <v>100</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>64</v>
@@ -5021,16 +5409,16 @@
     </row>
     <row r="47" s="1" customFormat="1" spans="2:12">
       <c r="B47" s="1" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="D47" s="1">
         <v>100</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="L47" s="1" t="s">
         <v>67</v>
@@ -5038,16 +5426,16 @@
     </row>
     <row r="48" s="1" customFormat="1" spans="2:12">
       <c r="B48" s="1" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="D48" s="1">
         <v>100</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>70</v>
@@ -5055,16 +5443,16 @@
     </row>
     <row r="49" s="1" customFormat="1" spans="2:12">
       <c r="B49" s="1" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="D49" s="1">
         <v>100</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="L49" s="1" t="s">
         <v>73</v>
@@ -5072,414 +5460,414 @@
     </row>
     <row r="50" s="1" customFormat="1" spans="2:5">
       <c r="B50" s="1" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="D50" s="1">
         <v>100</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" spans="2:5">
       <c r="B51" s="1" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="D51" s="1">
         <v>100</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" spans="2:5">
       <c r="B52" s="1" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="D52" s="1">
         <v>100</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" spans="2:5">
       <c r="B53" s="1" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="D53" s="1">
         <v>100</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" spans="2:5">
       <c r="B54" s="1" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="D54" s="1">
         <v>100</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" spans="2:5">
       <c r="B55" s="1" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="D55" s="1">
         <v>100</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" spans="2:5">
       <c r="B56" s="1" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="D56" s="1">
         <v>100</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" spans="2:5">
       <c r="B57" s="1" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="D57" s="1">
         <v>100</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" spans="2:5">
       <c r="B58" s="1" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="D58" s="1">
         <v>100</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" spans="2:5">
       <c r="B59" s="1" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="D59" s="1">
         <v>100</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" spans="2:5">
       <c r="B60" s="1" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="D60" s="1">
         <v>100</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" spans="2:5">
       <c r="B61" s="1" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="D61" s="1">
         <v>100</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" spans="2:5">
       <c r="B62" s="1" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="D62" s="1">
         <v>100</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" spans="2:5">
       <c r="B63" s="1" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="D63" s="1">
         <v>100</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
     </row>
     <row r="64" s="1" customFormat="1" spans="2:5">
       <c r="B64" s="1" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="D64" s="1">
         <v>100</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
     </row>
     <row r="65" s="1" customFormat="1" spans="2:5">
       <c r="B65" s="1" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="D65" s="1">
         <v>100</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
     </row>
     <row r="66" s="1" customFormat="1" spans="2:5">
       <c r="B66" s="1" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="D66" s="1">
         <v>100</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="67" s="1" customFormat="1" spans="2:5">
       <c r="B67" s="1" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="D67" s="1">
         <v>100</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
     </row>
     <row r="68" s="1" customFormat="1" spans="2:5">
       <c r="B68" s="1" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="D68" s="1">
         <v>100</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="69" s="1" customFormat="1" spans="2:5">
       <c r="B69" s="1" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="D69" s="1">
         <v>100</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
     </row>
     <row r="70" s="1" customFormat="1" spans="2:5">
       <c r="B70" s="1" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="D70" s="1">
         <v>100</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
     </row>
     <row r="71" s="1" customFormat="1" spans="2:5">
       <c r="B71" s="1" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="D71" s="1">
         <v>100</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
     </row>
     <row r="72" s="1" customFormat="1" spans="2:5">
       <c r="B72" s="1" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="D72" s="1">
         <v>100</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" spans="2:5">
       <c r="B73" s="1" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="D73" s="1">
         <v>100</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="1" spans="2:5">
       <c r="B74" s="1" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="D74" s="1">
         <v>100</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="1" spans="2:5">
       <c r="B75" s="1" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="D75" s="1">
         <v>100</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
     </row>
     <row r="76" s="1" customFormat="1" spans="2:5">
       <c r="B76" s="1" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="D76" s="1">
         <v>100</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" spans="2:5">
       <c r="B77" s="1" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="D77" s="1">
         <v>100</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
     </row>
     <row r="78" s="1" customFormat="1" spans="2:20">
       <c r="B78" s="1" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="D78" s="1">
         <v>100</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="R78" s="1" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="S78" s="1">
         <v>80</v>
@@ -5490,16 +5878,16 @@
     </row>
     <row r="79" s="1" customFormat="1" spans="2:20">
       <c r="B79" s="1" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="D79" s="1">
         <v>100</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="T79" s="1" t="s">
         <v>46</v>
@@ -5507,16 +5895,16 @@
     </row>
     <row r="80" s="1" customFormat="1" spans="2:20">
       <c r="B80" s="1" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="D80" s="1">
         <v>100</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="T80" s="1" t="s">
         <v>50</v>
@@ -5524,22 +5912,22 @@
     </row>
     <row r="81" s="1" customFormat="1" spans="2:20">
       <c r="B81" s="1" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="D81" s="1">
         <v>100</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="Q81" s="1" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="R81" s="1" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="S81" s="1">
         <v>100</v>
@@ -5550,16 +5938,16 @@
     </row>
     <row r="82" s="1" customFormat="1" spans="2:20">
       <c r="B82" s="1" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="D82" s="1">
         <v>100</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="T82" s="1" t="s">
         <v>67</v>
@@ -5567,16 +5955,16 @@
     </row>
     <row r="83" s="1" customFormat="1" spans="2:20">
       <c r="B83" s="1" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="D83" s="1">
         <v>100</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="T83" s="1" t="s">
         <v>61</v>
@@ -5584,22 +5972,22 @@
     </row>
     <row r="84" s="1" customFormat="1" spans="2:20">
       <c r="B84" s="1" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="D84" s="1">
         <v>100</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="Q84" s="1" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="R84" s="1" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="S84" s="1">
         <v>80</v>
@@ -5610,16 +5998,16 @@
     </row>
     <row r="85" s="1" customFormat="1" spans="2:20">
       <c r="B85" s="1" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="D85" s="1">
         <v>100</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="T85" s="1" t="s">
         <v>64</v>
@@ -5627,16 +6015,16 @@
     </row>
     <row r="86" s="1" customFormat="1" spans="2:20">
       <c r="B86" s="1" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="D86" s="1">
         <v>100</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="T86" s="1" t="s">
         <v>67</v>
@@ -5644,22 +6032,22 @@
     </row>
     <row r="87" s="1" customFormat="1" spans="2:20">
       <c r="B87" s="1" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="D87" s="1">
         <v>100</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="Q87" s="1" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="R87" s="1" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="S87" s="1">
         <v>100</v>
@@ -5670,16 +6058,16 @@
     </row>
     <row r="88" s="1" customFormat="1" spans="2:20">
       <c r="B88" s="1" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="D88" s="1">
         <v>100</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="T88" s="1" t="s">
         <v>31</v>
@@ -5687,16 +6075,16 @@
     </row>
     <row r="89" s="1" customFormat="1" spans="2:20">
       <c r="B89" s="1" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="D89" s="1">
         <v>100</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="T89" s="1" t="s">
         <v>50</v>
@@ -5704,22 +6092,22 @@
     </row>
     <row r="90" s="1" customFormat="1" spans="2:20">
       <c r="B90" s="1" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="D90" s="1">
         <v>100</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="Q90" s="1" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="S90" s="1">
         <v>100</v>
@@ -5730,16 +6118,16 @@
     </row>
     <row r="91" s="1" customFormat="1" spans="2:20">
       <c r="B91" s="1" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="D91" s="1">
         <v>100</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="T91" s="1" t="s">
         <v>77</v>
@@ -5747,22 +6135,22 @@
     </row>
     <row r="92" s="1" customFormat="1" spans="2:20">
       <c r="B92" s="1" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="D92" s="1">
         <v>100</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="Q92" s="1" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="R92" s="1" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="S92" s="1">
         <v>100</v>
@@ -5773,444 +6161,444 @@
     </row>
     <row r="93" s="1" customFormat="1" spans="2:5">
       <c r="B93" s="1" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="D93" s="1">
         <v>100</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
     </row>
     <row r="94" s="1" customFormat="1" spans="2:5">
       <c r="B94" s="1" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="D94" s="1">
         <v>100</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" spans="2:5">
       <c r="B95" s="1" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="D95" s="1">
         <v>100</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
     </row>
     <row r="96" s="1" customFormat="1" spans="2:5">
       <c r="B96" s="1" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="D96" s="1">
         <v>100</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
     </row>
     <row r="97" s="1" customFormat="1" spans="2:5">
       <c r="B97" s="1" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="D97" s="1">
         <v>100</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
     </row>
     <row r="98" s="1" customFormat="1" spans="2:5">
       <c r="B98" s="1" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="D98" s="1">
         <v>100</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
     </row>
     <row r="99" s="1" customFormat="1" spans="2:5">
       <c r="B99" s="1" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="D99" s="1">
         <v>100</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
     </row>
     <row r="100" s="1" customFormat="1" spans="2:5">
       <c r="B100" s="1" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="D100" s="1">
         <v>100</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
     </row>
     <row r="101" s="1" customFormat="1" spans="2:5">
       <c r="B101" s="1" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="D101" s="1">
         <v>100</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
     </row>
     <row r="102" s="1" customFormat="1" spans="2:5">
       <c r="B102" s="1" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="D102" s="1">
         <v>100</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
     </row>
     <row r="103" s="1" customFormat="1" spans="2:5">
       <c r="B103" s="1" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="D103" s="1">
         <v>100</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
     </row>
     <row r="104" s="1" customFormat="1" spans="2:5">
       <c r="B104" s="1" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="D104" s="1">
         <v>100</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" spans="2:5">
       <c r="B105" s="1" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="D105" s="1">
         <v>100</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
     </row>
     <row r="106" s="1" customFormat="1" spans="2:5">
       <c r="B106" s="1" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="D106" s="1">
         <v>100</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
     </row>
     <row r="107" s="1" customFormat="1" spans="2:5">
       <c r="B107" s="1" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="D107" s="1">
         <v>100</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
     </row>
     <row r="108" s="1" customFormat="1" spans="2:5">
       <c r="B108" s="1" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="D108" s="1">
         <v>100</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
     </row>
     <row r="109" s="1" customFormat="1" spans="2:5">
       <c r="B109" s="1" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="D109" s="1">
         <v>100</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
     </row>
     <row r="110" s="1" customFormat="1" spans="2:5">
       <c r="B110" s="1" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="D110" s="1">
         <v>100</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
     </row>
     <row r="111" s="1" customFormat="1" spans="2:5">
       <c r="B111" s="1" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="D111" s="1">
         <v>100</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
     </row>
     <row r="112" s="1" customFormat="1" spans="2:5">
       <c r="B112" s="1" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="D112" s="1">
         <v>100</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
     </row>
     <row r="113" s="1" customFormat="1" spans="2:5">
       <c r="B113" s="1" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="D113" s="1">
         <v>100</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
     </row>
     <row r="114" s="1" customFormat="1" spans="2:5">
       <c r="B114" s="1" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="D114" s="1">
         <v>100</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
     </row>
     <row r="115" s="1" customFormat="1" spans="2:5">
       <c r="B115" s="1" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="D115" s="1">
         <v>100</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
     </row>
     <row r="116" s="1" customFormat="1" spans="2:5">
       <c r="B116" s="1" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="D116" s="1">
         <v>100</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
     </row>
     <row r="117" s="1" customFormat="1" spans="2:5">
       <c r="B117" s="1" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="D117" s="1">
         <v>100</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
     </row>
     <row r="118" s="1" customFormat="1" spans="2:5">
       <c r="B118" s="1" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="D118" s="1">
         <v>100</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
     </row>
     <row r="119" s="1" customFormat="1" spans="2:5">
       <c r="B119" s="1" t="s">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="D119" s="1">
         <v>100</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
     </row>
     <row r="120" s="1" customFormat="1" spans="2:5">
       <c r="B120" s="1" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="D120" s="1">
         <v>100</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
     </row>
     <row r="121" s="1" customFormat="1" spans="2:5">
       <c r="B121" s="1" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="D121" s="1">
         <v>100</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
     </row>
     <row r="122" s="1" customFormat="1" spans="2:5">
       <c r="B122" s="1" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="D122" s="1">
         <v>100</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
     </row>
     <row r="123" s="1" customFormat="1" spans="2:5">
       <c r="B123" s="1" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="D123" s="1">
         <v>100</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
     </row>
     <row r="124" s="1" customFormat="1" spans="2:5">
       <c r="B124" s="1" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="D124" s="1">
         <v>100</v>
@@ -6221,10 +6609,10 @@
     </row>
     <row r="125" s="1" customFormat="1" spans="2:5">
       <c r="B125" s="1" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="D125" s="1">
         <v>100</v>
@@ -6235,570 +6623,570 @@
     </row>
     <row r="126" s="1" customFormat="1" spans="2:5">
       <c r="B126" s="1" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="D126" s="1">
         <v>100</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
     </row>
     <row r="127" s="1" customFormat="1" spans="2:5">
       <c r="B127" s="1" t="s">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="D127" s="1">
         <v>100</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
     </row>
     <row r="128" s="1" customFormat="1" spans="2:5">
       <c r="B128" s="1" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="D128" s="1">
         <v>100</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>533</v>
+        <v>544</v>
       </c>
     </row>
     <row r="129" s="1" customFormat="1" spans="2:5">
       <c r="B129" s="1" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="D129" s="1">
         <v>100</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>536</v>
+        <v>547</v>
       </c>
     </row>
     <row r="130" s="1" customFormat="1" spans="2:5">
       <c r="B130" s="1" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="D130" s="1">
         <v>100</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
     </row>
     <row r="131" s="1" customFormat="1" spans="2:5">
       <c r="B131" s="1" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="D131" s="1">
         <v>100</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
     </row>
     <row r="132" s="1" customFormat="1" spans="2:5">
       <c r="B132" s="1" t="s">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="D132" s="1">
         <v>100</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>545</v>
+        <v>556</v>
       </c>
     </row>
     <row r="133" s="1" customFormat="1" spans="2:5">
       <c r="B133" s="1" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="D133" s="1">
         <v>100</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>548</v>
+        <v>559</v>
       </c>
     </row>
     <row r="134" s="1" customFormat="1" spans="2:5">
       <c r="B134" s="1" t="s">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="D134" s="1">
         <v>100</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>551</v>
+        <v>562</v>
       </c>
     </row>
     <row r="135" s="1" customFormat="1" spans="2:5">
       <c r="B135" s="1" t="s">
-        <v>552</v>
+        <v>563</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="D135" s="1">
         <v>100</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>554</v>
+        <v>565</v>
       </c>
     </row>
     <row r="136" s="1" customFormat="1" spans="2:5">
       <c r="B136" s="1" t="s">
-        <v>555</v>
+        <v>566</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="D136" s="1">
         <v>100</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
     </row>
     <row r="137" s="1" customFormat="1" spans="2:5">
       <c r="B137" s="1" t="s">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>559</v>
+        <v>570</v>
       </c>
       <c r="D137" s="1">
         <v>100</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>560</v>
+        <v>571</v>
       </c>
     </row>
     <row r="138" s="1" customFormat="1" spans="2:5">
       <c r="B138" s="1" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="D138" s="1">
         <v>100</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>563</v>
+        <v>574</v>
       </c>
     </row>
     <row r="139" s="1" customFormat="1" spans="2:5">
       <c r="B139" s="1" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>565</v>
+        <v>576</v>
       </c>
       <c r="D139" s="1">
         <v>100</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>566</v>
+        <v>577</v>
       </c>
     </row>
     <row r="140" s="1" customFormat="1" spans="2:5">
       <c r="B140" s="1" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>567</v>
+        <v>578</v>
       </c>
       <c r="D140" s="1">
         <v>100</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>568</v>
+        <v>579</v>
       </c>
     </row>
     <row r="141" s="1" customFormat="1" spans="2:5">
       <c r="B141" s="1" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>569</v>
+        <v>580</v>
       </c>
       <c r="D141" s="1">
         <v>100</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>570</v>
+        <v>581</v>
       </c>
     </row>
     <row r="142" s="1" customFormat="1" spans="2:5">
       <c r="B142" s="1" t="s">
-        <v>571</v>
+        <v>582</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>572</v>
+        <v>583</v>
       </c>
       <c r="D142" s="1">
         <v>100</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>573</v>
+        <v>584</v>
       </c>
     </row>
     <row r="143" s="1" customFormat="1" spans="2:5">
       <c r="B143" s="1" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>575</v>
+        <v>586</v>
       </c>
       <c r="D143" s="1">
         <v>100</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>576</v>
+        <v>587</v>
       </c>
     </row>
     <row r="144" s="1" customFormat="1" spans="2:5">
       <c r="B144" s="1" t="s">
-        <v>577</v>
+        <v>588</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="D144" s="1">
         <v>100</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>579</v>
+        <v>590</v>
       </c>
     </row>
     <row r="145" s="1" customFormat="1" spans="2:5">
       <c r="B145" s="1" t="s">
-        <v>580</v>
+        <v>591</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>581</v>
+        <v>592</v>
       </c>
       <c r="D145" s="1">
         <v>100</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>582</v>
+        <v>593</v>
       </c>
     </row>
     <row r="146" s="1" customFormat="1" spans="2:5">
       <c r="B146" s="1" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="D146" s="1">
         <v>100</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>585</v>
+        <v>596</v>
       </c>
     </row>
     <row r="147" s="1" customFormat="1" spans="2:5">
       <c r="B147" s="1" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>587</v>
+        <v>598</v>
       </c>
       <c r="D147" s="1">
         <v>100</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>588</v>
+        <v>599</v>
       </c>
     </row>
     <row r="148" s="1" customFormat="1" spans="2:5">
       <c r="B148" s="1" t="s">
-        <v>589</v>
+        <v>600</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>590</v>
+        <v>601</v>
       </c>
       <c r="D148" s="1">
         <v>100</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>591</v>
+        <v>602</v>
       </c>
     </row>
     <row r="149" s="1" customFormat="1" spans="2:5">
       <c r="B149" s="1" t="s">
-        <v>592</v>
+        <v>603</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>593</v>
+        <v>604</v>
       </c>
       <c r="D149" s="1">
         <v>100</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>594</v>
+        <v>605</v>
       </c>
     </row>
     <row r="150" s="1" customFormat="1" spans="2:5">
       <c r="B150" s="1" t="s">
-        <v>595</v>
+        <v>606</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>596</v>
+        <v>607</v>
       </c>
       <c r="D150" s="1">
         <v>100</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>597</v>
+        <v>608</v>
       </c>
     </row>
     <row r="151" s="1" customFormat="1" spans="2:5">
       <c r="B151" s="1" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>598</v>
+        <v>609</v>
       </c>
       <c r="D151" s="1">
         <v>100</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>599</v>
+        <v>610</v>
       </c>
     </row>
     <row r="152" s="1" customFormat="1" spans="2:5">
       <c r="B152" s="1" t="s">
-        <v>600</v>
+        <v>611</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>601</v>
+        <v>612</v>
       </c>
       <c r="D152" s="1">
         <v>100</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>602</v>
+        <v>613</v>
       </c>
     </row>
     <row r="153" s="1" customFormat="1" spans="2:5">
       <c r="B153" s="1" t="s">
-        <v>603</v>
+        <v>614</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>604</v>
+        <v>615</v>
       </c>
       <c r="D153" s="1">
         <v>100</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>605</v>
+        <v>616</v>
       </c>
     </row>
     <row r="154" s="1" customFormat="1" spans="2:5">
       <c r="B154" s="1" t="s">
-        <v>606</v>
+        <v>617</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>607</v>
+        <v>618</v>
       </c>
       <c r="D154" s="1">
         <v>100</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>608</v>
+        <v>619</v>
       </c>
     </row>
     <row r="155" s="1" customFormat="1" spans="2:5">
       <c r="B155" s="1" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>610</v>
+        <v>621</v>
       </c>
       <c r="D155" s="1">
         <v>100</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>611</v>
+        <v>622</v>
       </c>
     </row>
     <row r="156" s="1" customFormat="1" spans="2:5">
       <c r="B156" s="1" t="s">
-        <v>612</v>
+        <v>623</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>613</v>
+        <v>624</v>
       </c>
       <c r="D156" s="1">
         <v>100</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>614</v>
+        <v>625</v>
       </c>
     </row>
     <row r="157" s="1" customFormat="1" spans="2:5">
       <c r="B157" s="1" t="s">
-        <v>615</v>
+        <v>626</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>616</v>
+        <v>627</v>
       </c>
       <c r="D157" s="1">
         <v>100</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>617</v>
+        <v>628</v>
       </c>
     </row>
     <row r="158" s="1" customFormat="1" spans="2:5">
       <c r="B158" s="1" t="s">
-        <v>618</v>
+        <v>629</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>619</v>
+        <v>630</v>
       </c>
       <c r="D158" s="1">
         <v>100</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
     </row>
     <row r="159" s="1" customFormat="1" spans="2:5">
       <c r="B159" s="1" t="s">
-        <v>621</v>
+        <v>632</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>622</v>
+        <v>633</v>
       </c>
       <c r="D159" s="1">
         <v>100</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>623</v>
+        <v>634</v>
       </c>
     </row>
     <row r="160" s="1" customFormat="1" spans="2:5">
       <c r="B160" s="1" t="s">
-        <v>624</v>
+        <v>635</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>625</v>
+        <v>636</v>
       </c>
       <c r="D160" s="1">
         <v>100</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>626</v>
+        <v>637</v>
       </c>
     </row>
     <row r="161" s="1" customFormat="1" spans="2:5">
       <c r="B161" s="1" t="s">
-        <v>627</v>
+        <v>638</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>628</v>
+        <v>639</v>
       </c>
       <c r="D161" s="1">
         <v>100</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>629</v>
+        <v>640</v>
       </c>
     </row>
     <row r="162" s="1" customFormat="1" spans="2:5">
       <c r="B162" s="1" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>631</v>
+        <v>642</v>
       </c>
       <c r="D162" s="1">
         <v>100</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>632</v>
+        <v>643</v>
       </c>
     </row>
     <row r="163" s="1" customFormat="1" spans="2:5">
       <c r="B163" s="1" t="s">
-        <v>633</v>
+        <v>644</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>634</v>
+        <v>645</v>
       </c>
       <c r="D163" s="1">
         <v>100</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>635</v>
+        <v>646</v>
       </c>
     </row>
     <row r="164" s="1" customFormat="1" spans="2:5">
       <c r="B164" s="1" t="s">
-        <v>636</v>
+        <v>647</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>637</v>
+        <v>648</v>
       </c>
       <c r="D164" s="1">
         <v>100</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>638</v>
+        <v>649</v>
       </c>
     </row>
     <row r="165" s="1" customFormat="1" spans="2:5">
       <c r="B165" s="1" t="s">
-        <v>639</v>
+        <v>650</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>640</v>
+        <v>651</v>
       </c>
       <c r="D165" s="1">
         <v>100</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>641</v>
+        <v>652</v>
       </c>
     </row>
     <row r="166" s="1" customFormat="1" spans="2:5">
       <c r="B166" s="1" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="D166" s="1">
         <v>100</v>
@@ -6836,22 +7224,22 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="D1" t="s">
-        <v>643</v>
+        <v>654</v>
       </c>
       <c r="E1" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="F1" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="G1" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="H1" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6859,25 +7247,25 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>648</v>
+        <v>659</v>
       </c>
       <c r="C2" t="s">
-        <v>649</v>
+        <v>660</v>
       </c>
       <c r="D2" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="E2" t="s">
-        <v>651</v>
+        <v>662</v>
       </c>
       <c r="F2" t="s">
-        <v>652</v>
+        <v>663</v>
       </c>
       <c r="G2" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="H2" t="s">
-        <v>654</v>
+        <v>665</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6888,19 +7276,19 @@
         <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="D3" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="E3" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="F3" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="G3" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="H3" t="s">
         <v>27</v>
@@ -6911,7 +7299,7 @@
         <v>89</v>
       </c>
       <c r="B4" t="s">
-        <v>656</v>
+        <v>667</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -6934,7 +7322,7 @@
         <v>89</v>
       </c>
       <c r="B5" t="s">
-        <v>657</v>
+        <v>668</v>
       </c>
       <c r="C5">
         <v>95</v>
@@ -6957,7 +7345,7 @@
         <v>89</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="C6">
         <v>80</v>
@@ -6980,7 +7368,7 @@
         <v>89</v>
       </c>
       <c r="B7" t="s">
-        <v>658</v>
+        <v>669</v>
       </c>
       <c r="C7">
         <v>1000</v>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -4076,7 +4076,7 @@
         <v>129</v>
       </c>
       <c r="E12" s="2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>130</v>
@@ -4109,7 +4109,7 @@
     </row>
     <row r="13" s="1" customFormat="1" spans="5:8">
       <c r="E13" s="2">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F13" s="2">
         <v>-1</v>
@@ -4370,7 +4370,7 @@
         <v>145</v>
       </c>
       <c r="E28" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>130</v>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="action" sheetId="1" r:id="R6c6bc2a6c2494778"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="large_group" sheetId="2" r:id="Rb6723b9641f74f05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="small_group" sheetId="3" r:id="Re0af9eb9d24f43e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="action" sheetId="1" r:id="R88c3276b39d4456f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="large_group" sheetId="2" r:id="R81e1915cfcfc436a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="small_group" sheetId="3" r:id="R8c7627cfb6a04fe2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -284,9 +284,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">偿还高利贷</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">扣除400金币</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Effect</x:t>
@@ -3570,17 +3567,17 @@
       <x:c r="C20" s="1" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="D20" s="1" t="s">
+      <x:c r="D20" s="1" t="str">
+        <x:v>扣除200金币</x:v>
+      </x:c>
+      <x:c r="E20" s="1" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="E20" s="1" t="s">
+      <x:c r="G20" s="1" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="G20" s="1" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="H20" s="1">
-        <x:v>-400</x:v>
+      <x:c r="H20" s="1" t="n">
+        <x:v>-200</x:v>
       </x:c>
       <x:c r="I20"/>
       <x:c r="J20" s="1">
@@ -3594,19 +3591,19 @@
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="C21" s="1" t="s">
+      <x:c r="D21" s="1" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="D21" s="1" t="s">
+      <x:c r="E21" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G21" s="1" t="s">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="E21" s="1" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="G21" s="1" t="s">
-        <x:v>97</x:v>
       </x:c>
       <x:c r="H21" s="1">
         <x:v>0</x:v>
@@ -3661,16 +3658,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="F1" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="F1" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="G1" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H1" s="1"/>
       <x:c r="I1"/>
@@ -3687,22 +3684,22 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s">
+      <x:c r="D2" s="1" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="D2" s="1" t="s">
+      <x:c r="E2" s="1" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="E2" s="1" t="s">
+      <x:c r="F2" s="1" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="F2" s="1" t="s">
+      <x:c r="G2" s="1" t="s">
         <x:v>106</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>107</x:v>
       </x:c>
       <x:c r="H2" s="1"/>
       <x:c r="I2"/>
@@ -3725,16 +3722,16 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="E3" s="1" t="s">
+      <x:c r="F3" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G3" t="s">
         <x:v>109</x:v>
-      </x:c>
-      <x:c r="F3" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="G3" t="s">
-        <x:v>110</x:v>
       </x:c>
       <x:c r="H3" s="1"/>
       <x:c r="I3"/>
@@ -3748,22 +3745,22 @@
     </x:row>
     <x:row r="4" s="1" customFormat="1">
       <x:c r="B4" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
         <x:v>111</x:v>
-      </x:c>
-      <x:c r="C4" s="1" t="s">
-        <x:v>112</x:v>
       </x:c>
       <x:c r="D4">
         <x:v>400</x:v>
       </x:c>
       <x:c r="E4" s="2" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="F4" s="2" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="F4" s="2" t="s">
+      <x:c r="G4" s="2" t="s">
         <x:v>114</x:v>
-      </x:c>
-      <x:c r="G4" s="2" t="s">
-        <x:v>115</x:v>
       </x:c>
       <x:c r="H4" s="3" t="str">
         <x:f>""</x:f>
@@ -3850,22 +3847,22 @@
     </x:row>
     <x:row r="8" s="1" customFormat="1">
       <x:c r="B8" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
         <x:v>116</x:v>
-      </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>117</x:v>
       </x:c>
       <x:c r="D8">
         <x:v>200</x:v>
       </x:c>
       <x:c r="E8" s="2" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="F8" s="2" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="F8" s="2" t="s">
+      <x:c r="G8" s="2" t="s">
         <x:v>119</x:v>
-      </x:c>
-      <x:c r="G8" s="2" t="s">
-        <x:v>120</x:v>
       </x:c>
       <x:c r="H8" s="3" t="str">
         <x:f>""</x:f>
@@ -3952,22 +3949,22 @@
     </x:row>
     <x:row r="12" s="1" customFormat="1">
       <x:c r="B12" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="C12" s="1" t="s">
+      <x:c r="D12">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E12" s="2" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="D12">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E12" s="2" t="s">
+      <x:c r="F12" s="2" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F12" s="2" t="s">
+      <x:c r="G12" s="2" t="s">
         <x:v>124</x:v>
-      </x:c>
-      <x:c r="G12" s="2" t="s">
-        <x:v>125</x:v>
       </x:c>
       <x:c r="H12" s="3" t="str">
         <x:f>""</x:f>
@@ -4055,22 +4052,22 @@
     </x:row>
     <x:row r="16" s="1" customFormat="1">
       <x:c r="B16" s="1" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="C16" s="1" t="s">
+      <x:c r="D16">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E16" s="2" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F16" s="2" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G16" s="2" t="s">
         <x:v>127</x:v>
-      </x:c>
-      <x:c r="D16">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E16" s="2" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="F16" s="2" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="G16" s="2" t="s">
-        <x:v>128</x:v>
       </x:c>
       <x:c r="H16" s="3" t="str">
         <x:f>""</x:f>
@@ -4158,22 +4155,22 @@
     </x:row>
     <x:row r="20" s="1" customFormat="1">
       <x:c r="B20" s="1" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
         <x:v>129</x:v>
-      </x:c>
-      <x:c r="C20" s="1" t="s">
-        <x:v>130</x:v>
       </x:c>
       <x:c r="D20">
         <x:v>150</x:v>
       </x:c>
       <x:c r="E20" s="2" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="F20" s="2" t="s">
-        <x:v>113</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G20" s="2" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="H20" s="3" t="str">
         <x:f>""</x:f>
@@ -4260,22 +4257,22 @@
     </x:row>
     <x:row r="24" s="1" customFormat="1">
       <x:c r="B24" s="1" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="C24" s="1" t="s">
+      <x:c r="D24">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E24" s="2" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F24" s="2" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G24" s="2" t="s">
         <x:v>133</x:v>
-      </x:c>
-      <x:c r="D24">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E24" s="2" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="F24" s="2" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="G24" s="2" t="s">
-        <x:v>134</x:v>
       </x:c>
       <x:c r="H24" s="3" t="str">
         <x:f>""</x:f>
@@ -4362,22 +4359,22 @@
     </x:row>
     <x:row r="28" s="1" customFormat="1">
       <x:c r="B28" s="1" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="C28" s="1" t="s">
         <x:v>135</x:v>
-      </x:c>
-      <x:c r="C28" s="1" t="s">
-        <x:v>136</x:v>
       </x:c>
       <x:c r="D28">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E28" s="2" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="F28" s="2" t="s">
-        <x:v>113</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G28" s="2" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H28" s="3" t="str">
         <x:f>""</x:f>
@@ -4553,10 +4550,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
         <x:v>138</x:v>
-      </x:c>
-      <x:c r="E1" s="1" t="s">
-        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="2" s="1" customFormat="1">
@@ -4564,16 +4561,16 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s">
+      <x:c r="D2" s="1" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="D2" s="1" t="s">
+      <x:c r="E2" s="1" t="s">
         <x:v>142</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1">
@@ -4590,316 +4587,316 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="1" customFormat="1">
       <x:c r="B4" s="1" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="C4" s="1" t="s">
+      <x:c r="D4" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="s">
         <x:v>145</x:v>
-      </x:c>
-      <x:c r="D4" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1">
       <x:c r="B5" s="1" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="s">
+      <x:c r="D5" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="D5" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E5" s="1" t="s">
+      <x:c r="R5" s="1" t="s">
         <x:v>149</x:v>
-      </x:c>
-      <x:c r="R5" s="1" t="s">
-        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1">
       <x:c r="B6" s="1" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
+      <x:c r="D6" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="D6" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="s">
+      <x:c r="R6" s="1" t="s">
         <x:v>153</x:v>
-      </x:c>
-      <x:c r="R6" s="1" t="s">
-        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1">
       <x:c r="B7" s="1" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="C7" s="1" t="s">
+      <x:c r="D7" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="D7" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E7" s="1" t="s">
+      <x:c r="R7" s="1" t="s">
         <x:v>157</x:v>
-      </x:c>
-      <x:c r="R7" s="1" t="s">
-        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="1" customFormat="1">
       <x:c r="B8" s="1" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="C8" s="1" t="s">
+      <x:c r="D8" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E8" s="1" t="s">
         <x:v>160</x:v>
-      </x:c>
-      <x:c r="D8" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E8" s="1" t="s">
-        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="1" customFormat="1">
       <x:c r="B9" s="1" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="C9" s="1" t="s">
+      <x:c r="D9" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
         <x:v>163</x:v>
-      </x:c>
-      <x:c r="D9" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="1" customFormat="1">
       <x:c r="B10" s="1" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="C10" s="1" t="s">
+      <x:c r="D10" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E10" s="1" t="s">
         <x:v>166</x:v>
-      </x:c>
-      <x:c r="D10" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="1" customFormat="1">
       <x:c r="B11" s="1" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="C11" s="1" t="s">
+      <x:c r="D11" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
         <x:v>169</x:v>
-      </x:c>
-      <x:c r="D11" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="1" customFormat="1">
       <x:c r="B12" s="1" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="C12" s="1" t="s">
+      <x:c r="D12" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
         <x:v>172</x:v>
-      </x:c>
-      <x:c r="D12" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="1" customFormat="1">
       <x:c r="B13" s="1" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="C13" s="1" t="s">
+      <x:c r="D13" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="s">
         <x:v>175</x:v>
-      </x:c>
-      <x:c r="D13" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="14" s="1" customFormat="1">
       <x:c r="B14" s="1" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="C14" s="1" t="s">
+      <x:c r="D14" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="D14" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>179</x:v>
-      </x:c>
       <x:c r="L14" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="M14" s="1" t="s">
         <x:v>111</x:v>
-      </x:c>
-      <x:c r="M14" s="1" t="s">
-        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="15" s="1" customFormat="1">
       <x:c r="B15" s="1" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="C15" s="1" t="s">
+      <x:c r="D15" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="D15" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>182</x:v>
-      </x:c>
       <x:c r="L15" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="M15" s="1" t="s">
         <x:v>116</x:v>
-      </x:c>
-      <x:c r="M15" s="1" t="s">
-        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="16" s="1" customFormat="1">
       <x:c r="B16" s="1" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="C16" s="1" t="s">
+      <x:c r="D16" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="D16" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>185</x:v>
-      </x:c>
       <x:c r="L16" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="M16" s="1" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="M16" s="1" t="s">
-        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="17" s="1" customFormat="1">
       <x:c r="B17" s="1" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="C17" s="1" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="C17" s="1" t="s">
+      <x:c r="D17" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="D17" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>188</x:v>
-      </x:c>
       <x:c r="L17" s="1" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="M17" s="1" t="s">
         <x:v>126</x:v>
-      </x:c>
-      <x:c r="M17" s="1" t="s">
-        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="18" s="1" customFormat="1">
       <x:c r="B18" s="1" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="C18" s="1" t="s">
+      <x:c r="D18" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E18" s="1" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="D18" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E18" s="1" t="s">
+      <x:c r="L18" s="1" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="L18" s="1" t="s">
+      <x:c r="M18" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="M18" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="19" s="1" customFormat="1">
       <x:c r="B19" s="1" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="C19" s="1" t="s">
+      <x:c r="D19" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E19" s="1" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="D19" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E19" s="1" t="s">
-        <x:v>196</x:v>
-      </x:c>
       <x:c r="L19" s="1" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="M19" s="1" t="s">
         <x:v>129</x:v>
-      </x:c>
-      <x:c r="M19" s="1" t="s">
-        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="20" s="1" customFormat="1">
       <x:c r="B20" s="1" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="C20" s="1" t="s">
+      <x:c r="D20" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E20" s="1" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="D20" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E20" s="1" t="s">
+      <x:c r="L20" s="1" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="M20" s="1" t="s">
         <x:v>199</x:v>
-      </x:c>
-      <x:c r="L20" s="1" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="M20" s="1" t="s">
-        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="21" s="1" customFormat="1">
       <x:c r="B21" s="1" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="C21" s="1" t="s">
+      <x:c r="D21" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E21" s="1" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="D21" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E21" s="1" t="s">
-        <x:v>203</x:v>
-      </x:c>
       <x:c r="L21" s="1" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="M21" s="1" t="s">
         <x:v>135</x:v>
-      </x:c>
-      <x:c r="M21" s="1" t="s">
-        <x:v>136</x:v>
       </x:c>
       <x:c r="R21" s="1" t="s">
         <x:v>31</x:v>
@@ -4913,22 +4910,22 @@
     </x:row>
     <x:row r="22" s="1" customFormat="1">
       <x:c r="B22" s="1" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="C22" s="1" t="s">
+      <x:c r="D22" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="D22" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E22" s="1" t="s">
+      <x:c r="L22" s="1" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="L22" s="1" t="s">
+      <x:c r="M22" s="1" t="s">
         <x:v>207</x:v>
-      </x:c>
-      <x:c r="M22" s="1" t="s">
-        <x:v>208</x:v>
       </x:c>
       <x:c r="R22" s="1" t="s">
         <x:v>31</x:v>
@@ -4942,16 +4939,16 @@
     </x:row>
     <x:row r="23" s="1" customFormat="1">
       <x:c r="B23" s="1" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="C23" s="1" t="s">
+      <x:c r="D23" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E23" s="1" t="s">
         <x:v>210</x:v>
-      </x:c>
-      <x:c r="D23" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E23" s="1" t="s">
-        <x:v>211</x:v>
       </x:c>
       <x:c r="R23" s="1" t="s">
         <x:v>31</x:v>
@@ -4965,16 +4962,16 @@
     </x:row>
     <x:row r="24" s="1" customFormat="1">
       <x:c r="B24" s="1" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="C24" s="1" t="s">
+      <x:c r="D24" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E24" s="1" t="s">
         <x:v>213</x:v>
-      </x:c>
-      <x:c r="D24" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E24" s="1" t="s">
-        <x:v>214</x:v>
       </x:c>
       <x:c r="R24" s="1" t="s">
         <x:v>31</x:v>
@@ -4988,16 +4985,16 @@
     </x:row>
     <x:row r="25" s="1" customFormat="1">
       <x:c r="B25" s="1" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="C25" s="1" t="s">
+      <x:c r="D25" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
         <x:v>216</x:v>
-      </x:c>
-      <x:c r="D25" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>217</x:v>
       </x:c>
       <x:c r="R25" s="1" t="s">
         <x:v>31</x:v>
@@ -5011,16 +5008,16 @@
     </x:row>
     <x:row r="26" s="1" customFormat="1">
       <x:c r="B26" s="1" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="C26" s="1" t="s">
+      <x:c r="D26" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="s">
         <x:v>219</x:v>
-      </x:c>
-      <x:c r="D26" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E26" s="1" t="s">
-        <x:v>220</x:v>
       </x:c>
       <x:c r="R26" s="1" t="s">
         <x:v>31</x:v>
@@ -5034,16 +5031,16 @@
     </x:row>
     <x:row r="27" s="1" customFormat="1">
       <x:c r="B27" s="1" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="C27" s="1" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="C27" s="1" t="s">
+      <x:c r="D27" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E27" s="1" t="s">
         <x:v>222</x:v>
-      </x:c>
-      <x:c r="D27" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E27" s="1" t="s">
-        <x:v>223</x:v>
       </x:c>
       <x:c r="R27" s="1" t="s">
         <x:v>38</x:v>
@@ -5057,16 +5054,16 @@
     </x:row>
     <x:row r="28" s="1" customFormat="1">
       <x:c r="B28" s="1" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="C28" s="1" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="C28" s="1" t="s">
+      <x:c r="D28" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E28" s="1" t="s">
         <x:v>225</x:v>
-      </x:c>
-      <x:c r="D28" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E28" s="1" t="s">
-        <x:v>226</x:v>
       </x:c>
       <x:c r="R28" s="1" t="s">
         <x:v>38</x:v>
@@ -5080,16 +5077,16 @@
     </x:row>
     <x:row r="29" s="1" customFormat="1">
       <x:c r="B29" s="1" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="C29" s="1" t="s">
+      <x:c r="D29" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="s">
         <x:v>228</x:v>
-      </x:c>
-      <x:c r="D29" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E29" s="1" t="s">
-        <x:v>229</x:v>
       </x:c>
       <x:c r="R29" s="1" t="s">
         <x:v>38</x:v>
@@ -5103,16 +5100,16 @@
     </x:row>
     <x:row r="30" s="1" customFormat="1">
       <x:c r="B30" s="1" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="C30" s="1" t="s">
+      <x:c r="D30" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="s">
         <x:v>231</x:v>
-      </x:c>
-      <x:c r="D30" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E30" s="1" t="s">
-        <x:v>232</x:v>
       </x:c>
       <x:c r="R30" s="1" t="s">
         <x:v>42</x:v>
@@ -5126,16 +5123,16 @@
     </x:row>
     <x:row r="31" s="1" customFormat="1">
       <x:c r="B31" s="1" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="C31" s="1" t="s">
+      <x:c r="D31" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E31" s="1" t="s">
         <x:v>234</x:v>
-      </x:c>
-      <x:c r="D31" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E31" s="1" t="s">
-        <x:v>235</x:v>
       </x:c>
       <x:c r="R31" s="1" t="s">
         <x:v>31</x:v>
@@ -5146,16 +5143,16 @@
     </x:row>
     <x:row r="32" s="1" customFormat="1">
       <x:c r="B32" s="1" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="C32" s="1" t="s">
+      <x:c r="D32" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E32" s="1" t="s">
         <x:v>237</x:v>
-      </x:c>
-      <x:c r="D32" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E32" s="1" t="s">
-        <x:v>238</x:v>
       </x:c>
       <x:c r="R32" s="1" t="s">
         <x:v>31</x:v>
@@ -5166,16 +5163,16 @@
     </x:row>
     <x:row r="33" s="1" customFormat="1">
       <x:c r="B33" s="1" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="C33" s="1" t="s">
+      <x:c r="D33" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E33" s="1" t="s">
         <x:v>240</x:v>
-      </x:c>
-      <x:c r="D33" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E33" s="1" t="s">
-        <x:v>241</x:v>
       </x:c>
       <x:c r="R33" s="1" t="s">
         <x:v>31</x:v>
@@ -5186,16 +5183,16 @@
     </x:row>
     <x:row r="34" s="1" customFormat="1">
       <x:c r="B34" s="1" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="C34" s="1" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="C34" s="1" t="s">
+      <x:c r="D34" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E34" s="1" t="s">
         <x:v>243</x:v>
-      </x:c>
-      <x:c r="D34" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E34" s="1" t="s">
-        <x:v>244</x:v>
       </x:c>
       <x:c r="R34" s="1" t="s">
         <x:v>31</x:v>
@@ -5206,16 +5203,16 @@
     </x:row>
     <x:row r="35" s="1" customFormat="1">
       <x:c r="B35" s="1" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="C35" s="1" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="C35" s="1" t="s">
+      <x:c r="D35" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E35" s="1" t="s">
         <x:v>246</x:v>
-      </x:c>
-      <x:c r="D35" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E35" s="1" t="s">
-        <x:v>247</x:v>
       </x:c>
       <x:c r="R35" s="1" t="s">
         <x:v>38</x:v>
@@ -5226,16 +5223,16 @@
     </x:row>
     <x:row r="36" s="1" customFormat="1">
       <x:c r="B36" s="1" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="C36" s="1" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="C36" s="1" t="s">
+      <x:c r="D36" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E36" s="1" t="s">
         <x:v>249</x:v>
-      </x:c>
-      <x:c r="D36" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E36" s="1" t="s">
-        <x:v>250</x:v>
       </x:c>
       <x:c r="R36" s="1" t="s">
         <x:v>38</x:v>
@@ -5246,16 +5243,16 @@
     </x:row>
     <x:row r="37" s="1" customFormat="1">
       <x:c r="B37" s="1" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="s">
         <x:v>251</x:v>
       </x:c>
-      <x:c r="C37" s="1" t="s">
+      <x:c r="D37" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E37" s="1" t="s">
         <x:v>252</x:v>
-      </x:c>
-      <x:c r="D37" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E37" s="1" t="s">
-        <x:v>253</x:v>
       </x:c>
       <x:c r="L37" s="1" t="s">
         <x:v>31</x:v>
@@ -5269,16 +5266,16 @@
     </x:row>
     <x:row r="38" s="1" customFormat="1">
       <x:c r="B38" s="1" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="C38" s="1" t="s">
         <x:v>254</x:v>
       </x:c>
-      <x:c r="C38" s="1" t="s">
+      <x:c r="D38" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E38" s="1" t="s">
         <x:v>255</x:v>
-      </x:c>
-      <x:c r="D38" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E38" s="1" t="s">
-        <x:v>256</x:v>
       </x:c>
       <x:c r="L38" s="1" t="s">
         <x:v>38</x:v>
@@ -5292,16 +5289,16 @@
     </x:row>
     <x:row r="39" s="1" customFormat="1">
       <x:c r="B39" s="1" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="s">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="C39" s="1" t="s">
+      <x:c r="D39" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E39" s="1" t="s">
         <x:v>258</x:v>
-      </x:c>
-      <x:c r="D39" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E39" s="1" t="s">
-        <x:v>259</x:v>
       </x:c>
       <x:c r="L39" s="1" t="s">
         <x:v>42</x:v>
@@ -5315,16 +5312,16 @@
     </x:row>
     <x:row r="40" s="1" customFormat="1">
       <x:c r="B40" s="1" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="C40" s="1" t="s">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="C40" s="1" t="s">
+      <x:c r="D40" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E40" s="1" t="s">
         <x:v>261</x:v>
-      </x:c>
-      <x:c r="D40" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E40" s="1" t="s">
-        <x:v>262</x:v>
       </x:c>
       <x:c r="L40" s="1" t="s">
         <x:v>46</x:v>
@@ -5338,16 +5335,16 @@
     </x:row>
     <x:row r="41" s="1" customFormat="1">
       <x:c r="B41" s="1" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="s">
         <x:v>263</x:v>
       </x:c>
-      <x:c r="C41" s="1" t="s">
+      <x:c r="D41" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E41" s="1" t="s">
         <x:v>264</x:v>
-      </x:c>
-      <x:c r="D41" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E41" s="1" t="s">
-        <x:v>265</x:v>
       </x:c>
       <x:c r="L41" s="1" t="s">
         <x:v>50</x:v>
@@ -5355,30 +5352,30 @@
     </x:row>
     <x:row r="42" s="1" customFormat="1">
       <x:c r="B42" s="1" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="C42" s="1" t="s">
         <x:v>266</x:v>
       </x:c>
-      <x:c r="C42" s="1" t="s">
+      <x:c r="D42" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E42" s="1" t="s">
         <x:v>267</x:v>
-      </x:c>
-      <x:c r="D42" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E42" s="1" t="s">
-        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="43" s="1" customFormat="1">
       <x:c r="B43" s="1" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="C43" s="1" t="s">
         <x:v>269</x:v>
       </x:c>
-      <x:c r="C43" s="1" t="s">
+      <x:c r="D43" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E43" s="1" t="s">
         <x:v>270</x:v>
-      </x:c>
-      <x:c r="D43" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E43" s="1" t="s">
-        <x:v>271</x:v>
       </x:c>
       <x:c r="L43" s="1" t="s">
         <x:v>54</x:v>
@@ -5386,16 +5383,16 @@
     </x:row>
     <x:row r="44" s="1" customFormat="1">
       <x:c r="B44" s="1" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="C44" s="1" t="s">
         <x:v>272</x:v>
       </x:c>
-      <x:c r="C44" s="1" t="s">
+      <x:c r="D44" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E44" s="1" t="s">
         <x:v>273</x:v>
-      </x:c>
-      <x:c r="D44" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E44" s="1" t="s">
-        <x:v>274</x:v>
       </x:c>
       <x:c r="L44" s="1" t="s">
         <x:v>58</x:v>
@@ -5403,16 +5400,16 @@
     </x:row>
     <x:row r="45" s="1" customFormat="1">
       <x:c r="B45" s="1" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="C45" s="1" t="s">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="C45" s="1" t="s">
+      <x:c r="D45" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E45" s="1" t="s">
         <x:v>276</x:v>
-      </x:c>
-      <x:c r="D45" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E45" s="1" t="s">
-        <x:v>277</x:v>
       </x:c>
       <x:c r="L45" s="1" t="s">
         <x:v>61</x:v>
@@ -5420,16 +5417,16 @@
     </x:row>
     <x:row r="46" s="1" customFormat="1">
       <x:c r="B46" s="1" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="C46" s="1" t="s">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="C46" s="1" t="s">
+      <x:c r="D46" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E46" s="1" t="s">
         <x:v>279</x:v>
-      </x:c>
-      <x:c r="D46" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E46" s="1" t="s">
-        <x:v>280</x:v>
       </x:c>
       <x:c r="L46" s="1" t="s">
         <x:v>64</x:v>
@@ -5437,16 +5434,16 @@
     </x:row>
     <x:row r="47" s="1" customFormat="1">
       <x:c r="B47" s="1" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="C47" s="1" t="s">
         <x:v>281</x:v>
       </x:c>
-      <x:c r="C47" s="1" t="s">
+      <x:c r="D47" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E47" s="1" t="s">
         <x:v>282</x:v>
-      </x:c>
-      <x:c r="D47" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E47" s="1" t="s">
-        <x:v>283</x:v>
       </x:c>
       <x:c r="L47" s="1" t="s">
         <x:v>67</x:v>
@@ -5454,16 +5451,16 @@
     </x:row>
     <x:row r="48" s="1" customFormat="1">
       <x:c r="B48" s="1" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="C48" s="1" t="s">
         <x:v>284</x:v>
       </x:c>
-      <x:c r="C48" s="1" t="s">
+      <x:c r="D48" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E48" s="1" t="s">
         <x:v>285</x:v>
-      </x:c>
-      <x:c r="D48" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E48" s="1" t="s">
-        <x:v>286</x:v>
       </x:c>
       <x:c r="L48" s="1" t="s">
         <x:v>70</x:v>
@@ -5471,16 +5468,16 @@
     </x:row>
     <x:row r="49" s="1" customFormat="1">
       <x:c r="B49" s="1" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="s">
         <x:v>287</x:v>
       </x:c>
-      <x:c r="C49" s="1" t="s">
+      <x:c r="D49" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E49" s="1" t="s">
         <x:v>288</x:v>
-      </x:c>
-      <x:c r="D49" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E49" s="1" t="s">
-        <x:v>289</x:v>
       </x:c>
       <x:c r="L49" s="1" t="s">
         <x:v>73</x:v>
@@ -5488,414 +5485,414 @@
     </x:row>
     <x:row r="50" s="1" customFormat="1">
       <x:c r="B50" s="1" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="C50" s="1" t="s">
         <x:v>290</x:v>
       </x:c>
-      <x:c r="C50" s="1" t="s">
+      <x:c r="D50" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E50" s="1" t="s">
         <x:v>291</x:v>
-      </x:c>
-      <x:c r="D50" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E50" s="1" t="s">
-        <x:v>292</x:v>
       </x:c>
     </x:row>
     <x:row r="51" s="1" customFormat="1">
       <x:c r="B51" s="1" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="C51" s="1" t="s">
         <x:v>293</x:v>
       </x:c>
-      <x:c r="C51" s="1" t="s">
+      <x:c r="D51" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E51" s="1" t="s">
         <x:v>294</x:v>
-      </x:c>
-      <x:c r="D51" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E51" s="1" t="s">
-        <x:v>295</x:v>
       </x:c>
     </x:row>
     <x:row r="52" s="1" customFormat="1">
       <x:c r="B52" s="1" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="C52" s="1" t="s">
         <x:v>296</x:v>
       </x:c>
-      <x:c r="C52" s="1" t="s">
+      <x:c r="D52" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E52" s="1" t="s">
         <x:v>297</x:v>
-      </x:c>
-      <x:c r="D52" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E52" s="1" t="s">
-        <x:v>298</x:v>
       </x:c>
     </x:row>
     <x:row r="53" s="1" customFormat="1">
       <x:c r="B53" s="1" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="C53" s="1" t="s">
         <x:v>299</x:v>
       </x:c>
-      <x:c r="C53" s="1" t="s">
+      <x:c r="D53" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E53" s="1" t="s">
         <x:v>300</x:v>
-      </x:c>
-      <x:c r="D53" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E53" s="1" t="s">
-        <x:v>301</x:v>
       </x:c>
     </x:row>
     <x:row r="54" s="1" customFormat="1">
       <x:c r="B54" s="1" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="C54" s="1" t="s">
         <x:v>302</x:v>
       </x:c>
-      <x:c r="C54" s="1" t="s">
+      <x:c r="D54" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E54" s="1" t="s">
         <x:v>303</x:v>
-      </x:c>
-      <x:c r="D54" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E54" s="1" t="s">
-        <x:v>304</x:v>
       </x:c>
     </x:row>
     <x:row r="55" s="1" customFormat="1">
       <x:c r="B55" s="1" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="C55" s="1" t="s">
         <x:v>305</x:v>
       </x:c>
-      <x:c r="C55" s="1" t="s">
+      <x:c r="D55" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E55" s="1" t="s">
         <x:v>306</x:v>
-      </x:c>
-      <x:c r="D55" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E55" s="1" t="s">
-        <x:v>307</x:v>
       </x:c>
     </x:row>
     <x:row r="56" s="1" customFormat="1">
       <x:c r="B56" s="1" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="C56" s="1" t="s">
         <x:v>308</x:v>
       </x:c>
-      <x:c r="C56" s="1" t="s">
+      <x:c r="D56" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E56" s="1" t="s">
         <x:v>309</x:v>
-      </x:c>
-      <x:c r="D56" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E56" s="1" t="s">
-        <x:v>310</x:v>
       </x:c>
     </x:row>
     <x:row r="57" s="1" customFormat="1">
       <x:c r="B57" s="1" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="C57" s="1" t="s">
         <x:v>311</x:v>
       </x:c>
-      <x:c r="C57" s="1" t="s">
+      <x:c r="D57" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E57" s="1" t="s">
         <x:v>312</x:v>
-      </x:c>
-      <x:c r="D57" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E57" s="1" t="s">
-        <x:v>313</x:v>
       </x:c>
     </x:row>
     <x:row r="58" s="1" customFormat="1">
       <x:c r="B58" s="1" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="C58" s="1" t="s">
         <x:v>314</x:v>
       </x:c>
-      <x:c r="C58" s="1" t="s">
+      <x:c r="D58" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E58" s="1" t="s">
         <x:v>315</x:v>
-      </x:c>
-      <x:c r="D58" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E58" s="1" t="s">
-        <x:v>316</x:v>
       </x:c>
     </x:row>
     <x:row r="59" s="1" customFormat="1">
       <x:c r="B59" s="1" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="C59" s="1" t="s">
         <x:v>317</x:v>
       </x:c>
-      <x:c r="C59" s="1" t="s">
+      <x:c r="D59" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E59" s="1" t="s">
         <x:v>318</x:v>
-      </x:c>
-      <x:c r="D59" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E59" s="1" t="s">
-        <x:v>319</x:v>
       </x:c>
     </x:row>
     <x:row r="60" s="1" customFormat="1">
       <x:c r="B60" s="1" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="C60" s="1" t="s">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="C60" s="1" t="s">
+      <x:c r="D60" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E60" s="1" t="s">
         <x:v>321</x:v>
-      </x:c>
-      <x:c r="D60" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E60" s="1" t="s">
-        <x:v>322</x:v>
       </x:c>
     </x:row>
     <x:row r="61" s="1" customFormat="1">
       <x:c r="B61" s="1" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="C61" s="1" t="s">
         <x:v>323</x:v>
       </x:c>
-      <x:c r="C61" s="1" t="s">
+      <x:c r="D61" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E61" s="1" t="s">
         <x:v>324</x:v>
-      </x:c>
-      <x:c r="D61" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E61" s="1" t="s">
-        <x:v>325</x:v>
       </x:c>
     </x:row>
     <x:row r="62" s="1" customFormat="1">
       <x:c r="B62" s="1" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="C62" s="1" t="s">
         <x:v>326</x:v>
       </x:c>
-      <x:c r="C62" s="1" t="s">
+      <x:c r="D62" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E62" s="1" t="s">
         <x:v>327</x:v>
-      </x:c>
-      <x:c r="D62" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E62" s="1" t="s">
-        <x:v>328</x:v>
       </x:c>
     </x:row>
     <x:row r="63" s="1" customFormat="1">
       <x:c r="B63" s="1" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="C63" s="1" t="s">
         <x:v>329</x:v>
       </x:c>
-      <x:c r="C63" s="1" t="s">
+      <x:c r="D63" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E63" s="1" t="s">
         <x:v>330</x:v>
-      </x:c>
-      <x:c r="D63" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E63" s="1" t="s">
-        <x:v>331</x:v>
       </x:c>
     </x:row>
     <x:row r="64" s="1" customFormat="1">
       <x:c r="B64" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="C64" s="1" t="s">
         <x:v>332</x:v>
       </x:c>
-      <x:c r="C64" s="1" t="s">
+      <x:c r="D64" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E64" s="1" t="s">
         <x:v>333</x:v>
-      </x:c>
-      <x:c r="D64" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E64" s="1" t="s">
-        <x:v>334</x:v>
       </x:c>
     </x:row>
     <x:row r="65" s="1" customFormat="1">
       <x:c r="B65" s="1" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="C65" s="1" t="s">
         <x:v>335</x:v>
       </x:c>
-      <x:c r="C65" s="1" t="s">
+      <x:c r="D65" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E65" s="1" t="s">
         <x:v>336</x:v>
-      </x:c>
-      <x:c r="D65" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E65" s="1" t="s">
-        <x:v>337</x:v>
       </x:c>
     </x:row>
     <x:row r="66" s="1" customFormat="1">
       <x:c r="B66" s="1" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="C66" s="1" t="s">
         <x:v>338</x:v>
       </x:c>
-      <x:c r="C66" s="1" t="s">
+      <x:c r="D66" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E66" s="1" t="s">
         <x:v>339</x:v>
-      </x:c>
-      <x:c r="D66" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E66" s="1" t="s">
-        <x:v>340</x:v>
       </x:c>
     </x:row>
     <x:row r="67" s="1" customFormat="1">
       <x:c r="B67" s="1" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="C67" s="1" t="s">
         <x:v>341</x:v>
       </x:c>
-      <x:c r="C67" s="1" t="s">
+      <x:c r="D67" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E67" s="1" t="s">
         <x:v>342</x:v>
-      </x:c>
-      <x:c r="D67" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E67" s="1" t="s">
-        <x:v>343</x:v>
       </x:c>
     </x:row>
     <x:row r="68" s="1" customFormat="1">
       <x:c r="B68" s="1" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="C68" s="1" t="s">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="C68" s="1" t="s">
+      <x:c r="D68" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E68" s="1" t="s">
         <x:v>345</x:v>
-      </x:c>
-      <x:c r="D68" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E68" s="1" t="s">
-        <x:v>346</x:v>
       </x:c>
     </x:row>
     <x:row r="69" s="1" customFormat="1">
       <x:c r="B69" s="1" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="C69" s="1" t="s">
         <x:v>347</x:v>
       </x:c>
-      <x:c r="C69" s="1" t="s">
+      <x:c r="D69" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E69" s="1" t="s">
         <x:v>348</x:v>
-      </x:c>
-      <x:c r="D69" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E69" s="1" t="s">
-        <x:v>349</x:v>
       </x:c>
     </x:row>
     <x:row r="70" s="1" customFormat="1">
       <x:c r="B70" s="1" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="C70" s="1" t="s">
         <x:v>350</x:v>
       </x:c>
-      <x:c r="C70" s="1" t="s">
+      <x:c r="D70" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E70" s="1" t="s">
         <x:v>351</x:v>
-      </x:c>
-      <x:c r="D70" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E70" s="1" t="s">
-        <x:v>352</x:v>
       </x:c>
     </x:row>
     <x:row r="71" s="1" customFormat="1">
       <x:c r="B71" s="1" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="C71" s="1" t="s">
         <x:v>353</x:v>
       </x:c>
-      <x:c r="C71" s="1" t="s">
+      <x:c r="D71" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E71" s="1" t="s">
         <x:v>354</x:v>
-      </x:c>
-      <x:c r="D71" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E71" s="1" t="s">
-        <x:v>355</x:v>
       </x:c>
     </x:row>
     <x:row r="72" s="1" customFormat="1">
       <x:c r="B72" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="C72" s="1" t="s">
         <x:v>356</x:v>
       </x:c>
-      <x:c r="C72" s="1" t="s">
+      <x:c r="D72" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E72" s="1" t="s">
         <x:v>357</x:v>
-      </x:c>
-      <x:c r="D72" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E72" s="1" t="s">
-        <x:v>358</x:v>
       </x:c>
     </x:row>
     <x:row r="73" s="1" customFormat="1">
       <x:c r="B73" s="1" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="C73" s="1" t="s">
         <x:v>359</x:v>
       </x:c>
-      <x:c r="C73" s="1" t="s">
+      <x:c r="D73" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E73" s="1" t="s">
         <x:v>360</x:v>
-      </x:c>
-      <x:c r="D73" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E73" s="1" t="s">
-        <x:v>361</x:v>
       </x:c>
     </x:row>
     <x:row r="74" s="1" customFormat="1">
       <x:c r="B74" s="1" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="C74" s="1" t="s">
         <x:v>362</x:v>
       </x:c>
-      <x:c r="C74" s="1" t="s">
+      <x:c r="D74" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E74" s="1" t="s">
         <x:v>363</x:v>
-      </x:c>
-      <x:c r="D74" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E74" s="1" t="s">
-        <x:v>364</x:v>
       </x:c>
     </x:row>
     <x:row r="75" s="1" customFormat="1">
       <x:c r="B75" s="1" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="C75" s="1" t="s">
         <x:v>365</x:v>
       </x:c>
-      <x:c r="C75" s="1" t="s">
+      <x:c r="D75" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E75" s="1" t="s">
         <x:v>366</x:v>
-      </x:c>
-      <x:c r="D75" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E75" s="1" t="s">
-        <x:v>367</x:v>
       </x:c>
     </x:row>
     <x:row r="76" s="1" customFormat="1">
       <x:c r="B76" s="1" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="C76" s="1" t="s">
         <x:v>368</x:v>
       </x:c>
-      <x:c r="C76" s="1" t="s">
+      <x:c r="D76" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E76" s="1" t="s">
         <x:v>369</x:v>
-      </x:c>
-      <x:c r="D76" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E76" s="1" t="s">
-        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="77" s="1" customFormat="1">
       <x:c r="B77" s="1" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="C77" s="1" t="s">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="C77" s="1" t="s">
+      <x:c r="D77" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E77" s="1" t="s">
         <x:v>372</x:v>
-      </x:c>
-      <x:c r="D77" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E77" s="1" t="s">
-        <x:v>373</x:v>
       </x:c>
     </x:row>
     <x:row r="78" s="1" customFormat="1">
       <x:c r="B78" s="1" t="s">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="C78" s="1" t="s">
         <x:v>374</x:v>
       </x:c>
-      <x:c r="C78" s="1" t="s">
+      <x:c r="D78" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E78" s="1" t="s">
         <x:v>375</x:v>
       </x:c>
-      <x:c r="D78" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E78" s="1" t="s">
+      <x:c r="Q78" s="1" t="s">
         <x:v>376</x:v>
       </x:c>
-      <x:c r="Q78" s="1" t="s">
+      <x:c r="R78" s="1" t="s">
         <x:v>377</x:v>
-      </x:c>
-      <x:c r="R78" s="1" t="s">
-        <x:v>378</x:v>
       </x:c>
       <x:c r="S78" s="1">
         <x:v>80</x:v>
@@ -5906,16 +5903,16 @@
     </x:row>
     <x:row r="79" s="1" customFormat="1">
       <x:c r="B79" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="C79" s="1" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="C79" s="1" t="s">
+      <x:c r="D79" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E79" s="1" t="s">
         <x:v>380</x:v>
-      </x:c>
-      <x:c r="D79" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E79" s="1" t="s">
-        <x:v>381</x:v>
       </x:c>
       <x:c r="T79" s="1" t="s">
         <x:v>46</x:v>
@@ -5923,16 +5920,16 @@
     </x:row>
     <x:row r="80" s="1" customFormat="1">
       <x:c r="B80" s="1" t="s">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="C80" s="1" t="s">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="C80" s="1" t="s">
+      <x:c r="D80" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E80" s="1" t="s">
         <x:v>383</x:v>
-      </x:c>
-      <x:c r="D80" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E80" s="1" t="s">
-        <x:v>384</x:v>
       </x:c>
       <x:c r="T80" s="1" t="s">
         <x:v>50</x:v>
@@ -5940,22 +5937,22 @@
     </x:row>
     <x:row r="81" s="1" customFormat="1">
       <x:c r="B81" s="1" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="C81" s="1" t="s">
         <x:v>385</x:v>
       </x:c>
-      <x:c r="C81" s="1" t="s">
+      <x:c r="D81" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E81" s="1" t="s">
         <x:v>386</x:v>
       </x:c>
-      <x:c r="D81" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E81" s="1" t="s">
+      <x:c r="Q81" s="1" t="s">
         <x:v>387</x:v>
       </x:c>
-      <x:c r="Q81" s="1" t="s">
+      <x:c r="R81" s="1" t="s">
         <x:v>388</x:v>
-      </x:c>
-      <x:c r="R81" s="1" t="s">
-        <x:v>389</x:v>
       </x:c>
       <x:c r="S81" s="1">
         <x:v>100</x:v>
@@ -5966,16 +5963,16 @@
     </x:row>
     <x:row r="82" s="1" customFormat="1">
       <x:c r="B82" s="1" t="s">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="C82" s="1" t="s">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="C82" s="1" t="s">
+      <x:c r="D82" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E82" s="1" t="s">
         <x:v>391</x:v>
-      </x:c>
-      <x:c r="D82" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E82" s="1" t="s">
-        <x:v>392</x:v>
       </x:c>
       <x:c r="T82" s="1" t="s">
         <x:v>67</x:v>
@@ -5983,16 +5980,16 @@
     </x:row>
     <x:row r="83" s="1" customFormat="1">
       <x:c r="B83" s="1" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="C83" s="1" t="s">
         <x:v>393</x:v>
       </x:c>
-      <x:c r="C83" s="1" t="s">
+      <x:c r="D83" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E83" s="1" t="s">
         <x:v>394</x:v>
-      </x:c>
-      <x:c r="D83" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E83" s="1" t="s">
-        <x:v>395</x:v>
       </x:c>
       <x:c r="T83" s="1" t="s">
         <x:v>61</x:v>
@@ -6000,22 +5997,22 @@
     </x:row>
     <x:row r="84" s="1" customFormat="1">
       <x:c r="B84" s="1" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="C84" s="1" t="s">
         <x:v>396</x:v>
       </x:c>
-      <x:c r="C84" s="1" t="s">
+      <x:c r="D84" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E84" s="1" t="s">
         <x:v>397</x:v>
       </x:c>
-      <x:c r="D84" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E84" s="1" t="s">
+      <x:c r="Q84" s="1" t="s">
         <x:v>398</x:v>
       </x:c>
-      <x:c r="Q84" s="1" t="s">
+      <x:c r="R84" s="1" t="s">
         <x:v>399</x:v>
-      </x:c>
-      <x:c r="R84" s="1" t="s">
-        <x:v>400</x:v>
       </x:c>
       <x:c r="S84" s="1">
         <x:v>80</x:v>
@@ -6026,16 +6023,16 @@
     </x:row>
     <x:row r="85" s="1" customFormat="1">
       <x:c r="B85" s="1" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="C85" s="1" t="s">
         <x:v>401</x:v>
       </x:c>
-      <x:c r="C85" s="1" t="s">
+      <x:c r="D85" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E85" s="1" t="s">
         <x:v>402</x:v>
-      </x:c>
-      <x:c r="D85" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E85" s="1" t="s">
-        <x:v>403</x:v>
       </x:c>
       <x:c r="T85" s="1" t="s">
         <x:v>64</x:v>
@@ -6043,16 +6040,16 @@
     </x:row>
     <x:row r="86" s="1" customFormat="1">
       <x:c r="B86" s="1" t="s">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="C86" s="1" t="s">
         <x:v>404</x:v>
       </x:c>
-      <x:c r="C86" s="1" t="s">
+      <x:c r="D86" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E86" s="1" t="s">
         <x:v>405</x:v>
-      </x:c>
-      <x:c r="D86" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E86" s="1" t="s">
-        <x:v>406</x:v>
       </x:c>
       <x:c r="T86" s="1" t="s">
         <x:v>67</x:v>
@@ -6060,22 +6057,22 @@
     </x:row>
     <x:row r="87" s="1" customFormat="1">
       <x:c r="B87" s="1" t="s">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="C87" s="1" t="s">
         <x:v>407</x:v>
       </x:c>
-      <x:c r="C87" s="1" t="s">
+      <x:c r="D87" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E87" s="1" t="s">
         <x:v>408</x:v>
       </x:c>
-      <x:c r="D87" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E87" s="1" t="s">
+      <x:c r="Q87" s="1" t="s">
         <x:v>409</x:v>
       </x:c>
-      <x:c r="Q87" s="1" t="s">
+      <x:c r="R87" s="1" t="s">
         <x:v>410</x:v>
-      </x:c>
-      <x:c r="R87" s="1" t="s">
-        <x:v>411</x:v>
       </x:c>
       <x:c r="S87" s="1">
         <x:v>100</x:v>
@@ -6086,16 +6083,16 @@
     </x:row>
     <x:row r="88" s="1" customFormat="1">
       <x:c r="B88" s="1" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="C88" s="1" t="s">
         <x:v>412</x:v>
       </x:c>
-      <x:c r="C88" s="1" t="s">
+      <x:c r="D88" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E88" s="1" t="s">
         <x:v>413</x:v>
-      </x:c>
-      <x:c r="D88" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E88" s="1" t="s">
-        <x:v>414</x:v>
       </x:c>
       <x:c r="T88" s="1" t="s">
         <x:v>31</x:v>
@@ -6103,16 +6100,16 @@
     </x:row>
     <x:row r="89" s="1" customFormat="1">
       <x:c r="B89" s="1" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="C89" s="1" t="s">
         <x:v>415</x:v>
       </x:c>
-      <x:c r="C89" s="1" t="s">
+      <x:c r="D89" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E89" s="1" t="s">
         <x:v>416</x:v>
-      </x:c>
-      <x:c r="D89" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E89" s="1" t="s">
-        <x:v>417</x:v>
       </x:c>
       <x:c r="T89" s="1" t="s">
         <x:v>50</x:v>
@@ -6120,22 +6117,22 @@
     </x:row>
     <x:row r="90" s="1" customFormat="1">
       <x:c r="B90" s="1" t="s">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="C90" s="1" t="s">
         <x:v>418</x:v>
       </x:c>
-      <x:c r="C90" s="1" t="s">
+      <x:c r="D90" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E90" s="1" t="s">
         <x:v>419</x:v>
       </x:c>
-      <x:c r="D90" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E90" s="1" t="s">
+      <x:c r="Q90" s="1" t="s">
         <x:v>420</x:v>
       </x:c>
-      <x:c r="Q90" s="1" t="s">
+      <x:c r="R90" s="1" t="s">
         <x:v>421</x:v>
-      </x:c>
-      <x:c r="R90" s="1" t="s">
-        <x:v>422</x:v>
       </x:c>
       <x:c r="S90" s="1">
         <x:v>100</x:v>
@@ -6146,16 +6143,16 @@
     </x:row>
     <x:row r="91" s="1" customFormat="1">
       <x:c r="B91" s="1" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="C91" s="1" t="s">
         <x:v>423</x:v>
       </x:c>
-      <x:c r="C91" s="1" t="s">
+      <x:c r="D91" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E91" s="1" t="s">
         <x:v>424</x:v>
-      </x:c>
-      <x:c r="D91" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E91" s="1" t="s">
-        <x:v>425</x:v>
       </x:c>
       <x:c r="T91" s="1" t="s">
         <x:v>77</x:v>
@@ -6163,22 +6160,22 @@
     </x:row>
     <x:row r="92" s="1" customFormat="1">
       <x:c r="B92" s="1" t="s">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="C92" s="1" t="s">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="C92" s="1" t="s">
+      <x:c r="D92" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E92" s="1" t="s">
         <x:v>427</x:v>
       </x:c>
-      <x:c r="D92" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E92" s="1" t="s">
+      <x:c r="Q92" s="1" t="s">
         <x:v>428</x:v>
       </x:c>
-      <x:c r="Q92" s="1" t="s">
+      <x:c r="R92" s="1" t="s">
         <x:v>429</x:v>
-      </x:c>
-      <x:c r="R92" s="1" t="s">
-        <x:v>430</x:v>
       </x:c>
       <x:c r="S92" s="1">
         <x:v>100</x:v>
@@ -6189,444 +6186,444 @@
     </x:row>
     <x:row r="93" s="1" customFormat="1">
       <x:c r="B93" s="1" t="s">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="C93" s="1" t="s">
         <x:v>431</x:v>
       </x:c>
-      <x:c r="C93" s="1" t="s">
+      <x:c r="D93" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E93" s="1" t="s">
         <x:v>432</x:v>
-      </x:c>
-      <x:c r="D93" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E93" s="1" t="s">
-        <x:v>433</x:v>
       </x:c>
     </x:row>
     <x:row r="94" s="1" customFormat="1">
       <x:c r="B94" s="1" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="C94" s="1" t="s">
         <x:v>434</x:v>
       </x:c>
-      <x:c r="C94" s="1" t="s">
+      <x:c r="D94" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E94" s="1" t="s">
         <x:v>435</x:v>
-      </x:c>
-      <x:c r="D94" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E94" s="1" t="s">
-        <x:v>436</x:v>
       </x:c>
     </x:row>
     <x:row r="95" s="1" customFormat="1">
       <x:c r="B95" s="1" t="s">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="C95" s="1" t="s">
         <x:v>437</x:v>
       </x:c>
-      <x:c r="C95" s="1" t="s">
+      <x:c r="D95" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E95" s="1" t="s">
         <x:v>438</x:v>
-      </x:c>
-      <x:c r="D95" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E95" s="1" t="s">
-        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="96" s="1" customFormat="1">
       <x:c r="B96" s="1" t="s">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="C96" s="1" t="s">
         <x:v>440</x:v>
       </x:c>
-      <x:c r="C96" s="1" t="s">
+      <x:c r="D96" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E96" s="1" t="s">
         <x:v>441</x:v>
-      </x:c>
-      <x:c r="D96" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E96" s="1" t="s">
-        <x:v>442</x:v>
       </x:c>
     </x:row>
     <x:row r="97" s="1" customFormat="1">
       <x:c r="B97" s="1" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="C97" s="1" t="s">
         <x:v>443</x:v>
       </x:c>
-      <x:c r="C97" s="1" t="s">
+      <x:c r="D97" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E97" s="1" t="s">
         <x:v>444</x:v>
-      </x:c>
-      <x:c r="D97" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E97" s="1" t="s">
-        <x:v>445</x:v>
       </x:c>
     </x:row>
     <x:row r="98" s="1" customFormat="1">
       <x:c r="B98" s="1" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="C98" s="1" t="s">
         <x:v>446</x:v>
       </x:c>
-      <x:c r="C98" s="1" t="s">
+      <x:c r="D98" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E98" s="1" t="s">
         <x:v>447</x:v>
-      </x:c>
-      <x:c r="D98" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E98" s="1" t="s">
-        <x:v>448</x:v>
       </x:c>
     </x:row>
     <x:row r="99" s="1" customFormat="1">
       <x:c r="B99" s="1" t="s">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="C99" s="1" t="s">
         <x:v>449</x:v>
       </x:c>
-      <x:c r="C99" s="1" t="s">
+      <x:c r="D99" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E99" s="1" t="s">
         <x:v>450</x:v>
-      </x:c>
-      <x:c r="D99" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E99" s="1" t="s">
-        <x:v>451</x:v>
       </x:c>
     </x:row>
     <x:row r="100" s="1" customFormat="1">
       <x:c r="B100" s="1" t="s">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="C100" s="1" t="s">
         <x:v>452</x:v>
       </x:c>
-      <x:c r="C100" s="1" t="s">
+      <x:c r="D100" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E100" s="1" t="s">
         <x:v>453</x:v>
-      </x:c>
-      <x:c r="D100" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E100" s="1" t="s">
-        <x:v>454</x:v>
       </x:c>
     </x:row>
     <x:row r="101" s="1" customFormat="1">
       <x:c r="B101" s="1" t="s">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="C101" s="1" t="s">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="C101" s="1" t="s">
+      <x:c r="D101" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E101" s="1" t="s">
         <x:v>456</x:v>
-      </x:c>
-      <x:c r="D101" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E101" s="1" t="s">
-        <x:v>457</x:v>
       </x:c>
     </x:row>
     <x:row r="102" s="1" customFormat="1">
       <x:c r="B102" s="1" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="C102" s="1" t="s">
         <x:v>458</x:v>
       </x:c>
-      <x:c r="C102" s="1" t="s">
+      <x:c r="D102" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E102" s="1" t="s">
         <x:v>459</x:v>
-      </x:c>
-      <x:c r="D102" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E102" s="1" t="s">
-        <x:v>460</x:v>
       </x:c>
     </x:row>
     <x:row r="103" s="1" customFormat="1">
       <x:c r="B103" s="1" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="C103" s="1" t="s">
         <x:v>461</x:v>
       </x:c>
-      <x:c r="C103" s="1" t="s">
+      <x:c r="D103" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E103" s="1" t="s">
         <x:v>462</x:v>
-      </x:c>
-      <x:c r="D103" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E103" s="1" t="s">
-        <x:v>463</x:v>
       </x:c>
     </x:row>
     <x:row r="104" s="1" customFormat="1">
       <x:c r="B104" s="1" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="C104" s="1" t="s">
         <x:v>464</x:v>
       </x:c>
-      <x:c r="C104" s="1" t="s">
+      <x:c r="D104" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E104" s="1" t="s">
         <x:v>465</x:v>
-      </x:c>
-      <x:c r="D104" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E104" s="1" t="s">
-        <x:v>466</x:v>
       </x:c>
     </x:row>
     <x:row r="105" s="1" customFormat="1">
       <x:c r="B105" s="1" t="s">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="C105" s="1" t="s">
         <x:v>467</x:v>
       </x:c>
-      <x:c r="C105" s="1" t="s">
+      <x:c r="D105" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E105" s="1" t="s">
         <x:v>468</x:v>
-      </x:c>
-      <x:c r="D105" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E105" s="1" t="s">
-        <x:v>469</x:v>
       </x:c>
     </x:row>
     <x:row r="106" s="1" customFormat="1">
       <x:c r="B106" s="1" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="C106" s="1" t="s">
         <x:v>470</x:v>
       </x:c>
-      <x:c r="C106" s="1" t="s">
+      <x:c r="D106" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E106" s="1" t="s">
         <x:v>471</x:v>
-      </x:c>
-      <x:c r="D106" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E106" s="1" t="s">
-        <x:v>472</x:v>
       </x:c>
     </x:row>
     <x:row r="107" s="1" customFormat="1">
       <x:c r="B107" s="1" t="s">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="C107" s="1" t="s">
         <x:v>473</x:v>
       </x:c>
-      <x:c r="C107" s="1" t="s">
+      <x:c r="D107" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E107" s="1" t="s">
         <x:v>474</x:v>
-      </x:c>
-      <x:c r="D107" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E107" s="1" t="s">
-        <x:v>475</x:v>
       </x:c>
     </x:row>
     <x:row r="108" s="1" customFormat="1">
       <x:c r="B108" s="1" t="s">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="C108" s="1" t="s">
         <x:v>476</x:v>
       </x:c>
-      <x:c r="C108" s="1" t="s">
+      <x:c r="D108" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E108" s="1" t="s">
         <x:v>477</x:v>
-      </x:c>
-      <x:c r="D108" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E108" s="1" t="s">
-        <x:v>478</x:v>
       </x:c>
     </x:row>
     <x:row r="109" s="1" customFormat="1">
       <x:c r="B109" s="1" t="s">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="C109" s="1" t="s">
         <x:v>479</x:v>
       </x:c>
-      <x:c r="C109" s="1" t="s">
+      <x:c r="D109" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E109" s="1" t="s">
         <x:v>480</x:v>
-      </x:c>
-      <x:c r="D109" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E109" s="1" t="s">
-        <x:v>481</x:v>
       </x:c>
     </x:row>
     <x:row r="110" s="1" customFormat="1">
       <x:c r="B110" s="1" t="s">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="C110" s="1" t="s">
         <x:v>482</x:v>
       </x:c>
-      <x:c r="C110" s="1" t="s">
+      <x:c r="D110" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E110" s="1" t="s">
         <x:v>483</x:v>
-      </x:c>
-      <x:c r="D110" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E110" s="1" t="s">
-        <x:v>484</x:v>
       </x:c>
     </x:row>
     <x:row r="111" s="1" customFormat="1">
       <x:c r="B111" s="1" t="s">
+        <x:v>484</x:v>
+      </x:c>
+      <x:c r="C111" s="1" t="s">
         <x:v>485</x:v>
       </x:c>
-      <x:c r="C111" s="1" t="s">
+      <x:c r="D111" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E111" s="1" t="s">
         <x:v>486</x:v>
-      </x:c>
-      <x:c r="D111" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E111" s="1" t="s">
-        <x:v>487</x:v>
       </x:c>
     </x:row>
     <x:row r="112" s="1" customFormat="1">
       <x:c r="B112" s="1" t="s">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="C112" s="1" t="s">
         <x:v>488</x:v>
       </x:c>
-      <x:c r="C112" s="1" t="s">
+      <x:c r="D112" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E112" s="1" t="s">
         <x:v>489</x:v>
-      </x:c>
-      <x:c r="D112" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E112" s="1" t="s">
-        <x:v>490</x:v>
       </x:c>
     </x:row>
     <x:row r="113" s="1" customFormat="1">
       <x:c r="B113" s="1" t="s">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="C113" s="1" t="s">
         <x:v>491</x:v>
       </x:c>
-      <x:c r="C113" s="1" t="s">
+      <x:c r="D113" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E113" s="1" t="s">
         <x:v>492</x:v>
-      </x:c>
-      <x:c r="D113" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E113" s="1" t="s">
-        <x:v>493</x:v>
       </x:c>
     </x:row>
     <x:row r="114" s="1" customFormat="1">
       <x:c r="B114" s="1" t="s">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="C114" s="1" t="s">
         <x:v>494</x:v>
       </x:c>
-      <x:c r="C114" s="1" t="s">
+      <x:c r="D114" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E114" s="1" t="s">
         <x:v>495</x:v>
-      </x:c>
-      <x:c r="D114" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E114" s="1" t="s">
-        <x:v>496</x:v>
       </x:c>
     </x:row>
     <x:row r="115" s="1" customFormat="1">
       <x:c r="B115" s="1" t="s">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="C115" s="1" t="s">
         <x:v>497</x:v>
       </x:c>
-      <x:c r="C115" s="1" t="s">
+      <x:c r="D115" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E115" s="1" t="s">
         <x:v>498</x:v>
-      </x:c>
-      <x:c r="D115" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E115" s="1" t="s">
-        <x:v>499</x:v>
       </x:c>
     </x:row>
     <x:row r="116" s="1" customFormat="1">
       <x:c r="B116" s="1" t="s">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="C116" s="1" t="s">
         <x:v>500</x:v>
       </x:c>
-      <x:c r="C116" s="1" t="s">
+      <x:c r="D116" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E116" s="1" t="s">
         <x:v>501</x:v>
-      </x:c>
-      <x:c r="D116" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E116" s="1" t="s">
-        <x:v>502</x:v>
       </x:c>
     </x:row>
     <x:row r="117" s="1" customFormat="1">
       <x:c r="B117" s="1" t="s">
+        <x:v>502</x:v>
+      </x:c>
+      <x:c r="C117" s="1" t="s">
         <x:v>503</x:v>
       </x:c>
-      <x:c r="C117" s="1" t="s">
+      <x:c r="D117" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E117" s="1" t="s">
         <x:v>504</x:v>
-      </x:c>
-      <x:c r="D117" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E117" s="1" t="s">
-        <x:v>505</x:v>
       </x:c>
     </x:row>
     <x:row r="118" s="1" customFormat="1">
       <x:c r="B118" s="1" t="s">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="C118" s="1" t="s">
         <x:v>506</x:v>
       </x:c>
-      <x:c r="C118" s="1" t="s">
+      <x:c r="D118" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E118" s="1" t="s">
         <x:v>507</x:v>
-      </x:c>
-      <x:c r="D118" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E118" s="1" t="s">
-        <x:v>508</x:v>
       </x:c>
     </x:row>
     <x:row r="119" s="1" customFormat="1">
       <x:c r="B119" s="1" t="s">
+        <x:v>508</x:v>
+      </x:c>
+      <x:c r="C119" s="1" t="s">
         <x:v>509</x:v>
       </x:c>
-      <x:c r="C119" s="1" t="s">
+      <x:c r="D119" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E119" s="1" t="s">
         <x:v>510</x:v>
-      </x:c>
-      <x:c r="D119" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E119" s="1" t="s">
-        <x:v>511</x:v>
       </x:c>
     </x:row>
     <x:row r="120" s="1" customFormat="1">
       <x:c r="B120" s="1" t="s">
+        <x:v>511</x:v>
+      </x:c>
+      <x:c r="C120" s="1" t="s">
         <x:v>512</x:v>
       </x:c>
-      <x:c r="C120" s="1" t="s">
+      <x:c r="D120" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E120" s="1" t="s">
         <x:v>513</x:v>
-      </x:c>
-      <x:c r="D120" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E120" s="1" t="s">
-        <x:v>514</x:v>
       </x:c>
     </x:row>
     <x:row r="121" s="1" customFormat="1">
       <x:c r="B121" s="1" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="C121" s="1" t="s">
         <x:v>515</x:v>
       </x:c>
-      <x:c r="C121" s="1" t="s">
+      <x:c r="D121" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E121" s="1" t="s">
         <x:v>516</x:v>
-      </x:c>
-      <x:c r="D121" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E121" s="1" t="s">
-        <x:v>517</x:v>
       </x:c>
     </x:row>
     <x:row r="122" s="1" customFormat="1">
       <x:c r="B122" s="1" t="s">
+        <x:v>517</x:v>
+      </x:c>
+      <x:c r="C122" s="1" t="s">
         <x:v>518</x:v>
       </x:c>
-      <x:c r="C122" s="1" t="s">
+      <x:c r="D122" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E122" s="1" t="s">
         <x:v>519</x:v>
-      </x:c>
-      <x:c r="D122" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E122" s="1" t="s">
-        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="123" s="1" customFormat="1">
       <x:c r="B123" s="1" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="C123" s="1" t="s">
         <x:v>521</x:v>
       </x:c>
-      <x:c r="C123" s="1" t="s">
+      <x:c r="D123" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E123" s="1" t="s">
         <x:v>522</x:v>
-      </x:c>
-      <x:c r="D123" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E123" s="1" t="s">
-        <x:v>523</x:v>
       </x:c>
     </x:row>
     <x:row r="124" s="1" customFormat="1">
       <x:c r="B124" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C124" s="1" t="s">
-        <x:v>524</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="D124" s="1">
         <x:v>100</x:v>
@@ -6637,10 +6634,10 @@
     </x:row>
     <x:row r="125" s="1" customFormat="1">
       <x:c r="B125" s="1" t="s">
+        <x:v>524</x:v>
+      </x:c>
+      <x:c r="C125" s="1" t="s">
         <x:v>525</x:v>
-      </x:c>
-      <x:c r="C125" s="1" t="s">
-        <x:v>526</x:v>
       </x:c>
       <x:c r="D125" s="1">
         <x:v>100</x:v>
@@ -6651,570 +6648,570 @@
     </x:row>
     <x:row r="126" s="1" customFormat="1">
       <x:c r="B126" s="1" t="s">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="C126" s="1" t="s">
         <x:v>527</x:v>
       </x:c>
-      <x:c r="C126" s="1" t="s">
+      <x:c r="D126" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E126" s="1" t="s">
         <x:v>528</x:v>
-      </x:c>
-      <x:c r="D126" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E126" s="1" t="s">
-        <x:v>529</x:v>
       </x:c>
     </x:row>
     <x:row r="127" s="1" customFormat="1">
       <x:c r="B127" s="1" t="s">
+        <x:v>529</x:v>
+      </x:c>
+      <x:c r="C127" s="1" t="s">
         <x:v>530</x:v>
       </x:c>
-      <x:c r="C127" s="1" t="s">
+      <x:c r="D127" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E127" s="1" t="s">
         <x:v>531</x:v>
-      </x:c>
-      <x:c r="D127" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E127" s="1" t="s">
-        <x:v>532</x:v>
       </x:c>
     </x:row>
     <x:row r="128" s="1" customFormat="1">
       <x:c r="B128" s="1" t="s">
+        <x:v>532</x:v>
+      </x:c>
+      <x:c r="C128" s="1" t="s">
         <x:v>533</x:v>
       </x:c>
-      <x:c r="C128" s="1" t="s">
+      <x:c r="D128" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E128" s="1" t="s">
         <x:v>534</x:v>
-      </x:c>
-      <x:c r="D128" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E128" s="1" t="s">
-        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="129" s="1" customFormat="1">
       <x:c r="B129" s="1" t="s">
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="C129" s="1" t="s">
         <x:v>536</x:v>
       </x:c>
-      <x:c r="C129" s="1" t="s">
+      <x:c r="D129" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E129" s="1" t="s">
         <x:v>537</x:v>
-      </x:c>
-      <x:c r="D129" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E129" s="1" t="s">
-        <x:v>538</x:v>
       </x:c>
     </x:row>
     <x:row r="130" s="1" customFormat="1">
       <x:c r="B130" s="1" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="C130" s="1" t="s">
         <x:v>539</x:v>
       </x:c>
-      <x:c r="C130" s="1" t="s">
+      <x:c r="D130" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E130" s="1" t="s">
         <x:v>540</x:v>
-      </x:c>
-      <x:c r="D130" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E130" s="1" t="s">
-        <x:v>541</x:v>
       </x:c>
     </x:row>
     <x:row r="131" s="1" customFormat="1">
       <x:c r="B131" s="1" t="s">
+        <x:v>541</x:v>
+      </x:c>
+      <x:c r="C131" s="1" t="s">
         <x:v>542</x:v>
       </x:c>
-      <x:c r="C131" s="1" t="s">
+      <x:c r="D131" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E131" s="1" t="s">
         <x:v>543</x:v>
-      </x:c>
-      <x:c r="D131" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E131" s="1" t="s">
-        <x:v>544</x:v>
       </x:c>
     </x:row>
     <x:row r="132" s="1" customFormat="1">
       <x:c r="B132" s="1" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="C132" s="1" t="s">
         <x:v>545</x:v>
       </x:c>
-      <x:c r="C132" s="1" t="s">
+      <x:c r="D132" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E132" s="1" t="s">
         <x:v>546</x:v>
-      </x:c>
-      <x:c r="D132" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E132" s="1" t="s">
-        <x:v>547</x:v>
       </x:c>
     </x:row>
     <x:row r="133" s="1" customFormat="1">
       <x:c r="B133" s="1" t="s">
+        <x:v>547</x:v>
+      </x:c>
+      <x:c r="C133" s="1" t="s">
         <x:v>548</x:v>
       </x:c>
-      <x:c r="C133" s="1" t="s">
+      <x:c r="D133" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E133" s="1" t="s">
         <x:v>549</x:v>
-      </x:c>
-      <x:c r="D133" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E133" s="1" t="s">
-        <x:v>550</x:v>
       </x:c>
     </x:row>
     <x:row r="134" s="1" customFormat="1">
       <x:c r="B134" s="1" t="s">
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="C134" s="1" t="s">
         <x:v>551</x:v>
       </x:c>
-      <x:c r="C134" s="1" t="s">
+      <x:c r="D134" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E134" s="1" t="s">
         <x:v>552</x:v>
-      </x:c>
-      <x:c r="D134" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E134" s="1" t="s">
-        <x:v>553</x:v>
       </x:c>
     </x:row>
     <x:row r="135" s="1" customFormat="1">
       <x:c r="B135" s="1" t="s">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="C135" s="1" t="s">
         <x:v>554</x:v>
       </x:c>
-      <x:c r="C135" s="1" t="s">
+      <x:c r="D135" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E135" s="1" t="s">
         <x:v>555</x:v>
-      </x:c>
-      <x:c r="D135" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E135" s="1" t="s">
-        <x:v>556</x:v>
       </x:c>
     </x:row>
     <x:row r="136" s="1" customFormat="1">
       <x:c r="B136" s="1" t="s">
+        <x:v>556</x:v>
+      </x:c>
+      <x:c r="C136" s="1" t="s">
         <x:v>557</x:v>
       </x:c>
-      <x:c r="C136" s="1" t="s">
+      <x:c r="D136" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E136" s="1" t="s">
         <x:v>558</x:v>
-      </x:c>
-      <x:c r="D136" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E136" s="1" t="s">
-        <x:v>559</x:v>
       </x:c>
     </x:row>
     <x:row r="137" s="1" customFormat="1">
       <x:c r="B137" s="1" t="s">
+        <x:v>559</x:v>
+      </x:c>
+      <x:c r="C137" s="1" t="s">
         <x:v>560</x:v>
       </x:c>
-      <x:c r="C137" s="1" t="s">
+      <x:c r="D137" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E137" s="1" t="s">
         <x:v>561</x:v>
-      </x:c>
-      <x:c r="D137" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E137" s="1" t="s">
-        <x:v>562</x:v>
       </x:c>
     </x:row>
     <x:row r="138" s="1" customFormat="1">
       <x:c r="B138" s="1" t="s">
+        <x:v>562</x:v>
+      </x:c>
+      <x:c r="C138" s="1" t="s">
         <x:v>563</x:v>
       </x:c>
-      <x:c r="C138" s="1" t="s">
+      <x:c r="D138" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E138" s="1" t="s">
         <x:v>564</x:v>
-      </x:c>
-      <x:c r="D138" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E138" s="1" t="s">
-        <x:v>565</x:v>
       </x:c>
     </x:row>
     <x:row r="139" s="1" customFormat="1">
       <x:c r="B139" s="1" t="s">
+        <x:v>565</x:v>
+      </x:c>
+      <x:c r="C139" s="1" t="s">
         <x:v>566</x:v>
       </x:c>
-      <x:c r="C139" s="1" t="s">
+      <x:c r="D139" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E139" s="1" t="s">
         <x:v>567</x:v>
-      </x:c>
-      <x:c r="D139" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E139" s="1" t="s">
-        <x:v>568</x:v>
       </x:c>
     </x:row>
     <x:row r="140" s="1" customFormat="1">
       <x:c r="B140" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C140" s="1" t="s">
+        <x:v>568</x:v>
+      </x:c>
+      <x:c r="D140" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E140" s="1" t="s">
         <x:v>569</x:v>
-      </x:c>
-      <x:c r="D140" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E140" s="1" t="s">
-        <x:v>570</x:v>
       </x:c>
     </x:row>
     <x:row r="141" s="1" customFormat="1">
       <x:c r="B141" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C141" s="1" t="s">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="D141" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E141" s="1" t="s">
         <x:v>571</x:v>
-      </x:c>
-      <x:c r="D141" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E141" s="1" t="s">
-        <x:v>572</x:v>
       </x:c>
     </x:row>
     <x:row r="142" s="1" customFormat="1">
       <x:c r="B142" s="1" t="s">
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="C142" s="1" t="s">
         <x:v>573</x:v>
       </x:c>
-      <x:c r="C142" s="1" t="s">
+      <x:c r="D142" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E142" s="1" t="s">
         <x:v>574</x:v>
-      </x:c>
-      <x:c r="D142" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E142" s="1" t="s">
-        <x:v>575</x:v>
       </x:c>
     </x:row>
     <x:row r="143" s="1" customFormat="1">
       <x:c r="B143" s="1" t="s">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="C143" s="1" t="s">
         <x:v>576</x:v>
       </x:c>
-      <x:c r="C143" s="1" t="s">
+      <x:c r="D143" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E143" s="1" t="s">
         <x:v>577</x:v>
-      </x:c>
-      <x:c r="D143" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E143" s="1" t="s">
-        <x:v>578</x:v>
       </x:c>
     </x:row>
     <x:row r="144" s="1" customFormat="1">
       <x:c r="B144" s="1" t="s">
+        <x:v>578</x:v>
+      </x:c>
+      <x:c r="C144" s="1" t="s">
         <x:v>579</x:v>
       </x:c>
-      <x:c r="C144" s="1" t="s">
+      <x:c r="D144" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E144" s="1" t="s">
         <x:v>580</x:v>
-      </x:c>
-      <x:c r="D144" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E144" s="1" t="s">
-        <x:v>581</x:v>
       </x:c>
     </x:row>
     <x:row r="145" s="1" customFormat="1">
       <x:c r="B145" s="1" t="s">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="C145" s="1" t="s">
         <x:v>582</x:v>
       </x:c>
-      <x:c r="C145" s="1" t="s">
+      <x:c r="D145" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E145" s="1" t="s">
         <x:v>583</x:v>
-      </x:c>
-      <x:c r="D145" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E145" s="1" t="s">
-        <x:v>584</x:v>
       </x:c>
     </x:row>
     <x:row r="146" s="1" customFormat="1">
       <x:c r="B146" s="1" t="s">
+        <x:v>584</x:v>
+      </x:c>
+      <x:c r="C146" s="1" t="s">
         <x:v>585</x:v>
       </x:c>
-      <x:c r="C146" s="1" t="s">
+      <x:c r="D146" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E146" s="1" t="s">
         <x:v>586</x:v>
-      </x:c>
-      <x:c r="D146" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E146" s="1" t="s">
-        <x:v>587</x:v>
       </x:c>
     </x:row>
     <x:row r="147" s="1" customFormat="1">
       <x:c r="B147" s="1" t="s">
+        <x:v>587</x:v>
+      </x:c>
+      <x:c r="C147" s="1" t="s">
         <x:v>588</x:v>
       </x:c>
-      <x:c r="C147" s="1" t="s">
+      <x:c r="D147" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E147" s="1" t="s">
         <x:v>589</x:v>
-      </x:c>
-      <x:c r="D147" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E147" s="1" t="s">
-        <x:v>590</x:v>
       </x:c>
     </x:row>
     <x:row r="148" s="1" customFormat="1">
       <x:c r="B148" s="1" t="s">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="C148" s="1" t="s">
         <x:v>591</x:v>
       </x:c>
-      <x:c r="C148" s="1" t="s">
+      <x:c r="D148" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E148" s="1" t="s">
         <x:v>592</x:v>
-      </x:c>
-      <x:c r="D148" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E148" s="1" t="s">
-        <x:v>593</x:v>
       </x:c>
     </x:row>
     <x:row r="149" s="1" customFormat="1">
       <x:c r="B149" s="1" t="s">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="C149" s="1" t="s">
         <x:v>594</x:v>
       </x:c>
-      <x:c r="C149" s="1" t="s">
+      <x:c r="D149" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E149" s="1" t="s">
         <x:v>595</x:v>
-      </x:c>
-      <x:c r="D149" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E149" s="1" t="s">
-        <x:v>596</x:v>
       </x:c>
     </x:row>
     <x:row r="150" s="1" customFormat="1">
       <x:c r="B150" s="1" t="s">
+        <x:v>596</x:v>
+      </x:c>
+      <x:c r="C150" s="1" t="s">
         <x:v>597</x:v>
       </x:c>
-      <x:c r="C150" s="1" t="s">
+      <x:c r="D150" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E150" s="1" t="s">
         <x:v>598</x:v>
-      </x:c>
-      <x:c r="D150" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E150" s="1" t="s">
-        <x:v>599</x:v>
       </x:c>
     </x:row>
     <x:row r="151" s="1" customFormat="1">
       <x:c r="B151" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C151" s="1" t="s">
+        <x:v>599</x:v>
+      </x:c>
+      <x:c r="D151" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E151" s="1" t="s">
         <x:v>600</x:v>
-      </x:c>
-      <x:c r="D151" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E151" s="1" t="s">
-        <x:v>601</x:v>
       </x:c>
     </x:row>
     <x:row r="152" s="1" customFormat="1">
       <x:c r="B152" s="1" t="s">
+        <x:v>601</x:v>
+      </x:c>
+      <x:c r="C152" s="1" t="s">
         <x:v>602</x:v>
       </x:c>
-      <x:c r="C152" s="1" t="s">
+      <x:c r="D152" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E152" s="1" t="s">
         <x:v>603</x:v>
-      </x:c>
-      <x:c r="D152" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E152" s="1" t="s">
-        <x:v>604</x:v>
       </x:c>
     </x:row>
     <x:row r="153" s="1" customFormat="1">
       <x:c r="B153" s="1" t="s">
+        <x:v>604</x:v>
+      </x:c>
+      <x:c r="C153" s="1" t="s">
         <x:v>605</x:v>
       </x:c>
-      <x:c r="C153" s="1" t="s">
+      <x:c r="D153" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E153" s="1" t="s">
         <x:v>606</x:v>
-      </x:c>
-      <x:c r="D153" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E153" s="1" t="s">
-        <x:v>607</x:v>
       </x:c>
     </x:row>
     <x:row r="154" s="1" customFormat="1">
       <x:c r="B154" s="1" t="s">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="C154" s="1" t="s">
         <x:v>608</x:v>
       </x:c>
-      <x:c r="C154" s="1" t="s">
+      <x:c r="D154" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E154" s="1" t="s">
         <x:v>609</x:v>
-      </x:c>
-      <x:c r="D154" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E154" s="1" t="s">
-        <x:v>610</x:v>
       </x:c>
     </x:row>
     <x:row r="155" s="1" customFormat="1">
       <x:c r="B155" s="1" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="C155" s="1" t="s">
         <x:v>611</x:v>
       </x:c>
-      <x:c r="C155" s="1" t="s">
+      <x:c r="D155" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E155" s="1" t="s">
         <x:v>612</x:v>
-      </x:c>
-      <x:c r="D155" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E155" s="1" t="s">
-        <x:v>613</x:v>
       </x:c>
     </x:row>
     <x:row r="156" s="1" customFormat="1">
       <x:c r="B156" s="1" t="s">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="C156" s="1" t="s">
         <x:v>614</x:v>
       </x:c>
-      <x:c r="C156" s="1" t="s">
+      <x:c r="D156" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E156" s="1" t="s">
         <x:v>615</x:v>
-      </x:c>
-      <x:c r="D156" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E156" s="1" t="s">
-        <x:v>616</x:v>
       </x:c>
     </x:row>
     <x:row r="157" s="1" customFormat="1">
       <x:c r="B157" s="1" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="C157" s="1" t="s">
         <x:v>617</x:v>
       </x:c>
-      <x:c r="C157" s="1" t="s">
+      <x:c r="D157" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E157" s="1" t="s">
         <x:v>618</x:v>
-      </x:c>
-      <x:c r="D157" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E157" s="1" t="s">
-        <x:v>619</x:v>
       </x:c>
     </x:row>
     <x:row r="158" s="1" customFormat="1">
       <x:c r="B158" s="1" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="C158" s="1" t="s">
         <x:v>620</x:v>
       </x:c>
-      <x:c r="C158" s="1" t="s">
+      <x:c r="D158" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E158" s="1" t="s">
         <x:v>621</x:v>
-      </x:c>
-      <x:c r="D158" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E158" s="1" t="s">
-        <x:v>622</x:v>
       </x:c>
     </x:row>
     <x:row r="159" s="1" customFormat="1">
       <x:c r="B159" s="1" t="s">
+        <x:v>622</x:v>
+      </x:c>
+      <x:c r="C159" s="1" t="s">
         <x:v>623</x:v>
       </x:c>
-      <x:c r="C159" s="1" t="s">
+      <x:c r="D159" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E159" s="1" t="s">
         <x:v>624</x:v>
-      </x:c>
-      <x:c r="D159" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E159" s="1" t="s">
-        <x:v>625</x:v>
       </x:c>
     </x:row>
     <x:row r="160" s="1" customFormat="1">
       <x:c r="B160" s="1" t="s">
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="C160" s="1" t="s">
         <x:v>626</x:v>
       </x:c>
-      <x:c r="C160" s="1" t="s">
+      <x:c r="D160" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E160" s="1" t="s">
         <x:v>627</x:v>
-      </x:c>
-      <x:c r="D160" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E160" s="1" t="s">
-        <x:v>628</x:v>
       </x:c>
     </x:row>
     <x:row r="161" s="1" customFormat="1">
       <x:c r="B161" s="1" t="s">
+        <x:v>628</x:v>
+      </x:c>
+      <x:c r="C161" s="1" t="s">
         <x:v>629</x:v>
       </x:c>
-      <x:c r="C161" s="1" t="s">
+      <x:c r="D161" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E161" s="1" t="s">
         <x:v>630</x:v>
-      </x:c>
-      <x:c r="D161" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E161" s="1" t="s">
-        <x:v>631</x:v>
       </x:c>
     </x:row>
     <x:row r="162" s="1" customFormat="1">
       <x:c r="B162" s="1" t="s">
+        <x:v>631</x:v>
+      </x:c>
+      <x:c r="C162" s="1" t="s">
         <x:v>632</x:v>
       </x:c>
-      <x:c r="C162" s="1" t="s">
+      <x:c r="D162" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E162" s="1" t="s">
         <x:v>633</x:v>
-      </x:c>
-      <x:c r="D162" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E162" s="1" t="s">
-        <x:v>634</x:v>
       </x:c>
     </x:row>
     <x:row r="163" s="1" customFormat="1">
       <x:c r="B163" s="1" t="s">
+        <x:v>634</x:v>
+      </x:c>
+      <x:c r="C163" s="1" t="s">
         <x:v>635</x:v>
       </x:c>
-      <x:c r="C163" s="1" t="s">
+      <x:c r="D163" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E163" s="1" t="s">
         <x:v>636</x:v>
-      </x:c>
-      <x:c r="D163" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E163" s="1" t="s">
-        <x:v>637</x:v>
       </x:c>
     </x:row>
     <x:row r="164" s="1" customFormat="1">
       <x:c r="B164" s="1" t="s">
+        <x:v>637</x:v>
+      </x:c>
+      <x:c r="C164" s="1" t="s">
         <x:v>638</x:v>
       </x:c>
-      <x:c r="C164" s="1" t="s">
+      <x:c r="D164" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E164" s="1" t="s">
         <x:v>639</x:v>
-      </x:c>
-      <x:c r="D164" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E164" s="1" t="s">
-        <x:v>640</x:v>
       </x:c>
     </x:row>
     <x:row r="165" s="1" customFormat="1">
       <x:c r="B165" s="1" t="s">
+        <x:v>640</x:v>
+      </x:c>
+      <x:c r="C165" s="1" t="s">
         <x:v>641</x:v>
       </x:c>
-      <x:c r="C165" s="1" t="s">
+      <x:c r="D165" s="1">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E165" s="1" t="s">
         <x:v>642</x:v>
-      </x:c>
-      <x:c r="D165" s="1">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E165" s="1" t="s">
-        <x:v>643</x:v>
       </x:c>
     </x:row>
     <x:row r="166" s="1" customFormat="1">
       <x:c r="B166" s="1" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="C166" s="1" t="s">
         <x:v>429</x:v>
-      </x:c>
-      <x:c r="C166" s="1" t="s">
-        <x:v>430</x:v>
       </x:c>
       <x:c r="D166" s="1">
         <x:v>100</x:v>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="action" sheetId="1" r:id="R88c3276b39d4456f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="large_group" sheetId="2" r:id="R81e1915cfcfc436a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="small_group" sheetId="3" r:id="R8c7627cfb6a04fe2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="action" sheetId="1" r:id="Rdea5418b4f884c89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="large_group" sheetId="2" r:id="Rcdbf39ecb8374392"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="small_group" sheetId="3" r:id="R3250ce9f3c1945f0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -66,9 +66,6 @@
     <x:t xml:space="preserve">行动行为(分派 handler)</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Food:关联具体美食 TbFood.id(1:1)</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">即时效果类型</x:t>
   </x:si>
   <x:si>
@@ -78,12 +75,6 @@
     <x:t xml:space="preserve">即时效果参数</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">本次最小耗时(0.1天)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">本次最大耗时(0.1天)</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">奖励 Tip 标题</x:t>
   </x:si>
   <x:si>
@@ -144,9 +135,6 @@
     <x:t xml:space="preserve">food_passive</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">道具2选1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">带来持续性的增益</x:t>
   </x:si>
   <x:si>
@@ -156,9 +144,6 @@
     <x:t xml:space="preserve">food_active_strengthen</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">强化箱2选1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">强化食物与餐桌格</x:t>
   </x:si>
   <x:si>
@@ -168,9 +153,6 @@
     <x:t xml:space="preserve">food_active_ajust</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">调整单2选1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">调整行动与时间轴</x:t>
   </x:si>
   <x:si>
@@ -201,27 +183,18 @@
     <x:t xml:space="preserve">food_hard_passive</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">道具4选1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">act_food_hard_active_strengthen</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">food_hard_active_strengthen</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">强化箱4选1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">act_food_hard_active_adjust</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">food_hard_active_ajust</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">调整单4选1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">act_event</x:t>
   </x:si>
   <x:si>
@@ -249,9 +222,6 @@
     <x:t xml:space="preserve">商店采购</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">琳琅满目的食物与道具</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Shop</x:t>
   </x:si>
   <x:si>
@@ -261,10 +231,6 @@
     <x:t xml:space="preserve">收取利息</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">满5金币收获1金币
-最多收获30金币</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Interest</x:t>
   </x:si>
   <x:si>
@@ -346,9 +312,6 @@
     <x:t xml:space="preserve">lg_normal</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">普通美食大组</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">1|1|1|1|2|2|2|2</x:t>
   </x:si>
   <x:si>
@@ -361,9 +324,6 @@
     <x:t xml:space="preserve">lg_normalHard</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">普通困难美食大组</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">0|0|0|0|1|1|1|1</x:t>
   </x:si>
   <x:si>
@@ -376,9 +336,6 @@
     <x:t xml:space="preserve">lg_hard</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">困难美食大组</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">0|0|0|0|0|0|0|0</x:t>
   </x:si>
   <x:si>
@@ -1142,9 +1099,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">sg_food_b</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">美食B</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">sg_normalHard_56</x:t>
@@ -2997,87 +2951,87 @@
       <x:c r="E2" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F2" s="1" t="s">
+      <x:c r="F2" s="1" t="str">
+        <x:v>Food:关联具体食物 TbFood.id(1:1)</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G2" s="1" t="s">
+      <x:c r="H2" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H2" s="1" t="s">
+      <x:c r="I2" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I2" s="1" t="s">
+      <x:c r="J2" s="1" t="str">
+        <x:v>本次最小耗时(0.1 天)</x:v>
+      </x:c>
+      <x:c r="K2" s="1" t="str">
+        <x:v>本次最大耗时(0.1 天)</x:v>
+      </x:c>
+      <x:c r="L2" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="J2" s="1" t="s">
+      <x:c r="M2" s="6" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="K2" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="L2" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="M2" s="6" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="17">
       <x:c r="A3" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F3" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G3" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B3" s="1" t="s">
+      <x:c r="H3" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C3" s="1" t="s">
+      <x:c r="I3" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J3" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D3" s="1" t="s">
+      <x:c r="K3" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F3" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G3" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H3" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="I3" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="J3" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="K3" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="L3" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="M3" s="6" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="17">
       <x:c r="B4" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F4" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C4" s="1" t="s">
+      <x:c r="G4" s="1" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F4" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="G4" s="1" t="s">
-        <x:v>35</x:v>
       </x:c>
       <x:c r="H4" s="1">
         <x:v>0</x:v>
@@ -3089,27 +3043,27 @@
         <x:v>1.2</x:v>
       </x:c>
       <x:c r="L4" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="M4" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="17">
       <x:c r="B5" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F5" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G5" s="1" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F5" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G5" s="1" t="s">
-        <x:v>35</x:v>
       </x:c>
       <x:c r="H5" s="1">
         <x:v>0</x:v>
@@ -3121,27 +3075,27 @@
         <x:v>1.2</x:v>
       </x:c>
       <x:c r="L5" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="M5" s="6" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="17">
       <x:c r="B6" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F6" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G6" s="1" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F6" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G6" s="1" t="s">
-        <x:v>35</x:v>
       </x:c>
       <x:c r="H6" s="1">
         <x:v>0</x:v>
@@ -3152,28 +3106,28 @@
       <x:c r="K6" s="1">
         <x:v>1.2</x:v>
       </x:c>
-      <x:c r="L6" t="s">
-        <x:v>44</x:v>
+      <x:c r="L6" t="str">
+        <x:v>装饰品和消耗品2 选 1</x:v>
       </x:c>
       <x:c r="M6" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="4" customFormat="1" ht="17">
       <x:c r="B7" s="4" t="s">
-        <x:v>46</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E7" s="4" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F7" s="4" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G7" s="4" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="E7" s="4" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F7" s="4" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G7" s="4" t="s">
-        <x:v>35</x:v>
       </x:c>
       <x:c r="H7" s="4">
         <x:v>0</x:v>
@@ -3185,28 +3139,28 @@
       <x:c r="K7" s="1">
         <x:v>1.2</x:v>
       </x:c>
-      <x:c r="L7" t="s">
-        <x:v>48</x:v>
+      <x:c r="L7" t="str">
+        <x:v>强化箱2 选 1</x:v>
       </x:c>
       <x:c r="M7" s="6" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="4" customFormat="1" ht="17">
       <x:c r="B8" s="4" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C8" s="4" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E8" s="4" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F8" s="4" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G8" s="4" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="E8" s="4" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F8" s="4" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G8" s="4" t="s">
-        <x:v>35</x:v>
       </x:c>
       <x:c r="H8" s="4">
         <x:v>0</x:v>
@@ -3218,28 +3172,28 @@
       <x:c r="K8" s="1">
         <x:v>1.2</x:v>
       </x:c>
-      <x:c r="L8" t="s">
-        <x:v>52</x:v>
+      <x:c r="L8" t="str">
+        <x:v>调整单2 选 1</x:v>
       </x:c>
       <x:c r="M8" s="6" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="17">
       <x:c r="B9" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H9" s="1">
         <x:v>0</x:v>
@@ -3251,27 +3205,27 @@
         <x:v>1.3</x:v>
       </x:c>
       <x:c r="L9" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M9" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="17">
       <x:c r="B10" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H10" s="1">
         <x:v>0</x:v>
@@ -3283,27 +3237,27 @@
         <x:v>1.3</x:v>
       </x:c>
       <x:c r="L10" t="s">
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M10" s="6" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="17">
       <x:c r="B11" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H11" s="1">
         <x:v>0</x:v>
@@ -3314,28 +3268,28 @@
       <x:c r="K11" s="1">
         <x:v>1.3</x:v>
       </x:c>
-      <x:c r="L11" t="s">
-        <x:v>63</x:v>
+      <x:c r="L11" t="str">
+        <x:v>装饰品和消耗品4 选 1</x:v>
       </x:c>
       <x:c r="M11" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="4" customFormat="1" ht="17">
       <x:c r="B12" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E12" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F12" s="4" t="s">
-        <x:v>65</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G12" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H12" s="4">
         <x:v>0</x:v>
@@ -3347,28 +3301,28 @@
       <x:c r="K12" s="1">
         <x:v>1.3</x:v>
       </x:c>
-      <x:c r="L12" t="s">
-        <x:v>66</x:v>
+      <x:c r="L12" t="str">
+        <x:v>强化箱4 选 1</x:v>
       </x:c>
       <x:c r="M12" s="6" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="4" customFormat="1" ht="17">
       <x:c r="B13" s="4" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E13" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F13" s="4" t="s">
-        <x:v>68</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G13" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H13" s="4">
         <x:v>0</x:v>
@@ -3380,25 +3334,25 @@
       <x:c r="K13" s="1">
         <x:v>1.3</x:v>
       </x:c>
-      <x:c r="L13" t="s">
-        <x:v>69</x:v>
+      <x:c r="L13" t="str">
+        <x:v>调整单4 选 1</x:v>
       </x:c>
       <x:c r="M13" s="6" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="B14" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H14" s="1">
         <x:v>0</x:v>
@@ -3414,19 +3368,19 @@
     </x:row>
     <x:row r="15">
       <x:c r="B15" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H15" s="1">
         <x:v>0</x:v>
@@ -3442,19 +3396,19 @@
     </x:row>
     <x:row r="16" ht="17">
       <x:c r="B16" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D16" s="5" t="s">
-        <x:v>79</x:v>
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D16" s="5" t="str">
+        <x:v>琳琅满目的食物与装饰品和消耗品</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H16" s="1">
         <x:v>0</x:v>
@@ -3470,25 +3424,26 @@
     </x:row>
     <x:row r="17" ht="34">
       <x:c r="B17" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D17" s="5" t="s">
-        <x:v>83</x:v>
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D17" s="5" t="str">
+        <x:v>满5 金币收获1 金币
+最多收获30 金币</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H17" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I17" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="J17" s="1">
         <x:v>0</x:v>
@@ -3501,19 +3456,19 @@
     </x:row>
     <x:row r="18">
       <x:c r="B18" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H18" s="1">
         <x:v>0</x:v>
@@ -3562,19 +3517,19 @@
     </x:row>
     <x:row r="20">
       <x:c r="B20" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D20" s="1" t="str">
-        <x:v>扣除200金币</x:v>
+        <x:v>扣除200 金币</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H20" s="1" t="n">
         <x:v>-200</x:v>
@@ -3591,19 +3546,19 @@
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="H21" s="1">
         <x:v>0</x:v>
@@ -3658,16 +3613,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F1" t="s">
-        <x:v>99</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G1" t="s">
-        <x:v>100</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H1" s="1"/>
       <x:c r="I1"/>
@@ -3684,22 +3639,22 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H2" s="1"/>
       <x:c r="I2"/>
@@ -3713,25 +3668,25 @@
     </x:row>
     <x:row r="3" s="1" customFormat="1">
       <x:c r="A3" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F3" t="s">
-        <x:v>108</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G3" t="s">
-        <x:v>109</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H3" s="1"/>
       <x:c r="I3"/>
@@ -3745,22 +3700,22 @@
     </x:row>
     <x:row r="4" s="1" customFormat="1">
       <x:c r="B4" s="1" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="C4" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="str">
+        <x:v>日常营业大组</x:v>
       </x:c>
       <x:c r="D4">
         <x:v>400</x:v>
       </x:c>
       <x:c r="E4" s="2" t="s">
-        <x:v>112</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F4" s="2" t="s">
-        <x:v>113</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G4" s="2" t="s">
-        <x:v>114</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H4" s="3" t="str">
         <x:f>""</x:f>
@@ -3847,22 +3802,22 @@
     </x:row>
     <x:row r="8" s="1" customFormat="1">
       <x:c r="B8" s="1" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="str">
+        <x:v>日常与火热营业大组</x:v>
       </x:c>
       <x:c r="D8">
         <x:v>200</x:v>
       </x:c>
       <x:c r="E8" s="2" t="s">
-        <x:v>117</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="F8" s="2" t="s">
-        <x:v>118</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G8" s="2" t="s">
-        <x:v>119</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H8" s="3" t="str">
         <x:f>""</x:f>
@@ -3949,22 +3904,22 @@
     </x:row>
     <x:row r="12" s="1" customFormat="1">
       <x:c r="B12" s="1" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="C12" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="str">
+        <x:v>困难食物大组</x:v>
       </x:c>
       <x:c r="D12">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E12" s="2" t="s">
-        <x:v>122</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F12" s="2" t="s">
-        <x:v>123</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G12" s="2" t="s">
-        <x:v>124</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="H12" s="3" t="str">
         <x:f>""</x:f>
@@ -4052,22 +4007,22 @@
     </x:row>
     <x:row r="16" s="1" customFormat="1">
       <x:c r="B16" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D16">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E16" s="2" t="s">
-        <x:v>122</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F16" s="2" t="s">
-        <x:v>112</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G16" s="2" t="s">
-        <x:v>127</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="H16" s="3" t="str">
         <x:f>""</x:f>
@@ -4155,22 +4110,22 @@
     </x:row>
     <x:row r="20" s="1" customFormat="1">
       <x:c r="B20" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D20">
         <x:v>150</x:v>
       </x:c>
       <x:c r="E20" s="2" t="s">
-        <x:v>122</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F20" s="2" t="s">
-        <x:v>112</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G20" s="2" t="s">
-        <x:v>130</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H20" s="3" t="str">
         <x:f>""</x:f>
@@ -4257,22 +4212,22 @@
     </x:row>
     <x:row r="24" s="1" customFormat="1">
       <x:c r="B24" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D24">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E24" s="2" t="s">
-        <x:v>122</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F24" s="2" t="s">
-        <x:v>112</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G24" s="2" t="s">
-        <x:v>133</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H24" s="3" t="str">
         <x:f>""</x:f>
@@ -4359,22 +4314,22 @@
     </x:row>
     <x:row r="28" s="1" customFormat="1">
       <x:c r="B28" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D28">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E28" s="2" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="F28" s="2" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G28" s="2" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="F28" s="2" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="G28" s="2" t="s">
-        <x:v>136</x:v>
       </x:c>
       <x:c r="H28" s="3" t="str">
         <x:f>""</x:f>
@@ -4550,10 +4505,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="2" s="1" customFormat="1">
@@ -4561,2663 +4516,2663 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1">
       <x:c r="A3" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="1" customFormat="1">
       <x:c r="B4" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1">
       <x:c r="B5" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="R5" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1">
       <x:c r="B6" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="R6" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1">
       <x:c r="B7" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="R7" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="1" customFormat="1">
       <x:c r="B8" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="1" customFormat="1">
       <x:c r="B9" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>162</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="1" customFormat="1">
       <x:c r="B10" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="1" customFormat="1">
       <x:c r="B11" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="1" customFormat="1">
       <x:c r="B12" s="1" t="s">
-        <x:v>170</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="1" customFormat="1">
       <x:c r="B13" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="14" s="1" customFormat="1">
       <x:c r="B14" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="L14" s="1" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="M14" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="M14" s="1" t="str">
+        <x:v>日常营业大组</x:v>
       </x:c>
     </x:row>
     <x:row r="15" s="1" customFormat="1">
       <x:c r="B15" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>181</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="L15" s="1" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="M15" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="M15" s="1" t="str">
+        <x:v>日常与火热营业大组</x:v>
       </x:c>
     </x:row>
     <x:row r="16" s="1" customFormat="1">
       <x:c r="B16" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>183</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="L16" s="1" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="M16" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="M16" s="1" t="str">
+        <x:v>困难食物大组</x:v>
       </x:c>
     </x:row>
     <x:row r="17" s="1" customFormat="1">
       <x:c r="B17" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>187</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="L17" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="M17" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="18" s="1" customFormat="1">
       <x:c r="B18" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>189</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="L18" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="M18" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="19" s="1" customFormat="1">
       <x:c r="B19" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="L19" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="M19" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="20" s="1" customFormat="1">
       <x:c r="B20" s="1" t="s">
-        <x:v>196</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>197</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>198</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="L20" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="M20" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="21" s="1" customFormat="1">
       <x:c r="B21" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="L21" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="M21" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="R21" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="S21" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="T21" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="22" s="1" customFormat="1">
       <x:c r="B22" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>204</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="L22" s="1" t="s">
-        <x:v>206</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="M22" s="1" t="s">
-        <x:v>207</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="R22" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="S22" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="T22" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="23" s="1" customFormat="1">
       <x:c r="B23" s="1" t="s">
-        <x:v>208</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>210</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="R23" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="S23" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="T23" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="24" s="1" customFormat="1">
       <x:c r="B24" s="1" t="s">
-        <x:v>211</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>213</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="R24" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="S24" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="T24" s="1" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="T24" s="1" t="s">
-        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="25" s="1" customFormat="1">
       <x:c r="B25" s="1" t="s">
-        <x:v>214</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>215</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>216</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="R25" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="S25" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="T25" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="26" s="1" customFormat="1">
       <x:c r="B26" s="1" t="s">
-        <x:v>217</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>218</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>219</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="R26" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="S26" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="T26" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="27" s="1" customFormat="1">
       <x:c r="B27" s="1" t="s">
-        <x:v>220</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>221</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>222</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="R27" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="S27" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="T27" s="1" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="T27" s="1" t="s">
-        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="28" s="1" customFormat="1">
       <x:c r="B28" s="1" t="s">
-        <x:v>223</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>225</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="R28" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="S28" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="T28" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="29" s="1" customFormat="1">
       <x:c r="B29" s="1" t="s">
-        <x:v>226</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>227</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="R29" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="S29" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="T29" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="30" s="1" customFormat="1">
       <x:c r="B30" s="1" t="s">
-        <x:v>229</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>230</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>231</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="R30" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="S30" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="S30" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="T30" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="31" s="1" customFormat="1">
       <x:c r="B31" s="1" t="s">
-        <x:v>232</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>233</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>234</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="R31" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="S31" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="32" s="1" customFormat="1">
       <x:c r="B32" s="1" t="s">
-        <x:v>235</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>236</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>237</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="R32" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="S32" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="33" s="1" customFormat="1">
       <x:c r="B33" s="1" t="s">
-        <x:v>238</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>240</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="R33" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="S33" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="34" s="1" customFormat="1">
       <x:c r="B34" s="1" t="s">
-        <x:v>241</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>242</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="R34" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="S34" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="35" s="1" customFormat="1">
       <x:c r="B35" s="1" t="s">
-        <x:v>244</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>245</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="R35" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="S35" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="36" s="1" customFormat="1">
       <x:c r="B36" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>248</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>249</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="R36" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="S36" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="37" s="1" customFormat="1">
       <x:c r="B37" s="1" t="s">
-        <x:v>250</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>251</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>252</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="L37" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="R37" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="S37" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="38" s="1" customFormat="1">
       <x:c r="B38" s="1" t="s">
-        <x:v>253</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>254</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>255</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="L38" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="R38" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="S38" s="1" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="S38" s="1" t="s">
-        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="39" s="1" customFormat="1">
       <x:c r="B39" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>257</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="L39" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="R39" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="S39" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="40" s="1" customFormat="1">
       <x:c r="B40" s="1" t="s">
-        <x:v>259</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>261</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="L40" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="R40" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="S40" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="41" s="1" customFormat="1">
       <x:c r="B41" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="L41" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="42" s="1" customFormat="1">
       <x:c r="B42" s="1" t="s">
-        <x:v>265</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>267</x:v>
+        <x:v>253</x:v>
       </x:c>
     </x:row>
     <x:row r="43" s="1" customFormat="1">
       <x:c r="B43" s="1" t="s">
-        <x:v>268</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>269</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>270</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="L43" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="44" s="1" customFormat="1">
       <x:c r="B44" s="1" t="s">
-        <x:v>271</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>272</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>273</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="L44" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="45" s="1" customFormat="1">
       <x:c r="B45" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>275</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>276</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="L45" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="46" s="1" customFormat="1">
       <x:c r="B46" s="1" t="s">
-        <x:v>277</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>278</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>279</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="L46" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="47" s="1" customFormat="1">
       <x:c r="B47" s="1" t="s">
-        <x:v>280</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>281</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="L47" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="48" s="1" customFormat="1">
       <x:c r="B48" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>285</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="L48" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="49" s="1" customFormat="1">
       <x:c r="B49" s="1" t="s">
-        <x:v>286</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>287</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="L49" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="50" s="1" customFormat="1">
       <x:c r="B50" s="1" t="s">
-        <x:v>289</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>290</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="51" s="1" customFormat="1">
       <x:c r="B51" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>294</x:v>
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="52" s="1" customFormat="1">
       <x:c r="B52" s="1" t="s">
-        <x:v>295</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>296</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>283</x:v>
       </x:c>
     </x:row>
     <x:row r="53" s="1" customFormat="1">
       <x:c r="B53" s="1" t="s">
-        <x:v>298</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>299</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>300</x:v>
+        <x:v>286</x:v>
       </x:c>
     </x:row>
     <x:row r="54" s="1" customFormat="1">
       <x:c r="B54" s="1" t="s">
-        <x:v>301</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>302</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>303</x:v>
+        <x:v>289</x:v>
       </x:c>
     </x:row>
     <x:row r="55" s="1" customFormat="1">
       <x:c r="B55" s="1" t="s">
-        <x:v>304</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>305</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>306</x:v>
+        <x:v>292</x:v>
       </x:c>
     </x:row>
     <x:row r="56" s="1" customFormat="1">
       <x:c r="B56" s="1" t="s">
-        <x:v>307</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>308</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>309</x:v>
+        <x:v>295</x:v>
       </x:c>
     </x:row>
     <x:row r="57" s="1" customFormat="1">
       <x:c r="B57" s="1" t="s">
-        <x:v>310</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>311</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="D57" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>298</x:v>
       </x:c>
     </x:row>
     <x:row r="58" s="1" customFormat="1">
       <x:c r="B58" s="1" t="s">
-        <x:v>313</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>314</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>315</x:v>
+        <x:v>301</x:v>
       </x:c>
     </x:row>
     <x:row r="59" s="1" customFormat="1">
       <x:c r="B59" s="1" t="s">
-        <x:v>316</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>317</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>318</x:v>
+        <x:v>304</x:v>
       </x:c>
     </x:row>
     <x:row r="60" s="1" customFormat="1">
       <x:c r="B60" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="D60" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>321</x:v>
+        <x:v>307</x:v>
       </x:c>
     </x:row>
     <x:row r="61" s="1" customFormat="1">
       <x:c r="B61" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="D61" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>310</x:v>
       </x:c>
     </x:row>
     <x:row r="62" s="1" customFormat="1">
       <x:c r="B62" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>326</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="D62" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>327</x:v>
+        <x:v>313</x:v>
       </x:c>
     </x:row>
     <x:row r="63" s="1" customFormat="1">
       <x:c r="B63" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="D63" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>316</x:v>
       </x:c>
     </x:row>
     <x:row r="64" s="1" customFormat="1">
       <x:c r="B64" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="D64" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>319</x:v>
       </x:c>
     </x:row>
     <x:row r="65" s="1" customFormat="1">
       <x:c r="B65" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="D65" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>322</x:v>
       </x:c>
     </x:row>
     <x:row r="66" s="1" customFormat="1">
       <x:c r="B66" s="1" t="s">
-        <x:v>337</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="D66" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>339</x:v>
+        <x:v>325</x:v>
       </x:c>
     </x:row>
     <x:row r="67" s="1" customFormat="1">
       <x:c r="B67" s="1" t="s">
-        <x:v>340</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>341</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="D67" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>328</x:v>
       </x:c>
     </x:row>
     <x:row r="68" s="1" customFormat="1">
       <x:c r="B68" s="1" t="s">
-        <x:v>343</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="D68" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>331</x:v>
       </x:c>
     </x:row>
     <x:row r="69" s="1" customFormat="1">
       <x:c r="B69" s="1" t="s">
-        <x:v>346</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>347</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="D69" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>348</x:v>
+        <x:v>334</x:v>
       </x:c>
     </x:row>
     <x:row r="70" s="1" customFormat="1">
       <x:c r="B70" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>350</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="D70" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>337</x:v>
       </x:c>
     </x:row>
     <x:row r="71" s="1" customFormat="1">
       <x:c r="B71" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="D71" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>340</x:v>
       </x:c>
     </x:row>
     <x:row r="72" s="1" customFormat="1">
       <x:c r="B72" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="D72" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>343</x:v>
       </x:c>
     </x:row>
     <x:row r="73" s="1" customFormat="1">
       <x:c r="B73" s="1" t="s">
-        <x:v>358</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>359</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="D73" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>360</x:v>
+        <x:v>346</x:v>
       </x:c>
     </x:row>
     <x:row r="74" s="1" customFormat="1">
       <x:c r="B74" s="1" t="s">
-        <x:v>361</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>362</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="D74" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>363</x:v>
+        <x:v>349</x:v>
       </x:c>
     </x:row>
     <x:row r="75" s="1" customFormat="1">
       <x:c r="B75" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>365</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="D75" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>366</x:v>
+        <x:v>352</x:v>
       </x:c>
     </x:row>
     <x:row r="76" s="1" customFormat="1">
       <x:c r="B76" s="1" t="s">
-        <x:v>367</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>368</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="D76" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>369</x:v>
+        <x:v>355</x:v>
       </x:c>
     </x:row>
     <x:row r="77" s="1" customFormat="1">
       <x:c r="B77" s="1" t="s">
-        <x:v>370</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>371</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="D77" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>358</x:v>
       </x:c>
     </x:row>
     <x:row r="78" s="1" customFormat="1">
       <x:c r="B78" s="1" t="s">
-        <x:v>373</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>374</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="D78" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="Q78" s="1" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="R78" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="R78" s="1" t="str">
+        <x:v>食物B</x:v>
       </x:c>
       <x:c r="S78" s="1">
         <x:v>80</x:v>
       </x:c>
       <x:c r="T78" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="79" s="1" customFormat="1">
       <x:c r="B79" s="1" t="s">
-        <x:v>378</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D79" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>380</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="T79" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="80" s="1" customFormat="1">
       <x:c r="B80" s="1" t="s">
-        <x:v>381</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="D80" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="T80" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="81" s="1" customFormat="1">
       <x:c r="B81" s="1" t="s">
-        <x:v>384</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="D81" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>386</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="Q81" s="1" t="s">
-        <x:v>387</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="R81" s="1" t="s">
-        <x:v>388</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="S81" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="T81" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="82" s="1" customFormat="1">
       <x:c r="B82" s="1" t="s">
-        <x:v>389</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>390</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="D82" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>391</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="T82" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="83" s="1" customFormat="1">
       <x:c r="B83" s="1" t="s">
-        <x:v>392</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>393</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="D83" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="T83" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="84" s="1" customFormat="1">
       <x:c r="B84" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="D84" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="Q84" s="1" t="s">
-        <x:v>398</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="R84" s="1" t="s">
-        <x:v>399</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="S84" s="1">
         <x:v>80</x:v>
       </x:c>
       <x:c r="T84" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="85" s="1" customFormat="1">
       <x:c r="B85" s="1" t="s">
-        <x:v>400</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="D85" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>402</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="T85" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="86" s="1" customFormat="1">
       <x:c r="B86" s="1" t="s">
-        <x:v>403</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="D86" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="T86" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="87" s="1" customFormat="1">
       <x:c r="B87" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>407</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="D87" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>408</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="Q87" s="1" t="s">
-        <x:v>409</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="R87" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="S87" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="T87" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="88" s="1" customFormat="1">
       <x:c r="B88" s="1" t="s">
-        <x:v>411</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>412</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="D88" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>413</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="T88" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="89" s="1" customFormat="1">
       <x:c r="B89" s="1" t="s">
-        <x:v>414</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>415</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="D89" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="T89" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="90" s="1" customFormat="1">
       <x:c r="B90" s="1" t="s">
-        <x:v>417</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="D90" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="Q90" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="R90" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="S90" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="T90" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="91" s="1" customFormat="1">
       <x:c r="B91" s="1" t="s">
-        <x:v>422</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>423</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="D91" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="T91" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="92" s="1" customFormat="1">
       <x:c r="B92" s="1" t="s">
-        <x:v>425</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>426</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="D92" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>427</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="Q92" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="R92" s="1" t="s">
-        <x:v>429</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="S92" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="T92" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="93" s="1" customFormat="1">
       <x:c r="B93" s="1" t="s">
-        <x:v>430</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>431</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="D93" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>432</x:v>
+        <x:v>417</x:v>
       </x:c>
     </x:row>
     <x:row r="94" s="1" customFormat="1">
       <x:c r="B94" s="1" t="s">
-        <x:v>433</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>434</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="D94" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>435</x:v>
+        <x:v>420</x:v>
       </x:c>
     </x:row>
     <x:row r="95" s="1" customFormat="1">
       <x:c r="B95" s="1" t="s">
-        <x:v>436</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>437</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="D95" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
-        <x:v>438</x:v>
+        <x:v>423</x:v>
       </x:c>
     </x:row>
     <x:row r="96" s="1" customFormat="1">
       <x:c r="B96" s="1" t="s">
-        <x:v>439</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>440</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="D96" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>441</x:v>
+        <x:v>426</x:v>
       </x:c>
     </x:row>
     <x:row r="97" s="1" customFormat="1">
       <x:c r="B97" s="1" t="s">
-        <x:v>442</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>443</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="D97" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>444</x:v>
+        <x:v>429</x:v>
       </x:c>
     </x:row>
     <x:row r="98" s="1" customFormat="1">
       <x:c r="B98" s="1" t="s">
-        <x:v>445</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>446</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="D98" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>447</x:v>
+        <x:v>432</x:v>
       </x:c>
     </x:row>
     <x:row r="99" s="1" customFormat="1">
       <x:c r="B99" s="1" t="s">
-        <x:v>448</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>449</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="D99" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>435</x:v>
       </x:c>
     </x:row>
     <x:row r="100" s="1" customFormat="1">
       <x:c r="B100" s="1" t="s">
-        <x:v>451</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>452</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="D100" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>453</x:v>
+        <x:v>438</x:v>
       </x:c>
     </x:row>
     <x:row r="101" s="1" customFormat="1">
       <x:c r="B101" s="1" t="s">
-        <x:v>454</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>455</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="D101" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>456</x:v>
+        <x:v>441</x:v>
       </x:c>
     </x:row>
     <x:row r="102" s="1" customFormat="1">
       <x:c r="B102" s="1" t="s">
-        <x:v>457</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="D102" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>444</x:v>
       </x:c>
     </x:row>
     <x:row r="103" s="1" customFormat="1">
       <x:c r="B103" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="D103" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>447</x:v>
       </x:c>
     </x:row>
     <x:row r="104" s="1" customFormat="1">
       <x:c r="B104" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="D104" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>450</x:v>
       </x:c>
     </x:row>
     <x:row r="105" s="1" customFormat="1">
       <x:c r="B105" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>467</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>468</x:v>
+        <x:v>453</x:v>
       </x:c>
     </x:row>
     <x:row r="106" s="1" customFormat="1">
       <x:c r="B106" s="1" t="s">
-        <x:v>469</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>471</x:v>
+        <x:v>456</x:v>
       </x:c>
     </x:row>
     <x:row r="107" s="1" customFormat="1">
       <x:c r="B107" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="D107" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>474</x:v>
+        <x:v>459</x:v>
       </x:c>
     </x:row>
     <x:row r="108" s="1" customFormat="1">
       <x:c r="B108" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="D108" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>462</x:v>
       </x:c>
     </x:row>
     <x:row r="109" s="1" customFormat="1">
       <x:c r="B109" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="D109" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>480</x:v>
+        <x:v>465</x:v>
       </x:c>
     </x:row>
     <x:row r="110" s="1" customFormat="1">
       <x:c r="B110" s="1" t="s">
-        <x:v>481</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>482</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="D110" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E110" s="1" t="s">
-        <x:v>483</x:v>
+        <x:v>468</x:v>
       </x:c>
     </x:row>
     <x:row r="111" s="1" customFormat="1">
       <x:c r="B111" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="D111" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
-        <x:v>486</x:v>
+        <x:v>471</x:v>
       </x:c>
     </x:row>
     <x:row r="112" s="1" customFormat="1">
       <x:c r="B112" s="1" t="s">
-        <x:v>487</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="D112" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
-        <x:v>489</x:v>
+        <x:v>474</x:v>
       </x:c>
     </x:row>
     <x:row r="113" s="1" customFormat="1">
       <x:c r="B113" s="1" t="s">
-        <x:v>490</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
-        <x:v>491</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D113" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E113" s="1" t="s">
-        <x:v>492</x:v>
+        <x:v>477</x:v>
       </x:c>
     </x:row>
     <x:row r="114" s="1" customFormat="1">
       <x:c r="B114" s="1" t="s">
-        <x:v>493</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C114" s="1" t="s">
-        <x:v>494</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="D114" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E114" s="1" t="s">
-        <x:v>495</x:v>
+        <x:v>480</x:v>
       </x:c>
     </x:row>
     <x:row r="115" s="1" customFormat="1">
       <x:c r="B115" s="1" t="s">
-        <x:v>496</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="C115" s="1" t="s">
-        <x:v>497</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="D115" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E115" s="1" t="s">
-        <x:v>498</x:v>
+        <x:v>483</x:v>
       </x:c>
     </x:row>
     <x:row r="116" s="1" customFormat="1">
       <x:c r="B116" s="1" t="s">
-        <x:v>499</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="C116" s="1" t="s">
-        <x:v>500</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="D116" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E116" s="1" t="s">
-        <x:v>501</x:v>
+        <x:v>486</x:v>
       </x:c>
     </x:row>
     <x:row r="117" s="1" customFormat="1">
       <x:c r="B117" s="1" t="s">
-        <x:v>502</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="C117" s="1" t="s">
-        <x:v>503</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="D117" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E117" s="1" t="s">
-        <x:v>504</x:v>
+        <x:v>489</x:v>
       </x:c>
     </x:row>
     <x:row r="118" s="1" customFormat="1">
       <x:c r="B118" s="1" t="s">
-        <x:v>505</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="C118" s="1" t="s">
-        <x:v>506</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="D118" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E118" s="1" t="s">
-        <x:v>507</x:v>
+        <x:v>492</x:v>
       </x:c>
     </x:row>
     <x:row r="119" s="1" customFormat="1">
       <x:c r="B119" s="1" t="s">
-        <x:v>508</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="C119" s="1" t="s">
-        <x:v>509</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="D119" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E119" s="1" t="s">
-        <x:v>510</x:v>
+        <x:v>495</x:v>
       </x:c>
     </x:row>
     <x:row r="120" s="1" customFormat="1">
       <x:c r="B120" s="1" t="s">
-        <x:v>511</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="C120" s="1" t="s">
-        <x:v>512</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="D120" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E120" s="1" t="s">
-        <x:v>513</x:v>
+        <x:v>498</x:v>
       </x:c>
     </x:row>
     <x:row r="121" s="1" customFormat="1">
       <x:c r="B121" s="1" t="s">
-        <x:v>514</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="C121" s="1" t="s">
-        <x:v>515</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="D121" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E121" s="1" t="s">
-        <x:v>516</x:v>
+        <x:v>501</x:v>
       </x:c>
     </x:row>
     <x:row r="122" s="1" customFormat="1">
       <x:c r="B122" s="1" t="s">
-        <x:v>517</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="C122" s="1" t="s">
-        <x:v>518</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="D122" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E122" s="1" t="s">
-        <x:v>519</x:v>
+        <x:v>504</x:v>
       </x:c>
     </x:row>
     <x:row r="123" s="1" customFormat="1">
       <x:c r="B123" s="1" t="s">
-        <x:v>520</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="C123" s="1" t="s">
-        <x:v>521</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="D123" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E123" s="1" t="s">
-        <x:v>522</x:v>
+        <x:v>507</x:v>
       </x:c>
     </x:row>
     <x:row r="124" s="1" customFormat="1">
       <x:c r="B124" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C124" s="1" t="s">
-        <x:v>523</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="D124" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E124" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="125" s="1" customFormat="1">
       <x:c r="B125" s="1" t="s">
-        <x:v>524</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="C125" s="1" t="s">
-        <x:v>525</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="D125" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E125" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="126" s="1" customFormat="1">
       <x:c r="B126" s="1" t="s">
-        <x:v>526</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="C126" s="1" t="s">
-        <x:v>527</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="D126" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E126" s="1" t="s">
-        <x:v>528</x:v>
+        <x:v>513</x:v>
       </x:c>
     </x:row>
     <x:row r="127" s="1" customFormat="1">
       <x:c r="B127" s="1" t="s">
-        <x:v>529</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="C127" s="1" t="s">
-        <x:v>530</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="D127" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E127" s="1" t="s">
-        <x:v>531</x:v>
+        <x:v>516</x:v>
       </x:c>
     </x:row>
     <x:row r="128" s="1" customFormat="1">
       <x:c r="B128" s="1" t="s">
-        <x:v>532</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="C128" s="1" t="s">
-        <x:v>533</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="D128" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E128" s="1" t="s">
-        <x:v>534</x:v>
+        <x:v>519</x:v>
       </x:c>
     </x:row>
     <x:row r="129" s="1" customFormat="1">
       <x:c r="B129" s="1" t="s">
-        <x:v>535</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C129" s="1" t="s">
-        <x:v>536</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="D129" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E129" s="1" t="s">
-        <x:v>537</x:v>
+        <x:v>522</x:v>
       </x:c>
     </x:row>
     <x:row r="130" s="1" customFormat="1">
       <x:c r="B130" s="1" t="s">
-        <x:v>538</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="C130" s="1" t="s">
-        <x:v>539</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="D130" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E130" s="1" t="s">
-        <x:v>540</x:v>
+        <x:v>525</x:v>
       </x:c>
     </x:row>
     <x:row r="131" s="1" customFormat="1">
       <x:c r="B131" s="1" t="s">
-        <x:v>541</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="C131" s="1" t="s">
-        <x:v>542</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="D131" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E131" s="1" t="s">
-        <x:v>543</x:v>
+        <x:v>528</x:v>
       </x:c>
     </x:row>
     <x:row r="132" s="1" customFormat="1">
       <x:c r="B132" s="1" t="s">
-        <x:v>544</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="C132" s="1" t="s">
-        <x:v>545</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="D132" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E132" s="1" t="s">
-        <x:v>546</x:v>
+        <x:v>531</x:v>
       </x:c>
     </x:row>
     <x:row r="133" s="1" customFormat="1">
       <x:c r="B133" s="1" t="s">
-        <x:v>547</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="C133" s="1" t="s">
-        <x:v>548</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="D133" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E133" s="1" t="s">
-        <x:v>549</x:v>
+        <x:v>534</x:v>
       </x:c>
     </x:row>
     <x:row r="134" s="1" customFormat="1">
       <x:c r="B134" s="1" t="s">
-        <x:v>550</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="C134" s="1" t="s">
-        <x:v>551</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="D134" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E134" s="1" t="s">
-        <x:v>552</x:v>
+        <x:v>537</x:v>
       </x:c>
     </x:row>
     <x:row r="135" s="1" customFormat="1">
       <x:c r="B135" s="1" t="s">
-        <x:v>553</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="C135" s="1" t="s">
-        <x:v>554</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="D135" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E135" s="1" t="s">
-        <x:v>555</x:v>
+        <x:v>540</x:v>
       </x:c>
     </x:row>
     <x:row r="136" s="1" customFormat="1">
       <x:c r="B136" s="1" t="s">
-        <x:v>556</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="C136" s="1" t="s">
-        <x:v>557</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="D136" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E136" s="1" t="s">
-        <x:v>558</x:v>
+        <x:v>543</x:v>
       </x:c>
     </x:row>
     <x:row r="137" s="1" customFormat="1">
       <x:c r="B137" s="1" t="s">
-        <x:v>559</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="C137" s="1" t="s">
-        <x:v>560</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="D137" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E137" s="1" t="s">
-        <x:v>561</x:v>
+        <x:v>546</x:v>
       </x:c>
     </x:row>
     <x:row r="138" s="1" customFormat="1">
       <x:c r="B138" s="1" t="s">
-        <x:v>562</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="C138" s="1" t="s">
-        <x:v>563</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="D138" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E138" s="1" t="s">
-        <x:v>564</x:v>
+        <x:v>549</x:v>
       </x:c>
     </x:row>
     <x:row r="139" s="1" customFormat="1">
       <x:c r="B139" s="1" t="s">
-        <x:v>565</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="C139" s="1" t="s">
-        <x:v>566</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="D139" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E139" s="1" t="s">
-        <x:v>567</x:v>
+        <x:v>552</x:v>
       </x:c>
     </x:row>
     <x:row r="140" s="1" customFormat="1">
       <x:c r="B140" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C140" s="1" t="s">
-        <x:v>568</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="D140" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E140" s="1" t="s">
-        <x:v>569</x:v>
+        <x:v>554</x:v>
       </x:c>
     </x:row>
     <x:row r="141" s="1" customFormat="1">
       <x:c r="B141" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C141" s="1" t="s">
-        <x:v>570</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="D141" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E141" s="1" t="s">
-        <x:v>571</x:v>
+        <x:v>556</x:v>
       </x:c>
     </x:row>
     <x:row r="142" s="1" customFormat="1">
       <x:c r="B142" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="C142" s="1" t="s">
-        <x:v>573</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="D142" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E142" s="1" t="s">
-        <x:v>574</x:v>
+        <x:v>559</x:v>
       </x:c>
     </x:row>
     <x:row r="143" s="1" customFormat="1">
       <x:c r="B143" s="1" t="s">
-        <x:v>575</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="C143" s="1" t="s">
-        <x:v>576</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="D143" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E143" s="1" t="s">
-        <x:v>577</x:v>
+        <x:v>562</x:v>
       </x:c>
     </x:row>
     <x:row r="144" s="1" customFormat="1">
       <x:c r="B144" s="1" t="s">
-        <x:v>578</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="C144" s="1" t="s">
-        <x:v>579</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="D144" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E144" s="1" t="s">
-        <x:v>580</x:v>
+        <x:v>565</x:v>
       </x:c>
     </x:row>
     <x:row r="145" s="1" customFormat="1">
       <x:c r="B145" s="1" t="s">
-        <x:v>581</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="C145" s="1" t="s">
-        <x:v>582</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="D145" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E145" s="1" t="s">
-        <x:v>583</x:v>
+        <x:v>568</x:v>
       </x:c>
     </x:row>
     <x:row r="146" s="1" customFormat="1">
       <x:c r="B146" s="1" t="s">
-        <x:v>584</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="C146" s="1" t="s">
-        <x:v>585</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="D146" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E146" s="1" t="s">
-        <x:v>586</x:v>
+        <x:v>571</x:v>
       </x:c>
     </x:row>
     <x:row r="147" s="1" customFormat="1">
       <x:c r="B147" s="1" t="s">
-        <x:v>587</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C147" s="1" t="s">
-        <x:v>588</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="D147" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E147" s="1" t="s">
-        <x:v>589</x:v>
+        <x:v>574</x:v>
       </x:c>
     </x:row>
     <x:row r="148" s="1" customFormat="1">
       <x:c r="B148" s="1" t="s">
-        <x:v>590</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="C148" s="1" t="s">
-        <x:v>591</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="D148" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E148" s="1" t="s">
-        <x:v>592</x:v>
+        <x:v>577</x:v>
       </x:c>
     </x:row>
     <x:row r="149" s="1" customFormat="1">
       <x:c r="B149" s="1" t="s">
-        <x:v>593</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="C149" s="1" t="s">
-        <x:v>594</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="D149" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E149" s="1" t="s">
-        <x:v>595</x:v>
+        <x:v>580</x:v>
       </x:c>
     </x:row>
     <x:row r="150" s="1" customFormat="1">
       <x:c r="B150" s="1" t="s">
-        <x:v>596</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="C150" s="1" t="s">
-        <x:v>597</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="D150" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E150" s="1" t="s">
-        <x:v>598</x:v>
+        <x:v>583</x:v>
       </x:c>
     </x:row>
     <x:row r="151" s="1" customFormat="1">
       <x:c r="B151" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C151" s="1" t="s">
-        <x:v>599</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="D151" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E151" s="1" t="s">
-        <x:v>600</x:v>
+        <x:v>585</x:v>
       </x:c>
     </x:row>
     <x:row r="152" s="1" customFormat="1">
       <x:c r="B152" s="1" t="s">
-        <x:v>601</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="C152" s="1" t="s">
-        <x:v>602</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="D152" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E152" s="1" t="s">
-        <x:v>603</x:v>
+        <x:v>588</x:v>
       </x:c>
     </x:row>
     <x:row r="153" s="1" customFormat="1">
       <x:c r="B153" s="1" t="s">
-        <x:v>604</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="C153" s="1" t="s">
-        <x:v>605</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="D153" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E153" s="1" t="s">
-        <x:v>606</x:v>
+        <x:v>591</x:v>
       </x:c>
     </x:row>
     <x:row r="154" s="1" customFormat="1">
       <x:c r="B154" s="1" t="s">
-        <x:v>607</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="C154" s="1" t="s">
-        <x:v>608</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="D154" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E154" s="1" t="s">
-        <x:v>609</x:v>
+        <x:v>594</x:v>
       </x:c>
     </x:row>
     <x:row r="155" s="1" customFormat="1">
       <x:c r="B155" s="1" t="s">
-        <x:v>610</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="C155" s="1" t="s">
-        <x:v>611</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="D155" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E155" s="1" t="s">
-        <x:v>612</x:v>
+        <x:v>597</x:v>
       </x:c>
     </x:row>
     <x:row r="156" s="1" customFormat="1">
       <x:c r="B156" s="1" t="s">
-        <x:v>613</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="C156" s="1" t="s">
-        <x:v>614</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="D156" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E156" s="1" t="s">
-        <x:v>615</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="157" s="1" customFormat="1">
       <x:c r="B157" s="1" t="s">
-        <x:v>616</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="C157" s="1" t="s">
-        <x:v>617</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="D157" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E157" s="1" t="s">
-        <x:v>618</x:v>
+        <x:v>603</x:v>
       </x:c>
     </x:row>
     <x:row r="158" s="1" customFormat="1">
       <x:c r="B158" s="1" t="s">
-        <x:v>619</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="C158" s="1" t="s">
-        <x:v>620</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="D158" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E158" s="1" t="s">
-        <x:v>621</x:v>
+        <x:v>606</x:v>
       </x:c>
     </x:row>
     <x:row r="159" s="1" customFormat="1">
       <x:c r="B159" s="1" t="s">
-        <x:v>622</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="C159" s="1" t="s">
-        <x:v>623</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="D159" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E159" s="1" t="s">
-        <x:v>624</x:v>
+        <x:v>609</x:v>
       </x:c>
     </x:row>
     <x:row r="160" s="1" customFormat="1">
       <x:c r="B160" s="1" t="s">
-        <x:v>625</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="C160" s="1" t="s">
-        <x:v>626</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="D160" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E160" s="1" t="s">
-        <x:v>627</x:v>
+        <x:v>612</x:v>
       </x:c>
     </x:row>
     <x:row r="161" s="1" customFormat="1">
       <x:c r="B161" s="1" t="s">
-        <x:v>628</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="C161" s="1" t="s">
-        <x:v>629</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="D161" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E161" s="1" t="s">
-        <x:v>630</x:v>
+        <x:v>615</x:v>
       </x:c>
     </x:row>
     <x:row r="162" s="1" customFormat="1">
       <x:c r="B162" s="1" t="s">
-        <x:v>631</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="C162" s="1" t="s">
-        <x:v>632</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="D162" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E162" s="1" t="s">
-        <x:v>633</x:v>
+        <x:v>618</x:v>
       </x:c>
     </x:row>
     <x:row r="163" s="1" customFormat="1">
       <x:c r="B163" s="1" t="s">
-        <x:v>634</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="C163" s="1" t="s">
-        <x:v>635</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="D163" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E163" s="1" t="s">
-        <x:v>636</x:v>
+        <x:v>621</x:v>
       </x:c>
     </x:row>
     <x:row r="164" s="1" customFormat="1">
       <x:c r="B164" s="1" t="s">
-        <x:v>637</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="C164" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="D164" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E164" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>624</x:v>
       </x:c>
     </x:row>
     <x:row r="165" s="1" customFormat="1">
       <x:c r="B165" s="1" t="s">
-        <x:v>640</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="C165" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="D165" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E165" s="1" t="s">
-        <x:v>642</x:v>
+        <x:v>627</x:v>
       </x:c>
     </x:row>
     <x:row r="166" s="1" customFormat="1">
       <x:c r="B166" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="C166" s="1" t="s">
-        <x:v>429</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="D166" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E166" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -255,7 +255,7 @@
     <t>商店采购</t>
   </si>
   <si>
-    <t>琳琅满目的食物与装饰品和消耗品</t>
+    <t>什么都有</t>
   </si>
   <si>
     <t>Shop</t>
@@ -267,8 +267,8 @@
     <t>收取利息</t>
   </si>
   <si>
-    <t>满5 金币收获1 金币
-最多收获30 金币</t>
+    <t>满3金币收获1金币
+最多收获50金币</t>
   </si>
   <si>
     <t>Interest</t>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15360" activeTab="2"/>
+    <workbookView windowHeight="15400" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="action" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="154">
   <si>
     <t>##var</t>
   </si>
@@ -446,7 +446,13 @@
     <t>FragmentChoice</t>
   </si>
   <si>
+    <t>0|0|0|0|0|0|1|1|1|1|1|1|1|1|1|1|1|1|1</t>
+  </si>
+  <si>
     <t>0|0|1|1|1|1|1|2|2|2|2|2|2|2|3|3|3|3|3|3|3</t>
+  </si>
+  <si>
+    <t>0|1|1|1|1|1|2|2|2|2|2|3|3|3|3|3</t>
   </si>
   <si>
     <t>passive</t>
@@ -1075,7 +1081,7 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3105,11 +3111,11 @@
       <c r="E8" s="6">
         <v>1</v>
       </c>
-      <c r="F8" s="6">
-        <v>-1</v>
+      <c r="F8" s="6" t="s">
+        <v>142</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -3120,11 +3126,11 @@
       <c r="E9" s="6">
         <v>1</v>
       </c>
-      <c r="F9" s="6">
-        <v>-1</v>
-      </c>
-      <c r="G9" s="11">
-        <v>-1</v>
+      <c r="F9" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -3135,11 +3141,11 @@
       <c r="E10" s="6">
         <v>1</v>
       </c>
-      <c r="F10" s="6">
-        <v>-1</v>
-      </c>
-      <c r="G10" s="11">
-        <v>-1</v>
+      <c r="F10" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -3150,23 +3156,23 @@
       <c r="E11" s="6">
         <v>1</v>
       </c>
-      <c r="F11" s="6">
-        <v>-1</v>
-      </c>
-      <c r="G11" s="11">
-        <v>-1</v>
+      <c r="F11" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="5"/>
       <c r="B12" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E12" s="6">
         <v>1</v>
@@ -3226,13 +3232,13 @@
     <row r="16" spans="1:7">
       <c r="A16" s="5"/>
       <c r="B16" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E16" s="6">
         <v>1</v>
@@ -3292,13 +3298,13 @@
     <row r="20" spans="1:7">
       <c r="A20" s="5"/>
       <c r="B20" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E20" s="6">
         <v>1</v>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15400" activeTab="3"/>
+    <workbookView windowHeight="15400"/>
   </bookViews>
   <sheets>
     <sheet name="action" sheetId="1" r:id="rId1"/>
@@ -268,7 +268,7 @@
     <t>收取利息</t>
   </si>
   <si>
-    <t>满3金币收获1金币
+    <t>满4金币收获1金币
 最多收获50金币</t>
   </si>
   <si>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15400"/>
+    <workbookView windowHeight="15240"/>
   </bookViews>
   <sheets>
     <sheet name="action" sheetId="1" r:id="rId1"/>
@@ -1947,10 +1947,10 @@
       </c>
       <c r="I4" s="22"/>
       <c r="J4" s="22">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K4" s="22">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="L4" s="22" t="s">
         <v>36</v>
@@ -1982,10 +1982,10 @@
       </c>
       <c r="I5" s="22"/>
       <c r="J5" s="22">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K5" s="22">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="L5" s="22" t="s">
         <v>40</v>
@@ -2017,10 +2017,10 @@
       </c>
       <c r="I6" s="22"/>
       <c r="J6" s="22">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K6" s="22">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="L6" s="22" t="s">
         <v>44</v>
@@ -2052,10 +2052,10 @@
       </c>
       <c r="I7" s="22"/>
       <c r="J7" s="22">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K7" s="22">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="L7" s="22" t="s">
         <v>48</v>
@@ -2087,10 +2087,10 @@
       </c>
       <c r="I8" s="22"/>
       <c r="J8" s="22">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K8" s="22">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="L8" s="22" t="s">
         <v>52</v>
@@ -2122,10 +2122,10 @@
       </c>
       <c r="I9" s="22"/>
       <c r="J9" s="22">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K9" s="22">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="L9" s="22" t="s">
         <v>57</v>
@@ -2157,10 +2157,10 @@
       </c>
       <c r="I10" s="22"/>
       <c r="J10" s="22">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K10" s="22">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="L10" s="22" t="s">
         <v>60</v>
@@ -2192,10 +2192,10 @@
       </c>
       <c r="I11" s="22"/>
       <c r="J11" s="22">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K11" s="22">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="L11" s="22" t="s">
         <v>63</v>
@@ -2227,10 +2227,10 @@
       </c>
       <c r="I12" s="22"/>
       <c r="J12" s="22">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K12" s="22">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="L12" s="22" t="s">
         <v>66</v>
@@ -2262,10 +2262,10 @@
       </c>
       <c r="I13" s="22"/>
       <c r="J13" s="22">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K13" s="22">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="L13" s="22" t="s">
         <v>69</v>
@@ -2295,10 +2295,10 @@
       </c>
       <c r="I14" s="22"/>
       <c r="J14" s="22">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="K14" s="22">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="L14" s="22"/>
       <c r="M14" s="26"/>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15160"/>
+    <workbookView windowHeight="15160" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="action" sheetId="1" r:id="rId1"/>
@@ -459,7 +459,7 @@
     <t>0|0|0|0|0|0|1|1|1|1|1|1|1|1|1|1|1|1|1</t>
   </si>
   <si>
-    <t>0|0|0|0|1|1|1|1|2|2|2|2|2|2|3|3|3|3|3|3|3</t>
+    <t>0|0|0|0|1|1|1|1|1|1|2|2|2|2|2|2|3|3|3|3|3</t>
   </si>
   <si>
     <t>passive</t>
@@ -1209,7 +1209,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1243,6 +1243,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="49" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="49" applyBorder="1" applyAlignment="1">
@@ -1767,19 +1770,19 @@
   <dimension ref="A1:M22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="12" style="21" customWidth="1"/>
-    <col min="2" max="2" width="31" style="21" customWidth="1"/>
-    <col min="3" max="3" width="17" style="21" customWidth="1"/>
-    <col min="4" max="4" width="32" style="21" customWidth="1"/>
-    <col min="5" max="5" width="17" style="21" customWidth="1"/>
-    <col min="6" max="6" width="26" style="21" customWidth="1"/>
-    <col min="7" max="7" width="22" style="21" customWidth="1"/>
-    <col min="8" max="8" width="15" style="21" customWidth="1"/>
-    <col min="9" max="9" width="23" style="21" customWidth="1"/>
-    <col min="10" max="11" width="18" style="21" customWidth="1"/>
-    <col min="12" max="12" width="21" style="21" customWidth="1"/>
-    <col min="13" max="13" width="24" style="21" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="22"/>
+    <col min="1" max="1" width="12" style="22" customWidth="1"/>
+    <col min="2" max="2" width="31" style="22" customWidth="1"/>
+    <col min="3" max="3" width="17" style="22" customWidth="1"/>
+    <col min="4" max="4" width="32" style="22" customWidth="1"/>
+    <col min="5" max="5" width="17" style="22" customWidth="1"/>
+    <col min="6" max="6" width="26" style="22" customWidth="1"/>
+    <col min="7" max="7" width="22" style="22" customWidth="1"/>
+    <col min="8" max="8" width="15" style="22" customWidth="1"/>
+    <col min="9" max="9" width="23" style="22" customWidth="1"/>
+    <col min="10" max="11" width="18" style="22" customWidth="1"/>
+    <col min="12" max="12" width="21" style="22" customWidth="1"/>
+    <col min="13" max="13" width="24" style="22" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1" spans="1:13">
@@ -1906,628 +1909,628 @@
       </c>
     </row>
     <row r="4" ht="17" customHeight="1" spans="1:13">
-      <c r="A4" s="23"/>
-      <c r="B4" s="24" t="s">
+      <c r="A4" s="24"/>
+      <c r="B4" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24" t="s">
+      <c r="D4" s="25"/>
+      <c r="E4" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="H4" s="24">
-        <v>0</v>
-      </c>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24">
+      <c r="H4" s="25">
+        <v>0</v>
+      </c>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25">
         <v>0.6</v>
       </c>
-      <c r="K4" s="24">
+      <c r="K4" s="25">
         <v>0.8</v>
       </c>
-      <c r="L4" s="24" t="s">
+      <c r="L4" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="M4" s="27" t="s">
+      <c r="M4" s="28" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:13">
-      <c r="A5" s="23"/>
-      <c r="B5" s="24" t="s">
+      <c r="A5" s="24"/>
+      <c r="B5" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24" t="s">
+      <c r="D5" s="25"/>
+      <c r="E5" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="24" t="s">
+      <c r="F5" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="24" t="s">
+      <c r="G5" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="24">
-        <v>0</v>
-      </c>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24">
+      <c r="H5" s="25">
+        <v>0</v>
+      </c>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25">
         <v>0.6</v>
       </c>
-      <c r="K5" s="24">
+      <c r="K5" s="25">
         <v>0.8</v>
       </c>
-      <c r="L5" s="24" t="s">
+      <c r="L5" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="M5" s="27" t="s">
+      <c r="M5" s="28" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1" spans="1:13">
-      <c r="A6" s="23"/>
-      <c r="B6" s="24" t="s">
+      <c r="A6" s="24"/>
+      <c r="B6" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24" t="s">
+      <c r="D6" s="25"/>
+      <c r="E6" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="F6" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="G6" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="24">
-        <v>0</v>
-      </c>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24">
+      <c r="H6" s="25">
+        <v>0</v>
+      </c>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25">
         <v>0.6</v>
       </c>
-      <c r="K6" s="24">
+      <c r="K6" s="25">
         <v>0.8</v>
       </c>
-      <c r="L6" s="24" t="s">
+      <c r="L6" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="M6" s="27" t="s">
+      <c r="M6" s="28" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1" spans="1:13">
-      <c r="A7" s="23"/>
-      <c r="B7" s="24" t="s">
+      <c r="A7" s="24"/>
+      <c r="B7" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24" t="s">
+      <c r="D7" s="25"/>
+      <c r="E7" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="F7" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="G7" s="24" t="s">
+      <c r="G7" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="24">
-        <v>0</v>
-      </c>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24">
+      <c r="H7" s="25">
+        <v>0</v>
+      </c>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25">
         <v>0.6</v>
       </c>
-      <c r="K7" s="24">
+      <c r="K7" s="25">
         <v>0.8</v>
       </c>
-      <c r="L7" s="24" t="s">
+      <c r="L7" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="M7" s="27" t="s">
+      <c r="M7" s="28" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1" spans="1:13">
-      <c r="A8" s="23"/>
-      <c r="B8" s="24" t="s">
+      <c r="A8" s="24"/>
+      <c r="B8" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24" t="s">
+      <c r="D8" s="25"/>
+      <c r="E8" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="24">
-        <v>0</v>
-      </c>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24">
+      <c r="H8" s="25">
+        <v>0</v>
+      </c>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25">
         <v>0.6</v>
       </c>
-      <c r="K8" s="24">
+      <c r="K8" s="25">
         <v>0.8</v>
       </c>
-      <c r="L8" s="24" t="s">
+      <c r="L8" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="M8" s="27" t="s">
+      <c r="M8" s="28" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1" spans="1:13">
-      <c r="A9" s="23"/>
-      <c r="B9" s="24" t="s">
+      <c r="A9" s="24"/>
+      <c r="B9" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24" t="s">
+      <c r="D9" s="25"/>
+      <c r="E9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="G9" s="24" t="s">
+      <c r="G9" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="24">
-        <v>0</v>
-      </c>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24">
+      <c r="H9" s="25">
+        <v>0</v>
+      </c>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25">
         <v>0.7</v>
       </c>
-      <c r="K9" s="24">
+      <c r="K9" s="25">
         <v>0.9</v>
       </c>
-      <c r="L9" s="24" t="s">
+      <c r="L9" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="M9" s="27" t="s">
+      <c r="M9" s="28" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:13">
-      <c r="A10" s="23"/>
-      <c r="B10" s="24" t="s">
+      <c r="A10" s="24"/>
+      <c r="B10" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24" t="s">
+      <c r="D10" s="25"/>
+      <c r="E10" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="24" t="s">
+      <c r="G10" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="24">
-        <v>0</v>
-      </c>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24">
+      <c r="H10" s="25">
+        <v>0</v>
+      </c>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25">
         <v>0.7</v>
       </c>
-      <c r="K10" s="24">
+      <c r="K10" s="25">
         <v>0.9</v>
       </c>
-      <c r="L10" s="24" t="s">
+      <c r="L10" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="M10" s="27" t="s">
+      <c r="M10" s="28" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1" spans="1:13">
-      <c r="A11" s="23"/>
-      <c r="B11" s="24" t="s">
+      <c r="A11" s="24"/>
+      <c r="B11" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24" t="s">
+      <c r="D11" s="25"/>
+      <c r="E11" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="F11" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="G11" s="24" t="s">
+      <c r="G11" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="24">
-        <v>0</v>
-      </c>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24">
+      <c r="H11" s="25">
+        <v>0</v>
+      </c>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25">
         <v>0.7</v>
       </c>
-      <c r="K11" s="24">
+      <c r="K11" s="25">
         <v>0.9</v>
       </c>
-      <c r="L11" s="24" t="s">
+      <c r="L11" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="M11" s="27" t="s">
+      <c r="M11" s="28" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1" spans="1:13">
-      <c r="A12" s="23"/>
-      <c r="B12" s="24" t="s">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24" t="s">
+      <c r="D12" s="25"/>
+      <c r="E12" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="24" t="s">
+      <c r="F12" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="G12" s="24" t="s">
+      <c r="G12" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="24">
-        <v>0</v>
-      </c>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24">
+      <c r="H12" s="25">
+        <v>0</v>
+      </c>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25">
         <v>0.7</v>
       </c>
-      <c r="K12" s="24">
+      <c r="K12" s="25">
         <v>0.9</v>
       </c>
-      <c r="L12" s="24" t="s">
+      <c r="L12" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="M12" s="27" t="s">
+      <c r="M12" s="28" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1" spans="1:13">
-      <c r="A13" s="23"/>
-      <c r="B13" s="24" t="s">
+      <c r="A13" s="24"/>
+      <c r="B13" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24" t="s">
+      <c r="D13" s="25"/>
+      <c r="E13" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="24" t="s">
+      <c r="F13" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="24" t="s">
+      <c r="G13" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="24">
-        <v>0</v>
-      </c>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24">
+      <c r="H13" s="25">
+        <v>0</v>
+      </c>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25">
         <v>0.7</v>
       </c>
-      <c r="K13" s="24">
+      <c r="K13" s="25">
         <v>0.9</v>
       </c>
-      <c r="L13" s="24" t="s">
+      <c r="L13" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="M13" s="27" t="s">
+      <c r="M13" s="28" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1" spans="1:13">
-      <c r="A14" s="23"/>
-      <c r="B14" s="24" t="s">
+      <c r="A14" s="24"/>
+      <c r="B14" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24" t="s">
+      <c r="D14" s="25"/>
+      <c r="E14" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24" t="s">
+      <c r="F14" s="25"/>
+      <c r="G14" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="H14" s="24">
-        <v>0</v>
-      </c>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24">
+      <c r="H14" s="25">
+        <v>0</v>
+      </c>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25">
         <v>0.4</v>
       </c>
-      <c r="K14" s="24">
+      <c r="K14" s="25">
         <v>0.5</v>
       </c>
-      <c r="L14" s="24"/>
-      <c r="M14" s="27"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="28"/>
     </row>
     <row r="15" ht="17" customHeight="1" spans="1:13">
-      <c r="A15" s="23"/>
-      <c r="B15" s="24" t="s">
+      <c r="A15" s="24"/>
+      <c r="B15" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24" t="s">
+      <c r="F15" s="25"/>
+      <c r="G15" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="24">
-        <v>0</v>
-      </c>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24">
-        <v>0</v>
-      </c>
-      <c r="K15" s="24">
-        <v>0</v>
-      </c>
-      <c r="L15" s="24"/>
-      <c r="M15" s="27"/>
+      <c r="H15" s="25">
+        <v>0</v>
+      </c>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25">
+        <v>0</v>
+      </c>
+      <c r="K15" s="25">
+        <v>0</v>
+      </c>
+      <c r="L15" s="25"/>
+      <c r="M15" s="28"/>
     </row>
     <row r="16" ht="17" customHeight="1" spans="1:13">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24" t="s">
+      <c r="A16" s="24"/>
+      <c r="B16" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24" t="s">
+      <c r="F16" s="25"/>
+      <c r="G16" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="H16" s="24">
-        <v>0</v>
-      </c>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24">
-        <v>0</v>
-      </c>
-      <c r="K16" s="24">
-        <v>0</v>
-      </c>
-      <c r="L16" s="24"/>
-      <c r="M16" s="27"/>
+      <c r="H16" s="25">
+        <v>0</v>
+      </c>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25">
+        <v>0</v>
+      </c>
+      <c r="K16" s="25">
+        <v>0</v>
+      </c>
+      <c r="L16" s="25"/>
+      <c r="M16" s="28"/>
     </row>
     <row r="17" ht="34" customHeight="1" spans="1:13">
-      <c r="A17" s="23"/>
-      <c r="B17" s="24" t="s">
+      <c r="A17" s="24"/>
+      <c r="B17" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="D17" s="24" t="s">
+      <c r="D17" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24" t="s">
+      <c r="F17" s="25"/>
+      <c r="G17" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="H17" s="24">
-        <v>0</v>
-      </c>
-      <c r="I17" s="24" t="s">
+      <c r="H17" s="25">
+        <v>0</v>
+      </c>
+      <c r="I17" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="J17" s="24">
-        <v>0</v>
-      </c>
-      <c r="K17" s="24">
-        <v>0</v>
-      </c>
-      <c r="L17" s="24"/>
-      <c r="M17" s="27"/>
+      <c r="J17" s="25">
+        <v>0</v>
+      </c>
+      <c r="K17" s="25">
+        <v>0</v>
+      </c>
+      <c r="L17" s="25"/>
+      <c r="M17" s="28"/>
     </row>
     <row r="18" ht="17" customHeight="1" spans="1:13">
-      <c r="A18" s="23"/>
-      <c r="B18" s="24" t="s">
+      <c r="A18" s="24"/>
+      <c r="B18" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C18" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24" t="s">
+      <c r="D18" s="25"/>
+      <c r="E18" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F18" s="24" t="s">
+      <c r="F18" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="G18" s="24" t="s">
+      <c r="G18" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="H18" s="24">
-        <v>0</v>
-      </c>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24">
-        <v>0</v>
-      </c>
-      <c r="K18" s="24">
-        <v>0</v>
-      </c>
-      <c r="L18" s="24"/>
-      <c r="M18" s="27"/>
+      <c r="H18" s="25">
+        <v>0</v>
+      </c>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25">
+        <v>0</v>
+      </c>
+      <c r="K18" s="25">
+        <v>0</v>
+      </c>
+      <c r="L18" s="25"/>
+      <c r="M18" s="28"/>
     </row>
     <row r="19" ht="17" customHeight="1" spans="1:13">
-      <c r="A19" s="23"/>
-      <c r="B19" s="24" t="s">
+      <c r="A19" s="24"/>
+      <c r="B19" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="C19" s="24" t="s">
+      <c r="C19" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="D19" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24" t="s">
+      <c r="F19" s="25"/>
+      <c r="G19" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="H19" s="24">
-        <v>0</v>
-      </c>
-      <c r="I19" s="24" t="s">
+      <c r="H19" s="25">
+        <v>0</v>
+      </c>
+      <c r="I19" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="J19" s="24">
-        <v>0</v>
-      </c>
-      <c r="K19" s="24">
-        <v>0</v>
-      </c>
-      <c r="L19" s="24"/>
-      <c r="M19" s="27"/>
+      <c r="J19" s="25">
+        <v>0</v>
+      </c>
+      <c r="K19" s="25">
+        <v>0</v>
+      </c>
+      <c r="L19" s="25"/>
+      <c r="M19" s="28"/>
     </row>
     <row r="20" ht="17" customHeight="1" spans="1:13">
-      <c r="A20" s="23"/>
-      <c r="B20" s="24" t="s">
+      <c r="A20" s="24"/>
+      <c r="B20" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D20" s="24" t="s">
+      <c r="D20" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24" t="s">
+      <c r="F20" s="25"/>
+      <c r="G20" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="H20" s="24">
+      <c r="H20" s="25">
         <v>-200</v>
       </c>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24">
-        <v>0</v>
-      </c>
-      <c r="K20" s="24">
-        <v>0</v>
-      </c>
-      <c r="L20" s="24"/>
-      <c r="M20" s="27"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25">
+        <v>0</v>
+      </c>
+      <c r="K20" s="25">
+        <v>0</v>
+      </c>
+      <c r="L20" s="25"/>
+      <c r="M20" s="28"/>
     </row>
     <row r="21" ht="17" customHeight="1" spans="1:13">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26" t="s">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C21" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="D21" s="26" t="s">
+      <c r="D21" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="E21" s="26" t="s">
+      <c r="E21" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26" t="s">
+      <c r="F21" s="27"/>
+      <c r="G21" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="H21" s="26">
-        <v>0</v>
-      </c>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26">
-        <v>0</v>
-      </c>
-      <c r="K21" s="26">
-        <v>0</v>
-      </c>
-      <c r="L21" s="26"/>
-      <c r="M21" s="28"/>
+      <c r="H21" s="27">
+        <v>0</v>
+      </c>
+      <c r="I21" s="27"/>
+      <c r="J21" s="27">
+        <v>0</v>
+      </c>
+      <c r="K21" s="27">
+        <v>0</v>
+      </c>
+      <c r="L21" s="27"/>
+      <c r="M21" s="29"/>
     </row>
     <row r="22" spans="2:11">
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="E22" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="G22" s="22" t="s">
+      <c r="G22" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="H22" s="22">
+      <c r="H22" s="23">
         <v>1</v>
       </c>
-      <c r="J22" s="22">
-        <v>0</v>
-      </c>
-      <c r="K22" s="22">
+      <c r="J22" s="23">
+        <v>0</v>
+      </c>
+      <c r="K22" s="23">
         <v>0</v>
       </c>
     </row>
@@ -2650,7 +2653,7 @@
       <c r="A10" s="8"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
-      <c r="D10" s="13"/>
+      <c r="D10" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2664,13 +2667,13 @@
   <dimension ref="A1:G15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13" style="14" customWidth="1"/>
-    <col min="2" max="2" width="16" style="14" customWidth="1"/>
-    <col min="3" max="3" width="18" style="14" customWidth="1"/>
-    <col min="4" max="4" width="22" style="14" customWidth="1"/>
-    <col min="5" max="5" width="23" style="14" customWidth="1"/>
-    <col min="6" max="7" width="58" style="14" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="14" customWidth="1"/>
+    <col min="1" max="1" width="13" style="15" customWidth="1"/>
+    <col min="2" max="2" width="16" style="15" customWidth="1"/>
+    <col min="3" max="3" width="18" style="15" customWidth="1"/>
+    <col min="4" max="4" width="22" style="15" customWidth="1"/>
+    <col min="5" max="5" width="23" style="15" customWidth="1"/>
+    <col min="6" max="7" width="58" style="15" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1" spans="1:7">
@@ -2743,200 +2746,200 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="15"/>
-      <c r="B4" s="16" t="s">
+      <c r="A4" s="16"/>
+      <c r="B4" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="17">
         <v>75</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="20">
         <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="15"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16">
+      <c r="A5" s="16"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17">
         <v>60</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="20">
         <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="15"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16">
+      <c r="A6" s="16"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17">
         <v>50</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="20">
         <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="15"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16">
+      <c r="A7" s="16"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17">
         <v>45</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="20">
         <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="15"/>
-      <c r="B8" s="16" t="s">
+      <c r="A8" s="16"/>
+      <c r="B8" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="17">
         <v>10</v>
       </c>
-      <c r="F8" s="16">
-        <v>-1</v>
-      </c>
-      <c r="G8" s="19">
+      <c r="F8" s="17">
+        <v>-1</v>
+      </c>
+      <c r="G8" s="20">
         <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="15"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16">
+      <c r="A9" s="16"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17">
         <v>25</v>
       </c>
-      <c r="F9" s="16">
-        <v>-1</v>
-      </c>
-      <c r="G9" s="19">
+      <c r="F9" s="17">
+        <v>-1</v>
+      </c>
+      <c r="G9" s="20">
         <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="15"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16">
+      <c r="A10" s="16"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17">
         <v>35</v>
       </c>
-      <c r="F10" s="16">
-        <v>-1</v>
-      </c>
-      <c r="G10" s="19">
+      <c r="F10" s="17">
+        <v>-1</v>
+      </c>
+      <c r="G10" s="20">
         <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="15"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16">
+      <c r="A11" s="16"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17">
         <v>40</v>
       </c>
-      <c r="F11" s="16">
-        <v>-1</v>
-      </c>
-      <c r="G11" s="19">
+      <c r="F11" s="17">
+        <v>-1</v>
+      </c>
+      <c r="G11" s="20">
         <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="15"/>
-      <c r="B12" s="16" t="s">
+      <c r="A12" s="16"/>
+      <c r="B12" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="17">
         <v>15</v>
       </c>
-      <c r="F12" s="16">
-        <v>-1</v>
-      </c>
-      <c r="G12" s="19">
+      <c r="F12" s="17">
+        <v>-1</v>
+      </c>
+      <c r="G12" s="20">
         <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="15"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16">
+      <c r="A13" s="16"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17">
         <v>15</v>
       </c>
-      <c r="F13" s="16">
-        <v>-1</v>
-      </c>
-      <c r="G13" s="19">
+      <c r="F13" s="17">
+        <v>-1</v>
+      </c>
+      <c r="G13" s="20">
         <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="15"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16">
+      <c r="A14" s="16"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17">
         <v>15</v>
       </c>
-      <c r="F14" s="16">
-        <v>-1</v>
-      </c>
-      <c r="G14" s="19">
+      <c r="F14" s="17">
+        <v>-1</v>
+      </c>
+      <c r="G14" s="20">
         <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="17"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18">
+      <c r="A15" s="18"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19">
         <v>15</v>
       </c>
-      <c r="F15" s="18">
-        <v>-1</v>
-      </c>
-      <c r="G15" s="20">
+      <c r="F15" s="19">
+        <v>-1</v>
+      </c>
+      <c r="G15" s="21">
         <v>-1</v>
       </c>
     </row>
@@ -3126,7 +3129,7 @@
       <c r="F9" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="13" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3141,7 +3144,7 @@
       <c r="F10" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="13" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3156,7 +3159,7 @@
       <c r="F11" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="13" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3354,7 +3357,7 @@
       <c r="F23" s="9">
         <v>-1</v>
       </c>
-      <c r="G23" s="13">
+      <c r="G23" s="14">
         <v>-1</v>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15160" activeTab="3"/>
+    <workbookView windowHeight="15160" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="action" sheetId="1" r:id="rId1"/>
@@ -2602,7 +2602,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="12">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2630,7 +2630,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4">

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15160" activeTab="1"/>
+    <workbookView windowHeight="15160"/>
   </bookViews>
   <sheets>
     <sheet name="action" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="158">
   <si>
     <t>##var</t>
   </si>
@@ -460,6 +460,12 @@
   </si>
   <si>
     <t>0|0|0|0|1|1|1|1|1|1|2|2|2|2|2|2|3|3|3|3|3</t>
+  </si>
+  <si>
+    <t>0|0|0|0|0|0|0|1|1|1|1|1|1|1|1|1|1|1|1</t>
+  </si>
+  <si>
+    <t>0|0|0|0|0|1|1|1|1|1|1|2|2|2|2|2|2|3|3|3|3</t>
   </si>
   <si>
     <t>passive</t>
@@ -1245,7 +1251,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="49" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="49" applyBorder="1" applyAlignment="1">
@@ -3127,10 +3133,10 @@
         <v>1</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -3142,10 +3148,10 @@
         <v>1</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -3160,19 +3166,19 @@
         <v>145</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="6"/>
       <c r="B12" s="7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E12" s="7">
         <v>1</v>
@@ -3232,13 +3238,13 @@
     <row r="16" spans="1:7">
       <c r="A16" s="6"/>
       <c r="B16" s="7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E16" s="7">
         <v>1</v>
@@ -3298,13 +3304,13 @@
     <row r="20" spans="1:7">
       <c r="A20" s="6"/>
       <c r="B20" s="7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E20" s="7">
         <v>1</v>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15160"/>
+    <workbookView windowHeight="15160" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="action" sheetId="1" r:id="rId1"/>
@@ -3049,7 +3049,7 @@
         <v>142</v>
       </c>
       <c r="E4" s="7">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F4" s="7">
         <v>-1</v>
@@ -3064,7 +3064,7 @@
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F5" s="7">
         <v>-1</v>
@@ -3079,7 +3079,7 @@
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F6" s="7">
         <v>-1</v>
@@ -3094,7 +3094,7 @@
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F7" s="7">
         <v>-1</v>
@@ -3115,7 +3115,7 @@
         <v>144</v>
       </c>
       <c r="E8" s="7">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>145</v>
@@ -3130,7 +3130,7 @@
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>147</v>
@@ -3145,7 +3145,7 @@
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>147</v>
@@ -3160,7 +3160,7 @@
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>145</v>
@@ -3181,7 +3181,7 @@
         <v>151</v>
       </c>
       <c r="E12" s="7">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F12" s="7">
         <v>-1</v>
@@ -3196,7 +3196,7 @@
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F13" s="7">
         <v>-1</v>
@@ -3211,7 +3211,7 @@
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F14" s="7">
         <v>-1</v>
@@ -3226,7 +3226,7 @@
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F15" s="7">
         <v>-1</v>
@@ -3247,7 +3247,7 @@
         <v>154</v>
       </c>
       <c r="E16" s="7">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F16" s="7">
         <v>-1</v>
@@ -3262,7 +3262,7 @@
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F17" s="7">
         <v>-1</v>
@@ -3277,7 +3277,7 @@
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F18" s="7">
         <v>-1</v>
@@ -3292,7 +3292,7 @@
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F19" s="7">
         <v>-1</v>
@@ -3313,7 +3313,7 @@
         <v>157</v>
       </c>
       <c r="E20" s="7">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F20" s="7">
         <v>-1</v>
@@ -3328,7 +3328,7 @@
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F21" s="7">
         <v>-1</v>
@@ -3343,7 +3343,7 @@
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F22" s="7">
         <v>-1</v>
@@ -3358,7 +3358,7 @@
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F23" s="9">
         <v>-1</v>

--- a/GourmetProject/GameConfig/Datas/action.xlsx
+++ b/GourmetProject/GameConfig/Datas/action.xlsx
@@ -3130,7 +3130,7 @@
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>147</v>
@@ -3145,7 +3145,7 @@
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>147</v>
@@ -3160,7 +3160,7 @@
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>145</v>
